--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27316"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10114"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="609" documentId="6_{07DD5C5E-4B7E-564D-9FFA-3C28EE9E5650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26D99028-58D3-457E-93E3-703616ED5CF6}"/>
+  <xr:revisionPtr revIDLastSave="705" documentId="6_{07DD5C5E-4B7E-564D-9FFA-3C28EE9E5650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8969198F-7CBC-B540-B609-55EDE1F9B34F}"/>
   <bookViews>
-    <workbookView xWindow="34580" yWindow="-5960" windowWidth="41380" windowHeight="20360" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="34580" yWindow="-5960" windowWidth="41380" windowHeight="20360" activeTab="1" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="273">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -164,6 +164,15 @@
     <t>Flags active (skips)</t>
   </si>
   <si>
+    <t>M1 subspecies</t>
+  </si>
+  <si>
+    <t>M1 species</t>
+  </si>
+  <si>
+    <t>M1 genus</t>
+  </si>
+  <si>
     <t>_ProjectKaskan, (Unpublished)</t>
   </si>
   <si>
@@ -320,6 +329,9 @@
     <t>summary to check more precise areas from ProjectKaskan</t>
   </si>
   <si>
+    <t>COMMON NAMES</t>
+  </si>
+  <si>
     <t>Chen, Z., &amp; Wiens, J. J. (2020). The origins of acoustic communication in vertebrates. Nature Communications, 11(1), 369. https://doi.org/10.1038/s41467-020-14356-3</t>
   </si>
   <si>
@@ -716,6 +728,9 @@
     <t>Figure 2 Top Left</t>
   </si>
   <si>
+    <t>area data not species</t>
+  </si>
+  <si>
     <t>Table 1-a</t>
   </si>
   <si>
@@ -728,6 +743,9 @@
     <t>Table 7</t>
   </si>
   <si>
+    <t>named in two rows (only brain and body anyway)</t>
+  </si>
+  <si>
     <t>Table S2</t>
   </si>
   <si>
@@ -761,6 +779,9 @@
     <t>SupplementaryTable1</t>
   </si>
   <si>
+    <t>individuals</t>
+  </si>
+  <si>
     <t>SupplementaryTable2</t>
   </si>
   <si>
@@ -797,9 +818,6 @@
     <t>--&gt; Species update</t>
   </si>
   <si>
-    <t>if shorthand speces names used, can update based on heading, note, text</t>
-  </si>
-  <si>
     <t>--&gt; Species note</t>
   </si>
   <si>
@@ -809,9 +827,6 @@
     <t>--&gt; Species correction</t>
   </si>
   <si>
-    <t>add a column to correct any errors in species names (e.g., misidentified or combined different species of same genus)</t>
-  </si>
-  <si>
     <t>--&gt; Corrections</t>
   </si>
   <si>
@@ -861,13 +876,19 @@
   </si>
   <si>
     <t xml:space="preserve">Ref last </t>
+  </si>
+  <si>
+    <t>if there are typos or shorthand speces names used, can update based on heading, note, text</t>
+  </si>
+  <si>
+    <t>add a column to correct any errors in species designations (e.g., misidentified or combined different species of same genus)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -978,7 +999,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
@@ -1005,8 +1026,7 @@
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1218,12 +1238,12 @@
         </row>
         <row r="37">
           <cell r="A37" t="str">
-            <v>10.3389%2Ffnhum.2013.00424.ReadMe.md</v>
+            <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38" t="str">
-            <v>10.3389%2Ffnhum.2013.00424.tsv</v>
+            <v>10.3389%2Ffnhum.2013.00424.ReadMe.md</v>
           </cell>
         </row>
         <row r="39">
@@ -1258,9 +1278,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1298,7 +1318,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1404,7 +1424,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1546,7 +1566,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1555,41 +1575,38 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AH48"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
+  <dimension ref="A1:AK48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="24.625" customWidth="1"/>
-    <col min="2" max="2" width="23.75" style="9" customWidth="1"/>
-    <col min="3" max="3" width="15" style="9" customWidth="1"/>
-    <col min="4" max="4" width="10.625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="5.75" style="9" customWidth="1"/>
-    <col min="6" max="6" width="8.875" style="9" customWidth="1"/>
-    <col min="7" max="7" width="25.5" customWidth="1"/>
-    <col min="8" max="8" width="19.5" customWidth="1"/>
-    <col min="9" max="9" width="16.125" customWidth="1"/>
-    <col min="10" max="10" width="31.25" customWidth="1"/>
-    <col min="11" max="11" width="48.25" customWidth="1"/>
-    <col min="12" max="13" width="14.125" customWidth="1"/>
-    <col min="14" max="14" width="41.25" customWidth="1"/>
-    <col min="15" max="15" width="49.125" customWidth="1"/>
-    <col min="16" max="19" width="14.125" customWidth="1"/>
-    <col min="20" max="20" width="13.875" customWidth="1"/>
-    <col min="21" max="21" width="12.625" customWidth="1"/>
-    <col min="22" max="22" width="22.125" customWidth="1"/>
-    <col min="23" max="23" width="14.375" customWidth="1"/>
-    <col min="24" max="24" width="15.375" customWidth="1"/>
+    <col min="1" max="1" width="2.5" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" style="9" customWidth="1"/>
+    <col min="3" max="6" width="2.1640625" style="9" customWidth="1"/>
+    <col min="7" max="8" width="2.1640625" customWidth="1"/>
+    <col min="9" max="9" width="17.1640625" customWidth="1"/>
+    <col min="10" max="10" width="31.1640625" customWidth="1"/>
+    <col min="11" max="11" width="46.5" customWidth="1"/>
+    <col min="12" max="13" width="14.1640625" customWidth="1"/>
+    <col min="14" max="14" width="41.1640625" customWidth="1"/>
+    <col min="15" max="15" width="49.1640625" customWidth="1"/>
+    <col min="16" max="19" width="14.1640625" customWidth="1"/>
+    <col min="20" max="20" width="13.83203125" customWidth="1"/>
+    <col min="21" max="21" width="12.6640625" customWidth="1"/>
+    <col min="22" max="22" width="22.1640625" customWidth="1"/>
+    <col min="23" max="23" width="14.33203125" customWidth="1"/>
+    <col min="24" max="24" width="15.33203125" customWidth="1"/>
     <col min="25" max="25" width="22" customWidth="1"/>
-    <col min="26" max="26" width="11.125" customWidth="1"/>
+    <col min="26" max="26" width="11.1640625" customWidth="1"/>
     <col min="27" max="27" width="5" customWidth="1"/>
     <col min="28" max="28" width="7.5" customWidth="1"/>
-    <col min="29" max="29" width="10.625" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" customWidth="1"/>
     <col min="30" max="30" width="6.5" customWidth="1"/>
     <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="32" width="16.75" customWidth="1"/>
-    <col min="33" max="33" width="14.75" customWidth="1"/>
+    <col min="32" max="34" width="10.83203125" customWidth="1"/>
+    <col min="35" max="35" width="12.5" customWidth="1"/>
+    <col min="36" max="36" width="2.83203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" s="6" customFormat="1">
+    <row r="1" spans="1:37" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1692,10 +1709,19 @@
       <c r="AH1" s="6" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="2" spans="1:34">
+      <c r="AI1" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B2" s="7" t="str">
         <f t="shared" ref="B2" si="0">C2 &amp; IF(D2&lt;&gt;"", "_" &amp; D2, "_") &amp; IF(E2&lt;&gt;"", "_" &amp; E2, "_") &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "")</f>
@@ -1732,7 +1758,7 @@
       </c>
       <c r="L2" s="3"/>
       <c r="M2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="N2" t="str" cm="1">
         <f t="array" ref="N2">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K2, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -1743,33 +1769,33 @@
         <v>notfound</v>
       </c>
       <c r="P2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q2" s="7"/>
       <c r="R2" s="8"/>
       <c r="T2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="U2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="X2" s="7"/>
       <c r="Y2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="Z2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AD2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AE2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B3" s="7" t="str">
         <f t="shared" ref="B3" si="3">C3 &amp; IF(D3&lt;&gt;"", "_" &amp; D3, "_") &amp; IF(E3&lt;&gt;"", "_" &amp; E3, "_") &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "")</f>
@@ -1791,15 +1817,15 @@
         <v>2019</v>
       </c>
       <c r="G3" t="str">
-        <f>_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
+        <f t="shared" ref="G3:G37" si="5">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
         <v>10.1093/jmammal/gyz043</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="J3" s="3" t="str">
-        <f t="shared" ref="J3:J44" si="5">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
+        <f t="shared" ref="J3:J44" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
       <c r="K3" s="21" t="str">
@@ -1807,10 +1833,10 @@
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="M3" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" ref="N3">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K3, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -1821,83 +1847,89 @@
         <v>notfound</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="Q3" s="9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="R3" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="S3" t="str">
         <f>IF(R3="N", Q3, "write file name")</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
       <c r="T3" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="U3" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V3" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X3" s="7"/>
       <c r="Y3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="Z3" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AD3" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="AE3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" ht="17.100000000000001" customHeight="1">
+        <v>44</v>
+      </c>
+      <c r="AI3">
+        <v>17</v>
+      </c>
+      <c r="AK3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B4" s="7" t="str">
-        <f t="shared" ref="B4:B44" si="6">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
+        <f t="shared" ref="B4:B44" si="7">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="C4" s="9" t="str">
-        <f t="shared" ref="C4:C44" si="7">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C4:C44" si="8">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
         <v>Caspar</v>
       </c>
       <c r="D4" s="9" t="str">
-        <f t="shared" ref="D4:D44" si="8">IF(ISNUMBER(FIND("&amp;", A4)),
+        <f t="shared" ref="D4:D44" si="9">IF(ISNUMBER(FIND("&amp;", A4)),
     IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=3, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E4" s="9" t="str">
-        <f t="shared" ref="E4:E44" si="9">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+        <f t="shared" ref="E4:E44" si="10">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
         <v>2022</v>
       </c>
       <c r="G4" t="str">
-        <f>_xlfn.TEXTAFTER(A4,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J4" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="K4" s="3" t="str">
-        <f t="shared" ref="K4:K44" si="10">IF(ISBLANK(H4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K4:K44" si="11">IF(ISBLANK(H4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="L4" s="3"/>
       <c r="M4" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N4" t="str" cm="1">
         <f t="array" ref="N4">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K4, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -1908,84 +1940,90 @@
         <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
       </c>
       <c r="P4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q4" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="R4" t="s">
+        <v>62</v>
+      </c>
+      <c r="S4" t="s">
+        <v>63</v>
+      </c>
+      <c r="T4" t="s">
+        <v>64</v>
+      </c>
+      <c r="U4" t="s">
+        <v>53</v>
+      </c>
+      <c r="V4" t="s">
+        <v>65</v>
+      </c>
+      <c r="W4" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="X4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>70</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>71</v>
+      </c>
+      <c r="AI4">
+        <v>7</v>
+      </c>
+      <c r="AK4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
         <v>58</v>
       </c>
-      <c r="R4" t="s">
-        <v>59</v>
-      </c>
-      <c r="S4" t="s">
-        <v>60</v>
-      </c>
-      <c r="T4" t="s">
-        <v>61</v>
-      </c>
-      <c r="U4" t="s">
-        <v>50</v>
-      </c>
-      <c r="V4" t="s">
-        <v>62</v>
-      </c>
-      <c r="W4" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="X4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="Y4" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z4" t="s">
-        <v>66</v>
-      </c>
-      <c r="AD4" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34">
-      <c r="A5" t="s">
-        <v>55</v>
-      </c>
       <c r="B5" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="C5" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Caspar</v>
       </c>
       <c r="D5" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E5" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2022</v>
       </c>
       <c r="G5" t="str">
-        <f>_xlfn.TEXTAFTER(A5,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="J5" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="K5" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="L5" s="12"/>
       <c r="M5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N5" t="str" cm="1">
         <f t="array" ref="N5">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K5, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -1996,82 +2034,88 @@
         <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
       </c>
       <c r="P5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="R5" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="S5" t="str">
         <f>IF(R5="N", Q5, "write file name")</f>
         <v>elife-77875-supp3-v1.xlsx</v>
       </c>
       <c r="T5" t="s">
+        <v>74</v>
+      </c>
+      <c r="U5" t="s">
+        <v>53</v>
+      </c>
+      <c r="V5" t="s">
+        <v>75</v>
+      </c>
+      <c r="W5" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="X5" s="9" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE5" t="s">
         <v>71</v>
       </c>
-      <c r="U5" t="s">
-        <v>50</v>
-      </c>
-      <c r="V5" t="s">
-        <v>72</v>
-      </c>
-      <c r="W5" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="X5" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y5" t="s">
-        <v>75</v>
-      </c>
-      <c r="Z5" t="s">
-        <v>53</v>
-      </c>
-      <c r="AE5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="6" spans="1:34">
+      <c r="AI5">
+        <v>5</v>
+      </c>
+      <c r="AK5">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B6" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Changizi__2001</v>
       </c>
       <c r="C6" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Changizi</v>
       </c>
       <c r="D6" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E6" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G6" t="str">
-        <f>_xlfn.TEXTAFTER(A6,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1007/s004220000205</v>
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="J6" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Changizi__2001_Figure3</v>
       </c>
       <c r="K6" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="L6" s="12"/>
       <c r="M6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N6" t="str" cm="1">
         <f t="array" ref="N6">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K6, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2082,78 +2126,81 @@
         <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
       <c r="P6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q6" s="9" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="R6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S6" s="9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="T6" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="V6" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="W6" s="13"/>
       <c r="X6" s="9"/>
       <c r="Y6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="Z6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AD6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34">
+        <v>87</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="B7" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Chen_etal_2020</v>
       </c>
       <c r="C7" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Chen</v>
       </c>
       <c r="D7" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E7" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2020</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" t="str">
-        <f>_xlfn.TEXTAFTER(A7,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1038/s41467-020-14356-3</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="J7" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Chen_etal_2020_SupplementaryData3</v>
       </c>
       <c r="K7" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
       <c r="L7" s="3"/>
       <c r="M7" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N7" t="str" cm="1">
         <f t="array" ref="N7">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K7, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2164,88 +2211,94 @@
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
       </c>
       <c r="P7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="R7" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="S7" t="str">
         <f>IF(R7="N", Q7, "write file name")</f>
         <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
       <c r="T7" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U7" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V7" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="W7" s="8" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="X7" s="7"/>
       <c r="Y7" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="Z7" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AC7" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AD7" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="AE7" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34">
+        <v>96</v>
+      </c>
+      <c r="AI7">
+        <v>10</v>
+      </c>
+      <c r="AK7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="B8" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>DosSantos_etal_2017</v>
       </c>
       <c r="C8" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>DosSantos</v>
       </c>
       <c r="D8" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E8" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2017</v>
       </c>
       <c r="G8" t="str">
-        <f>_xlfn.TEXTAFTER(A8,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000452856</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J8" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="K8" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N8" t="str" cm="1">
         <f t="array" ref="N8">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K8, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2256,88 +2309,94 @@
         <v>10.1159%2F000452856_TableS1.tsv</v>
       </c>
       <c r="P8" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q8" s="9" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="R8" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S8" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="T8" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="U8" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="V8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="W8" s="8" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="X8" s="9"/>
       <c r="Y8" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Z8" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AA8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AB8" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AE8" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="AF8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34">
+        <v>109</v>
+      </c>
+      <c r="AI8">
+        <v>0</v>
+      </c>
+      <c r="AK8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="B9" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>DosSantos_etal_2020</v>
       </c>
       <c r="C9" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>DosSantos</v>
       </c>
       <c r="D9" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E9" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2020</v>
       </c>
       <c r="G9" t="str">
-        <f>_xlfn.TEXTAFTER(A9,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J9" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>DosSantos_etal_2020_Table1</v>
       </c>
       <c r="K9" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
       <c r="L9" s="3"/>
       <c r="M9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N9" t="str" cm="1">
         <f t="array" ref="N9">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K9, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2348,71 +2407,77 @@
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
       <c r="P9" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q9" s="14" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="R9" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S9" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="T9" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="U9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X9" s="7"/>
       <c r="Y9" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Z9" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="AA9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AB9" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AE9" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34">
+        <v>115</v>
+      </c>
+      <c r="AI9">
+        <v>4</v>
+      </c>
+      <c r="AK9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="B10" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Finlay_etal_2006</v>
       </c>
       <c r="C10" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Finlay</v>
       </c>
       <c r="D10" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E10" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2006</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" t="str">
-        <f>_xlfn.TEXTAFTER(A10,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="J10" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Finlay_etal_2006_Table6.1</v>
       </c>
       <c r="K10" s="3" t="str">
@@ -2421,7 +2486,7 @@
       </c>
       <c r="L10" s="3"/>
       <c r="M10" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="N10" t="str" cm="1">
         <f t="array" ref="N10">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K10, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2432,83 +2497,89 @@
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
       </c>
       <c r="P10" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q10" s="9" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="R10" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S10" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="T10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V10" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W10" s="8" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="X10" s="7"/>
       <c r="Y10" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="Z10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="AD10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="AE10" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34">
+        <v>44</v>
+      </c>
+      <c r="AI10">
+        <v>3</v>
+      </c>
+      <c r="AK10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B11" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Heffner_etal_1975</v>
       </c>
       <c r="C11" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Heffner</v>
       </c>
       <c r="D11" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E11" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1975</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" t="str">
-        <f>_xlfn.TEXTAFTER(A11,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000124401</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J11" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Heffner_etal_1975_TableI</v>
       </c>
       <c r="K11" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N11" t="str" cm="1">
         <f t="array" ref="N11">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K11, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2519,80 +2590,86 @@
         <v>10.1159%2F000124401_TableI.tsv</v>
       </c>
       <c r="P11" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q11" s="9" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="R11" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="T11" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U11" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V11" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="X11" s="7"/>
       <c r="Y11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="Z11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="AC11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="AE11" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34">
+        <v>44</v>
+      </c>
+      <c r="AI11">
+        <v>7</v>
+      </c>
+      <c r="AK11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B12" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Heffner_etal_1983</v>
       </c>
       <c r="C12" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Heffner</v>
       </c>
       <c r="D12" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E12" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1983</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" t="str">
-        <f>_xlfn.TEXTAFTER(A12,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000121494</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J12" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Heffner_etal_1983_TableI</v>
       </c>
       <c r="K12" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000121494_TableI</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N12" t="str" cm="1">
         <f t="array" ref="N12">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K12, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2603,7 +2680,7 @@
         <v>notfound</v>
       </c>
       <c r="P12" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="S12" t="str">
@@ -2611,62 +2688,62 @@
         <v>write file name</v>
       </c>
       <c r="T12" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U12" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X12" s="7"/>
       <c r="Y12" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="AE12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="AG12" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B13" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Heldstab_etal_2016</v>
       </c>
       <c r="C13" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Heldstab</v>
       </c>
       <c r="D13" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E13" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2016</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" t="str">
-        <f>_xlfn.TEXTAFTER(A13,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1038/srep24528</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J13" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Heldstab_etal_2016_TableS1</v>
       </c>
       <c r="K13" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N13" t="str" cm="1">
         <f t="array" ref="N13">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K13, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2677,7 +2754,7 @@
         <v>notfound</v>
       </c>
       <c r="P13" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="S13" t="str">
@@ -2685,58 +2762,58 @@
         <v>write file name</v>
       </c>
       <c r="T13" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U13" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X13" s="7"/>
       <c r="Y13" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AE13" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B14" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C14" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D14" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E14" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="G14" t="str">
-        <f>_xlfn.TEXTAFTER(A14,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J14" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
       <c r="K14" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000437413_Table1</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N14" t="str" cm="1">
         <f t="array" ref="N14">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K14, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2747,85 +2824,91 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P14" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q14" s="14" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="R14" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="T14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V14" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W14" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="X14" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="Y14" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE14" t="s">
+        <v>141</v>
+      </c>
+      <c r="AI14">
+        <v>9</v>
+      </c>
+      <c r="AK14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
         <v>136</v>
       </c>
-      <c r="Y14" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34">
-      <c r="A15" t="s">
-        <v>132</v>
-      </c>
       <c r="B15" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C15" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D15" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E15" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" t="str">
-        <f>_xlfn.TEXTAFTER(A15,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J15" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
       <c r="K15" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000437413_Table2</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N15" t="str" cm="1">
         <f t="array" ref="N15">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K15, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2836,85 +2919,91 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P15" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q15" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S15" t="s">
+        <v>144</v>
+      </c>
+      <c r="T15" t="s">
+        <v>64</v>
+      </c>
+      <c r="U15" t="s">
+        <v>53</v>
+      </c>
+      <c r="V15" t="s">
+        <v>65</v>
+      </c>
+      <c r="W15" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="S15" t="s">
-        <v>140</v>
-      </c>
-      <c r="T15" t="s">
-        <v>61</v>
-      </c>
-      <c r="U15" t="s">
-        <v>50</v>
-      </c>
-      <c r="V15" t="s">
-        <v>62</v>
-      </c>
-      <c r="W15" s="8" t="s">
-        <v>135</v>
-      </c>
       <c r="X15" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y15" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA15" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB15" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE15" t="s">
         <v>141</v>
       </c>
-      <c r="Y15" t="s">
-        <v>101</v>
-      </c>
-      <c r="AA15" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB15" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE15" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34">
+      <c r="AI15">
+        <v>9</v>
+      </c>
+      <c r="AK15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B16" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C16" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D16" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E16" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" t="str">
-        <f>_xlfn.TEXTAFTER(A16,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J16" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
       <c r="K16" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000437413_Table3</v>
       </c>
       <c r="L16" s="3"/>
       <c r="M16" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N16" t="str" cm="1">
         <f t="array" ref="N16">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K16, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2925,85 +3014,91 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P16" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q16" s="16" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="R16" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S16" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="T16" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U16" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V16" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W16" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="X16" s="7" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="Y16" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AA16" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AB16" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AE16" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31">
+        <v>141</v>
+      </c>
+      <c r="AI16">
+        <v>9</v>
+      </c>
+      <c r="AK16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B17" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C17" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D17" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E17" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" t="str">
-        <f>_xlfn.TEXTAFTER(A17,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J17" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
       <c r="K17" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000437413_Table4</v>
       </c>
       <c r="L17" s="3"/>
       <c r="M17" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N17" t="str" cm="1">
         <f t="array" ref="N17">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K17, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3014,85 +3109,91 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P17" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q17" s="14" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="R17" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S17" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="T17" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U17" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V17" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W17" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="X17" s="9" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="Y17" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AA17" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AB17" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AE17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31">
+        <v>141</v>
+      </c>
+      <c r="AI17">
+        <v>8</v>
+      </c>
+      <c r="AK17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B18" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C18" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D18" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E18" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" t="str">
-        <f>_xlfn.TEXTAFTER(A18,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J18" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
       <c r="K18" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000437413_Table5</v>
       </c>
       <c r="L18" s="3"/>
       <c r="M18" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N18" t="str" cm="1">
         <f t="array" ref="N18">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K18, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3103,85 +3204,91 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P18" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q18" s="14" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="R18" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S18" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="T18" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U18" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V18" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W18" s="8" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="X18" s="9" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="Y18" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="AA18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AB18" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AE18" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31">
+        <v>141</v>
+      </c>
+      <c r="AI18">
+        <v>9</v>
+      </c>
+      <c r="AK18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B19" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="C19" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D19" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E19" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2020</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" t="str">
-        <f>_xlfn.TEXTAFTER(A19,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="J19" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="K19" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
       <c r="L19" s="3"/>
       <c r="M19" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N19" t="str" cm="1">
         <f t="array" ref="N19">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K19, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3192,82 +3299,91 @@
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="P19" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q19" s="14" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="R19" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="T19" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U19" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V19" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="X19" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>163</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>164</v>
+      </c>
+      <c r="AI19">
+        <v>0</v>
+      </c>
+      <c r="AJ19">
+        <v>0</v>
+      </c>
+      <c r="AK19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
         <v>158</v>
       </c>
-      <c r="Y19" t="s">
-        <v>159</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" ht="18.95" customHeight="1">
-      <c r="A20" t="s">
-        <v>154</v>
-      </c>
       <c r="B20" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="C20" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D20" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E20" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2020</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" t="str">
-        <f>_xlfn.TEXTAFTER(A20,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="J20" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
       <c r="K20" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
       <c r="L20" s="3"/>
       <c r="M20" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N20" t="str" cm="1">
         <f t="array" ref="N20">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K20, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3278,81 +3394,90 @@
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="P20" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q20" s="14" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="R20" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S20" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="T20" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U20" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V20" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="X20" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="Y20" t="s">
+        <v>169</v>
+      </c>
+      <c r="AA20" t="s">
+        <v>107</v>
+      </c>
+      <c r="AB20" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE20" t="s">
         <v>164</v>
       </c>
-      <c r="Y20" t="s">
-        <v>165</v>
-      </c>
-      <c r="AA20" t="s">
-        <v>103</v>
-      </c>
-      <c r="AB20" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE20" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" ht="17.100000000000001" customHeight="1">
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B21" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="C21" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Iwaniuk</v>
       </c>
       <c r="D21" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E21" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G21" t="str">
-        <f>_xlfn.TEXTAFTER(A21,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J21" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Iwaniuk_etal_2001_Table1</v>
       </c>
       <c r="K21" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
       <c r="L21" s="3"/>
       <c r="M21" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="N21" t="str" cm="1">
         <f t="array" ref="N21">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K21, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3363,7 +3488,7 @@
         <v>notfound</v>
       </c>
       <c r="P21" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q21" s="14"/>
       <c r="S21" t="str">
@@ -3371,60 +3496,60 @@
         <v>write file name</v>
       </c>
       <c r="T21" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U21" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X21" s="11" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="Y21" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AE21" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="22" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="22" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A22" t="s">
-        <v>166</v>
-      </c>
       <c r="B22" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="C22" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Iwaniuk</v>
       </c>
       <c r="D22" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E22" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G22" t="str">
-        <f>_xlfn.TEXTAFTER(A22,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J22" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Iwaniuk_etal_2001_Table2</v>
       </c>
       <c r="K22" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
       <c r="L22" s="3"/>
       <c r="M22" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="N22" t="str" cm="1">
         <f t="array" ref="N22">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K22, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3435,7 +3560,7 @@
         <v>notfound</v>
       </c>
       <c r="P22" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q22" s="14"/>
       <c r="S22" t="str">
@@ -3443,60 +3568,60 @@
         <v>write file name</v>
       </c>
       <c r="T22" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U22" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="Y22" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AE22" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A23" t="s">
-        <v>166</v>
-      </c>
       <c r="B23" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="C23" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Iwaniuk</v>
       </c>
       <c r="D23" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E23" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G23" t="str">
-        <f>_xlfn.TEXTAFTER(A23,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="J23" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Iwaniuk_etal_2001_Table3</v>
       </c>
       <c r="K23" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
       <c r="L23" s="3"/>
       <c r="M23" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="N23" t="str" cm="1">
         <f t="array" ref="N23">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K23, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3507,7 +3632,7 @@
         <v>notfound</v>
       </c>
       <c r="P23" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q23" s="14"/>
       <c r="S23" t="str">
@@ -3515,60 +3640,60 @@
         <v>write file name</v>
       </c>
       <c r="T23" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U23" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Y23" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="AE23" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A24" t="s">
-        <v>166</v>
-      </c>
       <c r="B24" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="C24" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Iwaniuk</v>
       </c>
       <c r="D24" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E24" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G24" t="str">
-        <f>_xlfn.TEXTAFTER(A24,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J24" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Iwaniuk_etal_2001_Table4</v>
       </c>
       <c r="K24" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="L24" s="3"/>
       <c r="M24" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="N24" t="str" cm="1">
         <f t="array" ref="N24">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K24, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3579,7 +3704,7 @@
         <v>notfound</v>
       </c>
       <c r="P24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="S24" t="str">
@@ -3587,60 +3712,60 @@
         <v>write file name</v>
       </c>
       <c r="T24" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U24" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X24" s="11" t="s">
+        <v>177</v>
+      </c>
+      <c r="Y24" t="s">
         <v>173</v>
       </c>
-      <c r="Y24" t="s">
-        <v>169</v>
-      </c>
       <c r="AE24" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B25" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>JardimMesseder_etal_2017</v>
       </c>
       <c r="C25" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>JardimMesseder</v>
       </c>
       <c r="D25" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E25" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2017</v>
       </c>
       <c r="G25" t="str">
-        <f>_xlfn.TEXTAFTER(A25,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.3389/fnana.2017.00118</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J25" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>JardimMesseder_etal_2017_Table1</v>
       </c>
       <c r="K25" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
       <c r="L25" s="3"/>
       <c r="M25" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N25" t="str" cm="1">
         <f t="array" ref="N25">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K25, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3651,88 +3776,94 @@
         <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="P25" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q25" s="14" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="R25" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S25" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="T25" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U25" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V25" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W25" s="8" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="X25" s="7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="Y25" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="Z25" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AA25" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AB25" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="AE25" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31">
+        <v>183</v>
+      </c>
+      <c r="AI25">
+        <v>2</v>
+      </c>
+      <c r="AK25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B26" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="C26" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Kverkova</v>
       </c>
       <c r="D26" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E26" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2018</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" t="str">
-        <f>_xlfn.TEXTAFTER(A26,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J26" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="K26" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N26" t="str" cm="1">
         <f t="array" ref="N26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3743,83 +3874,89 @@
         <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="P26" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q26" s="14"/>
       <c r="R26" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S26" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="T26" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="U26" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W26" s="8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="X26" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>163</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>189</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI26">
+        <v>1</v>
+      </c>
+      <c r="AK26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
         <v>184</v>
       </c>
-      <c r="Y26" t="s">
-        <v>159</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31">
-      <c r="A27" t="s">
-        <v>180</v>
-      </c>
       <c r="B27" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="C27" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Kverkova</v>
       </c>
       <c r="D27" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E27" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2018</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" t="str">
-        <f>_xlfn.TEXTAFTER(A27,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J27" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="K27" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="N27" t="str" cm="1">
         <f t="array" ref="N27">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K27, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3830,83 +3967,89 @@
         <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="P27" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="Q27" s="14"/>
       <c r="R27" s="3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="S27" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="T27" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="U27" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V27" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="W27" s="8" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="X27" s="7" t="s">
+        <v>194</v>
+      </c>
+      <c r="Y27" t="s">
+        <v>169</v>
+      </c>
+      <c r="Z27" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB27" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE27" t="s">
         <v>190</v>
       </c>
-      <c r="Y27" t="s">
-        <v>165</v>
-      </c>
-      <c r="Z27" t="s">
-        <v>102</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31">
+      <c r="AI27">
+        <v>1</v>
+      </c>
+      <c r="AK27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B28" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>ManyPrimates__2022</v>
       </c>
       <c r="C28" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ManyPrimates</v>
       </c>
       <c r="D28" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v/>
       </c>
       <c r="E28" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2022</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" t="str">
-        <f>_xlfn.TEXTAFTER(A28,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.26451/abc.09.04.06.2022</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="12" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="J28" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="K28" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N28" t="str" cm="1">
         <f t="array" ref="N28">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K28, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3917,81 +4060,81 @@
         <v>notfound</v>
       </c>
       <c r="P28" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q28" s="14"/>
       <c r="S28" t="str">
-        <f t="shared" ref="S28:S33" si="11">IF(R28="N", Q28, "write file name")</f>
+        <f t="shared" ref="S28:S33" si="12">IF(R28="N", Q28, "write file name")</f>
         <v>write file name</v>
       </c>
       <c r="T28" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U28" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V28" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="W28" s="8" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="X28" s="7"/>
       <c r="Y28" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="Z28" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AC28" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="AE28" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="B29" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Powell_etal_2017</v>
       </c>
       <c r="C29" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Powell</v>
       </c>
       <c r="D29" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E29" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2017</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" t="str">
-        <f>_xlfn.TEXTAFTER(A29,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1098/rspb.2017.1765</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="J29" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="K29" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N29" t="str" cm="1">
         <f t="array" ref="N29">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K29, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4002,81 +4145,81 @@
         <v>notfound</v>
       </c>
       <c r="P29" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q29" s="14"/>
       <c r="S29" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>write file name</v>
       </c>
       <c r="T29" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="U29" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="V29" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="W29" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="X29" s="7"/>
       <c r="Y29" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="Z29" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="AC29" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="AE29" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="B30" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="C30" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Sherwood</v>
       </c>
       <c r="D30" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E30" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2004</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G30" t="str">
-        <f>_xlfn.TEXTAFTER(A30,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="J30" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="K30" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="L30" s="3"/>
       <c r="M30" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N30" t="str" cm="1">
         <f t="array" ref="N30">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K30, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4087,74 +4230,74 @@
         <v>notfound</v>
       </c>
       <c r="P30" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q30" s="14"/>
       <c r="S30" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>write file name</v>
       </c>
       <c r="T30" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U30" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="X30" s="7" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="Y30" t="s">
+        <v>210</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE30" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
         <v>206</v>
       </c>
-      <c r="Z30" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="1:31">
-      <c r="A31" t="s">
-        <v>202</v>
-      </c>
       <c r="B31" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="C31" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Sherwood</v>
       </c>
       <c r="D31" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E31" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2004</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="G31" t="str">
-        <f>_xlfn.TEXTAFTER(A31,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="J31" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="K31" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="L31" s="3"/>
       <c r="M31" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N31" t="str" cm="1">
         <f t="array" ref="N31">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K31, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4165,72 +4308,72 @@
         <v>notfound</v>
       </c>
       <c r="P31" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q31" s="14"/>
       <c r="S31" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>write file name</v>
       </c>
       <c r="T31" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U31" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="X31" s="11" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="Y31" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="Z31" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="AE31" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="32" spans="1:31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B32" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Winkler_etal_2021</v>
       </c>
       <c r="C32" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Winkler</v>
       </c>
       <c r="D32" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E32" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2021</v>
       </c>
       <c r="F32" s="7"/>
       <c r="G32" t="str">
-        <f>_xlfn.TEXTAFTER(A32,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.1080/09524622.2021.1905065</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="J32" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Winkler_etal_2021_Figure1</v>
       </c>
       <c r="K32" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="L32" s="3"/>
       <c r="M32" s="15" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="N32" t="str" cm="1">
         <f t="array" ref="N32">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K32, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4241,67 +4384,67 @@
         <v>notfound</v>
       </c>
       <c r="P32" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q32" s="14"/>
       <c r="S32" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>write file name</v>
       </c>
       <c r="T32" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="U32" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="X32" s="7"/>
       <c r="Y32" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="AE32" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="33" spans="1:31">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B33" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Young_etal_2013</v>
       </c>
       <c r="C33" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Young</v>
       </c>
       <c r="D33" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E33" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2013</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" t="str">
-        <f>_xlfn.TEXTAFTER(A33,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.3389/fncir.2013.00030</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J33" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Young_etal_2013_Table1</v>
       </c>
       <c r="K33" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
       <c r="L33" s="3"/>
       <c r="M33" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N33" t="str" cm="1">
         <f t="array" ref="N33">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K33, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4312,60 +4455,60 @@
         <v>notfound</v>
       </c>
       <c r="P33" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="Q33" s="14"/>
       <c r="S33" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>write file name</v>
       </c>
       <c r="T33" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U33" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="X33" s="7"/>
       <c r="Y33" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="AE33" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B34" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Mota_etal_2015</v>
+      </c>
+      <c r="C34" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v>Mota</v>
+      </c>
+      <c r="D34" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>etal</v>
+      </c>
+      <c r="E34" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v>2015</v>
+      </c>
+      <c r="G34" t="str">
+        <f t="shared" si="5"/>
+        <v>10.1126/science.aaa9101</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J34" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Mota_etal_2015</v>
-      </c>
-      <c r="C34" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Mota</v>
-      </c>
-      <c r="D34" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
-      </c>
-      <c r="E34" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v>2015</v>
-      </c>
-      <c r="G34" t="str">
-        <f>_xlfn.TEXTAFTER(A34,"https://doi.org/")</f>
-        <v>10.1126/science.aaa9101</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="J34" s="3" t="str">
-        <f t="shared" si="5"/>
         <v>Mota_etal_2015_TableS1</v>
       </c>
       <c r="K34" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="N34" t="str" cm="1">
@@ -4377,42 +4520,48 @@
         <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="P34" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI34">
+        <v>10</v>
+      </c>
+      <c r="AK34">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B35" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>HerculanoHouzel_etal_2013</v>
+      </c>
+      <c r="C35" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D35" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>etal</v>
+      </c>
+      <c r="E35" s="9" t="str">
+        <f t="shared" si="10"/>
+        <v>2013</v>
+      </c>
+      <c r="G35" t="str">
+        <f t="shared" si="5"/>
+        <v>10.3389/fnana.2013.00035</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="J35" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="C35" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D35" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
-      </c>
-      <c r="E35" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v>2013</v>
-      </c>
-      <c r="G35" t="str">
-        <f>_xlfn.TEXTAFTER(A35,"https://doi.org/")</f>
-        <v>10.3389/fnana.2013.00035</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J35" s="3" t="str">
-        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="K35" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="N35" t="str" cm="1">
@@ -4424,45 +4573,48 @@
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI35" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B36" s="7" t="str">
-        <f t="shared" ref="B36" si="12">C36 &amp; IF(D36&lt;&gt;"", "_" &amp; D36, "_") &amp; IF(E36&lt;&gt;"", "_" &amp; E36, "_") &amp; IF(F36&lt;&gt;"", "_" &amp; F36, "")</f>
+        <f t="shared" ref="B36" si="13">C36 &amp; IF(D36&lt;&gt;"", "_" &amp; D36, "_") &amp; IF(E36&lt;&gt;"", "_" &amp; E36, "_") &amp; IF(F36&lt;&gt;"", "_" &amp; F36, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C36" s="9" t="str">
-        <f t="shared" ref="C36" si="13">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A36,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C36" si="14">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A36,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D36" s="9" t="str">
-        <f t="shared" ref="D36" si="14">IF(ISNUMBER(FIND("&amp;", A36)),
+        <f t="shared" ref="D36" si="15">IF(ISNUMBER(FIND("&amp;", A36)),
     IF(LEN(A36)-LEN(SUBSTITUTE(A36, ",", ""))&gt;=3, "etal", MID(A36, SEARCH("&amp; ", A36)+2, SEARCH(",", A36, SEARCH("&amp; ", A36)+2) - SEARCH("&amp; ", A36)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E36" s="9" t="str">
-        <f t="shared" ref="E36" si="15">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A36, "("), ")")</f>
+        <f t="shared" ref="E36" si="16">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A36, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="G36" t="str">
-        <f>_xlfn.TEXTAFTER(A36,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J36" s="3" t="str">
-        <f t="shared" ref="J36" si="16">TRIM(_xlfn.TEXTJOIN("_",FALSE,B36,(SUBSTITUTE(SUBSTITUTE(I36," ",""), "_", ""))))</f>
+        <f t="shared" ref="J36" si="17">TRIM(_xlfn.TEXTJOIN("_",FALSE,B36,(SUBSTITUTE(SUBSTITUTE(I36," ",""), "_", ""))))</f>
         <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
       <c r="K36" s="3" t="str">
-        <f t="shared" ref="K36" si="17">IF(ISBLANK(H36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K36" si="18">IF(ISBLANK(H36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
       <c r="N36" t="str" cm="1">
@@ -4474,45 +4626,48 @@
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI36" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B37" s="7" t="str">
-        <f t="shared" ref="B37" si="18">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
+        <f t="shared" ref="B37" si="19">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C37" s="9" t="str">
-        <f t="shared" ref="C37" si="19">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C37" si="20">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f t="shared" ref="D37" si="20">IF(ISNUMBER(FIND("&amp;", A37)),
+        <f t="shared" ref="D37" si="21">IF(ISNUMBER(FIND("&amp;", A37)),
     IF(LEN(A37)-LEN(SUBSTITUTE(A37, ",", ""))&gt;=3, "etal", MID(A37, SEARCH("&amp; ", A37)+2, SEARCH(",", A37, SEARCH("&amp; ", A37)+2) - SEARCH("&amp; ", A37)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E37" s="9" t="str">
-        <f t="shared" ref="E37" si="21">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
+        <f t="shared" ref="E37" si="22">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="G37" t="str">
-        <f>_xlfn.TEXTAFTER(A37,"https://doi.org/")</f>
+        <f t="shared" si="5"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="J37" s="3" t="str">
-        <f t="shared" ref="J37" si="22">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
+        <f t="shared" ref="J37" si="23">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
         <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
       <c r="K37" s="3" t="str">
-        <f t="shared" ref="K37" si="23">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K37" si="24">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
       <c r="N37" t="str" cm="1">
@@ -4524,45 +4679,48 @@
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B38" s="7" t="str">
-        <f t="shared" ref="B38" si="24">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
+        <f t="shared" ref="B38" si="25">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C38" s="9" t="str">
-        <f t="shared" ref="C38" si="25">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C38" si="26">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D38" s="9" t="str">
-        <f t="shared" ref="D38" si="26">IF(ISNUMBER(FIND("&amp;", A38)),
+        <f t="shared" ref="D38" si="27">IF(ISNUMBER(FIND("&amp;", A38)),
     IF(LEN(A38)-LEN(SUBSTITUTE(A38, ",", ""))&gt;=3, "etal", MID(A38, SEARCH("&amp; ", A38)+2, SEARCH(",", A38, SEARCH("&amp; ", A38)+2) - SEARCH("&amp; ", A38)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E38" s="9" t="str">
-        <f t="shared" ref="E38" si="27">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
+        <f t="shared" ref="E38" si="28">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" ref="G38" si="28">_xlfn.TEXTAFTER(A38,"https://doi.org/")</f>
+        <f t="shared" ref="G38" si="29">_xlfn.TEXTAFTER(A38,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="J38" s="3" t="str">
-        <f t="shared" ref="J38" si="29">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
+        <f t="shared" ref="J38" si="30">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Table2</v>
       </c>
       <c r="K38" s="3" t="str">
-        <f t="shared" ref="K38" si="30">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K38" si="31">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
       <c r="N38" t="str" cm="1">
@@ -4574,27 +4732,33 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI38">
+        <v>6</v>
+      </c>
+      <c r="AK38">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B39" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C39" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Isler</v>
       </c>
       <c r="D39" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E39" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2008</v>
       </c>
       <c r="G39" t="str">
@@ -4602,14 +4766,14 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J39" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Isler_etal_2008_Table7</v>
       </c>
       <c r="K39" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
       </c>
       <c r="N39" t="str" cm="1">
@@ -4621,27 +4785,33 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI39">
+        <v>3</v>
+      </c>
+      <c r="AK39">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B40" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C40" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Isler</v>
       </c>
       <c r="D40" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E40" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2008</v>
       </c>
       <c r="G40" t="str">
@@ -4649,14 +4819,14 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J40" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Isler_etal_2008_TableS1</v>
       </c>
       <c r="K40" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
       </c>
       <c r="N40" t="str" cm="1">
@@ -4668,45 +4838,48 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI40" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B41" s="7" t="str">
-        <f t="shared" ref="B41" si="31">C41 &amp; IF(D41&lt;&gt;"", "_" &amp; D41, "_") &amp; IF(E41&lt;&gt;"", "_" &amp; E41, "_") &amp; IF(F41&lt;&gt;"", "_" &amp; F41, "")</f>
+        <f t="shared" ref="B41" si="32">C41 &amp; IF(D41&lt;&gt;"", "_" &amp; D41, "_") &amp; IF(E41&lt;&gt;"", "_" &amp; E41, "_") &amp; IF(F41&lt;&gt;"", "_" &amp; F41, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C41" s="9" t="str">
-        <f t="shared" ref="C41" si="32">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A41,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C41" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A41,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D41" s="9" t="str">
-        <f t="shared" ref="D41" si="33">IF(ISNUMBER(FIND("&amp;", A41)),
+        <f t="shared" ref="D41" si="34">IF(ISNUMBER(FIND("&amp;", A41)),
     IF(LEN(A41)-LEN(SUBSTITUTE(A41, ",", ""))&gt;=3, "etal", MID(A41, SEARCH("&amp; ", A41)+2, SEARCH(",", A41, SEARCH("&amp; ", A41)+2) - SEARCH("&amp; ", A41)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E41" s="9" t="str">
-        <f t="shared" ref="E41" si="34">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A41, "("), ")")</f>
+        <f t="shared" ref="E41" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A41, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="G41" t="str">
-        <f t="shared" ref="G41" si="35">_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
+        <f t="shared" ref="G41" si="36">_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="J41" s="3" t="str">
-        <f t="shared" ref="J41" si="36">TRIM(_xlfn.TEXTJOIN("_",FALSE,B41,(SUBSTITUTE(SUBSTITUTE(I41," ",""), "_", ""))))</f>
+        <f t="shared" ref="J41" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,B41,(SUBSTITUTE(SUBSTITUTE(I41," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="K41" s="3" t="str">
-        <f t="shared" ref="K41" si="37">IF(ISBLANK(H41),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K41" si="38">IF(ISBLANK(H41),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="N41" t="str" cm="1">
@@ -4718,45 +4891,51 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI41">
+        <v>8</v>
+      </c>
+      <c r="AK41">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B42" s="7" t="str">
-        <f t="shared" ref="B42" si="38">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
+        <f t="shared" ref="B42" si="39">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C42" s="9" t="str">
-        <f t="shared" ref="C42" si="39">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C42" si="40">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D42" s="9" t="str">
-        <f t="shared" ref="D42" si="40">IF(ISNUMBER(FIND("&amp;", A42)),
+        <f t="shared" ref="D42" si="41">IF(ISNUMBER(FIND("&amp;", A42)),
     IF(LEN(A42)-LEN(SUBSTITUTE(A42, ",", ""))&gt;=3, "etal", MID(A42, SEARCH("&amp; ", A42)+2, SEARCH(",", A42, SEARCH("&amp; ", A42)+2) - SEARCH("&amp; ", A42)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E42" s="9" t="str">
-        <f t="shared" ref="E42" si="41">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
+        <f t="shared" ref="E42" si="42">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="G42" t="str">
-        <f t="shared" ref="G42" si="42">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
+        <f t="shared" ref="G42" si="43">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="J42" s="3" t="str">
-        <f t="shared" ref="J42" si="43">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
+        <f t="shared" ref="J42" si="44">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS3</v>
       </c>
       <c r="K42" s="3" t="str">
-        <f t="shared" ref="K42" si="44">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K42" si="45">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
       <c r="N42" t="str" cm="1">
@@ -4768,46 +4947,52 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" s="17" customFormat="1">
+        <v>49</v>
+      </c>
+      <c r="AI42">
+        <v>7</v>
+      </c>
+      <c r="AK42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" s="17" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B43" s="18" t="str">
-        <f t="shared" ref="B43" si="45">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
+        <f t="shared" ref="B43" si="46">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C43" s="19" t="str">
-        <f t="shared" ref="C43" si="46">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C43" si="47">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D43" s="19" t="str">
-        <f t="shared" ref="D43" si="47">IF(ISNUMBER(FIND("&amp;", A43)),
+        <f t="shared" ref="D43" si="48">IF(ISNUMBER(FIND("&amp;", A43)),
     IF(LEN(A43)-LEN(SUBSTITUTE(A43, ",", ""))&gt;=3, "etal", MID(A43, SEARCH("&amp; ", A43)+2, SEARCH(",", A43, SEARCH("&amp; ", A43)+2) - SEARCH("&amp; ", A43)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E43" s="19" t="str">
-        <f t="shared" ref="E43" si="48">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
+        <f t="shared" ref="E43" si="49">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="F43" s="19"/>
       <c r="G43" s="17" t="str">
-        <f t="shared" ref="G43" si="49">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
+        <f t="shared" ref="G43" si="50">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I43" s="20" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="J43" s="20" t="str">
-        <f t="shared" ref="J43" si="50">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
+        <f t="shared" ref="J43" si="51">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Tree.nex</v>
       </c>
       <c r="K43" s="21" t="str">
-        <f t="shared" ref="K43" si="51">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K43" si="52">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="N43" s="17" t="str" cm="1">
@@ -4819,27 +5004,27 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P43" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B44" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Lewitus_etal_2014</v>
       </c>
       <c r="C44" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Lewitus</v>
       </c>
       <c r="D44" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E44" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2014</v>
       </c>
       <c r="G44" t="str">
@@ -4847,14 +5032,14 @@
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="J44" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Lewitus_etal_2014_TableS1</v>
       </c>
       <c r="K44" s="3" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="N44" t="str" cm="1">
@@ -4866,30 +5051,36 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="P44" s="3" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="45" spans="1:31">
+        <v>49</v>
+      </c>
+      <c r="AI44">
+        <v>9</v>
+      </c>
+      <c r="AK44">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B45" s="7" t="str">
-        <f t="shared" ref="B45" si="52">C45 &amp; IF(D45&lt;&gt;"", "_" &amp; D45, "_") &amp; IF(E45&lt;&gt;"", "_" &amp; E45, "_") &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "")</f>
+        <f t="shared" ref="B45" si="53">C45 &amp; IF(D45&lt;&gt;"", "_" &amp; D45, "_") &amp; IF(E45&lt;&gt;"", "_" &amp; E45, "_") &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "")</f>
         <v>Lewitus_etal_2014</v>
       </c>
       <c r="C45" s="9" t="str">
-        <f t="shared" ref="C45" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C45" si="54">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
       <c r="D45" s="9" t="str">
-        <f t="shared" ref="D45" si="54">IF(ISNUMBER(FIND("&amp;", A45)),
+        <f t="shared" ref="D45" si="55">IF(ISNUMBER(FIND("&amp;", A45)),
     IF(LEN(A45)-LEN(SUBSTITUTE(A45, ",", ""))&gt;=3, "etal", MID(A45, SEARCH("&amp; ", A45)+2, SEARCH(",", A45, SEARCH("&amp; ", A45)+2) - SEARCH("&amp; ", A45)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E45" s="9" t="str">
-        <f t="shared" ref="E45" si="55">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
+        <f t="shared" ref="E45" si="56">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
         <v>2014</v>
       </c>
       <c r="G45" t="str">
@@ -4897,14 +5088,14 @@
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="J45" s="3" t="str">
-        <f t="shared" ref="J45" si="56">TRIM(_xlfn.TEXTJOIN("_",FALSE,B45,(SUBSTITUTE(SUBSTITUTE(I45," ",""), "_", ""))))</f>
+        <f t="shared" ref="J45" si="57">TRIM(_xlfn.TEXTJOIN("_",FALSE,B45,(SUBSTITUTE(SUBSTITUTE(I45," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2014_TableS8</v>
       </c>
       <c r="K45" s="3" t="str">
-        <f t="shared" ref="K45" si="57">IF(ISBLANK(H45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K45" si="58">IF(ISBLANK(H45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="N45" t="str" cm="1">
@@ -4916,33 +5107,39 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="X45" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31" s="17" customFormat="1">
+        <v>232</v>
+      </c>
+      <c r="AI45">
+        <v>6</v>
+      </c>
+      <c r="AK45">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" s="17" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B46" s="18" t="str">
-        <f t="shared" ref="B46" si="58">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
+        <f t="shared" ref="B46" si="59">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
         <v>Lewitus_etal_2013</v>
       </c>
       <c r="C46" s="19" t="str">
-        <f t="shared" ref="C46" si="59">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C46" si="60">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
       <c r="D46" s="19" t="str">
-        <f t="shared" ref="D46" si="60">IF(ISNUMBER(FIND("&amp;", A46)),
+        <f t="shared" ref="D46" si="61">IF(ISNUMBER(FIND("&amp;", A46)),
     IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=3, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E46" s="19" t="str">
-        <f t="shared" ref="E46" si="61">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
+        <f t="shared" ref="E46" si="62">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="F46" s="19"/>
@@ -4951,10 +5148,10 @@
         <v>10.3389/fnhum.2013.00424</v>
       </c>
       <c r="I46" s="20" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="J46" s="20" t="str">
-        <f t="shared" ref="J46" si="62">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
+        <f t="shared" ref="J46" si="63">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
       <c r="K46" s="21" t="str">
@@ -4963,114 +5160,126 @@
       </c>
       <c r="N46" s="17" t="str" cm="1">
         <f t="array" ref="N46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K46, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
       <c r="O46" s="17" t="str" cm="1">
         <f t="array" ref="O46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K46, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
       <c r="P46" s="20" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31" s="24" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A47" s="24" t="s">
-        <v>229</v>
+        <v>49</v>
+      </c>
+      <c r="AI46" s="17">
+        <v>7</v>
+      </c>
+      <c r="AK46" s="17">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="15" t="s">
+        <v>235</v>
       </c>
       <c r="B47" s="22" t="str">
-        <f t="shared" ref="B47" si="63">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
+        <f t="shared" ref="B47" si="64">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
-      <c r="C47" s="25" t="str">
-        <f t="shared" ref="C47" si="64">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
+      <c r="C47" s="24" t="str">
+        <f t="shared" ref="C47" si="65">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
-      <c r="D47" s="25" t="str">
-        <f t="shared" ref="D47" si="65">IF(ISNUMBER(FIND("&amp;", A47)),
+      <c r="D47" s="24" t="str">
+        <f t="shared" ref="D47" si="66">IF(ISNUMBER(FIND("&amp;", A47)),
     IF(LEN(A47)-LEN(SUBSTITUTE(A47, ",", ""))&gt;=3, "etal", MID(A47, SEARCH("&amp; ", A47)+2, SEARCH(",", A47, SEARCH("&amp; ", A47)+2) - SEARCH("&amp; ", A47)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E47" s="25" t="str">
-        <f t="shared" ref="E47" si="66">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
+      <c r="E47" s="24" t="str">
+        <f t="shared" ref="E47" si="67">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
         <v>2011</v>
       </c>
-      <c r="F47" s="25"/>
-      <c r="G47" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="I47" s="24" t="s">
-        <v>231</v>
+      <c r="F47" s="24"/>
+      <c r="G47" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="I47" s="15" t="s">
+        <v>237</v>
       </c>
       <c r="J47" s="23" t="str">
-        <f t="shared" ref="J47" si="67">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
+        <f t="shared" ref="J47" si="68">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="K47" s="23" t="str">
         <f>IF(ISBLANK(H47),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
-      <c r="N47" s="24" t="str" cm="1">
+      <c r="N47" s="15" t="str" cm="1">
         <f t="array" ref="N47">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K47, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
-      <c r="O47" s="24" t="str" cm="1">
+      <c r="O47" s="15" t="str" cm="1">
         <f t="array" ref="O47">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K47, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="P47" s="23" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31" s="24" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A48" s="24" t="s">
-        <v>229</v>
+        <v>49</v>
+      </c>
+      <c r="AI47" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="48" spans="1:37" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="15" t="s">
+        <v>235</v>
       </c>
       <c r="B48" s="22" t="str">
-        <f t="shared" ref="B48" si="68">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
+        <f t="shared" ref="B48" si="69">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
-      <c r="C48" s="25" t="str">
-        <f t="shared" ref="C48" si="69">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
+      <c r="C48" s="24" t="str">
+        <f t="shared" ref="C48" si="70">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
-      <c r="D48" s="25" t="str">
-        <f t="shared" ref="D48" si="70">IF(ISNUMBER(FIND("&amp;", A48)),
+      <c r="D48" s="24" t="str">
+        <f t="shared" ref="D48" si="71">IF(ISNUMBER(FIND("&amp;", A48)),
     IF(LEN(A48)-LEN(SUBSTITUTE(A48, ",", ""))&gt;=3, "etal", MID(A48, SEARCH("&amp; ", A48)+2, SEARCH(",", A48, SEARCH("&amp; ", A48)+2) - SEARCH("&amp; ", A48)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E48" s="25" t="str">
-        <f t="shared" ref="E48" si="71">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
+      <c r="E48" s="24" t="str">
+        <f t="shared" ref="E48" si="72">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
         <v>2011</v>
       </c>
-      <c r="F48" s="25"/>
-      <c r="G48" s="24" t="s">
-        <v>230</v>
-      </c>
-      <c r="I48" s="24" t="s">
-        <v>232</v>
+      <c r="F48" s="24"/>
+      <c r="G48" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>239</v>
       </c>
       <c r="J48" s="23" t="str">
-        <f t="shared" ref="J48" si="72">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
+        <f t="shared" ref="J48" si="73">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="K48" s="23" t="str">
         <f>IF(ISBLANK(H48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
-      <c r="N48" s="24" t="str" cm="1">
+      <c r="N48" s="15" t="str" cm="1">
         <f t="array" ref="N48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K48, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
       </c>
-      <c r="O48" s="24" t="str" cm="1">
+      <c r="O48" s="15" t="str" cm="1">
         <f t="array" ref="O48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K48, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="P48" s="23" t="s">
-        <v>46</v>
+        <v>49</v>
+      </c>
+      <c r="AI48" s="15" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -5097,104 +5306,104 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A05C489E-9770-1041-AA5F-EEF758A56CB8}">
   <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="B3" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B4" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="B5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="B6" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="B7" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B8" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B9" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="B10" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B11" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17.100000000000001">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="B12" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
     </row>
   </sheetData>
@@ -5206,64 +5415,64 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8377CCE6-51F2-A040-A333-66D02DBB8DB4}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.875" customWidth="1"/>
+    <col min="1" max="1" width="1.83203125" customWidth="1"/>
     <col min="2" max="2" width="126" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="C3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C4" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="C5" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C6" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -5272,6 +5481,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -5514,17 +5734,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -5535,13 +5744,45 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26276598-8A19-40B6-BED3-157936C93058}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26276598-8A19-40B6-BED3-157936C93058}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="705" documentId="6_{07DD5C5E-4B7E-564D-9FFA-3C28EE9E5650}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8969198F-7CBC-B540-B609-55EDE1F9B34F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34580" yWindow="-5960" windowWidth="41380" windowHeight="20360" activeTab="1" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="34560" yWindow="-5960" windowWidth="45100" windowHeight="20500" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="540" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="278">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -882,6 +882,21 @@
   </si>
   <si>
     <t>add a column to correct any errors in species designations (e.g., misidentified or combined different species of same genus)</t>
+  </si>
+  <si>
+    <t>Table 1. Origin and use of the experimental animals.</t>
+  </si>
+  <si>
+    <t>sample size and information</t>
+  </si>
+  <si>
+    <t>Kverkova_etal_2018_Table1_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>Kverkova_etal_2018_TableS1_snapshot.xlsx</t>
+  </si>
+  <si>
+    <t>Kverkova_etal_2018_TableS5_snapshot.csv</t>
   </si>
 </sst>
 </file>
@@ -1113,162 +1128,162 @@
         </row>
         <row r="12">
           <cell r="A12" t="str">
-            <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+            <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
           </cell>
         </row>
         <row r="13">
           <cell r="A13" t="str">
-            <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+            <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
           </cell>
         </row>
         <row r="14">
           <cell r="A14" t="str">
-            <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
+            <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
           </cell>
         </row>
         <row r="15">
           <cell r="A15" t="str">
-            <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+            <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
           </cell>
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>10.1159%2F000124401_TableI.tsv</v>
+            <v>10.1093%2Fjmammal%2Fgyz043.ReadMe.md</v>
           </cell>
         </row>
         <row r="17">
           <cell r="A17" t="str">
-            <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+            <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
           </cell>
         </row>
         <row r="18">
           <cell r="A18" t="str">
-            <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+            <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
           </cell>
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>10.1159%2F000323671.ReadMe.md</v>
+            <v>10.1159%2F000124401_TableI.tsv</v>
           </cell>
         </row>
         <row r="20">
           <cell r="A20" t="str">
-            <v>10.1159%2F000437413_Table1.tsv</v>
+            <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21" t="str">
-            <v>10.1159%2F000437413_Table2.tsv</v>
+            <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22" t="str">
-            <v>10.1159%2F000437413_Table3.tsv</v>
+            <v>10.1159%2F000323671.ReadMe.md</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23" t="str">
-            <v>10.1159%2F000437413_Table4.tsv</v>
+            <v>10.1159%2F000437413_Table1.tsv</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24" t="str">
-            <v>10.1159%2F000437413_Table5.tsv</v>
+            <v>10.1159%2F000437413_Table2.tsv</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25" t="str">
-            <v>10.1159%2F000452856_TableS1.tsv</v>
+            <v>10.1159%2F000437413_Table3.tsv</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+            <v>10.1159%2F000437413_Table4.tsv</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</v>
+            <v>10.1159%2F000437413_Table5.tsv</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+            <v>10.1159%2F000452856_TableS1.tsv</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29" t="str">
-            <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
+            <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
-            <v>10.3389%25Ffnana.2013.00035.svg</v>
+            <v>10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
+            <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
+            <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
+            <v>10.3389%25Ffnana.2013.00035.svg</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
+            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35" t="str">
-            <v>10.3389%2Ffnana.2013.00035.ReadMe.md</v>
+            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36" t="str">
-            <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+            <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37" t="str">
-            <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+            <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38" t="str">
-            <v>10.3389%2Ffnhum.2013.00424.ReadMe.md</v>
+            <v>10.3389%2Ffnana.2013.00035.ReadMe.md</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39" t="str">
-            <v>10.5061%2Fdryad.2r62k7s.ReadMe.md</v>
+            <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40" t="str">
-            <v>10.5061%2Fdryad.2r62k7s.tsv</v>
+            <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41" t="str">
-            <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
+            <v>10.3389%2Ffnhum.2013.00424.ReadMe.md</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42" t="str">
-            <v>10.7554%2FeLife.77875_Table1.tsv</v>
+            <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43" t="str">
-            <v>README.md</v>
+            <v>10.7554%2FeLife.77875_Table1.tsv</v>
           </cell>
         </row>
       </sheetData>
@@ -1278,9 +1293,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1318,7 +1333,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1424,7 +1439,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1566,7 +1581,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1575,7 +1590,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AK48"/>
+  <dimension ref="A1:AK49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.5" customWidth="1"/>
@@ -1817,7 +1832,7 @@
         <v>2019</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G37" si="5">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
+        <f t="shared" ref="G3:G38" si="5">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
         <v>10.1093/jmammal/gyz043</v>
       </c>
       <c r="H3" s="3"/>
@@ -1825,7 +1840,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3" t="str">
-        <f t="shared" ref="J3:J44" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
+        <f t="shared" ref="J3:J45" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
       <c r="K3" s="21" t="str">
@@ -1840,11 +1855,11 @@
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" ref="N3">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K3, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
       <c r="O3" t="str" cm="1">
         <f t="array" ref="O3">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K3, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
       <c r="P3" s="3" t="s">
         <v>49</v>
@@ -1893,22 +1908,22 @@
         <v>58</v>
       </c>
       <c r="B4" s="7" t="str">
-        <f t="shared" ref="B4:B44" si="7">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
+        <f t="shared" ref="B4:B45" si="7">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="C4" s="9" t="str">
-        <f t="shared" ref="C4:C44" si="8">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C4:C45" si="8">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
         <v>Caspar</v>
       </c>
       <c r="D4" s="9" t="str">
-        <f t="shared" ref="D4:D44" si="9">IF(ISNUMBER(FIND("&amp;", A4)),
+        <f t="shared" ref="D4:D45" si="9">IF(ISNUMBER(FIND("&amp;", A4)),
     IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=3, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E4" s="9" t="str">
-        <f t="shared" ref="E4:E44" si="10">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+        <f t="shared" ref="E4:E45" si="10">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
         <v>2022</v>
       </c>
       <c r="G4" t="str">
@@ -1924,7 +1939,7 @@
         <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="K4" s="3" t="str">
-        <f t="shared" ref="K4:K44" si="11">IF(ISBLANK(H4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K4:K45" si="11">IF(ISBLANK(H4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="L4" s="3"/>
@@ -3829,37 +3844,40 @@
         <v>184</v>
       </c>
       <c r="B26" s="7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="B26" si="12">C26 &amp; IF(D26&lt;&gt;"", "_" &amp; D26, "_") &amp; IF(E26&lt;&gt;"", "_" &amp; E26, "_") &amp; IF(F26&lt;&gt;"", "_" &amp; F26, "")</f>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="C26" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C26" si="13">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A26,","), "-", ""), " ", "")</f>
         <v>Kverkova</v>
       </c>
       <c r="D26" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="D26" si="14">IF(ISNUMBER(FIND("&amp;", A26)),
+    IF(LEN(A26)-LEN(SUBSTITUTE(A26, ",", ""))&gt;=3, "etal", MID(A26, SEARCH("&amp; ", A26)+2, SEARCH(",", A26, SEARCH("&amp; ", A26)+2) - SEARCH("&amp; ", A26)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
       <c r="E26" s="9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="E26" si="15">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A26, "("), ")")</f>
         <v>2018</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="G26" si="16">_xlfn.TEXTAFTER(A26,"https://doi.org/")</f>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="J26" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>Kverkova_etal_2018_TableS1</v>
+        <f t="shared" ref="J26" si="17">TRIM(_xlfn.TEXTJOIN("_",FALSE,B26,(SUBSTITUTE(SUBSTITUTE(I26," ",""), "_", ""))))</f>
+        <v>Kverkova_etal_2018_Table1</v>
       </c>
       <c r="K26" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
+        <f t="shared" ref="K26" si="18">IF(ISBLANK(H26),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="L26" s="3"/>
       <c r="M26" t="s">
@@ -3867,16 +3885,18 @@
       </c>
       <c r="N26" t="str" cm="1">
         <f t="array" ref="N26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="O26" t="str" cm="1">
         <f t="array" ref="O26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K26, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="P26" t="s">
         <v>60</v>
       </c>
-      <c r="Q26" s="14"/>
+      <c r="Q26" s="14" t="s">
+        <v>275</v>
+      </c>
       <c r="R26" s="3" t="s">
         <v>62</v>
       </c>
@@ -3889,20 +3909,15 @@
       <c r="U26" t="s">
         <v>53</v>
       </c>
-      <c r="V26" t="s">
-        <v>65</v>
-      </c>
-      <c r="W26" s="8" t="s">
-        <v>187</v>
-      </c>
+      <c r="W26" s="8"/>
       <c r="X26" s="7" t="s">
-        <v>188</v>
+        <v>273</v>
       </c>
       <c r="Y26" t="s">
-        <v>163</v>
+        <v>274</v>
       </c>
       <c r="Z26" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="AB26" t="s">
         <v>107</v>
@@ -3944,15 +3959,15 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Kverkova_etal_2018_TableS5</v>
+        <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="K27" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" t="s">
@@ -3960,24 +3975,26 @@
       </c>
       <c r="N27" t="str" cm="1">
         <f t="array" ref="N27">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K27, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="O27" t="str" cm="1">
         <f t="array" ref="O27">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K27, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="P27" t="s">
         <v>60</v>
       </c>
-      <c r="Q27" s="14"/>
+      <c r="Q27" s="14" t="s">
+        <v>276</v>
+      </c>
       <c r="R27" s="3" t="s">
         <v>62</v>
       </c>
       <c r="S27" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="T27" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="U27" t="s">
         <v>53</v>
@@ -3989,13 +4006,13 @@
         <v>187</v>
       </c>
       <c r="X27" s="7" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="Y27" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="Z27" t="s">
-        <v>106</v>
+        <v>189</v>
       </c>
       <c r="AB27" t="s">
         <v>107</v>
@@ -4012,129 +4029,139 @@
     </row>
     <row r="28" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="B28" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>ManyPrimates__2022</v>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="C28" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>ManyPrimates</v>
+        <v>Kverkova</v>
       </c>
       <c r="D28" s="9" t="str">
         <f t="shared" si="9"/>
-        <v/>
+        <v>etal</v>
       </c>
       <c r="E28" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>2022</v>
+        <v>2018</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" t="str">
         <f t="shared" si="5"/>
-        <v>10.26451/abc.09.04.06.2022</v>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H28" s="3"/>
-      <c r="I28" s="12" t="s">
-        <v>196</v>
+      <c r="I28" s="3" t="s">
+        <v>191</v>
       </c>
       <c r="J28" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
+        <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="K28" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" t="s">
-        <v>197</v>
+        <v>48</v>
       </c>
       <c r="N28" t="str" cm="1">
         <f t="array" ref="N28">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K28, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
       <c r="O28" t="str" cm="1">
         <f t="array" ref="O28">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K28, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="P28" t="s">
-        <v>38</v>
-      </c>
-      <c r="Q28" s="14"/>
-      <c r="S28" t="str">
-        <f t="shared" ref="S28:S33" si="12">IF(R28="N", Q28, "write file name")</f>
-        <v>write file name</v>
+        <v>60</v>
+      </c>
+      <c r="Q28" s="14" t="s">
+        <v>277</v>
+      </c>
+      <c r="R28" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S28" t="s">
+        <v>192</v>
       </c>
       <c r="T28" t="s">
-        <v>74</v>
+        <v>193</v>
       </c>
       <c r="U28" t="s">
         <v>53</v>
       </c>
       <c r="V28" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="W28" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="X28" s="7"/>
+        <v>187</v>
+      </c>
+      <c r="X28" s="7" t="s">
+        <v>194</v>
+      </c>
       <c r="Y28" t="s">
-        <v>199</v>
+        <v>169</v>
       </c>
       <c r="Z28" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC28" t="s">
-        <v>200</v>
+        <v>106</v>
+      </c>
+      <c r="AB28" t="s">
+        <v>107</v>
       </c>
       <c r="AE28" t="s">
-        <v>71</v>
+        <v>190</v>
+      </c>
+      <c r="AI28">
+        <v>1</v>
+      </c>
+      <c r="AK28">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="B29" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>Powell_etal_2017</v>
+        <v>ManyPrimates__2022</v>
       </c>
       <c r="C29" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Powell</v>
+        <v>ManyPrimates</v>
       </c>
       <c r="D29" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
+        <v/>
       </c>
       <c r="E29" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>2017</v>
+        <v>2022</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" t="str">
         <f t="shared" si="5"/>
-        <v>10.1098/rspb.2017.1765</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>203</v>
+        <v>10.26451/abc.09.04.06.2022</v>
+      </c>
+      <c r="H29" s="3"/>
+      <c r="I29" s="12" t="s">
+        <v>196</v>
       </c>
       <c r="J29" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Powell_etal_2017_Dataset1</v>
+        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="K29" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="L29" s="3"/>
-      <c r="M29" s="15" t="s">
-        <v>132</v>
+      <c r="M29" t="s">
+        <v>197</v>
       </c>
       <c r="N29" t="str" cm="1">
         <f t="array" ref="N29">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K29, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4149,7 +4176,7 @@
       </c>
       <c r="Q29" s="14"/>
       <c r="S29" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" ref="S29:S34" si="19">IF(R29="N", Q29, "write file name")</f>
         <v>write file name</v>
       </c>
       <c r="T29" t="s">
@@ -4162,17 +4189,17 @@
         <v>75</v>
       </c>
       <c r="W29" s="8" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="X29" s="7"/>
       <c r="Y29" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="Z29" t="s">
         <v>56</v>
       </c>
       <c r="AC29" t="s">
-        <v>55</v>
+        <v>200</v>
       </c>
       <c r="AE29" t="s">
         <v>71</v>
@@ -4180,15 +4207,15 @@
     </row>
     <row r="30" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B30" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>Sherwood_etal_2004_I</v>
+        <v>Powell_etal_2017</v>
       </c>
       <c r="C30" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Sherwood</v>
+        <v>Powell</v>
       </c>
       <c r="D30" s="9" t="str">
         <f t="shared" si="9"/>
@@ -4196,30 +4223,30 @@
       </c>
       <c r="E30" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>2004</v>
-      </c>
-      <c r="F30" s="7" t="s">
-        <v>207</v>
-      </c>
+        <v>2017</v>
+      </c>
+      <c r="F30" s="7"/>
       <c r="G30" t="str">
         <f t="shared" si="5"/>
-        <v>10.1159/000075672</v>
-      </c>
-      <c r="H30" s="3"/>
+        <v>10.1098/rspb.2017.1765</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="I30" s="3" t="s">
-        <v>150</v>
+        <v>203</v>
       </c>
       <c r="J30" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Sherwood_etal_2004_I_Table4</v>
+        <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="K30" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.1159%2F000075672_Table4</v>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="L30" s="3"/>
-      <c r="M30" t="s">
-        <v>197</v>
+      <c r="M30" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="N30" t="str" cm="1">
         <f t="array" ref="N30">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K30, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4234,23 +4261,30 @@
       </c>
       <c r="Q30" s="14"/>
       <c r="S30" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>write file name</v>
       </c>
       <c r="T30" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="U30" t="s">
-        <v>208</v>
-      </c>
-      <c r="X30" s="7" t="s">
-        <v>209</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="V30" t="s">
+        <v>75</v>
+      </c>
+      <c r="W30" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="X30" s="7"/>
       <c r="Y30" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="Z30" t="s">
-        <v>106</v>
+        <v>56</v>
+      </c>
+      <c r="AC30" t="s">
+        <v>55</v>
       </c>
       <c r="AE30" t="s">
         <v>71</v>
@@ -4285,15 +4319,15 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="J31" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Sherwood_etal_2004_I_Table5</v>
+        <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="K31" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.1159%2F000075672_Table5</v>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="L31" s="3"/>
       <c r="M31" t="s">
@@ -4312,7 +4346,7 @@
       </c>
       <c r="Q31" s="14"/>
       <c r="S31" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>write file name</v>
       </c>
       <c r="T31" t="s">
@@ -4321,8 +4355,8 @@
       <c r="U31" t="s">
         <v>208</v>
       </c>
-      <c r="X31" s="11" t="s">
-        <v>211</v>
+      <c r="X31" s="7" t="s">
+        <v>209</v>
       </c>
       <c r="Y31" t="s">
         <v>210</v>
@@ -4336,15 +4370,15 @@
     </row>
     <row r="32" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="B32" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>Winkler_etal_2021</v>
+        <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="C32" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Winkler</v>
+        <v>Sherwood</v>
       </c>
       <c r="D32" s="9" t="str">
         <f t="shared" si="9"/>
@@ -4352,28 +4386,30 @@
       </c>
       <c r="E32" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>2021</v>
-      </c>
-      <c r="F32" s="7"/>
+        <v>2004</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>207</v>
+      </c>
       <c r="G32" t="str">
         <f t="shared" si="5"/>
-        <v>10.1080/09524622.2021.1905065</v>
+        <v>10.1159/000075672</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>213</v>
+        <v>154</v>
       </c>
       <c r="J32" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Winkler_etal_2021_Figure1</v>
+        <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="K32" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="L32" s="3"/>
-      <c r="M32" s="15" t="s">
-        <v>132</v>
+      <c r="M32" t="s">
+        <v>197</v>
       </c>
       <c r="N32" t="str" cm="1">
         <f t="array" ref="N32">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K32, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4388,34 +4424,39 @@
       </c>
       <c r="Q32" s="14"/>
       <c r="S32" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>write file name</v>
       </c>
       <c r="T32" t="s">
         <v>64</v>
       </c>
       <c r="U32" t="s">
-        <v>214</v>
-      </c>
-      <c r="X32" s="7"/>
+        <v>208</v>
+      </c>
+      <c r="X32" s="11" t="s">
+        <v>211</v>
+      </c>
       <c r="Y32" t="s">
-        <v>215</v>
+        <v>210</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>106</v>
       </c>
       <c r="AE32" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="33" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B33" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>Young_etal_2013</v>
+        <v>Winkler_etal_2021</v>
       </c>
       <c r="C33" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Young</v>
+        <v>Winkler</v>
       </c>
       <c r="D33" s="9" t="str">
         <f t="shared" si="9"/>
@@ -4423,28 +4464,28 @@
       </c>
       <c r="E33" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>2013</v>
+        <v>2021</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" t="str">
         <f t="shared" si="5"/>
-        <v>10.3389/fncir.2013.00030</v>
+        <v>10.1080/09524622.2021.1905065</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
-        <v>59</v>
+        <v>213</v>
       </c>
       <c r="J33" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Young_etal_2013_Table1</v>
+        <v>Winkler_etal_2021_Figure1</v>
       </c>
       <c r="K33" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="L33" s="3"/>
-      <c r="M33" t="s">
-        <v>197</v>
+      <c r="M33" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="N33" t="str" cm="1">
         <f t="array" ref="N33">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K33, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4459,34 +4500,34 @@
       </c>
       <c r="Q33" s="14"/>
       <c r="S33" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>write file name</v>
       </c>
       <c r="T33" t="s">
-        <v>120</v>
+        <v>64</v>
       </c>
       <c r="U33" t="s">
-        <v>53</v>
+        <v>214</v>
       </c>
       <c r="X33" s="7"/>
       <c r="Y33" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AE33" t="s">
-        <v>71</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B34" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>Mota_etal_2015</v>
+        <v>Young_etal_2013</v>
       </c>
       <c r="C34" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Mota</v>
+        <v>Young</v>
       </c>
       <c r="D34" s="9" t="str">
         <f t="shared" si="9"/>
@@ -4494,52 +4535,70 @@
       </c>
       <c r="E34" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>2015</v>
-      </c>
+        <v>2013</v>
+      </c>
+      <c r="F34" s="7"/>
       <c r="G34" t="str">
         <f t="shared" si="5"/>
-        <v>10.1126/science.aaa9101</v>
-      </c>
+        <v>10.3389/fncir.2013.00030</v>
+      </c>
+      <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>98</v>
+        <v>59</v>
       </c>
       <c r="J34" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Mota_etal_2015_TableS1</v>
+        <v>Young_etal_2013_Table1</v>
       </c>
       <c r="K34" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+      </c>
+      <c r="L34" s="3"/>
+      <c r="M34" t="s">
+        <v>197</v>
       </c>
       <c r="N34" t="str" cm="1">
         <f t="array" ref="N34">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K34, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="O34" t="str" cm="1">
         <f t="array" ref="O34">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K34, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI34">
-        <v>10</v>
-      </c>
-      <c r="AK34">
-        <v>15</v>
+        <v>notfound</v>
+      </c>
+      <c r="P34" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q34" s="14"/>
+      <c r="S34" t="str">
+        <f t="shared" si="19"/>
+        <v>write file name</v>
+      </c>
+      <c r="T34" t="s">
+        <v>120</v>
+      </c>
+      <c r="U34" t="s">
+        <v>53</v>
+      </c>
+      <c r="X34" s="7"/>
+      <c r="Y34" t="s">
+        <v>217</v>
+      </c>
+      <c r="AE34" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="35" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B35" s="7" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2013</v>
+        <v>Mota_etal_2015</v>
       </c>
       <c r="C35" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
+        <v>Mota</v>
       </c>
       <c r="D35" s="9" t="str">
         <f t="shared" si="9"/>
@@ -4547,36 +4606,39 @@
       </c>
       <c r="E35" s="9" t="str">
         <f t="shared" si="10"/>
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="G35" t="str">
         <f t="shared" si="5"/>
-        <v>10.3389/fnana.2013.00035</v>
+        <v>10.1126/science.aaa9101</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>220</v>
+        <v>98</v>
       </c>
       <c r="J35" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
+        <v>Mota_etal_2015_TableS1</v>
       </c>
       <c r="K35" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="N35" t="str" cm="1">
         <f t="array" ref="N35">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K35, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="O35" t="str" cm="1">
         <f t="array" ref="O35">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K35, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="P35" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AI35" t="s">
-        <v>221</v>
+      <c r="AI35">
+        <v>10</v>
+      </c>
+      <c r="AK35">
+        <v>15</v>
       </c>
     </row>
     <row r="36" spans="1:37" ht="16" x14ac:dyDescent="0.2">
@@ -4584,22 +4646,19 @@
         <v>219</v>
       </c>
       <c r="B36" s="7" t="str">
-        <f t="shared" ref="B36" si="13">C36 &amp; IF(D36&lt;&gt;"", "_" &amp; D36, "_") &amp; IF(E36&lt;&gt;"", "_" &amp; E36, "_") &amp; IF(F36&lt;&gt;"", "_" &amp; F36, "")</f>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C36" s="9" t="str">
-        <f t="shared" ref="C36" si="14">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A36,","), "-", ""), " ", "")</f>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D36" s="9" t="str">
-        <f t="shared" ref="D36" si="15">IF(ISNUMBER(FIND("&amp;", A36)),
-    IF(LEN(A36)-LEN(SUBSTITUTE(A36, ",", ""))&gt;=3, "etal", MID(A36, SEARCH("&amp; ", A36)+2, SEARCH(",", A36, SEARCH("&amp; ", A36)+2) - SEARCH("&amp; ", A36)-2)),
-    ""
-)</f>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E36" s="9" t="str">
-        <f t="shared" ref="E36" si="16">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A36, "("), ")")</f>
+        <f t="shared" si="10"/>
         <v>2013</v>
       </c>
       <c r="G36" t="str">
@@ -4607,19 +4666,19 @@
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="J36" s="3" t="str">
-        <f t="shared" ref="J36" si="17">TRIM(_xlfn.TEXTJOIN("_",FALSE,B36,(SUBSTITUTE(SUBSTITUTE(I36," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2013_Table1-a</v>
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="K36" s="3" t="str">
-        <f t="shared" ref="K36" si="18">IF(ISBLANK(H36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
+        <f t="shared" si="11"/>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="N36" t="str" cm="1">
         <f t="array" ref="N36">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K36, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
       <c r="O36" t="str" cm="1">
         <f t="array" ref="O36">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K36, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
@@ -4637,22 +4696,22 @@
         <v>219</v>
       </c>
       <c r="B37" s="7" t="str">
-        <f t="shared" ref="B37" si="19">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
+        <f t="shared" ref="B37" si="20">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C37" s="9" t="str">
-        <f t="shared" ref="C37" si="20">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C37" si="21">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f t="shared" ref="D37" si="21">IF(ISNUMBER(FIND("&amp;", A37)),
+        <f t="shared" ref="D37" si="22">IF(ISNUMBER(FIND("&amp;", A37)),
     IF(LEN(A37)-LEN(SUBSTITUTE(A37, ",", ""))&gt;=3, "etal", MID(A37, SEARCH("&amp; ", A37)+2, SEARCH(",", A37, SEARCH("&amp; ", A37)+2) - SEARCH("&amp; ", A37)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E37" s="9" t="str">
-        <f t="shared" ref="E37" si="22">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
+        <f t="shared" ref="E37" si="23">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="G37" t="str">
@@ -4660,19 +4719,19 @@
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J37" s="3" t="str">
-        <f t="shared" ref="J37" si="23">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2013_Table1-b</v>
+        <f t="shared" ref="J37" si="24">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
+        <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
       <c r="K37" s="3" t="str">
-        <f t="shared" ref="K37" si="24">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
+        <f t="shared" ref="K37" si="25">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
       <c r="N37" t="str" cm="1">
         <f t="array" ref="N37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K37, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
       <c r="O37" t="str" cm="1">
         <f t="array" ref="O37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K37, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
@@ -4687,58 +4746,55 @@
     </row>
     <row r="38" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="B38" s="7" t="str">
-        <f t="shared" ref="B38" si="25">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
-        <v>Isler_etal_2008</v>
+        <f t="shared" ref="B38" si="26">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
+        <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C38" s="9" t="str">
-        <f t="shared" ref="C38" si="26">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
+        <f t="shared" ref="C38" si="27">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
+        <v>HerculanoHouzel</v>
       </c>
       <c r="D38" s="9" t="str">
-        <f t="shared" ref="D38" si="27">IF(ISNUMBER(FIND("&amp;", A38)),
+        <f t="shared" ref="D38" si="28">IF(ISNUMBER(FIND("&amp;", A38)),
     IF(LEN(A38)-LEN(SUBSTITUTE(A38, ",", ""))&gt;=3, "etal", MID(A38, SEARCH("&amp; ", A38)+2, SEARCH(",", A38, SEARCH("&amp; ", A38)+2) - SEARCH("&amp; ", A38)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E38" s="9" t="str">
-        <f t="shared" ref="E38" si="28">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
-        <v>2008</v>
+        <f t="shared" ref="E38" si="29">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
+        <v>2013</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" ref="G38" si="29">_xlfn.TEXTAFTER(A38,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <f t="shared" si="5"/>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
       <c r="J38" s="3" t="str">
         <f t="shared" ref="J38" si="30">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Table2</v>
+        <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
       <c r="K38" s="3" t="str">
         <f t="shared" ref="K38" si="31">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
       <c r="N38" t="str" cm="1">
         <f t="array" ref="N38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K38, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
       <c r="O38" t="str" cm="1">
         <f t="array" ref="O38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K38, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
       </c>
       <c r="P38" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AI38">
-        <v>6</v>
-      </c>
-      <c r="AK38">
-        <v>7</v>
+      <c r="AI38" t="s">
+        <v>221</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="16" x14ac:dyDescent="0.2">
@@ -4746,39 +4802,42 @@
         <v>224</v>
       </c>
       <c r="B39" s="7" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="B39" si="32">C39 &amp; IF(D39&lt;&gt;"", "_" &amp; D39, "_") &amp; IF(E39&lt;&gt;"", "_" &amp; E39, "_") &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C39" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" ref="C39" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A39,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D39" s="9" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="D39" si="34">IF(ISNUMBER(FIND("&amp;", A39)),
+    IF(LEN(A39)-LEN(SUBSTITUTE(A39, ",", ""))&gt;=3, "etal", MID(A39, SEARCH("&amp; ", A39)+2, SEARCH(",", A39, SEARCH("&amp; ", A39)+2) - SEARCH("&amp; ", A39)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
       <c r="E39" s="9" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" ref="E39" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="G39" t="str">
-        <f>_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
+        <f t="shared" ref="G39" si="36">_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>225</v>
+        <v>142</v>
       </c>
       <c r="J39" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>Isler_etal_2008_Table7</v>
+        <f t="shared" ref="J39" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,B39,(SUBSTITUTE(SUBSTITUTE(I39," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_Table2</v>
       </c>
       <c r="K39" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+        <f t="shared" ref="K39" si="38">IF(ISBLANK(H39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
       <c r="N39" t="str" cm="1">
         <f t="array" ref="N39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K39, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="O39" t="str" cm="1">
         <f t="array" ref="O39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K39, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
@@ -4788,10 +4847,10 @@
         <v>49</v>
       </c>
       <c r="AI39">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AK39">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:37" ht="16" x14ac:dyDescent="0.2">
@@ -4819,19 +4878,19 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>98</v>
+        <v>225</v>
       </c>
       <c r="J40" s="3" t="str">
         <f t="shared" si="6"/>
-        <v>Isler_etal_2008_TableS1</v>
+        <v>Isler_etal_2008_Table7</v>
       </c>
       <c r="K40" s="3" t="str">
         <f t="shared" si="11"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
       </c>
       <c r="N40" t="str" cm="1">
         <f t="array" ref="N40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K40, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
       <c r="O40" t="str" cm="1">
         <f t="array" ref="O40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K40, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
@@ -4840,8 +4899,11 @@
       <c r="P40" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AI40" t="s">
-        <v>226</v>
+      <c r="AI40">
+        <v>3</v>
+      </c>
+      <c r="AK40">
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:37" ht="16" x14ac:dyDescent="0.2">
@@ -4849,42 +4911,39 @@
         <v>224</v>
       </c>
       <c r="B41" s="7" t="str">
-        <f t="shared" ref="B41" si="32">C41 &amp; IF(D41&lt;&gt;"", "_" &amp; D41, "_") &amp; IF(E41&lt;&gt;"", "_" &amp; E41, "_") &amp; IF(F41&lt;&gt;"", "_" &amp; F41, "")</f>
+        <f t="shared" si="7"/>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C41" s="9" t="str">
-        <f t="shared" ref="C41" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A41,","), "-", ""), " ", "")</f>
+        <f t="shared" si="8"/>
         <v>Isler</v>
       </c>
       <c r="D41" s="9" t="str">
-        <f t="shared" ref="D41" si="34">IF(ISNUMBER(FIND("&amp;", A41)),
-    IF(LEN(A41)-LEN(SUBSTITUTE(A41, ",", ""))&gt;=3, "etal", MID(A41, SEARCH("&amp; ", A41)+2, SEARCH(",", A41, SEARCH("&amp; ", A41)+2) - SEARCH("&amp; ", A41)-2)),
-    ""
-)</f>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E41" s="9" t="str">
-        <f t="shared" ref="E41" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A41, "("), ")")</f>
+        <f t="shared" si="10"/>
         <v>2008</v>
       </c>
       <c r="G41" t="str">
-        <f t="shared" ref="G41" si="36">_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
+        <f>_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>227</v>
+        <v>98</v>
       </c>
       <c r="J41" s="3" t="str">
-        <f t="shared" ref="J41" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,B41,(SUBSTITUTE(SUBSTITUTE(I41," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_TableS2</v>
+        <f t="shared" si="6"/>
+        <v>Isler_etal_2008_TableS1</v>
       </c>
       <c r="K41" s="3" t="str">
-        <f t="shared" ref="K41" si="38">IF(ISBLANK(H41),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
+        <f t="shared" si="11"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
       </c>
       <c r="N41" t="str" cm="1">
         <f t="array" ref="N41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K41, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
       <c r="O41" t="str" cm="1">
         <f t="array" ref="O41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K41, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
@@ -4893,11 +4952,8 @@
       <c r="P41" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AI41">
-        <v>8</v>
-      </c>
-      <c r="AK41">
-        <v>11</v>
+      <c r="AI41" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="16" x14ac:dyDescent="0.2">
@@ -4928,19 +4984,19 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J42" s="3" t="str">
         <f t="shared" ref="J42" si="44">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_TableS3</v>
+        <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="K42" s="3" t="str">
         <f t="shared" ref="K42" si="45">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="N42" t="str" cm="1">
         <f t="array" ref="N42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K42, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
       <c r="O42" t="str" cm="1">
         <f t="array" ref="O42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K42, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
@@ -4950,114 +5006,117 @@
         <v>49</v>
       </c>
       <c r="AI42">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK42">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="17" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
         <v>224</v>
       </c>
-      <c r="B43" s="18" t="str">
+      <c r="B43" s="7" t="str">
         <f t="shared" ref="B43" si="46">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C43" s="19" t="str">
+      <c r="C43" s="9" t="str">
         <f t="shared" ref="C43" si="47">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D43" s="19" t="str">
+      <c r="D43" s="9" t="str">
         <f t="shared" ref="D43" si="48">IF(ISNUMBER(FIND("&amp;", A43)),
     IF(LEN(A43)-LEN(SUBSTITUTE(A43, ",", ""))&gt;=3, "etal", MID(A43, SEARCH("&amp; ", A43)+2, SEARCH(",", A43, SEARCH("&amp; ", A43)+2) - SEARCH("&amp; ", A43)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E43" s="19" t="str">
+      <c r="E43" s="9" t="str">
         <f t="shared" ref="E43" si="49">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="17" t="str">
+      <c r="G43" t="str">
         <f t="shared" ref="G43" si="50">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I43" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="J43" s="20" t="str">
+      <c r="I43" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J43" s="3" t="str">
         <f t="shared" ref="J43" si="51">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Tree.nex</v>
-      </c>
-      <c r="K43" s="21" t="str">
+        <v>Isler_etal_2008_TableS3</v>
+      </c>
+      <c r="K43" s="3" t="str">
         <f t="shared" ref="K43" si="52">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
-      </c>
-      <c r="N43" s="17" t="str" cm="1">
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
+      </c>
+      <c r="N43" t="str" cm="1">
         <f t="array" ref="N43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K43, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="O43" s="17" t="str" cm="1">
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
+      </c>
+      <c r="O43" t="str" cm="1">
         <f t="array" ref="O43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K43, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
-      <c r="P43" s="20" t="s">
+      <c r="P43" s="3" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="44" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" t="s">
-        <v>230</v>
-      </c>
-      <c r="B44" s="7" t="str">
-        <f t="shared" si="7"/>
-        <v>Lewitus_etal_2014</v>
-      </c>
-      <c r="C44" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>Lewitus</v>
-      </c>
-      <c r="D44" s="9" t="str">
-        <f t="shared" si="9"/>
+      <c r="AI43">
+        <v>7</v>
+      </c>
+      <c r="AK43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B44" s="18" t="str">
+        <f t="shared" ref="B44" si="53">C44 &amp; IF(D44&lt;&gt;"", "_" &amp; D44, "_") &amp; IF(E44&lt;&gt;"", "_" &amp; E44, "_") &amp; IF(F44&lt;&gt;"", "_" &amp; F44, "")</f>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C44" s="19" t="str">
+        <f t="shared" ref="C44" si="54">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A44,","), "-", ""), " ", "")</f>
+        <v>Isler</v>
+      </c>
+      <c r="D44" s="19" t="str">
+        <f t="shared" ref="D44" si="55">IF(ISNUMBER(FIND("&amp;", A44)),
+    IF(LEN(A44)-LEN(SUBSTITUTE(A44, ",", ""))&gt;=3, "etal", MID(A44, SEARCH("&amp; ", A44)+2, SEARCH(",", A44, SEARCH("&amp; ", A44)+2) - SEARCH("&amp; ", A44)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
-      <c r="E44" s="9" t="str">
-        <f t="shared" si="10"/>
-        <v>2014</v>
-      </c>
-      <c r="G44" t="str">
-        <f>_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
-        <v>10.1371/journal.pbio.1002000</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J44" s="3" t="str">
-        <f t="shared" si="6"/>
-        <v>Lewitus_etal_2014_TableS1</v>
-      </c>
-      <c r="K44" s="3" t="str">
-        <f t="shared" si="11"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
-      </c>
-      <c r="N44" t="str" cm="1">
+      <c r="E44" s="19" t="str">
+        <f t="shared" ref="E44" si="56">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A44, "("), ")")</f>
+        <v>2008</v>
+      </c>
+      <c r="F44" s="19"/>
+      <c r="G44" s="17" t="str">
+        <f t="shared" ref="G44" si="57">_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="J44" s="20" t="str">
+        <f t="shared" ref="J44" si="58">TRIM(_xlfn.TEXTJOIN("_",FALSE,B44,(SUBSTITUTE(SUBSTITUTE(I44," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_Tree.nex</v>
+      </c>
+      <c r="K44" s="21" t="str">
+        <f t="shared" ref="K44" si="59">IF(ISBLANK(H44),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
+      </c>
+      <c r="N44" s="17" t="str" cm="1">
         <f t="array" ref="N44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K44, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
-      </c>
-      <c r="O44" t="str" cm="1">
+        <v>notfound</v>
+      </c>
+      <c r="O44" s="17" t="str" cm="1">
         <f t="array" ref="O44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K44, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
-      </c>
-      <c r="P44" s="3" t="s">
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="P44" s="20" t="s">
         <v>49</v>
-      </c>
-      <c r="AI44">
-        <v>9</v>
-      </c>
-      <c r="AK44">
-        <v>20</v>
       </c>
     </row>
     <row r="45" spans="1:37" ht="16" x14ac:dyDescent="0.2">
@@ -5065,22 +5124,19 @@
         <v>230</v>
       </c>
       <c r="B45" s="7" t="str">
-        <f t="shared" ref="B45" si="53">C45 &amp; IF(D45&lt;&gt;"", "_" &amp; D45, "_") &amp; IF(E45&lt;&gt;"", "_" &amp; E45, "_") &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "")</f>
+        <f t="shared" si="7"/>
         <v>Lewitus_etal_2014</v>
       </c>
       <c r="C45" s="9" t="str">
-        <f t="shared" ref="C45" si="54">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
+        <f t="shared" si="8"/>
         <v>Lewitus</v>
       </c>
       <c r="D45" s="9" t="str">
-        <f t="shared" ref="D45" si="55">IF(ISNUMBER(FIND("&amp;", A45)),
-    IF(LEN(A45)-LEN(SUBSTITUTE(A45, ",", ""))&gt;=3, "etal", MID(A45, SEARCH("&amp; ", A45)+2, SEARCH(",", A45, SEARCH("&amp; ", A45)+2) - SEARCH("&amp; ", A45)-2)),
-    ""
-)</f>
+        <f t="shared" si="9"/>
         <v>etal</v>
       </c>
       <c r="E45" s="9" t="str">
-        <f t="shared" ref="E45" si="56">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
+        <f t="shared" si="10"/>
         <v>2014</v>
       </c>
       <c r="G45" t="str">
@@ -5088,19 +5144,19 @@
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>231</v>
+        <v>98</v>
       </c>
       <c r="J45" s="3" t="str">
-        <f t="shared" ref="J45" si="57">TRIM(_xlfn.TEXTJOIN("_",FALSE,B45,(SUBSTITUTE(SUBSTITUTE(I45," ",""), "_", ""))))</f>
-        <v>Lewitus_etal_2014_TableS8</v>
+        <f t="shared" si="6"/>
+        <v>Lewitus_etal_2014_TableS1</v>
       </c>
       <c r="K45" s="3" t="str">
-        <f t="shared" ref="K45" si="58">IF(ISBLANK(H45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+        <f t="shared" si="11"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="N45" t="str" cm="1">
         <f t="array" ref="N45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K45, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="O45" t="str" cm="1">
         <f t="array" ref="O45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K45, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
@@ -5109,124 +5165,127 @@
       <c r="P45" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="X45" t="s">
-        <v>232</v>
-      </c>
       <c r="AI45">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AK45">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="46" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="B46" s="18" t="str">
-        <f t="shared" ref="B46" si="59">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
-        <v>Lewitus_etal_2013</v>
-      </c>
-      <c r="C46" s="19" t="str">
-        <f t="shared" ref="C46" si="60">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" s="7" t="str">
+        <f t="shared" ref="B46" si="60">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="C46" s="9" t="str">
+        <f t="shared" ref="C46" si="61">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
-      <c r="D46" s="19" t="str">
-        <f t="shared" ref="D46" si="61">IF(ISNUMBER(FIND("&amp;", A46)),
+      <c r="D46" s="9" t="str">
+        <f t="shared" ref="D46" si="62">IF(ISNUMBER(FIND("&amp;", A46)),
     IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=3, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E46" s="19" t="str">
-        <f t="shared" ref="E46" si="62">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
-        <v>2013</v>
-      </c>
-      <c r="F46" s="19"/>
-      <c r="G46" s="17" t="str">
+      <c r="E46" s="9" t="str">
+        <f t="shared" ref="E46" si="63">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
+        <v>2014</v>
+      </c>
+      <c r="G46" t="str">
         <f>_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
-        <v>10.3389/fnhum.2013.00424</v>
-      </c>
-      <c r="I46" s="20" t="s">
-        <v>234</v>
-      </c>
-      <c r="J46" s="20" t="str">
-        <f t="shared" ref="J46" si="63">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
-        <v>Lewitus_etal_2013_TableS2partial</v>
-      </c>
-      <c r="K46" s="21" t="str">
-        <f>IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
-      </c>
-      <c r="N46" s="17" t="str" cm="1">
+        <v>10.1371/journal.pbio.1002000</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J46" s="3" t="str">
+        <f t="shared" ref="J46" si="64">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
+        <v>Lewitus_etal_2014_TableS8</v>
+      </c>
+      <c r="K46" s="3" t="str">
+        <f t="shared" ref="K46" si="65">IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+      </c>
+      <c r="N46" t="str" cm="1">
         <f t="array" ref="N46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K46, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
-      </c>
-      <c r="O46" s="17" t="str" cm="1">
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+      </c>
+      <c r="O46" t="str" cm="1">
         <f t="array" ref="O46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K46, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
-      </c>
-      <c r="P46" s="20" t="s">
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+      </c>
+      <c r="P46" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AI46" s="17">
-        <v>7</v>
-      </c>
-      <c r="AK46" s="17">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="47" spans="1:37" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="B47" s="22" t="str">
-        <f t="shared" ref="B47" si="64">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
-        <v>Smaers_etal_2011</v>
-      </c>
-      <c r="C47" s="24" t="str">
-        <f t="shared" ref="C47" si="65">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
-        <v>Smaers</v>
-      </c>
-      <c r="D47" s="24" t="str">
-        <f t="shared" ref="D47" si="66">IF(ISNUMBER(FIND("&amp;", A47)),
+      <c r="X46" t="s">
+        <v>232</v>
+      </c>
+      <c r="AI46">
+        <v>6</v>
+      </c>
+      <c r="AK46">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B47" s="18" t="str">
+        <f t="shared" ref="B47" si="66">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
+        <v>Lewitus_etal_2013</v>
+      </c>
+      <c r="C47" s="19" t="str">
+        <f t="shared" ref="C47" si="67">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
+        <v>Lewitus</v>
+      </c>
+      <c r="D47" s="19" t="str">
+        <f t="shared" ref="D47" si="68">IF(ISNUMBER(FIND("&amp;", A47)),
     IF(LEN(A47)-LEN(SUBSTITUTE(A47, ",", ""))&gt;=3, "etal", MID(A47, SEARCH("&amp; ", A47)+2, SEARCH(",", A47, SEARCH("&amp; ", A47)+2) - SEARCH("&amp; ", A47)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E47" s="24" t="str">
-        <f t="shared" ref="E47" si="67">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
-        <v>2011</v>
-      </c>
-      <c r="F47" s="24"/>
-      <c r="G47" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="I47" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="J47" s="23" t="str">
-        <f t="shared" ref="J47" si="68">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
-      </c>
-      <c r="K47" s="23" t="str">
+      <c r="E47" s="19" t="str">
+        <f t="shared" ref="E47" si="69">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
+        <v>2013</v>
+      </c>
+      <c r="F47" s="19"/>
+      <c r="G47" s="17" t="str">
+        <f>_xlfn.TEXTAFTER(A47,"https://doi.org/")</f>
+        <v>10.3389/fnhum.2013.00424</v>
+      </c>
+      <c r="I47" s="20" t="s">
+        <v>234</v>
+      </c>
+      <c r="J47" s="20" t="str">
+        <f t="shared" ref="J47" si="70">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
+        <v>Lewitus_etal_2013_TableS2partial</v>
+      </c>
+      <c r="K47" s="21" t="str">
         <f>IF(ISBLANK(H47),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
-      </c>
-      <c r="N47" s="15" t="str" cm="1">
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
+      </c>
+      <c r="N47" s="17" t="str" cm="1">
         <f t="array" ref="N47">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K47, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="O47" s="15" t="str" cm="1">
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+      </c>
+      <c r="O47" s="17" t="str" cm="1">
         <f t="array" ref="O47">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K47, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="P47" s="23" t="s">
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+      </c>
+      <c r="P47" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="AI47" s="15" t="s">
-        <v>238</v>
+      <c r="AI47" s="17">
+        <v>7</v>
+      </c>
+      <c r="AK47" s="17">
+        <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:37" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -5234,22 +5293,22 @@
         <v>235</v>
       </c>
       <c r="B48" s="22" t="str">
-        <f t="shared" ref="B48" si="69">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
+        <f t="shared" ref="B48" si="71">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="C48" s="24" t="str">
-        <f t="shared" ref="C48" si="70">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C48" si="72">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
       <c r="D48" s="24" t="str">
-        <f t="shared" ref="D48" si="71">IF(ISNUMBER(FIND("&amp;", A48)),
+        <f t="shared" ref="D48" si="73">IF(ISNUMBER(FIND("&amp;", A48)),
     IF(LEN(A48)-LEN(SUBSTITUTE(A48, ",", ""))&gt;=3, "etal", MID(A48, SEARCH("&amp; ", A48)+2, SEARCH(",", A48, SEARCH("&amp; ", A48)+2) - SEARCH("&amp; ", A48)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E48" s="24" t="str">
-        <f t="shared" ref="E48" si="72">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
+        <f t="shared" ref="E48" si="74">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
         <v>2011</v>
       </c>
       <c r="F48" s="24"/>
@@ -5257,19 +5316,19 @@
         <v>236</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="J48" s="23" t="str">
-        <f t="shared" ref="J48" si="73">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
+        <f t="shared" ref="J48" si="75">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="K48" s="23" t="str">
         <f>IF(ISBLANK(H48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="N48" s="15" t="str" cm="1">
         <f t="array" ref="N48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K48, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="O48" s="15" t="str" cm="1">
         <f t="array" ref="O48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K48, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
@@ -5279,6 +5338,59 @@
         <v>49</v>
       </c>
       <c r="AI48" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:35" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B49" s="22" t="str">
+        <f t="shared" ref="B49" si="76">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="C49" s="24" t="str">
+        <f t="shared" ref="C49" si="77">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
+        <v>Smaers</v>
+      </c>
+      <c r="D49" s="24" t="str">
+        <f t="shared" ref="D49" si="78">IF(ISNUMBER(FIND("&amp;", A49)),
+    IF(LEN(A49)-LEN(SUBSTITUTE(A49, ",", ""))&gt;=3, "etal", MID(A49, SEARCH("&amp; ", A49)+2, SEARCH(",", A49, SEARCH("&amp; ", A49)+2) - SEARCH("&amp; ", A49)-2)),
+    ""
+)</f>
+        <v>etal</v>
+      </c>
+      <c r="E49" s="24" t="str">
+        <f t="shared" ref="E49" si="79">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
+        <v>2011</v>
+      </c>
+      <c r="F49" s="24"/>
+      <c r="G49" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="J49" s="23" t="str">
+        <f t="shared" ref="J49" si="80">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
+      </c>
+      <c r="K49" s="23" t="str">
+        <f>IF(ISBLANK(H49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
+      </c>
+      <c r="N49" s="15" t="str" cm="1">
+        <f t="array" ref="N49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K49, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+      </c>
+      <c r="O49" s="15" t="str" cm="1">
+        <f t="array" ref="O49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K49, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+      </c>
+      <c r="P49" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI49" s="15" t="s">
         <v>238</v>
       </c>
     </row>
@@ -5290,12 +5402,12 @@
     <hyperlink ref="W7" r:id="rId3" xr:uid="{5C533C8B-7E31-6247-B07A-DA36A2ECB804}"/>
     <hyperlink ref="W8" r:id="rId4" xr:uid="{C7A27B14-F289-2345-8125-B9AE06601A7B}"/>
     <hyperlink ref="W10" r:id="rId5" xr:uid="{BC8CFBF1-94B9-B04B-B168-9B969B0A4C7D}"/>
-    <hyperlink ref="W28" r:id="rId6" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
-    <hyperlink ref="W29" r:id="rId7" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
+    <hyperlink ref="W29" r:id="rId6" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
+    <hyperlink ref="W30" r:id="rId7" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
     <hyperlink ref="W14" r:id="rId8" xr:uid="{9534F0D1-7C63-EC4F-921C-5D21474866A4}"/>
     <hyperlink ref="W15:W18" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{0070BD27-D760-3846-9F0D-91BB5EDD333F}"/>
-    <hyperlink ref="W27" r:id="rId10" xr:uid="{FD223821-8B74-3345-B8A9-FA7536E78F2E}"/>
-    <hyperlink ref="W26" r:id="rId11" xr:uid="{8FF3DE15-909D-F043-B90F-3D2A3402F9DE}"/>
+    <hyperlink ref="W28" r:id="rId10" xr:uid="{FD223821-8B74-3345-B8A9-FA7536E78F2E}"/>
+    <hyperlink ref="W27" r:id="rId11" xr:uid="{8FF3DE15-909D-F043-B90F-3D2A3402F9DE}"/>
     <hyperlink ref="W25" r:id="rId12" xr:uid="{236492C9-FC3A-614B-84DC-0D56063EE72E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5481,6 +5593,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
@@ -5491,7 +5612,7 @@
 </p:properties>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -5734,16 +5855,15 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
@@ -5760,7 +5880,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26276598-8A19-40B6-BED3-157936C93058}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5777,12 +5897,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Species/Evo-M1-Trait-Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1B0C5D4-7D06-DB44-A210-C6BFA5FA6EB8}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-5960" windowWidth="45100" windowHeight="20500" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20140" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
   <externalReferences>
     <externalReference r:id="rId4"/>
   </externalReferences>
-  <calcPr calcId="191028" refMode="R1C1" iterateCount="0" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -1609,7 +1609,7 @@
     <col min="22" max="22" width="22.1640625" customWidth="1"/>
     <col min="23" max="23" width="14.33203125" customWidth="1"/>
     <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="22" customWidth="1"/>
+    <col min="25" max="25" width="39.5" customWidth="1"/>
     <col min="26" max="26" width="11.1640625" customWidth="1"/>
     <col min="27" max="27" width="5" customWidth="1"/>
     <col min="28" max="28" width="7.5" customWidth="1"/>
@@ -1739,7 +1739,7 @@
         <v>36</v>
       </c>
       <c r="B2" s="7" t="str">
-        <f t="shared" ref="B2" si="0">C2 &amp; IF(D2&lt;&gt;"", "_" &amp; D2, "_") &amp; IF(E2&lt;&gt;"", "_" &amp; E2, "_") &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "")</f>
+        <f>C2 &amp; IF(D2&lt;&gt;"", "_" &amp; D2, "_") &amp; IF(E2&lt;&gt;"", "_" &amp; E2, "_") &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "")</f>
         <v>_ProjectKaskan__Unpublished</v>
       </c>
       <c r="C2" s="9" t="str">
@@ -1754,11 +1754,11 @@
         <v/>
       </c>
       <c r="E2" s="9" t="str">
-        <f t="shared" ref="E2" si="1">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
+        <f t="shared" ref="E2" si="0">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
         <v>Unpublished</v>
       </c>
       <c r="G2" t="e">
-        <f t="shared" ref="G2" si="2">_xlfn.TEXTAFTER(A2,"https://doi.org/")</f>
+        <f t="shared" ref="G2" si="1">_xlfn.TEXTAFTER(A2,"https://doi.org/")</f>
         <v>#N/A</v>
       </c>
       <c r="H2" s="3"/>
@@ -1813,7 +1813,7 @@
         <v>45</v>
       </c>
       <c r="B3" s="7" t="str">
-        <f t="shared" ref="B3" si="3">C3 &amp; IF(D3&lt;&gt;"", "_" &amp; D3, "_") &amp; IF(E3&lt;&gt;"", "_" &amp; E3, "_") &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "")</f>
+        <f t="shared" ref="B3" si="2">C3 &amp; IF(D3&lt;&gt;"", "_" &amp; D3, "_") &amp; IF(E3&lt;&gt;"", "_" &amp; E3, "_") &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "")</f>
         <v>Burger_etal_2019</v>
       </c>
       <c r="C3" s="9" t="str">
@@ -1828,11 +1828,11 @@
         <v>etal</v>
       </c>
       <c r="E3" s="9" t="str">
-        <f t="shared" ref="E3" si="4">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
+        <f t="shared" ref="E3" si="3">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G38" si="5">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
+        <f t="shared" ref="G3:G38" si="4">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
         <v>10.1093/jmammal/gyz043</v>
       </c>
       <c r="H3" s="3"/>
@@ -1840,7 +1840,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3" t="str">
-        <f t="shared" ref="J3:J45" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
+        <f t="shared" ref="J3:J45" si="5">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
       <c r="K3" s="21" t="str">
@@ -1908,26 +1908,26 @@
         <v>58</v>
       </c>
       <c r="B4" s="7" t="str">
-        <f t="shared" ref="B4:B45" si="7">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
+        <f t="shared" ref="B4:B45" si="6">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="C4" s="9" t="str">
-        <f t="shared" ref="C4:C45" si="8">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C4:C45" si="7">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
         <v>Caspar</v>
       </c>
       <c r="D4" s="9" t="str">
-        <f t="shared" ref="D4:D45" si="9">IF(ISNUMBER(FIND("&amp;", A4)),
+        <f t="shared" ref="D4:D45" si="8">IF(ISNUMBER(FIND("&amp;", A4)),
     IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=3, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E4" s="9" t="str">
-        <f t="shared" ref="E4:E45" si="10">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+        <f t="shared" ref="E4:E45" si="9">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
         <v>2022</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="H4" s="10"/>
@@ -1935,11 +1935,11 @@
         <v>59</v>
       </c>
       <c r="J4" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="K4" s="3" t="str">
-        <f t="shared" ref="K4:K45" si="11">IF(ISBLANK(H4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K4:K45" si="10">IF(ISBLANK(H4),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H4, SUBSTITUTE(I4,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="L4" s="3"/>
@@ -2005,23 +2005,23 @@
         <v>58</v>
       </c>
       <c r="B5" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Caspar_etal_2022</v>
+      </c>
+      <c r="C5" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Caspar_etal_2022</v>
-      </c>
-      <c r="C5" s="9" t="str">
+        <v>Caspar</v>
+      </c>
+      <c r="D5" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Caspar</v>
-      </c>
-      <c r="D5" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E5" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E5" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2022</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="H5" s="12"/>
@@ -2029,11 +2029,11 @@
         <v>72</v>
       </c>
       <c r="J5" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="K5" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="L5" s="12"/>
@@ -2097,23 +2097,23 @@
         <v>79</v>
       </c>
       <c r="B6" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Changizi__2001</v>
+      </c>
+      <c r="C6" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Changizi__2001</v>
-      </c>
-      <c r="C6" s="9" t="str">
+        <v>Changizi</v>
+      </c>
+      <c r="D6" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Changizi</v>
-      </c>
-      <c r="D6" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E6" s="9" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E6" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1007/s004220000205</v>
       </c>
       <c r="H6" s="12"/>
@@ -2121,11 +2121,11 @@
         <v>80</v>
       </c>
       <c r="J6" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Changizi__2001_Figure3</v>
       </c>
       <c r="K6" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="L6" s="12"/>
@@ -2181,24 +2181,24 @@
         <v>89</v>
       </c>
       <c r="B7" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Chen_etal_2020</v>
+      </c>
+      <c r="C7" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Chen_etal_2020</v>
-      </c>
-      <c r="C7" s="9" t="str">
+        <v>Chen</v>
+      </c>
+      <c r="D7" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Chen</v>
-      </c>
-      <c r="D7" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E7" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E7" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2020</v>
       </c>
       <c r="F7" s="7"/>
       <c r="G7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1038/s41467-020-14356-3</v>
       </c>
       <c r="H7" s="3"/>
@@ -2206,11 +2206,11 @@
         <v>90</v>
       </c>
       <c r="J7" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Chen_etal_2020_SupplementaryData3</v>
       </c>
       <c r="K7" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
       <c r="L7" s="3"/>
@@ -2278,23 +2278,23 @@
         <v>97</v>
       </c>
       <c r="B8" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>DosSantos_etal_2017</v>
+      </c>
+      <c r="C8" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>DosSantos_etal_2017</v>
-      </c>
-      <c r="C8" s="9" t="str">
+        <v>DosSantos</v>
+      </c>
+      <c r="D8" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="D8" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E8" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E8" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2017</v>
       </c>
       <c r="G8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000452856</v>
       </c>
       <c r="H8" s="3"/>
@@ -2302,11 +2302,11 @@
         <v>98</v>
       </c>
       <c r="J8" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="K8" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="L8" s="3" t="s">
@@ -2378,23 +2378,23 @@
         <v>110</v>
       </c>
       <c r="B9" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>DosSantos_etal_2020</v>
+      </c>
+      <c r="C9" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>DosSantos_etal_2020</v>
-      </c>
-      <c r="C9" s="9" t="str">
+        <v>DosSantos</v>
+      </c>
+      <c r="D9" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="D9" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E9" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E9" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2020</v>
       </c>
       <c r="G9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="H9" s="3"/>
@@ -2402,11 +2402,11 @@
         <v>59</v>
       </c>
       <c r="J9" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>DosSantos_etal_2020_Table1</v>
       </c>
       <c r="K9" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
       <c r="L9" s="3"/>
@@ -2467,24 +2467,24 @@
         <v>116</v>
       </c>
       <c r="B10" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Finlay_etal_2006</v>
+      </c>
+      <c r="C10" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Finlay_etal_2006</v>
-      </c>
-      <c r="C10" s="9" t="str">
+        <v>Finlay</v>
+      </c>
+      <c r="D10" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Finlay</v>
-      </c>
-      <c r="D10" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E10" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E10" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2006</v>
       </c>
       <c r="F10" s="7"/>
       <c r="G10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="H10" s="3"/>
@@ -2492,7 +2492,7 @@
         <v>117</v>
       </c>
       <c r="J10" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Finlay_etal_2006_Table6.1</v>
       </c>
       <c r="K10" s="3" t="str">
@@ -2560,24 +2560,24 @@
         <v>124</v>
       </c>
       <c r="B11" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Heffner_etal_1975</v>
+      </c>
+      <c r="C11" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Heffner_etal_1975</v>
-      </c>
-      <c r="C11" s="9" t="str">
+        <v>Heffner</v>
+      </c>
+      <c r="D11" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Heffner</v>
-      </c>
-      <c r="D11" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E11" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E11" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>1975</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000124401</v>
       </c>
       <c r="H11" s="3"/>
@@ -2585,11 +2585,11 @@
         <v>125</v>
       </c>
       <c r="J11" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Heffner_etal_1975_TableI</v>
       </c>
       <c r="K11" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="L11" s="3"/>
@@ -2650,24 +2650,24 @@
         <v>131</v>
       </c>
       <c r="B12" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Heffner_etal_1983</v>
+      </c>
+      <c r="C12" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Heffner_etal_1983</v>
-      </c>
-      <c r="C12" s="9" t="str">
+        <v>Heffner</v>
+      </c>
+      <c r="D12" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Heffner</v>
-      </c>
-      <c r="D12" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E12" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E12" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>1983</v>
       </c>
       <c r="F12" s="7"/>
       <c r="G12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000121494</v>
       </c>
       <c r="H12" s="3"/>
@@ -2675,11 +2675,11 @@
         <v>125</v>
       </c>
       <c r="J12" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Heffner_etal_1983_TableI</v>
       </c>
       <c r="K12" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000121494_TableI</v>
       </c>
       <c r="L12" s="3"/>
@@ -2724,24 +2724,24 @@
         <v>134</v>
       </c>
       <c r="B13" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Heldstab_etal_2016</v>
+      </c>
+      <c r="C13" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Heldstab_etal_2016</v>
-      </c>
-      <c r="C13" s="9" t="str">
+        <v>Heldstab</v>
+      </c>
+      <c r="D13" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Heldstab</v>
-      </c>
-      <c r="D13" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E13" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E13" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2016</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1038/srep24528</v>
       </c>
       <c r="H13" s="3"/>
@@ -2749,11 +2749,11 @@
         <v>98</v>
       </c>
       <c r="J13" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Heldstab_etal_2016_TableS1</v>
       </c>
       <c r="K13" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
       <c r="L13" s="3"/>
@@ -2795,23 +2795,23 @@
         <v>136</v>
       </c>
       <c r="B14" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="C14" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="C14" s="9" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D14" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D14" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E14" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E14" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="G14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H14" s="3"/>
@@ -2819,11 +2819,11 @@
         <v>59</v>
       </c>
       <c r="J14" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
       <c r="K14" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000437413_Table1</v>
       </c>
       <c r="L14" s="3"/>
@@ -2889,24 +2889,24 @@
         <v>136</v>
       </c>
       <c r="B15" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="C15" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="C15" s="9" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D15" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D15" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E15" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E15" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H15" s="3"/>
@@ -2914,11 +2914,11 @@
         <v>142</v>
       </c>
       <c r="J15" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
       <c r="K15" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000437413_Table2</v>
       </c>
       <c r="L15" s="3"/>
@@ -2984,24 +2984,24 @@
         <v>136</v>
       </c>
       <c r="B16" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="C16" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="C16" s="9" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D16" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D16" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E16" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E16" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="F16" s="7"/>
       <c r="G16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H16" s="3"/>
@@ -3009,11 +3009,11 @@
         <v>146</v>
       </c>
       <c r="J16" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
       <c r="K16" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000437413_Table3</v>
       </c>
       <c r="L16" s="3"/>
@@ -3079,24 +3079,24 @@
         <v>136</v>
       </c>
       <c r="B17" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="C17" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="C17" s="9" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D17" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D17" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E17" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E17" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="F17" s="7"/>
       <c r="G17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H17" s="3"/>
@@ -3104,11 +3104,11 @@
         <v>150</v>
       </c>
       <c r="J17" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
       <c r="K17" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000437413_Table4</v>
       </c>
       <c r="L17" s="3"/>
@@ -3174,24 +3174,24 @@
         <v>136</v>
       </c>
       <c r="B18" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2015</v>
+      </c>
+      <c r="C18" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2015</v>
-      </c>
-      <c r="C18" s="9" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D18" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D18" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E18" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E18" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H18" s="3"/>
@@ -3199,11 +3199,11 @@
         <v>154</v>
       </c>
       <c r="J18" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
       <c r="K18" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000437413_Table5</v>
       </c>
       <c r="L18" s="3"/>
@@ -3269,24 +3269,24 @@
         <v>158</v>
       </c>
       <c r="B19" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="C19" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2020</v>
-      </c>
-      <c r="C19" s="9" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D19" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D19" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E19" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E19" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2020</v>
       </c>
       <c r="F19" s="7"/>
       <c r="G19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="H19" s="3"/>
@@ -3294,11 +3294,11 @@
         <v>159</v>
       </c>
       <c r="J19" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="K19" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
       <c r="L19" s="3"/>
@@ -3364,24 +3364,24 @@
         <v>158</v>
       </c>
       <c r="B20" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="C20" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2020</v>
-      </c>
-      <c r="C20" s="9" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D20" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D20" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E20" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E20" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2020</v>
       </c>
       <c r="F20" s="7"/>
       <c r="G20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="H20" s="3"/>
@@ -3389,11 +3389,11 @@
         <v>165</v>
       </c>
       <c r="J20" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
       <c r="K20" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
       <c r="L20" s="3"/>
@@ -3459,23 +3459,23 @@
         <v>170</v>
       </c>
       <c r="B21" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="C21" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="C21" s="9" t="str">
+        <v>Iwaniuk</v>
+      </c>
+      <c r="D21" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="D21" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E21" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E21" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H21" s="3"/>
@@ -3483,11 +3483,11 @@
         <v>59</v>
       </c>
       <c r="J21" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Iwaniuk_etal_2001_Table1</v>
       </c>
       <c r="K21" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
       <c r="L21" s="3"/>
@@ -3531,23 +3531,23 @@
         <v>170</v>
       </c>
       <c r="B22" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="C22" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="C22" s="9" t="str">
+        <v>Iwaniuk</v>
+      </c>
+      <c r="D22" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="D22" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E22" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E22" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H22" s="3"/>
@@ -3555,11 +3555,11 @@
         <v>142</v>
       </c>
       <c r="J22" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Iwaniuk_etal_2001_Table2</v>
       </c>
       <c r="K22" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
       <c r="L22" s="3"/>
@@ -3603,23 +3603,23 @@
         <v>170</v>
       </c>
       <c r="B23" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="C23" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="C23" s="9" t="str">
+        <v>Iwaniuk</v>
+      </c>
+      <c r="D23" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="D23" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E23" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E23" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H23" s="3"/>
@@ -3627,11 +3627,11 @@
         <v>146</v>
       </c>
       <c r="J23" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Iwaniuk_etal_2001_Table3</v>
       </c>
       <c r="K23" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
       <c r="L23" s="3"/>
@@ -3675,23 +3675,23 @@
         <v>170</v>
       </c>
       <c r="B24" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="C24" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="C24" s="9" t="str">
+        <v>Iwaniuk</v>
+      </c>
+      <c r="D24" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="D24" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E24" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E24" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2001</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H24" s="3"/>
@@ -3699,11 +3699,11 @@
         <v>150</v>
       </c>
       <c r="J24" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Iwaniuk_etal_2001_Table4</v>
       </c>
       <c r="K24" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="L24" s="3"/>
@@ -3747,23 +3747,23 @@
         <v>178</v>
       </c>
       <c r="B25" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>JardimMesseder_etal_2017</v>
+      </c>
+      <c r="C25" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>JardimMesseder_etal_2017</v>
-      </c>
-      <c r="C25" s="9" t="str">
+        <v>JardimMesseder</v>
+      </c>
+      <c r="D25" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>JardimMesseder</v>
-      </c>
-      <c r="D25" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E25" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E25" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2017</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.3389/fnana.2017.00118</v>
       </c>
       <c r="H25" s="3"/>
@@ -3771,11 +3771,11 @@
         <v>59</v>
       </c>
       <c r="J25" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>JardimMesseder_etal_2017_Table1</v>
       </c>
       <c r="K25" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
       <c r="L25" s="3"/>
@@ -3844,27 +3844,27 @@
         <v>184</v>
       </c>
       <c r="B26" s="7" t="str">
-        <f t="shared" ref="B26" si="12">C26 &amp; IF(D26&lt;&gt;"", "_" &amp; D26, "_") &amp; IF(E26&lt;&gt;"", "_" &amp; E26, "_") &amp; IF(F26&lt;&gt;"", "_" &amp; F26, "")</f>
+        <f t="shared" ref="B26" si="11">C26 &amp; IF(D26&lt;&gt;"", "_" &amp; D26, "_") &amp; IF(E26&lt;&gt;"", "_" &amp; E26, "_") &amp; IF(F26&lt;&gt;"", "_" &amp; F26, "")</f>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="C26" s="9" t="str">
-        <f t="shared" ref="C26" si="13">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A26,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C26" si="12">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A26,","), "-", ""), " ", "")</f>
         <v>Kverkova</v>
       </c>
       <c r="D26" s="9" t="str">
-        <f t="shared" ref="D26" si="14">IF(ISNUMBER(FIND("&amp;", A26)),
+        <f t="shared" ref="D26" si="13">IF(ISNUMBER(FIND("&amp;", A26)),
     IF(LEN(A26)-LEN(SUBSTITUTE(A26, ",", ""))&gt;=3, "etal", MID(A26, SEARCH("&amp; ", A26)+2, SEARCH(",", A26, SEARCH("&amp; ", A26)+2) - SEARCH("&amp; ", A26)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E26" s="9" t="str">
-        <f t="shared" ref="E26" si="15">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A26, "("), ")")</f>
+        <f t="shared" ref="E26" si="14">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A26, "("), ")")</f>
         <v>2018</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" t="str">
-        <f t="shared" ref="G26" si="16">_xlfn.TEXTAFTER(A26,"https://doi.org/")</f>
+        <f t="shared" ref="G26" si="15">_xlfn.TEXTAFTER(A26,"https://doi.org/")</f>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H26" s="3"/>
@@ -3872,11 +3872,11 @@
         <v>59</v>
       </c>
       <c r="J26" s="3" t="str">
-        <f t="shared" ref="J26" si="17">TRIM(_xlfn.TEXTJOIN("_",FALSE,B26,(SUBSTITUTE(SUBSTITUTE(I26," ",""), "_", ""))))</f>
+        <f t="shared" ref="J26" si="16">TRIM(_xlfn.TEXTJOIN("_",FALSE,B26,(SUBSTITUTE(SUBSTITUTE(I26," ",""), "_", ""))))</f>
         <v>Kverkova_etal_2018_Table1</v>
       </c>
       <c r="K26" s="3" t="str">
-        <f t="shared" ref="K26" si="18">IF(ISBLANK(H26),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K26" si="17">IF(ISBLANK(H26),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="L26" s="3"/>
@@ -3937,24 +3937,24 @@
         <v>184</v>
       </c>
       <c r="B27" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="C27" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Kverkova_etal_2018</v>
-      </c>
-      <c r="C27" s="9" t="str">
+        <v>Kverkova</v>
+      </c>
+      <c r="D27" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Kverkova</v>
-      </c>
-      <c r="D27" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E27" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E27" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2018</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H27" s="3"/>
@@ -3962,11 +3962,11 @@
         <v>98</v>
       </c>
       <c r="J27" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="K27" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="L27" s="3"/>
@@ -4032,24 +4032,24 @@
         <v>184</v>
       </c>
       <c r="B28" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="C28" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Kverkova_etal_2018</v>
-      </c>
-      <c r="C28" s="9" t="str">
+        <v>Kverkova</v>
+      </c>
+      <c r="D28" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Kverkova</v>
-      </c>
-      <c r="D28" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E28" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E28" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2018</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H28" s="3"/>
@@ -4057,11 +4057,11 @@
         <v>191</v>
       </c>
       <c r="J28" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="K28" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="L28" s="3"/>
@@ -4127,24 +4127,24 @@
         <v>195</v>
       </c>
       <c r="B29" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>ManyPrimates__2022</v>
+      </c>
+      <c r="C29" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>ManyPrimates__2022</v>
-      </c>
-      <c r="C29" s="9" t="str">
+        <v>ManyPrimates</v>
+      </c>
+      <c r="D29" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>ManyPrimates</v>
-      </c>
-      <c r="D29" s="9" t="str">
+        <v/>
+      </c>
+      <c r="E29" s="9" t="str">
         <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="E29" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2022</v>
       </c>
       <c r="F29" s="7"/>
       <c r="G29" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.26451/abc.09.04.06.2022</v>
       </c>
       <c r="H29" s="3"/>
@@ -4152,11 +4152,11 @@
         <v>196</v>
       </c>
       <c r="J29" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="K29" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="L29" s="3"/>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="Q29" s="14"/>
       <c r="S29" t="str">
-        <f t="shared" ref="S29:S34" si="19">IF(R29="N", Q29, "write file name")</f>
+        <f t="shared" ref="S29:S34" si="18">IF(R29="N", Q29, "write file name")</f>
         <v>write file name</v>
       </c>
       <c r="T29" t="s">
@@ -4210,24 +4210,24 @@
         <v>201</v>
       </c>
       <c r="B30" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Powell_etal_2017</v>
+      </c>
+      <c r="C30" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Powell_etal_2017</v>
-      </c>
-      <c r="C30" s="9" t="str">
+        <v>Powell</v>
+      </c>
+      <c r="D30" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Powell</v>
-      </c>
-      <c r="D30" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E30" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E30" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2017</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1098/rspb.2017.1765</v>
       </c>
       <c r="H30" s="3" t="s">
@@ -4237,11 +4237,11 @@
         <v>203</v>
       </c>
       <c r="J30" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="K30" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="L30" s="3"/>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="Q30" s="14"/>
       <c r="S30" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>write file name</v>
       </c>
       <c r="T30" t="s">
@@ -4295,26 +4295,26 @@
         <v>206</v>
       </c>
       <c r="B31" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="C31" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Sherwood_etal_2004_I</v>
-      </c>
-      <c r="C31" s="9" t="str">
+        <v>Sherwood</v>
+      </c>
+      <c r="D31" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Sherwood</v>
-      </c>
-      <c r="D31" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E31" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E31" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2004</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>207</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="H31" s="3"/>
@@ -4322,11 +4322,11 @@
         <v>150</v>
       </c>
       <c r="J31" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="K31" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="L31" s="3"/>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="Q31" s="14"/>
       <c r="S31" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>write file name</v>
       </c>
       <c r="T31" t="s">
@@ -4373,26 +4373,26 @@
         <v>206</v>
       </c>
       <c r="B32" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="C32" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Sherwood_etal_2004_I</v>
-      </c>
-      <c r="C32" s="9" t="str">
+        <v>Sherwood</v>
+      </c>
+      <c r="D32" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Sherwood</v>
-      </c>
-      <c r="D32" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E32" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E32" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2004</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>207</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="H32" s="3"/>
@@ -4400,11 +4400,11 @@
         <v>154</v>
       </c>
       <c r="J32" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="K32" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="L32" s="3"/>
@@ -4424,7 +4424,7 @@
       </c>
       <c r="Q32" s="14"/>
       <c r="S32" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>write file name</v>
       </c>
       <c r="T32" t="s">
@@ -4451,24 +4451,24 @@
         <v>212</v>
       </c>
       <c r="B33" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Winkler_etal_2021</v>
+      </c>
+      <c r="C33" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Winkler_etal_2021</v>
-      </c>
-      <c r="C33" s="9" t="str">
+        <v>Winkler</v>
+      </c>
+      <c r="D33" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Winkler</v>
-      </c>
-      <c r="D33" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E33" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E33" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2021</v>
       </c>
       <c r="F33" s="7"/>
       <c r="G33" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1080/09524622.2021.1905065</v>
       </c>
       <c r="H33" s="3"/>
@@ -4476,11 +4476,11 @@
         <v>213</v>
       </c>
       <c r="J33" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Winkler_etal_2021_Figure1</v>
       </c>
       <c r="K33" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="L33" s="3"/>
@@ -4500,7 +4500,7 @@
       </c>
       <c r="Q33" s="14"/>
       <c r="S33" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>write file name</v>
       </c>
       <c r="T33" t="s">
@@ -4522,24 +4522,24 @@
         <v>216</v>
       </c>
       <c r="B34" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="C34" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Young_etal_2013</v>
-      </c>
-      <c r="C34" s="9" t="str">
+        <v>Young</v>
+      </c>
+      <c r="D34" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Young</v>
-      </c>
-      <c r="D34" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E34" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E34" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2013</v>
       </c>
       <c r="F34" s="7"/>
       <c r="G34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.3389/fncir.2013.00030</v>
       </c>
       <c r="H34" s="3"/>
@@ -4547,11 +4547,11 @@
         <v>59</v>
       </c>
       <c r="J34" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Young_etal_2013_Table1</v>
       </c>
       <c r="K34" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
       <c r="L34" s="3"/>
@@ -4571,7 +4571,7 @@
       </c>
       <c r="Q34" s="14"/>
       <c r="S34" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>write file name</v>
       </c>
       <c r="T34" t="s">
@@ -4593,34 +4593,34 @@
         <v>218</v>
       </c>
       <c r="B35" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Mota_etal_2015</v>
+      </c>
+      <c r="C35" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Mota_etal_2015</v>
-      </c>
-      <c r="C35" s="9" t="str">
+        <v>Mota</v>
+      </c>
+      <c r="D35" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Mota</v>
-      </c>
-      <c r="D35" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E35" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E35" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2015</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.1126/science.aaa9101</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>98</v>
       </c>
       <c r="J35" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Mota_etal_2015_TableS1</v>
       </c>
       <c r="K35" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="N35" t="str" cm="1">
@@ -4646,34 +4646,34 @@
         <v>219</v>
       </c>
       <c r="B36" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>HerculanoHouzel_etal_2013</v>
+      </c>
+      <c r="C36" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="C36" s="9" t="str">
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D36" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D36" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E36" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E36" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2013</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>220</v>
       </c>
       <c r="J36" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="K36" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="N36" t="str" cm="1">
@@ -4696,37 +4696,37 @@
         <v>219</v>
       </c>
       <c r="B37" s="7" t="str">
-        <f t="shared" ref="B37" si="20">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
+        <f t="shared" ref="B37" si="19">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C37" s="9" t="str">
-        <f t="shared" ref="C37" si="21">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C37" si="20">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f t="shared" ref="D37" si="22">IF(ISNUMBER(FIND("&amp;", A37)),
+        <f t="shared" ref="D37" si="21">IF(ISNUMBER(FIND("&amp;", A37)),
     IF(LEN(A37)-LEN(SUBSTITUTE(A37, ",", ""))&gt;=3, "etal", MID(A37, SEARCH("&amp; ", A37)+2, SEARCH(",", A37, SEARCH("&amp; ", A37)+2) - SEARCH("&amp; ", A37)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E37" s="9" t="str">
-        <f t="shared" ref="E37" si="23">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
+        <f t="shared" ref="E37" si="22">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="G37" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I37" s="3" t="s">
         <v>222</v>
       </c>
       <c r="J37" s="3" t="str">
-        <f t="shared" ref="J37" si="24">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
+        <f t="shared" ref="J37" si="23">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
         <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
       <c r="K37" s="3" t="str">
-        <f t="shared" ref="K37" si="25">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K37" si="24">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
       <c r="N37" t="str" cm="1">
@@ -4749,37 +4749,37 @@
         <v>219</v>
       </c>
       <c r="B38" s="7" t="str">
-        <f t="shared" ref="B38" si="26">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
+        <f t="shared" ref="B38" si="25">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C38" s="9" t="str">
-        <f t="shared" ref="C38" si="27">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C38" si="26">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D38" s="9" t="str">
-        <f t="shared" ref="D38" si="28">IF(ISNUMBER(FIND("&amp;", A38)),
+        <f t="shared" ref="D38" si="27">IF(ISNUMBER(FIND("&amp;", A38)),
     IF(LEN(A38)-LEN(SUBSTITUTE(A38, ",", ""))&gt;=3, "etal", MID(A38, SEARCH("&amp; ", A38)+2, SEARCH(",", A38, SEARCH("&amp; ", A38)+2) - SEARCH("&amp; ", A38)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E38" s="9" t="str">
-        <f t="shared" ref="E38" si="29">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
+        <f t="shared" ref="E38" si="28">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="G38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="4"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I38" s="3" t="s">
         <v>223</v>
       </c>
       <c r="J38" s="3" t="str">
-        <f t="shared" ref="J38" si="30">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
+        <f t="shared" ref="J38" si="29">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
         <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
       <c r="K38" s="3" t="str">
-        <f t="shared" ref="K38" si="31">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K38" si="30">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
       <c r="N38" t="str" cm="1">
@@ -4802,37 +4802,37 @@
         <v>224</v>
       </c>
       <c r="B39" s="7" t="str">
-        <f t="shared" ref="B39" si="32">C39 &amp; IF(D39&lt;&gt;"", "_" &amp; D39, "_") &amp; IF(E39&lt;&gt;"", "_" &amp; E39, "_") &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "")</f>
+        <f t="shared" ref="B39" si="31">C39 &amp; IF(D39&lt;&gt;"", "_" &amp; D39, "_") &amp; IF(E39&lt;&gt;"", "_" &amp; E39, "_") &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C39" s="9" t="str">
-        <f t="shared" ref="C39" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A39,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C39" si="32">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A39,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D39" s="9" t="str">
-        <f t="shared" ref="D39" si="34">IF(ISNUMBER(FIND("&amp;", A39)),
+        <f t="shared" ref="D39" si="33">IF(ISNUMBER(FIND("&amp;", A39)),
     IF(LEN(A39)-LEN(SUBSTITUTE(A39, ",", ""))&gt;=3, "etal", MID(A39, SEARCH("&amp; ", A39)+2, SEARCH(",", A39, SEARCH("&amp; ", A39)+2) - SEARCH("&amp; ", A39)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E39" s="9" t="str">
-        <f t="shared" ref="E39" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, "("), ")")</f>
+        <f t="shared" ref="E39" si="34">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="G39" t="str">
-        <f t="shared" ref="G39" si="36">_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
+        <f t="shared" ref="G39" si="35">_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I39" s="3" t="s">
         <v>142</v>
       </c>
       <c r="J39" s="3" t="str">
-        <f t="shared" ref="J39" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,B39,(SUBSTITUTE(SUBSTITUTE(I39," ",""), "_", ""))))</f>
+        <f t="shared" ref="J39" si="36">TRIM(_xlfn.TEXTJOIN("_",FALSE,B39,(SUBSTITUTE(SUBSTITUTE(I39," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Table2</v>
       </c>
       <c r="K39" s="3" t="str">
-        <f t="shared" ref="K39" si="38">IF(ISBLANK(H39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K39" si="37">IF(ISBLANK(H39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
       <c r="N39" t="str" cm="1">
@@ -4858,19 +4858,19 @@
         <v>224</v>
       </c>
       <c r="B40" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C40" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="C40" s="9" t="str">
+        <v>Isler</v>
+      </c>
+      <c r="D40" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Isler</v>
-      </c>
-      <c r="D40" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E40" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E40" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2008</v>
       </c>
       <c r="G40" t="str">
@@ -4881,11 +4881,11 @@
         <v>225</v>
       </c>
       <c r="J40" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Isler_etal_2008_Table7</v>
       </c>
       <c r="K40" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
       </c>
       <c r="N40" t="str" cm="1">
@@ -4911,19 +4911,19 @@
         <v>224</v>
       </c>
       <c r="B41" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C41" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="C41" s="9" t="str">
+        <v>Isler</v>
+      </c>
+      <c r="D41" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Isler</v>
-      </c>
-      <c r="D41" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E41" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E41" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2008</v>
       </c>
       <c r="G41" t="str">
@@ -4934,11 +4934,11 @@
         <v>98</v>
       </c>
       <c r="J41" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Isler_etal_2008_TableS1</v>
       </c>
       <c r="K41" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
       </c>
       <c r="N41" t="str" cm="1">
@@ -4961,37 +4961,37 @@
         <v>224</v>
       </c>
       <c r="B42" s="7" t="str">
-        <f t="shared" ref="B42" si="39">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
+        <f t="shared" ref="B42" si="38">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C42" s="9" t="str">
-        <f t="shared" ref="C42" si="40">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C42" si="39">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D42" s="9" t="str">
-        <f t="shared" ref="D42" si="41">IF(ISNUMBER(FIND("&amp;", A42)),
+        <f t="shared" ref="D42" si="40">IF(ISNUMBER(FIND("&amp;", A42)),
     IF(LEN(A42)-LEN(SUBSTITUTE(A42, ",", ""))&gt;=3, "etal", MID(A42, SEARCH("&amp; ", A42)+2, SEARCH(",", A42, SEARCH("&amp; ", A42)+2) - SEARCH("&amp; ", A42)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E42" s="9" t="str">
-        <f t="shared" ref="E42" si="42">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
+        <f t="shared" ref="E42" si="41">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="G42" t="str">
-        <f t="shared" ref="G42" si="43">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
+        <f t="shared" ref="G42" si="42">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>227</v>
       </c>
       <c r="J42" s="3" t="str">
-        <f t="shared" ref="J42" si="44">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
+        <f t="shared" ref="J42" si="43">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="K42" s="3" t="str">
-        <f t="shared" ref="K42" si="45">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K42" si="44">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="N42" t="str" cm="1">
@@ -5017,37 +5017,37 @@
         <v>224</v>
       </c>
       <c r="B43" s="7" t="str">
-        <f t="shared" ref="B43" si="46">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
+        <f t="shared" ref="B43" si="45">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C43" s="9" t="str">
-        <f t="shared" ref="C43" si="47">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C43" si="46">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D43" s="9" t="str">
-        <f t="shared" ref="D43" si="48">IF(ISNUMBER(FIND("&amp;", A43)),
+        <f t="shared" ref="D43" si="47">IF(ISNUMBER(FIND("&amp;", A43)),
     IF(LEN(A43)-LEN(SUBSTITUTE(A43, ",", ""))&gt;=3, "etal", MID(A43, SEARCH("&amp; ", A43)+2, SEARCH(",", A43, SEARCH("&amp; ", A43)+2) - SEARCH("&amp; ", A43)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E43" s="9" t="str">
-        <f t="shared" ref="E43" si="49">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
+        <f t="shared" ref="E43" si="48">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="G43" t="str">
-        <f t="shared" ref="G43" si="50">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
+        <f t="shared" ref="G43" si="49">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I43" s="3" t="s">
         <v>228</v>
       </c>
       <c r="J43" s="3" t="str">
-        <f t="shared" ref="J43" si="51">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
+        <f t="shared" ref="J43" si="50">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS3</v>
       </c>
       <c r="K43" s="3" t="str">
-        <f t="shared" ref="K43" si="52">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K43" si="51">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
       <c r="N43" t="str" cm="1">
@@ -5073,38 +5073,38 @@
         <v>224</v>
       </c>
       <c r="B44" s="18" t="str">
-        <f t="shared" ref="B44" si="53">C44 &amp; IF(D44&lt;&gt;"", "_" &amp; D44, "_") &amp; IF(E44&lt;&gt;"", "_" &amp; E44, "_") &amp; IF(F44&lt;&gt;"", "_" &amp; F44, "")</f>
+        <f t="shared" ref="B44" si="52">C44 &amp; IF(D44&lt;&gt;"", "_" &amp; D44, "_") &amp; IF(E44&lt;&gt;"", "_" &amp; E44, "_") &amp; IF(F44&lt;&gt;"", "_" &amp; F44, "")</f>
         <v>Isler_etal_2008</v>
       </c>
       <c r="C44" s="19" t="str">
-        <f t="shared" ref="C44" si="54">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A44,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C44" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A44,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
       <c r="D44" s="19" t="str">
-        <f t="shared" ref="D44" si="55">IF(ISNUMBER(FIND("&amp;", A44)),
+        <f t="shared" ref="D44" si="54">IF(ISNUMBER(FIND("&amp;", A44)),
     IF(LEN(A44)-LEN(SUBSTITUTE(A44, ",", ""))&gt;=3, "etal", MID(A44, SEARCH("&amp; ", A44)+2, SEARCH(",", A44, SEARCH("&amp; ", A44)+2) - SEARCH("&amp; ", A44)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E44" s="19" t="str">
-        <f t="shared" ref="E44" si="56">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A44, "("), ")")</f>
+        <f t="shared" ref="E44" si="55">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A44, "("), ")")</f>
         <v>2008</v>
       </c>
       <c r="F44" s="19"/>
       <c r="G44" s="17" t="str">
-        <f t="shared" ref="G44" si="57">_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
+        <f t="shared" ref="G44" si="56">_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I44" s="20" t="s">
         <v>229</v>
       </c>
       <c r="J44" s="20" t="str">
-        <f t="shared" ref="J44" si="58">TRIM(_xlfn.TEXTJOIN("_",FALSE,B44,(SUBSTITUTE(SUBSTITUTE(I44," ",""), "_", ""))))</f>
+        <f t="shared" ref="J44" si="57">TRIM(_xlfn.TEXTJOIN("_",FALSE,B44,(SUBSTITUTE(SUBSTITUTE(I44," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Tree.nex</v>
       </c>
       <c r="K44" s="21" t="str">
-        <f t="shared" ref="K44" si="59">IF(ISBLANK(H44),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K44" si="58">IF(ISBLANK(H44),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="N44" s="17" t="str" cm="1">
@@ -5124,19 +5124,19 @@
         <v>230</v>
       </c>
       <c r="B45" s="7" t="str">
+        <f t="shared" si="6"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="C45" s="9" t="str">
         <f t="shared" si="7"/>
-        <v>Lewitus_etal_2014</v>
-      </c>
-      <c r="C45" s="9" t="str">
+        <v>Lewitus</v>
+      </c>
+      <c r="D45" s="9" t="str">
         <f t="shared" si="8"/>
-        <v>Lewitus</v>
-      </c>
-      <c r="D45" s="9" t="str">
+        <v>etal</v>
+      </c>
+      <c r="E45" s="9" t="str">
         <f t="shared" si="9"/>
-        <v>etal</v>
-      </c>
-      <c r="E45" s="9" t="str">
-        <f t="shared" si="10"/>
         <v>2014</v>
       </c>
       <c r="G45" t="str">
@@ -5147,11 +5147,11 @@
         <v>98</v>
       </c>
       <c r="J45" s="3" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>Lewitus_etal_2014_TableS1</v>
       </c>
       <c r="K45" s="3" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="N45" t="str" cm="1">
@@ -5177,22 +5177,22 @@
         <v>230</v>
       </c>
       <c r="B46" s="7" t="str">
-        <f t="shared" ref="B46" si="60">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
+        <f t="shared" ref="B46" si="59">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
         <v>Lewitus_etal_2014</v>
       </c>
       <c r="C46" s="9" t="str">
-        <f t="shared" ref="C46" si="61">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C46" si="60">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
       <c r="D46" s="9" t="str">
-        <f t="shared" ref="D46" si="62">IF(ISNUMBER(FIND("&amp;", A46)),
+        <f t="shared" ref="D46" si="61">IF(ISNUMBER(FIND("&amp;", A46)),
     IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=3, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E46" s="9" t="str">
-        <f t="shared" ref="E46" si="63">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
+        <f t="shared" ref="E46" si="62">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
         <v>2014</v>
       </c>
       <c r="G46" t="str">
@@ -5203,11 +5203,11 @@
         <v>231</v>
       </c>
       <c r="J46" s="3" t="str">
-        <f t="shared" ref="J46" si="64">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
+        <f t="shared" ref="J46" si="63">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2014_TableS8</v>
       </c>
       <c r="K46" s="3" t="str">
-        <f t="shared" ref="K46" si="65">IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="K46" si="64">IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="N46" t="str" cm="1">
@@ -5236,22 +5236,22 @@
         <v>233</v>
       </c>
       <c r="B47" s="18" t="str">
-        <f t="shared" ref="B47" si="66">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
+        <f t="shared" ref="B47" si="65">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
         <v>Lewitus_etal_2013</v>
       </c>
       <c r="C47" s="19" t="str">
-        <f t="shared" ref="C47" si="67">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C47" si="66">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
       <c r="D47" s="19" t="str">
-        <f t="shared" ref="D47" si="68">IF(ISNUMBER(FIND("&amp;", A47)),
+        <f t="shared" ref="D47" si="67">IF(ISNUMBER(FIND("&amp;", A47)),
     IF(LEN(A47)-LEN(SUBSTITUTE(A47, ",", ""))&gt;=3, "etal", MID(A47, SEARCH("&amp; ", A47)+2, SEARCH(",", A47, SEARCH("&amp; ", A47)+2) - SEARCH("&amp; ", A47)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E47" s="19" t="str">
-        <f t="shared" ref="E47" si="69">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
+        <f t="shared" ref="E47" si="68">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="F47" s="19"/>
@@ -5263,7 +5263,7 @@
         <v>234</v>
       </c>
       <c r="J47" s="20" t="str">
-        <f t="shared" ref="J47" si="70">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
+        <f t="shared" ref="J47" si="69">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
       <c r="K47" s="21" t="str">
@@ -5293,22 +5293,22 @@
         <v>235</v>
       </c>
       <c r="B48" s="22" t="str">
-        <f t="shared" ref="B48" si="71">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
+        <f t="shared" ref="B48" si="70">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="C48" s="24" t="str">
-        <f t="shared" ref="C48" si="72">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C48" si="71">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
       <c r="D48" s="24" t="str">
-        <f t="shared" ref="D48" si="73">IF(ISNUMBER(FIND("&amp;", A48)),
+        <f t="shared" ref="D48" si="72">IF(ISNUMBER(FIND("&amp;", A48)),
     IF(LEN(A48)-LEN(SUBSTITUTE(A48, ",", ""))&gt;=3, "etal", MID(A48, SEARCH("&amp; ", A48)+2, SEARCH(",", A48, SEARCH("&amp; ", A48)+2) - SEARCH("&amp; ", A48)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E48" s="24" t="str">
-        <f t="shared" ref="E48" si="74">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
+        <f t="shared" ref="E48" si="73">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
         <v>2011</v>
       </c>
       <c r="F48" s="24"/>
@@ -5319,7 +5319,7 @@
         <v>237</v>
       </c>
       <c r="J48" s="23" t="str">
-        <f t="shared" ref="J48" si="75">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
+        <f t="shared" ref="J48" si="74">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="K48" s="23" t="str">
@@ -5346,22 +5346,22 @@
         <v>235</v>
       </c>
       <c r="B49" s="22" t="str">
-        <f t="shared" ref="B49" si="76">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
+        <f t="shared" ref="B49" si="75">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="C49" s="24" t="str">
-        <f t="shared" ref="C49" si="77">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C49" si="76">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
       <c r="D49" s="24" t="str">
-        <f t="shared" ref="D49" si="78">IF(ISNUMBER(FIND("&amp;", A49)),
+        <f t="shared" ref="D49" si="77">IF(ISNUMBER(FIND("&amp;", A49)),
     IF(LEN(A49)-LEN(SUBSTITUTE(A49, ",", ""))&gt;=3, "etal", MID(A49, SEARCH("&amp; ", A49)+2, SEARCH(",", A49, SEARCH("&amp; ", A49)+2) - SEARCH("&amp; ", A49)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E49" s="24" t="str">
-        <f t="shared" ref="E49" si="79">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
+        <f t="shared" ref="E49" si="78">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
         <v>2011</v>
       </c>
       <c r="F49" s="24"/>
@@ -5372,7 +5372,7 @@
         <v>239</v>
       </c>
       <c r="J49" s="23" t="str">
-        <f t="shared" ref="J49" si="80">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
+        <f t="shared" ref="J49" si="79">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="K49" s="23" t="str">
@@ -5593,15 +5593,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
@@ -5610,6 +5601,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5856,26 +5856,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A1B0C5D4-7D06-DB44-A210-C6BFA5FA6EB8}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17DA8DA6-16B6-C54B-9DC1-33E8AE2A2DCE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20140" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="557" uniqueCount="278">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -2708,6 +2708,9 @@
       <c r="U12" t="s">
         <v>53</v>
       </c>
+      <c r="V12" t="s">
+        <v>85</v>
+      </c>
       <c r="X12" s="7"/>
       <c r="Y12" t="s">
         <v>128</v>
@@ -5593,15 +5596,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
@@ -5610,6 +5604,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5856,26 +5859,26 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10211"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10311"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{32752C55-B6BF-A242-9DFD-CB091070879E}"/>
+  <xr:revisionPtr revIDLastSave="73" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E6B17D0-2911-AA42-BCCE-08D385DE0529}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-5960" windowWidth="34680" windowHeight="18920" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="34560" yWindow="-5960" windowWidth="38400" windowHeight="17420" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="561" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="290">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -903,6 +903,36 @@
   </si>
   <si>
     <t>L</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iwaniuk, A. N., Pellis, S. M., &amp; Whishaw, I. Q. (1999). Is digital dexterity really related to corticospinal projections?: a re-analysis of the Heffner and Masterton data set using modern comparative statistics. Behav Brain Res, 101(2), 173-187. https://doi.org/10.1016/s0166-4328(98)00151-x 	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Genoud, M., Isler, K., &amp; Martin, R. D. (2018). Comparative analyses of basal rate of metabolism in mammals: data selection does matter. Biol Rev Camb Philos Soc, 93(1), 404-438. https://doi.org/10.1111/brv.12350 	</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mota, B., Dos Santos, S. E., Ventura-Antunes, L., Jardim-Messeder, D., Neves, K., Kazu, R. S., Noctor, S., Lambert, K., Bertelsen, M. F., Manger, P. R., Sherwood, C. C., Kaas, J. H., &amp; Herculano-Houzel, S. (2019). White matter volume and white/gray matter ratio in mammalian species as a consequence of the universal scaling of cortical folding. Proc Natl Acad Sci U S A, 116(30), 15253-15261. https://doi.org/10.1073/pnas.1716956116 	</t>
+  </si>
+  <si>
+    <t>10.1159/000323672</t>
+  </si>
+  <si>
+    <t>10.1159/000323673</t>
+  </si>
+  <si>
+    <t>Supplementary Table S1. Morphometrical and cell number data used in this study (“our dataset”).</t>
+  </si>
+  <si>
+    <t>Supplementary Table S1</t>
+  </si>
+  <si>
+    <t>Table S2. Basal metabolic rate (BMR) database.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Burish, M. J., Peebles, J. K., Baldwin, M. K., Tavares, L., Kaas, J. H., &amp; Herculano-Houzel, S. (2010). Cellular scaling rules for primate spinal cords. Brain Behav Evol, 76(1), 45-59. https://doi.org/10.1159/000319019 </t>
+  </si>
+  <si>
+    <t>Table 1. Cellular composition of the spinal cord</t>
   </si>
 </sst>
 </file>
@@ -1596,12 +1626,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AK49"/>
+  <dimension ref="A1:AK53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.5" customWidth="1"/>
+    <col min="1" max="1" width="36.6640625" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" style="9" customWidth="1"/>
-    <col min="3" max="6" width="2.1640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" style="9" customWidth="1"/>
+    <col min="4" max="4" width="15" style="9" customWidth="1"/>
+    <col min="5" max="6" width="2.1640625" style="9" customWidth="1"/>
     <col min="7" max="8" width="2.1640625" customWidth="1"/>
     <col min="9" max="9" width="17.1640625" customWidth="1"/>
     <col min="10" max="10" width="31.1640625" customWidth="1"/>
@@ -1754,7 +1786,7 @@
       </c>
       <c r="D2" s="9" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A2)),
-    IF(LEN(A2)-LEN(SUBSTITUTE(A2, ",", ""))&gt;=3, "etal", MID(A2, SEARCH("&amp; ", A2)+2, SEARCH(",", A2, SEARCH("&amp; ", A2)+2) - SEARCH("&amp; ", A2)-2)),
+    IF(LEN(A2)-LEN(SUBSTITUTE(A2, ",", ""))&gt;=6, "etal", MID(A2, SEARCH("&amp; ", A2)+2, SEARCH(",", A2, SEARCH("&amp; ", A2)+2) - SEARCH("&amp; ", A2)-2)),
     ""
 )</f>
         <v/>
@@ -1827,18 +1859,18 @@
         <v>Burger</v>
       </c>
       <c r="D3" s="9" t="str">
-        <f>IF(ISNUMBER(FIND("&amp;", A3)),
-    IF(LEN(A3)-LEN(SUBSTITUTE(A3, ",", ""))&gt;=3, "etal", MID(A3, SEARCH("&amp; ", A3)+2, SEARCH(",", A3, SEARCH("&amp; ", A3)+2) - SEARCH("&amp; ", A3)-2)),
+        <f t="shared" ref="D3:D49" si="3">IF(ISNUMBER(FIND("&amp;", A3)),
+    IF(LEN(A3)-LEN(SUBSTITUTE(A3, ",", ""))&gt;=6, "etal", MID(A3, SEARCH("&amp; ", A3)+2, SEARCH(",", A3, SEARCH("&amp; ", A3)+2) - SEARCH("&amp; ", A3)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E3" s="9" t="str">
-        <f t="shared" ref="E3" si="3">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
+        <f t="shared" ref="E3" si="4">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="G3" t="str">
-        <f t="shared" ref="G3:G38" si="4">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
+        <f t="shared" ref="G3:G38" si="5">_xlfn.TEXTAFTER(A3,"https://doi.org/")</f>
         <v>10.1093/jmammal/gyz043</v>
       </c>
       <c r="H3" s="3"/>
@@ -1846,7 +1878,7 @@
         <v>46</v>
       </c>
       <c r="J3" s="3" t="str">
-        <f t="shared" ref="J3:J45" si="5">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
+        <f t="shared" ref="J3:J45" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
       <c r="K3" s="21" t="str">
@@ -1914,18 +1946,15 @@
         <v>58</v>
       </c>
       <c r="B4" s="7" t="str">
-        <f t="shared" ref="B4:B45" si="6">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
+        <f t="shared" ref="B4:B45" si="7">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="C4" s="9" t="str">
-        <f t="shared" ref="C4:C45" si="7">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C4:C45" si="8">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
         <v>Caspar</v>
       </c>
       <c r="D4" s="9" t="str">
-        <f t="shared" ref="D4:D45" si="8">IF(ISNUMBER(FIND("&amp;", A4)),
-    IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=3, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
-    ""
-)</f>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E4" s="9" t="str">
@@ -1933,7 +1962,7 @@
         <v>2022</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="H4" s="10"/>
@@ -1941,7 +1970,7 @@
         <v>59</v>
       </c>
       <c r="J4" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="K4" s="3" t="str">
@@ -2011,15 +2040,15 @@
         <v>58</v>
       </c>
       <c r="B5" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="C5" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Caspar</v>
       </c>
       <c r="D5" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E5" s="9" t="str">
@@ -2027,7 +2056,7 @@
         <v>2022</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="H5" s="12"/>
@@ -2035,7 +2064,7 @@
         <v>72</v>
       </c>
       <c r="J5" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="K5" s="3" t="str">
@@ -2103,15 +2132,15 @@
         <v>79</v>
       </c>
       <c r="B6" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Changizi__2001</v>
       </c>
       <c r="C6" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Changizi</v>
       </c>
       <c r="D6" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="E6" s="9" t="str">
@@ -2119,7 +2148,7 @@
         <v>2001</v>
       </c>
       <c r="G6" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1007/s004220000205</v>
       </c>
       <c r="H6" s="12"/>
@@ -2127,7 +2156,7 @@
         <v>80</v>
       </c>
       <c r="J6" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Changizi__2001_Figure3</v>
       </c>
       <c r="K6" s="3" t="str">
@@ -2187,16 +2216,16 @@
         <v>89</v>
       </c>
       <c r="B7" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>Chen_etal_2020</v>
+        <f t="shared" si="7"/>
+        <v>Chen_Wiens_2020</v>
       </c>
       <c r="C7" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Chen</v>
       </c>
       <c r="D7" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
+        <f t="shared" si="3"/>
+        <v>Wiens</v>
       </c>
       <c r="E7" s="9" t="str">
         <f t="shared" si="9"/>
@@ -2204,7 +2233,7 @@
       </c>
       <c r="F7" s="7"/>
       <c r="G7" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1038/s41467-020-14356-3</v>
       </c>
       <c r="H7" s="3"/>
@@ -2212,8 +2241,8 @@
         <v>90</v>
       </c>
       <c r="J7" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Chen_etal_2020_SupplementaryData3</v>
+        <f t="shared" si="6"/>
+        <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
       <c r="K7" s="3" t="str">
         <f t="shared" si="10"/>
@@ -2284,15 +2313,15 @@
         <v>97</v>
       </c>
       <c r="B8" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>DosSantos_etal_2017</v>
       </c>
       <c r="C8" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>DosSantos</v>
       </c>
       <c r="D8" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E8" s="9" t="str">
@@ -2300,7 +2329,7 @@
         <v>2017</v>
       </c>
       <c r="G8" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000452856</v>
       </c>
       <c r="H8" s="3"/>
@@ -2308,7 +2337,7 @@
         <v>98</v>
       </c>
       <c r="J8" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="K8" s="3" t="str">
@@ -2384,15 +2413,15 @@
         <v>110</v>
       </c>
       <c r="B9" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>DosSantos_etal_2020</v>
       </c>
       <c r="C9" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>DosSantos</v>
       </c>
       <c r="D9" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E9" s="9" t="str">
@@ -2400,7 +2429,7 @@
         <v>2020</v>
       </c>
       <c r="G9" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="H9" s="3"/>
@@ -2408,7 +2437,7 @@
         <v>59</v>
       </c>
       <c r="J9" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>DosSantos_etal_2020_Table1</v>
       </c>
       <c r="K9" s="3" t="str">
@@ -2473,15 +2502,15 @@
         <v>116</v>
       </c>
       <c r="B10" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Finlay_etal_2006</v>
       </c>
       <c r="C10" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Finlay</v>
       </c>
       <c r="D10" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E10" s="9" t="str">
@@ -2490,7 +2519,7 @@
       </c>
       <c r="F10" s="7"/>
       <c r="G10" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="H10" s="3"/>
@@ -2498,7 +2527,7 @@
         <v>117</v>
       </c>
       <c r="J10" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Finlay_etal_2006_Table6.1</v>
       </c>
       <c r="K10" s="3" t="str">
@@ -2566,16 +2595,16 @@
         <v>124</v>
       </c>
       <c r="B11" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>Heffner_etal_1975</v>
+        <f>C11 &amp; IF(D11&lt;&gt;"", "_" &amp; D11, "_") &amp; IF(E11&lt;&gt;"", "_" &amp; E11, "_") &amp; IF(F11&lt;&gt;"", "_" &amp; F11, "")</f>
+        <v>Heffner_Masterton_1975</v>
       </c>
       <c r="C11" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Heffner</v>
       </c>
       <c r="D11" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
+        <f t="shared" si="3"/>
+        <v>Masterton</v>
       </c>
       <c r="E11" s="9" t="str">
         <f t="shared" si="9"/>
@@ -2583,7 +2612,7 @@
       </c>
       <c r="F11" s="7"/>
       <c r="G11" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000124401</v>
       </c>
       <c r="H11" s="3"/>
@@ -2591,8 +2620,8 @@
         <v>125</v>
       </c>
       <c r="J11" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Heffner_etal_1975_TableI</v>
+        <f t="shared" si="6"/>
+        <v>Heffner_Masterton_1975_TableI</v>
       </c>
       <c r="K11" s="3" t="str">
         <f t="shared" si="10"/>
@@ -2656,16 +2685,16 @@
         <v>131</v>
       </c>
       <c r="B12" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>Heffner_etal_1983</v>
+        <f t="shared" si="7"/>
+        <v>Heffner_Masterton_1983</v>
       </c>
       <c r="C12" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Heffner</v>
       </c>
       <c r="D12" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
+        <f t="shared" si="3"/>
+        <v>Masterton</v>
       </c>
       <c r="E12" s="9" t="str">
         <f t="shared" si="9"/>
@@ -2673,7 +2702,7 @@
       </c>
       <c r="F12" s="7"/>
       <c r="G12" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000121494</v>
       </c>
       <c r="H12" s="3"/>
@@ -2681,8 +2710,8 @@
         <v>125</v>
       </c>
       <c r="J12" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Heffner_etal_1983_TableI</v>
+        <f t="shared" si="6"/>
+        <v>Heffner_Masterton_1983_TableI</v>
       </c>
       <c r="K12" s="3" t="str">
         <f t="shared" si="10"/>
@@ -2733,15 +2762,15 @@
         <v>134</v>
       </c>
       <c r="B13" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Heldstab_etal_2016</v>
       </c>
       <c r="C13" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Heldstab</v>
       </c>
       <c r="D13" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E13" s="9" t="str">
@@ -2750,7 +2779,7 @@
       </c>
       <c r="F13" s="7"/>
       <c r="G13" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1038/srep24528</v>
       </c>
       <c r="H13" s="3"/>
@@ -2758,7 +2787,7 @@
         <v>98</v>
       </c>
       <c r="J13" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Heldstab_etal_2016_TableS1</v>
       </c>
       <c r="K13" s="3" t="str">
@@ -2804,15 +2833,15 @@
         <v>136</v>
       </c>
       <c r="B14" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C14" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D14" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E14" s="9" t="str">
@@ -2820,7 +2849,7 @@
         <v>2015</v>
       </c>
       <c r="G14" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H14" s="3"/>
@@ -2828,7 +2857,7 @@
         <v>59</v>
       </c>
       <c r="J14" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
       <c r="K14" s="3" t="str">
@@ -2898,15 +2927,18 @@
         <v>136</v>
       </c>
       <c r="B15" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C15" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D15" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(ISNUMBER(FIND("&amp;", A15)),
+    IF(LEN(A15)-LEN(SUBSTITUTE(A15, ",", ""))&gt;=6, "etal", MID(A15, SEARCH("&amp; ", A15)+2, SEARCH(",", A15, SEARCH("&amp; ", A15)+2) - SEARCH("&amp; ", A15)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
       <c r="E15" s="9" t="str">
@@ -2915,7 +2947,7 @@
       </c>
       <c r="F15" s="7"/>
       <c r="G15" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H15" s="3"/>
@@ -2923,7 +2955,7 @@
         <v>142</v>
       </c>
       <c r="J15" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
       <c r="K15" s="3" t="str">
@@ -2993,15 +3025,15 @@
         <v>136</v>
       </c>
       <c r="B16" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C16" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D16" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E16" s="9" t="str">
@@ -3010,7 +3042,7 @@
       </c>
       <c r="F16" s="7"/>
       <c r="G16" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H16" s="3"/>
@@ -3018,7 +3050,7 @@
         <v>146</v>
       </c>
       <c r="J16" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
       <c r="K16" s="3" t="str">
@@ -3088,15 +3120,15 @@
         <v>136</v>
       </c>
       <c r="B17" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C17" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D17" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E17" s="9" t="str">
@@ -3105,7 +3137,7 @@
       </c>
       <c r="F17" s="7"/>
       <c r="G17" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H17" s="3"/>
@@ -3113,7 +3145,7 @@
         <v>150</v>
       </c>
       <c r="J17" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
       <c r="K17" s="3" t="str">
@@ -3183,15 +3215,15 @@
         <v>136</v>
       </c>
       <c r="B18" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="C18" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D18" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E18" s="9" t="str">
@@ -3200,7 +3232,7 @@
       </c>
       <c r="F18" s="7"/>
       <c r="G18" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="H18" s="3"/>
@@ -3208,7 +3240,7 @@
         <v>154</v>
       </c>
       <c r="J18" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
       <c r="K18" s="3" t="str">
@@ -3278,15 +3310,15 @@
         <v>158</v>
       </c>
       <c r="B19" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="C19" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D19" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E19" s="9" t="str">
@@ -3295,7 +3327,7 @@
       </c>
       <c r="F19" s="7"/>
       <c r="G19" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="H19" s="3"/>
@@ -3303,7 +3335,7 @@
         <v>159</v>
       </c>
       <c r="J19" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="K19" s="3" t="str">
@@ -3373,15 +3405,15 @@
         <v>158</v>
       </c>
       <c r="B20" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="C20" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D20" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E20" s="9" t="str">
@@ -3390,7 +3422,7 @@
       </c>
       <c r="F20" s="7"/>
       <c r="G20" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1002/cne.24985</v>
       </c>
       <c r="H20" s="3"/>
@@ -3398,7 +3430,7 @@
         <v>165</v>
       </c>
       <c r="J20" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
       <c r="K20" s="3" t="str">
@@ -3468,15 +3500,18 @@
         <v>170</v>
       </c>
       <c r="B21" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="C21" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Iwaniuk</v>
       </c>
       <c r="D21" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(ISNUMBER(FIND("&amp;", A21)),
+    IF(LEN(A21)-LEN(SUBSTITUTE(A21, ",", ""))&gt;=6, "etal", MID(A21, SEARCH("&amp; ", A21)+2, SEARCH(",", A21, SEARCH("&amp; ", A21)+2) - SEARCH("&amp; ", A21)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
       <c r="E21" s="9" t="str">
@@ -3484,7 +3519,7 @@
         <v>2001</v>
       </c>
       <c r="G21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H21" s="3"/>
@@ -3492,7 +3527,7 @@
         <v>59</v>
       </c>
       <c r="J21" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Iwaniuk_etal_2001_Table1</v>
       </c>
       <c r="K21" s="3" t="str">
@@ -3540,15 +3575,15 @@
         <v>170</v>
       </c>
       <c r="B22" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="C22" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Iwaniuk</v>
       </c>
       <c r="D22" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E22" s="9" t="str">
@@ -3556,7 +3591,7 @@
         <v>2001</v>
       </c>
       <c r="G22" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H22" s="3"/>
@@ -3564,7 +3599,7 @@
         <v>142</v>
       </c>
       <c r="J22" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Iwaniuk_etal_2001_Table2</v>
       </c>
       <c r="K22" s="3" t="str">
@@ -3612,15 +3647,15 @@
         <v>170</v>
       </c>
       <c r="B23" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="C23" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Iwaniuk</v>
       </c>
       <c r="D23" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E23" s="9" t="str">
@@ -3628,7 +3663,7 @@
         <v>2001</v>
       </c>
       <c r="G23" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H23" s="3"/>
@@ -3636,7 +3671,7 @@
         <v>146</v>
       </c>
       <c r="J23" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Iwaniuk_etal_2001_Table3</v>
       </c>
       <c r="K23" s="3" t="str">
@@ -3684,15 +3719,15 @@
         <v>170</v>
       </c>
       <c r="B24" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="C24" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Iwaniuk</v>
       </c>
       <c r="D24" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E24" s="9" t="str">
@@ -3700,7 +3735,7 @@
         <v>2001</v>
       </c>
       <c r="G24" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="H24" s="3"/>
@@ -3708,7 +3743,7 @@
         <v>150</v>
       </c>
       <c r="J24" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Iwaniuk_etal_2001_Table4</v>
       </c>
       <c r="K24" s="3" t="str">
@@ -3756,15 +3791,15 @@
         <v>178</v>
       </c>
       <c r="B25" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>JardimMesseder_etal_2017</v>
       </c>
       <c r="C25" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>JardimMesseder</v>
       </c>
       <c r="D25" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E25" s="9" t="str">
@@ -3772,7 +3807,7 @@
         <v>2017</v>
       </c>
       <c r="G25" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.3389/fnana.2017.00118</v>
       </c>
       <c r="H25" s="3"/>
@@ -3780,7 +3815,7 @@
         <v>59</v>
       </c>
       <c r="J25" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>JardimMesseder_etal_2017_Table1</v>
       </c>
       <c r="K25" s="3" t="str">
@@ -3861,109 +3896,109 @@
         <v>Kverkova</v>
       </c>
       <c r="D26" s="9" t="str">
-        <f t="shared" ref="D26" si="13">IF(ISNUMBER(FIND("&amp;", A26)),
-    IF(LEN(A26)-LEN(SUBSTITUTE(A26, ",", ""))&gt;=3, "etal", MID(A26, SEARCH("&amp; ", A26)+2, SEARCH(",", A26, SEARCH("&amp; ", A26)+2) - SEARCH("&amp; ", A26)-2)),
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E26" s="9" t="str">
+        <f t="shared" ref="E26" si="13">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A26, "("), ")")</f>
+        <v>2018</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" t="str">
+        <f t="shared" ref="G26" si="14">_xlfn.TEXTAFTER(A26,"https://doi.org/")</f>
+        <v>10.1038/s41598-018-26062-8</v>
+      </c>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J26" s="3" t="str">
+        <f t="shared" ref="J26" si="15">TRIM(_xlfn.TEXTJOIN("_",FALSE,B26,(SUBSTITUTE(SUBSTITUTE(I26," ",""), "_", ""))))</f>
+        <v>Kverkova_etal_2018_Table1</v>
+      </c>
+      <c r="K26" s="3" t="str">
+        <f t="shared" ref="K26" si="16">IF(ISBLANK(H26),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
+      </c>
+      <c r="L26" s="3"/>
+      <c r="M26" t="s">
+        <v>48</v>
+      </c>
+      <c r="N26" t="str" cm="1">
+        <f t="array" ref="N26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+      </c>
+      <c r="O26" t="str" cm="1">
+        <f t="array" ref="O26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K26, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+      </c>
+      <c r="P26" t="s">
+        <v>60</v>
+      </c>
+      <c r="Q26" s="14" t="s">
+        <v>275</v>
+      </c>
+      <c r="R26" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="S26" t="s">
+        <v>185</v>
+      </c>
+      <c r="T26" t="s">
+        <v>186</v>
+      </c>
+      <c r="U26" t="s">
+        <v>53</v>
+      </c>
+      <c r="W26" s="8"/>
+      <c r="X26" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="Y26" t="s">
+        <v>274</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>107</v>
+      </c>
+      <c r="AE26" t="s">
+        <v>190</v>
+      </c>
+      <c r="AI26">
+        <v>1</v>
+      </c>
+      <c r="AK26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>184</v>
+      </c>
+      <c r="B27" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="C27" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v>Kverkova</v>
+      </c>
+      <c r="D27" s="9" t="str">
+        <f>IF(ISNUMBER(FIND("&amp;", A27)),
+    IF(LEN(A27)-LEN(SUBSTITUTE(A27, ",", ""))&gt;=6, "etal", MID(A27, SEARCH("&amp; ", A27)+2, SEARCH(",", A27, SEARCH("&amp; ", A27)+2) - SEARCH("&amp; ", A27)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E26" s="9" t="str">
-        <f t="shared" ref="E26" si="14">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A26, "("), ")")</f>
-        <v>2018</v>
-      </c>
-      <c r="F26" s="7"/>
-      <c r="G26" t="str">
-        <f t="shared" ref="G26" si="15">_xlfn.TEXTAFTER(A26,"https://doi.org/")</f>
-        <v>10.1038/s41598-018-26062-8</v>
-      </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="J26" s="3" t="str">
-        <f t="shared" ref="J26" si="16">TRIM(_xlfn.TEXTJOIN("_",FALSE,B26,(SUBSTITUTE(SUBSTITUTE(I26," ",""), "_", ""))))</f>
-        <v>Kverkova_etal_2018_Table1</v>
-      </c>
-      <c r="K26" s="3" t="str">
-        <f t="shared" ref="K26" si="17">IF(ISBLANK(H26),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H26, SUBSTITUTE(I26,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
-      </c>
-      <c r="L26" s="3"/>
-      <c r="M26" t="s">
-        <v>48</v>
-      </c>
-      <c r="N26" t="str" cm="1">
-        <f t="array" ref="N26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
-      </c>
-      <c r="O26" t="str" cm="1">
-        <f t="array" ref="O26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K26, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
-      </c>
-      <c r="P26" t="s">
-        <v>60</v>
-      </c>
-      <c r="Q26" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="R26" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S26" t="s">
-        <v>185</v>
-      </c>
-      <c r="T26" t="s">
-        <v>186</v>
-      </c>
-      <c r="U26" t="s">
-        <v>53</v>
-      </c>
-      <c r="W26" s="8"/>
-      <c r="X26" s="7" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y26" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z26" t="s">
-        <v>106</v>
-      </c>
-      <c r="AB26" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE26" t="s">
-        <v>190</v>
-      </c>
-      <c r="AI26">
-        <v>1</v>
-      </c>
-      <c r="AK26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
-        <v>184</v>
-      </c>
-      <c r="B27" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>Kverkova_etal_2018</v>
-      </c>
-      <c r="C27" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Kverkova</v>
-      </c>
-      <c r="D27" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
-      </c>
       <c r="E27" s="9" t="str">
         <f t="shared" si="9"/>
         <v>2018</v>
       </c>
       <c r="F27" s="7"/>
       <c r="G27" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H27" s="3"/>
@@ -3971,7 +4006,7 @@
         <v>98</v>
       </c>
       <c r="J27" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="K27" s="3" t="str">
@@ -4041,15 +4076,15 @@
         <v>184</v>
       </c>
       <c r="B28" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Kverkova_etal_2018</v>
       </c>
       <c r="C28" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Kverkova</v>
       </c>
       <c r="D28" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E28" s="9" t="str">
@@ -4058,7 +4093,7 @@
       </c>
       <c r="F28" s="7"/>
       <c r="G28" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="H28" s="3"/>
@@ -4066,7 +4101,7 @@
         <v>191</v>
       </c>
       <c r="J28" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="K28" s="3" t="str">
@@ -4136,15 +4171,15 @@
         <v>195</v>
       </c>
       <c r="B29" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>ManyPrimates__2022</v>
       </c>
       <c r="C29" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>ManyPrimates</v>
       </c>
       <c r="D29" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v/>
       </c>
       <c r="E29" s="9" t="str">
@@ -4153,7 +4188,7 @@
       </c>
       <c r="F29" s="7"/>
       <c r="G29" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.26451/abc.09.04.06.2022</v>
       </c>
       <c r="H29" s="3"/>
@@ -4161,7 +4196,7 @@
         <v>196</v>
       </c>
       <c r="J29" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="K29" s="3" t="str">
@@ -4185,7 +4220,7 @@
       </c>
       <c r="Q29" s="14"/>
       <c r="S29" t="str">
-        <f t="shared" ref="S29:S34" si="18">IF(R29="N", Q29, "write file name")</f>
+        <f t="shared" ref="S29:S34" si="17">IF(R29="N", Q29, "write file name")</f>
         <v>write file name</v>
       </c>
       <c r="T29" t="s">
@@ -4219,15 +4254,15 @@
         <v>201</v>
       </c>
       <c r="B30" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Powell_etal_2017</v>
       </c>
       <c r="C30" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Powell</v>
       </c>
       <c r="D30" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E30" s="9" t="str">
@@ -4236,7 +4271,7 @@
       </c>
       <c r="F30" s="7"/>
       <c r="G30" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1098/rspb.2017.1765</v>
       </c>
       <c r="H30" s="3" t="s">
@@ -4246,7 +4281,7 @@
         <v>203</v>
       </c>
       <c r="J30" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="K30" s="3" t="str">
@@ -4270,7 +4305,7 @@
       </c>
       <c r="Q30" s="14"/>
       <c r="S30" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>write file name</v>
       </c>
       <c r="T30" t="s">
@@ -4304,15 +4339,15 @@
         <v>206</v>
       </c>
       <c r="B31" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="C31" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Sherwood</v>
       </c>
       <c r="D31" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E31" s="9" t="str">
@@ -4323,7 +4358,7 @@
         <v>207</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="H31" s="3"/>
@@ -4331,7 +4366,7 @@
         <v>150</v>
       </c>
       <c r="J31" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="K31" s="3" t="str">
@@ -4355,7 +4390,7 @@
       </c>
       <c r="Q31" s="14"/>
       <c r="S31" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>write file name</v>
       </c>
       <c r="T31" t="s">
@@ -4382,15 +4417,18 @@
         <v>206</v>
       </c>
       <c r="B32" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="C32" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Sherwood</v>
       </c>
       <c r="D32" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f>IF(ISNUMBER(FIND("&amp;", A32)),
+    IF(LEN(A32)-LEN(SUBSTITUTE(A32, ",", ""))&gt;=6, "etal", MID(A32, SEARCH("&amp; ", A32)+2, SEARCH(",", A32, SEARCH("&amp; ", A32)+2) - SEARCH("&amp; ", A32)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
       <c r="E32" s="9" t="str">
@@ -4401,7 +4439,7 @@
         <v>207</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1159/000075672</v>
       </c>
       <c r="H32" s="3"/>
@@ -4409,7 +4447,7 @@
         <v>154</v>
       </c>
       <c r="J32" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="K32" s="3" t="str">
@@ -4433,7 +4471,7 @@
       </c>
       <c r="Q32" s="14"/>
       <c r="S32" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>write file name</v>
       </c>
       <c r="T32" t="s">
@@ -4460,16 +4498,16 @@
         <v>212</v>
       </c>
       <c r="B33" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>Winkler_etal_2021</v>
+        <f t="shared" si="7"/>
+        <v>Winkler_Bryant_2021</v>
       </c>
       <c r="C33" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Winkler</v>
       </c>
       <c r="D33" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
+        <f t="shared" si="3"/>
+        <v>Bryant</v>
       </c>
       <c r="E33" s="9" t="str">
         <f t="shared" si="9"/>
@@ -4477,7 +4515,7 @@
       </c>
       <c r="F33" s="7"/>
       <c r="G33" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1080/09524622.2021.1905065</v>
       </c>
       <c r="H33" s="3"/>
@@ -4485,8 +4523,8 @@
         <v>213</v>
       </c>
       <c r="J33" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Winkler_etal_2021_Figure1</v>
+        <f t="shared" si="6"/>
+        <v>Winkler_Bryant_2021_Figure1</v>
       </c>
       <c r="K33" s="3" t="str">
         <f t="shared" si="10"/>
@@ -4509,7 +4547,7 @@
       </c>
       <c r="Q33" s="14"/>
       <c r="S33" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>write file name</v>
       </c>
       <c r="T33" t="s">
@@ -4531,15 +4569,15 @@
         <v>216</v>
       </c>
       <c r="B34" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Young_etal_2013</v>
       </c>
       <c r="C34" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Young</v>
       </c>
       <c r="D34" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E34" s="9" t="str">
@@ -4548,7 +4586,7 @@
       </c>
       <c r="F34" s="7"/>
       <c r="G34" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.3389/fncir.2013.00030</v>
       </c>
       <c r="H34" s="3"/>
@@ -4556,7 +4594,7 @@
         <v>59</v>
       </c>
       <c r="J34" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Young_etal_2013_Table1</v>
       </c>
       <c r="K34" s="3" t="str">
@@ -4580,7 +4618,7 @@
       </c>
       <c r="Q34" s="14"/>
       <c r="S34" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>write file name</v>
       </c>
       <c r="T34" t="s">
@@ -4602,15 +4640,15 @@
         <v>218</v>
       </c>
       <c r="B35" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>Mota_etal_2015</v>
       </c>
       <c r="C35" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>Mota</v>
       </c>
       <c r="D35" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E35" s="9" t="str">
@@ -4618,14 +4656,14 @@
         <v>2015</v>
       </c>
       <c r="G35" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.1126/science.aaa9101</v>
       </c>
       <c r="I35" s="3" t="s">
         <v>98</v>
       </c>
       <c r="J35" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>Mota_etal_2015_TableS1</v>
       </c>
       <c r="K35" s="3" t="str">
@@ -4655,15 +4693,15 @@
         <v>219</v>
       </c>
       <c r="B36" s="7" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C36" s="9" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D36" s="9" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="3"/>
         <v>etal</v>
       </c>
       <c r="E36" s="9" t="str">
@@ -4671,14 +4709,14 @@
         <v>2013</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I36" s="3" t="s">
         <v>220</v>
       </c>
       <c r="J36" s="3" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="K36" s="3" t="str">
@@ -4705,571 +4743,553 @@
         <v>219</v>
       </c>
       <c r="B37" s="7" t="str">
-        <f t="shared" ref="B37" si="19">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
+        <f t="shared" ref="B37" si="18">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="C37" s="9" t="str">
-        <f t="shared" ref="C37" si="20">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C37" si="19">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
       <c r="D37" s="9" t="str">
-        <f t="shared" ref="D37" si="21">IF(ISNUMBER(FIND("&amp;", A37)),
-    IF(LEN(A37)-LEN(SUBSTITUTE(A37, ",", ""))&gt;=3, "etal", MID(A37, SEARCH("&amp; ", A37)+2, SEARCH(",", A37, SEARCH("&amp; ", A37)+2) - SEARCH("&amp; ", A37)-2)),
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E37" s="9" t="str">
+        <f t="shared" ref="E37" si="20">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
+        <v>2013</v>
+      </c>
+      <c r="G37" t="str">
+        <f t="shared" si="5"/>
+        <v>10.3389/fnana.2013.00035</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="J37" s="3" t="str">
+        <f t="shared" ref="J37" si="21">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
+        <v>HerculanoHouzel_etal_2013_Table1-a</v>
+      </c>
+      <c r="K37" s="3" t="str">
+        <f t="shared" ref="K37" si="22">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
+      </c>
+      <c r="N37" t="str" cm="1">
+        <f t="array" ref="N37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K37, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
+      </c>
+      <c r="O37" t="str" cm="1">
+        <f t="array" ref="O37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K37, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI37" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="38" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>219</v>
+      </c>
+      <c r="B38" s="7" t="str">
+        <f t="shared" ref="B38" si="23">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
+        <v>HerculanoHouzel_etal_2013</v>
+      </c>
+      <c r="C38" s="9" t="str">
+        <f t="shared" ref="C38" si="24">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="D38" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E38" s="9" t="str">
+        <f t="shared" ref="E38" si="25">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
+        <v>2013</v>
+      </c>
+      <c r="G38" t="str">
+        <f t="shared" si="5"/>
+        <v>10.3389/fnana.2013.00035</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="J38" s="3" t="str">
+        <f t="shared" ref="J38" si="26">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
+        <v>HerculanoHouzel_etal_2013_Table1-b</v>
+      </c>
+      <c r="K38" s="3" t="str">
+        <f t="shared" ref="K38" si="27">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
+      </c>
+      <c r="N38" t="str" cm="1">
+        <f t="array" ref="N38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K38, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
+      </c>
+      <c r="O38" t="str" cm="1">
+        <f t="array" ref="O38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K38, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI38" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="39" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="7" t="str">
+        <f t="shared" ref="B39" si="28">C39 &amp; IF(D39&lt;&gt;"", "_" &amp; D39, "_") &amp; IF(E39&lt;&gt;"", "_" &amp; E39, "_") &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "")</f>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C39" s="9" t="str">
+        <f t="shared" ref="C39" si="29">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A39,","), "-", ""), " ", "")</f>
+        <v>Isler</v>
+      </c>
+      <c r="D39" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E39" s="9" t="str">
+        <f t="shared" ref="E39" si="30">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, "("), ")")</f>
+        <v>2008</v>
+      </c>
+      <c r="G39" t="str">
+        <f t="shared" ref="G39" si="31">_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="J39" s="3" t="str">
+        <f t="shared" ref="J39" si="32">TRIM(_xlfn.TEXTJOIN("_",FALSE,B39,(SUBSTITUTE(SUBSTITUTE(I39," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_Table2</v>
+      </c>
+      <c r="K39" s="3" t="str">
+        <f t="shared" ref="K39" si="33">IF(ISBLANK(H39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
+      </c>
+      <c r="N39" t="str" cm="1">
+        <f t="array" ref="N39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K39, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="O39" t="str" cm="1">
+        <f t="array" ref="O39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K39, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI39">
+        <v>6</v>
+      </c>
+      <c r="AK39">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="40" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>224</v>
+      </c>
+      <c r="B40" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C40" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v>Isler</v>
+      </c>
+      <c r="D40" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E40" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>2008</v>
+      </c>
+      <c r="G40" t="str">
+        <f>_xlfn.TEXTAFTER(A40,"https://doi.org/")</f>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="J40" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Isler_etal_2008_Table7</v>
+      </c>
+      <c r="K40" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+      </c>
+      <c r="N40" t="str" cm="1">
+        <f t="array" ref="N40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K40, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
+      </c>
+      <c r="O40" t="str" cm="1">
+        <f t="array" ref="O40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K40, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI40">
+        <v>3</v>
+      </c>
+      <c r="AK40">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>224</v>
+      </c>
+      <c r="B41" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C41" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v>Isler</v>
+      </c>
+      <c r="D41" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E41" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>2008</v>
+      </c>
+      <c r="G41" t="str">
+        <f>_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J41" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Isler_etal_2008_TableS1</v>
+      </c>
+      <c r="K41" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
+      </c>
+      <c r="N41" t="str" cm="1">
+        <f t="array" ref="N41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K41, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
+      </c>
+      <c r="O41" t="str" cm="1">
+        <f t="array" ref="O41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K41, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI41" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="42" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>224</v>
+      </c>
+      <c r="B42" s="7" t="str">
+        <f t="shared" ref="B42" si="34">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C42" s="9" t="str">
+        <f t="shared" ref="C42" si="35">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
+        <v>Isler</v>
+      </c>
+      <c r="D42" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E42" s="9" t="str">
+        <f t="shared" ref="E42" si="36">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
+        <v>2008</v>
+      </c>
+      <c r="G42" t="str">
+        <f t="shared" ref="G42" si="37">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="J42" s="3" t="str">
+        <f t="shared" ref="J42" si="38">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_TableS2</v>
+      </c>
+      <c r="K42" s="3" t="str">
+        <f t="shared" ref="K42" si="39">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
+      </c>
+      <c r="N42" t="str" cm="1">
+        <f t="array" ref="N42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K42, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
+      </c>
+      <c r="O42" t="str" cm="1">
+        <f t="array" ref="O42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K42, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI42">
+        <v>8</v>
+      </c>
+      <c r="AK42">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="43" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>224</v>
+      </c>
+      <c r="B43" s="7" t="str">
+        <f t="shared" ref="B43" si="40">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C43" s="9" t="str">
+        <f t="shared" ref="C43" si="41">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
+        <v>Isler</v>
+      </c>
+      <c r="D43" s="9" t="str">
+        <f>IF(ISNUMBER(FIND("&amp;", A43)),
+    IF(LEN(A43)-LEN(SUBSTITUTE(A43, ",", ""))&gt;=6, "etal", MID(A43, SEARCH("&amp; ", A43)+2, SEARCH(",", A43, SEARCH("&amp; ", A43)+2) - SEARCH("&amp; ", A43)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E37" s="9" t="str">
-        <f t="shared" ref="E37" si="22">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
-        <v>2013</v>
-      </c>
-      <c r="G37" t="str">
-        <f t="shared" si="4"/>
-        <v>10.3389/fnana.2013.00035</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="J37" s="3" t="str">
-        <f t="shared" ref="J37" si="23">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2013_Table1-a</v>
-      </c>
-      <c r="K37" s="3" t="str">
-        <f t="shared" ref="K37" si="24">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
-      </c>
-      <c r="N37" t="str" cm="1">
-        <f t="array" ref="N37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K37, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
-      </c>
-      <c r="O37" t="str" cm="1">
-        <f t="array" ref="O37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K37, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
-      </c>
-      <c r="P37" s="3" t="s">
+      <c r="E43" s="9" t="str">
+        <f t="shared" ref="E43" si="42">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
+        <v>2008</v>
+      </c>
+      <c r="G43" t="str">
+        <f t="shared" ref="G43" si="43">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="J43" s="3" t="str">
+        <f t="shared" ref="J43" si="44">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_TableS3</v>
+      </c>
+      <c r="K43" s="3" t="str">
+        <f t="shared" ref="K43" si="45">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
+      </c>
+      <c r="N43" t="str" cm="1">
+        <f t="array" ref="N43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K43, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
+      </c>
+      <c r="O43" t="str" cm="1">
+        <f t="array" ref="O43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K43, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="P43" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AI37" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="38" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A38" t="s">
-        <v>219</v>
-      </c>
-      <c r="B38" s="7" t="str">
-        <f t="shared" ref="B38" si="25">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
-        <v>HerculanoHouzel_etal_2013</v>
-      </c>
-      <c r="C38" s="9" t="str">
-        <f t="shared" ref="C38" si="26">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="D38" s="9" t="str">
-        <f t="shared" ref="D38" si="27">IF(ISNUMBER(FIND("&amp;", A38)),
-    IF(LEN(A38)-LEN(SUBSTITUTE(A38, ",", ""))&gt;=3, "etal", MID(A38, SEARCH("&amp; ", A38)+2, SEARCH(",", A38, SEARCH("&amp; ", A38)+2) - SEARCH("&amp; ", A38)-2)),
+      <c r="AI43">
+        <v>7</v>
+      </c>
+      <c r="AK43">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A44" s="17" t="s">
+        <v>224</v>
+      </c>
+      <c r="B44" s="18" t="str">
+        <f t="shared" ref="B44" si="46">C44 &amp; IF(D44&lt;&gt;"", "_" &amp; D44, "_") &amp; IF(E44&lt;&gt;"", "_" &amp; E44, "_") &amp; IF(F44&lt;&gt;"", "_" &amp; F44, "")</f>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="C44" s="19" t="str">
+        <f t="shared" ref="C44" si="47">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A44,","), "-", ""), " ", "")</f>
+        <v>Isler</v>
+      </c>
+      <c r="D44" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E44" s="19" t="str">
+        <f t="shared" ref="E44" si="48">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A44, "("), ")")</f>
+        <v>2008</v>
+      </c>
+      <c r="F44" s="19"/>
+      <c r="G44" s="17" t="str">
+        <f t="shared" ref="G44" si="49">_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="I44" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="J44" s="20" t="str">
+        <f t="shared" ref="J44" si="50">TRIM(_xlfn.TEXTJOIN("_",FALSE,B44,(SUBSTITUTE(SUBSTITUTE(I44," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_Tree.nex</v>
+      </c>
+      <c r="K44" s="21" t="str">
+        <f t="shared" ref="K44" si="51">IF(ISBLANK(H44),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
+      </c>
+      <c r="N44" s="17" t="str" cm="1">
+        <f t="array" ref="N44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K44, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="O44" s="17" t="str" cm="1">
+        <f t="array" ref="O44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K44, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="P44" s="20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="45" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>230</v>
+      </c>
+      <c r="B45" s="7" t="str">
+        <f t="shared" si="7"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="C45" s="9" t="str">
+        <f t="shared" si="8"/>
+        <v>Lewitus</v>
+      </c>
+      <c r="D45" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E45" s="9" t="str">
+        <f t="shared" si="9"/>
+        <v>2014</v>
+      </c>
+      <c r="G45" t="str">
+        <f>_xlfn.TEXTAFTER(A45,"https://doi.org/")</f>
+        <v>10.1371/journal.pbio.1002000</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J45" s="3" t="str">
+        <f t="shared" si="6"/>
+        <v>Lewitus_etal_2014_TableS1</v>
+      </c>
+      <c r="K45" s="3" t="str">
+        <f t="shared" si="10"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
+      </c>
+      <c r="N45" t="str" cm="1">
+        <f t="array" ref="N45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K45, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+      </c>
+      <c r="O45" t="str" cm="1">
+        <f t="array" ref="O45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K45, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="X45" t="s">
+        <v>278</v>
+      </c>
+      <c r="AA45" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI45">
+        <v>9</v>
+      </c>
+      <c r="AK45">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="46" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>230</v>
+      </c>
+      <c r="B46" s="7" t="str">
+        <f t="shared" ref="B46" si="52">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="C46" s="9" t="str">
+        <f t="shared" ref="C46" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
+        <v>Lewitus</v>
+      </c>
+      <c r="D46" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E46" s="9" t="str">
+        <f t="shared" ref="E46" si="54">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
+        <v>2014</v>
+      </c>
+      <c r="G46" t="str">
+        <f>_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
+        <v>10.1371/journal.pbio.1002000</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="J46" s="3" t="str">
+        <f t="shared" ref="J46" si="55">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
+        <v>Lewitus_etal_2014_TableS8</v>
+      </c>
+      <c r="K46" s="3" t="str">
+        <f t="shared" ref="K46" si="56">IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+      </c>
+      <c r="N46" t="str" cm="1">
+        <f t="array" ref="N46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K46, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+      </c>
+      <c r="O46" t="str" cm="1">
+        <f t="array" ref="O46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K46, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="X46" t="s">
+        <v>232</v>
+      </c>
+      <c r="AA46" t="s">
+        <v>279</v>
+      </c>
+      <c r="AI46">
+        <v>6</v>
+      </c>
+      <c r="AK46">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="47" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
+      <c r="A47" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="B47" s="18" t="str">
+        <f t="shared" ref="B47" si="57">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
+        <v>Lewitus_etal_2013</v>
+      </c>
+      <c r="C47" s="19" t="str">
+        <f t="shared" ref="C47" si="58">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
+        <v>Lewitus</v>
+      </c>
+      <c r="D47" s="9" t="str">
+        <f>IF(ISNUMBER(FIND("&amp;", A47)),
+    IF(LEN(A47)-LEN(SUBSTITUTE(A47, ",", ""))&gt;=6, "etal", MID(A47, SEARCH("&amp; ", A47)+2, SEARCH(",", A47, SEARCH("&amp; ", A47)+2) - SEARCH("&amp; ", A47)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E38" s="9" t="str">
-        <f t="shared" ref="E38" si="28">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
-        <v>2013</v>
-      </c>
-      <c r="G38" t="str">
-        <f t="shared" si="4"/>
-        <v>10.3389/fnana.2013.00035</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="J38" s="3" t="str">
-        <f t="shared" ref="J38" si="29">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
-        <v>HerculanoHouzel_etal_2013_Table1-b</v>
-      </c>
-      <c r="K38" s="3" t="str">
-        <f t="shared" ref="K38" si="30">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
-      </c>
-      <c r="N38" t="str" cm="1">
-        <f t="array" ref="N38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K38, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
-      </c>
-      <c r="O38" t="str" cm="1">
-        <f t="array" ref="O38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K38, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI38" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="39" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A39" t="s">
-        <v>224</v>
-      </c>
-      <c r="B39" s="7" t="str">
-        <f t="shared" ref="B39" si="31">C39 &amp; IF(D39&lt;&gt;"", "_" &amp; D39, "_") &amp; IF(E39&lt;&gt;"", "_" &amp; E39, "_") &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "")</f>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="C39" s="9" t="str">
-        <f t="shared" ref="C39" si="32">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A39,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
-      </c>
-      <c r="D39" s="9" t="str">
-        <f t="shared" ref="D39" si="33">IF(ISNUMBER(FIND("&amp;", A39)),
-    IF(LEN(A39)-LEN(SUBSTITUTE(A39, ",", ""))&gt;=3, "etal", MID(A39, SEARCH("&amp; ", A39)+2, SEARCH(",", A39, SEARCH("&amp; ", A39)+2) - SEARCH("&amp; ", A39)-2)),
-    ""
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="E39" s="9" t="str">
-        <f t="shared" ref="E39" si="34">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, "("), ")")</f>
-        <v>2008</v>
-      </c>
-      <c r="G39" t="str">
-        <f t="shared" ref="G39" si="35">_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="J39" s="3" t="str">
-        <f t="shared" ref="J39" si="36">TRIM(_xlfn.TEXTJOIN("_",FALSE,B39,(SUBSTITUTE(SUBSTITUTE(I39," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Table2</v>
-      </c>
-      <c r="K39" s="3" t="str">
-        <f t="shared" ref="K39" si="37">IF(ISBLANK(H39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H39, SUBSTITUTE(I39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
-      </c>
-      <c r="N39" t="str" cm="1">
-        <f t="array" ref="N39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K39, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
-      </c>
-      <c r="O39" t="str" cm="1">
-        <f t="array" ref="O39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K39, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI39">
-        <v>6</v>
-      </c>
-      <c r="AK39">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A40" t="s">
-        <v>224</v>
-      </c>
-      <c r="B40" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="C40" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Isler</v>
-      </c>
-      <c r="D40" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
-      </c>
-      <c r="E40" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v>2008</v>
-      </c>
-      <c r="G40" t="str">
-        <f>_xlfn.TEXTAFTER(A40,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J40" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Isler_etal_2008_Table7</v>
-      </c>
-      <c r="K40" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
-      </c>
-      <c r="N40" t="str" cm="1">
-        <f t="array" ref="N40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K40, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
-      </c>
-      <c r="O40" t="str" cm="1">
-        <f t="array" ref="O40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K40, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI40">
-        <v>3</v>
-      </c>
-      <c r="AK40">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A41" t="s">
-        <v>224</v>
-      </c>
-      <c r="B41" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="C41" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Isler</v>
-      </c>
-      <c r="D41" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
-      </c>
-      <c r="E41" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v>2008</v>
-      </c>
-      <c r="G41" t="str">
-        <f>_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J41" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Isler_etal_2008_TableS1</v>
-      </c>
-      <c r="K41" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
-      </c>
-      <c r="N41" t="str" cm="1">
-        <f t="array" ref="N41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K41, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
-      </c>
-      <c r="O41" t="str" cm="1">
-        <f t="array" ref="O41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K41, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI41" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="42" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A42" t="s">
-        <v>224</v>
-      </c>
-      <c r="B42" s="7" t="str">
-        <f t="shared" ref="B42" si="38">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="C42" s="9" t="str">
-        <f t="shared" ref="C42" si="39">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
-      </c>
-      <c r="D42" s="9" t="str">
-        <f t="shared" ref="D42" si="40">IF(ISNUMBER(FIND("&amp;", A42)),
-    IF(LEN(A42)-LEN(SUBSTITUTE(A42, ",", ""))&gt;=3, "etal", MID(A42, SEARCH("&amp; ", A42)+2, SEARCH(",", A42, SEARCH("&amp; ", A42)+2) - SEARCH("&amp; ", A42)-2)),
-    ""
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="E42" s="9" t="str">
-        <f t="shared" ref="E42" si="41">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
-        <v>2008</v>
-      </c>
-      <c r="G42" t="str">
-        <f t="shared" ref="G42" si="42">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="J42" s="3" t="str">
-        <f t="shared" ref="J42" si="43">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_TableS2</v>
-      </c>
-      <c r="K42" s="3" t="str">
-        <f t="shared" ref="K42" si="44">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
-      </c>
-      <c r="N42" t="str" cm="1">
-        <f t="array" ref="N42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K42, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
-      </c>
-      <c r="O42" t="str" cm="1">
-        <f t="array" ref="O42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K42, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI42">
-        <v>8</v>
-      </c>
-      <c r="AK42">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="43" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" t="s">
-        <v>224</v>
-      </c>
-      <c r="B43" s="7" t="str">
-        <f t="shared" ref="B43" si="45">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="C43" s="9" t="str">
-        <f t="shared" ref="C43" si="46">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
-      </c>
-      <c r="D43" s="9" t="str">
-        <f t="shared" ref="D43" si="47">IF(ISNUMBER(FIND("&amp;", A43)),
-    IF(LEN(A43)-LEN(SUBSTITUTE(A43, ",", ""))&gt;=3, "etal", MID(A43, SEARCH("&amp; ", A43)+2, SEARCH(",", A43, SEARCH("&amp; ", A43)+2) - SEARCH("&amp; ", A43)-2)),
-    ""
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="E43" s="9" t="str">
-        <f t="shared" ref="E43" si="48">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
-        <v>2008</v>
-      </c>
-      <c r="G43" t="str">
-        <f t="shared" ref="G43" si="49">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J43" s="3" t="str">
-        <f t="shared" ref="J43" si="50">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_TableS3</v>
-      </c>
-      <c r="K43" s="3" t="str">
-        <f t="shared" ref="K43" si="51">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
-      </c>
-      <c r="N43" t="str" cm="1">
-        <f t="array" ref="N43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K43, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
-      </c>
-      <c r="O43" t="str" cm="1">
-        <f t="array" ref="O43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K43, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI43">
-        <v>7</v>
-      </c>
-      <c r="AK43">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A44" s="17" t="s">
-        <v>224</v>
-      </c>
-      <c r="B44" s="18" t="str">
-        <f t="shared" ref="B44" si="52">C44 &amp; IF(D44&lt;&gt;"", "_" &amp; D44, "_") &amp; IF(E44&lt;&gt;"", "_" &amp; E44, "_") &amp; IF(F44&lt;&gt;"", "_" &amp; F44, "")</f>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="C44" s="19" t="str">
-        <f t="shared" ref="C44" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A44,","), "-", ""), " ", "")</f>
-        <v>Isler</v>
-      </c>
-      <c r="D44" s="19" t="str">
-        <f t="shared" ref="D44" si="54">IF(ISNUMBER(FIND("&amp;", A44)),
-    IF(LEN(A44)-LEN(SUBSTITUTE(A44, ",", ""))&gt;=3, "etal", MID(A44, SEARCH("&amp; ", A44)+2, SEARCH(",", A44, SEARCH("&amp; ", A44)+2) - SEARCH("&amp; ", A44)-2)),
-    ""
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="E44" s="19" t="str">
-        <f t="shared" ref="E44" si="55">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A44, "("), ")")</f>
-        <v>2008</v>
-      </c>
-      <c r="F44" s="19"/>
-      <c r="G44" s="17" t="str">
-        <f t="shared" ref="G44" si="56">_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="I44" s="20" t="s">
-        <v>229</v>
-      </c>
-      <c r="J44" s="20" t="str">
-        <f t="shared" ref="J44" si="57">TRIM(_xlfn.TEXTJOIN("_",FALSE,B44,(SUBSTITUTE(SUBSTITUTE(I44," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Tree.nex</v>
-      </c>
-      <c r="K44" s="21" t="str">
-        <f t="shared" ref="K44" si="58">IF(ISBLANK(H44),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H44, SUBSTITUTE(I44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
-      </c>
-      <c r="N44" s="17" t="str" cm="1">
-        <f t="array" ref="N44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K44, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="O44" s="17" t="str" cm="1">
-        <f t="array" ref="O44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K44, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
-      </c>
-      <c r="P44" s="20" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="45" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>230</v>
-      </c>
-      <c r="B45" s="7" t="str">
-        <f t="shared" si="6"/>
-        <v>Lewitus_etal_2014</v>
-      </c>
-      <c r="C45" s="9" t="str">
-        <f t="shared" si="7"/>
-        <v>Lewitus</v>
-      </c>
-      <c r="D45" s="9" t="str">
-        <f t="shared" si="8"/>
-        <v>etal</v>
-      </c>
-      <c r="E45" s="9" t="str">
-        <f t="shared" si="9"/>
-        <v>2014</v>
-      </c>
-      <c r="G45" t="str">
-        <f>_xlfn.TEXTAFTER(A45,"https://doi.org/")</f>
-        <v>10.1371/journal.pbio.1002000</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="J45" s="3" t="str">
-        <f t="shared" si="5"/>
-        <v>Lewitus_etal_2014_TableS1</v>
-      </c>
-      <c r="K45" s="3" t="str">
-        <f t="shared" si="10"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
-      </c>
-      <c r="N45" t="str" cm="1">
-        <f t="array" ref="N45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K45, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
-      </c>
-      <c r="O45" t="str" cm="1">
-        <f t="array" ref="O45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K45, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="X45" t="s">
-        <v>278</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI45">
-        <v>9</v>
-      </c>
-      <c r="AK45">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:37" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>230</v>
-      </c>
-      <c r="B46" s="7" t="str">
-        <f t="shared" ref="B46" si="59">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
-        <v>Lewitus_etal_2014</v>
-      </c>
-      <c r="C46" s="9" t="str">
-        <f t="shared" ref="C46" si="60">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
-        <v>Lewitus</v>
-      </c>
-      <c r="D46" s="9" t="str">
-        <f t="shared" ref="D46" si="61">IF(ISNUMBER(FIND("&amp;", A46)),
-    IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=3, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
-    ""
-)</f>
-        <v>etal</v>
-      </c>
-      <c r="E46" s="9" t="str">
-        <f t="shared" ref="E46" si="62">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
-        <v>2014</v>
-      </c>
-      <c r="G46" t="str">
-        <f>_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
-        <v>10.1371/journal.pbio.1002000</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J46" s="3" t="str">
-        <f t="shared" ref="J46" si="63">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
-        <v>Lewitus_etal_2014_TableS8</v>
-      </c>
-      <c r="K46" s="3" t="str">
-        <f t="shared" ref="K46" si="64">IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
-      </c>
-      <c r="N46" t="str" cm="1">
-        <f t="array" ref="N46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K46, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
-      </c>
-      <c r="O46" t="str" cm="1">
-        <f t="array" ref="O46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K46, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="X46" t="s">
-        <v>232</v>
-      </c>
-      <c r="AA46" t="s">
-        <v>279</v>
-      </c>
-      <c r="AI46">
-        <v>6</v>
-      </c>
-      <c r="AK46">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="47" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A47" s="17" t="s">
-        <v>233</v>
-      </c>
-      <c r="B47" s="18" t="str">
-        <f t="shared" ref="B47" si="65">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
-        <v>Lewitus_etal_2013</v>
-      </c>
-      <c r="C47" s="19" t="str">
-        <f t="shared" ref="C47" si="66">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
-        <v>Lewitus</v>
-      </c>
-      <c r="D47" s="19" t="str">
-        <f t="shared" ref="D47" si="67">IF(ISNUMBER(FIND("&amp;", A47)),
-    IF(LEN(A47)-LEN(SUBSTITUTE(A47, ",", ""))&gt;=3, "etal", MID(A47, SEARCH("&amp; ", A47)+2, SEARCH(",", A47, SEARCH("&amp; ", A47)+2) - SEARCH("&amp; ", A47)-2)),
-    ""
-)</f>
-        <v>etal</v>
-      </c>
       <c r="E47" s="19" t="str">
-        <f t="shared" ref="E47" si="68">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
+        <f t="shared" ref="E47" si="59">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="F47" s="19"/>
@@ -5281,7 +5301,7 @@
         <v>234</v>
       </c>
       <c r="J47" s="20" t="str">
-        <f t="shared" ref="J47" si="69">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
+        <f t="shared" ref="J47" si="60">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
       <c r="K47" s="21" t="str">
@@ -5314,105 +5334,274 @@
         <v>235</v>
       </c>
       <c r="B48" s="22" t="str">
-        <f t="shared" ref="B48" si="70">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
+        <f t="shared" ref="B48" si="61">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="C48" s="24" t="str">
-        <f t="shared" ref="C48" si="71">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C48" si="62">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
-      <c r="D48" s="24" t="str">
-        <f t="shared" ref="D48" si="72">IF(ISNUMBER(FIND("&amp;", A48)),
-    IF(LEN(A48)-LEN(SUBSTITUTE(A48, ",", ""))&gt;=3, "etal", MID(A48, SEARCH("&amp; ", A48)+2, SEARCH(",", A48, SEARCH("&amp; ", A48)+2) - SEARCH("&amp; ", A48)-2)),
+      <c r="D48" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E48" s="24" t="str">
+        <f t="shared" ref="E48" si="63">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
+        <v>2011</v>
+      </c>
+      <c r="F48" s="24"/>
+      <c r="G48" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="I48" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="J48" s="23" t="str">
+        <f t="shared" ref="J48" si="64">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
+      </c>
+      <c r="K48" s="23" t="str">
+        <f>IF(ISBLANK(H48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
+      </c>
+      <c r="N48" s="15" t="str" cm="1">
+        <f t="array" ref="N48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K48, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+      </c>
+      <c r="O48" s="15" t="str" cm="1">
+        <f t="array" ref="O48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K48, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+      </c>
+      <c r="P48" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI48" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="49" spans="1:35" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B49" s="22" t="str">
+        <f t="shared" ref="B49" si="65">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="C49" s="24" t="str">
+        <f t="shared" ref="C49" si="66">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
+        <v>Smaers</v>
+      </c>
+      <c r="D49" s="9" t="str">
+        <f t="shared" si="3"/>
+        <v>etal</v>
+      </c>
+      <c r="E49" s="24" t="str">
+        <f t="shared" ref="E49" si="67">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
+        <v>2011</v>
+      </c>
+      <c r="F49" s="24"/>
+      <c r="G49" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="I49" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="J49" s="23" t="str">
+        <f t="shared" ref="J49" si="68">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
+      </c>
+      <c r="K49" s="23" t="str">
+        <f>IF(ISBLANK(H49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
+      </c>
+      <c r="N49" s="15" t="str" cm="1">
+        <f t="array" ref="N49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K49, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+      </c>
+      <c r="O49" s="15" t="str" cm="1">
+        <f t="array" ref="O49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K49, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+      </c>
+      <c r="P49" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI49" s="15" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="50" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>280</v>
+      </c>
+      <c r="B50" s="22" t="str">
+        <f t="shared" ref="B50:B53" si="69">C50 &amp; IF(D50&lt;&gt;"", "_" &amp; D50, "_") &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "")</f>
+        <v>Iwaniuk_etal_1999</v>
+      </c>
+      <c r="C50" s="24" t="str">
+        <f t="shared" ref="C50:C53" si="70">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
+        <v>Iwaniuk</v>
+      </c>
+      <c r="D50" s="9" t="str">
+        <f t="shared" ref="D50:D53" si="71">IF(ISNUMBER(FIND("&amp;", A50)),
+    IF(LEN(A50)-LEN(SUBSTITUTE(A50, ",", ""))&gt;=6, "etal", MID(A50, SEARCH("&amp; ", A50)+2, SEARCH(",", A50, SEARCH("&amp; ", A50)+2) - SEARCH("&amp; ", A50)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E48" s="24" t="str">
-        <f t="shared" ref="E48" si="73">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
-        <v>2011</v>
-      </c>
-      <c r="F48" s="24"/>
-      <c r="G48" s="15" t="s">
+      <c r="E50" s="24" t="str">
+        <f t="shared" ref="E50:E52" si="72">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
+        <v>1999</v>
+      </c>
+      <c r="F50" s="24"/>
+      <c r="G50" s="15" t="s">
         <v>236</v>
       </c>
-      <c r="I48" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="J48" s="23" t="str">
-        <f t="shared" ref="J48" si="74">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
-      </c>
-      <c r="K48" s="23" t="str">
-        <f>IF(ISBLANK(H48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
-      </c>
-      <c r="N48" s="15" t="str" cm="1">
-        <f t="array" ref="N48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K48, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="O48" s="15" t="str" cm="1">
-        <f t="array" ref="O48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K48, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="P48" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI48" s="15" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="49" spans="1:35" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="B49" s="22" t="str">
-        <f t="shared" ref="B49" si="75">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
-        <v>Smaers_etal_2011</v>
-      </c>
-      <c r="C49" s="24" t="str">
-        <f t="shared" ref="C49" si="76">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
-        <v>Smaers</v>
-      </c>
-      <c r="D49" s="24" t="str">
-        <f t="shared" ref="D49" si="77">IF(ISNUMBER(FIND("&amp;", A49)),
-    IF(LEN(A49)-LEN(SUBSTITUTE(A49, ",", ""))&gt;=3, "etal", MID(A49, SEARCH("&amp; ", A49)+2, SEARCH(",", A49, SEARCH("&amp; ", A49)+2) - SEARCH("&amp; ", A49)-2)),
-    ""
-)</f>
+      <c r="H50" s="15"/>
+      <c r="I50" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J50" s="23" t="str">
+        <f t="shared" ref="J50:J52" si="73">TRIM(_xlfn.TEXTJOIN("_",FALSE,B50,(SUBSTITUTE(SUBSTITUTE(I50," ",""), "_", ""))))</f>
+        <v>Iwaniuk_etal_1999_Table1</v>
+      </c>
+      <c r="K50" s="23" t="str">
+        <f>IF(ISBLANK(H50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000323671_Table1</v>
+      </c>
+      <c r="M50" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="V50" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>281</v>
+      </c>
+      <c r="B51" s="22" t="str">
+        <f t="shared" si="69"/>
+        <v>Genoud_etal_2018</v>
+      </c>
+      <c r="C51" s="24" t="str">
+        <f t="shared" si="70"/>
+        <v>Genoud</v>
+      </c>
+      <c r="D51" s="9" t="str">
+        <f t="shared" si="71"/>
         <v>etal</v>
       </c>
-      <c r="E49" s="24" t="str">
-        <f t="shared" ref="E49" si="78">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
-        <v>2011</v>
-      </c>
-      <c r="F49" s="24"/>
-      <c r="G49" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="I49" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="J49" s="23" t="str">
-        <f t="shared" ref="J49" si="79">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
-      </c>
-      <c r="K49" s="23" t="str">
-        <f>IF(ISBLANK(H49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
-      </c>
-      <c r="N49" s="15" t="str" cm="1">
-        <f t="array" ref="N49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K49, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
-      </c>
-      <c r="O49" s="15" t="str" cm="1">
-        <f t="array" ref="O49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K49, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="P49" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="AI49" s="15" t="s">
-        <v>238</v>
+      <c r="E51" s="24" t="str">
+        <f t="shared" si="72"/>
+        <v>2018</v>
+      </c>
+      <c r="F51" s="24"/>
+      <c r="G51" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="H51" s="15"/>
+      <c r="I51" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="J51" s="23" t="str">
+        <f t="shared" si="73"/>
+        <v>Genoud_etal_2018_TableS2</v>
+      </c>
+      <c r="K51" s="23" t="str">
+        <f t="shared" ref="K51:K52" si="74">IF(ISBLANK(H51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000323672_TableS2</v>
+      </c>
+      <c r="M51" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="X51" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="52" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>282</v>
+      </c>
+      <c r="B52" s="22" t="str">
+        <f t="shared" si="69"/>
+        <v>Mota_etal_2019</v>
+      </c>
+      <c r="C52" s="24" t="str">
+        <f t="shared" si="70"/>
+        <v>Mota</v>
+      </c>
+      <c r="D52" s="9" t="str">
+        <f t="shared" si="71"/>
+        <v>etal</v>
+      </c>
+      <c r="E52" s="24" t="str">
+        <f t="shared" si="72"/>
+        <v>2019</v>
+      </c>
+      <c r="F52" s="24"/>
+      <c r="G52" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="H52" s="15"/>
+      <c r="I52" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="J52" s="23" t="str">
+        <f t="shared" si="73"/>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
+      </c>
+      <c r="K52" s="23" t="str">
+        <f t="shared" si="74"/>
+        <v>10.1159%2F000323673_SupplementaryTableS1</v>
+      </c>
+      <c r="M52" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="X52" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="53" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>288</v>
+      </c>
+      <c r="B53" s="22" t="str">
+        <f t="shared" si="69"/>
+        <v>Burish_etal_2010</v>
+      </c>
+      <c r="C53" s="24" t="str">
+        <f t="shared" si="70"/>
+        <v>Burish</v>
+      </c>
+      <c r="D53" s="9" t="str">
+        <f t="shared" si="71"/>
+        <v>etal</v>
+      </c>
+      <c r="E53" s="24" t="str">
+        <f t="shared" ref="E53" si="75">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
+        <v>2010</v>
+      </c>
+      <c r="F53" s="24"/>
+      <c r="G53" s="15" t="s">
+        <v>284</v>
+      </c>
+      <c r="H53" s="15"/>
+      <c r="I53" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="J53" s="23" t="str">
+        <f t="shared" ref="J53" si="76">TRIM(_xlfn.TEXTJOIN("_",FALSE,B53,(SUBSTITUTE(SUBSTITUTE(I53," ",""), "_", ""))))</f>
+        <v>Burish_etal_2010_Table1</v>
+      </c>
+      <c r="K53" s="23" t="str">
+        <f t="shared" ref="K53" si="77">IF(ISBLANK(H53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000323673_Table1</v>
+      </c>
+      <c r="M53" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="X53" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -5879,16 +6068,16 @@
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="108" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1FCB6B39-592B-7347-A777-25143F16DD52}"/>
+  <xr:revisionPtr revIDLastSave="122" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA210EDE-9D37-0F45-9337-A732F37A7BA2}"/>
   <bookViews>
-    <workbookView xWindow="34560" yWindow="-5960" windowWidth="44700" windowHeight="16720" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="34560" yWindow="-5960" windowWidth="40260" windowHeight="17620" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="600" uniqueCount="303">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -131,9 +131,6 @@
     <t>Source URL link</t>
   </si>
   <si>
-    <t>Item description</t>
-  </si>
-  <si>
     <t>Main Trait(s)</t>
   </si>
   <si>
@@ -966,6 +963,15 @@
   </si>
   <si>
     <t>Burish_etal_2010_SupplementaryTable1_snapshot.csv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MacLarnon, A. (1996). The scaling of gross dimensions of the spinal cord in primates and other species. J Hum Evol, 30(1), 71-87. https://doi.org/10.1006/jhev.1996.0005 	</t>
+  </si>
+  <si>
+    <t>Table 1 Data</t>
+  </si>
+  <si>
+    <t>Item full name</t>
   </si>
 </sst>
 </file>
@@ -1139,7 +1145,7 @@
       <sheetName val="FileList"/>
     </sheetNames>
     <sheetDataSet>
-      <sheetData sheetId="0" refreshError="1">
+      <sheetData sheetId="0">
         <row r="1">
           <cell r="A1" t="str">
             <v>Files</v>
@@ -1237,122 +1243,122 @@
         </row>
         <row r="20">
           <cell r="A20" t="str">
-            <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+            <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
           </cell>
         </row>
         <row r="21">
           <cell r="A21" t="str">
-            <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+            <v>10.1159%2F000319019_Table1.tsv</v>
           </cell>
         </row>
         <row r="22">
           <cell r="A22" t="str">
-            <v>10.1159%2F000323671.ReadMe.md</v>
+            <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
           </cell>
         </row>
         <row r="23">
           <cell r="A23" t="str">
-            <v>10.1159%2F000437413_Table1.tsv</v>
+            <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
           </cell>
         </row>
         <row r="24">
           <cell r="A24" t="str">
-            <v>10.1159%2F000437413_Table2.tsv</v>
+            <v>10.1159%2F000323671.ReadMe.md</v>
           </cell>
         </row>
         <row r="25">
           <cell r="A25" t="str">
-            <v>10.1159%2F000437413_Table3.tsv</v>
+            <v>10.1159%2F000437413_Table1.tsv</v>
           </cell>
         </row>
         <row r="26">
           <cell r="A26" t="str">
-            <v>10.1159%2F000437413_Table4.tsv</v>
+            <v>10.1159%2F000437413_Table2.tsv</v>
           </cell>
         </row>
         <row r="27">
           <cell r="A27" t="str">
-            <v>10.1159%2F000437413_Table5.tsv</v>
+            <v>10.1159%2F000437413_Table3.tsv</v>
           </cell>
         </row>
         <row r="28">
           <cell r="A28" t="str">
-            <v>10.1159%2F000452856_TableS1.tsv</v>
+            <v>10.1159%2F000437413_Table4.tsv</v>
           </cell>
         </row>
         <row r="29">
           <cell r="A29" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+            <v>10.1159%2F000437413_Table5.tsv</v>
           </cell>
         </row>
         <row r="30">
           <cell r="A30" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</v>
+            <v>10.1159%2F000452856_TableS1.tsv</v>
           </cell>
         </row>
         <row r="31">
           <cell r="A31" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+            <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
           </cell>
         </row>
         <row r="32">
           <cell r="A32" t="str">
-            <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
+            <v>10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</v>
           </cell>
         </row>
         <row r="33">
           <cell r="A33" t="str">
-            <v>10.3389%25Ffnana.2013.00035.svg</v>
+            <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
           </cell>
         </row>
         <row r="34">
           <cell r="A34" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
+            <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
           </cell>
         </row>
         <row r="35">
           <cell r="A35" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
+            <v>10.3389%25Ffnana.2013.00035.svg</v>
           </cell>
         </row>
         <row r="36">
           <cell r="A36" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
+            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
           </cell>
         </row>
         <row r="37">
           <cell r="A37" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
+            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
           </cell>
         </row>
         <row r="38">
           <cell r="A38" t="str">
-            <v>10.3389%2Ffnana.2013.00035.ReadMe.md</v>
+            <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
           </cell>
         </row>
         <row r="39">
           <cell r="A39" t="str">
-            <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+            <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
           </cell>
         </row>
         <row r="40">
           <cell r="A40" t="str">
-            <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+            <v>10.3389%2Ffnana.2013.00035.ReadMe.md</v>
           </cell>
         </row>
         <row r="41">
           <cell r="A41" t="str">
-            <v>10.3389%2Ffnhum.2013.00424.ReadMe.md</v>
+            <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
           </cell>
         </row>
         <row r="42">
           <cell r="A42" t="str">
-            <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
+            <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
           </cell>
         </row>
         <row r="43">
           <cell r="A43" t="str">
-            <v>10.7554%2FeLife.77875_Table1.tsv</v>
+            <v>10.3389%2Ffnhum.2013.00424.ReadMe.md</v>
           </cell>
         </row>
       </sheetData>
@@ -1659,10 +1665,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AK55"/>
+  <dimension ref="A1:AK56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" customWidth="1"/>
+    <col min="1" max="1" width="77.83203125" customWidth="1"/>
     <col min="2" max="2" width="23.6640625" style="9" customWidth="1"/>
     <col min="3" max="3" width="16.83203125" style="9" customWidth="1"/>
     <col min="4" max="4" width="15" style="9" customWidth="1"/>
@@ -1764,51 +1770,51 @@
         <v>21</v>
       </c>
       <c r="X1" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="Y1" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Z1" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="AA1" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AB1" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AC1" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AD1" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AE1" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AF1" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AG1" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AH1" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AI1" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AJ1" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AK1" s="6" t="s">
         <v>34</v>
-      </c>
-      <c r="AK1" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="2" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="7" t="str">
         <f>C2 &amp; IF(D2&lt;&gt;"", "_" &amp; D2, "_") &amp; IF(E2&lt;&gt;"", "_" &amp; E2, "_") &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "")</f>
@@ -1845,7 +1851,7 @@
       </c>
       <c r="L2" s="3"/>
       <c r="M2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="N2" t="str" cm="1">
         <f t="array" ref="N2">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K2, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -1856,33 +1862,33 @@
         <v>notfound</v>
       </c>
       <c r="P2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q2" s="7"/>
       <c r="R2" s="8"/>
       <c r="T2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U2" t="s">
         <v>39</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
       </c>
       <c r="X2" s="7"/>
       <c r="Y2" t="s">
+        <v>40</v>
+      </c>
+      <c r="Z2" t="s">
         <v>41</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AD2" t="s">
         <v>42</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>43</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3" s="7" t="str">
         <f t="shared" ref="B3" si="2">C3 &amp; IF(D3&lt;&gt;"", "_" &amp; D3, "_") &amp; IF(E3&lt;&gt;"", "_" &amp; E3, "_") &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "")</f>
@@ -1909,7 +1915,7 @@
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="3" t="str">
         <f t="shared" ref="J3:J45" si="6">TRIM(_xlfn.TEXTJOIN("_",FALSE,B3,(SUBSTITUTE(SUBSTITUTE(I3," ",""), "_", ""))))</f>
@@ -1920,10 +1926,10 @@
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
       <c r="L3" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="M3" t="s">
         <v>47</v>
-      </c>
-      <c r="M3" t="s">
-        <v>48</v>
       </c>
       <c r="N3" t="str" cm="1">
         <f t="array" ref="N3">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K3, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -1934,39 +1940,39 @@
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
       <c r="P3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="Q3" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="R3" t="s">
         <v>50</v>
-      </c>
-      <c r="R3" t="s">
-        <v>51</v>
       </c>
       <c r="S3" t="str">
         <f>IF(R3="N", Q3, "write file name")</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
       <c r="T3" t="s">
+        <v>51</v>
+      </c>
+      <c r="U3" t="s">
         <v>52</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
         <v>53</v>
-      </c>
-      <c r="V3" t="s">
-        <v>54</v>
       </c>
       <c r="X3" s="7"/>
       <c r="Y3" t="s">
+        <v>54</v>
+      </c>
+      <c r="Z3" t="s">
         <v>55</v>
       </c>
-      <c r="Z3" t="s">
+      <c r="AD3" t="s">
         <v>56</v>
       </c>
-      <c r="AD3" t="s">
-        <v>57</v>
-      </c>
       <c r="AE3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AI3">
         <v>17</v>
@@ -1977,7 +1983,7 @@
     </row>
     <row r="4" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="7" t="str">
         <f t="shared" ref="B4:B45" si="7">C4 &amp; IF(D4&lt;&gt;"", "_" &amp; D4, "_") &amp; IF(E4&lt;&gt;"", "_" &amp; E4, "_") &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "")</f>
@@ -2001,7 +2007,7 @@
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J4" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2013,54 +2019,54 @@
       </c>
       <c r="L4" s="3"/>
       <c r="M4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N4" t="str" cm="1">
         <f t="array" ref="N4">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K4, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.7554%2FeLife.77875_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="O4" t="str" cm="1">
         <f t="array" ref="O4">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K4, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="P4" t="s">
+        <v>59</v>
+      </c>
+      <c r="Q4" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="R4" t="s">
         <v>61</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>62</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>63</v>
       </c>
-      <c r="T4" t="s">
+      <c r="U4" t="s">
+        <v>52</v>
+      </c>
+      <c r="V4" t="s">
         <v>64</v>
       </c>
-      <c r="U4" t="s">
-        <v>53</v>
-      </c>
-      <c r="V4" t="s">
+      <c r="W4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="W4" s="8" t="s">
+      <c r="X4" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="Y4" t="s">
         <v>67</v>
       </c>
-      <c r="Y4" t="s">
+      <c r="Z4" t="s">
         <v>68</v>
       </c>
-      <c r="Z4" t="s">
+      <c r="AD4" t="s">
         <v>69</v>
       </c>
-      <c r="AD4" t="s">
+      <c r="AE4" t="s">
         <v>70</v>
-      </c>
-      <c r="AE4" t="s">
-        <v>71</v>
       </c>
       <c r="AI4">
         <v>7</v>
@@ -2071,7 +2077,7 @@
     </row>
     <row r="5" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2095,7 +2101,7 @@
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J5" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2107,52 +2113,52 @@
       </c>
       <c r="L5" s="12"/>
       <c r="M5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N5" t="str" cm="1">
         <f t="array" ref="N5">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K5, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="O5" t="str" cm="1">
         <f t="array" ref="O5">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K5, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="P5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q5" s="9" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="R5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S5" t="str">
         <f>IF(R5="N", Q5, "write file name")</f>
         <v>elife-77875-supp3-v1.xlsx</v>
       </c>
       <c r="T5" t="s">
+        <v>73</v>
+      </c>
+      <c r="U5" t="s">
+        <v>52</v>
+      </c>
+      <c r="V5" t="s">
         <v>74</v>
       </c>
-      <c r="U5" t="s">
-        <v>53</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="W5" s="13" t="s">
         <v>75</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="X5" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="X5" s="9" t="s">
+      <c r="Y5" t="s">
         <v>77</v>
       </c>
-      <c r="Y5" t="s">
-        <v>78</v>
-      </c>
       <c r="Z5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AE5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="AI5">
         <v>5</v>
@@ -2163,7 +2169,7 @@
     </row>
     <row r="6" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B6" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2187,7 +2193,7 @@
       </c>
       <c r="H6" s="12"/>
       <c r="I6" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J6" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2199,7 +2205,7 @@
       </c>
       <c r="L6" s="12"/>
       <c r="M6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N6" t="str" cm="1">
         <f t="array" ref="N6">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K6, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2210,44 +2216,44 @@
         <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
       <c r="P6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q6" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="R6" t="s">
+        <v>61</v>
+      </c>
+      <c r="S6" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="R6" t="s">
-        <v>62</v>
-      </c>
-      <c r="S6" s="9" t="s">
+      <c r="T6" t="s">
+        <v>63</v>
+      </c>
+      <c r="U6" t="s">
         <v>83</v>
       </c>
-      <c r="T6" t="s">
-        <v>64</v>
-      </c>
-      <c r="U6" t="s">
+      <c r="V6" t="s">
         <v>84</v>
-      </c>
-      <c r="V6" t="s">
-        <v>85</v>
       </c>
       <c r="W6" s="13"/>
       <c r="X6" s="9"/>
       <c r="Y6" t="s">
+        <v>85</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD6" t="s">
         <v>86</v>
       </c>
-      <c r="Z6" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD6" t="s">
+      <c r="AI6" t="s">
         <v>87</v>
-      </c>
-      <c r="AI6" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="7" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B7" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2272,7 +2278,7 @@
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="J7" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2284,7 +2290,7 @@
       </c>
       <c r="L7" s="3"/>
       <c r="M7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N7" t="str" cm="1">
         <f t="array" ref="N7">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K7, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2295,45 +2301,45 @@
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
       </c>
       <c r="P7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q7" s="9" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="R7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="S7" t="str">
         <f>IF(R7="N", Q7, "write file name")</f>
         <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
       <c r="T7" t="s">
+        <v>73</v>
+      </c>
+      <c r="U7" t="s">
+        <v>52</v>
+      </c>
+      <c r="V7" t="s">
         <v>74</v>
       </c>
-      <c r="U7" t="s">
-        <v>53</v>
-      </c>
-      <c r="V7" t="s">
-        <v>75</v>
-      </c>
       <c r="W7" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="X7" s="7"/>
       <c r="Y7" t="s">
+        <v>92</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC7" t="s">
         <v>93</v>
       </c>
-      <c r="Z7" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC7" t="s">
+      <c r="AD7" t="s">
         <v>94</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>95</v>
-      </c>
-      <c r="AE7" t="s">
-        <v>96</v>
       </c>
       <c r="AI7">
         <v>10</v>
@@ -2344,7 +2350,7 @@
     </row>
     <row r="8" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B8" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2368,7 +2374,7 @@
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J8" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2379,10 +2385,10 @@
         <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N8" t="str" cm="1">
         <f t="array" ref="N8">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K8, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2393,47 +2399,47 @@
         <v>10.1159%2F000452856_TableS1.tsv</v>
       </c>
       <c r="P8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q8" s="9" t="s">
+        <v>99</v>
+      </c>
+      <c r="R8" t="s">
+        <v>61</v>
+      </c>
+      <c r="S8" t="s">
         <v>100</v>
       </c>
-      <c r="R8" t="s">
-        <v>62</v>
-      </c>
-      <c r="S8" t="s">
+      <c r="T8" t="s">
         <v>101</v>
       </c>
-      <c r="T8" t="s">
+      <c r="U8" t="s">
         <v>102</v>
       </c>
-      <c r="U8" t="s">
+      <c r="V8" t="s">
+        <v>74</v>
+      </c>
+      <c r="W8" s="8" t="s">
         <v>103</v>
-      </c>
-      <c r="V8" t="s">
-        <v>75</v>
-      </c>
-      <c r="W8" s="8" t="s">
-        <v>104</v>
       </c>
       <c r="X8" s="9"/>
       <c r="Y8" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z8" t="s">
         <v>105</v>
       </c>
-      <c r="Z8" t="s">
+      <c r="AA8" t="s">
         <v>106</v>
       </c>
-      <c r="AA8" t="s">
+      <c r="AB8" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE8" t="s">
         <v>107</v>
       </c>
-      <c r="AB8" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE8" t="s">
+      <c r="AF8" t="s">
         <v>108</v>
-      </c>
-      <c r="AF8" t="s">
-        <v>109</v>
       </c>
       <c r="AI8">
         <v>0</v>
@@ -2444,7 +2450,7 @@
     </row>
     <row r="9" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B9" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2468,7 +2474,7 @@
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J9" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2480,7 +2486,7 @@
       </c>
       <c r="L9" s="3"/>
       <c r="M9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N9" t="str" cm="1">
         <f t="array" ref="N9">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K9, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2491,38 +2497,38 @@
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
       <c r="P9" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q9" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="R9" t="s">
+        <v>61</v>
+      </c>
+      <c r="S9" t="s">
         <v>111</v>
       </c>
-      <c r="R9" t="s">
-        <v>62</v>
-      </c>
-      <c r="S9" t="s">
+      <c r="T9" t="s">
         <v>112</v>
       </c>
-      <c r="T9" t="s">
-        <v>113</v>
-      </c>
       <c r="U9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X9" s="7"/>
       <c r="Y9" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Z9" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE9" t="s">
         <v>114</v>
-      </c>
-      <c r="AA9" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB9" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE9" t="s">
-        <v>115</v>
       </c>
       <c r="AI9">
         <v>4</v>
@@ -2533,7 +2539,7 @@
     </row>
     <row r="10" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B10" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2558,7 +2564,7 @@
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J10" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2570,7 +2576,7 @@
       </c>
       <c r="L10" s="3"/>
       <c r="M10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="N10" t="str" cm="1">
         <f t="array" ref="N10">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K10, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2581,41 +2587,41 @@
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
       </c>
       <c r="P10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q10" s="9" t="s">
+        <v>117</v>
+      </c>
+      <c r="R10" t="s">
+        <v>61</v>
+      </c>
+      <c r="S10" t="s">
         <v>118</v>
       </c>
-      <c r="R10" t="s">
-        <v>62</v>
-      </c>
-      <c r="S10" t="s">
+      <c r="T10" t="s">
         <v>119</v>
       </c>
-      <c r="T10" t="s">
+      <c r="U10" t="s">
+        <v>52</v>
+      </c>
+      <c r="V10" t="s">
+        <v>64</v>
+      </c>
+      <c r="W10" s="8" t="s">
         <v>120</v>
-      </c>
-      <c r="U10" t="s">
-        <v>53</v>
-      </c>
-      <c r="V10" t="s">
-        <v>65</v>
-      </c>
-      <c r="W10" s="8" t="s">
-        <v>121</v>
       </c>
       <c r="X10" s="7"/>
       <c r="Y10" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>41</v>
+      </c>
+      <c r="AD10" t="s">
         <v>122</v>
       </c>
-      <c r="Z10" t="s">
-        <v>42</v>
-      </c>
-      <c r="AD10" t="s">
-        <v>123</v>
-      </c>
       <c r="AE10" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AI10">
         <v>3</v>
@@ -2626,7 +2632,7 @@
     </row>
     <row r="11" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B11" s="7" t="str">
         <f>C11 &amp; IF(D11&lt;&gt;"", "_" &amp; D11, "_") &amp; IF(E11&lt;&gt;"", "_" &amp; E11, "_") &amp; IF(F11&lt;&gt;"", "_" &amp; F11, "")</f>
@@ -2651,7 +2657,7 @@
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J11" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2663,7 +2669,7 @@
       </c>
       <c r="L11" s="3"/>
       <c r="M11" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N11" t="str" cm="1">
         <f t="array" ref="N11">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K11, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2674,38 +2680,38 @@
         <v>10.1159%2F000124401_TableI.tsv</v>
       </c>
       <c r="P11" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q11" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="R11" t="s">
+        <v>61</v>
+      </c>
+      <c r="S11" t="s">
         <v>126</v>
       </c>
-      <c r="R11" t="s">
-        <v>62</v>
-      </c>
-      <c r="S11" t="s">
-        <v>127</v>
-      </c>
       <c r="T11" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V11" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X11" s="7"/>
       <c r="Y11" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z11" t="s">
         <v>128</v>
       </c>
-      <c r="Z11" t="s">
+      <c r="AC11" t="s">
         <v>129</v>
       </c>
-      <c r="AC11" t="s">
-        <v>130</v>
-      </c>
       <c r="AE11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AI11">
         <v>7</v>
@@ -2716,7 +2722,7 @@
     </row>
     <row r="12" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B12" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2741,7 +2747,7 @@
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="J12" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2753,7 +2759,7 @@
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N12" t="str" cm="1">
         <f t="array" ref="N12">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K12, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2764,7 +2770,7 @@
         <v>notfound</v>
       </c>
       <c r="P12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q12" s="14"/>
       <c r="S12" t="str">
@@ -2772,28 +2778,28 @@
         <v>write file name</v>
       </c>
       <c r="T12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="V12" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="X12" s="7"/>
       <c r="Y12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AE12" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG12" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B13" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2818,7 +2824,7 @@
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J13" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2830,7 +2836,7 @@
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N13" t="str" cm="1">
         <f t="array" ref="N13">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K13, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2841,7 +2847,7 @@
         <v>notfound</v>
       </c>
       <c r="P13" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q13" s="14"/>
       <c r="S13" t="str">
@@ -2849,22 +2855,22 @@
         <v>write file name</v>
       </c>
       <c r="T13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X13" s="7"/>
       <c r="Y13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B14" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2888,7 +2894,7 @@
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J14" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2900,7 +2906,7 @@
       </c>
       <c r="L14" s="3"/>
       <c r="M14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N14" t="str" cm="1">
         <f t="array" ref="N14">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K14, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -2911,43 +2917,43 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q14" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="R14" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S14" t="s">
         <v>137</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S14" t="s">
+      <c r="T14" t="s">
+        <v>63</v>
+      </c>
+      <c r="U14" t="s">
+        <v>52</v>
+      </c>
+      <c r="V14" t="s">
+        <v>64</v>
+      </c>
+      <c r="W14" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="T14" t="s">
-        <v>64</v>
-      </c>
-      <c r="U14" t="s">
-        <v>53</v>
-      </c>
-      <c r="V14" t="s">
-        <v>65</v>
-      </c>
-      <c r="W14" s="8" t="s">
+      <c r="X14" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="X14" s="7" t="s">
+      <c r="Y14" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB14" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE14" t="s">
         <v>140</v>
-      </c>
-      <c r="Y14" t="s">
-        <v>105</v>
-      </c>
-      <c r="AA14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB14" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE14" t="s">
-        <v>141</v>
       </c>
       <c r="AI14">
         <v>9</v>
@@ -2958,7 +2964,7 @@
     </row>
     <row r="15" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B15" s="7" t="str">
         <f t="shared" si="7"/>
@@ -2986,7 +2992,7 @@
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J15" s="3" t="str">
         <f t="shared" si="6"/>
@@ -2998,7 +3004,7 @@
       </c>
       <c r="L15" s="3"/>
       <c r="M15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N15" t="str" cm="1">
         <f t="array" ref="N15">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K15, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3009,43 +3015,43 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q15" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="R15" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S15" t="s">
         <v>143</v>
       </c>
-      <c r="R15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S15" t="s">
+      <c r="T15" t="s">
+        <v>63</v>
+      </c>
+      <c r="U15" t="s">
+        <v>52</v>
+      </c>
+      <c r="V15" t="s">
+        <v>64</v>
+      </c>
+      <c r="W15" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="X15" s="7" t="s">
         <v>144</v>
       </c>
-      <c r="T15" t="s">
-        <v>64</v>
-      </c>
-      <c r="U15" t="s">
-        <v>53</v>
-      </c>
-      <c r="V15" t="s">
-        <v>65</v>
-      </c>
-      <c r="W15" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="X15" s="7" t="s">
-        <v>145</v>
-      </c>
       <c r="Y15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AA15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB15" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AE15" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AI15">
         <v>9</v>
@@ -3056,7 +3062,7 @@
     </row>
     <row r="16" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B16" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3081,7 +3087,7 @@
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J16" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3093,7 +3099,7 @@
       </c>
       <c r="L16" s="3"/>
       <c r="M16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N16" t="str" cm="1">
         <f t="array" ref="N16">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K16, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3104,43 +3110,43 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P16" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q16" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="R16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S16" t="s">
         <v>147</v>
       </c>
-      <c r="R16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S16" t="s">
+      <c r="T16" t="s">
+        <v>63</v>
+      </c>
+      <c r="U16" t="s">
+        <v>52</v>
+      </c>
+      <c r="V16" t="s">
+        <v>64</v>
+      </c>
+      <c r="W16" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="X16" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="T16" t="s">
-        <v>64</v>
-      </c>
-      <c r="U16" t="s">
-        <v>53</v>
-      </c>
-      <c r="V16" t="s">
-        <v>65</v>
-      </c>
-      <c r="W16" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="X16" s="7" t="s">
-        <v>149</v>
-      </c>
       <c r="Y16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AA16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB16" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AE16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AI16">
         <v>9</v>
@@ -3151,7 +3157,7 @@
     </row>
     <row r="17" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B17" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3176,7 +3182,7 @@
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J17" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3188,7 +3194,7 @@
       </c>
       <c r="L17" s="3"/>
       <c r="M17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N17" t="str" cm="1">
         <f t="array" ref="N17">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K17, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3199,43 +3205,43 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q17" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="R17" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S17" t="s">
         <v>151</v>
       </c>
-      <c r="R17" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S17" t="s">
+      <c r="T17" t="s">
+        <v>63</v>
+      </c>
+      <c r="U17" t="s">
+        <v>52</v>
+      </c>
+      <c r="V17" t="s">
+        <v>64</v>
+      </c>
+      <c r="W17" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="X17" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="T17" t="s">
-        <v>64</v>
-      </c>
-      <c r="U17" t="s">
-        <v>53</v>
-      </c>
-      <c r="V17" t="s">
-        <v>65</v>
-      </c>
-      <c r="W17" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="X17" s="9" t="s">
-        <v>153</v>
-      </c>
       <c r="Y17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AA17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AE17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AI17">
         <v>8</v>
@@ -3246,7 +3252,7 @@
     </row>
     <row r="18" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B18" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3271,7 +3277,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J18" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3283,7 +3289,7 @@
       </c>
       <c r="L18" s="3"/>
       <c r="M18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N18" t="str" cm="1">
         <f t="array" ref="N18">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K18, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3294,43 +3300,43 @@
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="P18" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q18" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="R18" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S18" t="s">
         <v>155</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S18" t="s">
+      <c r="T18" t="s">
+        <v>63</v>
+      </c>
+      <c r="U18" t="s">
+        <v>52</v>
+      </c>
+      <c r="V18" t="s">
+        <v>64</v>
+      </c>
+      <c r="W18" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="X18" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="T18" t="s">
-        <v>64</v>
-      </c>
-      <c r="U18" t="s">
-        <v>53</v>
-      </c>
-      <c r="V18" t="s">
-        <v>65</v>
-      </c>
-      <c r="W18" s="8" t="s">
-        <v>139</v>
-      </c>
-      <c r="X18" s="9" t="s">
-        <v>157</v>
-      </c>
       <c r="Y18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AA18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AE18" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AI18">
         <v>9</v>
@@ -3341,7 +3347,7 @@
     </row>
     <row r="19" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B19" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3366,7 +3372,7 @@
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="J19" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3378,7 +3384,7 @@
       </c>
       <c r="L19" s="3"/>
       <c r="M19" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N19" t="str" cm="1">
         <f t="array" ref="N19">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K19, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3389,40 +3395,40 @@
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="P19" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q19" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="R19" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S19" t="s">
         <v>160</v>
       </c>
-      <c r="R19" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S19" t="s">
+      <c r="T19" t="s">
+        <v>63</v>
+      </c>
+      <c r="U19" t="s">
+        <v>52</v>
+      </c>
+      <c r="V19" t="s">
+        <v>84</v>
+      </c>
+      <c r="X19" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="T19" t="s">
-        <v>64</v>
-      </c>
-      <c r="U19" t="s">
-        <v>53</v>
-      </c>
-      <c r="V19" t="s">
-        <v>85</v>
-      </c>
-      <c r="X19" s="7" t="s">
+      <c r="Y19" t="s">
         <v>162</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="AA19" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE19" t="s">
         <v>163</v>
-      </c>
-      <c r="AA19" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB19" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE19" t="s">
-        <v>164</v>
       </c>
       <c r="AI19">
         <v>0</v>
@@ -3436,7 +3442,7 @@
     </row>
     <row r="20" spans="1:37" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B20" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3461,7 +3467,7 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J20" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3473,7 +3479,7 @@
       </c>
       <c r="L20" s="3"/>
       <c r="M20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N20" t="str" cm="1">
         <f t="array" ref="N20">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K20, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3484,40 +3490,40 @@
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="P20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q20" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="R20" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S20" t="s">
         <v>166</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="T20" t="s">
+        <v>63</v>
+      </c>
+      <c r="U20" t="s">
+        <v>52</v>
+      </c>
+      <c r="V20" t="s">
+        <v>84</v>
+      </c>
+      <c r="X20" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="T20" t="s">
-        <v>64</v>
-      </c>
-      <c r="U20" t="s">
-        <v>53</v>
-      </c>
-      <c r="V20" t="s">
-        <v>85</v>
-      </c>
-      <c r="X20" s="7" t="s">
+      <c r="Y20" t="s">
         <v>168</v>
       </c>
-      <c r="Y20" t="s">
-        <v>169</v>
-      </c>
       <c r="AA20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AB20" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AE20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="AI20">
         <v>0</v>
@@ -3531,7 +3537,7 @@
     </row>
     <row r="21" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B21" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3558,7 +3564,7 @@
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J21" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3570,7 +3576,7 @@
       </c>
       <c r="L21" s="3"/>
       <c r="M21" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N21" t="str" cm="1">
         <f t="array" ref="N21">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K21, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3581,7 +3587,7 @@
         <v>notfound</v>
       </c>
       <c r="P21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q21" s="14"/>
       <c r="S21" t="str">
@@ -3589,24 +3595,24 @@
         <v>write file name</v>
       </c>
       <c r="T21" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X21" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="Y21" t="s">
         <v>172</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="AE21" t="s">
         <v>173</v>
-      </c>
-      <c r="AE21" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B22" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3630,7 +3636,7 @@
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J22" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3642,7 +3648,7 @@
       </c>
       <c r="L22" s="3"/>
       <c r="M22" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N22" t="str" cm="1">
         <f t="array" ref="N22">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K22, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3653,7 +3659,7 @@
         <v>notfound</v>
       </c>
       <c r="P22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q22" s="14"/>
       <c r="S22" t="str">
@@ -3661,24 +3667,24 @@
         <v>write file name</v>
       </c>
       <c r="T22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X22" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="Y22" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE22" t="s">
         <v>173</v>
-      </c>
-      <c r="AE22" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B23" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3702,7 +3708,7 @@
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="J23" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3714,7 +3720,7 @@
       </c>
       <c r="L23" s="3"/>
       <c r="M23" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N23" t="str" cm="1">
         <f t="array" ref="N23">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K23, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3725,7 +3731,7 @@
         <v>notfound</v>
       </c>
       <c r="P23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q23" s="14"/>
       <c r="S23" t="str">
@@ -3733,24 +3739,24 @@
         <v>write file name</v>
       </c>
       <c r="T23" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U23" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X23" s="11" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="Y23" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE23" t="s">
         <v>173</v>
-      </c>
-      <c r="AE23" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B24" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3774,7 +3780,7 @@
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J24" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3786,7 +3792,7 @@
       </c>
       <c r="L24" s="3"/>
       <c r="M24" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="N24" t="str" cm="1">
         <f t="array" ref="N24">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K24, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3797,7 +3803,7 @@
         <v>notfound</v>
       </c>
       <c r="P24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q24" s="14"/>
       <c r="S24" t="str">
@@ -3805,24 +3811,24 @@
         <v>write file name</v>
       </c>
       <c r="T24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U24" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X24" s="11" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="Y24" t="s">
+        <v>172</v>
+      </c>
+      <c r="AE24" t="s">
         <v>173</v>
-      </c>
-      <c r="AE24" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B25" s="7" t="str">
         <f t="shared" si="7"/>
@@ -3846,7 +3852,7 @@
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J25" s="3" t="str">
         <f t="shared" si="6"/>
@@ -3858,7 +3864,7 @@
       </c>
       <c r="L25" s="3"/>
       <c r="M25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N25" t="str" cm="1">
         <f t="array" ref="N25">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K25, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3869,46 +3875,46 @@
         <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="P25" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q25" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="R25" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="S25" t="s">
         <v>179</v>
       </c>
-      <c r="R25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="S25" t="s">
+      <c r="T25" t="s">
+        <v>63</v>
+      </c>
+      <c r="U25" t="s">
+        <v>52</v>
+      </c>
+      <c r="V25" t="s">
+        <v>64</v>
+      </c>
+      <c r="W25" s="8" t="s">
         <v>180</v>
       </c>
-      <c r="T25" t="s">
-        <v>64</v>
-      </c>
-      <c r="U25" t="s">
-        <v>53</v>
-      </c>
-      <c r="V25" t="s">
-        <v>65</v>
-      </c>
-      <c r="W25" s="8" t="s">
+      <c r="X25" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="X25" s="7" t="s">
+      <c r="Y25" t="s">
+        <v>104</v>
+      </c>
+      <c r="Z25" t="s">
+        <v>105</v>
+      </c>
+      <c r="AA25" t="s">
+        <v>106</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE25" t="s">
         <v>182</v>
-      </c>
-      <c r="Y25" t="s">
-        <v>105</v>
-      </c>
-      <c r="Z25" t="s">
-        <v>106</v>
-      </c>
-      <c r="AA25" t="s">
-        <v>107</v>
-      </c>
-      <c r="AB25" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE25" t="s">
-        <v>183</v>
       </c>
       <c r="AI25">
         <v>2</v>
@@ -3919,7 +3925,7 @@
     </row>
     <row r="26" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B26" s="7" t="str">
         <f t="shared" ref="B26" si="11">C26 &amp; IF(D26&lt;&gt;"", "_" &amp; D26, "_") &amp; IF(E26&lt;&gt;"", "_" &amp; E26, "_") &amp; IF(F26&lt;&gt;"", "_" &amp; F26, "")</f>
@@ -3944,7 +3950,7 @@
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J26" s="3" t="str">
         <f t="shared" ref="J26" si="15">TRIM(_xlfn.TEXTJOIN("_",FALSE,B26,(SUBSTITUTE(SUBSTITUTE(I26," ",""), "_", ""))))</f>
@@ -3956,7 +3962,7 @@
       </c>
       <c r="L26" s="3"/>
       <c r="M26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N26" t="str" cm="1">
         <f t="array" ref="N26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -3967,38 +3973,38 @@
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="P26" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q26" s="14" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="R26" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S26" t="s">
+        <v>184</v>
+      </c>
+      <c r="T26" t="s">
         <v>185</v>
       </c>
-      <c r="T26" t="s">
-        <v>186</v>
-      </c>
       <c r="U26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="W26" s="8"/>
       <c r="X26" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="Y26" t="s">
         <v>272</v>
       </c>
-      <c r="Y26" t="s">
-        <v>273</v>
-      </c>
       <c r="Z26" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB26" t="s">
         <v>106</v>
       </c>
-      <c r="AB26" t="s">
-        <v>107</v>
-      </c>
       <c r="AE26" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AI26">
         <v>1</v>
@@ -4009,7 +4015,7 @@
     </row>
     <row r="27" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B27" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4037,7 +4043,7 @@
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J27" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4049,7 +4055,7 @@
       </c>
       <c r="L27" s="3"/>
       <c r="M27" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N27" t="str" cm="1">
         <f t="array" ref="N27">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K27, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4060,43 +4066,43 @@
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="P27" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q27" s="14" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="R27" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S27" t="s">
+        <v>184</v>
+      </c>
+      <c r="T27" t="s">
         <v>185</v>
       </c>
-      <c r="T27" t="s">
+      <c r="U27" t="s">
+        <v>52</v>
+      </c>
+      <c r="V27" t="s">
+        <v>64</v>
+      </c>
+      <c r="W27" s="8" t="s">
         <v>186</v>
       </c>
-      <c r="U27" t="s">
-        <v>53</v>
-      </c>
-      <c r="V27" t="s">
-        <v>65</v>
-      </c>
-      <c r="W27" s="8" t="s">
+      <c r="X27" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="X27" s="7" t="s">
+      <c r="Y27" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z27" t="s">
         <v>188</v>
       </c>
-      <c r="Y27" t="s">
-        <v>163</v>
-      </c>
-      <c r="Z27" t="s">
+      <c r="AB27" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE27" t="s">
         <v>189</v>
-      </c>
-      <c r="AB27" t="s">
-        <v>107</v>
-      </c>
-      <c r="AE27" t="s">
-        <v>190</v>
       </c>
       <c r="AI27">
         <v>1</v>
@@ -4107,7 +4113,7 @@
     </row>
     <row r="28" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B28" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4132,7 +4138,7 @@
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="J28" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4144,7 +4150,7 @@
       </c>
       <c r="L28" s="3"/>
       <c r="M28" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N28" t="str" cm="1">
         <f t="array" ref="N28">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K28, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4155,43 +4161,43 @@
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="P28" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q28" s="14" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="R28" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="S28" t="s">
+        <v>191</v>
+      </c>
+      <c r="T28" t="s">
         <v>192</v>
       </c>
-      <c r="T28" t="s">
+      <c r="U28" t="s">
+        <v>52</v>
+      </c>
+      <c r="V28" t="s">
+        <v>64</v>
+      </c>
+      <c r="W28" s="8" t="s">
+        <v>186</v>
+      </c>
+      <c r="X28" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="U28" t="s">
-        <v>53</v>
-      </c>
-      <c r="V28" t="s">
-        <v>65</v>
-      </c>
-      <c r="W28" s="8" t="s">
-        <v>187</v>
-      </c>
-      <c r="X28" s="7" t="s">
-        <v>194</v>
-      </c>
       <c r="Y28" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="Z28" t="s">
+        <v>105</v>
+      </c>
+      <c r="AB28" t="s">
         <v>106</v>
       </c>
-      <c r="AB28" t="s">
-        <v>107</v>
-      </c>
       <c r="AE28" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AI28">
         <v>1</v>
@@ -4202,7 +4208,7 @@
     </row>
     <row r="29" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B29" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4227,7 +4233,7 @@
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="12" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J29" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4239,7 +4245,7 @@
       </c>
       <c r="L29" s="3"/>
       <c r="M29" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N29" t="str" cm="1">
         <f t="array" ref="N29">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K29, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4250,7 +4256,7 @@
         <v>notfound</v>
       </c>
       <c r="P29" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q29" s="14"/>
       <c r="S29" t="str">
@@ -4258,34 +4264,34 @@
         <v>write file name</v>
       </c>
       <c r="T29" t="s">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s">
+        <v>52</v>
+      </c>
+      <c r="V29" t="s">
         <v>74</v>
       </c>
-      <c r="U29" t="s">
-        <v>53</v>
-      </c>
-      <c r="V29" t="s">
-        <v>75</v>
-      </c>
       <c r="W29" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X29" s="7"/>
       <c r="Y29" t="s">
+        <v>198</v>
+      </c>
+      <c r="Z29" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC29" t="s">
         <v>199</v>
       </c>
-      <c r="Z29" t="s">
-        <v>56</v>
-      </c>
-      <c r="AC29" t="s">
-        <v>200</v>
-      </c>
       <c r="AE29" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="30" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B30" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4309,10 +4315,10 @@
         <v>10.1098/rspb.2017.1765</v>
       </c>
       <c r="H30" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I30" s="3" t="s">
         <v>202</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>203</v>
       </c>
       <c r="J30" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4324,7 +4330,7 @@
       </c>
       <c r="L30" s="3"/>
       <c r="M30" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N30" t="str" cm="1">
         <f t="array" ref="N30">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K30, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4335,7 +4341,7 @@
         <v>notfound</v>
       </c>
       <c r="P30" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q30" s="14"/>
       <c r="S30" t="str">
@@ -4343,34 +4349,34 @@
         <v>write file name</v>
       </c>
       <c r="T30" t="s">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s">
+        <v>52</v>
+      </c>
+      <c r="V30" t="s">
         <v>74</v>
       </c>
-      <c r="U30" t="s">
-        <v>53</v>
-      </c>
-      <c r="V30" t="s">
-        <v>75</v>
-      </c>
       <c r="W30" s="8" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="X30" s="7"/>
       <c r="Y30" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="Z30" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AC30" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AE30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B31" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4389,7 +4395,7 @@
         <v>2004</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="5"/>
@@ -4397,7 +4403,7 @@
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J31" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4409,7 +4415,7 @@
       </c>
       <c r="L31" s="3"/>
       <c r="M31" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N31" t="str" cm="1">
         <f t="array" ref="N31">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K31, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4420,7 +4426,7 @@
         <v>notfound</v>
       </c>
       <c r="P31" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q31" s="14"/>
       <c r="S31" t="str">
@@ -4428,27 +4434,27 @@
         <v>write file name</v>
       </c>
       <c r="T31" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U31" t="s">
+        <v>207</v>
+      </c>
+      <c r="X31" s="7" t="s">
         <v>208</v>
       </c>
-      <c r="X31" s="7" t="s">
+      <c r="Y31" t="s">
         <v>209</v>
       </c>
-      <c r="Y31" t="s">
-        <v>210</v>
-      </c>
       <c r="Z31" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AE31" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="32" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B32" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4470,7 +4476,7 @@
         <v>2004</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G32" t="str">
         <f t="shared" si="5"/>
@@ -4478,7 +4484,7 @@
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="J32" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4490,7 +4496,7 @@
       </c>
       <c r="L32" s="3"/>
       <c r="M32" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N32" t="str" cm="1">
         <f t="array" ref="N32">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K32, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4501,7 +4507,7 @@
         <v>notfound</v>
       </c>
       <c r="P32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q32" s="14"/>
       <c r="S32" t="str">
@@ -4509,27 +4515,27 @@
         <v>write file name</v>
       </c>
       <c r="T32" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U32" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X32" s="11" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="Y32" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="Z32" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="AE32" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="33" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B33" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4554,7 +4560,7 @@
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="J33" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4566,7 +4572,7 @@
       </c>
       <c r="L33" s="3"/>
       <c r="M33" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N33" t="str" cm="1">
         <f t="array" ref="N33">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K33, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4577,7 +4583,7 @@
         <v>notfound</v>
       </c>
       <c r="P33" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q33" s="14"/>
       <c r="S33" t="str">
@@ -4585,22 +4591,22 @@
         <v>write file name</v>
       </c>
       <c r="T33" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="U33" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="X33" s="7"/>
       <c r="Y33" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AE33" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B34" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4625,7 +4631,7 @@
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J34" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4637,7 +4643,7 @@
       </c>
       <c r="L34" s="3"/>
       <c r="M34" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N34" t="str" cm="1">
         <f t="array" ref="N34">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K34, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
@@ -4648,7 +4654,7 @@
         <v>notfound</v>
       </c>
       <c r="P34" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="Q34" s="14"/>
       <c r="S34" t="str">
@@ -4656,22 +4662,22 @@
         <v>write file name</v>
       </c>
       <c r="T34" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U34" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="X34" s="7"/>
       <c r="Y34" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AE34" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="35" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B35" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4694,7 +4700,7 @@
         <v>10.1126/science.aaa9101</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J35" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4713,7 +4719,7 @@
         <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="P35" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI35">
         <v>10</v>
@@ -4724,7 +4730,7 @@
     </row>
     <row r="36" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B36" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4747,7 +4753,7 @@
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J36" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4766,15 +4772,15 @@
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
       </c>
       <c r="P36" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI36" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B37" s="7" t="str">
         <f t="shared" ref="B37" si="18">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
@@ -4797,7 +4803,7 @@
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="J37" s="3" t="str">
         <f t="shared" ref="J37" si="21">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
@@ -4816,15 +4822,15 @@
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
       </c>
       <c r="P37" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI37" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="38" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B38" s="7" t="str">
         <f t="shared" ref="B38" si="23">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
@@ -4847,7 +4853,7 @@
         <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="J38" s="3" t="str">
         <f t="shared" ref="J38" si="26">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
@@ -4866,15 +4872,15 @@
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
       </c>
       <c r="P38" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI38" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="39" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B39" s="7" t="str">
         <f t="shared" ref="B39" si="28">C39 &amp; IF(D39&lt;&gt;"", "_" &amp; D39, "_") &amp; IF(E39&lt;&gt;"", "_" &amp; E39, "_") &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "")</f>
@@ -4897,7 +4903,7 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J39" s="3" t="str">
         <f t="shared" ref="J39" si="32">TRIM(_xlfn.TEXTJOIN("_",FALSE,B39,(SUBSTITUTE(SUBSTITUTE(I39," ",""), "_", ""))))</f>
@@ -4916,7 +4922,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P39" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI39">
         <v>6</v>
@@ -4927,7 +4933,7 @@
     </row>
     <row r="40" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B40" s="7" t="str">
         <f t="shared" si="7"/>
@@ -4950,7 +4956,7 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="J40" s="3" t="str">
         <f t="shared" si="6"/>
@@ -4969,7 +4975,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P40" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI40">
         <v>3</v>
@@ -4980,7 +4986,7 @@
     </row>
     <row r="41" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B41" s="7" t="str">
         <f t="shared" si="7"/>
@@ -5003,7 +5009,7 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J41" s="3" t="str">
         <f t="shared" si="6"/>
@@ -5022,15 +5028,15 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P41" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI41" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="42" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B42" s="7" t="str">
         <f t="shared" ref="B42" si="34">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
@@ -5053,7 +5059,7 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J42" s="3" t="str">
         <f t="shared" ref="J42" si="38">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
@@ -5072,7 +5078,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P42" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI42">
         <v>8</v>
@@ -5083,7 +5089,7 @@
     </row>
     <row r="43" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B43" s="7" t="str">
         <f t="shared" ref="B43" si="40">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
@@ -5109,7 +5115,7 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J43" s="3" t="str">
         <f t="shared" ref="J43" si="44">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
@@ -5128,7 +5134,7 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P43" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI43">
         <v>7</v>
@@ -5139,7 +5145,7 @@
     </row>
     <row r="44" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A44" s="17" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B44" s="18" t="str">
         <f t="shared" ref="B44" si="46">C44 &amp; IF(D44&lt;&gt;"", "_" &amp; D44, "_") &amp; IF(E44&lt;&gt;"", "_" &amp; E44, "_") &amp; IF(F44&lt;&gt;"", "_" &amp; F44, "")</f>
@@ -5163,7 +5169,7 @@
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="I44" s="20" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="J44" s="20" t="str">
         <f t="shared" ref="J44" si="50">TRIM(_xlfn.TEXTJOIN("_",FALSE,B44,(SUBSTITUTE(SUBSTITUTE(I44," ",""), "_", ""))))</f>
@@ -5182,12 +5188,12 @@
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
       <c r="P44" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="45" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B45" s="7" t="str">
         <f t="shared" si="7"/>
@@ -5210,7 +5216,7 @@
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J45" s="3" t="str">
         <f t="shared" si="6"/>
@@ -5229,13 +5235,13 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="P45" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X45" t="s">
+        <v>276</v>
+      </c>
+      <c r="AA45" t="s">
         <v>277</v>
-      </c>
-      <c r="AA45" t="s">
-        <v>278</v>
       </c>
       <c r="AI45">
         <v>9</v>
@@ -5246,7 +5252,7 @@
     </row>
     <row r="46" spans="1:37" ht="16" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B46" s="7" t="str">
         <f t="shared" ref="B46" si="52">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
@@ -5269,7 +5275,7 @@
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="J46" s="3" t="str">
         <f t="shared" ref="J46" si="55">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
@@ -5288,13 +5294,13 @@
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="P46" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="X46" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="AA46" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AI46">
         <v>6</v>
@@ -5305,7 +5311,7 @@
     </row>
     <row r="47" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
       <c r="A47" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B47" s="18" t="str">
         <f t="shared" ref="B47" si="57">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
@@ -5332,7 +5338,7 @@
         <v>10.3389/fnhum.2013.00424</v>
       </c>
       <c r="I47" s="20" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="J47" s="20" t="str">
         <f t="shared" ref="J47" si="60">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
@@ -5351,10 +5357,10 @@
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
       <c r="P47" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AA47" s="17" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="AI47" s="17">
         <v>7</v>
@@ -5365,7 +5371,7 @@
     </row>
     <row r="48" spans="1:37" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B48" s="22" t="str">
         <f t="shared" ref="B48" si="61">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
@@ -5389,7 +5395,7 @@
         <v>10.1159/000323671</v>
       </c>
       <c r="I48" s="15" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="J48" s="23" t="str">
         <f t="shared" ref="J48" si="64">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
@@ -5408,15 +5414,15 @@
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="P48" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI48" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="49" spans="1:35" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B49" s="22" t="str">
         <f t="shared" ref="B49" si="65">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
@@ -5440,7 +5446,7 @@
         <v>10.1159/000323671</v>
       </c>
       <c r="I49" s="15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="J49" s="23" t="str">
         <f t="shared" ref="J49" si="69">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
@@ -5459,15 +5465,15 @@
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="P49" s="23" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AI49" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="50" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B50" s="22" t="str">
         <f t="shared" ref="B50:B53" si="70">C50 &amp; IF(D50&lt;&gt;"", "_" &amp; D50, "_") &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "")</f>
@@ -5495,7 +5501,7 @@
       </c>
       <c r="H50" s="15"/>
       <c r="I50" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J50" s="23" t="str">
         <f t="shared" ref="J50:J52" si="74">TRIM(_xlfn.TEXTJOIN("_",FALSE,B50,(SUBSTITUTE(SUBSTITUTE(I50," ",""), "_", ""))))</f>
@@ -5506,15 +5512,23 @@
         <v>10.1016%2Fs0166-4328(98)00151-x	_Table1</v>
       </c>
       <c r="M50" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="N50" s="15" t="str" cm="1">
+        <f t="array" ref="N50">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K50, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="O50" s="15" t="str" cm="1">
+        <f t="array" ref="O50">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K50, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>notfound</v>
       </c>
       <c r="V50" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B51" s="22" t="str">
         <f t="shared" si="70"/>
@@ -5539,7 +5553,7 @@
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J51" s="23" t="str">
         <f t="shared" si="74"/>
@@ -5550,18 +5564,26 @@
         <v>10.1111%2Fbrv.12350	_TableS2</v>
       </c>
       <c r="M51" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="N51" s="15" t="str" cm="1">
+        <f t="array" ref="N51">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K51, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="O51" s="15" t="str" cm="1">
+        <f t="array" ref="O51">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K51, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>notfound</v>
       </c>
       <c r="X51" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="AC51" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="52" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B52" s="22" t="str">
         <f t="shared" si="70"/>
@@ -5586,7 +5608,7 @@
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J52" s="23" t="str">
         <f t="shared" si="74"/>
@@ -5597,18 +5619,26 @@
         <v>10.1073%2Fpnas.1716956116	_SupplementaryTableS1</v>
       </c>
       <c r="M52" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="N52" s="15" t="str" cm="1">
+        <f t="array" ref="N52">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K52, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="O52" s="15" t="str" cm="1">
+        <f t="array" ref="O52">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K52, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>notfound</v>
       </c>
       <c r="X52" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="AC52" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="53" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B53" s="22" t="str">
         <f t="shared" si="70"/>
@@ -5633,7 +5663,7 @@
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J53" s="23" t="str">
         <f t="shared" ref="J53" si="77">TRIM(_xlfn.TEXTJOIN("_",FALSE,B53,(SUBSTITUTE(SUBSTITUTE(I53," ",""), "_", ""))))</f>
@@ -5644,66 +5674,66 @@
         <v>10.1159%2F000319019_Table1</v>
       </c>
       <c r="M53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N53" s="15" t="str" cm="1">
         <f t="array" ref="N53">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K53, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
       <c r="O53" s="15" t="str" cm="1">
         <f t="array" ref="O53">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K53, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
       <c r="P53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q53" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="X53" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="Z53" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="AC53" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="AE53" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B54" s="22" t="str">
-        <f t="shared" ref="B54:B55" si="79">C54 &amp; IF(D54&lt;&gt;"", "_" &amp; D54, "_") &amp; IF(E54&lt;&gt;"", "_" &amp; E54, "_") &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "")</f>
+        <f t="shared" ref="B54:B56" si="79">C54 &amp; IF(D54&lt;&gt;"", "_" &amp; D54, "_") &amp; IF(E54&lt;&gt;"", "_" &amp; E54, "_") &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "")</f>
         <v>Burish_etal_2010</v>
       </c>
       <c r="C54" s="24" t="str">
-        <f t="shared" ref="C54:C55" si="80">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="C54:C56" si="80">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
         <v>Burish</v>
       </c>
       <c r="D54" s="9" t="str">
-        <f t="shared" ref="D54:D55" si="81">IF(ISNUMBER(FIND("&amp;", A54)),
+        <f t="shared" ref="D54:D56" si="81">IF(ISNUMBER(FIND("&amp;", A54)),
     IF(LEN(A54)-LEN(SUBSTITUTE(A54, ",", ""))&gt;=6, "etal", MID(A54, SEARCH("&amp; ", A54)+2, SEARCH(",", A54, SEARCH("&amp; ", A54)+2) - SEARCH("&amp; ", A54)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="E54" s="24" t="str">
-        <f t="shared" ref="E54:E55" si="82">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
+        <f t="shared" ref="E54:E56" si="82">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
         <v>2010</v>
       </c>
       <c r="F54" s="24"/>
       <c r="G54" t="str">
-        <f t="shared" ref="G54:G55" si="83">_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
+        <f t="shared" ref="G54:G56" si="83">_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
         <v xml:space="preserve">10.1159/000319019 </v>
       </c>
       <c r="H54" s="15"/>
       <c r="I54" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J54" s="23" t="str">
         <f t="shared" ref="J54:J55" si="84">TRIM(_xlfn.TEXTJOIN("_",FALSE,B54,(SUBSTITUTE(SUBSTITUTE(I54," ",""), "_", ""))))</f>
@@ -5714,27 +5744,35 @@
         <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
       <c r="M54" s="15" t="s">
-        <v>298</v>
+        <v>297</v>
+      </c>
+      <c r="N54" s="15" t="str" cm="1">
+        <f t="array" ref="N54">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K54, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
+      </c>
+      <c r="O54" s="15" t="str" cm="1">
+        <f t="array" ref="O54">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K54, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
       <c r="Q54" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="X54" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="Z54" t="s">
+        <v>289</v>
+      </c>
+      <c r="AC54" t="s">
+        <v>292</v>
+      </c>
+      <c r="AE54" t="s">
         <v>290</v>
-      </c>
-      <c r="AC54" t="s">
-        <v>293</v>
-      </c>
-      <c r="AE54" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="55" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B55" s="22" t="str">
         <f t="shared" si="79"/>
@@ -5757,7 +5795,7 @@
         <v xml:space="preserve">10.1007/s00429-012-0462-x 	</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J55" s="23" t="str">
         <f t="shared" si="84"/>
@@ -5768,16 +5806,74 @@
         <v>10.1007%2Fs00429-012-0462-x	_Table1</v>
       </c>
       <c r="M55" s="15" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="N55" s="15" t="str" cm="1">
+        <f t="array" ref="N55">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K55, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="O55" s="15" t="str" cm="1">
+        <f t="array" ref="O55">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K55, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>notfound</v>
       </c>
       <c r="X55" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="Z55" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="AC55" t="s">
-        <v>293</v>
+        <v>292</v>
+      </c>
+    </row>
+    <row r="56" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>300</v>
+      </c>
+      <c r="B56" s="22" t="str">
+        <f t="shared" si="79"/>
+        <v>MacLarnon__1996</v>
+      </c>
+      <c r="C56" s="24" t="str">
+        <f t="shared" si="80"/>
+        <v>MacLarnon</v>
+      </c>
+      <c r="D56" s="9" t="str">
+        <f t="shared" si="81"/>
+        <v/>
+      </c>
+      <c r="E56" s="24" t="str">
+        <f t="shared" si="82"/>
+        <v>1996</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="83"/>
+        <v xml:space="preserve">10.1006/jhev.1996.0005 	</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="J56" s="23" t="str">
+        <f t="shared" ref="J56" si="86">TRIM(_xlfn.TEXTJOIN("_",FALSE,B56,(SUBSTITUTE(SUBSTITUTE(I56," ",""), "_", ""))))</f>
+        <v>MacLarnon__1996_Table1</v>
+      </c>
+      <c r="K56" s="23" t="str">
+        <f t="shared" ref="K56" si="87">IF(ISBLANK(H56),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G56, SUBSTITUTE(I56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H56, SUBSTITUTE(I56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1006%2Fjhev.1996.0005	_Table1</v>
+      </c>
+      <c r="M56" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="N56" s="15" t="str" cm="1">
+        <f t="array" ref="N56">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K56, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="O56" s="15" t="str" cm="1">
+        <f t="array" ref="O56">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K56, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="X56" t="s">
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -5811,97 +5907,97 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" t="s">
         <v>241</v>
-      </c>
-      <c r="B3" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="B4" t="s">
         <v>243</v>
-      </c>
-      <c r="B4" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="B5" t="s">
         <v>245</v>
-      </c>
-      <c r="B5" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="B6" t="s">
         <v>247</v>
-      </c>
-      <c r="B6" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" t="s">
         <v>250</v>
-      </c>
-      <c r="B8" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B9" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="B10" t="s">
         <v>253</v>
-      </c>
-      <c r="B10" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B11" t="s">
         <v>255</v>
-      </c>
-      <c r="B11" t="s">
-        <v>256</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="B12" t="s">
         <v>257</v>
-      </c>
-      <c r="B12" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
   </sheetData>
@@ -5921,12 +6017,12 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -5934,10 +6030,10 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
+        <v>261</v>
+      </c>
+      <c r="C3" t="s">
         <v>262</v>
-      </c>
-      <c r="C3" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -5945,10 +6041,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C4" t="s">
         <v>264</v>
-      </c>
-      <c r="C4" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
@@ -5956,10 +6052,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
+        <v>265</v>
+      </c>
+      <c r="C5" t="s">
         <v>266</v>
-      </c>
-      <c r="C5" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
@@ -5967,10 +6063,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
+        <v>267</v>
+      </c>
+      <c r="C6" t="s">
         <v>268</v>
-      </c>
-      <c r="C6" t="s">
-        <v>269</v>
       </c>
     </row>
   </sheetData>
@@ -5979,6 +6075,17 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -6221,17 +6328,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -6242,6 +6338,23 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26276598-8A19-40B6-BED3-157936C93058}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -6260,23 +6373,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
   <ds:schemaRefs>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -8,19 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="150" documentId="13_ncr:1_{0FC7810F-34CA-C64C-B96F-ABDAC602D8AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0725EF1A-AA76-D147-92BB-751950291942}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{46EFEAD8-FD4A-C04E-827C-11F37E67926D}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="33080" windowHeight="20280" activeTab="1" xr2:uid="{D451F2D8-9E4F-7644-8584-5A4B2BCAED4A}"/>
+    <workbookView xWindow="41160" yWindow="-5960" windowWidth="37740" windowHeight="26820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Pipeline" sheetId="3" r:id="rId2"/>
     <sheet name="Conflcts" sheetId="4" r:id="rId3"/>
+    <sheet name="FileList" sheetId="6" r:id="rId4"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId4"/>
-  </externalReferences>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,30 +38,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="644" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="352">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -170,7 +146,7 @@
     <t>M1 genus</t>
   </si>
   <si>
-    <t/>
+    <t>NA</t>
   </si>
   <si>
     <t>primary (derived from published materials)</t>
@@ -953,61 +929,173 @@
     <t>Item full name</t>
   </si>
   <si>
+    <t>if there are typos or shorthand species names used, can update based on heading, note, text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wimberly, A. N., Slater, G. J., &amp; Granatosky, M. C. (2021). Evolutionary history of quadrupedal walking gaits shows mammalian release from locomotor constraint. Proc Biol Sci, 288(1957), 20210937. https://doi.org/10.1098/rspb.2021.0937 	</t>
+  </si>
+  <si>
+    <t>Files</t>
+  </si>
+  <si>
+    <t>10.1002%2Fcne.24985_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t>10.1002%2Fcne.24985_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t>10.1007%2Fs004220000205_Figure3.tsv</t>
+  </si>
+  <si>
+    <t>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</t>
+  </si>
+  <si>
+    <t>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</t>
+  </si>
+  <si>
+    <t>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</t>
+  </si>
+  <si>
+    <t>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</t>
+  </si>
+  <si>
+    <t>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</t>
+  </si>
+  <si>
+    <t>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</t>
+  </si>
+  <si>
+    <t>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</t>
+  </si>
+  <si>
+    <t>10.1038%2Fs41598-018-26062-8_Table1.tsv</t>
+  </si>
+  <si>
+    <t>10.1038%2Fs41598-018-26062-8_TableS1.tsv</t>
+  </si>
+  <si>
+    <t>10.1038%2Fs41598-018-26062-8_TableS5.tsv</t>
+  </si>
+  <si>
+    <t>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</t>
+  </si>
+  <si>
+    <t>10.1093%2Fjmammal%2Fgyz043.ReadMe.md</t>
+  </si>
+  <si>
+    <t>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</t>
+  </si>
+  <si>
+    <t>10.1126%2Fscience.aaa9101_TableS1.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000124401_TableI.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000319019_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000319019_Table1.tsv</t>
+  </si>
+  <si>
     <t>10.1159%2F000323671_SupplementaryTable1.tsv</t>
   </si>
   <si>
-    <t>notfound</t>
-  </si>
-  <si>
-    <t>10.1159%2F000319019_SupplementaryTable1.tsv</t>
+    <t>10.1159%2F000323671_SupplementaryTable2.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000323671.ReadMe.md</t>
+  </si>
+  <si>
+    <t>10.1159%2F000437413_Table1.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000437413_Table2.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000437413_Table3.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000437413_Table4.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000437413_Table5.tsv</t>
+  </si>
+  <si>
+    <t>10.1159%2F000452856_TableS1.tsv</t>
   </si>
   <si>
     <t>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</t>
   </si>
   <si>
-    <t>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</t>
+    <t>10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</t>
+  </si>
+  <si>
+    <t>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</t>
+  </si>
+  <si>
+    <t>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</t>
+  </si>
+  <si>
+    <t>10.3389%25Ffnana.2013.00035.svg</t>
   </si>
   <si>
     <t>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</t>
   </si>
   <si>
-    <t>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000452856_TableS1.tsv</t>
-  </si>
-  <si>
-    <t>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</t>
-  </si>
-  <si>
-    <t>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</t>
-  </si>
-  <si>
-    <t>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</t>
-  </si>
-  <si>
-    <t>10.1007%2Fs004220000205_Figure3.tsv</t>
-  </si>
-  <si>
-    <t>10.1126%2Fscience.aaa9101_TableS1.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000124401_TableI.tsv</t>
-  </si>
-  <si>
-    <t>10.1038%2Fs41598-018-26062-8_Table1.tsv</t>
+    <t>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</t>
+  </si>
+  <si>
+    <t>10.3389%2Ffnana.2013.00035_Table1-a.tsv</t>
+  </si>
+  <si>
+    <t>10.3389%2Ffnana.2013.00035_Table1-b.tsv</t>
+  </si>
+  <si>
+    <t>10.3389%2Ffnana.2013.00035.ReadMe.md</t>
   </si>
   <si>
     <t>10.3389%2Ffnana.2017.00118_Table1.tsv</t>
   </si>
   <si>
-    <t>10.1002%2Fcne.24985_TABLE1.tsv</t>
-  </si>
-  <si>
-    <t>10.1159%2F000437413_Table1.tsv</t>
-  </si>
-  <si>
-    <t>if there are typos or shorthand species names used, can update based on heading, note, text</t>
+    <t>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</t>
+  </si>
+  <si>
+    <t>10.3389%2Ffnhum.2013.00424.ReadMe.md</t>
+  </si>
+  <si>
+    <t>10.7554%2FeLife.77875_Supplementaryfile3.tsv</t>
+  </si>
+  <si>
+    <t>10.7554%2FeLife.77875_Table1.tsv</t>
+  </si>
+  <si>
+    <t>README.md</t>
+  </si>
+  <si>
+    <t>Table S1. Locomotor profiles for the species used in this
+study.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Granatosky, M. C. (2018). A Review of locomotor diversity in mammals with analyses exploring the influence of substrate use, body mass and intermembral index in primates. Journal of Zoology, 306(4), 207-216. https://doi.org/10.1111/jzo.12608 	</t>
+  </si>
+  <si>
+    <t>mammal_gait.txt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wilman, H., Belmaker, J., Simpson, J., de la Rosa, C., Rivadeneira, M. M., &amp; Jetz, W. (2014). EltonTraits 1.0: Species‐level foraging attributes of the world's birds and mammals. Ecology, 95(7), 2027-2027. https://doi.org/10.1890/13-1917.1 	</t>
+  </si>
+  <si>
+    <t>MamFuncDat.txt</t>
+  </si>
+  <si>
+    <t>References</t>
+  </si>
+  <si>
+    <t>Table 1 The anatomical and behavioural traits used the comparative analysis</t>
+  </si>
+  <si>
+    <t>reference list</t>
   </si>
 </sst>
 </file>
@@ -1023,42 +1111,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1072,11 +1124,19 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
+      <u/>
       <sz val="12"/>
-      <color theme="1"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -1096,6 +1156,35 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1121,41 +1210,29 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1169,237 +1246,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="FileList"/>
-      <sheetName val="__file_list"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="A1" t="str">
-            <v>Files</v>
-          </cell>
-        </row>
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>10.1007%2Fs004220000205_Figure3.tsv</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
-          </cell>
-        </row>
-        <row r="8">
-          <cell r="A8" t="str">
-            <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
-          </cell>
-        </row>
-        <row r="9">
-          <cell r="A9" t="str">
-            <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
-          </cell>
-        </row>
-        <row r="10">
-          <cell r="A10" t="str">
-            <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
-          </cell>
-        </row>
-        <row r="11">
-          <cell r="A11" t="str">
-            <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
-          </cell>
-        </row>
-        <row r="12">
-          <cell r="A12" t="str">
-            <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
-          </cell>
-        </row>
-        <row r="13">
-          <cell r="A13" t="str">
-            <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
-          </cell>
-        </row>
-        <row r="14">
-          <cell r="A14" t="str">
-            <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="A15" t="str">
-            <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="A16" t="str">
-            <v>10.1093%2Fjmammal%2Fgyz043.ReadMe.md</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="A17" t="str">
-            <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="A18" t="str">
-            <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="A19" t="str">
-            <v>10.1159%2F000124401_TableI.tsv</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="A20" t="str">
-            <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="A21" t="str">
-            <v>10.1159%2F000319019_Table1.tsv</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="A22" t="str">
-            <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="A23" t="str">
-            <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="A24" t="str">
-            <v>10.1159%2F000323671.ReadMe.md</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="A25" t="str">
-            <v>10.1159%2F000437413_Table1.tsv</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="A26" t="str">
-            <v>10.1159%2F000437413_Table2.tsv</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="A27" t="str">
-            <v>10.1159%2F000437413_Table3.tsv</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="A28" t="str">
-            <v>10.1159%2F000437413_Table4.tsv</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="A29" t="str">
-            <v>10.1159%2F000437413_Table5.tsv</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="A30" t="str">
-            <v>10.1159%2F000452856_TableS1.tsv</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="A31" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="A32" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="A33" t="str">
-            <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="A34" t="str">
-            <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="A35" t="str">
-            <v>10.3389%25Ffnana.2013.00035.svg</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="A36" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="A37" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="A38" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="A39" t="str">
-            <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="A40" t="str">
-            <v>10.3389%2Ffnana.2013.00035.ReadMe.md</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="A41" t="str">
-            <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="A42" t="str">
-            <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="A43" t="str">
-            <v>10.3389%2Ffnhum.2013.00424.ReadMe.md</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1698,175 +1544,170 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8148A1DF-1B63-6441-BF14-74AB84A91AD4}">
-  <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AK55"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:AJ59"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="27" customWidth="1"/>
-    <col min="2" max="2" width="23.6640625" style="9" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" style="9" customWidth="1"/>
-    <col min="4" max="4" width="15" style="9" customWidth="1"/>
-    <col min="5" max="6" width="2.1640625" style="9" customWidth="1"/>
-    <col min="7" max="7" width="2.1640625" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="15" customWidth="1"/>
+    <col min="5" max="7" width="2.1640625" customWidth="1"/>
     <col min="8" max="8" width="9.6640625" customWidth="1"/>
     <col min="9" max="9" width="17.1640625" customWidth="1"/>
     <col min="10" max="10" width="31.1640625" customWidth="1"/>
     <col min="11" max="11" width="46.5" customWidth="1"/>
-    <col min="12" max="13" width="14.1640625" customWidth="1"/>
-    <col min="14" max="14" width="41.1640625" customWidth="1"/>
-    <col min="15" max="15" width="49.1640625" customWidth="1"/>
-    <col min="16" max="19" width="14.1640625" customWidth="1"/>
-    <col min="20" max="20" width="13.83203125" customWidth="1"/>
-    <col min="21" max="21" width="12.6640625" customWidth="1"/>
-    <col min="22" max="22" width="22.1640625" customWidth="1"/>
-    <col min="23" max="23" width="14.33203125" customWidth="1"/>
-    <col min="24" max="24" width="15.33203125" customWidth="1"/>
-    <col min="25" max="25" width="39.5" customWidth="1"/>
-    <col min="26" max="26" width="11.1640625" customWidth="1"/>
-    <col min="27" max="27" width="5" customWidth="1"/>
-    <col min="28" max="28" width="7.5" customWidth="1"/>
-    <col min="29" max="29" width="10.6640625" customWidth="1"/>
-    <col min="30" max="30" width="6.5" customWidth="1"/>
-    <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="34" width="10.83203125" customWidth="1"/>
-    <col min="35" max="35" width="12.5" customWidth="1"/>
-    <col min="36" max="36" width="2.83203125" hidden="1" customWidth="1"/>
+    <col min="12" max="12" width="24" customWidth="1"/>
+    <col min="13" max="13" width="5" customWidth="1"/>
+    <col min="14" max="14" width="49.83203125" customWidth="1"/>
+    <col min="15" max="18" width="14.1640625" customWidth="1"/>
+    <col min="19" max="19" width="13.83203125" customWidth="1"/>
+    <col min="20" max="20" width="12.6640625" customWidth="1"/>
+    <col min="21" max="21" width="22.1640625" customWidth="1"/>
+    <col min="22" max="22" width="14.33203125" customWidth="1"/>
+    <col min="23" max="23" width="15.33203125" customWidth="1"/>
+    <col min="24" max="24" width="39.5" customWidth="1"/>
+    <col min="25" max="25" width="11.1640625" customWidth="1"/>
+    <col min="26" max="26" width="5" customWidth="1"/>
+    <col min="27" max="27" width="7.5" customWidth="1"/>
+    <col min="28" max="28" width="10.6640625" customWidth="1"/>
+    <col min="29" max="29" width="6.5" customWidth="1"/>
+    <col min="30" max="30" width="11" customWidth="1"/>
+    <col min="31" max="33" width="10.83203125" customWidth="1"/>
+    <col min="34" max="34" width="12.5" customWidth="1"/>
+    <col min="35" max="35" width="2.83203125" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" s="6" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="M1" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="P1" s="6" t="s">
+      <c r="O1" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="P1" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="Q1" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="R1" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="S1" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="T1" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="U1" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="V1" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="W1" s="11" t="s">
         <v>295</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="X1" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Y1" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="Z1" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AA1" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AB1" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AC1" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AD1" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AE1" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AF1" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AG1" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="AI1" s="6" t="s">
+      <c r="AH1" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="AJ1" s="6" t="s">
+      <c r="AI1" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="AK1" s="6" t="s">
+      <c r="AJ1" s="11" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>38</v>
       </c>
-      <c r="B2" s="7" t="str">
+      <c r="B2" s="2" t="str">
         <f t="shared" ref="B2" si="0">C2 &amp; IF(D2&lt;&gt;"", "_" &amp; D2, "_") &amp; IF(E2&lt;&gt;"", "_" &amp; E2, "_") &amp; IF(F2&lt;&gt;"", "_" &amp; F2, "")</f>
         <v>Burger_etal_2019</v>
       </c>
-      <c r="C2" s="9" t="str">
+      <c r="C2" s="2" t="str">
         <f>SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A2,","), "-", ""), " ", "")</f>
         <v>Burger</v>
       </c>
-      <c r="D2" s="9" t="str">
+      <c r="D2" s="2" t="str">
         <f t="shared" ref="D2:D48" si="1">IF(ISNUMBER(FIND("&amp;", A2)),
     IF(LEN(A2)-LEN(SUBSTITUTE(A2, ",", ""))&gt;=6, "etal", MID(A2, SEARCH("&amp; ", A2)+2, SEARCH(",", A2, SEARCH("&amp; ", A2)+2) - SEARCH("&amp; ", A2)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E2" s="9" t="str">
+      <c r="E2" s="2" t="str">
         <f t="shared" ref="E2" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
         <v>2019</v>
       </c>
@@ -1874,90 +1715,87 @@
         <f t="shared" ref="G2:G37" si="3">_xlfn.TEXTAFTER(A2,"https://doi.org/")</f>
         <v>10.1093/jmammal/gyz043</v>
       </c>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
+      <c r="H2" s="1"/>
+      <c r="I2" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="J2" s="3" t="str">
+      <c r="J2" s="1" t="str">
         <f t="shared" ref="J2:J44" si="4">TRIM(_xlfn.TEXTJOIN("_",FALSE,B2,(SUBSTITUTE(SUBSTITUTE(I2," ",""), "_", ""))))</f>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
-      <c r="K2" s="21" t="str">
+      <c r="K2" s="8" t="str">
         <f>IF(ISBLANK(H2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G2, SUBSTITUTE(I2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H2, SUBSTITUTE(I2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="1" t="s">
         <v>40</v>
       </c>
       <c r="M2" t="s">
         <v>41</v>
       </c>
-      <c r="N2" t="str" cm="1">
-        <f t="array" ref="N2">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K2, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N2" t="str">
+        <f t="array" ref="N2">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K2, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
-      <c r="O2" t="s">
-        <v>306</v>
-      </c>
-      <c r="P2" s="3" t="s">
+      <c r="O2" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="9" t="s">
+      <c r="P2" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="R2" t="s">
+      <c r="Q2" t="s">
         <v>44</v>
       </c>
-      <c r="S2" t="str">
-        <f>IF(R2="N", Q2, "write file name")</f>
+      <c r="R2" t="str">
+        <f>IF(Q2="N", P2, "write file name")</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
+      <c r="S2" t="s">
+        <v>45</v>
+      </c>
       <c r="T2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="U2" t="s">
-        <v>46</v>
-      </c>
-      <c r="V2" t="s">
         <v>47</v>
       </c>
-      <c r="X2" s="7"/>
+      <c r="W2" s="2"/>
+      <c r="X2" t="s">
+        <v>48</v>
+      </c>
       <c r="Y2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Z2" t="s">
         <v>49</v>
       </c>
+      <c r="AC2" t="s">
+        <v>50</v>
+      </c>
       <c r="AD2" t="s">
-        <v>50</v>
-      </c>
-      <c r="AE2" t="s">
         <v>37</v>
       </c>
-      <c r="AI2">
+      <c r="AH2">
         <v>17</v>
       </c>
-      <c r="AK2">
+      <c r="AJ2">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>51</v>
       </c>
-      <c r="B3" s="7" t="str">
+      <c r="B3" s="2" t="str">
         <f t="shared" ref="B3:B44" si="5">C3 &amp; IF(D3&lt;&gt;"", "_" &amp; D3, "_") &amp; IF(E3&lt;&gt;"", "_" &amp; E3, "_") &amp; IF(F3&lt;&gt;"", "_" &amp; F3, "")</f>
         <v>Caspar_etal_2022</v>
       </c>
-      <c r="C3" s="9" t="str">
+      <c r="C3" s="2" t="str">
         <f t="shared" ref="C3:C44" si="6">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
         <v>Caspar</v>
       </c>
-      <c r="D3" s="9" t="str">
+      <c r="D3" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E3" s="9" t="str">
+      <c r="E3" s="2" t="str">
         <f t="shared" ref="E3:E44" si="7">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
         <v>2022</v>
       </c>
@@ -1965,92 +1803,89 @@
         <f t="shared" si="3"/>
         <v>10.7554/eLife.77875</v>
       </c>
-      <c r="H3" s="10"/>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="1"/>
+      <c r="I3" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J3" s="3" t="str">
+      <c r="J3" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Caspar_etal_2022_Table1</v>
       </c>
-      <c r="K3" s="3" t="str">
+      <c r="K3" s="1" t="str">
         <f t="shared" ref="K3:K44" si="8">IF(ISBLANK(H3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G3, SUBSTITUTE(I3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H3, SUBSTITUTE(I3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.7554%2FeLife.77875_Table1</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="1"/>
       <c r="M3" t="s">
         <v>41</v>
       </c>
-      <c r="N3" t="str" cm="1">
-        <f t="array" ref="N3">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K3, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N3" t="str">
+        <f t="array" ref="N3">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K3, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O3" t="s">
-        <v>297</v>
-      </c>
-      <c r="P3" t="s">
         <v>53</v>
       </c>
-      <c r="Q3" s="9" t="s">
+      <c r="P3" s="2" t="s">
         <v>54</v>
       </c>
+      <c r="Q3" t="s">
+        <v>55</v>
+      </c>
       <c r="R3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="T3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U3" t="s">
-        <v>46</v>
-      </c>
-      <c r="V3" t="s">
         <v>58</v>
       </c>
-      <c r="W3" s="8" t="s">
+      <c r="V3" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="X3" s="9" t="s">
+      <c r="W3" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="X3" t="s">
+        <v>61</v>
+      </c>
       <c r="Y3" t="s">
-        <v>61</v>
-      </c>
-      <c r="Z3" t="s">
         <v>62</v>
       </c>
+      <c r="AC3" t="s">
+        <v>63</v>
+      </c>
       <c r="AD3" t="s">
-        <v>63</v>
-      </c>
-      <c r="AE3" t="s">
         <v>64</v>
       </c>
-      <c r="AI3">
+      <c r="AH3">
         <v>7</v>
       </c>
-      <c r="AK3">
+      <c r="AJ3">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="7" t="str">
+      <c r="B4" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Caspar_etal_2022</v>
       </c>
-      <c r="C4" s="9" t="str">
+      <c r="C4" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Caspar</v>
       </c>
-      <c r="D4" s="9" t="str">
+      <c r="D4" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E4" s="9" t="str">
+      <c r="E4" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2022</v>
       </c>
@@ -2058,90 +1893,87 @@
         <f t="shared" si="3"/>
         <v>10.7554/eLife.77875</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12" t="s">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="J4" s="3" t="str">
+      <c r="J4" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
-      <c r="K4" s="3" t="str">
+      <c r="K4" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
-      <c r="L4" s="12"/>
+      <c r="L4" s="1"/>
       <c r="M4" t="s">
         <v>41</v>
       </c>
-      <c r="N4" t="str" cm="1">
-        <f t="array" ref="N4">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K4, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N4" t="str">
+        <f t="array" ref="N4">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K4, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O4" t="s">
-        <v>297</v>
-      </c>
-      <c r="P4" t="s">
         <v>53</v>
       </c>
-      <c r="Q4" s="9" t="s">
+      <c r="P4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="R4" t="s">
+      <c r="Q4" t="s">
         <v>44</v>
       </c>
-      <c r="S4" t="str">
-        <f>IF(R4="N", Q4, "write file name")</f>
+      <c r="R4" t="str">
+        <f>IF(Q4="N", P4, "write file name")</f>
         <v>elife-77875-supp3-v1.xlsx</v>
       </c>
+      <c r="S4" t="s">
+        <v>67</v>
+      </c>
       <c r="T4" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="U4" t="s">
-        <v>46</v>
-      </c>
-      <c r="V4" t="s">
         <v>68</v>
       </c>
-      <c r="W4" s="13" t="s">
+      <c r="V4" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="X4" s="9" t="s">
+      <c r="W4" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="X4" t="s">
+        <v>71</v>
+      </c>
       <c r="Y4" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z4" t="s">
         <v>49</v>
       </c>
-      <c r="AE4" t="s">
+      <c r="AD4" t="s">
         <v>64</v>
       </c>
-      <c r="AI4">
+      <c r="AH4">
         <v>5</v>
       </c>
-      <c r="AK4">
+      <c r="AJ4">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>72</v>
       </c>
-      <c r="B5" s="7" t="str">
+      <c r="B5" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Changizi__2001</v>
       </c>
-      <c r="C5" s="9" t="str">
+      <c r="C5" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Changizi</v>
       </c>
-      <c r="D5" s="9" t="str">
+      <c r="D5" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E5" s="9" t="str">
+      <c r="E5" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2001</v>
       </c>
@@ -2149,178 +1981,172 @@
         <f t="shared" si="3"/>
         <v>10.1007/s004220000205</v>
       </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12" t="s">
+      <c r="H5" s="1"/>
+      <c r="I5" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="J5" s="3" t="str">
+      <c r="J5" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Changizi__2001_Figure3</v>
       </c>
-      <c r="K5" s="3" t="str">
+      <c r="K5" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
-      <c r="L5" s="12"/>
+      <c r="L5" s="1"/>
       <c r="M5" t="s">
         <v>74</v>
       </c>
-      <c r="N5" t="str" cm="1">
-        <f t="array" ref="N5">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K5, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N5" t="str">
+        <f t="array" ref="N5">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K5, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
       <c r="O5" t="s">
-        <v>307</v>
-      </c>
-      <c r="P5" t="s">
         <v>35</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="P5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="R5" t="s">
+      <c r="Q5" t="s">
         <v>55</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="R5" s="2" t="s">
         <v>76</v>
       </c>
+      <c r="S5" t="s">
+        <v>57</v>
+      </c>
       <c r="T5" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="U5" t="s">
-        <v>77</v>
-      </c>
-      <c r="V5" t="s">
         <v>78</v>
       </c>
-      <c r="W5" s="13"/>
-      <c r="X5" s="9"/>
+      <c r="V5" s="3"/>
+      <c r="W5" s="2"/>
+      <c r="X5" t="s">
+        <v>79</v>
+      </c>
       <c r="Y5" t="s">
-        <v>79</v>
-      </c>
-      <c r="Z5" t="s">
         <v>36</v>
       </c>
-      <c r="AD5" t="s">
+      <c r="AC5" t="s">
         <v>80</v>
       </c>
-      <c r="AI5" t="s">
+      <c r="AH5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>82</v>
       </c>
-      <c r="B6" s="7" t="str">
+      <c r="B6" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Chen_Wiens_2020</v>
       </c>
-      <c r="C6" s="9" t="str">
+      <c r="C6" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Chen</v>
       </c>
-      <c r="D6" s="9" t="str">
+      <c r="D6" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Wiens</v>
       </c>
-      <c r="E6" s="9" t="str">
+      <c r="E6" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2020</v>
       </c>
-      <c r="F6" s="7"/>
+      <c r="F6" s="2"/>
       <c r="G6" t="str">
         <f t="shared" si="3"/>
         <v>10.1038/s41467-020-14356-3</v>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3" t="s">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="J6" s="3" t="str">
+      <c r="J6" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
-      <c r="K6" s="3" t="str">
+      <c r="K6" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
-      <c r="L6" s="3"/>
+      <c r="L6" s="1"/>
       <c r="M6" t="s">
         <v>41</v>
       </c>
-      <c r="N6" t="str" cm="1">
-        <f t="array" ref="N6">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K6, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N6" t="str">
+        <f t="array" ref="N6">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K6, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
       </c>
       <c r="O6" t="s">
-        <v>302</v>
-      </c>
-      <c r="P6" t="s">
         <v>53</v>
       </c>
-      <c r="Q6" s="9" t="s">
+      <c r="P6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="R6" t="s">
+      <c r="Q6" t="s">
         <v>44</v>
       </c>
-      <c r="S6" t="str">
-        <f>IF(R6="N", Q6, "write file name")</f>
+      <c r="R6" t="str">
+        <f>IF(Q6="N", P6, "write file name")</f>
         <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
       </c>
+      <c r="S6" t="s">
+        <v>67</v>
+      </c>
       <c r="T6" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="U6" t="s">
-        <v>46</v>
-      </c>
-      <c r="V6" t="s">
         <v>68</v>
       </c>
-      <c r="W6" s="8" t="s">
+      <c r="V6" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="X6" s="7"/>
+      <c r="W6" s="2"/>
+      <c r="X6" t="s">
+        <v>86</v>
+      </c>
       <c r="Y6" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z6" t="s">
         <v>49</v>
       </c>
+      <c r="AB6" t="s">
+        <v>87</v>
+      </c>
       <c r="AC6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD6" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE6" t="s">
         <v>89</v>
       </c>
-      <c r="AI6">
+      <c r="AH6">
         <v>10</v>
       </c>
-      <c r="AK6">
+      <c r="AJ6">
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>90</v>
       </c>
-      <c r="B7" s="7" t="str">
+      <c r="B7" s="2" t="str">
         <f t="shared" si="5"/>
         <v>DosSantos_etal_2017</v>
       </c>
-      <c r="C7" s="9" t="str">
+      <c r="C7" s="2" t="str">
         <f t="shared" si="6"/>
         <v>DosSantos</v>
       </c>
-      <c r="D7" s="9" t="str">
+      <c r="D7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E7" s="9" t="str">
+      <c r="E7" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2017</v>
       </c>
@@ -2328,98 +2154,95 @@
         <f t="shared" si="3"/>
         <v>10.1159/000452856</v>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J7" s="3" t="str">
+      <c r="J7" s="1" t="str">
         <f t="shared" si="4"/>
         <v>DosSantos_etal_2017_TableS1</v>
       </c>
-      <c r="K7" s="3" t="str">
+      <c r="K7" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000452856_TableS1</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="L7" s="1" t="s">
         <v>92</v>
       </c>
       <c r="M7" t="s">
         <v>41</v>
       </c>
-      <c r="N7" t="str" cm="1">
-        <f t="array" ref="N7">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K7, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N7" t="str">
+        <f t="array" ref="N7">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K7, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000452856_TableS1.tsv</v>
       </c>
       <c r="O7" t="s">
-        <v>303</v>
-      </c>
-      <c r="P7" t="s">
         <v>53</v>
       </c>
-      <c r="Q7" s="9" t="s">
+      <c r="P7" s="2" t="s">
         <v>93</v>
       </c>
+      <c r="Q7" t="s">
+        <v>55</v>
+      </c>
       <c r="R7" t="s">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="S7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="T7" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="U7" t="s">
-        <v>96</v>
-      </c>
-      <c r="V7" t="s">
         <v>68</v>
       </c>
-      <c r="W7" s="8" t="s">
+      <c r="V7" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="X7" s="9"/>
+      <c r="W7" s="2"/>
+      <c r="X7" t="s">
+        <v>98</v>
+      </c>
       <c r="Y7" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AA7" t="s">
         <v>100</v>
       </c>
-      <c r="AB7" t="s">
-        <v>100</v>
+      <c r="AD7" t="s">
+        <v>101</v>
       </c>
       <c r="AE7" t="s">
-        <v>101</v>
-      </c>
-      <c r="AF7" t="s">
         <v>102</v>
       </c>
-      <c r="AI7">
+      <c r="AH7">
         <v>0</v>
       </c>
-      <c r="AK7">
+      <c r="AJ7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>103</v>
       </c>
-      <c r="B8" s="7" t="str">
+      <c r="B8" s="2" t="str">
         <f t="shared" si="5"/>
         <v>DosSantos_etal_2020</v>
       </c>
-      <c r="C8" s="9" t="str">
+      <c r="C8" s="2" t="str">
         <f t="shared" si="6"/>
         <v>DosSantos</v>
       </c>
-      <c r="D8" s="9" t="str">
+      <c r="D8" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E8" s="9" t="str">
+      <c r="E8" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2020</v>
       </c>
@@ -2427,414 +2250,399 @@
         <f t="shared" si="3"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
+      <c r="H8" s="1"/>
+      <c r="I8" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J8" s="3" t="str">
+      <c r="J8" s="1" t="str">
         <f t="shared" si="4"/>
         <v>DosSantos_etal_2020_Table1</v>
       </c>
-      <c r="K8" s="3" t="str">
+      <c r="K8" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
-      <c r="L8" s="3"/>
+      <c r="L8" s="1"/>
       <c r="M8" t="s">
         <v>41</v>
       </c>
-      <c r="N8" t="str" cm="1">
-        <f t="array" ref="N8">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K8, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N8" t="str">
+        <f t="array" ref="N8">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K8, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
       <c r="O8" t="s">
-        <v>304</v>
-      </c>
-      <c r="P8" t="s">
         <v>53</v>
       </c>
-      <c r="Q8" s="14" t="s">
+      <c r="P8" s="4" t="s">
         <v>104</v>
       </c>
+      <c r="Q8" t="s">
+        <v>55</v>
+      </c>
       <c r="R8" t="s">
-        <v>55</v>
+        <v>105</v>
       </c>
       <c r="S8" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="T8" t="s">
-        <v>106</v>
-      </c>
-      <c r="U8" t="s">
         <v>46</v>
       </c>
-      <c r="X8" s="7"/>
+      <c r="W8" s="2"/>
+      <c r="X8" t="s">
+        <v>98</v>
+      </c>
       <c r="Y8" t="s">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="Z8" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="AA8" t="s">
         <v>100</v>
       </c>
-      <c r="AB8" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE8" t="s">
+      <c r="AD8" t="s">
         <v>108</v>
       </c>
-      <c r="AI8">
+      <c r="AH8">
         <v>4</v>
       </c>
-      <c r="AK8">
+      <c r="AJ8">
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>109</v>
       </c>
-      <c r="B9" s="7" t="str">
+      <c r="B9" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Finlay_etal_2006</v>
       </c>
-      <c r="C9" s="9" t="str">
+      <c r="C9" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Finlay</v>
       </c>
-      <c r="D9" s="9" t="str">
+      <c r="D9" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E9" s="9" t="str">
+      <c r="E9" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2006</v>
       </c>
-      <c r="F9" s="7"/>
+      <c r="F9" s="2"/>
       <c r="G9" t="str">
         <f t="shared" si="3"/>
         <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3" t="s">
+      <c r="H9" s="1"/>
+      <c r="I9" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="J9" s="3" t="str">
+      <c r="J9" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Finlay_etal_2006_Table6.1</v>
       </c>
-      <c r="K9" s="3" t="str">
+      <c r="K9" s="1" t="str">
         <f>IF(ISBLANK(H9),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G9, SUBSTITUTE(I9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H9, SUBSTITUTE(I9,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="1"/>
       <c r="M9" t="s">
         <v>74</v>
       </c>
-      <c r="N9" t="str" cm="1">
-        <f t="array" ref="N9">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K9, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N9" t="str">
+        <f t="array" ref="N9">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K9, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
       </c>
       <c r="O9" t="s">
-        <v>305</v>
-      </c>
-      <c r="P9" t="s">
         <v>35</v>
       </c>
-      <c r="Q9" s="9" t="s">
+      <c r="P9" s="2" t="s">
         <v>111</v>
       </c>
+      <c r="Q9" t="s">
+        <v>55</v>
+      </c>
       <c r="R9" t="s">
-        <v>55</v>
+        <v>112</v>
       </c>
       <c r="S9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T9" t="s">
-        <v>113</v>
+        <v>46</v>
       </c>
       <c r="U9" t="s">
-        <v>46</v>
-      </c>
-      <c r="V9" t="s">
         <v>58</v>
       </c>
-      <c r="W9" s="8" t="s">
+      <c r="V9" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="X9" s="7"/>
+      <c r="W9" s="2"/>
+      <c r="X9" t="s">
+        <v>115</v>
+      </c>
       <c r="Y9" t="s">
-        <v>115</v>
-      </c>
-      <c r="Z9" t="s">
         <v>36</v>
       </c>
+      <c r="AC9" t="s">
+        <v>116</v>
+      </c>
       <c r="AD9" t="s">
-        <v>116</v>
-      </c>
-      <c r="AE9" t="s">
         <v>37</v>
       </c>
-      <c r="AI9">
+      <c r="AH9">
         <v>3</v>
       </c>
-      <c r="AK9">
+      <c r="AJ9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>117</v>
       </c>
-      <c r="B10" s="7" t="str">
+      <c r="B10" s="2" t="str">
         <f>C10 &amp; IF(D10&lt;&gt;"", "_" &amp; D10, "_") &amp; IF(E10&lt;&gt;"", "_" &amp; E10, "_") &amp; IF(F10&lt;&gt;"", "_" &amp; F10, "")</f>
         <v>Heffner_Masterton_1975</v>
       </c>
-      <c r="C10" s="9" t="str">
+      <c r="C10" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Heffner</v>
       </c>
-      <c r="D10" s="9" t="str">
+      <c r="D10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Masterton</v>
       </c>
-      <c r="E10" s="9" t="str">
+      <c r="E10" s="2" t="str">
         <f t="shared" si="7"/>
         <v>1975</v>
       </c>
-      <c r="F10" s="7"/>
+      <c r="F10" s="2"/>
       <c r="G10" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000124401</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J10" s="3" t="str">
+      <c r="J10" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Heffner_Masterton_1975_TableI</v>
       </c>
-      <c r="K10" s="3" t="str">
+      <c r="K10" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000124401_TableI</v>
       </c>
-      <c r="L10" s="3"/>
+      <c r="L10" s="1"/>
       <c r="M10" t="s">
         <v>41</v>
       </c>
-      <c r="N10" t="str" cm="1">
-        <f t="array" ref="N10">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K10, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N10" t="str">
+        <f t="array" ref="N10">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K10, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000124401_TableI.tsv</v>
       </c>
       <c r="O10" t="s">
-        <v>309</v>
-      </c>
-      <c r="P10" t="s">
         <v>53</v>
       </c>
-      <c r="Q10" s="9" t="s">
+      <c r="P10" s="2" t="s">
         <v>119</v>
       </c>
+      <c r="Q10" t="s">
+        <v>55</v>
+      </c>
       <c r="R10" t="s">
-        <v>55</v>
+        <v>120</v>
       </c>
       <c r="S10" t="s">
-        <v>120</v>
+        <v>57</v>
       </c>
       <c r="T10" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U10" t="s">
-        <v>46</v>
-      </c>
-      <c r="V10" t="s">
         <v>78</v>
       </c>
-      <c r="X10" s="7"/>
+      <c r="W10" s="2"/>
+      <c r="X10" t="s">
+        <v>121</v>
+      </c>
       <c r="Y10" t="s">
-        <v>121</v>
-      </c>
-      <c r="Z10" t="s">
         <v>122</v>
       </c>
-      <c r="AC10" t="s">
+      <c r="AB10" t="s">
         <v>123</v>
       </c>
-      <c r="AE10" t="s">
+      <c r="AD10" t="s">
         <v>37</v>
       </c>
-      <c r="AI10">
+      <c r="AH10">
         <v>7</v>
       </c>
-      <c r="AK10">
+      <c r="AJ10">
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>124</v>
       </c>
-      <c r="B11" s="7" t="str">
+      <c r="B11" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Heffner_Masterton_1983</v>
       </c>
-      <c r="C11" s="9" t="str">
+      <c r="C11" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Heffner</v>
       </c>
-      <c r="D11" s="9" t="str">
+      <c r="D11" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Masterton</v>
       </c>
-      <c r="E11" s="9" t="str">
+      <c r="E11" s="2" t="str">
         <f t="shared" si="7"/>
         <v>1983</v>
       </c>
-      <c r="F11" s="7"/>
+      <c r="F11" s="2"/>
       <c r="G11" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000121494</v>
       </c>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
+      <c r="H11" s="1"/>
+      <c r="I11" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="J11" s="3" t="str">
+      <c r="J11" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Heffner_Masterton_1983_TableI</v>
       </c>
-      <c r="K11" s="3" t="str">
+      <c r="K11" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000121494_TableI</v>
       </c>
-      <c r="L11" s="3"/>
-      <c r="M11" s="15" t="s">
+      <c r="L11" s="1"/>
+      <c r="M11" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N11" t="str" cm="1">
-        <f t="array" ref="N11">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K11, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N11" t="str">
+        <f t="array" ref="N11">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K11, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O11" t="s">
-        <v>297</v>
-      </c>
-      <c r="P11" t="s">
         <v>35</v>
       </c>
-      <c r="Q11" s="14"/>
-      <c r="S11" t="str">
-        <f>IF(R11="N", Q11, "write file name")</f>
+      <c r="P11" s="4"/>
+      <c r="R11" t="str">
+        <f>IF(Q11="N", P11, "write file name")</f>
         <v>write file name</v>
       </c>
+      <c r="S11" t="s">
+        <v>57</v>
+      </c>
       <c r="T11" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U11" t="s">
-        <v>46</v>
-      </c>
-      <c r="V11" t="s">
         <v>78</v>
       </c>
-      <c r="X11" s="7"/>
-      <c r="Y11" t="s">
+      <c r="W11" s="2"/>
+      <c r="X11" t="s">
         <v>121</v>
       </c>
-      <c r="AE11" t="s">
+      <c r="AD11" t="s">
         <v>37</v>
       </c>
-      <c r="AG11" t="s">
+      <c r="AF11" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="12" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>127</v>
       </c>
-      <c r="B12" s="7" t="str">
+      <c r="B12" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Heldstab_etal_2016</v>
       </c>
-      <c r="C12" s="9" t="str">
+      <c r="C12" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Heldstab</v>
       </c>
-      <c r="D12" s="9" t="str">
+      <c r="D12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E12" s="9" t="str">
+      <c r="E12" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2016</v>
       </c>
-      <c r="F12" s="7"/>
+      <c r="F12" s="2"/>
       <c r="G12" t="str">
         <f t="shared" si="3"/>
         <v>10.1038/srep24528</v>
       </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3" t="s">
+      <c r="H12" s="1"/>
+      <c r="I12" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J12" s="3" t="str">
+      <c r="J12" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Heldstab_etal_2016_TableS1</v>
       </c>
-      <c r="K12" s="3" t="str">
+      <c r="K12" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
-      <c r="L12" s="3"/>
-      <c r="M12" s="15" t="s">
+      <c r="L12" s="1"/>
+      <c r="M12" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N12" t="str" cm="1">
-        <f t="array" ref="N12">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K12, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N12" t="str">
+        <f t="array" ref="N12">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K12, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O12" t="s">
-        <v>297</v>
-      </c>
-      <c r="P12" t="s">
         <v>35</v>
       </c>
-      <c r="Q12" s="14"/>
-      <c r="S12" t="str">
-        <f>IF(R12="N", Q12, "write file name")</f>
+      <c r="P12" s="4"/>
+      <c r="R12" t="str">
+        <f>IF(Q12="N", P12, "write file name")</f>
         <v>write file name</v>
       </c>
+      <c r="S12" t="s">
+        <v>57</v>
+      </c>
       <c r="T12" t="s">
-        <v>57</v>
-      </c>
-      <c r="U12" t="s">
         <v>46</v>
       </c>
-      <c r="X12" s="7"/>
-      <c r="Y12" t="s">
+      <c r="W12" s="2"/>
+      <c r="X12" t="s">
         <v>128</v>
       </c>
-      <c r="AE12" t="s">
+      <c r="AD12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>129</v>
       </c>
-      <c r="B13" s="7" t="str">
+      <c r="B13" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="C13" s="9" t="str">
+      <c r="C13" s="2" t="str">
         <f t="shared" si="6"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D13" s="9" t="str">
+      <c r="D13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E13" s="9" t="str">
+      <c r="E13" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2015</v>
       </c>
@@ -2842,537 +2650,522 @@
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3" t="s">
+      <c r="H13" s="1"/>
+      <c r="I13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="3" t="str">
+      <c r="J13" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
-      <c r="K13" s="3" t="str">
+      <c r="K13" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000437413_Table1</v>
       </c>
-      <c r="L13" s="3"/>
+      <c r="L13" s="1"/>
       <c r="M13" t="s">
         <v>41</v>
       </c>
-      <c r="N13" t="str" cm="1">
-        <f t="array" ref="N13">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K13, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N13" t="str">
+        <f t="array" ref="N13">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K13, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="O13" t="s">
-        <v>313</v>
-      </c>
-      <c r="P13" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="14" t="s">
+      <c r="P13" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="R13" s="3" t="s">
+      <c r="Q13" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R13" t="s">
+        <v>131</v>
+      </c>
       <c r="S13" t="s">
-        <v>131</v>
+        <v>57</v>
       </c>
       <c r="T13" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U13" t="s">
-        <v>46</v>
-      </c>
-      <c r="V13" t="s">
         <v>58</v>
       </c>
-      <c r="W13" s="8" t="s">
+      <c r="V13" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="X13" s="7" t="s">
+      <c r="W13" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="X13" t="s">
         <v>98</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>100</v>
       </c>
       <c r="AA13" t="s">
         <v>100</v>
       </c>
-      <c r="AB13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE13" t="s">
+      <c r="AD13" t="s">
         <v>134</v>
       </c>
-      <c r="AI13">
+      <c r="AH13">
         <v>9</v>
       </c>
-      <c r="AK13">
+      <c r="AJ13">
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>129</v>
       </c>
-      <c r="B14" s="7" t="str">
+      <c r="B14" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="C14" s="9" t="str">
+      <c r="C14" s="2" t="str">
         <f t="shared" si="6"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D14" s="9" t="str">
+      <c r="D14" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A14)),
     IF(LEN(A14)-LEN(SUBSTITUTE(A14, ",", ""))&gt;=6, "etal", MID(A14, SEARCH("&amp; ", A14)+2, SEARCH(",", A14, SEARCH("&amp; ", A14)+2) - SEARCH("&amp; ", A14)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E14" s="9" t="str">
+      <c r="E14" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2015</v>
       </c>
-      <c r="F14" s="7"/>
+      <c r="F14" s="2"/>
       <c r="G14" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3" t="s">
+      <c r="H14" s="1"/>
+      <c r="I14" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J14" s="3" t="str">
+      <c r="J14" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
-      <c r="K14" s="3" t="str">
+      <c r="K14" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000437413_Table2</v>
       </c>
-      <c r="L14" s="3"/>
+      <c r="L14" s="1"/>
       <c r="M14" t="s">
         <v>41</v>
       </c>
-      <c r="N14" t="str" cm="1">
-        <f t="array" ref="N14">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K14, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N14" t="str">
+        <f t="array" ref="N14">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K14, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
       <c r="O14" t="s">
-        <v>313</v>
-      </c>
-      <c r="P14" t="s">
         <v>53</v>
       </c>
-      <c r="Q14" s="14" t="s">
+      <c r="P14" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="Q14" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R14" t="s">
+        <v>137</v>
+      </c>
       <c r="S14" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="T14" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U14" t="s">
-        <v>46</v>
-      </c>
-      <c r="V14" t="s">
         <v>58</v>
       </c>
-      <c r="W14" s="8" t="s">
+      <c r="V14" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="X14" s="7" t="s">
+      <c r="W14" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="Y14" t="s">
+      <c r="X14" t="s">
         <v>98</v>
+      </c>
+      <c r="Z14" t="s">
+        <v>100</v>
       </c>
       <c r="AA14" t="s">
         <v>100</v>
       </c>
-      <c r="AB14" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE14" t="s">
+      <c r="AD14" t="s">
         <v>134</v>
       </c>
-      <c r="AI14">
+      <c r="AH14">
         <v>9</v>
       </c>
-      <c r="AK14">
+      <c r="AJ14">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>129</v>
       </c>
-      <c r="B15" s="7" t="str">
+      <c r="B15" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="C15" s="9" t="str">
+      <c r="C15" s="2" t="str">
         <f t="shared" si="6"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D15" s="9" t="str">
+      <c r="D15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E15" s="9" t="str">
+      <c r="E15" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2015</v>
       </c>
-      <c r="F15" s="7"/>
+      <c r="F15" s="2"/>
       <c r="G15" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3" t="s">
+      <c r="H15" s="1"/>
+      <c r="I15" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J15" s="3" t="str">
+      <c r="J15" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
-      <c r="K15" s="3" t="str">
+      <c r="K15" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000437413_Table3</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="1"/>
       <c r="M15" t="s">
         <v>41</v>
       </c>
-      <c r="N15" t="str" cm="1">
-        <f t="array" ref="N15">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K15, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N15" t="str">
+        <f t="array" ref="N15">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K15, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
       <c r="O15" t="s">
-        <v>313</v>
-      </c>
-      <c r="P15" t="s">
         <v>53</v>
       </c>
-      <c r="Q15" s="16" t="s">
+      <c r="P15" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="R15" s="3" t="s">
+      <c r="Q15" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R15" t="s">
+        <v>141</v>
+      </c>
       <c r="S15" t="s">
-        <v>141</v>
+        <v>57</v>
       </c>
       <c r="T15" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U15" t="s">
-        <v>46</v>
-      </c>
-      <c r="V15" t="s">
         <v>58</v>
       </c>
-      <c r="W15" s="8" t="s">
+      <c r="V15" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="X15" s="7" t="s">
+      <c r="W15" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="Y15" t="s">
+      <c r="X15" t="s">
         <v>98</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>100</v>
       </c>
       <c r="AA15" t="s">
         <v>100</v>
       </c>
-      <c r="AB15" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE15" t="s">
+      <c r="AD15" t="s">
         <v>134</v>
       </c>
-      <c r="AI15">
+      <c r="AH15">
         <v>9</v>
       </c>
-      <c r="AK15">
+      <c r="AJ15">
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>129</v>
       </c>
-      <c r="B16" s="7" t="str">
+      <c r="B16" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="C16" s="9" t="str">
+      <c r="C16" s="2" t="str">
         <f t="shared" si="6"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D16" s="9" t="str">
+      <c r="D16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E16" s="9" t="str">
+      <c r="E16" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2015</v>
       </c>
-      <c r="F16" s="7"/>
+      <c r="F16" s="2"/>
       <c r="G16" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3" t="s">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J16" s="3" t="str">
+      <c r="J16" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
-      <c r="K16" s="3" t="str">
+      <c r="K16" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000437413_Table4</v>
       </c>
-      <c r="L16" s="3"/>
+      <c r="L16" s="1"/>
       <c r="M16" t="s">
         <v>41</v>
       </c>
-      <c r="N16" t="str" cm="1">
-        <f t="array" ref="N16">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K16, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N16" t="str">
+        <f t="array" ref="N16">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K16, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
       <c r="O16" t="s">
-        <v>313</v>
-      </c>
-      <c r="P16" t="s">
         <v>53</v>
       </c>
-      <c r="Q16" s="14" t="s">
+      <c r="P16" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="R16" s="3" t="s">
+      <c r="Q16" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R16" t="s">
+        <v>145</v>
+      </c>
       <c r="S16" t="s">
-        <v>145</v>
+        <v>57</v>
       </c>
       <c r="T16" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U16" t="s">
-        <v>46</v>
-      </c>
-      <c r="V16" t="s">
         <v>58</v>
       </c>
-      <c r="W16" s="8" t="s">
+      <c r="V16" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="X16" s="9" t="s">
+      <c r="W16" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="Y16" t="s">
+      <c r="X16" t="s">
         <v>98</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>100</v>
       </c>
       <c r="AA16" t="s">
         <v>100</v>
       </c>
-      <c r="AB16" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE16" t="s">
+      <c r="AD16" t="s">
         <v>134</v>
       </c>
-      <c r="AI16">
+      <c r="AH16">
         <v>8</v>
       </c>
-      <c r="AK16">
+      <c r="AJ16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>129</v>
       </c>
-      <c r="B17" s="7" t="str">
+      <c r="B17" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="C17" s="9" t="str">
+      <c r="C17" s="2" t="str">
         <f t="shared" si="6"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D17" s="9" t="str">
+      <c r="D17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E17" s="9" t="str">
+      <c r="E17" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2015</v>
       </c>
-      <c r="F17" s="7"/>
+      <c r="F17" s="2"/>
       <c r="G17" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3" t="s">
+      <c r="H17" s="1"/>
+      <c r="I17" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J17" s="3" t="str">
+      <c r="J17" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
-      <c r="K17" s="3" t="str">
+      <c r="K17" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000437413_Table5</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="1"/>
       <c r="M17" t="s">
         <v>41</v>
       </c>
-      <c r="N17" t="str" cm="1">
-        <f t="array" ref="N17">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K17, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N17" t="str">
+        <f t="array" ref="N17">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K17, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
       <c r="O17" t="s">
-        <v>313</v>
-      </c>
-      <c r="P17" t="s">
         <v>53</v>
       </c>
-      <c r="Q17" s="14" t="s">
+      <c r="P17" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="R17" s="3" t="s">
+      <c r="Q17" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R17" t="s">
+        <v>149</v>
+      </c>
       <c r="S17" t="s">
-        <v>149</v>
+        <v>57</v>
       </c>
       <c r="T17" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U17" t="s">
-        <v>46</v>
-      </c>
-      <c r="V17" t="s">
         <v>58</v>
       </c>
-      <c r="W17" s="8" t="s">
+      <c r="V17" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="X17" s="9" t="s">
+      <c r="W17" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="Y17" t="s">
+      <c r="X17" t="s">
         <v>98</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>100</v>
       </c>
       <c r="AA17" t="s">
         <v>100</v>
       </c>
-      <c r="AB17" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE17" t="s">
+      <c r="AD17" t="s">
         <v>134</v>
       </c>
-      <c r="AI17">
+      <c r="AH17">
         <v>9</v>
       </c>
-      <c r="AK17">
+      <c r="AJ17">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>151</v>
       </c>
-      <c r="B18" s="7" t="str">
+      <c r="B18" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
-      <c r="C18" s="9" t="str">
+      <c r="C18" s="2" t="str">
         <f t="shared" si="6"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D18" s="9" t="str">
+      <c r="D18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E18" s="9" t="str">
+      <c r="E18" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2020</v>
       </c>
-      <c r="F18" s="7"/>
+      <c r="F18" s="2"/>
       <c r="G18" t="str">
         <f t="shared" si="3"/>
         <v>10.1002/cne.24985</v>
       </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3" t="s">
+      <c r="H18" s="1"/>
+      <c r="I18" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="J18" s="3" t="str">
+      <c r="J18" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
-      <c r="K18" s="3" t="str">
+      <c r="K18" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="1"/>
       <c r="M18" t="s">
         <v>41</v>
       </c>
-      <c r="N18" t="str" cm="1">
-        <f t="array" ref="N18">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K18, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N18" t="str">
+        <f t="array" ref="N18">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K18, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
       <c r="O18" t="s">
-        <v>312</v>
-      </c>
-      <c r="P18" t="s">
         <v>53</v>
       </c>
-      <c r="Q18" s="14" t="s">
+      <c r="P18" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="R18" s="3" t="s">
+      <c r="Q18" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R18" t="s">
+        <v>154</v>
+      </c>
       <c r="S18" t="s">
-        <v>154</v>
+        <v>57</v>
       </c>
       <c r="T18" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U18" t="s">
-        <v>46</v>
-      </c>
-      <c r="V18" t="s">
         <v>78</v>
       </c>
-      <c r="X18" s="7" t="s">
+      <c r="W18" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="Y18" t="s">
+      <c r="X18" t="s">
         <v>156</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>100</v>
       </c>
       <c r="AA18" t="s">
         <v>100</v>
       </c>
-      <c r="AB18" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE18" t="s">
+      <c r="AD18" t="s">
         <v>157</v>
+      </c>
+      <c r="AH18">
+        <v>0</v>
       </c>
       <c r="AI18">
         <v>0</v>
@@ -3380,93 +3173,90 @@
       <c r="AJ18">
         <v>0</v>
       </c>
-      <c r="AK18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:37" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="19" spans="1:36" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>151</v>
       </c>
-      <c r="B19" s="7" t="str">
+      <c r="B19" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
-      <c r="C19" s="9" t="str">
+      <c r="C19" s="2" t="str">
         <f t="shared" si="6"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D19" s="9" t="str">
+      <c r="D19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E19" s="9" t="str">
+      <c r="E19" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2020</v>
       </c>
-      <c r="F19" s="7"/>
+      <c r="F19" s="2"/>
       <c r="G19" t="str">
         <f t="shared" si="3"/>
         <v>10.1002/cne.24985</v>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3" t="s">
+      <c r="H19" s="1"/>
+      <c r="I19" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="J19" s="3" t="str">
+      <c r="J19" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
-      <c r="K19" s="3" t="str">
+      <c r="K19" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
-      <c r="L19" s="3"/>
+      <c r="L19" s="1"/>
       <c r="M19" t="s">
         <v>41</v>
       </c>
-      <c r="N19" t="str" cm="1">
-        <f t="array" ref="N19">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K19, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N19" t="str">
+        <f t="array" ref="N19">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K19, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
       </c>
       <c r="O19" t="s">
-        <v>312</v>
-      </c>
-      <c r="P19" t="s">
         <v>53</v>
       </c>
-      <c r="Q19" s="14" t="s">
+      <c r="P19" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="R19" s="3" t="s">
+      <c r="Q19" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R19" t="s">
+        <v>160</v>
+      </c>
       <c r="S19" t="s">
-        <v>160</v>
+        <v>57</v>
       </c>
       <c r="T19" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U19" t="s">
-        <v>46</v>
-      </c>
-      <c r="V19" t="s">
         <v>78</v>
       </c>
-      <c r="X19" s="7" t="s">
+      <c r="W19" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="Y19" t="s">
+      <c r="X19" t="s">
         <v>162</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>100</v>
       </c>
       <c r="AA19" t="s">
         <v>100</v>
       </c>
-      <c r="AB19" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE19" t="s">
+      <c r="AD19" t="s">
         <v>157</v>
+      </c>
+      <c r="AH19">
+        <v>0</v>
       </c>
       <c r="AI19">
         <v>0</v>
@@ -3474,30 +3264,27 @@
       <c r="AJ19">
         <v>0</v>
       </c>
-      <c r="AK19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="20" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>163</v>
       </c>
-      <c r="B20" s="7" t="str">
+      <c r="B20" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
-      <c r="C20" s="9" t="str">
+      <c r="C20" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Iwaniuk</v>
       </c>
-      <c r="D20" s="9" t="str">
+      <c r="D20" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A20)),
     IF(LEN(A20)-LEN(SUBSTITUTE(A20, ",", ""))&gt;=6, "etal", MID(A20, SEARCH("&amp; ", A20)+2, SEARCH(",", A20, SEARCH("&amp; ", A20)+2) - SEARCH("&amp; ", A20)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E20" s="9" t="str">
+      <c r="E20" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2001</v>
       </c>
@@ -3505,70 +3292,67 @@
         <f t="shared" si="3"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3" t="s">
+      <c r="H20" s="1"/>
+      <c r="I20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J20" s="3" t="str">
+      <c r="J20" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Iwaniuk_etal_2001_Table1</v>
       </c>
-      <c r="K20" s="3" t="str">
+      <c r="K20" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
-      <c r="L20" s="3"/>
+      <c r="L20" s="1"/>
       <c r="M20" t="s">
         <v>164</v>
       </c>
-      <c r="N20" t="str" cm="1">
-        <f t="array" ref="N20">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K20, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N20" t="str">
+        <f t="array" ref="N20">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K20, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O20" t="s">
-        <v>297</v>
-      </c>
-      <c r="P20" t="s">
         <v>35</v>
       </c>
-      <c r="Q20" s="14"/>
-      <c r="S20" t="str">
-        <f>IF(R20="N", Q20, "write file name")</f>
+      <c r="P20" s="4"/>
+      <c r="R20" t="str">
+        <f>IF(Q20="N", P20, "write file name")</f>
         <v>write file name</v>
       </c>
+      <c r="S20" t="s">
+        <v>57</v>
+      </c>
       <c r="T20" t="s">
-        <v>57</v>
-      </c>
-      <c r="U20" t="s">
         <v>46</v>
       </c>
-      <c r="X20" s="11" t="s">
+      <c r="W20" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="Y20" t="s">
+      <c r="X20" t="s">
         <v>166</v>
       </c>
-      <c r="AE20" t="s">
+      <c r="AD20" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="21" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>163</v>
       </c>
-      <c r="B21" s="7" t="str">
+      <c r="B21" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
-      <c r="C21" s="9" t="str">
+      <c r="C21" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Iwaniuk</v>
       </c>
-      <c r="D21" s="9" t="str">
+      <c r="D21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E21" s="9" t="str">
+      <c r="E21" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2001</v>
       </c>
@@ -3576,70 +3360,67 @@
         <f t="shared" si="3"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3" t="s">
+      <c r="H21" s="1"/>
+      <c r="I21" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J21" s="3" t="str">
+      <c r="J21" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Iwaniuk_etal_2001_Table2</v>
       </c>
-      <c r="K21" s="3" t="str">
+      <c r="K21" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
-      <c r="L21" s="3"/>
+      <c r="L21" s="1"/>
       <c r="M21" t="s">
         <v>164</v>
       </c>
-      <c r="N21" t="str" cm="1">
-        <f t="array" ref="N21">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K21, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N21" t="str">
+        <f t="array" ref="N21">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O21" t="s">
-        <v>297</v>
-      </c>
-      <c r="P21" t="s">
         <v>35</v>
       </c>
-      <c r="Q21" s="14"/>
-      <c r="S21" t="str">
-        <f>IF(R21="N", Q21, "write file name")</f>
+      <c r="P21" s="4"/>
+      <c r="R21" t="str">
+        <f>IF(Q21="N", P21, "write file name")</f>
         <v>write file name</v>
       </c>
+      <c r="S21" t="s">
+        <v>57</v>
+      </c>
       <c r="T21" t="s">
-        <v>57</v>
-      </c>
-      <c r="U21" t="s">
         <v>46</v>
       </c>
-      <c r="X21" s="11" t="s">
+      <c r="W21" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Y21" t="s">
+      <c r="X21" t="s">
         <v>166</v>
       </c>
-      <c r="AE21" t="s">
+      <c r="AD21" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="22" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>163</v>
       </c>
-      <c r="B22" s="7" t="str">
+      <c r="B22" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
-      <c r="C22" s="9" t="str">
+      <c r="C22" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Iwaniuk</v>
       </c>
-      <c r="D22" s="9" t="str">
+      <c r="D22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E22" s="9" t="str">
+      <c r="E22" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2001</v>
       </c>
@@ -3647,70 +3428,67 @@
         <f t="shared" si="3"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
-      <c r="H22" s="3"/>
-      <c r="I22" s="3" t="s">
+      <c r="H22" s="1"/>
+      <c r="I22" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="J22" s="3" t="str">
+      <c r="J22" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Iwaniuk_etal_2001_Table3</v>
       </c>
-      <c r="K22" s="3" t="str">
+      <c r="K22" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
-      <c r="L22" s="3"/>
+      <c r="L22" s="1"/>
       <c r="M22" t="s">
         <v>164</v>
       </c>
-      <c r="N22" t="str" cm="1">
-        <f t="array" ref="N22">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K22, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N22" t="str">
+        <f t="array" ref="N22">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K22, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O22" t="s">
-        <v>297</v>
-      </c>
-      <c r="P22" t="s">
         <v>35</v>
       </c>
-      <c r="Q22" s="14"/>
-      <c r="S22" t="str">
-        <f>IF(R22="N", Q22, "write file name")</f>
+      <c r="P22" s="4"/>
+      <c r="R22" t="str">
+        <f>IF(Q22="N", P22, "write file name")</f>
         <v>write file name</v>
       </c>
+      <c r="S22" t="s">
+        <v>57</v>
+      </c>
       <c r="T22" t="s">
-        <v>57</v>
-      </c>
-      <c r="U22" t="s">
         <v>46</v>
       </c>
-      <c r="X22" s="11" t="s">
+      <c r="W22" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="Y22" t="s">
+      <c r="X22" t="s">
         <v>166</v>
       </c>
-      <c r="AE22" t="s">
+      <c r="AD22" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="23" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>163</v>
       </c>
-      <c r="B23" s="7" t="str">
+      <c r="B23" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
-      <c r="C23" s="9" t="str">
+      <c r="C23" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Iwaniuk</v>
       </c>
-      <c r="D23" s="9" t="str">
+      <c r="D23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E23" s="9" t="str">
+      <c r="E23" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2001</v>
       </c>
@@ -3718,70 +3496,67 @@
         <f t="shared" si="3"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3" t="s">
+      <c r="H23" s="1"/>
+      <c r="I23" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J23" s="3" t="str">
+      <c r="J23" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Iwaniuk_etal_2001_Table4</v>
       </c>
-      <c r="K23" s="3" t="str">
+      <c r="K23" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
-      <c r="L23" s="3"/>
+      <c r="L23" s="1"/>
       <c r="M23" t="s">
         <v>164</v>
       </c>
-      <c r="N23" t="str" cm="1">
-        <f t="array" ref="N23">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K23, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N23" t="str">
+        <f t="array" ref="N23">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K23, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O23" t="s">
-        <v>297</v>
-      </c>
-      <c r="P23" t="s">
         <v>35</v>
       </c>
-      <c r="Q23" s="14"/>
-      <c r="S23" t="str">
-        <f>IF(R23="N", Q23, "write file name")</f>
+      <c r="P23" s="4"/>
+      <c r="R23" t="str">
+        <f>IF(Q23="N", P23, "write file name")</f>
         <v>write file name</v>
       </c>
+      <c r="S23" t="s">
+        <v>57</v>
+      </c>
       <c r="T23" t="s">
-        <v>57</v>
-      </c>
-      <c r="U23" t="s">
         <v>46</v>
       </c>
-      <c r="X23" s="11" t="s">
+      <c r="W23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="Y23" t="s">
+      <c r="X23" t="s">
         <v>166</v>
       </c>
-      <c r="AE23" t="s">
+      <c r="AD23" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="24" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>171</v>
       </c>
-      <c r="B24" s="7" t="str">
+      <c r="B24" s="2" t="str">
         <f t="shared" si="5"/>
         <v>JardimMesseder_etal_2017</v>
       </c>
-      <c r="C24" s="9" t="str">
+      <c r="C24" s="2" t="str">
         <f t="shared" si="6"/>
         <v>JardimMesseder</v>
       </c>
-      <c r="D24" s="9" t="str">
+      <c r="D24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E24" s="9" t="str">
+      <c r="E24" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2017</v>
       </c>
@@ -3789,838 +3564,808 @@
         <f t="shared" si="3"/>
         <v>10.3389/fnana.2017.00118</v>
       </c>
-      <c r="H24" s="3"/>
-      <c r="I24" s="3" t="s">
+      <c r="H24" s="1"/>
+      <c r="I24" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J24" s="3" t="str">
+      <c r="J24" s="1" t="str">
         <f t="shared" si="4"/>
         <v>JardimMesseder_etal_2017_Table1</v>
       </c>
-      <c r="K24" s="3" t="str">
+      <c r="K24" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
-      <c r="L24" s="3"/>
+      <c r="L24" s="1"/>
       <c r="M24" t="s">
         <v>41</v>
       </c>
-      <c r="N24" t="str" cm="1">
-        <f t="array" ref="N24">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K24, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N24" t="str">
+        <f t="array" ref="N24">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K24, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="O24" t="s">
-        <v>311</v>
-      </c>
-      <c r="P24" t="s">
         <v>53</v>
       </c>
-      <c r="Q24" s="14" t="s">
+      <c r="P24" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="R24" s="3" t="s">
+      <c r="Q24" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R24" t="s">
+        <v>173</v>
+      </c>
       <c r="S24" t="s">
-        <v>173</v>
+        <v>57</v>
       </c>
       <c r="T24" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U24" t="s">
-        <v>46</v>
-      </c>
-      <c r="V24" t="s">
         <v>58</v>
       </c>
-      <c r="W24" s="8" t="s">
+      <c r="V24" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="X24" s="7" t="s">
+      <c r="W24" s="2" t="s">
         <v>175</v>
       </c>
+      <c r="X24" t="s">
+        <v>98</v>
+      </c>
       <c r="Y24" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Z24" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AA24" t="s">
         <v>100</v>
       </c>
-      <c r="AB24" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE24" t="s">
+      <c r="AD24" t="s">
         <v>176</v>
       </c>
-      <c r="AI24">
+      <c r="AH24">
         <v>2</v>
       </c>
-      <c r="AK24">
+      <c r="AJ24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>177</v>
       </c>
-      <c r="B25" s="7" t="str">
+      <c r="B25" s="2" t="str">
         <f t="shared" ref="B25" si="9">C25 &amp; IF(D25&lt;&gt;"", "_" &amp; D25, "_") &amp; IF(E25&lt;&gt;"", "_" &amp; E25, "_") &amp; IF(F25&lt;&gt;"", "_" &amp; F25, "")</f>
         <v>Kverkova_etal_2018</v>
       </c>
-      <c r="C25" s="9" t="str">
+      <c r="C25" s="2" t="str">
         <f t="shared" ref="C25" si="10">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A25,","), "-", ""), " ", "")</f>
         <v>Kverkova</v>
       </c>
-      <c r="D25" s="9" t="str">
+      <c r="D25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E25" s="9" t="str">
+      <c r="E25" s="2" t="str">
         <f t="shared" ref="E25" si="11">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A25, "("), ")")</f>
         <v>2018</v>
       </c>
-      <c r="F25" s="7"/>
+      <c r="F25" s="2"/>
       <c r="G25" t="str">
         <f t="shared" ref="G25" si="12">_xlfn.TEXTAFTER(A25,"https://doi.org/")</f>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3" t="s">
+      <c r="H25" s="1"/>
+      <c r="I25" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J25" s="3" t="str">
+      <c r="J25" s="1" t="str">
         <f t="shared" ref="J25" si="13">TRIM(_xlfn.TEXTJOIN("_",FALSE,B25,(SUBSTITUTE(SUBSTITUTE(I25," ",""), "_", ""))))</f>
         <v>Kverkova_etal_2018_Table1</v>
       </c>
-      <c r="K25" s="3" t="str">
+      <c r="K25" s="1" t="str">
         <f t="shared" ref="K25" si="14">IF(ISBLANK(H25),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G25, SUBSTITUTE(I25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H25, SUBSTITUTE(I25,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
-      <c r="L25" s="3"/>
+      <c r="L25" s="1"/>
       <c r="M25" t="s">
         <v>41</v>
       </c>
-      <c r="N25" t="str" cm="1">
-        <f t="array" ref="N25">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K25, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N25" t="str">
+        <f t="array" ref="N25">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K25, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="O25" t="s">
-        <v>310</v>
-      </c>
-      <c r="P25" t="s">
         <v>53</v>
       </c>
-      <c r="Q25" s="14" t="s">
+      <c r="P25" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="R25" s="3" t="s">
+      <c r="Q25" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R25" t="s">
+        <v>178</v>
+      </c>
       <c r="S25" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T25" t="s">
-        <v>179</v>
-      </c>
-      <c r="U25" t="s">
         <v>46</v>
       </c>
-      <c r="W25" s="8"/>
-      <c r="X25" s="7" t="s">
+      <c r="V25" s="3"/>
+      <c r="W25" s="2" t="s">
         <v>264</v>
       </c>
+      <c r="X25" t="s">
+        <v>265</v>
+      </c>
       <c r="Y25" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z25" t="s">
         <v>99</v>
       </c>
-      <c r="AB25" t="s">
+      <c r="AA25" t="s">
         <v>100</v>
       </c>
-      <c r="AE25" t="s">
+      <c r="AD25" t="s">
         <v>183</v>
       </c>
-      <c r="AI25">
+      <c r="AH25">
         <v>1</v>
       </c>
-      <c r="AK25">
+      <c r="AJ25">
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>177</v>
       </c>
-      <c r="B26" s="7" t="str">
+      <c r="B26" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Kverkova_etal_2018</v>
       </c>
-      <c r="C26" s="9" t="str">
+      <c r="C26" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Kverkova</v>
       </c>
-      <c r="D26" s="9" t="str">
+      <c r="D26" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A26)),
     IF(LEN(A26)-LEN(SUBSTITUTE(A26, ",", ""))&gt;=6, "etal", MID(A26, SEARCH("&amp; ", A26)+2, SEARCH(",", A26, SEARCH("&amp; ", A26)+2) - SEARCH("&amp; ", A26)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E26" s="9" t="str">
+      <c r="E26" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2018</v>
       </c>
-      <c r="F26" s="7"/>
+      <c r="F26" s="2"/>
       <c r="G26" t="str">
         <f t="shared" si="3"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3" t="s">
+      <c r="H26" s="1"/>
+      <c r="I26" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J26" s="3" t="str">
+      <c r="J26" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Kverkova_etal_2018_TableS1</v>
       </c>
-      <c r="K26" s="3" t="str">
+      <c r="K26" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
-      <c r="L26" s="3"/>
+      <c r="L26" s="1"/>
       <c r="M26" t="s">
         <v>41</v>
       </c>
-      <c r="N26" t="str" cm="1">
-        <f t="array" ref="N26">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N26" t="str">
+        <f t="array" ref="N26">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K26, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="O26" t="s">
-        <v>310</v>
-      </c>
-      <c r="P26" t="s">
         <v>53</v>
       </c>
-      <c r="Q26" s="14" t="s">
+      <c r="P26" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="R26" s="3" t="s">
+      <c r="Q26" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R26" t="s">
+        <v>178</v>
+      </c>
       <c r="S26" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="T26" t="s">
-        <v>179</v>
+        <v>46</v>
       </c>
       <c r="U26" t="s">
-        <v>46</v>
-      </c>
-      <c r="V26" t="s">
         <v>58</v>
       </c>
-      <c r="W26" s="8" t="s">
+      <c r="V26" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="X26" s="7" t="s">
+      <c r="W26" s="2" t="s">
         <v>181</v>
       </c>
+      <c r="X26" t="s">
+        <v>156</v>
+      </c>
       <c r="Y26" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z26" t="s">
         <v>182</v>
       </c>
-      <c r="AB26" t="s">
+      <c r="AA26" t="s">
         <v>100</v>
       </c>
-      <c r="AE26" t="s">
+      <c r="AD26" t="s">
         <v>183</v>
       </c>
-      <c r="AI26">
+      <c r="AH26">
         <v>1</v>
       </c>
-      <c r="AK26">
+      <c r="AJ26">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>177</v>
       </c>
-      <c r="B27" s="7" t="str">
+      <c r="B27" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Kverkova_etal_2018</v>
       </c>
-      <c r="C27" s="9" t="str">
+      <c r="C27" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Kverkova</v>
       </c>
-      <c r="D27" s="9" t="str">
+      <c r="D27" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E27" s="9" t="str">
+      <c r="E27" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2018</v>
       </c>
-      <c r="F27" s="7"/>
+      <c r="F27" s="2"/>
       <c r="G27" t="str">
         <f t="shared" si="3"/>
         <v>10.1038/s41598-018-26062-8</v>
       </c>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3" t="s">
+      <c r="H27" s="1"/>
+      <c r="I27" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="J27" s="3" t="str">
+      <c r="J27" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Kverkova_etal_2018_TableS5</v>
       </c>
-      <c r="K27" s="3" t="str">
+      <c r="K27" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
-      <c r="L27" s="3"/>
+      <c r="L27" s="1"/>
       <c r="M27" t="s">
         <v>41</v>
       </c>
-      <c r="N27" t="str" cm="1">
-        <f t="array" ref="N27">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K27, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N27" t="str">
+        <f t="array" ref="N27">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K27, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
       <c r="O27" t="s">
-        <v>310</v>
-      </c>
-      <c r="P27" t="s">
         <v>53</v>
       </c>
-      <c r="Q27" s="14" t="s">
+      <c r="P27" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="R27" s="3" t="s">
+      <c r="Q27" s="1" t="s">
         <v>55</v>
       </c>
+      <c r="R27" t="s">
+        <v>185</v>
+      </c>
       <c r="S27" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="T27" t="s">
-        <v>186</v>
+        <v>46</v>
       </c>
       <c r="U27" t="s">
-        <v>46</v>
-      </c>
-      <c r="V27" t="s">
         <v>58</v>
       </c>
-      <c r="W27" s="8" t="s">
+      <c r="V27" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="X27" s="7" t="s">
+      <c r="W27" s="2" t="s">
         <v>187</v>
       </c>
+      <c r="X27" t="s">
+        <v>162</v>
+      </c>
       <c r="Y27" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z27" t="s">
         <v>99</v>
       </c>
-      <c r="AB27" t="s">
+      <c r="AA27" t="s">
         <v>100</v>
       </c>
-      <c r="AE27" t="s">
+      <c r="AD27" t="s">
         <v>183</v>
       </c>
-      <c r="AI27">
+      <c r="AH27">
         <v>1</v>
       </c>
-      <c r="AK27">
+      <c r="AJ27">
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>188</v>
       </c>
-      <c r="B28" s="7" t="str">
+      <c r="B28" s="2" t="str">
         <f t="shared" si="5"/>
         <v>ManyPrimates__2022</v>
       </c>
-      <c r="C28" s="9" t="str">
+      <c r="C28" s="2" t="str">
         <f t="shared" si="6"/>
         <v>ManyPrimates</v>
       </c>
-      <c r="D28" s="9" t="str">
+      <c r="D28" s="2" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
-      <c r="E28" s="9" t="str">
+      <c r="E28" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2022</v>
       </c>
-      <c r="F28" s="7"/>
+      <c r="F28" s="2"/>
       <c r="G28" t="str">
         <f t="shared" si="3"/>
         <v>10.26451/abc.09.04.06.2022</v>
       </c>
-      <c r="H28" s="3"/>
-      <c r="I28" s="12" t="s">
+      <c r="H28" s="1"/>
+      <c r="I28" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="J28" s="3" t="str">
+      <c r="J28" s="1" t="str">
         <f t="shared" si="4"/>
         <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
-      <c r="K28" s="3" t="str">
+      <c r="K28" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
-      <c r="L28" s="3"/>
+      <c r="L28" s="1"/>
       <c r="M28" t="s">
         <v>190</v>
       </c>
-      <c r="N28" t="str" cm="1">
-        <f t="array" ref="N28">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K28, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N28" t="str">
+        <f t="array" ref="N28">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K28, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O28" t="s">
-        <v>297</v>
-      </c>
-      <c r="P28" t="s">
         <v>35</v>
       </c>
-      <c r="Q28" s="14"/>
-      <c r="S28" t="str">
-        <f t="shared" ref="S28:S33" si="15">IF(R28="N", Q28, "write file name")</f>
+      <c r="P28" s="4"/>
+      <c r="R28" t="str">
+        <f t="shared" ref="R28:R33" si="15">IF(Q28="N", P28, "write file name")</f>
         <v>write file name</v>
       </c>
+      <c r="S28" t="s">
+        <v>67</v>
+      </c>
       <c r="T28" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="U28" t="s">
-        <v>46</v>
-      </c>
-      <c r="V28" t="s">
         <v>68</v>
       </c>
-      <c r="W28" s="8" t="s">
+      <c r="V28" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="X28" s="7"/>
+      <c r="W28" s="2"/>
+      <c r="X28" t="s">
+        <v>192</v>
+      </c>
       <c r="Y28" t="s">
-        <v>192</v>
-      </c>
-      <c r="Z28" t="s">
         <v>49</v>
       </c>
-      <c r="AC28" t="s">
+      <c r="AB28" t="s">
         <v>193</v>
       </c>
-      <c r="AE28" t="s">
+      <c r="AD28" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>194</v>
       </c>
-      <c r="B29" s="7" t="str">
+      <c r="B29" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Powell_etal_2017</v>
       </c>
-      <c r="C29" s="9" t="str">
+      <c r="C29" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Powell</v>
       </c>
-      <c r="D29" s="9" t="str">
+      <c r="D29" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E29" s="9" t="str">
+      <c r="E29" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2017</v>
       </c>
-      <c r="F29" s="7"/>
+      <c r="F29" s="2"/>
       <c r="G29" t="str">
         <f t="shared" si="3"/>
         <v>10.1098/rspb.2017.1765</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H29" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="I29" s="3" t="s">
+      <c r="I29" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="J29" s="3" t="str">
+      <c r="J29" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Powell_etal_2017_Dataset1</v>
       </c>
-      <c r="K29" s="3" t="str">
+      <c r="K29" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
-      <c r="L29" s="3"/>
-      <c r="M29" s="15" t="s">
+      <c r="L29" s="1"/>
+      <c r="M29" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N29" t="str" cm="1">
-        <f t="array" ref="N29">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K29, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N29" t="str">
+        <f t="array" ref="N29">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K29, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O29" t="s">
-        <v>297</v>
-      </c>
-      <c r="P29" t="s">
         <v>35</v>
       </c>
-      <c r="Q29" s="14"/>
-      <c r="S29" t="str">
+      <c r="P29" s="4"/>
+      <c r="R29" t="str">
         <f t="shared" si="15"/>
         <v>write file name</v>
       </c>
+      <c r="S29" t="s">
+        <v>67</v>
+      </c>
       <c r="T29" t="s">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="U29" t="s">
-        <v>46</v>
-      </c>
-      <c r="V29" t="s">
         <v>68</v>
       </c>
-      <c r="W29" s="8" t="s">
+      <c r="V29" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="X29" s="7"/>
+      <c r="W29" s="2"/>
+      <c r="X29" t="s">
+        <v>198</v>
+      </c>
       <c r="Y29" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z29" t="s">
         <v>49</v>
       </c>
-      <c r="AC29" t="s">
+      <c r="AB29" t="s">
         <v>48</v>
       </c>
-      <c r="AE29" t="s">
+      <c r="AD29" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>199</v>
       </c>
-      <c r="B30" s="7" t="str">
+      <c r="B30" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
-      <c r="C30" s="9" t="str">
+      <c r="C30" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Sherwood</v>
       </c>
-      <c r="D30" s="9" t="str">
+      <c r="D30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E30" s="9" t="str">
+      <c r="E30" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2004</v>
       </c>
-      <c r="F30" s="7" t="s">
+      <c r="F30" s="2" t="s">
         <v>200</v>
       </c>
       <c r="G30" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000075672</v>
       </c>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3" t="s">
+      <c r="H30" s="1"/>
+      <c r="I30" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="J30" s="3" t="str">
+      <c r="J30" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Sherwood_etal_2004_I_Table4</v>
       </c>
-      <c r="K30" s="3" t="str">
+      <c r="K30" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000075672_Table4</v>
       </c>
-      <c r="L30" s="3"/>
+      <c r="L30" s="1"/>
       <c r="M30" t="s">
         <v>190</v>
       </c>
-      <c r="N30" t="str" cm="1">
-        <f t="array" ref="N30">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K30, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N30" t="str">
+        <f t="array" ref="N30">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K30, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O30" t="s">
-        <v>297</v>
-      </c>
-      <c r="P30" t="s">
         <v>35</v>
       </c>
-      <c r="Q30" s="14"/>
-      <c r="S30" t="str">
+      <c r="P30" s="4"/>
+      <c r="R30" t="str">
         <f t="shared" si="15"/>
         <v>write file name</v>
       </c>
+      <c r="S30" t="s">
+        <v>57</v>
+      </c>
       <c r="T30" t="s">
-        <v>57</v>
-      </c>
-      <c r="U30" t="s">
         <v>201</v>
       </c>
-      <c r="X30" s="7" t="s">
+      <c r="W30" s="2" t="s">
         <v>202</v>
       </c>
+      <c r="X30" t="s">
+        <v>203</v>
+      </c>
       <c r="Y30" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z30" t="s">
         <v>99</v>
       </c>
-      <c r="AE30" t="s">
+      <c r="AD30" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>199</v>
       </c>
-      <c r="B31" s="7" t="str">
+      <c r="B31" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Sherwood_etal_2004_I</v>
       </c>
-      <c r="C31" s="9" t="str">
+      <c r="C31" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Sherwood</v>
       </c>
-      <c r="D31" s="9" t="str">
+      <c r="D31" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A31)),
     IF(LEN(A31)-LEN(SUBSTITUTE(A31, ",", ""))&gt;=6, "etal", MID(A31, SEARCH("&amp; ", A31)+2, SEARCH(",", A31, SEARCH("&amp; ", A31)+2) - SEARCH("&amp; ", A31)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E31" s="9" t="str">
+      <c r="E31" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2004</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="F31" s="2" t="s">
         <v>200</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="3"/>
         <v>10.1159/000075672</v>
       </c>
-      <c r="H31" s="3"/>
-      <c r="I31" s="3" t="s">
+      <c r="H31" s="1"/>
+      <c r="I31" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="J31" s="3" t="str">
+      <c r="J31" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Sherwood_etal_2004_I_Table5</v>
       </c>
-      <c r="K31" s="3" t="str">
+      <c r="K31" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1159%2F000075672_Table5</v>
       </c>
-      <c r="L31" s="3"/>
+      <c r="L31" s="1"/>
       <c r="M31" t="s">
         <v>190</v>
       </c>
-      <c r="N31" t="str" cm="1">
-        <f t="array" ref="N31">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K31, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N31" t="str">
+        <f t="array" ref="N31">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O31" t="s">
-        <v>297</v>
-      </c>
-      <c r="P31" t="s">
         <v>35</v>
       </c>
-      <c r="Q31" s="14"/>
-      <c r="S31" t="str">
+      <c r="P31" s="4"/>
+      <c r="R31" t="str">
         <f t="shared" si="15"/>
         <v>write file name</v>
       </c>
+      <c r="S31" t="s">
+        <v>57</v>
+      </c>
       <c r="T31" t="s">
-        <v>57</v>
-      </c>
-      <c r="U31" t="s">
         <v>201</v>
       </c>
-      <c r="X31" s="11" t="s">
+      <c r="W31" s="2" t="s">
         <v>204</v>
       </c>
+      <c r="X31" t="s">
+        <v>203</v>
+      </c>
       <c r="Y31" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z31" t="s">
         <v>99</v>
       </c>
-      <c r="AE31" t="s">
+      <c r="AD31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>205</v>
       </c>
-      <c r="B32" s="7" t="str">
+      <c r="B32" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Winkler_Bryant_2021</v>
       </c>
-      <c r="C32" s="9" t="str">
+      <c r="C32" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Winkler</v>
       </c>
-      <c r="D32" s="9" t="str">
+      <c r="D32" s="2" t="str">
         <f t="shared" si="1"/>
         <v>Bryant</v>
       </c>
-      <c r="E32" s="9" t="str">
+      <c r="E32" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2021</v>
       </c>
-      <c r="F32" s="7"/>
+      <c r="F32" s="2"/>
       <c r="G32" t="str">
         <f t="shared" si="3"/>
         <v>10.1080/09524622.2021.1905065</v>
       </c>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3" t="s">
+      <c r="H32" s="1"/>
+      <c r="I32" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="J32" s="3" t="str">
+      <c r="J32" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Winkler_Bryant_2021_Figure1</v>
       </c>
-      <c r="K32" s="3" t="str">
+      <c r="K32" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
-      <c r="L32" s="3"/>
-      <c r="M32" s="15" t="s">
+      <c r="L32" s="1"/>
+      <c r="M32" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N32" t="str" cm="1">
-        <f t="array" ref="N32">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K32, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N32" t="str">
+        <f t="array" ref="N32">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O32" t="s">
-        <v>297</v>
-      </c>
-      <c r="P32" t="s">
         <v>35</v>
       </c>
-      <c r="Q32" s="14"/>
-      <c r="S32" t="str">
+      <c r="P32" s="4"/>
+      <c r="R32" t="str">
         <f t="shared" si="15"/>
         <v>write file name</v>
       </c>
+      <c r="S32" t="s">
+        <v>57</v>
+      </c>
       <c r="T32" t="s">
-        <v>57</v>
-      </c>
-      <c r="U32" t="s">
         <v>207</v>
       </c>
-      <c r="X32" s="7"/>
-      <c r="Y32" t="s">
+      <c r="W32" s="2"/>
+      <c r="X32" t="s">
         <v>208</v>
       </c>
-      <c r="AE32" t="s">
+      <c r="AD32" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>209</v>
       </c>
-      <c r="B33" s="7" t="str">
+      <c r="B33" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Young_etal_2013</v>
       </c>
-      <c r="C33" s="9" t="str">
+      <c r="C33" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Young</v>
       </c>
-      <c r="D33" s="9" t="str">
+      <c r="D33" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E33" s="9" t="str">
+      <c r="E33" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2013</v>
       </c>
-      <c r="F33" s="7"/>
+      <c r="F33" s="2"/>
       <c r="G33" t="str">
         <f t="shared" si="3"/>
         <v>10.3389/fncir.2013.00030</v>
       </c>
-      <c r="H33" s="3"/>
-      <c r="I33" s="3" t="s">
+      <c r="H33" s="1"/>
+      <c r="I33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J33" s="3" t="str">
+      <c r="J33" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Young_etal_2013_Table1</v>
       </c>
-      <c r="K33" s="3" t="str">
+      <c r="K33" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
-      <c r="L33" s="3"/>
+      <c r="L33" s="1"/>
       <c r="M33" t="s">
         <v>190</v>
       </c>
-      <c r="N33" t="str" cm="1">
-        <f t="array" ref="N33">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K33, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N33" t="str">
+        <f t="array" ref="N33">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="O33" t="s">
-        <v>297</v>
-      </c>
-      <c r="P33" t="s">
         <v>35</v>
       </c>
-      <c r="Q33" s="14"/>
-      <c r="S33" t="str">
+      <c r="P33" s="4"/>
+      <c r="R33" t="str">
         <f t="shared" si="15"/>
         <v>write file name</v>
       </c>
+      <c r="S33" t="s">
+        <v>113</v>
+      </c>
       <c r="T33" t="s">
-        <v>113</v>
-      </c>
-      <c r="U33" t="s">
         <v>46</v>
       </c>
-      <c r="X33" s="7"/>
-      <c r="Y33" t="s">
+      <c r="W33" s="2"/>
+      <c r="X33" t="s">
         <v>210</v>
       </c>
-      <c r="AE33" t="s">
+      <c r="AD33" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>211</v>
       </c>
-      <c r="B34" s="7" t="str">
+      <c r="B34" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Mota_etal_2015</v>
       </c>
-      <c r="C34" s="9" t="str">
+      <c r="C34" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Mota</v>
       </c>
-      <c r="D34" s="9" t="str">
+      <c r="D34" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E34" s="9" t="str">
+      <c r="E34" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2015</v>
       </c>
@@ -4628,51 +4373,48 @@
         <f t="shared" si="3"/>
         <v>10.1126/science.aaa9101</v>
       </c>
-      <c r="I34" s="3" t="s">
+      <c r="I34" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J34" s="3" t="str">
+      <c r="J34" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Mota_etal_2015_TableS1</v>
       </c>
-      <c r="K34" s="3" t="str">
+      <c r="K34" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
-      <c r="N34" t="str" cm="1">
-        <f t="array" ref="N34">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K34, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N34" t="str">
+        <f t="array" ref="N34">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
-      <c r="O34" t="s">
-        <v>308</v>
-      </c>
-      <c r="P34" s="3" t="s">
+      <c r="O34" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI34">
+      <c r="AH34">
         <v>10</v>
       </c>
-      <c r="AK34">
+      <c r="AJ34">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>212</v>
       </c>
-      <c r="B35" s="7" t="str">
+      <c r="B35" s="2" t="str">
         <f t="shared" si="5"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
-      <c r="C35" s="9" t="str">
+      <c r="C35" s="2" t="str">
         <f t="shared" si="6"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D35" s="9" t="str">
+      <c r="D35" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E35" s="9" t="str">
+      <c r="E35" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2013</v>
       </c>
@@ -4680,48 +4422,45 @@
         <f t="shared" si="3"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="I35" s="3" t="s">
+      <c r="I35" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="J35" s="3" t="str">
+      <c r="J35" s="1" t="str">
         <f t="shared" si="4"/>
         <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
-      <c r="K35" s="3" t="str">
+      <c r="K35" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
-      <c r="N35" t="str" cm="1">
-        <f t="array" ref="N35">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K35, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N35" t="str">
+        <f t="array" ref="N35">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
-      <c r="O35" t="s">
-        <v>301</v>
-      </c>
-      <c r="P35" s="3" t="s">
+      <c r="O35" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI35" t="s">
+      <c r="AH35" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>212</v>
       </c>
-      <c r="B36" s="7" t="str">
+      <c r="B36" s="2" t="str">
         <f t="shared" ref="B36" si="16">C36 &amp; IF(D36&lt;&gt;"", "_" &amp; D36, "_") &amp; IF(E36&lt;&gt;"", "_" &amp; E36, "_") &amp; IF(F36&lt;&gt;"", "_" &amp; F36, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
-      <c r="C36" s="9" t="str">
+      <c r="C36" s="2" t="str">
         <f t="shared" ref="C36" si="17">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A36,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D36" s="9" t="str">
+      <c r="D36" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E36" s="9" t="str">
+      <c r="E36" s="2" t="str">
         <f t="shared" ref="E36" si="18">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A36, "("), ")")</f>
         <v>2013</v>
       </c>
@@ -4729,48 +4468,45 @@
         <f t="shared" si="3"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="I36" s="3" t="s">
+      <c r="I36" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="J36" s="3" t="str">
+      <c r="J36" s="1" t="str">
         <f t="shared" ref="J36" si="19">TRIM(_xlfn.TEXTJOIN("_",FALSE,B36,(SUBSTITUTE(SUBSTITUTE(I36," ",""), "_", ""))))</f>
         <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
-      <c r="K36" s="3" t="str">
+      <c r="K36" s="1" t="str">
         <f t="shared" ref="K36" si="20">IF(ISBLANK(H36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H36, SUBSTITUTE(I36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
-      <c r="N36" t="str" cm="1">
-        <f t="array" ref="N36">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K36, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N36" t="str">
+        <f t="array" ref="N36">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
-      <c r="O36" t="s">
-        <v>301</v>
-      </c>
-      <c r="P36" s="3" t="s">
+      <c r="O36" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI36" t="s">
+      <c r="AH36" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>212</v>
       </c>
-      <c r="B37" s="7" t="str">
+      <c r="B37" s="2" t="str">
         <f t="shared" ref="B37" si="21">C37 &amp; IF(D37&lt;&gt;"", "_" &amp; D37, "_") &amp; IF(E37&lt;&gt;"", "_" &amp; E37, "_") &amp; IF(F37&lt;&gt;"", "_" &amp; F37, "")</f>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
-      <c r="C37" s="9" t="str">
+      <c r="C37" s="2" t="str">
         <f t="shared" ref="C37" si="22">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="D37" s="9" t="str">
+      <c r="D37" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E37" s="9" t="str">
+      <c r="E37" s="2" t="str">
         <f t="shared" ref="E37" si="23">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
         <v>2013</v>
       </c>
@@ -4778,48 +4514,45 @@
         <f t="shared" si="3"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="I37" s="3" t="s">
+      <c r="I37" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="J37" s="3" t="str">
+      <c r="J37" s="1" t="str">
         <f t="shared" ref="J37" si="24">TRIM(_xlfn.TEXTJOIN("_",FALSE,B37,(SUBSTITUTE(SUBSTITUTE(I37," ",""), "_", ""))))</f>
         <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
-      <c r="K37" s="3" t="str">
+      <c r="K37" s="1" t="str">
         <f t="shared" ref="K37" si="25">IF(ISBLANK(H37),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H37, SUBSTITUTE(I37,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
-      <c r="N37" t="str" cm="1">
-        <f t="array" ref="N37">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K37, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N37" t="str">
+        <f t="array" ref="N37">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
-      <c r="O37" t="s">
-        <v>301</v>
-      </c>
-      <c r="P37" s="3" t="s">
+      <c r="O37" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI37" t="s">
+      <c r="AH37" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>217</v>
       </c>
-      <c r="B38" s="7" t="str">
+      <c r="B38" s="2" t="str">
         <f t="shared" ref="B38" si="26">C38 &amp; IF(D38&lt;&gt;"", "_" &amp; D38, "_") &amp; IF(E38&lt;&gt;"", "_" &amp; E38, "_") &amp; IF(F38&lt;&gt;"", "_" &amp; F38, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C38" s="9" t="str">
+      <c r="C38" s="2" t="str">
         <f t="shared" ref="C38" si="27">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A38,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D38" s="9" t="str">
+      <c r="D38" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E38" s="9" t="str">
+      <c r="E38" s="2" t="str">
         <f t="shared" ref="E38" si="28">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
         <v>2008</v>
       </c>
@@ -4827,51 +4560,48 @@
         <f t="shared" ref="G38" si="29">_xlfn.TEXTAFTER(A38,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I38" s="3" t="s">
+      <c r="I38" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="J38" s="3" t="str">
+      <c r="J38" s="1" t="str">
         <f t="shared" ref="J38" si="30">TRIM(_xlfn.TEXTJOIN("_",FALSE,B38,(SUBSTITUTE(SUBSTITUTE(I38," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Table2</v>
       </c>
-      <c r="K38" s="3" t="str">
+      <c r="K38" s="1" t="str">
         <f t="shared" ref="K38" si="31">IF(ISBLANK(H38),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H38, SUBSTITUTE(I38,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
-      <c r="N38" t="str" cm="1">
-        <f t="array" ref="N38">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K38, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N38" t="str">
+        <f t="array" ref="N38">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
-      <c r="O38" t="s">
-        <v>300</v>
-      </c>
-      <c r="P38" s="3" t="s">
+      <c r="O38" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI38">
+      <c r="AH38">
         <v>6</v>
       </c>
-      <c r="AK38">
+      <c r="AJ38">
         <v>7</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>217</v>
       </c>
-      <c r="B39" s="7" t="str">
+      <c r="B39" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C39" s="9" t="str">
+      <c r="C39" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Isler</v>
       </c>
-      <c r="D39" s="9" t="str">
+      <c r="D39" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E39" s="9" t="str">
+      <c r="E39" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2008</v>
       </c>
@@ -4879,51 +4609,48 @@
         <f>_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I39" s="3" t="s">
+      <c r="I39" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J39" s="3" t="str">
+      <c r="J39" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Isler_etal_2008_Table7</v>
       </c>
-      <c r="K39" s="3" t="str">
+      <c r="K39" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
       </c>
-      <c r="N39" t="str" cm="1">
-        <f t="array" ref="N39">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K39, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N39" t="str">
+        <f t="array" ref="N39">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
-      <c r="O39" t="s">
-        <v>300</v>
-      </c>
-      <c r="P39" s="3" t="s">
+      <c r="O39" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI39">
+      <c r="AH39">
         <v>3</v>
       </c>
-      <c r="AK39">
+      <c r="AJ39">
         <v>6</v>
       </c>
     </row>
-    <row r="40" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>217</v>
       </c>
-      <c r="B40" s="7" t="str">
+      <c r="B40" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C40" s="9" t="str">
+      <c r="C40" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Isler</v>
       </c>
-      <c r="D40" s="9" t="str">
+      <c r="D40" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E40" s="9" t="str">
+      <c r="E40" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2008</v>
       </c>
@@ -4931,48 +4658,45 @@
         <f>_xlfn.TEXTAFTER(A40,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I40" s="3" t="s">
+      <c r="I40" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J40" s="3" t="str">
+      <c r="J40" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Isler_etal_2008_TableS1</v>
       </c>
-      <c r="K40" s="3" t="str">
+      <c r="K40" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
       </c>
-      <c r="N40" t="str" cm="1">
-        <f t="array" ref="N40">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K40, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N40" t="str">
+        <f t="array" ref="N40">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
-      <c r="O40" t="s">
-        <v>300</v>
-      </c>
-      <c r="P40" s="3" t="s">
+      <c r="O40" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI40" t="s">
+      <c r="AH40" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="41" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>217</v>
       </c>
-      <c r="B41" s="7" t="str">
+      <c r="B41" s="2" t="str">
         <f t="shared" ref="B41" si="32">C41 &amp; IF(D41&lt;&gt;"", "_" &amp; D41, "_") &amp; IF(E41&lt;&gt;"", "_" &amp; E41, "_") &amp; IF(F41&lt;&gt;"", "_" &amp; F41, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C41" s="9" t="str">
+      <c r="C41" s="2" t="str">
         <f t="shared" ref="C41" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A41,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D41" s="9" t="str">
+      <c r="D41" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E41" s="9" t="str">
+      <c r="E41" s="2" t="str">
         <f t="shared" ref="E41" si="34">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A41, "("), ")")</f>
         <v>2008</v>
       </c>
@@ -4980,54 +4704,51 @@
         <f t="shared" ref="G41" si="35">_xlfn.TEXTAFTER(A41,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I41" s="3" t="s">
+      <c r="I41" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="J41" s="3" t="str">
+      <c r="J41" s="1" t="str">
         <f t="shared" ref="J41" si="36">TRIM(_xlfn.TEXTJOIN("_",FALSE,B41,(SUBSTITUTE(SUBSTITUTE(I41," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS2</v>
       </c>
-      <c r="K41" s="3" t="str">
+      <c r="K41" s="1" t="str">
         <f t="shared" ref="K41" si="37">IF(ISBLANK(H41),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H41, SUBSTITUTE(I41,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
-      <c r="N41" t="str" cm="1">
-        <f t="array" ref="N41">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K41, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N41" t="str">
+        <f t="array" ref="N41">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
-      <c r="O41" t="s">
-        <v>300</v>
-      </c>
-      <c r="P41" s="3" t="s">
+      <c r="O41" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI41">
+      <c r="AH41">
         <v>8</v>
       </c>
-      <c r="AK41">
+      <c r="AJ41">
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>217</v>
       </c>
-      <c r="B42" s="7" t="str">
+      <c r="B42" s="2" t="str">
         <f t="shared" ref="B42" si="38">C42 &amp; IF(D42&lt;&gt;"", "_" &amp; D42, "_") &amp; IF(E42&lt;&gt;"", "_" &amp; E42, "_") &amp; IF(F42&lt;&gt;"", "_" &amp; F42, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C42" s="9" t="str">
+      <c r="C42" s="2" t="str">
         <f t="shared" ref="C42" si="39">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A42,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D42" s="9" t="str">
+      <c r="D42" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A42)),
     IF(LEN(A42)-LEN(SUBSTITUTE(A42, ",", ""))&gt;=6, "etal", MID(A42, SEARCH("&amp; ", A42)+2, SEARCH(",", A42, SEARCH("&amp; ", A42)+2) - SEARCH("&amp; ", A42)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E42" s="9" t="str">
+      <c r="E42" s="2" t="str">
         <f t="shared" ref="E42" si="40">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A42, "("), ")")</f>
         <v>2008</v>
       </c>
@@ -5035,98 +4756,92 @@
         <f t="shared" ref="G42" si="41">_xlfn.TEXTAFTER(A42,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I42" s="3" t="s">
+      <c r="I42" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="J42" s="3" t="str">
+      <c r="J42" s="1" t="str">
         <f t="shared" ref="J42" si="42">TRIM(_xlfn.TEXTJOIN("_",FALSE,B42,(SUBSTITUTE(SUBSTITUTE(I42," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS3</v>
       </c>
-      <c r="K42" s="3" t="str">
+      <c r="K42" s="1" t="str">
         <f t="shared" ref="K42" si="43">IF(ISBLANK(H42),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H42, SUBSTITUTE(I42,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
-      <c r="N42" t="str" cm="1">
-        <f t="array" ref="N42">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K42, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N42" t="str">
+        <f t="array" ref="N42">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
-      <c r="O42" t="s">
-        <v>300</v>
-      </c>
-      <c r="P42" s="3" t="s">
+      <c r="O42" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AI42">
+      <c r="AH42">
         <v>7</v>
       </c>
-      <c r="AK42">
+      <c r="AJ42" s="6">
         <v>10</v>
       </c>
     </row>
-    <row r="43" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A43" s="17" t="s">
+    <row r="43" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B43" s="18" t="str">
+      <c r="B43" s="7" t="str">
         <f t="shared" ref="B43" si="44">C43 &amp; IF(D43&lt;&gt;"", "_" &amp; D43, "_") &amp; IF(E43&lt;&gt;"", "_" &amp; E43, "_") &amp; IF(F43&lt;&gt;"", "_" &amp; F43, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="C43" s="19" t="str">
+      <c r="C43" s="7" t="str">
         <f t="shared" ref="C43" si="45">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A43,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="D43" s="9" t="str">
+      <c r="D43" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E43" s="19" t="str">
+      <c r="E43" s="7" t="str">
         <f t="shared" ref="E43" si="46">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A43, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="F43" s="19"/>
-      <c r="G43" s="17" t="str">
+      <c r="F43" s="7"/>
+      <c r="G43" s="6" t="str">
         <f t="shared" ref="G43" si="47">_xlfn.TEXTAFTER(A43,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="I43" s="20" t="s">
+      <c r="I43" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="J43" s="20" t="str">
+      <c r="J43" s="6" t="str">
         <f t="shared" ref="J43" si="48">TRIM(_xlfn.TEXTJOIN("_",FALSE,B43,(SUBSTITUTE(SUBSTITUTE(I43," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_Tree.nex</v>
       </c>
-      <c r="K43" s="21" t="str">
+      <c r="K43" s="8" t="str">
         <f t="shared" ref="K43" si="49">IF(ISBLANK(H43),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H43, SUBSTITUTE(I43,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
-      <c r="N43" t="str" cm="1">
-        <f t="array" ref="N43">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K43, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N43" t="str">
+        <f t="array" ref="N43">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O43" s="17" t="s">
-        <v>300</v>
-      </c>
-      <c r="P43" s="20" t="s">
+      <c r="O43" s="6" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="44" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>223</v>
       </c>
-      <c r="B44" s="7" t="str">
+      <c r="B44" s="2" t="str">
         <f t="shared" si="5"/>
         <v>Lewitus_etal_2014</v>
       </c>
-      <c r="C44" s="9" t="str">
+      <c r="C44" s="2" t="str">
         <f t="shared" si="6"/>
         <v>Lewitus</v>
       </c>
-      <c r="D44" s="9" t="str">
+      <c r="D44" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E44" s="9" t="str">
+      <c r="E44" s="2" t="str">
         <f t="shared" si="7"/>
         <v>2014</v>
       </c>
@@ -5134,57 +4849,54 @@
         <f>_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
-      <c r="I44" s="3" t="s">
+      <c r="I44" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="J44" s="3" t="str">
+      <c r="J44" s="1" t="str">
         <f t="shared" si="4"/>
         <v>Lewitus_etal_2014_TableS1</v>
       </c>
-      <c r="K44" s="3" t="str">
+      <c r="K44" s="1" t="str">
         <f t="shared" si="8"/>
         <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
-      <c r="N44" t="str" cm="1">
-        <f t="array" ref="N44">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K44, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N44" t="str">
+        <f t="array" ref="N44">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K44, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
-      <c r="O44" t="s">
-        <v>299</v>
-      </c>
-      <c r="P44" s="3" t="s">
+      <c r="O44" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X44" t="s">
+      <c r="W44" t="s">
         <v>269</v>
       </c>
-      <c r="AA44" t="s">
+      <c r="Z44" t="s">
         <v>270</v>
       </c>
-      <c r="AI44">
+      <c r="AH44">
         <v>9</v>
       </c>
-      <c r="AK44">
+      <c r="AJ44">
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:37" ht="16" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>223</v>
       </c>
-      <c r="B45" s="7" t="str">
+      <c r="B45" s="2" t="str">
         <f t="shared" ref="B45" si="50">C45 &amp; IF(D45&lt;&gt;"", "_" &amp; D45, "_") &amp; IF(E45&lt;&gt;"", "_" &amp; E45, "_") &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "")</f>
         <v>Lewitus_etal_2014</v>
       </c>
-      <c r="C45" s="9" t="str">
+      <c r="C45" s="2" t="str">
         <f t="shared" ref="C45" si="51">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
-      <c r="D45" s="9" t="str">
+      <c r="D45" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E45" s="9" t="str">
+      <c r="E45" s="2" t="str">
         <f t="shared" ref="E45" si="52">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
         <v>2014</v>
       </c>
@@ -5192,623 +4904,780 @@
         <f>_xlfn.TEXTAFTER(A45,"https://doi.org/")</f>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
-      <c r="I45" s="3" t="s">
+      <c r="I45" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="J45" s="3" t="str">
+      <c r="J45" s="1" t="str">
         <f t="shared" ref="J45" si="53">TRIM(_xlfn.TEXTJOIN("_",FALSE,B45,(SUBSTITUTE(SUBSTITUTE(I45," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2014_TableS8</v>
       </c>
-      <c r="K45" s="3" t="str">
+      <c r="K45" s="1" t="str">
         <f t="shared" ref="K45" si="54">IF(ISBLANK(H45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(I45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
-      <c r="N45" t="str" cm="1">
-        <f t="array" ref="N45">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K45, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N45" t="str">
+        <f t="array" ref="N45">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K45, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
-      <c r="O45" t="s">
-        <v>299</v>
-      </c>
-      <c r="P45" s="3" t="s">
+      <c r="O45" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X45" t="s">
+      <c r="W45" t="s">
         <v>225</v>
       </c>
-      <c r="AA45" t="s">
+      <c r="Z45" t="s">
         <v>270</v>
       </c>
-      <c r="AI45">
+      <c r="AH45">
         <v>6</v>
       </c>
-      <c r="AK45">
+      <c r="AJ45" s="6">
         <v>13</v>
       </c>
     </row>
-    <row r="46" spans="1:37" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.2">
-      <c r="A46" s="17" t="s">
+    <row r="46" spans="1:36" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="B46" s="18" t="str">
+      <c r="B46" s="7" t="str">
         <f t="shared" ref="B46" si="55">C46 &amp; IF(D46&lt;&gt;"", "_" &amp; D46, "_") &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "")</f>
         <v>Lewitus_etal_2013</v>
       </c>
-      <c r="C46" s="19" t="str">
+      <c r="C46" s="7" t="str">
         <f t="shared" ref="C46" si="56">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
-      <c r="D46" s="9" t="str">
+      <c r="D46" s="2" t="str">
         <f>IF(ISNUMBER(FIND("&amp;", A46)),
     IF(LEN(A46)-LEN(SUBSTITUTE(A46, ",", ""))&gt;=6, "etal", MID(A46, SEARCH("&amp; ", A46)+2, SEARCH(",", A46, SEARCH("&amp; ", A46)+2) - SEARCH("&amp; ", A46)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E46" s="19" t="str">
+      <c r="E46" s="7" t="str">
         <f t="shared" ref="E46" si="57">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
         <v>2013</v>
       </c>
-      <c r="F46" s="19"/>
-      <c r="G46" s="17" t="str">
+      <c r="F46" s="7"/>
+      <c r="G46" s="6" t="str">
         <f>_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
         <v>10.3389/fnhum.2013.00424</v>
       </c>
-      <c r="I46" s="20" t="s">
+      <c r="I46" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="J46" s="20" t="str">
+      <c r="J46" s="6" t="str">
         <f t="shared" ref="J46" si="58">TRIM(_xlfn.TEXTJOIN("_",FALSE,B46,(SUBSTITUTE(SUBSTITUTE(I46," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
-      <c r="K46" s="21" t="str">
+      <c r="K46" s="8" t="str">
         <f>IF(ISBLANK(H46),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H46, SUBSTITUTE(I46,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
-      <c r="N46" t="str" cm="1">
-        <f t="array" ref="N46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K46, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N46" t="str">
+        <f t="array" ref="N46">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
-      <c r="O46" s="17" t="str" cm="1">
-        <f t="array" ref="O46">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(_xlfn.TEXTBEFORE(K46, "_"), _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, "_"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
-      </c>
-      <c r="P46" s="20" t="s">
+      <c r="O46" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="AA46" s="17" t="s">
+      <c r="Z46" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="AI46" s="17">
+      <c r="AH46" s="6">
         <v>7</v>
       </c>
-      <c r="AK46" s="17">
+      <c r="AJ46" s="6">
         <v>14</v>
       </c>
     </row>
-    <row r="47" spans="1:37" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="15" t="s">
+    <row r="47" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B47" s="22" t="str">
+      <c r="B47" s="9" t="str">
         <f t="shared" ref="B47" si="59">C47 &amp; IF(D47&lt;&gt;"", "_" &amp; D47, "_") &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
-      <c r="C47" s="24" t="str">
+      <c r="C47" s="9" t="str">
         <f t="shared" ref="C47" si="60">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
-      <c r="D47" s="9" t="str">
+      <c r="D47" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E47" s="24" t="str">
+      <c r="E47" s="9" t="str">
         <f t="shared" ref="E47" si="61">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
         <v>2011</v>
       </c>
-      <c r="F47" s="24"/>
+      <c r="F47" s="9"/>
       <c r="G47" t="str">
         <f>_xlfn.TEXTAFTER(A47,"https://doi.org/")</f>
         <v>10.1159/000323671</v>
       </c>
-      <c r="I47" s="15" t="s">
+      <c r="I47" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="J47" s="23" t="str">
+      <c r="J47" s="5" t="str">
         <f t="shared" ref="J47" si="62">TRIM(_xlfn.TEXTJOIN("_",FALSE,B47,(SUBSTITUTE(SUBSTITUTE(I47," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
-      <c r="K47" s="23" t="str">
+      <c r="K47" s="5" t="str">
         <f>IF(ISBLANK(H47),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H47, SUBSTITUTE(I47,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
-      <c r="N47" t="str" cm="1">
-        <f t="array" ref="N47">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K47, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N47" t="str">
+        <f t="array" ref="N47">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
-      <c r="O47" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="P47" s="23" t="s">
+      <c r="O47" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AI47" s="15" t="s">
+      <c r="AH47" s="5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="48" spans="1:37" s="15" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="15" t="s">
+    <row r="48" spans="1:36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="B48" s="22" t="str">
+      <c r="B48" s="9" t="str">
         <f t="shared" ref="B48" si="63">C48 &amp; IF(D48&lt;&gt;"", "_" &amp; D48, "_") &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
-      <c r="C48" s="24" t="str">
+      <c r="C48" s="9" t="str">
         <f t="shared" ref="C48" si="64">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
-      <c r="D48" s="9" t="str">
+      <c r="D48" s="2" t="str">
         <f t="shared" si="1"/>
         <v>etal</v>
       </c>
-      <c r="E48" s="24" t="str">
+      <c r="E48" s="9" t="str">
         <f t="shared" ref="E48" si="65">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
         <v>2011</v>
       </c>
-      <c r="F48" s="24"/>
+      <c r="F48" s="9"/>
       <c r="G48" t="str">
-        <f t="shared" ref="G48:G52" si="66">_xlfn.TEXTAFTER(A48,"https://doi.org/")</f>
+        <f t="shared" ref="G48:G53" si="66">_xlfn.TEXTAFTER(A48,"https://doi.org/")</f>
         <v>10.1159/000323671</v>
       </c>
-      <c r="I48" s="15" t="s">
+      <c r="I48" s="5" t="s">
         <v>231</v>
       </c>
-      <c r="J48" s="23" t="str">
+      <c r="J48" s="5" t="str">
         <f t="shared" ref="J48" si="67">TRIM(_xlfn.TEXTJOIN("_",FALSE,B48,(SUBSTITUTE(SUBSTITUTE(I48," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
-      <c r="K48" s="23" t="str">
+      <c r="K48" s="5" t="str">
         <f>IF(ISBLANK(H48),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H48, SUBSTITUTE(I48,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
-      <c r="N48" t="str" cm="1">
-        <f t="array" ref="N48">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K48, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N48" t="str">
+        <f t="array" ref="N48">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
       </c>
-      <c r="O48" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="P48" s="23" t="s">
+      <c r="O48" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="AI48" s="15" t="s">
+      <c r="AH48" s="5" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>271</v>
       </c>
-      <c r="B49" s="22" t="str">
-        <f t="shared" ref="B49:B52" si="68">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
+      <c r="B49" s="9" t="str">
+        <f t="shared" ref="B49:B53" si="68">C49 &amp; IF(D49&lt;&gt;"", "_" &amp; D49, "_") &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "")</f>
         <v>Iwaniuk_etal_1999</v>
       </c>
-      <c r="C49" s="24" t="str">
-        <f t="shared" ref="C49:C52" si="69">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
+      <c r="C49" s="9" t="str">
+        <f t="shared" ref="C49:C53" si="69">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
         <v>Iwaniuk</v>
       </c>
-      <c r="D49" s="9" t="str">
-        <f t="shared" ref="D49:D52" si="70">IF(ISNUMBER(FIND("&amp;", A49)),
+      <c r="D49" s="2" t="str">
+        <f t="shared" ref="D49:D53" si="70">IF(ISNUMBER(FIND("&amp;", A49)),
     IF(LEN(A49)-LEN(SUBSTITUTE(A49, ",", ""))&gt;=6, "etal", MID(A49, SEARCH("&amp; ", A49)+2, SEARCH(",", A49, SEARCH("&amp; ", A49)+2) - SEARCH("&amp; ", A49)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E49" s="24" t="str">
-        <f t="shared" ref="E49:E51" si="71">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
+      <c r="E49" s="9" t="str">
+        <f t="shared" ref="E49:E52" si="71">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
         <v>1999</v>
       </c>
-      <c r="F49" s="24"/>
+      <c r="F49" s="9"/>
       <c r="G49" t="str">
         <f t="shared" si="66"/>
         <v xml:space="preserve">10.1016/s0166-4328(98)00151-x 	</v>
       </c>
-      <c r="H49" s="15"/>
-      <c r="I49" s="3" t="s">
+      <c r="H49" s="5"/>
+      <c r="I49" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J49" s="23" t="str">
-        <f t="shared" ref="J49:J51" si="72">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
+      <c r="J49" s="5" t="str">
+        <f t="shared" ref="J49:J52" si="72">TRIM(_xlfn.TEXTJOIN("_",FALSE,B49,(SUBSTITUTE(SUBSTITUTE(I49," ",""), "_", ""))))</f>
         <v>Iwaniuk_etal_1999_Table1</v>
       </c>
-      <c r="K49" s="23" t="str">
+      <c r="K49" s="5" t="str">
         <f>IF(ISBLANK(H49),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H49, SUBSTITUTE(I49,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fs0166-4328(98)00151-x	_Table1</v>
       </c>
-      <c r="M49" s="15" t="s">
+      <c r="M49" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N49" t="str" cm="1">
-        <f t="array" ref="N49">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K49, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N49" t="str">
+        <f t="array" ref="N49">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O49" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="V49" t="s">
+      <c r="T49" t="s">
+        <v>46</v>
+      </c>
+      <c r="U49" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="50" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="W49" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="50" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
-        <v>272</v>
-      </c>
-      <c r="B50" s="22" t="str">
-        <f t="shared" si="68"/>
-        <v>Genoud_etal_2018</v>
-      </c>
-      <c r="C50" s="24" t="str">
-        <f t="shared" si="69"/>
-        <v>Genoud</v>
-      </c>
-      <c r="D50" s="9" t="str">
-        <f t="shared" si="70"/>
-        <v>etal</v>
-      </c>
-      <c r="E50" s="24" t="str">
-        <f t="shared" si="71"/>
-        <v>2018</v>
-      </c>
-      <c r="F50" s="24"/>
-      <c r="G50" t="str">
-        <f t="shared" si="66"/>
-        <v xml:space="preserve">10.1111/brv.12350 	</v>
-      </c>
-      <c r="H50" s="15"/>
-      <c r="I50" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J50" s="23" t="str">
-        <f t="shared" si="72"/>
-        <v>Genoud_etal_2018_TableS2</v>
-      </c>
-      <c r="K50" s="23" t="str">
-        <f t="shared" ref="K50:K51" si="73">IF(ISBLANK(H50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1111%2Fbrv.12350	_TableS2</v>
-      </c>
-      <c r="M50" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="N50" t="str" cm="1">
-        <f t="array" ref="N50">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K50, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="O50" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="X50" t="s">
-        <v>276</v>
-      </c>
-      <c r="AC50" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" t="s">
-        <v>273</v>
-      </c>
-      <c r="B51" s="22" t="str">
-        <f t="shared" si="68"/>
-        <v>Mota_etal_2019</v>
-      </c>
-      <c r="C51" s="24" t="str">
-        <f t="shared" si="69"/>
-        <v>Mota</v>
-      </c>
-      <c r="D51" s="9" t="str">
-        <f t="shared" si="70"/>
-        <v>etal</v>
-      </c>
-      <c r="E51" s="24" t="str">
-        <f t="shared" si="71"/>
-        <v>2019</v>
-      </c>
-      <c r="F51" s="24"/>
-      <c r="G51" t="str">
-        <f t="shared" si="66"/>
-        <v xml:space="preserve">10.1073/pnas.1716956116 	</v>
-      </c>
-      <c r="H51" s="15"/>
-      <c r="I51" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J51" s="23" t="str">
-        <f t="shared" si="72"/>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
-      </c>
-      <c r="K51" s="23" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1073%2Fpnas.1716956116	_SupplementaryTableS1</v>
-      </c>
-      <c r="M51" s="15" t="s">
-        <v>125</v>
-      </c>
-      <c r="N51" t="str" cm="1">
-        <f t="array" ref="N51">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K51, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="O51" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="X51" t="s">
-        <v>274</v>
-      </c>
-      <c r="AC51" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" t="s">
-        <v>277</v>
-      </c>
-      <c r="B52" s="22" t="str">
-        <f t="shared" si="68"/>
-        <v>Burish_etal_2010</v>
-      </c>
-      <c r="C52" s="24" t="str">
-        <f t="shared" si="69"/>
-        <v>Burish</v>
-      </c>
-      <c r="D52" s="9" t="str">
-        <f t="shared" si="70"/>
-        <v>etal</v>
-      </c>
-      <c r="E52" s="24" t="str">
-        <f t="shared" ref="E52" si="74">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A52, "("), ")")</f>
-        <v>2010</v>
-      </c>
-      <c r="F52" s="24"/>
-      <c r="G52" t="str">
-        <f t="shared" si="66"/>
-        <v xml:space="preserve">10.1159/000319019 </v>
-      </c>
-      <c r="H52" s="15"/>
-      <c r="I52" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J52" s="23" t="str">
-        <f t="shared" ref="J52" si="75">TRIM(_xlfn.TEXTJOIN("_",FALSE,B52,(SUBSTITUTE(SUBSTITUTE(I52," ",""), "_", ""))))</f>
-        <v>Burish_etal_2010_Table1</v>
-      </c>
-      <c r="K52" s="23" t="str">
-        <f t="shared" ref="K52" si="76">IF(ISBLANK(H52),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G52, SUBSTITUTE(I52,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H52, SUBSTITUTE(I52,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1159%2F000319019_Table1</v>
-      </c>
-      <c r="M52" t="s">
-        <v>41</v>
-      </c>
-      <c r="N52" t="str" cm="1">
-        <f t="array" ref="N52">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K52, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_Table1.tsv</v>
-      </c>
-      <c r="O52" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="P52" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>291</v>
-      </c>
-      <c r="X52" t="s">
-        <v>278</v>
-      </c>
-      <c r="Z52" t="s">
-        <v>281</v>
-      </c>
-      <c r="AC52" t="s">
-        <v>285</v>
-      </c>
-      <c r="AE52" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" t="s">
-        <v>277</v>
-      </c>
-      <c r="B53" s="22" t="str">
-        <f t="shared" ref="B53:B55" si="77">C53 &amp; IF(D53&lt;&gt;"", "_" &amp; D53, "_") &amp; IF(E53&lt;&gt;"", "_" &amp; E53, "_") &amp; IF(F53&lt;&gt;"", "_" &amp; F53, "")</f>
-        <v>Burish_etal_2010</v>
-      </c>
-      <c r="C53" s="24" t="str">
-        <f t="shared" ref="C53:C55" si="78">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A53,","), "-", ""), " ", "")</f>
-        <v>Burish</v>
-      </c>
-      <c r="D53" s="9" t="str">
-        <f t="shared" ref="D53:D55" si="79">IF(ISNUMBER(FIND("&amp;", A53)),
-    IF(LEN(A53)-LEN(SUBSTITUTE(A53, ",", ""))&gt;=6, "etal", MID(A53, SEARCH("&amp; ", A53)+2, SEARCH(",", A53, SEARCH("&amp; ", A53)+2) - SEARCH("&amp; ", A53)-2)),
+        <v>271</v>
+      </c>
+      <c r="B50" s="9" t="str">
+        <f t="shared" ref="B50" si="73">C50 &amp; IF(D50&lt;&gt;"", "_" &amp; D50, "_") &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "")</f>
+        <v>Iwaniuk_etal_1999</v>
+      </c>
+      <c r="C50" s="9" t="str">
+        <f t="shared" ref="C50" si="74">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
+        <v>Iwaniuk</v>
+      </c>
+      <c r="D50" s="2" t="str">
+        <f t="shared" ref="D50" si="75">IF(ISNUMBER(FIND("&amp;", A50)),
+    IF(LEN(A50)-LEN(SUBSTITUTE(A50, ",", ""))&gt;=6, "etal", MID(A50, SEARCH("&amp; ", A50)+2, SEARCH(",", A50, SEARCH("&amp; ", A50)+2) - SEARCH("&amp; ", A50)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="E53" s="24" t="str">
-        <f t="shared" ref="E53:E55" si="80">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
+      <c r="E50" s="9" t="str">
+        <f t="shared" ref="E50" si="76">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
+        <v>1999</v>
+      </c>
+      <c r="F50" s="9"/>
+      <c r="G50" t="str">
+        <f t="shared" ref="G50" si="77">_xlfn.TEXTAFTER(A50,"https://doi.org/")</f>
+        <v xml:space="preserve">10.1016/s0166-4328(98)00151-x 	</v>
+      </c>
+      <c r="H50" s="5"/>
+      <c r="I50" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="J50" s="5" t="str">
+        <f t="shared" ref="J50" si="78">TRIM(_xlfn.TEXTJOIN("_",FALSE,B50,(SUBSTITUTE(SUBSTITUTE(I50," ",""), "_", ""))))</f>
+        <v>Iwaniuk_etal_1999_References</v>
+      </c>
+      <c r="K50" s="5" t="str">
+        <f>IF(ISBLANK(H50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H50, SUBSTITUTE(I50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fs0166-4328(98)00151-x	_References</v>
+      </c>
+      <c r="M50" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N50" t="str">
+        <f t="array" ref="N50">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="T50" t="s">
+        <v>351</v>
+      </c>
+      <c r="U50" t="s">
+        <v>78</v>
+      </c>
+      <c r="W50" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="51" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A51" t="s">
+        <v>272</v>
+      </c>
+      <c r="B51" s="9" t="str">
+        <f t="shared" si="68"/>
+        <v>Genoud_etal_2018</v>
+      </c>
+      <c r="C51" s="9" t="str">
+        <f t="shared" si="69"/>
+        <v>Genoud</v>
+      </c>
+      <c r="D51" s="2" t="str">
+        <f t="shared" si="70"/>
+        <v>etal</v>
+      </c>
+      <c r="E51" s="9" t="str">
+        <f t="shared" si="71"/>
+        <v>2018</v>
+      </c>
+      <c r="F51" s="9"/>
+      <c r="G51" t="str">
+        <f t="shared" si="66"/>
+        <v xml:space="preserve">10.1111/brv.12350 	</v>
+      </c>
+      <c r="H51" s="5"/>
+      <c r="I51" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="J51" s="5" t="str">
+        <f t="shared" si="72"/>
+        <v>Genoud_etal_2018_TableS2</v>
+      </c>
+      <c r="K51" s="5" t="str">
+        <f t="shared" ref="K51:K52" si="79">IF(ISBLANK(H51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(I51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1111%2Fbrv.12350	_TableS2</v>
+      </c>
+      <c r="M51" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N51" t="str">
+        <f t="array" ref="N51">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K51, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="W51" t="s">
+        <v>276</v>
+      </c>
+      <c r="AB51" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="52" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>273</v>
+      </c>
+      <c r="B52" s="9" t="str">
+        <f t="shared" si="68"/>
+        <v>Mota_etal_2019</v>
+      </c>
+      <c r="C52" s="9" t="str">
+        <f t="shared" si="69"/>
+        <v>Mota</v>
+      </c>
+      <c r="D52" s="2" t="str">
+        <f t="shared" si="70"/>
+        <v>etal</v>
+      </c>
+      <c r="E52" s="9" t="str">
+        <f t="shared" si="71"/>
+        <v>2019</v>
+      </c>
+      <c r="F52" s="9"/>
+      <c r="G52" t="str">
+        <f t="shared" si="66"/>
+        <v xml:space="preserve">10.1073/pnas.1716956116 	</v>
+      </c>
+      <c r="H52" s="5"/>
+      <c r="I52" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J52" s="5" t="str">
+        <f t="shared" si="72"/>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
+      </c>
+      <c r="K52" s="5" t="str">
+        <f t="shared" si="79"/>
+        <v>10.1073%2Fpnas.1716956116	_SupplementaryTableS1</v>
+      </c>
+      <c r="M52" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N52" t="str">
+        <f t="array" ref="N52">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K52, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="W52" t="s">
+        <v>274</v>
+      </c>
+      <c r="AB52" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="53" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>277</v>
+      </c>
+      <c r="B53" s="9" t="str">
+        <f t="shared" si="68"/>
+        <v>Burish_etal_2010</v>
+      </c>
+      <c r="C53" s="9" t="str">
+        <f t="shared" si="69"/>
+        <v>Burish</v>
+      </c>
+      <c r="D53" s="2" t="str">
+        <f t="shared" si="70"/>
+        <v>etal</v>
+      </c>
+      <c r="E53" s="9" t="str">
+        <f t="shared" ref="E53" si="80">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
         <v>2010</v>
       </c>
-      <c r="F53" s="24"/>
+      <c r="F53" s="9"/>
       <c r="G53" t="str">
-        <f t="shared" ref="G53:G55" si="81">_xlfn.TEXTAFTER(A53,"https://doi.org/")</f>
+        <f t="shared" si="66"/>
         <v xml:space="preserve">10.1159/000319019 </v>
       </c>
-      <c r="H53" s="15"/>
-      <c r="I53" s="3" t="s">
+      <c r="H53" s="5"/>
+      <c r="I53" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J53" s="5" t="str">
+        <f t="shared" ref="J53" si="81">TRIM(_xlfn.TEXTJOIN("_",FALSE,B53,(SUBSTITUTE(SUBSTITUTE(I53," ",""), "_", ""))))</f>
+        <v>Burish_etal_2010_Table1</v>
+      </c>
+      <c r="K53" s="5" t="str">
+        <f t="shared" ref="K53" si="82">IF(ISBLANK(H53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1159%2F000319019_Table1</v>
+      </c>
+      <c r="M53" t="s">
+        <v>41</v>
+      </c>
+      <c r="N53" t="str">
+        <f t="array" ref="N53">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K53, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000319019_Table1.tsv</v>
+      </c>
+      <c r="O53" t="s">
+        <v>53</v>
+      </c>
+      <c r="P53" t="s">
+        <v>291</v>
+      </c>
+      <c r="W53" t="s">
+        <v>278</v>
+      </c>
+      <c r="Y53" t="s">
+        <v>281</v>
+      </c>
+      <c r="AB53" t="s">
+        <v>285</v>
+      </c>
+      <c r="AD53" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A54" t="s">
+        <v>277</v>
+      </c>
+      <c r="B54" s="9" t="str">
+        <f t="shared" ref="B54:B59" si="83">C54 &amp; IF(D54&lt;&gt;"", "_" &amp; D54, "_") &amp; IF(E54&lt;&gt;"", "_" &amp; E54, "_") &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "")</f>
+        <v>Burish_etal_2010</v>
+      </c>
+      <c r="C54" s="9" t="str">
+        <f t="shared" ref="C54:C59" si="84">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
+        <v>Burish</v>
+      </c>
+      <c r="D54" s="2" t="str">
+        <f t="shared" ref="D54:D59" si="85">IF(ISNUMBER(FIND("&amp;", A54)),
+    IF(LEN(A54)-LEN(SUBSTITUTE(A54, ",", ""))&gt;=6, "etal", MID(A54, SEARCH("&amp; ", A54)+2, SEARCH(",", A54, SEARCH("&amp; ", A54)+2) - SEARCH("&amp; ", A54)-2)),
+    ""
+)</f>
+        <v>etal</v>
+      </c>
+      <c r="E54" s="9" t="str">
+        <f t="shared" ref="E54:E59" si="86">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
+        <v>2010</v>
+      </c>
+      <c r="F54" s="9"/>
+      <c r="G54" t="str">
+        <f t="shared" ref="G54:G59" si="87">_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
+        <v xml:space="preserve">10.1159/000319019 </v>
+      </c>
+      <c r="H54" s="5"/>
+      <c r="I54" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="J53" s="23" t="str">
-        <f t="shared" ref="J53:J54" si="82">TRIM(_xlfn.TEXTJOIN("_",FALSE,B53,(SUBSTITUTE(SUBSTITUTE(I53," ",""), "_", ""))))</f>
+      <c r="J54" s="5" t="str">
+        <f t="shared" ref="J54:J55" si="88">TRIM(_xlfn.TEXTJOIN("_",FALSE,B54,(SUBSTITUTE(SUBSTITUTE(I54," ",""), "_", ""))))</f>
         <v>Burish_etal_2010_SupplementaryTable1</v>
       </c>
-      <c r="K53" s="23" t="str">
-        <f t="shared" ref="K53:K54" si="83">IF(ISBLANK(H53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(I53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="K54" s="5" t="str">
+        <f t="shared" ref="K54:K55" si="89">IF(ISBLANK(H54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G54, SUBSTITUTE(I54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H54, SUBSTITUTE(I54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
-      <c r="M53" s="15" t="s">
+      <c r="M54" s="5" t="s">
         <v>290</v>
       </c>
-      <c r="N53" t="str" cm="1">
-        <f t="array" ref="N53">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K53, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N54" t="str">
+        <f t="array" ref="N54">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K54, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
-      <c r="O53" s="15" t="s">
-        <v>298</v>
-      </c>
-      <c r="Q53" t="s">
+      <c r="P54" t="s">
         <v>292</v>
       </c>
-      <c r="X53" t="s">
+      <c r="W54" t="s">
         <v>279</v>
       </c>
-      <c r="Z53" t="s">
+      <c r="Y54" t="s">
         <v>282</v>
       </c>
-      <c r="AC53" t="s">
+      <c r="AB54" t="s">
         <v>285</v>
       </c>
-      <c r="AE53" t="s">
+      <c r="AD54" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" t="s">
+    <row r="55" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A55" t="s">
         <v>287</v>
       </c>
-      <c r="B54" s="22" t="str">
-        <f t="shared" si="77"/>
+      <c r="B55" s="9" t="str">
+        <f t="shared" si="83"/>
         <v>Fu_etal_2013</v>
       </c>
-      <c r="C54" s="24" t="str">
-        <f t="shared" si="78"/>
+      <c r="C55" s="9" t="str">
+        <f t="shared" si="84"/>
         <v>Fu</v>
       </c>
-      <c r="D54" s="9" t="str">
-        <f t="shared" si="79"/>
+      <c r="D55" s="2" t="str">
+        <f t="shared" si="85"/>
         <v>etal</v>
       </c>
-      <c r="E54" s="24" t="str">
-        <f t="shared" si="80"/>
+      <c r="E55" s="9" t="str">
+        <f t="shared" si="86"/>
         <v>2013</v>
       </c>
-      <c r="G54" t="str">
-        <f t="shared" si="81"/>
+      <c r="G55" t="str">
+        <f t="shared" si="87"/>
         <v xml:space="preserve">10.1007/s00429-012-0462-x 	</v>
       </c>
-      <c r="I54" s="3" t="s">
+      <c r="I55" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="J54" s="23" t="str">
-        <f t="shared" si="82"/>
+      <c r="J55" s="5" t="str">
+        <f t="shared" si="88"/>
         <v>Fu_etal_2013_Table1</v>
       </c>
-      <c r="K54" s="23" t="str">
+      <c r="K55" s="5" t="str">
+        <f t="shared" si="89"/>
+        <v>10.1007%2Fs00429-012-0462-x	_Table1</v>
+      </c>
+      <c r="M55" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N55" t="str">
+        <f t="array" ref="N55">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K55, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="W55" t="s">
+        <v>289</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>288</v>
+      </c>
+      <c r="AB55" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>293</v>
+      </c>
+      <c r="B56" s="9" t="str">
         <f t="shared" si="83"/>
-        <v>10.1007%2Fs00429-012-0462-x	_Table1</v>
-      </c>
-      <c r="M54" s="15" t="s">
+        <v>MacLarnon__1996</v>
+      </c>
+      <c r="C56" s="9" t="str">
+        <f t="shared" si="84"/>
+        <v>MacLarnon</v>
+      </c>
+      <c r="D56" s="2" t="str">
+        <f t="shared" si="85"/>
+        <v/>
+      </c>
+      <c r="E56" s="9" t="str">
+        <f t="shared" si="86"/>
+        <v>1996</v>
+      </c>
+      <c r="G56" t="str">
+        <f t="shared" si="87"/>
+        <v xml:space="preserve">10.1006/jhev.1996.0005 	</v>
+      </c>
+      <c r="I56" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="J56" s="5" t="str">
+        <f t="shared" ref="J56:J59" si="90">TRIM(_xlfn.TEXTJOIN("_",FALSE,B56,(SUBSTITUTE(SUBSTITUTE(I56," ",""), "_", ""))))</f>
+        <v>MacLarnon__1996_Table1</v>
+      </c>
+      <c r="K56" s="5" t="str">
+        <f t="shared" ref="K56:K59" si="91">IF(ISBLANK(H56),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G56, SUBSTITUTE(I56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H56, SUBSTITUTE(I56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1006%2Fjhev.1996.0005	_Table1</v>
+      </c>
+      <c r="M56" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N54" t="str" cm="1">
-        <f t="array" ref="N54">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K54, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N56" t="str">
+        <f t="array" ref="N56">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K56, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O54" s="15" t="s">
+      <c r="W56" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
         <v>297</v>
       </c>
-      <c r="X54" t="s">
-        <v>289</v>
-      </c>
-      <c r="Z54" t="s">
-        <v>288</v>
-      </c>
-      <c r="AC54" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" t="s">
-        <v>293</v>
-      </c>
-      <c r="B55" s="22" t="str">
-        <f t="shared" si="77"/>
-        <v>MacLarnon__1996</v>
-      </c>
-      <c r="C55" s="24" t="str">
-        <f t="shared" si="78"/>
-        <v>MacLarnon</v>
-      </c>
-      <c r="D55" s="9" t="str">
-        <f t="shared" si="79"/>
+      <c r="B57" s="9" t="str">
+        <f t="shared" si="83"/>
+        <v>Wimberly_etal_2021</v>
+      </c>
+      <c r="C57" s="9" t="str">
+        <f t="shared" si="84"/>
+        <v>Wimberly</v>
+      </c>
+      <c r="D57" s="2" t="str">
+        <f t="shared" si="85"/>
+        <v>etal</v>
+      </c>
+      <c r="E57" s="9" t="str">
+        <f t="shared" si="86"/>
+        <v>2021</v>
+      </c>
+      <c r="G57" t="str">
+        <f t="shared" si="87"/>
+        <v xml:space="preserve">10.1098/rspb.2021.0937 	</v>
+      </c>
+      <c r="I57" t="s">
+        <v>346</v>
+      </c>
+      <c r="J57" s="5" t="str">
+        <f t="shared" si="90"/>
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
+      </c>
+      <c r="K57" s="5" t="str">
+        <f t="shared" si="91"/>
+        <v>10.1098%2Frspb.2021.0937	_mammalgait.txt</v>
+      </c>
+      <c r="M57" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="N57" t="str">
+        <f t="array" ref="N57">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K57, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>345</v>
+      </c>
+      <c r="B58" s="9" t="str">
+        <f t="shared" si="83"/>
+        <v>Granatosky__2018</v>
+      </c>
+      <c r="C58" s="9" t="str">
+        <f t="shared" si="84"/>
+        <v>Granatosky</v>
+      </c>
+      <c r="D58" s="2" t="str">
+        <f t="shared" si="85"/>
         <v/>
       </c>
-      <c r="E55" s="24" t="str">
-        <f t="shared" si="80"/>
-        <v>1996</v>
-      </c>
-      <c r="G55" t="str">
-        <f t="shared" si="81"/>
-        <v xml:space="preserve">10.1006/jhev.1996.0005 	</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="J55" s="23" t="str">
-        <f t="shared" ref="J55" si="84">TRIM(_xlfn.TEXTJOIN("_",FALSE,B55,(SUBSTITUTE(SUBSTITUTE(I55," ",""), "_", ""))))</f>
-        <v>MacLarnon__1996_Table1</v>
-      </c>
-      <c r="K55" s="23" t="str">
-        <f t="shared" ref="K55" si="85">IF(ISBLANK(H55),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, G55, SUBSTITUTE(I55,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H55, SUBSTITUTE(I55,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1006%2Fjhev.1996.0005	_Table1</v>
-      </c>
-      <c r="M55" s="15" t="s">
+      <c r="E58" s="9" t="str">
+        <f t="shared" si="86"/>
+        <v>2018</v>
+      </c>
+      <c r="G58" t="str">
+        <f t="shared" si="87"/>
+        <v xml:space="preserve">10.1111/jzo.12608 	</v>
+      </c>
+      <c r="I58" t="s">
+        <v>91</v>
+      </c>
+      <c r="J58" s="5" t="str">
+        <f t="shared" si="90"/>
+        <v>Granatosky__2018_TableS1</v>
+      </c>
+      <c r="K58" s="5" t="str">
+        <f t="shared" si="91"/>
+        <v>10.1111%2Fjzo.12608	_TableS1</v>
+      </c>
+      <c r="M58" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="N55" t="str" cm="1">
-        <f t="array" ref="N55">IFERROR(INDEX([1]FileList!$A$1:$A$43, MATCH(K55, _xlfn.TEXTBEFORE([1]FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="N58" t="str">
+        <f t="array" ref="N58">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K58, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O55" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="X55" t="s">
-        <v>294</v>
+      <c r="W58" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>347</v>
+      </c>
+      <c r="B59" s="9" t="str">
+        <f t="shared" si="83"/>
+        <v>Wilman_etal_2014</v>
+      </c>
+      <c r="C59" s="9" t="str">
+        <f t="shared" si="84"/>
+        <v>Wilman</v>
+      </c>
+      <c r="D59" s="2" t="str">
+        <f t="shared" si="85"/>
+        <v>etal</v>
+      </c>
+      <c r="E59" s="9" t="str">
+        <f t="shared" si="86"/>
+        <v>2014</v>
+      </c>
+      <c r="G59" t="str">
+        <f t="shared" si="87"/>
+        <v xml:space="preserve">10.1890/13-1917.1 	</v>
+      </c>
+      <c r="I59" t="s">
+        <v>348</v>
+      </c>
+      <c r="J59" s="5" t="str">
+        <f t="shared" si="90"/>
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+      </c>
+      <c r="K59" s="5" t="str">
+        <f t="shared" si="91"/>
+        <v>10.1890%2F13-1917.1	_MamFuncDat.txt</v>
+      </c>
+      <c r="N59" t="str">
+        <f t="array" ref="N59">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(K59, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="W3" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{E0793C32-CFF3-BA46-91D5-CE57A5CB5249}"/>
-    <hyperlink ref="W4" r:id="rId2" xr:uid="{0C8D4DAC-C617-2547-BF75-D17B07FAB104}"/>
-    <hyperlink ref="W6" r:id="rId3" xr:uid="{5C533C8B-7E31-6247-B07A-DA36A2ECB804}"/>
-    <hyperlink ref="W7" r:id="rId4" xr:uid="{C7A27B14-F289-2345-8125-B9AE06601A7B}"/>
-    <hyperlink ref="W9" r:id="rId5" xr:uid="{BC8CFBF1-94B9-B04B-B168-9B969B0A4C7D}"/>
-    <hyperlink ref="W28" r:id="rId6" xr:uid="{C4869E3C-B5B1-6647-A144-091B1A64A38B}"/>
-    <hyperlink ref="W29" r:id="rId7" xr:uid="{808C07EB-0E2A-B640-A28C-8E310E5A987B}"/>
-    <hyperlink ref="W13" r:id="rId8" xr:uid="{9534F0D1-7C63-EC4F-921C-5D21474866A4}"/>
-    <hyperlink ref="W14:W17" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{0070BD27-D760-3846-9F0D-91BB5EDD333F}"/>
-    <hyperlink ref="W27" r:id="rId10" xr:uid="{FD223821-8B74-3345-B8A9-FA7536E78F2E}"/>
-    <hyperlink ref="W26" r:id="rId11" xr:uid="{8FF3DE15-909D-F043-B90F-3D2A3402F9DE}"/>
-    <hyperlink ref="W24" r:id="rId12" xr:uid="{236492C9-FC3A-614B-84DC-0D56063EE72E}"/>
+    <hyperlink ref="V3" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="V4" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="V6" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="V7" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="V9" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="V28" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="V29" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="V13" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="V14:V17" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="V27" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="V26" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="V24" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A05C489E-9770-1041-AA5F-EEF758A56CB8}">
-  <sheetPr codeName="Sheet2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.1640625" customWidth="1"/>
   </cols>
@@ -5824,7 +5693,7 @@
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="12" t="s">
         <v>234</v>
       </c>
       <c r="B3" t="s">
@@ -5832,7 +5701,7 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="12" t="s">
         <v>236</v>
       </c>
       <c r="B4" t="s">
@@ -5840,7 +5709,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="12" t="s">
         <v>238</v>
       </c>
       <c r="B5" t="s">
@@ -5848,7 +5717,7 @@
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="12" t="s">
         <v>240</v>
       </c>
       <c r="B6" t="s">
@@ -5856,15 +5725,15 @@
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="12" t="s">
         <v>242</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="12" t="s">
         <v>243</v>
       </c>
       <c r="B8" t="s">
@@ -5872,7 +5741,7 @@
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1" t="s">
+      <c r="A9" s="12" t="s">
         <v>245</v>
       </c>
       <c r="B9" t="s">
@@ -5880,7 +5749,7 @@
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="12" t="s">
         <v>246</v>
       </c>
       <c r="B10" t="s">
@@ -5888,15 +5757,15 @@
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="12" t="s">
         <v>248</v>
       </c>
       <c r="B11" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="2" t="s">
+    <row r="12" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="13" t="s">
         <v>250</v>
       </c>
       <c r="B12" t="s">
@@ -5904,20 +5773,20 @@
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="14" t="s">
         <v>252</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8377CCE6-51F2-A040-A333-66D02DBB8DB4}">
-  <sheetPr codeName="Sheet3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="1.83203125" customWidth="1"/>
     <col min="2" max="2" width="126" customWidth="1"/>
@@ -5979,23 +5848,263 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:A46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>343</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="16" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="66af2654134d243f62aac8e2b322f1d6">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2bc3adf68671d86faa9c37249f400344" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="d42a73f51a03135be35f4acb272f8cf1">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2ea21b36c10eaa86a5cb337ec7f4e0a6" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -6019,6 +6128,8 @@
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -6093,6 +6204,16 @@
     <xsd:element name="MediaServiceSearchProperties" ma:index="23" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="24" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="25" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -6237,33 +6358,26 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6B6DEDC7-93D0-4B5E-BED5-006DF8C890FC}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E6C6718-1083-4BA4-895F-4D544A70F5E5}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{26276598-8A19-40B6-BED3-157936C93058}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{626A4699-A325-43EA-975B-831A3E6EEB9F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -6282,9 +6396,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{025C630B-64D2-4AAA-9CA6-B49D96BBCC82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7313F8-A05E-4214-AA83-B148B6D9FF29}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10414"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{47D15A47-F99B-7246-8B5B-2AFC1BCCAE91}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1936AC6B-01E4-6049-903E-6E6C4FEF2BF5}"/>
   <bookViews>
-    <workbookView xWindow="35000" yWindow="-5960" windowWidth="49660" windowHeight="24360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34560" yWindow="-7080" windowWidth="38400" windowHeight="19680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Pipeline" sheetId="3" r:id="rId2"/>
-    <sheet name="Conflcts" sheetId="4" r:id="rId3"/>
+    <sheet name="Conflicts" sheetId="4" r:id="rId3"/>
     <sheet name="FileList" sheetId="6" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -1695,7 +1695,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>38</v>
       </c>
@@ -5025,7 +5025,7 @@
         <v>2014</v>
       </c>
       <c r="H44" t="str">
-        <f>_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
+        <f t="shared" ref="H44:H49" si="51">_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="J44" s="1" t="s">
@@ -5068,11 +5068,11 @@
         <v>0</v>
       </c>
       <c r="C45" s="2" t="str">
-        <f t="shared" ref="C45" si="51">D45 &amp; IF(E45&lt;&gt;"", "_" &amp; E45, "_") &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "_") &amp; IF(G45&lt;&gt;"", "_" &amp; G45, "")</f>
+        <f t="shared" ref="C45" si="52">D45 &amp; IF(E45&lt;&gt;"", "_" &amp; E45, "_") &amp; IF(F45&lt;&gt;"", "_" &amp; F45, "_") &amp; IF(G45&lt;&gt;"", "_" &amp; G45, "")</f>
         <v>Lewitus_etal_2014</v>
       </c>
       <c r="D45" s="2" t="str">
-        <f t="shared" ref="D45" si="52">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="D45" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A45,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
       <c r="E45" s="2" t="str">
@@ -5080,22 +5080,22 @@
         <v>etal</v>
       </c>
       <c r="F45" s="2" t="str">
-        <f t="shared" ref="F45" si="53">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
+        <f t="shared" ref="F45" si="54">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A45, "("), ")")</f>
         <v>2014</v>
       </c>
       <c r="H45" t="str">
-        <f>_xlfn.TEXTAFTER(A45,"https://doi.org/")</f>
+        <f t="shared" si="51"/>
         <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="J45" s="1" t="s">
         <v>224</v>
       </c>
       <c r="K45" s="1" t="str">
-        <f t="shared" ref="K45" si="54">TRIM(_xlfn.TEXTJOIN("_",FALSE,C45,(SUBSTITUTE(SUBSTITUTE(J45," ",""), "_", ""))))</f>
+        <f t="shared" ref="K45" si="55">TRIM(_xlfn.TEXTJOIN("_",FALSE,C45,(SUBSTITUTE(SUBSTITUTE(J45," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2014_TableS8</v>
       </c>
       <c r="L45" s="1" t="str">
-        <f t="shared" ref="L45" si="55">IF(ISBLANK(I45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(J45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I45, SUBSTITUTE(J45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L45" si="56">IF(ISBLANK(I45),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H45, SUBSTITUTE(J45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I45, SUBSTITUTE(J45,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="O45" t="str">
@@ -5127,11 +5127,11 @@
         <v>4</v>
       </c>
       <c r="C46" s="7" t="str">
-        <f t="shared" ref="C46" si="56">D46 &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "_") &amp; IF(G46&lt;&gt;"", "_" &amp; G46, "")</f>
+        <f t="shared" ref="C46" si="57">D46 &amp; IF(E46&lt;&gt;"", "_" &amp; E46, "_") &amp; IF(F46&lt;&gt;"", "_" &amp; F46, "_") &amp; IF(G46&lt;&gt;"", "_" &amp; G46, "")</f>
         <v>Lewitus_etal_2013</v>
       </c>
       <c r="D46" s="7" t="str">
-        <f t="shared" ref="D46" si="57">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="D46" si="58">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A46,","), "-", ""), " ", "")</f>
         <v>Lewitus</v>
       </c>
       <c r="E46" s="2" t="str">
@@ -5142,19 +5142,19 @@
         <v>etal</v>
       </c>
       <c r="F46" s="7" t="str">
-        <f t="shared" ref="F46" si="58">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
+        <f t="shared" ref="F46" si="59">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A46, "("), ")")</f>
         <v>2013</v>
       </c>
       <c r="G46" s="7"/>
       <c r="H46" s="6" t="str">
-        <f>_xlfn.TEXTAFTER(A46,"https://doi.org/")</f>
+        <f t="shared" si="51"/>
         <v>10.3389/fnhum.2013.00424</v>
       </c>
       <c r="J46" s="6" t="s">
         <v>227</v>
       </c>
       <c r="K46" s="6" t="str">
-        <f t="shared" ref="K46" si="59">TRIM(_xlfn.TEXTJOIN("_",FALSE,C46,(SUBSTITUTE(SUBSTITUTE(J46," ",""), "_", ""))))</f>
+        <f t="shared" ref="K46" si="60">TRIM(_xlfn.TEXTJOIN("_",FALSE,C46,(SUBSTITUTE(SUBSTITUTE(J46," ",""), "_", ""))))</f>
         <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
       <c r="L46" s="8" t="str">
@@ -5187,11 +5187,11 @@
         <v>1</v>
       </c>
       <c r="C47" s="9" t="str">
-        <f t="shared" ref="C47" si="60">D47 &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "_") &amp; IF(G47&lt;&gt;"", "_" &amp; G47, "")</f>
+        <f t="shared" ref="C47" si="61">D47 &amp; IF(E47&lt;&gt;"", "_" &amp; E47, "_") &amp; IF(F47&lt;&gt;"", "_" &amp; F47, "_") &amp; IF(G47&lt;&gt;"", "_" &amp; G47, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="D47" s="9" t="str">
-        <f t="shared" ref="D47" si="61">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="D47" si="62">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
       <c r="E47" s="2" t="str">
@@ -5199,19 +5199,19 @@
         <v>etal</v>
       </c>
       <c r="F47" s="9" t="str">
-        <f t="shared" ref="F47" si="62">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
+        <f t="shared" ref="F47" si="63">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
         <v>2011</v>
       </c>
       <c r="G47" s="9"/>
       <c r="H47" t="str">
-        <f>_xlfn.TEXTAFTER(A47,"https://doi.org/")</f>
+        <f t="shared" si="51"/>
         <v>10.1159/000323671</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>229</v>
       </c>
       <c r="K47" s="5" t="str">
-        <f t="shared" ref="K47" si="63">TRIM(_xlfn.TEXTJOIN("_",FALSE,C47,(SUBSTITUTE(SUBSTITUTE(J47," ",""), "_", ""))))</f>
+        <f t="shared" ref="K47" si="64">TRIM(_xlfn.TEXTJOIN("_",FALSE,C47,(SUBSTITUTE(SUBSTITUTE(J47," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="L47" s="5" t="str">
@@ -5238,11 +5238,11 @@
         <v>1</v>
       </c>
       <c r="C48" s="9" t="str">
-        <f t="shared" ref="C48" si="64">D48 &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "_") &amp; IF(G48&lt;&gt;"", "_" &amp; G48, "")</f>
+        <f t="shared" ref="C48" si="65">D48 &amp; IF(E48&lt;&gt;"", "_" &amp; E48, "_") &amp; IF(F48&lt;&gt;"", "_" &amp; F48, "_") &amp; IF(G48&lt;&gt;"", "_" &amp; G48, "")</f>
         <v>Smaers_etal_2011</v>
       </c>
       <c r="D48" s="9" t="str">
-        <f t="shared" ref="D48" si="65">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="D48" si="66">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A48,","), "-", ""), " ", "")</f>
         <v>Smaers</v>
       </c>
       <c r="E48" s="2" t="str">
@@ -5250,19 +5250,19 @@
         <v>etal</v>
       </c>
       <c r="F48" s="9" t="str">
-        <f t="shared" ref="F48" si="66">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
+        <f t="shared" ref="F48" si="67">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A48, "("), ")")</f>
         <v>2011</v>
       </c>
       <c r="G48" s="9"/>
       <c r="H48" t="str">
-        <f>_xlfn.TEXTAFTER(A48,"https://doi.org/")</f>
+        <f t="shared" si="51"/>
         <v>10.1159/000323671</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>231</v>
       </c>
       <c r="K48" s="5" t="str">
-        <f t="shared" ref="K48" si="67">TRIM(_xlfn.TEXTJOIN("_",FALSE,C48,(SUBSTITUTE(SUBSTITUTE(J48," ",""), "_", ""))))</f>
+        <f t="shared" ref="K48" si="68">TRIM(_xlfn.TEXTJOIN("_",FALSE,C48,(SUBSTITUTE(SUBSTITUTE(J48," ",""), "_", ""))))</f>
         <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="L48" s="5" t="str">
@@ -5289,27 +5289,27 @@
         <v>x</v>
       </c>
       <c r="C49" s="9" t="str">
-        <f t="shared" ref="C49:C53" si="68">D49 &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "_") &amp; IF(G49&lt;&gt;"", "_" &amp; G49, "")</f>
+        <f t="shared" ref="C49:C53" si="69">D49 &amp; IF(E49&lt;&gt;"", "_" &amp; E49, "_") &amp; IF(F49&lt;&gt;"", "_" &amp; F49, "_") &amp; IF(G49&lt;&gt;"", "_" &amp; G49, "")</f>
         <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="D49" s="9" t="str">
-        <f t="shared" ref="D49:D53" si="69">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="D49:D53" si="70">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A49,","), "-", ""), " ", "")</f>
         <v>Iwaniuk</v>
       </c>
       <c r="E49" s="2" t="str">
-        <f t="shared" ref="E49:E53" si="70">IF(ISNUMBER(FIND("&amp;", A49)),
+        <f t="shared" ref="E49:E53" si="71">IF(ISNUMBER(FIND("&amp;", A49)),
     IF(LEN(A49)-LEN(SUBSTITUTE(A49, ",", ""))&gt;=6, "etal", MID(A49, SEARCH("&amp; ", A49)+2, SEARCH(",", A49, SEARCH("&amp; ", A49)+2) - SEARCH("&amp; ", A49)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="F49" s="9" t="str">
-        <f t="shared" ref="F49:F52" si="71">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
+        <f t="shared" ref="F49:F52" si="72">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A49, "("), ")")</f>
         <v>1999</v>
       </c>
       <c r="G49" s="9"/>
       <c r="H49" t="str">
-        <f>_xlfn.TEXTAFTER(A49,"https://doi.org/")</f>
+        <f t="shared" si="51"/>
         <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="I49" s="5"/>
@@ -5317,7 +5317,7 @@
         <v>52</v>
       </c>
       <c r="K49" s="5" t="str">
-        <f t="shared" ref="K49:K52" si="72">TRIM(_xlfn.TEXTJOIN("_",FALSE,C49,(SUBSTITUTE(SUBSTITUTE(J49," ",""), "_", ""))))</f>
+        <f t="shared" ref="K49:K52" si="73">TRIM(_xlfn.TEXTJOIN("_",FALSE,C49,(SUBSTITUTE(SUBSTITUTE(J49," ",""), "_", ""))))</f>
         <v>Iwaniuk_etal_1999_Table1</v>
       </c>
       <c r="L49" s="5" t="str">
@@ -5350,27 +5350,27 @@
         <v>x</v>
       </c>
       <c r="C50" s="9" t="str">
-        <f t="shared" ref="C50" si="73">D50 &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "_") &amp; IF(G50&lt;&gt;"", "_" &amp; G50, "")</f>
+        <f t="shared" ref="C50" si="74">D50 &amp; IF(E50&lt;&gt;"", "_" &amp; E50, "_") &amp; IF(F50&lt;&gt;"", "_" &amp; F50, "_") &amp; IF(G50&lt;&gt;"", "_" &amp; G50, "")</f>
         <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="D50" s="9" t="str">
-        <f t="shared" ref="D50" si="74">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="D50" si="75">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
         <v>Iwaniuk</v>
       </c>
       <c r="E50" s="2" t="str">
-        <f t="shared" ref="E50" si="75">IF(ISNUMBER(FIND("&amp;", A50)),
+        <f t="shared" ref="E50" si="76">IF(ISNUMBER(FIND("&amp;", A50)),
     IF(LEN(A50)-LEN(SUBSTITUTE(A50, ",", ""))&gt;=6, "etal", MID(A50, SEARCH("&amp; ", A50)+2, SEARCH(",", A50, SEARCH("&amp; ", A50)+2) - SEARCH("&amp; ", A50)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="F50" s="9" t="str">
-        <f t="shared" ref="F50" si="76">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
+        <f t="shared" ref="F50" si="77">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
         <v>1999</v>
       </c>
       <c r="G50" s="9"/>
       <c r="H50" t="str">
-        <f t="shared" ref="H50" si="77">_xlfn.TEXTAFTER(A50,"https://doi.org/")</f>
+        <f t="shared" ref="H50" si="78">_xlfn.TEXTAFTER(A50,"https://doi.org/")</f>
         <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="I50" s="5"/>
@@ -5378,7 +5378,7 @@
         <v>340</v>
       </c>
       <c r="K50" s="5" t="str">
-        <f t="shared" ref="K50" si="78">TRIM(_xlfn.TEXTJOIN("_",FALSE,C50,(SUBSTITUTE(SUBSTITUTE(J50," ",""), "_", ""))))</f>
+        <f t="shared" ref="K50" si="79">TRIM(_xlfn.TEXTJOIN("_",FALSE,C50,(SUBSTITUTE(SUBSTITUTE(J50," ",""), "_", ""))))</f>
         <v>Iwaniuk_etal_1999_References</v>
       </c>
       <c r="L50" s="5" t="str">
@@ -5411,19 +5411,19 @@
         <v>0</v>
       </c>
       <c r="C51" s="9" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>Genoud_etal_2018</v>
       </c>
       <c r="D51" s="9" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>Genoud</v>
       </c>
       <c r="E51" s="2" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>etal</v>
       </c>
       <c r="F51" s="9" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2018</v>
       </c>
       <c r="G51" s="9"/>
@@ -5436,11 +5436,11 @@
         <v>220</v>
       </c>
       <c r="K51" s="5" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>Genoud_etal_2018_TableS2</v>
       </c>
       <c r="L51" s="5" t="str">
-        <f t="shared" ref="L51:L52" si="79">IF(ISBLANK(I51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(J51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I51, SUBSTITUTE(J51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L51:L52" si="80">IF(ISBLANK(I51),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H51, SUBSTITUTE(J51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I51, SUBSTITUTE(J51,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1111%2Fbrv.12350_TableS2</v>
       </c>
       <c r="N51" s="5" t="s">
@@ -5466,19 +5466,19 @@
         <v>6</v>
       </c>
       <c r="C52" s="9" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>Mota_etal_2019</v>
       </c>
       <c r="D52" s="9" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>Mota</v>
       </c>
       <c r="E52" s="2" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>etal</v>
       </c>
       <c r="F52" s="9" t="str">
-        <f t="shared" si="71"/>
+        <f t="shared" si="72"/>
         <v>2019</v>
       </c>
       <c r="G52" s="9"/>
@@ -5491,11 +5491,11 @@
         <v>272</v>
       </c>
       <c r="K52" s="5" t="str">
-        <f t="shared" si="72"/>
+        <f t="shared" si="73"/>
         <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="L52" s="5" t="str">
-        <f t="shared" si="79"/>
+        <f t="shared" si="80"/>
         <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="N52" s="5" t="s">
@@ -5521,19 +5521,19 @@
         <v>9</v>
       </c>
       <c r="C53" s="9" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="69"/>
         <v>Burish_etal_2010</v>
       </c>
       <c r="D53" s="9" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="70"/>
         <v>Burish</v>
       </c>
       <c r="E53" s="2" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="71"/>
         <v>etal</v>
       </c>
       <c r="F53" s="9" t="str">
-        <f t="shared" ref="F53" si="80">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
+        <f t="shared" ref="F53" si="81">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A53, "("), ")")</f>
         <v>2010</v>
       </c>
       <c r="G53" s="9"/>
@@ -5546,11 +5546,11 @@
         <v>52</v>
       </c>
       <c r="K53" s="5" t="str">
-        <f t="shared" ref="K53" si="81">TRIM(_xlfn.TEXTJOIN("_",FALSE,C53,(SUBSTITUTE(SUBSTITUTE(J53," ",""), "_", ""))))</f>
+        <f t="shared" ref="K53" si="82">TRIM(_xlfn.TEXTJOIN("_",FALSE,C53,(SUBSTITUTE(SUBSTITUTE(J53," ",""), "_", ""))))</f>
         <v>Burish_etal_2010_Table1</v>
       </c>
       <c r="L53" s="5" t="str">
-        <f t="shared" ref="L53" si="82">IF(ISBLANK(I53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(J53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I53, SUBSTITUTE(J53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L53" si="83">IF(ISBLANK(I53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H53, SUBSTITUTE(J53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I53, SUBSTITUTE(J53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000319019_Table1</v>
       </c>
       <c r="N53" t="s">
@@ -5588,27 +5588,27 @@
         <v>9</v>
       </c>
       <c r="C54" s="9" t="str">
-        <f t="shared" ref="C54:C59" si="83">D54 &amp; IF(E54&lt;&gt;"", "_" &amp; E54, "_") &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "_") &amp; IF(G54&lt;&gt;"", "_" &amp; G54, "")</f>
+        <f t="shared" ref="C54:C59" si="84">D54 &amp; IF(E54&lt;&gt;"", "_" &amp; E54, "_") &amp; IF(F54&lt;&gt;"", "_" &amp; F54, "_") &amp; IF(G54&lt;&gt;"", "_" &amp; G54, "")</f>
         <v>Burish_etal_2010</v>
       </c>
       <c r="D54" s="9" t="str">
-        <f t="shared" ref="D54:D59" si="84">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="D54:D59" si="85">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A54,","), "-", ""), " ", "")</f>
         <v>Burish</v>
       </c>
       <c r="E54" s="2" t="str">
-        <f t="shared" ref="E54:E59" si="85">IF(ISNUMBER(FIND("&amp;", A54)),
+        <f t="shared" ref="E54:E59" si="86">IF(ISNUMBER(FIND("&amp;", A54)),
     IF(LEN(A54)-LEN(SUBSTITUTE(A54, ",", ""))&gt;=6, "etal", MID(A54, SEARCH("&amp; ", A54)+2, SEARCH(",", A54, SEARCH("&amp; ", A54)+2) - SEARCH("&amp; ", A54)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="F54" s="9" t="str">
-        <f t="shared" ref="F54:F59" si="86">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
+        <f t="shared" ref="F54:F59" si="87">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A54, "("), ")")</f>
         <v>2010</v>
       </c>
       <c r="G54" s="9"/>
       <c r="H54" t="str">
-        <f t="shared" ref="H54:H59" si="87">_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
+        <f t="shared" ref="H54:H59" si="88">_xlfn.TEXTAFTER(A54,"https://doi.org/")</f>
         <v>10.1159/000319019</v>
       </c>
       <c r="I54" s="5"/>
@@ -5616,11 +5616,11 @@
         <v>276</v>
       </c>
       <c r="K54" s="5" t="str">
-        <f t="shared" ref="K54:K55" si="88">TRIM(_xlfn.TEXTJOIN("_",FALSE,C54,(SUBSTITUTE(SUBSTITUTE(J54," ",""), "_", ""))))</f>
+        <f t="shared" ref="K54:K55" si="89">TRIM(_xlfn.TEXTJOIN("_",FALSE,C54,(SUBSTITUTE(SUBSTITUTE(J54," ",""), "_", ""))))</f>
         <v>Burish_etal_2010_SupplementaryTable1</v>
       </c>
       <c r="L54" s="5" t="str">
-        <f t="shared" ref="L54:L55" si="89">IF(ISBLANK(I54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H54, SUBSTITUTE(J54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I54, SUBSTITUTE(J54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L54:L55" si="90">IF(ISBLANK(I54),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H54, SUBSTITUTE(J54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I54, SUBSTITUTE(J54,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
       <c r="N54" s="5" t="s">
@@ -5655,34 +5655,34 @@
         <v>x</v>
       </c>
       <c r="C55" s="9" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>Fu_etal_2013</v>
       </c>
       <c r="D55" s="9" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>Fu</v>
       </c>
       <c r="E55" s="2" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>etal</v>
       </c>
       <c r="F55" s="9" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>2013</v>
       </c>
       <c r="H55" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>10.1007/s00429-012-0462-x</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>52</v>
       </c>
       <c r="K55" s="5" t="str">
-        <f t="shared" si="88"/>
+        <f t="shared" si="89"/>
         <v>Fu_etal_2013_Table1</v>
       </c>
       <c r="L55" s="5" t="str">
-        <f t="shared" si="89"/>
+        <f t="shared" si="90"/>
         <v>10.1007%2Fs00429-012-0462-x_Table1</v>
       </c>
       <c r="N55" s="5" t="s">
@@ -5711,34 +5711,34 @@
         <v>5</v>
       </c>
       <c r="C56" s="9" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>MacLarnon__1996</v>
       </c>
       <c r="D56" s="9" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>MacLarnon</v>
       </c>
       <c r="E56" s="2" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="F56" s="9" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>1996</v>
       </c>
       <c r="H56" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>10.1006/jhev.1996.0005</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>52</v>
       </c>
       <c r="K56" s="5" t="str">
-        <f t="shared" ref="K56:K59" si="90">TRIM(_xlfn.TEXTJOIN("_",FALSE,C56,(SUBSTITUTE(SUBSTITUTE(J56," ",""), "_", ""))))</f>
+        <f t="shared" ref="K56:K59" si="91">TRIM(_xlfn.TEXTJOIN("_",FALSE,C56,(SUBSTITUTE(SUBSTITUTE(J56," ",""), "_", ""))))</f>
         <v>MacLarnon__1996_Table1</v>
       </c>
       <c r="L56" s="5" t="str">
-        <f t="shared" ref="L56:L59" si="91">IF(ISBLANK(I56),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H56, SUBSTITUTE(J56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I56, SUBSTITUTE(J56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L56:L59" si="92">IF(ISBLANK(I56),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H56, SUBSTITUTE(J56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I56, SUBSTITUTE(J56,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1006%2Fjhev.1996.0005_Table1</v>
       </c>
       <c r="N56" s="5" t="s">
@@ -5761,34 +5761,34 @@
         <v>7</v>
       </c>
       <c r="C57" s="9" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>Wimberly_etal_2021</v>
       </c>
       <c r="D57" s="9" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>Wimberly</v>
       </c>
       <c r="E57" s="2" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>etal</v>
       </c>
       <c r="F57" s="9" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>2021</v>
       </c>
       <c r="H57" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>10.1098/rspb.2021.0937</v>
       </c>
       <c r="J57" t="s">
         <v>338</v>
       </c>
       <c r="K57" s="5" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>Wimberly_etal_2021_mammalgait.txt</v>
       </c>
       <c r="L57" s="5" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
       </c>
       <c r="N57" s="5" t="s">
@@ -5808,34 +5808,34 @@
         <v>8</v>
       </c>
       <c r="C58" s="9" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>Granatosky__2018</v>
       </c>
       <c r="D58" s="9" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>Granatosky</v>
       </c>
       <c r="E58" s="2" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v/>
       </c>
       <c r="F58" s="9" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>2018</v>
       </c>
       <c r="H58" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>10.1111/jzo.12608</v>
       </c>
       <c r="J58" t="s">
         <v>91</v>
       </c>
       <c r="K58" s="5" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>Granatosky__2018_TableS1</v>
       </c>
       <c r="L58" s="5" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>10.1111%2Fjzo.12608_TableS1</v>
       </c>
       <c r="N58" s="5" t="s">
@@ -5858,34 +5858,34 @@
         <v>1</v>
       </c>
       <c r="C59" s="9" t="str">
-        <f t="shared" si="83"/>
+        <f t="shared" si="84"/>
         <v>Wilman_etal_2014</v>
       </c>
       <c r="D59" s="9" t="str">
-        <f t="shared" si="84"/>
+        <f t="shared" si="85"/>
         <v>Wilman</v>
       </c>
       <c r="E59" s="2" t="str">
-        <f t="shared" si="85"/>
+        <f t="shared" si="86"/>
         <v>etal</v>
       </c>
       <c r="F59" s="9" t="str">
-        <f t="shared" si="86"/>
+        <f t="shared" si="87"/>
         <v>2014</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" si="87"/>
+        <f t="shared" si="88"/>
         <v>10.1890/13-1917.1</v>
       </c>
       <c r="J59" t="s">
         <v>339</v>
       </c>
       <c r="K59" s="5" t="str">
-        <f t="shared" si="90"/>
+        <f t="shared" si="91"/>
         <v>Wilman_etal_2014_MamFuncDat.txt</v>
       </c>
       <c r="L59" s="5" t="str">
-        <f t="shared" si="91"/>
+        <f t="shared" si="92"/>
         <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
       </c>
       <c r="O59" t="str">
@@ -6638,15 +6638,15 @@
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7313F8-A05E-4214-AA83-B148B6D9FF29}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="244" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06A6870C-C12F-EC40-BA79-F426324FC52E}"/>
+  <xr:revisionPtr revIDLastSave="304" documentId="6_{3E294B1E-BE69-A04D-8F66-E6809E46817C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCA05431-0A0A-F341-B8A4-457186DC1F7E}"/>
   <bookViews>
-    <workbookView xWindow="35120" yWindow="-5120" windowWidth="45340" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="25320" windowHeight="20560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="704" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="388">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -1159,6 +1159,51 @@
   </si>
   <si>
     <t>unpublished</t>
+  </si>
+  <si>
+    <t>DeCasien, A. R., &amp; Higham, J. P. (2019). Primate mosaic brain evolution reflects selection on sensory and cognitive specialization. Nat Ecol Evol, 3(10), 1483-1493. https://doi.org/10.1038/s41559-019-0969-0</t>
+  </si>
+  <si>
+    <t>Supplementary Data 1 Brain Region Data (mm3)</t>
+  </si>
+  <si>
+    <t>table Sheet 1</t>
+  </si>
+  <si>
+    <t>https://www.nature.com/articles/s41559-019-0969-0#Sec13</t>
+  </si>
+  <si>
+    <t>Brain Regions Volumes</t>
+  </si>
+  <si>
+    <t>Supplementary Data 1-Brain Region</t>
+  </si>
+  <si>
+    <t>Supplementary Data 1-Activity Period</t>
+  </si>
+  <si>
+    <t>Supplementary Data 1-Diet</t>
+  </si>
+  <si>
+    <t>Supplementary Data 1-Social System</t>
+  </si>
+  <si>
+    <t>Activity Period</t>
+  </si>
+  <si>
+    <t>Diet</t>
+  </si>
+  <si>
+    <t>Social System</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mostly Stephan and other Ddorf studies </t>
+  </si>
+  <si>
+    <t>10.0000/placeholder.2</t>
+  </si>
+  <si>
+    <t>Baron, G., Stephan, H., &amp; Frahm, H. D. (1987). Comparison of brain structure volumes in Insectivora and Primates. VI. Paleocortical components. J Hirnforsch, 28(4), 463-477. http://www.ncbi.nlm.nih.gov/pubmed/3116076</t>
   </si>
 </sst>
 </file>
@@ -1652,7 +1697,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AK69"/>
+  <dimension ref="A1:AK74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="40.6640625" style="13" customWidth="1"/>
@@ -1661,10 +1706,10 @@
     <col min="4" max="4" width="23.6640625" customWidth="1"/>
     <col min="5" max="5" width="16.83203125" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="2.1640625" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" customWidth="1"/>
     <col min="8" max="8" width="4.5" customWidth="1"/>
     <col min="9" max="9" width="37.5" style="13" customWidth="1"/>
-    <col min="10" max="10" width="17.1640625" style="13" customWidth="1"/>
+    <col min="10" max="10" width="34.83203125" style="13" customWidth="1"/>
     <col min="11" max="11" width="31.1640625" customWidth="1"/>
     <col min="12" max="12" width="46.5" customWidth="1"/>
     <col min="13" max="13" width="49.83203125" customWidth="1"/>
@@ -1841,7 +1886,7 @@
         <v>AvelinodeSouza_etal_2025_TABLE1</v>
       </c>
       <c r="L2" s="1" t="str">
-        <f t="shared" ref="L2:L38" si="7">IF(ISBLANK(I2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f t="shared" ref="L2:L43" si="7">IF(ISBLANK(I2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I2, SUBSTITUTE(J2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1002%2Fcne.70089_TABLE1</v>
       </c>
       <c r="M2" t="str">
@@ -1854,7 +1899,7 @@
         <v>370</v>
       </c>
       <c r="C3" t="str">
-        <f t="shared" ref="C3" si="8">RIGHT(A3,1)</f>
+        <f t="shared" ref="C3:C4" si="8">RIGHT(A3,1)</f>
         <v>5</v>
       </c>
       <c r="D3" t="str">
@@ -1901,316 +1946,291 @@
     </row>
     <row r="4" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="13" t="s">
-        <v>354</v>
+        <v>387</v>
       </c>
       <c r="C4" t="str">
-        <f t="shared" ref="C4:C38" si="16">RIGHT(A4,1)</f>
-        <v>0</v>
+        <f t="shared" si="8"/>
+        <v>6</v>
       </c>
       <c r="D4" t="str">
-        <f t="shared" ref="D4:D38" si="17">E4 &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "_") &amp; IF(G4&lt;&gt;"", "_" &amp; G4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
-        <v>Brodmann__1913</v>
+        <f t="shared" ref="D4" si="16">E4 &amp; IF(F4&lt;&gt;"", "_" &amp; F4, "_") &amp; IF(G4&lt;&gt;"", "_" &amp; G4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
+        <v>Baron_etal_1987</v>
       </c>
       <c r="E4" s="2" t="str">
-        <f t="shared" ref="E4:E38" si="18">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
-        <v>Brodmann</v>
+        <f t="shared" ref="E4" si="17">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <v>Baron</v>
       </c>
       <c r="F4" s="2" t="str">
-        <f t="shared" ref="F4:F38" si="19">IF(ISNUMBER(FIND("&amp;", A4)),
+        <f t="shared" ref="F4" si="18">IF(ISNUMBER(FIND("&amp;", A4)),
     IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=6, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
     ""
 )</f>
+        <v>etal</v>
+      </c>
+      <c r="G4" s="2" t="str">
+        <f t="shared" ref="G4" si="19">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+        <v>1987</v>
+      </c>
+      <c r="H4" t="e">
+        <f t="shared" ref="H4" si="20">_xlfn.TEXTAFTER(A4,"https://doi.org/")</f>
+        <v>#N/A</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="J4" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+    </row>
+    <row r="5" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="13" t="s">
+        <v>354</v>
+      </c>
+      <c r="C5" t="str">
+        <f t="shared" ref="C5:C43" si="21">RIGHT(A5,1)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" t="str">
+        <f t="shared" ref="D5:D43" si="22">E5 &amp; IF(F5&lt;&gt;"", "_" &amp; F5, "_") &amp; IF(G5&lt;&gt;"", "_" &amp; G5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
+        <v>Brodmann__1913</v>
+      </c>
+      <c r="E5" s="2" t="str">
+        <f t="shared" ref="E5:E43" si="23">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
+        <v>Brodmann</v>
+      </c>
+      <c r="F5" s="2" t="str">
+        <f t="shared" ref="F5:F43" si="24">IF(ISNUMBER(FIND("&amp;", A5)),
+    IF(LEN(A5)-LEN(SUBSTITUTE(A5, ",", ""))&gt;=6, "etal", MID(A5, SEARCH("&amp; ", A5)+2, SEARCH(",", A5, SEARCH("&amp; ", A5)+2) - SEARCH("&amp; ", A5)-2)),
+    ""
+)</f>
         <v/>
       </c>
-      <c r="G4" s="2" t="str">
-        <f t="shared" ref="G4:G38" si="20">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+      <c r="G5" s="2" t="str">
+        <f t="shared" ref="G5:G43" si="25">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
         <v>1913</v>
       </c>
-      <c r="H4" t="e">
-        <f t="shared" ref="H4:H38" si="21">_xlfn.TEXTAFTER(A4,"https://doi.org/")</f>
+      <c r="H5" t="e">
+        <f t="shared" ref="H5:H43" si="26">_xlfn.TEXTAFTER(A5,"https://doi.org/")</f>
         <v>#N/A</v>
       </c>
-      <c r="I4" s="13" t="s">
+      <c r="I5" s="13" t="s">
         <v>352</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J5" s="13" t="s">
         <v>353</v>
       </c>
-      <c r="K4" s="1" t="str">
-        <f t="shared" ref="K4:K38" si="22">TRIM(_xlfn.TEXTJOIN("_",FALSE,D4,(SUBSTITUTE(SUBSTITUTE(J4," ",""), "_", ""))))</f>
+      <c r="K5" s="1" t="str">
+        <f t="shared" ref="K5:K43" si="27">TRIM(_xlfn.TEXTJOIN("_",FALSE,D5,(SUBSTITUTE(SUBSTITUTE(J5," ",""), "_", ""))))</f>
         <v>Brodmann__1913_Tabelle1</v>
       </c>
-      <c r="L4" s="1" t="str">
+      <c r="L5" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.0000%2Fplaceholder_Tabelle1</v>
       </c>
-      <c r="M4" t="str">
-        <f t="array" ref="M4">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L4, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M5" t="str">
+        <f t="array" ref="M5">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L5, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
     </row>
-    <row r="5" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+    <row r="6" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C5" t="str">
-        <f t="shared" si="16"/>
+      <c r="C6" t="str">
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
-      <c r="D5" t="str">
-        <f t="shared" si="17"/>
+      <c r="D6" t="str">
+        <f t="shared" si="22"/>
         <v>Burger_etal_2019</v>
       </c>
-      <c r="E5" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E6" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>Burger</v>
       </c>
-      <c r="F5" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F6" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G5" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G6" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2019</v>
       </c>
-      <c r="H5" t="str">
-        <f t="shared" si="21"/>
+      <c r="H6" t="str">
+        <f t="shared" si="26"/>
         <v>10.1093/jmammal/gyz043</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J6" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="K5" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K6" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
-      <c r="L5" s="6" t="str">
+      <c r="L6" s="6" t="str">
         <f t="shared" si="7"/>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
-      <c r="M5" t="str">
-        <f t="array" ref="M5">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L5, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M6" t="str">
+        <f t="array" ref="M6">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L6, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
       </c>
-      <c r="O5" s="13" t="s">
+      <c r="O6" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="P5" s="13" t="s">
+      <c r="P6" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q5" s="13" t="s">
+      <c r="Q6" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="R5" s="13" t="s">
+      <c r="R6" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="S5" s="13" t="s">
+      <c r="S6" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="T5" s="13" t="str">
-        <f>IF(S5="N", R5, "write file name")</f>
+      <c r="T6" s="13" t="str">
+        <f>IF(S6="N", R6, "write file name")</f>
         <v>gyz043_suppl_Supplement_Data.csv</v>
       </c>
-      <c r="U5" s="13" t="s">
+      <c r="U6" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="V5" s="13" t="s">
+      <c r="V6" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W5" s="13" t="s">
+      <c r="W6" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="Y5" s="13" t="s">
+      <c r="Y6" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="Z5" s="13" t="s">
+      <c r="Z6" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="AD5" s="13" t="s">
+      <c r="AD6" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="AE5" s="13" t="s">
+      <c r="AE6" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="AI5" s="13">
+      <c r="AI6" s="13">
         <v>17</v>
       </c>
-      <c r="AK5" s="13">
+      <c r="AK6" s="13">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+    <row r="7" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="C6" t="str">
-        <f t="shared" si="16"/>
+      <c r="C7" t="str">
+        <f t="shared" si="21"/>
         <v>9</v>
       </c>
-      <c r="D6" t="str">
-        <f t="shared" si="17"/>
+      <c r="D7" t="str">
+        <f t="shared" si="22"/>
         <v>Burish_etal_2010</v>
       </c>
-      <c r="E6" s="7" t="str">
-        <f t="shared" si="18"/>
+      <c r="E7" s="7" t="str">
+        <f t="shared" si="23"/>
         <v>Burish</v>
       </c>
-      <c r="F6" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F7" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G6" s="7" t="str">
-        <f t="shared" si="20"/>
+      <c r="G7" s="7" t="str">
+        <f t="shared" si="25"/>
         <v>2010</v>
       </c>
-      <c r="H6" t="str">
-        <f t="shared" si="21"/>
+      <c r="H7" t="str">
+        <f t="shared" si="26"/>
         <v>10.1159/000319019</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J7" s="13" t="s">
         <v>276</v>
       </c>
-      <c r="K6" s="3" t="str">
-        <f t="shared" si="22"/>
+      <c r="K7" s="3" t="str">
+        <f t="shared" si="27"/>
         <v>Burish_etal_2010_SupplementaryTable1</v>
       </c>
-      <c r="L6" s="3" t="str">
+      <c r="L7" s="3" t="str">
         <f t="shared" si="7"/>
         <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
-      <c r="M6" t="str">
-        <f t="array" ref="M6">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L6, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M7" t="str">
+        <f t="array" ref="M7">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L7, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
-      <c r="N6" s="13" t="s">
+      <c r="N7" s="13" t="s">
         <v>275</v>
       </c>
-      <c r="P6" s="13" t="s">
+      <c r="P7" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="R6" s="13" t="s">
+      <c r="R7" s="13" t="s">
         <v>286</v>
       </c>
-      <c r="Z6" s="13" t="s">
+      <c r="Z7" s="13" t="s">
         <v>278</v>
       </c>
-      <c r="AC6" s="13" t="s">
+      <c r="AC7" s="13" t="s">
         <v>281</v>
       </c>
-      <c r="AE6" s="13" t="s">
+      <c r="AE7" s="13" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="7" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
+    <row r="8" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="13" t="s">
         <v>345</v>
       </c>
-      <c r="C7" t="str">
-        <f t="shared" si="16"/>
+      <c r="C8" t="str">
+        <f t="shared" si="21"/>
         <v>9</v>
       </c>
-      <c r="D7" t="str">
-        <f t="shared" si="17"/>
+      <c r="D8" t="str">
+        <f t="shared" si="22"/>
         <v>Burish_etal_2010</v>
       </c>
-      <c r="E7" s="7" t="str">
-        <f t="shared" si="18"/>
+      <c r="E8" s="7" t="str">
+        <f t="shared" si="23"/>
         <v>Burish</v>
       </c>
-      <c r="F7" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F8" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G7" s="7" t="str">
-        <f t="shared" si="20"/>
+      <c r="G8" s="7" t="str">
+        <f t="shared" si="25"/>
         <v>2010</v>
       </c>
-      <c r="H7" t="str">
-        <f t="shared" si="21"/>
+      <c r="H8" t="str">
+        <f t="shared" si="26"/>
         <v>10.1159/000319019</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J8" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K7" s="3" t="str">
-        <f t="shared" si="22"/>
+      <c r="K8" s="3" t="str">
+        <f t="shared" si="27"/>
         <v>Burish_etal_2010_Table1</v>
       </c>
-      <c r="L7" s="3" t="str">
+      <c r="L8" s="3" t="str">
         <f t="shared" si="7"/>
         <v>10.1159%2F000319019_Table1</v>
       </c>
-      <c r="M7" t="str">
-        <f t="array" ref="M7">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L7, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_Table1.tsv</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>274</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q7" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R7" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="Z7" s="13" t="s">
-        <v>277</v>
-      </c>
-      <c r="AC7" s="13" t="s">
-        <v>281</v>
-      </c>
-      <c r="AE7" s="13" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="8" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="str">
-        <f t="shared" si="16"/>
-        <v>5</v>
-      </c>
-      <c r="D8" t="str">
-        <f t="shared" si="17"/>
-        <v>Caspar_etal_2022</v>
-      </c>
-      <c r="E8" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Caspar</v>
-      </c>
-      <c r="F8" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>etal</v>
-      </c>
-      <c r="G8" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2022</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="21"/>
-        <v>10.7554/eLife.77875</v>
-      </c>
-      <c r="J8" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="K8" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>Caspar_etal_2022_Supplementaryfile3</v>
-      </c>
-      <c r="L8" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
-      </c>
       <c r="M8" t="str">
         <f t="array" ref="M8">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L8, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>70</v>
+        <v>274</v>
       </c>
       <c r="P8" s="13" t="s">
         <v>41</v>
@@ -2219,41 +2239,16 @@
         <v>53</v>
       </c>
       <c r="R8" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="S8" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T8" s="13" t="str">
-        <f>IF(S8="N", R8, "write file name")</f>
-        <v>elife-77875-supp3-v1.xlsx</v>
-      </c>
-      <c r="U8" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="V8" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W8" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X8" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y8" s="13" t="s">
-        <v>71</v>
+        <v>285</v>
       </c>
       <c r="Z8" s="13" t="s">
-        <v>49</v>
+        <v>277</v>
+      </c>
+      <c r="AC8" s="13" t="s">
+        <v>281</v>
       </c>
       <c r="AE8" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI8" s="13">
-        <v>5</v>
-      </c>
-      <c r="AK8" s="13">
-        <v>12</v>
+        <v>279</v>
       </c>
     </row>
     <row r="9" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
@@ -2261,46 +2256,46 @@
         <v>51</v>
       </c>
       <c r="C9" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="D9" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="22"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="23"/>
         <v>Caspar</v>
       </c>
       <c r="F9" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
       <c r="G9" s="2" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>2022</v>
       </c>
       <c r="H9" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="26"/>
         <v>10.7554/eLife.77875</v>
       </c>
       <c r="J9" s="13" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="K9" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>Caspar_etal_2022_Table1</v>
+        <f t="shared" si="27"/>
+        <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="L9" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>10.7554%2FeLife.77875_Table1</v>
+        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="M9" t="str">
         <f t="array" ref="M9">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L9, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="P9" s="13" t="s">
         <v>41</v>
@@ -2309,3711 +2304,3736 @@
         <v>53</v>
       </c>
       <c r="R9" s="13" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="S9" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T9" s="13" t="s">
-        <v>56</v>
+        <v>44</v>
+      </c>
+      <c r="T9" s="13" t="str">
+        <f>IF(S9="N", R9, "write file name")</f>
+        <v>elife-77875-supp3-v1.xlsx</v>
       </c>
       <c r="U9" s="13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="V9" s="13" t="s">
         <v>46</v>
       </c>
       <c r="W9" s="13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="X9" s="13" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="Y9" s="13" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="Z9" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="AD9" s="13" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="AE9" s="13" t="s">
         <v>64</v>
       </c>
       <c r="AI9" s="13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AK9" s="13">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="13" t="s">
-        <v>72</v>
+        <v>51</v>
       </c>
       <c r="C10" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="D10" t="str">
-        <f t="shared" si="17"/>
-        <v>Changizi__2001</v>
+        <f t="shared" si="22"/>
+        <v>Caspar_etal_2022</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Changizi</v>
+        <f t="shared" si="23"/>
+        <v>Caspar</v>
       </c>
       <c r="F10" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v/>
+        <f t="shared" si="24"/>
+        <v>etal</v>
       </c>
       <c r="G10" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2001</v>
+        <f t="shared" si="25"/>
+        <v>2022</v>
       </c>
       <c r="H10" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1007/s004220000205</v>
+        <f t="shared" si="26"/>
+        <v>10.7554/eLife.77875</v>
       </c>
       <c r="J10" s="13" t="s">
-        <v>73</v>
+        <v>52</v>
       </c>
       <c r="K10" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>Changizi__2001_Figure3</v>
+        <f t="shared" si="27"/>
+        <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="L10" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>10.1007%2Fs004220000205_Figure3</v>
+        <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="M10" t="str">
         <f t="array" ref="M10">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L10, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N10" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="P10" s="13" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q10" s="13" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R10" s="13" t="s">
-        <v>75</v>
+        <v>54</v>
       </c>
       <c r="S10" s="13" t="s">
         <v>55</v>
       </c>
       <c r="T10" s="13" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="U10" s="13" t="s">
         <v>57</v>
       </c>
       <c r="V10" s="13" t="s">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="W10" s="13" t="s">
-        <v>78</v>
+        <v>58</v>
+      </c>
+      <c r="X10" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="Y10" s="13" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="Z10" s="13" t="s">
-        <v>36</v>
+        <v>62</v>
       </c>
       <c r="AD10" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="AI10" s="13" t="s">
-        <v>81</v>
+        <v>63</v>
+      </c>
+      <c r="AE10" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="AI10" s="13">
+        <v>7</v>
+      </c>
+      <c r="AK10" s="13">
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="13" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="C11" t="str">
-        <f t="shared" si="16"/>
-        <v>3</v>
+        <f t="shared" si="21"/>
+        <v>5</v>
       </c>
       <c r="D11" t="str">
-        <f t="shared" si="17"/>
-        <v>Chen_Wiens_2020</v>
+        <f t="shared" si="22"/>
+        <v>Changizi__2001</v>
       </c>
       <c r="E11" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Chen</v>
+        <f t="shared" si="23"/>
+        <v>Changizi</v>
       </c>
       <c r="F11" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Wiens</v>
+        <f t="shared" si="24"/>
+        <v/>
       </c>
       <c r="G11" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2020</v>
+        <f t="shared" si="25"/>
+        <v>2001</v>
       </c>
       <c r="H11" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1038/s41467-020-14356-3</v>
+        <f t="shared" si="26"/>
+        <v>10.1007/s004220000205</v>
       </c>
       <c r="J11" s="13" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="K11" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>Chen_Wiens_2020_SupplementaryData3</v>
+        <f t="shared" si="27"/>
+        <v>Changizi__2001_Figure3</v>
       </c>
       <c r="L11" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
+        <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="M11" t="str">
         <f t="array" ref="M11">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L11, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
+        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
       <c r="P11" s="13" t="s">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="Q11" s="13" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="R11" s="13" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="S11" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="T11" s="13" t="str">
-        <f>IF(S11="N", R11, "write file name")</f>
-        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
+        <v>55</v>
+      </c>
+      <c r="T11" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="U11" s="13" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="V11" s="13" t="s">
-        <v>46</v>
+        <v>77</v>
       </c>
       <c r="W11" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X11" s="13" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="Y11" s="13" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="Z11" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC11" s="13" t="s">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="AD11" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="AE11" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="AI11" s="13">
-        <v>10</v>
-      </c>
-      <c r="AK11" s="13">
-        <v>13</v>
+        <v>80</v>
+      </c>
+      <c r="AI11" s="13" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="13" t="s">
+        <v>82</v>
+      </c>
+      <c r="C12" t="str">
+        <f t="shared" si="21"/>
+        <v>3</v>
+      </c>
+      <c r="D12" t="str">
+        <f t="shared" si="22"/>
+        <v>Chen_Wiens_2020</v>
+      </c>
+      <c r="E12" s="2" t="str">
+        <f t="shared" si="23"/>
+        <v>Chen</v>
+      </c>
+      <c r="F12" s="2" t="str">
+        <f t="shared" si="24"/>
+        <v>Wiens</v>
+      </c>
+      <c r="G12" s="2" t="str">
+        <f t="shared" si="25"/>
+        <v>2020</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1038/s41467-020-14356-3</v>
+      </c>
+      <c r="J12" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="K12" s="1" t="str">
+        <f t="shared" si="27"/>
+        <v>Chen_Wiens_2020_SupplementaryData3</v>
+      </c>
+      <c r="L12" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="array" ref="M12">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L12, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
+      </c>
+      <c r="P12" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q12" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R12" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="S12" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="T12" s="13" t="str">
+        <f>IF(S12="N", R12, "write file name")</f>
+        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
+      </c>
+      <c r="U12" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="V12" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W12" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X12" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="Y12" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z12" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC12" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD12" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="AE12" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="AI12" s="13">
+        <v>10</v>
+      </c>
+      <c r="AK12" s="13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="13" t="s">
         <v>356</v>
       </c>
-      <c r="C12" t="str">
-        <f t="shared" si="16"/>
+      <c r="C13" t="str">
+        <f t="shared" si="21"/>
         <v>7</v>
       </c>
-      <c r="D12" t="str">
-        <f t="shared" si="17"/>
+      <c r="D13" t="str">
+        <f t="shared" si="22"/>
         <v>Collins_etal_2010</v>
       </c>
-      <c r="E12" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E13" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>Collins</v>
       </c>
-      <c r="F12" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F13" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G12" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G13" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2010</v>
       </c>
-      <c r="H12" t="str">
-        <f t="shared" si="21"/>
+      <c r="H13" t="str">
+        <f t="shared" si="26"/>
         <v>10.1073/pnas.1010356107</v>
       </c>
-      <c r="J12" s="13" t="s">
+      <c r="J13" s="13" t="s">
         <v>357</v>
       </c>
-      <c r="K12" t="str">
-        <f t="shared" si="22"/>
+      <c r="K13" t="str">
+        <f t="shared" si="27"/>
         <v>Collins_etal_2010_DatasetS1</v>
       </c>
-      <c r="L12" t="str">
+      <c r="L13" t="str">
         <f t="shared" si="7"/>
         <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
       </c>
-      <c r="M12" t="str">
-        <f t="array" ref="M12">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L12, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="Y12" s="13" t="s">
-        <v>355</v>
-      </c>
-      <c r="Z12" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="13" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C13" t="str">
-        <f t="shared" si="16"/>
-        <v>6</v>
-      </c>
-      <c r="D13" t="str">
-        <f t="shared" si="17"/>
-        <v>DosSantos_etal_2017</v>
-      </c>
-      <c r="E13" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="F13" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>etal</v>
-      </c>
-      <c r="G13" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2017</v>
-      </c>
-      <c r="H13" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1159/000452856</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K13" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>DosSantos_etal_2017_TableS1</v>
-      </c>
-      <c r="L13" s="1" t="str">
-        <f t="shared" si="7"/>
-        <v>10.1159%2F000452856_TableS1</v>
-      </c>
       <c r="M13" t="str">
         <f t="array" ref="M13">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L13, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000452856_TableS1.tsv</v>
-      </c>
-      <c r="O13" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="P13" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q13" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R13" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="S13" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T13" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="U13" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="V13" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="W13" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X13" s="13" t="s">
-        <v>97</v>
+        <v>notfound</v>
       </c>
       <c r="Y13" s="13" t="s">
-        <v>98</v>
+        <v>355</v>
       </c>
       <c r="Z13" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="AA13" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB13" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE13" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="AF13" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="AI13" s="13">
-        <v>0</v>
-      </c>
-      <c r="AK13" s="13">
-        <v>0</v>
-      </c>
     </row>
     <row r="14" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="13" t="s">
-        <v>103</v>
+        <v>373</v>
       </c>
       <c r="C14" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="D14" t="str">
-        <f t="shared" si="17"/>
-        <v>DosSantos_etal_2020</v>
+        <f t="shared" si="22"/>
+        <v>DeCasien_Higham_2019</v>
       </c>
       <c r="E14" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>DosSantos</v>
+        <f t="shared" si="23"/>
+        <v>DeCasien</v>
       </c>
       <c r="F14" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>etal</v>
+        <f t="shared" si="24"/>
+        <v>Higham</v>
       </c>
       <c r="G14" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2020</v>
+        <f t="shared" si="25"/>
+        <v>2019</v>
       </c>
       <c r="H14" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1523/JNEUROSCI.2339-19.2020</v>
+        <f t="shared" si="26"/>
+        <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="J14" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>DosSantos_etal_2020_Table1</v>
-      </c>
-      <c r="L14" s="1" t="str">
+        <v>378</v>
+      </c>
+      <c r="K14" t="str">
+        <f t="shared" si="27"/>
+        <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
+      </c>
+      <c r="L14" t="str">
         <f t="shared" si="7"/>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="M14" t="str">
         <f t="array" ref="M14">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L14, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
-      </c>
-      <c r="P14" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q14" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R14" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="S14" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T14" s="13" t="s">
-        <v>105</v>
+        <v>notfound</v>
+      </c>
+      <c r="N14" s="13" t="s">
+        <v>374</v>
       </c>
       <c r="U14" s="13" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="V14" s="13" t="s">
-        <v>46</v>
+        <v>375</v>
+      </c>
+      <c r="W14" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X14" s="13" t="s">
+        <v>376</v>
       </c>
       <c r="Y14" s="13" t="s">
-        <v>98</v>
+        <v>377</v>
       </c>
       <c r="Z14" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA14" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB14" s="13" t="s">
-        <v>100</v>
+        <v>49</v>
+      </c>
+      <c r="AD14" s="13" t="s">
+        <v>385</v>
       </c>
       <c r="AE14" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI14" s="13">
-        <v>4</v>
-      </c>
-      <c r="AK14" s="13">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="13" t="s">
-        <v>103</v>
+        <v>373</v>
       </c>
       <c r="C15" t="str">
-        <f t="shared" ref="C15" si="23">RIGHT(A15,1)</f>
+        <f t="shared" ref="C15" si="28">RIGHT(A15,1)</f>
         <v>0</v>
       </c>
       <c r="D15" t="str">
-        <f t="shared" ref="D15" si="24">E15 &amp; IF(F15&lt;&gt;"", "_" &amp; F15, "_") &amp; IF(G15&lt;&gt;"", "_" &amp; G15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
-        <v>DosSantos_etal_2020</v>
+        <f t="shared" ref="D15" si="29">E15 &amp; IF(F15&lt;&gt;"", "_" &amp; F15, "_") &amp; IF(G15&lt;&gt;"", "_" &amp; G15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
+        <v>DeCasien_Higham_2019</v>
       </c>
       <c r="E15" s="2" t="str">
-        <f t="shared" ref="E15" si="25">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
-        <v>DosSantos</v>
+        <f t="shared" ref="E15" si="30">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
+        <v>DeCasien</v>
       </c>
       <c r="F15" s="2" t="str">
-        <f t="shared" ref="F15" si="26">IF(ISNUMBER(FIND("&amp;", A15)),
+        <f t="shared" ref="F15" si="31">IF(ISNUMBER(FIND("&amp;", A15)),
     IF(LEN(A15)-LEN(SUBSTITUTE(A15, ",", ""))&gt;=6, "etal", MID(A15, SEARCH("&amp; ", A15)+2, SEARCH(",", A15, SEARCH("&amp; ", A15)+2) - SEARCH("&amp; ", A15)-2)),
     ""
 )</f>
-        <v>etal</v>
+        <v>Higham</v>
       </c>
       <c r="G15" s="2" t="str">
-        <f t="shared" ref="G15" si="27">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
-        <v>2020</v>
+        <f t="shared" ref="G15" si="32">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
+        <v>2019</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" ref="H15" si="28">_xlfn.TEXTAFTER(A15,"https://doi.org/")</f>
-        <v>10.1523/JNEUROSCI.2339-19.2020</v>
+        <f t="shared" ref="H15" si="33">_xlfn.TEXTAFTER(A15,"https://doi.org/")</f>
+        <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="J15" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="K15" s="1" t="str">
-        <f t="shared" ref="K15" si="29">TRIM(_xlfn.TEXTJOIN("_",FALSE,D15,(SUBSTITUTE(SUBSTITUTE(J15," ",""), "_", ""))))</f>
-        <v>DosSantos_etal_2020_unpublished</v>
-      </c>
-      <c r="L15" s="1" t="str">
-        <f t="shared" ref="L15" si="30">IF(ISBLANK(I15),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H15, SUBSTITUTE(J15,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I15, SUBSTITUTE(J15,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished</v>
+        <v>379</v>
+      </c>
+      <c r="K15" t="str">
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D15,(SUBSTITUTE(SUBSTITUTE(J16," ",""), "_", ""))))</f>
+        <v>DeCasien_Higham_2019_SupplementaryData1-Diet</v>
+      </c>
+      <c r="L15" t="str">
+        <f>IF(ISBLANK(I15),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H15, SUBSTITUTE(J16,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I15, SUBSTITUTE(J16,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-Diet</v>
       </c>
       <c r="M15" t="str">
         <f t="array" ref="M15">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L15, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P15" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q15" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R15" s="14" t="s">
-        <v>104</v>
-      </c>
-      <c r="S15" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T15" s="13" t="s">
-        <v>105</v>
+      <c r="N15" s="13" t="s">
+        <v>374</v>
       </c>
       <c r="U15" s="13" t="s">
-        <v>106</v>
+        <v>67</v>
       </c>
       <c r="V15" s="13" t="s">
-        <v>46</v>
+        <v>375</v>
+      </c>
+      <c r="W15" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X15" s="13" t="s">
+        <v>376</v>
       </c>
       <c r="Y15" s="13" t="s">
-        <v>98</v>
+        <v>382</v>
       </c>
       <c r="Z15" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="AA15" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB15" s="13" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="AE15" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="AI15" s="13">
-        <v>4</v>
-      </c>
-      <c r="AK15" s="13">
-        <v>10</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="13" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C16" t="str">
-        <f t="shared" si="16"/>
-        <v>5</v>
+        <f t="shared" ref="C16" si="34">RIGHT(A16,1)</f>
+        <v>0</v>
       </c>
       <c r="D16" t="str">
-        <f t="shared" si="17"/>
-        <v>Falcone_etal_2019</v>
+        <f t="shared" ref="D16" si="35">E16 &amp; IF(F16&lt;&gt;"", "_" &amp; F16, "_") &amp; IF(G16&lt;&gt;"", "_" &amp; G16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
+        <v>DeCasien_Higham_2019</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Falcone</v>
+        <f t="shared" ref="E16" si="36">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
+        <v>DeCasien</v>
       </c>
       <c r="F16" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>etal</v>
+        <f t="shared" ref="F16" si="37">IF(ISNUMBER(FIND("&amp;", A16)),
+    IF(LEN(A16)-LEN(SUBSTITUTE(A16, ",", ""))&gt;=6, "etal", MID(A16, SEARCH("&amp; ", A16)+2, SEARCH(",", A16, SEARCH("&amp; ", A16)+2) - SEARCH("&amp; ", A16)-2)),
+    ""
+)</f>
+        <v>Higham</v>
       </c>
       <c r="G16" s="2" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" ref="G16" si="38">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1002/cne.24605</v>
+        <f t="shared" ref="H16" si="39">_xlfn.TEXTAFTER(A16,"https://doi.org/")</f>
+        <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>152</v>
+        <v>380</v>
       </c>
       <c r="K16" t="str">
-        <f t="shared" si="22"/>
-        <v>Falcone_etal_2019_TABLE1</v>
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,D16,(SUBSTITUTE(SUBSTITUTE(J17," ",""), "_", ""))))</f>
+        <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L16" t="str">
-        <f t="shared" si="7"/>
-        <v>10.1002%2Fcne.24605_TABLE1</v>
+        <f>IF(ISBLANK(I16),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H16, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I16, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="M16" t="str">
         <f t="array" ref="M16">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L16, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="R16" s="14"/>
+        <v>374</v>
+      </c>
       <c r="U16" s="13" t="s">
-        <v>113</v>
+        <v>67</v>
+      </c>
+      <c r="V16" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="W16" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X16" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="Y16" s="13" t="s">
+        <v>383</v>
+      </c>
+      <c r="Z16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE16" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="13" t="s">
-        <v>366</v>
+        <v>373</v>
       </c>
       <c r="C17" t="str">
-        <f t="shared" ref="C17" si="31">RIGHT(A17,1)</f>
-        <v>5</v>
+        <f t="shared" ref="C17" si="40">RIGHT(A17,1)</f>
+        <v>0</v>
       </c>
       <c r="D17" t="str">
-        <f t="shared" ref="D17" si="32">E17 &amp; IF(F17&lt;&gt;"", "_" &amp; F17, "_") &amp; IF(G17&lt;&gt;"", "_" &amp; G17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
-        <v>Falcone_etal_2019</v>
+        <f t="shared" ref="D17" si="41">E17 &amp; IF(F17&lt;&gt;"", "_" &amp; F17, "_") &amp; IF(G17&lt;&gt;"", "_" &amp; G17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
+        <v>DeCasien_Higham_2019</v>
       </c>
       <c r="E17" s="2" t="str">
-        <f t="shared" ref="E17" si="33">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
-        <v>Falcone</v>
+        <f t="shared" ref="E17" si="42">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
+        <v>DeCasien</v>
       </c>
       <c r="F17" s="2" t="str">
-        <f t="shared" ref="F17" si="34">IF(ISNUMBER(FIND("&amp;", A17)),
+        <f t="shared" ref="F17" si="43">IF(ISNUMBER(FIND("&amp;", A17)),
     IF(LEN(A17)-LEN(SUBSTITUTE(A17, ",", ""))&gt;=6, "etal", MID(A17, SEARCH("&amp; ", A17)+2, SEARCH(",", A17, SEARCH("&amp; ", A17)+2) - SEARCH("&amp; ", A17)-2)),
     ""
 )</f>
-        <v>etal</v>
+        <v>Higham</v>
       </c>
       <c r="G17" s="2" t="str">
-        <f t="shared" ref="G17" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
+        <f t="shared" ref="G17" si="44">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" ref="H17" si="36">_xlfn.TEXTAFTER(A17,"https://doi.org/")</f>
-        <v>10.1002/cne.24605</v>
+        <f t="shared" ref="H17" si="45">_xlfn.TEXTAFTER(A17,"https://doi.org/")</f>
+        <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>158</v>
+        <v>381</v>
       </c>
       <c r="K17" t="str">
-        <f t="shared" ref="K17" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,D17,(SUBSTITUTE(SUBSTITUTE(J17," ",""), "_", ""))))</f>
-        <v>Falcone_etal_2019_TABLE2</v>
+        <f t="shared" ref="K17" si="46">TRIM(_xlfn.TEXTJOIN("_",FALSE,D17,(SUBSTITUTE(SUBSTITUTE(J17," ",""), "_", ""))))</f>
+        <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L17" t="str">
-        <f t="shared" ref="L17" si="38">IF(ISBLANK(I17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H17, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I17, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1002%2Fcne.24605_TABLE2</v>
+        <f t="shared" ref="L17" si="47">IF(ISBLANK(I17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H17, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I17, SUBSTITUTE(J17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="M17" t="str">
         <f t="array" ref="M17">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L17, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="R17" s="14"/>
+        <v>374</v>
+      </c>
       <c r="U17" s="13" t="s">
-        <v>113</v>
+        <v>67</v>
+      </c>
+      <c r="V17" s="13" t="s">
+        <v>375</v>
+      </c>
+      <c r="W17" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X17" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="Y17" s="13" t="s">
+        <v>384</v>
+      </c>
+      <c r="Z17" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE17" s="13" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="13" t="s">
-        <v>109</v>
+        <v>90</v>
       </c>
       <c r="C18" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="21"/>
         <v>6</v>
       </c>
       <c r="D18" t="str">
-        <f t="shared" si="17"/>
-        <v>Finlay_etal_2006</v>
+        <f t="shared" si="22"/>
+        <v>DosSantos_etal_2017</v>
       </c>
       <c r="E18" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Finlay</v>
+        <f t="shared" si="23"/>
+        <v>DosSantos</v>
       </c>
       <c r="F18" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
       <c r="G18" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2006</v>
+        <f t="shared" si="25"/>
+        <v>2017</v>
       </c>
       <c r="H18" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1093/oso/9780198568742.003.0006</v>
+        <f t="shared" si="26"/>
+        <v>10.1159/000452856</v>
       </c>
       <c r="J18" s="13" t="s">
-        <v>110</v>
+        <v>91</v>
       </c>
       <c r="K18" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>Finlay_etal_2006_Table6.1</v>
+        <f t="shared" si="27"/>
+        <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="L18" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
+        <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="M18" t="str">
         <f t="array" ref="M18">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L18, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
-      </c>
-      <c r="N18" s="17"/>
+        <v>10.1159%2F000452856_TableS1.tsv</v>
+      </c>
+      <c r="O18" s="13" t="s">
+        <v>92</v>
+      </c>
       <c r="P18" s="13" t="s">
-        <v>74</v>
+        <v>41</v>
       </c>
       <c r="Q18" s="13" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="R18" s="13" t="s">
-        <v>111</v>
+        <v>93</v>
       </c>
       <c r="S18" s="13" t="s">
         <v>55</v>
       </c>
       <c r="T18" s="13" t="s">
-        <v>112</v>
+        <v>94</v>
       </c>
       <c r="U18" s="13" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="V18" s="13" t="s">
-        <v>46</v>
+        <v>96</v>
       </c>
       <c r="W18" s="13" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="X18" s="13" t="s">
-        <v>114</v>
+        <v>97</v>
       </c>
       <c r="Y18" s="13" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="Z18" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="AD18" s="13" t="s">
-        <v>116</v>
+        <v>99</v>
+      </c>
+      <c r="AA18" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB18" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="AE18" s="13" t="s">
-        <v>37</v>
+        <v>101</v>
+      </c>
+      <c r="AF18" s="13" t="s">
+        <v>102</v>
       </c>
       <c r="AI18" s="13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK18" s="13">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="13" t="s">
-        <v>346</v>
+        <v>103</v>
       </c>
       <c r="C19" t="str">
-        <f t="shared" si="16"/>
-        <v>x</v>
+        <f t="shared" si="21"/>
+        <v>0</v>
       </c>
       <c r="D19" t="str">
-        <f t="shared" si="17"/>
-        <v>Fu_etal_2013</v>
-      </c>
-      <c r="E19" s="7" t="str">
-        <f t="shared" si="18"/>
-        <v>Fu</v>
+        <f t="shared" si="22"/>
+        <v>DosSantos_etal_2020</v>
+      </c>
+      <c r="E19" s="2" t="str">
+        <f t="shared" si="23"/>
+        <v>DosSantos</v>
       </c>
       <c r="F19" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G19" s="7" t="str">
-        <f t="shared" si="20"/>
-        <v>2013</v>
+      <c r="G19" s="2" t="str">
+        <f t="shared" si="25"/>
+        <v>2020</v>
       </c>
       <c r="H19" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1007/s00429-012-0462-x</v>
+        <f t="shared" si="26"/>
+        <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="J19" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K19" s="3" t="str">
-        <f t="shared" si="22"/>
-        <v>Fu_etal_2013_Table1</v>
-      </c>
-      <c r="L19" s="3" t="str">
+      <c r="K19" s="1" t="str">
+        <f t="shared" si="27"/>
+        <v>DosSantos_etal_2020_Table1</v>
+      </c>
+      <c r="L19" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
       </c>
       <c r="M19" t="str">
         <f t="array" ref="M19">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L19, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N19" s="13" t="s">
-        <v>358</v>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
       <c r="P19" s="13" t="s">
-        <v>125</v>
+        <v>41</v>
+      </c>
+      <c r="Q19" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R19" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="S19" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T19" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="U19" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="V19" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y19" s="13" t="s">
+        <v>98</v>
       </c>
       <c r="Z19" s="13" t="s">
-        <v>283</v>
-      </c>
-      <c r="AC19" s="13" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="20" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="AA19" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB19" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE19" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI19" s="13">
+        <v>4</v>
+      </c>
+      <c r="AK19" s="13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
-        <v>360</v>
+        <v>103</v>
       </c>
       <c r="C20" t="str">
-        <f t="shared" si="16"/>
-        <v>6</v>
+        <f t="shared" ref="C20" si="48">RIGHT(A20,1)</f>
+        <v>0</v>
       </c>
       <c r="D20" t="str">
-        <f t="shared" si="17"/>
-        <v>Garwicz_etal_2009</v>
+        <f t="shared" ref="D20" si="49">E20 &amp; IF(F20&lt;&gt;"", "_" &amp; F20, "_") &amp; IF(G20&lt;&gt;"", "_" &amp; G20, "_") &amp; IF(B20&lt;&gt;"", "_" &amp; B20, "")</f>
+        <v>DosSantos_etal_2020</v>
       </c>
       <c r="E20" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Garwicz</v>
+        <f t="shared" ref="E20" si="50">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A20,","), "-", ""), " ", "")</f>
+        <v>DosSantos</v>
       </c>
       <c r="F20" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F20" si="51">IF(ISNUMBER(FIND("&amp;", A20)),
+    IF(LEN(A20)-LEN(SUBSTITUTE(A20, ",", ""))&gt;=6, "etal", MID(A20, SEARCH("&amp; ", A20)+2, SEARCH(",", A20, SEARCH("&amp; ", A20)+2) - SEARCH("&amp; ", A20)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
       <c r="G20" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2009</v>
+        <f t="shared" ref="G20" si="52">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A20, "("), ")")</f>
+        <v>2020</v>
       </c>
       <c r="H20" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1073/pnas.0905777106</v>
+        <f t="shared" ref="H20" si="53">_xlfn.TEXTAFTER(A20,"https://doi.org/")</f>
+        <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K20" t="str">
-        <f t="shared" si="22"/>
-        <v>Garwicz_etal_2009_TableS1</v>
-      </c>
-      <c r="L20" t="str">
-        <f t="shared" si="7"/>
-        <v>10.1073%2Fpnas.0905777106_TableS1</v>
+        <v>372</v>
+      </c>
+      <c r="K20" s="1" t="str">
+        <f t="shared" ref="K20" si="54">TRIM(_xlfn.TEXTJOIN("_",FALSE,D20,(SUBSTITUTE(SUBSTITUTE(J20," ",""), "_", ""))))</f>
+        <v>DosSantos_etal_2020_unpublished</v>
+      </c>
+      <c r="L20" s="1" t="str">
+        <f t="shared" ref="L20" si="55">IF(ISBLANK(I20),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H20, SUBSTITUTE(J20,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I20, SUBSTITUTE(J20,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished</v>
       </c>
       <c r="M20" t="str">
         <f t="array" ref="M20">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L20, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N20" s="13" t="s">
-        <v>361</v>
+      <c r="P20" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q20" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R20" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="S20" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T20" s="13" t="s">
+        <v>105</v>
       </c>
       <c r="U20" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="W20" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X20" s="16" t="s">
-        <v>365</v>
+        <v>106</v>
+      </c>
+      <c r="V20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y20" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z20" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AA20" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AB20" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE20" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AI20" s="13">
+        <v>4</v>
+      </c>
+      <c r="AK20" s="13">
+        <v>10</v>
       </c>
     </row>
     <row r="21" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="C21" t="str">
-        <f t="shared" si="16"/>
-        <v>6</v>
+        <f t="shared" si="21"/>
+        <v>5</v>
       </c>
       <c r="D21" t="str">
-        <f t="shared" si="17"/>
-        <v>Garwicz_etal_2009</v>
+        <f t="shared" si="22"/>
+        <v>Falcone_etal_2019</v>
       </c>
       <c r="E21" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Garwicz</v>
+        <f t="shared" si="23"/>
+        <v>Falcone</v>
       </c>
       <c r="F21" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
       <c r="G21" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2009</v>
+        <f t="shared" si="25"/>
+        <v>2019</v>
       </c>
       <c r="H21" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1073/pnas.0905777106</v>
+        <f t="shared" si="26"/>
+        <v>10.1002/cne.24605</v>
       </c>
       <c r="J21" s="13" t="s">
-        <v>220</v>
+        <v>152</v>
       </c>
       <c r="K21" t="str">
-        <f t="shared" si="22"/>
-        <v>Garwicz_etal_2009_TableS2</v>
+        <f t="shared" si="27"/>
+        <v>Falcone_etal_2019_TABLE1</v>
       </c>
       <c r="L21" t="str">
         <f t="shared" si="7"/>
-        <v>10.1073%2Fpnas.0905777106_TableS2</v>
+        <v>10.1002%2Fcne.24605_TABLE1</v>
       </c>
       <c r="M21" t="str">
         <f t="array" ref="M21">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N21" s="13" t="s">
-        <v>359</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="R21" s="14"/>
       <c r="U21" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="W21" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X21" s="16" t="s">
-        <v>365</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
-        <v>343</v>
+        <v>366</v>
       </c>
       <c r="C22" t="str">
-        <f t="shared" si="16"/>
-        <v>0</v>
+        <f t="shared" ref="C22" si="56">RIGHT(A22,1)</f>
+        <v>5</v>
       </c>
       <c r="D22" t="str">
-        <f t="shared" si="17"/>
-        <v>Genoud_etal_2018</v>
-      </c>
-      <c r="E22" s="7" t="str">
-        <f t="shared" si="18"/>
-        <v>Genoud</v>
+        <f t="shared" ref="D22" si="57">E22 &amp; IF(F22&lt;&gt;"", "_" &amp; F22, "_") &amp; IF(G22&lt;&gt;"", "_" &amp; G22, "_") &amp; IF(B22&lt;&gt;"", "_" &amp; B22, "")</f>
+        <v>Falcone_etal_2019</v>
+      </c>
+      <c r="E22" s="2" t="str">
+        <f t="shared" ref="E22" si="58">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A22,","), "-", ""), " ", "")</f>
+        <v>Falcone</v>
       </c>
       <c r="F22" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F22" si="59">IF(ISNUMBER(FIND("&amp;", A22)),
+    IF(LEN(A22)-LEN(SUBSTITUTE(A22, ",", ""))&gt;=6, "etal", MID(A22, SEARCH("&amp; ", A22)+2, SEARCH(",", A22, SEARCH("&amp; ", A22)+2) - SEARCH("&amp; ", A22)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
-      <c r="G22" s="7" t="str">
-        <f t="shared" si="20"/>
-        <v>2018</v>
+      <c r="G22" s="2" t="str">
+        <f t="shared" ref="G22" si="60">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A22, "("), ")")</f>
+        <v>2019</v>
       </c>
       <c r="H22" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1111/brv.12350</v>
+        <f t="shared" ref="H22" si="61">_xlfn.TEXTAFTER(A22,"https://doi.org/")</f>
+        <v>10.1002/cne.24605</v>
       </c>
       <c r="J22" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="K22" s="3" t="str">
-        <f t="shared" si="22"/>
-        <v>Genoud_etal_2018_TableS2</v>
-      </c>
-      <c r="L22" s="3" t="str">
-        <f t="shared" si="7"/>
-        <v>10.1111%2Fbrv.12350_TableS2</v>
+        <v>158</v>
+      </c>
+      <c r="K22" t="str">
+        <f t="shared" ref="K22" si="62">TRIM(_xlfn.TEXTJOIN("_",FALSE,D22,(SUBSTITUTE(SUBSTITUTE(J22," ",""), "_", ""))))</f>
+        <v>Falcone_etal_2019_TABLE2</v>
+      </c>
+      <c r="L22" t="str">
+        <f t="shared" ref="L22" si="63">IF(ISBLANK(I22),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H22, SUBSTITUTE(J22,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I22, SUBSTITUTE(J22,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1002%2Fcne.24605_TABLE2</v>
       </c>
       <c r="M22" t="str">
         <f t="array" ref="M22">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L22, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N22" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="P22" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC22" s="13" t="s">
-        <v>282</v>
+        <v>368</v>
+      </c>
+      <c r="R22" s="14"/>
+      <c r="U22" s="13" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="23" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
-        <v>349</v>
+        <v>109</v>
       </c>
       <c r="C23" t="str">
-        <f t="shared" si="16"/>
-        <v>8</v>
+        <f t="shared" si="21"/>
+        <v>6</v>
       </c>
       <c r="D23" t="str">
-        <f t="shared" si="17"/>
-        <v>Granatosky__2018</v>
-      </c>
-      <c r="E23" s="7" t="str">
-        <f t="shared" si="18"/>
-        <v>Granatosky</v>
+        <f t="shared" si="22"/>
+        <v>Finlay_etal_2006</v>
+      </c>
+      <c r="E23" s="2" t="str">
+        <f t="shared" si="23"/>
+        <v>Finlay</v>
       </c>
       <c r="F23" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v/>
-      </c>
-      <c r="G23" s="7" t="str">
-        <f t="shared" si="20"/>
-        <v>2018</v>
+        <f t="shared" si="24"/>
+        <v>etal</v>
+      </c>
+      <c r="G23" s="2" t="str">
+        <f t="shared" si="25"/>
+        <v>2006</v>
       </c>
       <c r="H23" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1111/jzo.12608</v>
+        <f t="shared" si="26"/>
+        <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="J23" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K23" s="3" t="str">
-        <f t="shared" si="22"/>
-        <v>Granatosky__2018_TableS1</v>
-      </c>
-      <c r="L23" s="3" t="str">
+        <v>110</v>
+      </c>
+      <c r="K23" s="1" t="str">
+        <f t="shared" si="27"/>
+        <v>Finlay_etal_2006_Table6.1</v>
+      </c>
+      <c r="L23" s="1" t="str">
         <f t="shared" si="7"/>
-        <v>10.1111%2Fjzo.12608_TableS1</v>
+        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
       <c r="M23" t="str">
         <f t="array" ref="M23">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L23, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N23" s="13" t="s">
-        <v>336</v>
-      </c>
+        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
+      </c>
+      <c r="N23" s="17"/>
       <c r="P23" s="13" t="s">
-        <v>125</v>
+        <v>74</v>
+      </c>
+      <c r="Q23" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R23" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="S23" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T23" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="U23" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="V23" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W23" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X23" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="Y23" s="13" t="s">
+        <v>115</v>
+      </c>
+      <c r="Z23" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD23" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="AE23" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI23" s="13">
+        <v>3</v>
+      </c>
+      <c r="AK23" s="13">
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
-        <v>117</v>
+        <v>346</v>
       </c>
       <c r="C24" t="str">
-        <f t="shared" si="16"/>
-        <v>1</v>
+        <f t="shared" si="21"/>
+        <v>x</v>
       </c>
       <c r="D24" t="str">
-        <f t="shared" si="17"/>
-        <v>Heffner_Masterton_1975</v>
-      </c>
-      <c r="E24" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Heffner</v>
+        <f t="shared" si="22"/>
+        <v>Fu_etal_2013</v>
+      </c>
+      <c r="E24" s="7" t="str">
+        <f t="shared" si="23"/>
+        <v>Fu</v>
       </c>
       <c r="F24" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Masterton</v>
-      </c>
-      <c r="G24" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>1975</v>
+        <f t="shared" si="24"/>
+        <v>etal</v>
+      </c>
+      <c r="G24" s="7" t="str">
+        <f t="shared" si="25"/>
+        <v>2013</v>
       </c>
       <c r="H24" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1159/000124401</v>
+        <f t="shared" si="26"/>
+        <v>10.1007/s00429-012-0462-x</v>
       </c>
       <c r="J24" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="K24" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>Heffner_Masterton_1975_TableI</v>
-      </c>
-      <c r="L24" s="1" t="str">
+        <v>52</v>
+      </c>
+      <c r="K24" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>Fu_etal_2013_Table1</v>
+      </c>
+      <c r="L24" s="3" t="str">
         <f t="shared" si="7"/>
-        <v>10.1159%2F000124401_TableI</v>
+        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
       </c>
       <c r="M24" t="str">
         <f t="array" ref="M24">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L24, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000124401_TableI.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N24" s="13" t="s">
+        <v>358</v>
       </c>
       <c r="P24" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q24" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R24" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="S24" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T24" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="U24" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V24" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W24" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y24" s="13" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="Z24" s="13" t="s">
-        <v>122</v>
+        <v>283</v>
       </c>
       <c r="AC24" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE24" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AI24" s="13">
-        <v>7</v>
-      </c>
-      <c r="AK24" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="13" t="s">
-        <v>124</v>
+        <v>360</v>
       </c>
       <c r="C25" t="str">
-        <f t="shared" si="16"/>
-        <v>4</v>
+        <f t="shared" si="21"/>
+        <v>6</v>
       </c>
       <c r="D25" t="str">
-        <f t="shared" si="17"/>
-        <v>Heffner_Masterton_1983</v>
+        <f t="shared" si="22"/>
+        <v>Garwicz_etal_2009</v>
       </c>
       <c r="E25" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Heffner</v>
+        <f t="shared" si="23"/>
+        <v>Garwicz</v>
       </c>
       <c r="F25" s="2" t="str">
-        <f t="shared" si="19"/>
-        <v>Masterton</v>
+        <f t="shared" si="24"/>
+        <v>etal</v>
       </c>
       <c r="G25" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>1983</v>
+        <f t="shared" si="25"/>
+        <v>2009</v>
       </c>
       <c r="H25" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1159/000121494</v>
+        <f t="shared" si="26"/>
+        <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="J25" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="K25" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>Heffner_Masterton_1983_TableI</v>
-      </c>
-      <c r="L25" s="1" t="str">
+        <v>91</v>
+      </c>
+      <c r="K25" t="str">
+        <f t="shared" si="27"/>
+        <v>Garwicz_etal_2009_TableS1</v>
+      </c>
+      <c r="L25" t="str">
         <f t="shared" si="7"/>
-        <v>10.1159%2F000121494_TableI</v>
+        <v>10.1073%2Fpnas.0905777106_TableS1</v>
       </c>
       <c r="M25" t="str">
         <f t="array" ref="M25">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L25, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P25" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q25" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R25" s="14"/>
-      <c r="T25" s="13" t="str">
-        <f>IF(S25="N", R25, "write file name")</f>
-        <v>write file name</v>
+      <c r="N25" s="13" t="s">
+        <v>361</v>
       </c>
       <c r="U25" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V25" s="13" t="s">
-        <v>46</v>
-      </c>
       <c r="W25" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y25" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="AE25" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="AG25" s="13" t="s">
-        <v>126</v>
+        <v>68</v>
+      </c>
+      <c r="X25" s="16" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="26" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="13" t="s">
-        <v>127</v>
+        <v>360</v>
       </c>
       <c r="C26" t="str">
-        <f t="shared" si="16"/>
-        <v>8</v>
+        <f t="shared" si="21"/>
+        <v>6</v>
       </c>
       <c r="D26" t="str">
-        <f t="shared" si="17"/>
-        <v>Heldstab_etal_2016</v>
+        <f t="shared" si="22"/>
+        <v>Garwicz_etal_2009</v>
       </c>
       <c r="E26" s="2" t="str">
-        <f t="shared" si="18"/>
-        <v>Heldstab</v>
+        <f t="shared" si="23"/>
+        <v>Garwicz</v>
       </c>
       <c r="F26" s="2" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
       <c r="G26" s="2" t="str">
-        <f t="shared" si="20"/>
-        <v>2016</v>
+        <f t="shared" si="25"/>
+        <v>2009</v>
       </c>
       <c r="H26" t="str">
-        <f t="shared" si="21"/>
-        <v>10.1038/srep24528</v>
+        <f t="shared" si="26"/>
+        <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="J26" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K26" s="1" t="str">
-        <f t="shared" si="22"/>
-        <v>Heldstab_etal_2016_TableS1</v>
-      </c>
-      <c r="L26" s="1" t="str">
+        <v>220</v>
+      </c>
+      <c r="K26" t="str">
+        <f t="shared" si="27"/>
+        <v>Garwicz_etal_2009_TableS2</v>
+      </c>
+      <c r="L26" t="str">
         <f t="shared" si="7"/>
-        <v>10.1038%2Fsrep24528_TableS1</v>
+        <v>10.1073%2Fpnas.0905777106_TableS2</v>
       </c>
       <c r="M26" t="str">
         <f t="array" ref="M26">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L26, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P26" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q26" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R26" s="14"/>
-      <c r="T26" s="13" t="str">
-        <f>IF(S26="N", R26, "write file name")</f>
-        <v>write file name</v>
+      <c r="N26" s="13" t="s">
+        <v>359</v>
       </c>
       <c r="U26" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V26" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y26" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="AE26" s="13" t="s">
-        <v>64</v>
+      <c r="W26" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X26" s="16" t="s">
+        <v>365</v>
       </c>
     </row>
     <row r="27" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="13" t="s">
+        <v>343</v>
+      </c>
+      <c r="C27" t="str">
+        <f t="shared" si="21"/>
+        <v>0</v>
+      </c>
+      <c r="D27" t="str">
+        <f t="shared" si="22"/>
+        <v>Genoud_etal_2018</v>
+      </c>
+      <c r="E27" s="7" t="str">
+        <f t="shared" si="23"/>
+        <v>Genoud</v>
+      </c>
+      <c r="F27" s="2" t="str">
+        <f t="shared" si="24"/>
+        <v>etal</v>
+      </c>
+      <c r="G27" s="7" t="str">
+        <f t="shared" si="25"/>
+        <v>2018</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1111/brv.12350</v>
+      </c>
+      <c r="J27" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="K27" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>Genoud_etal_2018_TableS2</v>
+      </c>
+      <c r="L27" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1111%2Fbrv.12350_TableS2</v>
+      </c>
+      <c r="M27" t="str">
+        <f t="array" ref="M27">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L27, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N27" s="13" t="s">
+        <v>273</v>
+      </c>
+      <c r="P27" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC27" s="13" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="13" t="s">
+        <v>349</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="D28" t="str">
+        <f t="shared" si="22"/>
+        <v>Granatosky__2018</v>
+      </c>
+      <c r="E28" s="7" t="str">
+        <f t="shared" si="23"/>
+        <v>Granatosky</v>
+      </c>
+      <c r="F28" s="2" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="G28" s="7" t="str">
+        <f t="shared" si="25"/>
+        <v>2018</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1111/jzo.12608</v>
+      </c>
+      <c r="J28" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K28" s="3" t="str">
+        <f t="shared" si="27"/>
+        <v>Granatosky__2018_TableS1</v>
+      </c>
+      <c r="L28" s="3" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1111%2Fjzo.12608_TableS1</v>
+      </c>
+      <c r="M28" t="str">
+        <f t="array" ref="M28">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L28, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N28" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="P28" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="C29" t="str">
+        <f t="shared" si="21"/>
+        <v>1</v>
+      </c>
+      <c r="D29" t="str">
+        <f t="shared" si="22"/>
+        <v>Heffner_Masterton_1975</v>
+      </c>
+      <c r="E29" s="2" t="str">
+        <f t="shared" si="23"/>
+        <v>Heffner</v>
+      </c>
+      <c r="F29" s="2" t="str">
+        <f t="shared" si="24"/>
+        <v>Masterton</v>
+      </c>
+      <c r="G29" s="2" t="str">
+        <f t="shared" si="25"/>
+        <v>1975</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1159/000124401</v>
+      </c>
+      <c r="J29" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="K29" s="1" t="str">
+        <f t="shared" si="27"/>
+        <v>Heffner_Masterton_1975_TableI</v>
+      </c>
+      <c r="L29" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000124401_TableI</v>
+      </c>
+      <c r="M29" t="str">
+        <f t="array" ref="M29">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L29, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000124401_TableI.tsv</v>
+      </c>
+      <c r="P29" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q29" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R29" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="S29" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T29" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="U29" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V29" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W29" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y29" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="Z29" s="13" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC29" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="AE29" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AI29" s="13">
+        <v>7</v>
+      </c>
+      <c r="AK29" s="13">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="13" t="s">
+        <v>124</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="21"/>
+        <v>4</v>
+      </c>
+      <c r="D30" t="str">
+        <f t="shared" si="22"/>
+        <v>Heffner_Masterton_1983</v>
+      </c>
+      <c r="E30" s="2" t="str">
+        <f t="shared" si="23"/>
+        <v>Heffner</v>
+      </c>
+      <c r="F30" s="2" t="str">
+        <f t="shared" si="24"/>
+        <v>Masterton</v>
+      </c>
+      <c r="G30" s="2" t="str">
+        <f t="shared" si="25"/>
+        <v>1983</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1159/000121494</v>
+      </c>
+      <c r="J30" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="K30" s="1" t="str">
+        <f t="shared" si="27"/>
+        <v>Heffner_Masterton_1983_TableI</v>
+      </c>
+      <c r="L30" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1159%2F000121494_TableI</v>
+      </c>
+      <c r="M30" t="str">
+        <f t="array" ref="M30">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L30, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P30" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q30" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R30" s="14"/>
+      <c r="T30" s="13" t="str">
+        <f>IF(S30="N", R30, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U30" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V30" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W30" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="Y30" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE30" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG30" s="13" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C31" t="str">
+        <f t="shared" si="21"/>
+        <v>8</v>
+      </c>
+      <c r="D31" t="str">
+        <f t="shared" si="22"/>
+        <v>Heldstab_etal_2016</v>
+      </c>
+      <c r="E31" s="2" t="str">
+        <f t="shared" si="23"/>
+        <v>Heldstab</v>
+      </c>
+      <c r="F31" s="2" t="str">
+        <f t="shared" si="24"/>
+        <v>etal</v>
+      </c>
+      <c r="G31" s="2" t="str">
+        <f t="shared" si="25"/>
+        <v>2016</v>
+      </c>
+      <c r="H31" t="str">
+        <f t="shared" si="26"/>
+        <v>10.1038/srep24528</v>
+      </c>
+      <c r="J31" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="K31" s="1" t="str">
+        <f t="shared" si="27"/>
+        <v>Heldstab_etal_2016_TableS1</v>
+      </c>
+      <c r="L31" s="1" t="str">
+        <f t="shared" si="7"/>
+        <v>10.1038%2Fsrep24528_TableS1</v>
+      </c>
+      <c r="M31" t="str">
+        <f t="array" ref="M31">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P31" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q31" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R31" s="14"/>
+      <c r="T31" s="13" t="str">
+        <f>IF(S31="N", R31, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U31" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V31" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y31" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE31" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="C27" t="str">
-        <f t="shared" si="16"/>
+      <c r="C32" t="str">
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
-      <c r="D27" t="str">
-        <f t="shared" si="17"/>
+      <c r="D32" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
-      <c r="E27" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E32" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F27" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F32" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G27" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G32" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2013</v>
       </c>
-      <c r="H27" t="str">
-        <f t="shared" si="21"/>
+      <c r="H32" t="str">
+        <f t="shared" si="26"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="J27" s="13" t="s">
+      <c r="J32" s="13" t="s">
         <v>213</v>
       </c>
-      <c r="K27" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K32" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
-      <c r="L27" s="1" t="str">
+      <c r="L32" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
-      <c r="M27" t="str">
-        <f t="array" ref="M27">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L27, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M32" t="str">
+        <f t="array" ref="M32">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
-      <c r="Q27" s="13" t="s">
+      <c r="Q32" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AI27" s="13" t="s">
+      <c r="AI32" s="13" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="28" spans="1:37" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="13" t="s">
+    <row r="33" spans="1:37" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="C28" t="str">
-        <f t="shared" si="16"/>
+      <c r="C33" t="str">
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
-      <c r="D28" t="str">
-        <f t="shared" si="17"/>
+      <c r="D33" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
-      <c r="E28" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E33" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F28" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F33" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G28" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G33" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2013</v>
       </c>
-      <c r="H28" t="str">
-        <f t="shared" si="21"/>
+      <c r="H33" t="str">
+        <f t="shared" si="26"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="J28" s="13" t="s">
+      <c r="J33" s="13" t="s">
         <v>215</v>
       </c>
-      <c r="K28" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K33" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
-      <c r="L28" s="1" t="str">
+      <c r="L33" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
-      <c r="M28" t="str">
-        <f t="array" ref="M28">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L28, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M33" t="str">
+        <f t="array" ref="M33">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
-      <c r="Q28" s="13" t="s">
+      <c r="Q33" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AI28" s="13" t="s">
+      <c r="AI33" s="13" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="29" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="13" t="s">
+    <row r="34" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="13" t="s">
         <v>212</v>
       </c>
-      <c r="C29" t="str">
-        <f t="shared" si="16"/>
+      <c r="C34" t="str">
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
-      <c r="D29" t="str">
-        <f t="shared" si="17"/>
+      <c r="D34" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2013</v>
       </c>
-      <c r="E29" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E34" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F29" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F34" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G29" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G34" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2013</v>
       </c>
-      <c r="H29" t="str">
-        <f t="shared" si="21"/>
+      <c r="H34" t="str">
+        <f t="shared" si="26"/>
         <v>10.3389/fnana.2013.00035</v>
       </c>
-      <c r="J29" s="13" t="s">
+      <c r="J34" s="13" t="s">
         <v>216</v>
       </c>
-      <c r="K29" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K34" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
-      <c r="L29" s="1" t="str">
+      <c r="L34" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
-      <c r="M29" t="str">
-        <f t="array" ref="M29">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L29, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M34" t="str">
+        <f t="array" ref="M34">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
-      <c r="Q29" s="13" t="s">
+      <c r="Q34" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AI29" s="13" t="s">
+      <c r="AI34" s="13" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="30" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="13" t="s">
+    <row r="35" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C30" t="str">
-        <f t="shared" si="16"/>
+      <c r="C35" t="str">
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
-      <c r="D30" t="str">
-        <f t="shared" si="17"/>
+      <c r="D35" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="E30" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E35" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F30" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F35" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G30" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G35" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2015</v>
       </c>
-      <c r="H30" t="str">
-        <f t="shared" si="21"/>
+      <c r="H35" t="str">
+        <f t="shared" si="26"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="J30" s="13" t="s">
+      <c r="J35" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K30" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K35" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
-      <c r="L30" s="1" t="str">
+      <c r="L35" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1159%2F000437413_Table1</v>
       </c>
-      <c r="M30" t="str">
-        <f t="array" ref="M30">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L30, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M35" t="str">
+        <f t="array" ref="M35">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
-      <c r="N30" s="13" t="s">
+      <c r="N35" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="P30" s="13" t="s">
+      <c r="P35" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q30" s="13" t="s">
+      <c r="Q35" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="R30" s="14" t="s">
+      <c r="R35" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="S30" s="13" t="s">
+      <c r="S35" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="T30" s="13" t="s">
+      <c r="T35" s="13" t="s">
         <v>131</v>
       </c>
-      <c r="U30" s="13" t="s">
+      <c r="U35" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V30" s="13" t="s">
+      <c r="V35" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W30" s="13" t="s">
+      <c r="W35" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="X30" s="13" t="s">
+      <c r="X35" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="Y30" s="13" t="s">
+      <c r="Y35" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="AA30" s="13" t="s">
+      <c r="AA35" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB30" s="13" t="s">
+      <c r="AB35" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AE30" s="13" t="s">
+      <c r="AE35" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AI30" s="13">
+      <c r="AI35" s="13">
         <v>9</v>
       </c>
-      <c r="AK30" s="13">
+      <c r="AK35" s="13">
         <v>15</v>
       </c>
     </row>
-    <row r="31" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="13" t="s">
+    <row r="36" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C31" t="str">
-        <f t="shared" si="16"/>
+      <c r="C36" t="str">
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
-      <c r="D31" t="str">
-        <f t="shared" si="17"/>
+      <c r="D36" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="E31" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E36" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F31" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F36" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G31" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G36" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2015</v>
       </c>
-      <c r="H31" t="str">
-        <f t="shared" si="21"/>
+      <c r="H36" t="str">
+        <f t="shared" si="26"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="J31" s="13" t="s">
+      <c r="J36" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="K31" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K36" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
-      <c r="L31" s="1" t="str">
+      <c r="L36" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1159%2F000437413_Table2</v>
       </c>
-      <c r="M31" t="str">
-        <f t="array" ref="M31">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M36" t="str">
+        <f t="array" ref="M36">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
-      <c r="N31" s="13" t="s">
+      <c r="N36" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="P31" s="13" t="s">
+      <c r="P36" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q31" s="13" t="s">
+      <c r="Q36" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="R31" s="14" t="s">
+      <c r="R36" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="S31" s="13" t="s">
+      <c r="S36" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="T31" s="13" t="s">
+      <c r="T36" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="U31" s="13" t="s">
+      <c r="U36" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V31" s="13" t="s">
+      <c r="V36" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W31" s="13" t="s">
+      <c r="W36" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="X31" s="13" t="s">
+      <c r="X36" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="Y31" s="13" t="s">
+      <c r="Y36" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="AA31" s="13" t="s">
+      <c r="AA36" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB31" s="13" t="s">
+      <c r="AB36" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AE31" s="13" t="s">
+      <c r="AE36" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AI31" s="13">
+      <c r="AI36" s="13">
         <v>9</v>
       </c>
-      <c r="AK31" s="13">
+      <c r="AK36" s="13">
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="13" t="s">
+    <row r="37" spans="1:37" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C32" t="str">
-        <f t="shared" si="16"/>
+      <c r="C37" t="str">
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
-      <c r="D32" t="str">
-        <f t="shared" si="17"/>
+      <c r="D37" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="E32" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E37" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F32" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F37" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G32" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G37" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2015</v>
       </c>
-      <c r="H32" t="str">
-        <f t="shared" si="21"/>
+      <c r="H37" t="str">
+        <f t="shared" si="26"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="J32" s="13" t="s">
+      <c r="J37" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="K32" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K37" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
-      <c r="L32" s="1" t="str">
+      <c r="L37" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1159%2F000437413_Table3</v>
       </c>
-      <c r="M32" t="str">
-        <f t="array" ref="M32">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M37" t="str">
+        <f t="array" ref="M37">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
-      <c r="N32" s="13" t="s">
+      <c r="N37" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="P32" s="13" t="s">
+      <c r="P37" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q32" s="13" t="s">
+      <c r="Q37" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="R32" s="14" t="s">
+      <c r="R37" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="S32" s="13" t="s">
+      <c r="S37" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="T32" s="13" t="s">
+      <c r="T37" s="13" t="s">
         <v>141</v>
       </c>
-      <c r="U32" s="13" t="s">
+      <c r="U37" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V32" s="13" t="s">
+      <c r="V37" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W32" s="13" t="s">
+      <c r="W37" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="X32" s="13" t="s">
+      <c r="X37" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="Y32" s="13" t="s">
+      <c r="Y37" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="AA32" s="13" t="s">
+      <c r="AA37" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB32" s="13" t="s">
+      <c r="AB37" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AE32" s="13" t="s">
+      <c r="AE37" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AI32" s="13">
+      <c r="AI37" s="13">
         <v>9</v>
       </c>
-      <c r="AK32" s="13">
+      <c r="AK37" s="13">
         <v>15</v>
       </c>
     </row>
-    <row r="33" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="13" t="s">
+    <row r="38" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C33" t="str">
-        <f t="shared" si="16"/>
+      <c r="C38" t="str">
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
-      <c r="D33" t="str">
-        <f t="shared" si="17"/>
+      <c r="D38" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="E33" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E38" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F33" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F38" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G33" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G38" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2015</v>
       </c>
-      <c r="H33" t="str">
-        <f t="shared" si="21"/>
+      <c r="H38" t="str">
+        <f t="shared" si="26"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="J33" s="13" t="s">
+      <c r="J38" s="13" t="s">
         <v>143</v>
       </c>
-      <c r="K33" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K38" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
-      <c r="L33" s="1" t="str">
+      <c r="L38" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1159%2F000437413_Table4</v>
       </c>
-      <c r="M33" t="str">
-        <f t="array" ref="M33">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M38" t="str">
+        <f t="array" ref="M38">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
-      <c r="N33" s="13" t="s">
+      <c r="N38" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="P33" s="13" t="s">
+      <c r="P38" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q33" s="13" t="s">
+      <c r="Q38" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="R33" s="14" t="s">
+      <c r="R38" s="14" t="s">
         <v>144</v>
       </c>
-      <c r="S33" s="13" t="s">
+      <c r="S38" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="T33" s="13" t="s">
+      <c r="T38" s="13" t="s">
         <v>145</v>
       </c>
-      <c r="U33" s="13" t="s">
+      <c r="U38" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V33" s="13" t="s">
+      <c r="V38" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W33" s="13" t="s">
+      <c r="W38" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="X33" s="13" t="s">
+      <c r="X38" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="Y33" s="13" t="s">
+      <c r="Y38" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="AA33" s="13" t="s">
+      <c r="AA38" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB33" s="13" t="s">
+      <c r="AB38" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AE33" s="13" t="s">
+      <c r="AE38" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AI33" s="13">
+      <c r="AI38" s="13">
         <v>8</v>
       </c>
-      <c r="AK33" s="13">
+      <c r="AK38" s="13">
         <v>12</v>
       </c>
     </row>
-    <row r="34" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="13" t="s">
+    <row r="39" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="C34" t="str">
-        <f t="shared" si="16"/>
+      <c r="C39" t="str">
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
-      <c r="D34" t="str">
-        <f t="shared" si="17"/>
+      <c r="D39" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
-      <c r="E34" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E39" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F34" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F39" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G34" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G39" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2015</v>
       </c>
-      <c r="H34" t="str">
-        <f t="shared" si="21"/>
+      <c r="H39" t="str">
+        <f t="shared" si="26"/>
         <v>10.1159/000437413</v>
       </c>
-      <c r="J34" s="13" t="s">
+      <c r="J39" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="K34" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K39" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
-      <c r="L34" s="1" t="str">
+      <c r="L39" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1159%2F000437413_Table5</v>
       </c>
-      <c r="M34" t="str">
-        <f t="array" ref="M34">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M39" t="str">
+        <f t="array" ref="M39">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1159%2F000437413_Table5.tsv</v>
       </c>
-      <c r="N34" s="13" t="s">
+      <c r="N39" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="P34" s="13" t="s">
+      <c r="P39" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q34" s="13" t="s">
+      <c r="Q39" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="R34" s="14" t="s">
+      <c r="R39" s="14" t="s">
         <v>148</v>
       </c>
-      <c r="S34" s="13" t="s">
+      <c r="S39" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="T34" s="13" t="s">
+      <c r="T39" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="U34" s="13" t="s">
+      <c r="U39" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V34" s="13" t="s">
+      <c r="V39" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W34" s="13" t="s">
+      <c r="W39" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="X34" s="13" t="s">
+      <c r="X39" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="Y34" s="13" t="s">
+      <c r="Y39" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="AA34" s="13" t="s">
+      <c r="AA39" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB34" s="13" t="s">
+      <c r="AB39" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AE34" s="13" t="s">
+      <c r="AE39" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="AI34" s="13">
+      <c r="AI39" s="13">
         <v>9</v>
       </c>
-      <c r="AK34" s="13">
+      <c r="AK39" s="13">
         <v>15</v>
       </c>
     </row>
-    <row r="35" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="13" t="s">
+    <row r="40" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="C35" t="str">
-        <f t="shared" si="16"/>
+      <c r="C40" t="str">
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
-      <c r="D35" t="str">
-        <f t="shared" si="17"/>
+      <c r="D40" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
-      <c r="E35" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E40" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F35" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F40" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G35" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G40" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2020</v>
       </c>
-      <c r="H35" t="str">
-        <f t="shared" si="21"/>
+      <c r="H40" t="str">
+        <f t="shared" si="26"/>
         <v>10.1002/cne.24985</v>
       </c>
-      <c r="J35" s="13" t="s">
+      <c r="J40" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="K35" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K40" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
-      <c r="L35" s="1" t="str">
+      <c r="L40" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
-      <c r="M35" t="str">
-        <f t="array" ref="M35">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M40" t="str">
+        <f t="array" ref="M40">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
       </c>
-      <c r="N35" s="13" t="s">
+      <c r="N40" s="13" t="s">
         <v>155</v>
       </c>
-      <c r="P35" s="13" t="s">
+      <c r="P40" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q35" s="13" t="s">
+      <c r="Q40" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="R35" s="14" t="s">
+      <c r="R40" s="14" t="s">
         <v>153</v>
       </c>
-      <c r="S35" s="13" t="s">
+      <c r="S40" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="T35" s="13" t="s">
+      <c r="T40" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="U35" s="13" t="s">
+      <c r="U40" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V35" s="13" t="s">
+      <c r="V40" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W35" s="13" t="s">
+      <c r="W40" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="Y35" s="13" t="s">
+      <c r="Y40" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="AA35" s="13" t="s">
+      <c r="AA40" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB35" s="13" t="s">
+      <c r="AB40" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AE35" s="13" t="s">
+      <c r="AE40" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AI35" s="13">
+      <c r="AI40" s="13">
         <v>0</v>
       </c>
-      <c r="AJ35" s="13">
+      <c r="AJ40" s="13">
         <v>0</v>
       </c>
-      <c r="AK35" s="13">
+      <c r="AK40" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="13" t="s">
+    <row r="41" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="13" t="s">
         <v>151</v>
       </c>
-      <c r="C36" t="str">
-        <f t="shared" si="16"/>
+      <c r="C41" t="str">
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
-      <c r="D36" t="str">
-        <f t="shared" si="17"/>
+      <c r="D41" t="str">
+        <f t="shared" si="22"/>
         <v>HerculanoHouzel_etal_2020</v>
       </c>
-      <c r="E36" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E41" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>HerculanoHouzel</v>
       </c>
-      <c r="F36" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F41" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G36" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G41" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2020</v>
       </c>
-      <c r="H36" t="str">
-        <f t="shared" si="21"/>
+      <c r="H41" t="str">
+        <f t="shared" si="26"/>
         <v>10.1002/cne.24985</v>
       </c>
-      <c r="J36" s="13" t="s">
+      <c r="J41" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="K36" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K41" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>HerculanoHouzel_etal_2020_TABLE2</v>
       </c>
-      <c r="L36" s="1" t="str">
+      <c r="L41" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1002%2Fcne.24985_TABLE2</v>
       </c>
-      <c r="M36" t="str">
-        <f t="array" ref="M36">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M41" t="str">
+        <f t="array" ref="M41">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
       </c>
-      <c r="N36" s="13" t="s">
+      <c r="N41" s="13" t="s">
         <v>161</v>
       </c>
-      <c r="P36" s="13" t="s">
+      <c r="P41" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="Q36" s="13" t="s">
+      <c r="Q41" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="R36" s="14" t="s">
+      <c r="R41" s="14" t="s">
         <v>159</v>
       </c>
-      <c r="S36" s="13" t="s">
+      <c r="S41" s="13" t="s">
         <v>55</v>
       </c>
-      <c r="T36" s="13" t="s">
+      <c r="T41" s="13" t="s">
         <v>160</v>
       </c>
-      <c r="U36" s="13" t="s">
+      <c r="U41" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="V36" s="13" t="s">
+      <c r="V41" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W36" s="13" t="s">
+      <c r="W41" s="13" t="s">
         <v>78</v>
       </c>
-      <c r="Y36" s="13" t="s">
+      <c r="Y41" s="13" t="s">
         <v>162</v>
       </c>
-      <c r="AA36" s="13" t="s">
+      <c r="AA41" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AB36" s="13" t="s">
+      <c r="AB41" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="AE36" s="13" t="s">
+      <c r="AE41" s="13" t="s">
         <v>157</v>
       </c>
-      <c r="AI36" s="13">
+      <c r="AI41" s="13">
         <v>0</v>
       </c>
-      <c r="AJ36" s="13">
+      <c r="AJ41" s="13">
         <v>0</v>
       </c>
-      <c r="AK36" s="13">
+      <c r="AK41" s="13">
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="13" t="s">
+    <row r="42" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C37" t="str">
-        <f t="shared" si="16"/>
+      <c r="C42" t="str">
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="D37" t="str">
-        <f t="shared" si="17"/>
+      <c r="D42" t="str">
+        <f t="shared" si="22"/>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="E37" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E42" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>Isler</v>
       </c>
-      <c r="F37" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F42" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G37" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G42" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2008</v>
       </c>
-      <c r="H37" t="str">
-        <f t="shared" si="21"/>
+      <c r="H42" t="str">
+        <f t="shared" si="26"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="J37" s="13" t="s">
+      <c r="J42" s="13" t="s">
         <v>135</v>
       </c>
-      <c r="K37" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K42" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>Isler_etal_2008_Table2</v>
       </c>
-      <c r="L37" s="1" t="str">
+      <c r="L42" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
       </c>
-      <c r="M37" t="str">
-        <f t="array" ref="M37">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M42" t="str">
+        <f t="array" ref="M42">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
       </c>
-      <c r="Q37" s="13" t="s">
+      <c r="Q42" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AI37" s="13">
+      <c r="AI42" s="13">
         <v>6</v>
       </c>
-      <c r="AK37" s="13">
+      <c r="AK42" s="13">
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="13" t="s">
+    <row r="43" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C38" t="str">
-        <f t="shared" si="16"/>
+      <c r="C43" t="str">
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="D38" t="str">
-        <f t="shared" si="17"/>
+      <c r="D43" t="str">
+        <f t="shared" si="22"/>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="E38" s="2" t="str">
-        <f t="shared" si="18"/>
+      <c r="E43" s="2" t="str">
+        <f t="shared" si="23"/>
         <v>Isler</v>
       </c>
-      <c r="F38" s="2" t="str">
-        <f t="shared" si="19"/>
+      <c r="F43" s="2" t="str">
+        <f t="shared" si="24"/>
         <v>etal</v>
       </c>
-      <c r="G38" s="2" t="str">
-        <f t="shared" si="20"/>
+      <c r="G43" s="2" t="str">
+        <f t="shared" si="25"/>
         <v>2008</v>
       </c>
-      <c r="H38" t="str">
-        <f t="shared" si="21"/>
+      <c r="H43" t="str">
+        <f t="shared" si="26"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="J38" s="13" t="s">
+      <c r="J43" s="13" t="s">
         <v>218</v>
       </c>
-      <c r="K38" s="1" t="str">
-        <f t="shared" si="22"/>
+      <c r="K43" s="1" t="str">
+        <f t="shared" si="27"/>
         <v>Isler_etal_2008_Table7</v>
       </c>
-      <c r="L38" s="1" t="str">
+      <c r="L43" s="1" t="str">
         <f t="shared" si="7"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
       </c>
-      <c r="M38" t="str">
-        <f t="array" ref="M38">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+      <c r="M43" t="str">
+        <f t="array" ref="M43">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
-      <c r="Q38" s="13" t="s">
+      <c r="Q43" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AI38" s="13">
+      <c r="AI43" s="13">
         <v>3</v>
       </c>
-      <c r="AK38" s="13">
+      <c r="AK43" s="13">
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="13" t="s">
+    <row r="44" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="13" t="s">
         <v>217</v>
       </c>
-      <c r="C39" t="str">
-        <f t="shared" ref="C39:C69" si="39">RIGHT(A39,1)</f>
+      <c r="C44" t="str">
+        <f t="shared" ref="C44:C74" si="64">RIGHT(A44,1)</f>
         <v>4</v>
       </c>
-      <c r="D39" t="str">
-        <f t="shared" ref="D39:D69" si="40">E39 &amp; IF(F39&lt;&gt;"", "_" &amp; F39, "_") &amp; IF(G39&lt;&gt;"", "_" &amp; G39, "_") &amp; IF(B39&lt;&gt;"", "_" &amp; B39, "")</f>
+      <c r="D44" t="str">
+        <f t="shared" ref="D44:D74" si="65">E44 &amp; IF(F44&lt;&gt;"", "_" &amp; F44, "_") &amp; IF(G44&lt;&gt;"", "_" &amp; G44, "_") &amp; IF(B44&lt;&gt;"", "_" &amp; B44, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="E39" s="2" t="str">
-        <f t="shared" ref="E39:E69" si="41">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A39,","), "-", ""), " ", "")</f>
+      <c r="E44" s="2" t="str">
+        <f t="shared" ref="E44:E74" si="66">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A44,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="F39" s="2" t="str">
-        <f t="shared" ref="F39:F69" si="42">IF(ISNUMBER(FIND("&amp;", A39)),
-    IF(LEN(A39)-LEN(SUBSTITUTE(A39, ",", ""))&gt;=6, "etal", MID(A39, SEARCH("&amp; ", A39)+2, SEARCH(",", A39, SEARCH("&amp; ", A39)+2) - SEARCH("&amp; ", A39)-2)),
+      <c r="F44" s="2" t="str">
+        <f t="shared" ref="F44:F74" si="67">IF(ISNUMBER(FIND("&amp;", A44)),
+    IF(LEN(A44)-LEN(SUBSTITUTE(A44, ",", ""))&gt;=6, "etal", MID(A44, SEARCH("&amp; ", A44)+2, SEARCH(",", A44, SEARCH("&amp; ", A44)+2) - SEARCH("&amp; ", A44)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="G39" s="2" t="str">
-        <f t="shared" ref="G39:G69" si="43">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A39, "("), ")")</f>
+      <c r="G44" s="2" t="str">
+        <f t="shared" ref="G44:G74" si="68">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A44, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="H39" t="str">
-        <f t="shared" ref="H39:H69" si="44">_xlfn.TEXTAFTER(A39,"https://doi.org/")</f>
+      <c r="H44" t="str">
+        <f t="shared" ref="H44:H74" si="69">_xlfn.TEXTAFTER(A44,"https://doi.org/")</f>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="J39" s="13" t="s">
+      <c r="J44" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="K39" s="1" t="str">
-        <f t="shared" ref="K39:K69" si="45">TRIM(_xlfn.TEXTJOIN("_",FALSE,D39,(SUBSTITUTE(SUBSTITUTE(J39," ",""), "_", ""))))</f>
+      <c r="K44" s="1" t="str">
+        <f t="shared" ref="K44:K74" si="70">TRIM(_xlfn.TEXTJOIN("_",FALSE,D44,(SUBSTITUTE(SUBSTITUTE(J44," ",""), "_", ""))))</f>
         <v>Isler_etal_2008_TableS1</v>
       </c>
-      <c r="L39" s="1" t="str">
-        <f t="shared" ref="L39:L69" si="46">IF(ISBLANK(I39),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H39, SUBSTITUTE(J39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I39, SUBSTITUTE(J39,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+      <c r="L44" s="1" t="str">
+        <f t="shared" ref="L44:L74" si="71">IF(ISBLANK(I44),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, H44, SUBSTITUTE(J44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, I44, SUBSTITUTE(J44,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
-      </c>
-      <c r="M39" t="str">
-        <f t="array" ref="M39">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
-      </c>
-      <c r="Q39" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI39" s="13" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="40" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C40" t="str">
-        <f t="shared" si="39"/>
-        <v>4</v>
-      </c>
-      <c r="D40" t="str">
-        <f t="shared" si="40"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="E40" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Isler</v>
-      </c>
-      <c r="F40" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v>etal</v>
-      </c>
-      <c r="G40" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2008</v>
-      </c>
-      <c r="H40" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="J40" s="13" t="s">
-        <v>220</v>
-      </c>
-      <c r="K40" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Isler_etal_2008_TableS2</v>
-      </c>
-      <c r="L40" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
-      </c>
-      <c r="M40" t="str">
-        <f t="array" ref="M40">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
-      </c>
-      <c r="Q40" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI40" s="13">
-        <v>8</v>
-      </c>
-      <c r="AK40" s="13">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="41" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C41" t="str">
-        <f t="shared" si="39"/>
-        <v>4</v>
-      </c>
-      <c r="D41" t="str">
-        <f t="shared" si="40"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="E41" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Isler</v>
-      </c>
-      <c r="F41" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v>etal</v>
-      </c>
-      <c r="G41" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2008</v>
-      </c>
-      <c r="H41" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="J41" s="13" t="s">
-        <v>221</v>
-      </c>
-      <c r="K41" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Isler_etal_2008_TableS3</v>
-      </c>
-      <c r="L41" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
-      </c>
-      <c r="M41" t="str">
-        <f t="array" ref="M41">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
-      </c>
-      <c r="Q41" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI41" s="13">
-        <v>7</v>
-      </c>
-      <c r="AK41" s="13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="13" t="s">
-        <v>217</v>
-      </c>
-      <c r="C42" t="str">
-        <f t="shared" si="39"/>
-        <v>4</v>
-      </c>
-      <c r="D42" t="str">
-        <f t="shared" si="40"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="E42" s="5" t="str">
-        <f t="shared" si="41"/>
-        <v>Isler</v>
-      </c>
-      <c r="F42" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v>etal</v>
-      </c>
-      <c r="G42" s="5" t="str">
-        <f t="shared" si="43"/>
-        <v>2008</v>
-      </c>
-      <c r="H42" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="J42" s="13" t="s">
-        <v>222</v>
-      </c>
-      <c r="K42" s="4" t="str">
-        <f t="shared" si="45"/>
-        <v>Isler_etal_2008_Tree.nex</v>
-      </c>
-      <c r="L42" s="6" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
-      </c>
-      <c r="M42" t="str">
-        <f t="array" ref="M42">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="Q42" s="13" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="43" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C43" t="str">
-        <f t="shared" si="39"/>
-        <v>x</v>
-      </c>
-      <c r="D43" t="str">
-        <f t="shared" si="40"/>
-        <v>Iwaniuk_etal_1999</v>
-      </c>
-      <c r="E43" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="F43" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v>etal</v>
-      </c>
-      <c r="G43" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>1999</v>
-      </c>
-      <c r="H43" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016/s0166-4328(98)00151-x</v>
-      </c>
-      <c r="J43" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="K43" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>Iwaniuk_etal_1999_References</v>
-      </c>
-      <c r="L43" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
-      </c>
-      <c r="M43" t="str">
-        <f t="array" ref="M43">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N43" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="P43" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="V43" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="W43" s="13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="44" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C44" t="str">
-        <f t="shared" si="39"/>
-        <v>x</v>
-      </c>
-      <c r="D44" t="str">
-        <f t="shared" si="40"/>
-        <v>Iwaniuk_etal_1999</v>
-      </c>
-      <c r="E44" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>Iwaniuk</v>
-      </c>
-      <c r="F44" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v>etal</v>
-      </c>
-      <c r="G44" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>1999</v>
-      </c>
-      <c r="H44" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1016/s0166-4328(98)00151-x</v>
-      </c>
-      <c r="J44" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K44" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>Iwaniuk_etal_1999_Table1</v>
-      </c>
-      <c r="L44" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
       </c>
       <c r="M44" t="str">
         <f t="array" ref="M44">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L44, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N44" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="P44" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="V44" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W44" s="13" t="s">
-        <v>78</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
+      </c>
+      <c r="Q44" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI44" s="13" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="45" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="C45" t="str">
-        <f t="shared" si="39"/>
-        <v>9</v>
+        <f t="shared" si="64"/>
+        <v>4</v>
       </c>
       <c r="D45" t="str">
-        <f t="shared" si="40"/>
-        <v>Iwaniuk_etal_2001</v>
+        <f t="shared" si="65"/>
+        <v>Isler_etal_2008</v>
       </c>
       <c r="E45" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Iwaniuk</v>
+        <f t="shared" si="66"/>
+        <v>Isler</v>
       </c>
       <c r="F45" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G45" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2001</v>
+        <f t="shared" si="68"/>
+        <v>2008</v>
       </c>
       <c r="H45" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="69"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J45" s="13" t="s">
-        <v>52</v>
+        <v>220</v>
       </c>
       <c r="K45" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Iwaniuk_etal_2001_Table1</v>
+        <f t="shared" si="70"/>
+        <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="L45" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
+        <f t="shared" si="71"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="M45" t="str">
         <f t="array" ref="M45">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L45, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N45" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="P45" s="13" t="s">
-        <v>164</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
       </c>
       <c r="Q45" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R45" s="14"/>
-      <c r="T45" s="13" t="str">
-        <f>IF(S45="N", R45, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U45" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V45" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y45" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE45" s="13" t="s">
-        <v>167</v>
+        <v>42</v>
+      </c>
+      <c r="AI45" s="13">
+        <v>8</v>
+      </c>
+      <c r="AK45" s="13">
+        <v>11</v>
       </c>
     </row>
     <row r="46" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="C46" t="str">
-        <f t="shared" si="39"/>
-        <v>9</v>
+        <f t="shared" si="64"/>
+        <v>4</v>
       </c>
       <c r="D46" t="str">
-        <f t="shared" si="40"/>
-        <v>Iwaniuk_etal_2001</v>
+        <f t="shared" si="65"/>
+        <v>Isler_etal_2008</v>
       </c>
       <c r="E46" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Iwaniuk</v>
+        <f t="shared" si="66"/>
+        <v>Isler</v>
       </c>
       <c r="F46" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G46" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2001</v>
+        <f t="shared" si="68"/>
+        <v>2008</v>
       </c>
       <c r="H46" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="69"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J46" s="13" t="s">
-        <v>135</v>
+        <v>221</v>
       </c>
       <c r="K46" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Iwaniuk_etal_2001_Table2</v>
+        <f t="shared" si="70"/>
+        <v>Isler_etal_2008_TableS3</v>
       </c>
       <c r="L46" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
+        <f t="shared" si="71"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
       <c r="M46" t="str">
         <f t="array" ref="M46">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N46" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="P46" s="13" t="s">
-        <v>164</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
       </c>
       <c r="Q46" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R46" s="14"/>
-      <c r="T46" s="13" t="str">
-        <f>IF(S46="N", R46, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U46" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V46" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y46" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE46" s="13" t="s">
-        <v>167</v>
+        <v>42</v>
+      </c>
+      <c r="AI46" s="13">
+        <v>7</v>
+      </c>
+      <c r="AK46" s="13">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="13" t="s">
-        <v>163</v>
+        <v>217</v>
       </c>
       <c r="C47" t="str">
-        <f t="shared" si="39"/>
-        <v>9</v>
+        <f t="shared" si="64"/>
+        <v>4</v>
       </c>
       <c r="D47" t="str">
-        <f t="shared" si="40"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="E47" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Iwaniuk</v>
+        <f t="shared" si="65"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="E47" s="5" t="str">
+        <f t="shared" si="66"/>
+        <v>Isler</v>
       </c>
       <c r="F47" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G47" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2001</v>
-      </c>
-      <c r="H47" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1037/0735-7036.115.1.29</v>
+      <c r="G47" s="5" t="str">
+        <f t="shared" si="68"/>
+        <v>2008</v>
+      </c>
+      <c r="H47" s="4" t="str">
+        <f t="shared" si="69"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="J47" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="K47" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Iwaniuk_etal_2001_Table3</v>
-      </c>
-      <c r="L47" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
+        <v>222</v>
+      </c>
+      <c r="K47" s="4" t="str">
+        <f t="shared" si="70"/>
+        <v>Isler_etal_2008_Tree.nex</v>
+      </c>
+      <c r="L47" s="6" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="M47" t="str">
         <f t="array" ref="M47">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N47" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="P47" s="13" t="s">
-        <v>164</v>
-      </c>
       <c r="Q47" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R47" s="14"/>
-      <c r="T47" s="13" t="str">
-        <f>IF(S47="N", R47, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U47" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V47" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y47" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE47" s="13" t="s">
-        <v>167</v>
+        <v>42</v>
       </c>
     </row>
     <row r="48" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="13" t="s">
-        <v>163</v>
+        <v>342</v>
       </c>
       <c r="C48" t="str">
-        <f t="shared" si="39"/>
-        <v>9</v>
+        <f t="shared" si="64"/>
+        <v>x</v>
       </c>
       <c r="D48" t="str">
-        <f t="shared" si="40"/>
-        <v>Iwaniuk_etal_2001</v>
-      </c>
-      <c r="E48" s="2" t="str">
-        <f t="shared" si="41"/>
+        <f t="shared" si="65"/>
+        <v>Iwaniuk_etal_1999</v>
+      </c>
+      <c r="E48" s="7" t="str">
+        <f t="shared" si="66"/>
         <v>Iwaniuk</v>
       </c>
       <c r="F48" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G48" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2001</v>
+      <c r="G48" s="7" t="str">
+        <f t="shared" si="68"/>
+        <v>1999</v>
       </c>
       <c r="H48" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="69"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="J48" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="K48" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Iwaniuk_etal_2001_Table4</v>
-      </c>
-      <c r="L48" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
+        <v>339</v>
+      </c>
+      <c r="K48" s="3" t="str">
+        <f t="shared" si="70"/>
+        <v>Iwaniuk_etal_1999_References</v>
+      </c>
+      <c r="L48" s="3" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
       </c>
       <c r="M48" t="str">
         <f t="array" ref="M48">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N48" s="13" t="s">
-        <v>170</v>
+        <v>339</v>
       </c>
       <c r="P48" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q48" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R48" s="14"/>
-      <c r="T48" s="13" t="str">
-        <f>IF(S48="N", R48, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U48" s="13" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="V48" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="Y48" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="AE48" s="13" t="s">
-        <v>167</v>
+        <v>341</v>
+      </c>
+      <c r="W48" s="13" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="49" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="13" t="s">
-        <v>171</v>
+        <v>342</v>
       </c>
       <c r="C49" t="str">
-        <f t="shared" si="39"/>
-        <v>8</v>
+        <f t="shared" si="64"/>
+        <v>x</v>
       </c>
       <c r="D49" t="str">
-        <f t="shared" si="40"/>
-        <v>JardimMesseder_etal_2017</v>
-      </c>
-      <c r="E49" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>JardimMesseder</v>
+        <f t="shared" si="65"/>
+        <v>Iwaniuk_etal_1999</v>
+      </c>
+      <c r="E49" s="7" t="str">
+        <f t="shared" si="66"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F49" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G49" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2017</v>
+      <c r="G49" s="7" t="str">
+        <f t="shared" si="68"/>
+        <v>1999</v>
       </c>
       <c r="H49" t="str">
-        <f t="shared" si="44"/>
-        <v>10.3389/fnana.2017.00118</v>
+        <f t="shared" si="69"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="J49" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="K49" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>JardimMesseder_etal_2017_Table1</v>
-      </c>
-      <c r="L49" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.3389%2Ffnana.2017.00118_Table1</v>
+      <c r="K49" s="3" t="str">
+        <f t="shared" si="70"/>
+        <v>Iwaniuk_etal_1999_Table1</v>
+      </c>
+      <c r="L49" s="3" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
       </c>
       <c r="M49" t="str">
         <f t="array" ref="M49">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N49" s="13" t="s">
-        <v>175</v>
+        <v>340</v>
       </c>
       <c r="P49" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q49" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R49" s="14" t="s">
-        <v>172</v>
-      </c>
-      <c r="S49" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T49" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="U49" s="13" t="s">
-        <v>57</v>
+        <v>125</v>
       </c>
       <c r="V49" s="13" t="s">
         <v>46</v>
       </c>
       <c r="W49" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X49" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="Y49" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="Z49" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AA49" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB49" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="AE49" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="AI49" s="13">
-        <v>2</v>
-      </c>
-      <c r="AK49" s="13">
-        <v>3</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="13" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C50" t="str">
-        <f t="shared" si="39"/>
-        <v>8</v>
+        <f t="shared" si="64"/>
+        <v>9</v>
       </c>
       <c r="D50" t="str">
-        <f t="shared" si="40"/>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="65"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="E50" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Kverkova</v>
+        <f t="shared" si="66"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F50" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G50" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2018</v>
+        <f t="shared" si="68"/>
+        <v>2001</v>
       </c>
       <c r="H50" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="69"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="J50" s="13" t="s">
         <v>52</v>
       </c>
       <c r="K50" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Kverkova_etal_2018_Table1</v>
+        <f t="shared" si="70"/>
+        <v>Iwaniuk_etal_2001_Table1</v>
       </c>
       <c r="L50" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
+        <f t="shared" si="71"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
       <c r="M50" t="str">
         <f t="array" ref="M50">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N50" s="13" t="s">
-        <v>264</v>
+        <v>165</v>
       </c>
       <c r="P50" s="13" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="Q50" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R50" s="14" t="s">
-        <v>266</v>
-      </c>
-      <c r="S50" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T50" s="13" t="s">
-        <v>178</v>
+        <v>35</v>
+      </c>
+      <c r="R50" s="14"/>
+      <c r="T50" s="13" t="str">
+        <f>IF(S50="N", R50, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U50" s="13" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="V50" s="13" t="s">
         <v>46</v>
       </c>
       <c r="Y50" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="Z50" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB50" s="13" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="AE50" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI50" s="13">
-        <v>1</v>
-      </c>
-      <c r="AK50" s="13">
-        <v>1</v>
+        <v>167</v>
       </c>
     </row>
     <row r="51" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="13" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C51" t="str">
-        <f t="shared" si="39"/>
-        <v>8</v>
+        <f t="shared" si="64"/>
+        <v>9</v>
       </c>
       <c r="D51" t="str">
-        <f t="shared" si="40"/>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="65"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="E51" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Kverkova</v>
+        <f t="shared" si="66"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F51" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G51" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2018</v>
+        <f t="shared" si="68"/>
+        <v>2001</v>
       </c>
       <c r="H51" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="69"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="J51" s="13" t="s">
-        <v>91</v>
+        <v>135</v>
       </c>
       <c r="K51" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Kverkova_etal_2018_TableS1</v>
+        <f t="shared" si="70"/>
+        <v>Iwaniuk_etal_2001_Table2</v>
       </c>
       <c r="L51" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
+        <f t="shared" si="71"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
       <c r="M51" t="str">
         <f t="array" ref="M51">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L51, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N51" s="13" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="P51" s="13" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="Q51" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R51" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="S51" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T51" s="13" t="s">
-        <v>178</v>
+        <v>35</v>
+      </c>
+      <c r="R51" s="14"/>
+      <c r="T51" s="13" t="str">
+        <f>IF(S51="N", R51, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U51" s="13" t="s">
-        <v>179</v>
+        <v>57</v>
       </c>
       <c r="V51" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W51" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X51" s="13" t="s">
-        <v>180</v>
-      </c>
       <c r="Y51" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="Z51" s="13" t="s">
-        <v>182</v>
-      </c>
-      <c r="AB51" s="13" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="AE51" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI51" s="13">
-        <v>1</v>
-      </c>
-      <c r="AK51" s="13">
-        <v>1</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="13" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="C52" t="str">
-        <f t="shared" si="39"/>
-        <v>8</v>
+        <f t="shared" si="64"/>
+        <v>9</v>
       </c>
       <c r="D52" t="str">
-        <f t="shared" si="40"/>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="65"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="E52" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Kverkova</v>
+        <f t="shared" si="66"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F52" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G52" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2018</v>
+        <f t="shared" si="68"/>
+        <v>2001</v>
       </c>
       <c r="H52" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="69"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="J52" s="13" t="s">
-        <v>184</v>
+        <v>139</v>
       </c>
       <c r="K52" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Kverkova_etal_2018_TableS5</v>
+        <f t="shared" si="70"/>
+        <v>Iwaniuk_etal_2001_Table3</v>
       </c>
       <c r="L52" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
+        <f t="shared" si="71"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
       <c r="M52" t="str">
         <f t="array" ref="M52">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L52, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N52" s="13" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="P52" s="13" t="s">
-        <v>41</v>
+        <v>164</v>
       </c>
       <c r="Q52" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="R52" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="S52" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="T52" s="13" t="s">
-        <v>185</v>
+        <v>35</v>
+      </c>
+      <c r="R52" s="14"/>
+      <c r="T52" s="13" t="str">
+        <f>IF(S52="N", R52, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U52" s="13" t="s">
-        <v>186</v>
+        <v>57</v>
       </c>
       <c r="V52" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="W52" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="X52" s="13" t="s">
-        <v>180</v>
-      </c>
       <c r="Y52" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="Z52" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AB52" s="13" t="s">
-        <v>100</v>
+        <v>166</v>
       </c>
       <c r="AE52" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="AI52" s="13">
-        <v>1</v>
-      </c>
-      <c r="AK52" s="13">
-        <v>1</v>
+        <v>167</v>
       </c>
     </row>
     <row r="53" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="13" t="s">
-        <v>226</v>
+        <v>163</v>
       </c>
       <c r="C53" t="str">
-        <f t="shared" si="39"/>
-        <v>4</v>
+        <f t="shared" si="64"/>
+        <v>9</v>
       </c>
       <c r="D53" t="str">
-        <f t="shared" si="40"/>
-        <v>Lewitus_etal_2013</v>
-      </c>
-      <c r="E53" s="5" t="str">
-        <f t="shared" si="41"/>
-        <v>Lewitus</v>
+        <f t="shared" si="65"/>
+        <v>Iwaniuk_etal_2001</v>
+      </c>
+      <c r="E53" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="F53" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G53" s="5" t="str">
-        <f t="shared" si="43"/>
-        <v>2013</v>
-      </c>
-      <c r="H53" s="4" t="str">
-        <f t="shared" si="44"/>
-        <v>10.3389/fnhum.2013.00424</v>
+      <c r="G53" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2001</v>
+      </c>
+      <c r="H53" t="str">
+        <f t="shared" si="69"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="J53" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="K53" s="4" t="str">
-        <f t="shared" si="45"/>
-        <v>Lewitus_etal_2013_TableS2partial</v>
-      </c>
-      <c r="L53" s="6" t="str">
-        <f t="shared" si="46"/>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
+        <v>143</v>
+      </c>
+      <c r="K53" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Iwaniuk_etal_2001_Table4</v>
+      </c>
+      <c r="L53" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="M53" t="str">
         <f t="array" ref="M53">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L53, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N53" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="P53" s="13" t="s">
+        <v>164</v>
       </c>
       <c r="Q53" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA53" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="AI53" s="13">
-        <v>7</v>
-      </c>
-      <c r="AK53" s="13">
-        <v>14</v>
+        <v>35</v>
+      </c>
+      <c r="R53" s="14"/>
+      <c r="T53" s="13" t="str">
+        <f>IF(S53="N", R53, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U53" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V53" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y53" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="AE53" s="13" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="13" t="s">
-        <v>223</v>
+        <v>171</v>
       </c>
       <c r="C54" t="str">
-        <f t="shared" si="39"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>8</v>
       </c>
       <c r="D54" t="str">
-        <f t="shared" si="40"/>
-        <v>Lewitus_etal_2014</v>
+        <f t="shared" si="65"/>
+        <v>JardimMesseder_etal_2017</v>
       </c>
       <c r="E54" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Lewitus</v>
+        <f t="shared" si="66"/>
+        <v>JardimMesseder</v>
       </c>
       <c r="F54" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G54" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2014</v>
+        <f t="shared" si="68"/>
+        <v>2017</v>
       </c>
       <c r="H54" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1371/journal.pbio.1002000</v>
+        <f t="shared" si="69"/>
+        <v>10.3389/fnana.2017.00118</v>
       </c>
       <c r="J54" s="13" t="s">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="K54" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Lewitus_etal_2014_TableS1</v>
+        <f t="shared" si="70"/>
+        <v>JardimMesseder_etal_2017_Table1</v>
       </c>
       <c r="L54" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
+        <f t="shared" si="71"/>
+        <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
       <c r="M54" t="str">
         <f t="array" ref="M54">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L54, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="N54" s="13" t="s">
-        <v>269</v>
+        <v>175</v>
+      </c>
+      <c r="P54" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q54" s="13" t="s">
-        <v>42</v>
+        <v>53</v>
+      </c>
+      <c r="R54" s="14" t="s">
+        <v>172</v>
+      </c>
+      <c r="S54" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T54" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="U54" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V54" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W54" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X54" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="Y54" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="Z54" s="13" t="s">
+        <v>99</v>
       </c>
       <c r="AA54" s="13" t="s">
-        <v>270</v>
+        <v>100</v>
+      </c>
+      <c r="AB54" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE54" s="13" t="s">
+        <v>176</v>
       </c>
       <c r="AI54" s="13">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="AK54" s="13">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="13" t="s">
-        <v>223</v>
+        <v>177</v>
       </c>
       <c r="C55" t="str">
-        <f t="shared" si="39"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>8</v>
       </c>
       <c r="D55" t="str">
-        <f t="shared" si="40"/>
-        <v>Lewitus_etal_2014</v>
+        <f t="shared" si="65"/>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="E55" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Lewitus</v>
+        <f t="shared" si="66"/>
+        <v>Kverkova</v>
       </c>
       <c r="F55" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G55" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2014</v>
+        <f t="shared" si="68"/>
+        <v>2018</v>
       </c>
       <c r="H55" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1371/journal.pbio.1002000</v>
+        <f t="shared" si="69"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="J55" s="13" t="s">
-        <v>224</v>
+        <v>52</v>
       </c>
       <c r="K55" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Lewitus_etal_2014_TableS8</v>
+        <f t="shared" si="70"/>
+        <v>Kverkova_etal_2018_Table1</v>
       </c>
       <c r="L55" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+        <f t="shared" si="71"/>
+        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="M55" t="str">
         <f t="array" ref="M55">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L55, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="N55" s="13" t="s">
-        <v>225</v>
+        <v>264</v>
+      </c>
+      <c r="P55" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="Q55" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AA55" s="13" t="s">
-        <v>270</v>
+        <v>53</v>
+      </c>
+      <c r="R55" s="14" t="s">
+        <v>266</v>
+      </c>
+      <c r="S55" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T55" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="U55" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="V55" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="Y55" s="13" t="s">
+        <v>265</v>
+      </c>
+      <c r="Z55" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB55" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE55" s="13" t="s">
+        <v>183</v>
       </c>
       <c r="AI55" s="13">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="AK55" s="13">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="56" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="13" t="s">
-        <v>347</v>
+        <v>177</v>
       </c>
       <c r="C56" t="str">
-        <f t="shared" si="39"/>
-        <v>5</v>
+        <f t="shared" si="64"/>
+        <v>8</v>
       </c>
       <c r="D56" t="str">
-        <f t="shared" si="40"/>
-        <v>MacLarnon__1996</v>
-      </c>
-      <c r="E56" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>MacLarnon</v>
+        <f t="shared" si="65"/>
+        <v>Kverkova_etal_2018</v>
+      </c>
+      <c r="E56" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Kverkova</v>
       </c>
       <c r="F56" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v/>
-      </c>
-      <c r="G56" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>1996</v>
+        <f t="shared" si="67"/>
+        <v>etal</v>
+      </c>
+      <c r="G56" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2018</v>
       </c>
       <c r="H56" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1006/jhev.1996.0005</v>
+        <f t="shared" si="69"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="J56" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K56" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>MacLarnon__1996_Table1</v>
-      </c>
-      <c r="L56" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1006%2Fjhev.1996.0005_Table1</v>
+        <v>91</v>
+      </c>
+      <c r="K56" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Kverkova_etal_2018_TableS1</v>
+      </c>
+      <c r="L56" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="M56" t="str">
         <f t="array" ref="M56">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L56, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="N56" s="13" t="s">
-        <v>287</v>
+        <v>181</v>
       </c>
       <c r="P56" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="57" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+      <c r="Q56" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="R56" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="S56" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T56" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="U56" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="V56" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W56" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="X56" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="Y56" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="Z56" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB56" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="AE56" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="AI56" s="13">
+        <v>1</v>
+      </c>
+      <c r="AK56" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="13" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="C57" t="str">
-        <f t="shared" si="39"/>
-        <v>2</v>
+        <f t="shared" si="64"/>
+        <v>8</v>
       </c>
       <c r="D57" t="str">
-        <f t="shared" si="40"/>
-        <v>ManyPrimates__2022</v>
+        <f t="shared" si="65"/>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="E57" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>ManyPrimates</v>
+        <f t="shared" si="66"/>
+        <v>Kverkova</v>
       </c>
       <c r="F57" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v/>
+        <f t="shared" si="67"/>
+        <v>etal</v>
       </c>
       <c r="G57" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2022</v>
+        <f t="shared" si="68"/>
+        <v>2018</v>
       </c>
       <c r="H57" t="str">
-        <f t="shared" si="44"/>
-        <v>10.26451/abc.09.04.06.2022</v>
+        <f t="shared" si="69"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="J57" s="13" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="K57" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
+        <f t="shared" si="70"/>
+        <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="L57" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
+        <f t="shared" si="71"/>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="M57" t="str">
         <f t="array" ref="M57">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L57, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+      </c>
+      <c r="N57" s="13" t="s">
+        <v>187</v>
       </c>
       <c r="P57" s="13" t="s">
-        <v>190</v>
+        <v>41</v>
       </c>
       <c r="Q57" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R57" s="14"/>
-      <c r="T57" s="13" t="str">
-        <f>IF(S57="N", R57, "write file name")</f>
-        <v>write file name</v>
+        <v>53</v>
+      </c>
+      <c r="R57" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="S57" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="T57" s="13" t="s">
+        <v>185</v>
       </c>
       <c r="U57" s="13" t="s">
-        <v>67</v>
+        <v>186</v>
       </c>
       <c r="V57" s="13" t="s">
         <v>46</v>
       </c>
       <c r="W57" s="13" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="X57" s="13" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="Y57" s="13" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="Z57" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC57" s="13" t="s">
-        <v>193</v>
+        <v>99</v>
+      </c>
+      <c r="AB57" s="13" t="s">
+        <v>100</v>
       </c>
       <c r="AE57" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>183</v>
+      </c>
+      <c r="AI57" s="13">
+        <v>1</v>
+      </c>
+      <c r="AK57" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="13" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="C58" t="str">
-        <f t="shared" si="39"/>
-        <v>1</v>
+        <f t="shared" si="64"/>
+        <v>4</v>
       </c>
       <c r="D58" t="str">
-        <f t="shared" si="40"/>
-        <v>Mota_etal_2015</v>
-      </c>
-      <c r="E58" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Mota</v>
+        <f t="shared" si="65"/>
+        <v>Lewitus_etal_2013</v>
+      </c>
+      <c r="E58" s="5" t="str">
+        <f t="shared" si="66"/>
+        <v>Lewitus</v>
       </c>
       <c r="F58" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G58" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2015</v>
-      </c>
-      <c r="H58" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1126/science.aaa9101</v>
+      <c r="G58" s="5" t="str">
+        <f t="shared" si="68"/>
+        <v>2013</v>
+      </c>
+      <c r="H58" s="4" t="str">
+        <f t="shared" si="69"/>
+        <v>10.3389/fnhum.2013.00424</v>
       </c>
       <c r="J58" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="K58" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Mota_etal_2015_TableS1</v>
-      </c>
-      <c r="L58" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
+        <v>227</v>
+      </c>
+      <c r="K58" s="4" t="str">
+        <f t="shared" si="70"/>
+        <v>Lewitus_etal_2013_TableS2partial</v>
+      </c>
+      <c r="L58" s="6" t="str">
+        <f t="shared" si="71"/>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
       <c r="M58" t="str">
         <f t="array" ref="M58">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L58, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
       <c r="Q58" s="13" t="s">
         <v>42</v>
       </c>
+      <c r="AA58" s="13" t="s">
+        <v>270</v>
+      </c>
       <c r="AI58" s="13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AK58" s="13">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="59" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="59" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="13" t="s">
-        <v>344</v>
+        <v>223</v>
       </c>
       <c r="C59" t="str">
-        <f t="shared" si="39"/>
-        <v>6</v>
+        <f t="shared" si="64"/>
+        <v>0</v>
       </c>
       <c r="D59" t="str">
-        <f t="shared" si="40"/>
-        <v>Mota_etal_2019</v>
-      </c>
-      <c r="E59" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>Mota</v>
+        <f t="shared" si="65"/>
+        <v>Lewitus_etal_2014</v>
+      </c>
+      <c r="E59" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Lewitus</v>
       </c>
       <c r="F59" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G59" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>2019</v>
+      <c r="G59" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2014</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1073/pnas.1716956116</v>
+        <f t="shared" si="69"/>
+        <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="J59" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="K59" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
-      </c>
-      <c r="L59" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+        <v>91</v>
+      </c>
+      <c r="K59" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Lewitus_etal_2014_TableS1</v>
+      </c>
+      <c r="L59" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="M59" t="str">
         <f t="array" ref="M59">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L59, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
       </c>
       <c r="N59" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="P59" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="AC59" s="13" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="60" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+      <c r="Q59" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AA59" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="AI59" s="13">
+        <v>9</v>
+      </c>
+      <c r="AK59" s="13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="60" spans="1:37" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="13" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="C60" t="str">
-        <f t="shared" si="39"/>
-        <v>5</v>
+        <f t="shared" si="64"/>
+        <v>0</v>
       </c>
       <c r="D60" t="str">
-        <f t="shared" si="40"/>
-        <v>Powell_etal_2017</v>
+        <f t="shared" si="65"/>
+        <v>Lewitus_etal_2014</v>
       </c>
       <c r="E60" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Powell</v>
+        <f t="shared" si="66"/>
+        <v>Lewitus</v>
       </c>
       <c r="F60" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G60" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2017</v>
+        <f t="shared" si="68"/>
+        <v>2014</v>
       </c>
       <c r="H60" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1098/rspb.2017.1765</v>
-      </c>
-      <c r="I60" s="13" t="s">
-        <v>195</v>
+        <f t="shared" si="69"/>
+        <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="J60" s="13" t="s">
-        <v>196</v>
+        <v>224</v>
       </c>
       <c r="K60" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Powell_etal_2017_Dataset1</v>
+        <f t="shared" si="70"/>
+        <v>Lewitus_etal_2014_TableS8</v>
       </c>
       <c r="L60" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <f t="shared" si="71"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="M60" t="str">
         <f t="array" ref="M60">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L60, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P60" s="13" t="s">
-        <v>125</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+      </c>
+      <c r="N60" s="13" t="s">
+        <v>225</v>
       </c>
       <c r="Q60" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R60" s="14"/>
-      <c r="T60" s="13" t="str">
-        <f>IF(S60="N", R60, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U60" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="V60" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="W60" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="X60" s="13" t="s">
-        <v>197</v>
-      </c>
-      <c r="Y60" s="13" t="s">
-        <v>198</v>
-      </c>
-      <c r="Z60" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="AC60" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="AE60" s="13" t="s">
-        <v>64</v>
+        <v>42</v>
+      </c>
+      <c r="AA60" s="13" t="s">
+        <v>270</v>
+      </c>
+      <c r="AI60" s="13">
+        <v>6</v>
+      </c>
+      <c r="AK60" s="13">
+        <v>13</v>
       </c>
     </row>
     <row r="61" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>200</v>
+        <v>347</v>
       </c>
       <c r="C61" t="str">
-        <f t="shared" si="39"/>
-        <v>2</v>
+        <f t="shared" si="64"/>
+        <v>5</v>
       </c>
       <c r="D61" t="str">
-        <f t="shared" si="40"/>
-        <v>Sherwood_etal_2004_I</v>
-      </c>
-      <c r="E61" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Sherwood</v>
+        <f t="shared" si="65"/>
+        <v>MacLarnon__1996</v>
+      </c>
+      <c r="E61" s="7" t="str">
+        <f t="shared" si="66"/>
+        <v>MacLarnon</v>
       </c>
       <c r="F61" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v>etal</v>
-      </c>
-      <c r="G61" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2004</v>
+        <f t="shared" si="67"/>
+        <v/>
+      </c>
+      <c r="G61" s="7" t="str">
+        <f t="shared" si="68"/>
+        <v>1996</v>
       </c>
       <c r="H61" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159/000075672</v>
+        <f t="shared" si="69"/>
+        <v>10.1006/jhev.1996.0005</v>
       </c>
       <c r="J61" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="K61" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Sherwood_etal_2004_I_Table4</v>
-      </c>
-      <c r="L61" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1159%2F000075672_Table4</v>
+        <v>52</v>
+      </c>
+      <c r="K61" s="3" t="str">
+        <f t="shared" si="70"/>
+        <v>MacLarnon__1996_Table1</v>
+      </c>
+      <c r="L61" s="3" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1006%2Fjhev.1996.0005_Table1</v>
       </c>
       <c r="M61" t="str">
         <f t="array" ref="M61">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L61, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N61" s="13" t="s">
-        <v>202</v>
+        <v>287</v>
       </c>
       <c r="P61" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q61" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R61" s="14"/>
-      <c r="T61" s="13" t="str">
-        <f>IF(S61="N", R61, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U61" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V61" s="13" t="s">
-        <v>201</v>
-      </c>
-      <c r="Y61" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="Z61" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="AE61" s="13" t="s">
-        <v>64</v>
+        <v>125</v>
       </c>
     </row>
     <row r="62" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="13" t="s">
-        <v>199</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="C62" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="64"/>
         <v>2</v>
       </c>
       <c r="D62" t="str">
-        <f t="shared" si="40"/>
-        <v>Sherwood_etal_2004_I</v>
+        <f t="shared" si="65"/>
+        <v>ManyPrimates__2022</v>
       </c>
       <c r="E62" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Sherwood</v>
+        <f t="shared" si="66"/>
+        <v>ManyPrimates</v>
       </c>
       <c r="F62" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v>etal</v>
+        <f t="shared" si="67"/>
+        <v/>
       </c>
       <c r="G62" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2004</v>
+        <f t="shared" si="68"/>
+        <v>2022</v>
       </c>
       <c r="H62" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159/000075672</v>
+        <f t="shared" si="69"/>
+        <v>10.26451/abc.09.04.06.2022</v>
       </c>
       <c r="J62" s="13" t="s">
-        <v>147</v>
+        <v>189</v>
       </c>
       <c r="K62" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Sherwood_etal_2004_I_Table5</v>
+        <f t="shared" si="70"/>
+        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="L62" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1159%2F000075672_Table5</v>
+        <f t="shared" si="71"/>
+        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="M62" t="str">
         <f t="array" ref="M62">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L62, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
-      </c>
-      <c r="N62" s="13" t="s">
-        <v>204</v>
       </c>
       <c r="P62" s="13" t="s">
         <v>190</v>
@@ -6027,16 +6047,25 @@
         <v>write file name</v>
       </c>
       <c r="U62" s="13" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="V62" s="13" t="s">
-        <v>201</v>
+        <v>46</v>
+      </c>
+      <c r="W62" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X62" s="13" t="s">
+        <v>191</v>
       </c>
       <c r="Y62" s="13" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="Z62" s="13" t="s">
-        <v>99</v>
+        <v>49</v>
+      </c>
+      <c r="AC62" s="13" t="s">
+        <v>193</v>
       </c>
       <c r="AE62" s="13" t="s">
         <v>64</v>
@@ -6044,398 +6073,738 @@
     </row>
     <row r="63" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="13" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="C63" t="str">
-        <f t="shared" si="39"/>
+        <f t="shared" si="64"/>
         <v>1</v>
       </c>
       <c r="D63" t="str">
-        <f t="shared" si="40"/>
-        <v>Smaers_etal_2011</v>
-      </c>
-      <c r="E63" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>Smaers</v>
+        <f t="shared" si="65"/>
+        <v>Mota_etal_2015</v>
+      </c>
+      <c r="E63" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Mota</v>
       </c>
       <c r="F63" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G63" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>2011</v>
+      <c r="G63" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2015</v>
       </c>
       <c r="H63" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159/000323671</v>
+        <f t="shared" si="69"/>
+        <v>10.1126/science.aaa9101</v>
       </c>
       <c r="J63" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="K63" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
-      </c>
-      <c r="L63" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
+        <v>91</v>
+      </c>
+      <c r="K63" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Mota_etal_2015_TableS1</v>
+      </c>
+      <c r="L63" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="M63" t="str">
         <f t="array" ref="M63">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L63, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="Q63" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="AI63" s="13" t="s">
-        <v>230</v>
+      <c r="AI63" s="13">
+        <v>10</v>
+      </c>
+      <c r="AK63" s="13">
+        <v>15</v>
       </c>
     </row>
     <row r="64" spans="1:37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="13" t="s">
-        <v>228</v>
+        <v>344</v>
       </c>
       <c r="C64" t="str">
-        <f t="shared" si="39"/>
-        <v>1</v>
+        <f t="shared" si="64"/>
+        <v>6</v>
       </c>
       <c r="D64" t="str">
-        <f t="shared" si="40"/>
-        <v>Smaers_etal_2011</v>
+        <f t="shared" si="65"/>
+        <v>Mota_etal_2019</v>
       </c>
       <c r="E64" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>Smaers</v>
+        <f t="shared" si="66"/>
+        <v>Mota</v>
       </c>
       <c r="F64" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
       <c r="G64" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>2011</v>
+        <f t="shared" si="68"/>
+        <v>2019</v>
       </c>
       <c r="H64" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159/000323671</v>
+        <f t="shared" si="69"/>
+        <v>10.1073/pnas.1716956116</v>
       </c>
       <c r="J64" s="13" t="s">
-        <v>231</v>
+        <v>272</v>
       </c>
       <c r="K64" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
+        <f t="shared" si="70"/>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="L64" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
+        <f t="shared" si="71"/>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="M64" t="str">
         <f t="array" ref="M64">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L64, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
-      </c>
-      <c r="Q64" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="AI64" s="13" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="65" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+      <c r="N64" s="13" t="s">
+        <v>271</v>
+      </c>
+      <c r="P64" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="AC64" s="13" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="65" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="13" t="s">
-        <v>364</v>
+        <v>194</v>
       </c>
       <c r="C65" t="str">
-        <f t="shared" si="39"/>
-        <v>2</v>
+        <f t="shared" si="64"/>
+        <v>5</v>
       </c>
       <c r="D65" t="str">
-        <f t="shared" si="40"/>
-        <v>Turner_etal_2016</v>
-      </c>
-      <c r="E65" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>Turner</v>
+        <f t="shared" si="65"/>
+        <v>Powell_etal_2017</v>
+      </c>
+      <c r="E65" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Powell</v>
       </c>
       <c r="F65" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G65" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>2016</v>
+      <c r="G65" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2017</v>
       </c>
       <c r="H65" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1159/000446762</v>
+        <f t="shared" si="69"/>
+        <v>10.1098/rspb.2017.1765</v>
+      </c>
+      <c r="I65" s="13" t="s">
+        <v>195</v>
       </c>
       <c r="J65" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K65" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>Turner_etal_2016_Table1</v>
-      </c>
-      <c r="L65" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1159%2F000446762_Table1</v>
+        <v>196</v>
+      </c>
+      <c r="K65" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Powell_etal_2017_Dataset1</v>
+      </c>
+      <c r="L65" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="M65" t="str">
         <f t="array" ref="M65">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L65, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N65" s="13" t="s">
-        <v>362</v>
+      <c r="P65" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q65" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R65" s="14"/>
+      <c r="T65" s="13" t="str">
+        <f>IF(S65="N", R65, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U65" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="V65" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="W65" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="X65" s="13" t="s">
+        <v>197</v>
       </c>
       <c r="Y65" s="13" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="66" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>198</v>
+      </c>
+      <c r="Z65" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="AC65" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="AE65" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="13" t="s">
-        <v>350</v>
+        <v>199</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="C66" t="str">
-        <f t="shared" si="39"/>
-        <v>1</v>
+        <f t="shared" si="64"/>
+        <v>2</v>
       </c>
       <c r="D66" t="str">
-        <f t="shared" si="40"/>
-        <v>Wilman_etal_2014</v>
-      </c>
-      <c r="E66" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>Wilman</v>
+        <f t="shared" si="65"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="E66" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Sherwood</v>
       </c>
       <c r="F66" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G66" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>2014</v>
+      <c r="G66" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2004</v>
       </c>
       <c r="H66" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1890/13-1917.1</v>
+        <f t="shared" si="69"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="J66" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="K66" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>Wilman_etal_2014_MamFuncDat.txt</v>
-      </c>
-      <c r="L66" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+        <v>143</v>
+      </c>
+      <c r="K66" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Sherwood_etal_2004_I_Table4</v>
+      </c>
+      <c r="L66" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="M66" t="str">
         <f t="array" ref="M66">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L66, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-    </row>
-    <row r="67" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N66" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="P66" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q66" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R66" s="14"/>
+      <c r="T66" s="13" t="str">
+        <f>IF(S66="N", R66, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U66" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V66" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y66" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z66" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE66" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="13" t="s">
-        <v>348</v>
+        <v>199</v>
+      </c>
+      <c r="B67" s="13" t="s">
+        <v>200</v>
       </c>
       <c r="C67" t="str">
-        <f t="shared" si="39"/>
-        <v>7</v>
+        <f t="shared" si="64"/>
+        <v>2</v>
       </c>
       <c r="D67" t="str">
-        <f t="shared" si="40"/>
-        <v>Wimberly_etal_2021</v>
-      </c>
-      <c r="E67" s="7" t="str">
-        <f t="shared" si="41"/>
-        <v>Wimberly</v>
+        <f t="shared" si="65"/>
+        <v>Sherwood_etal_2004_I</v>
+      </c>
+      <c r="E67" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Sherwood</v>
       </c>
       <c r="F67" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G67" s="7" t="str">
-        <f t="shared" si="43"/>
-        <v>2021</v>
+      <c r="G67" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2004</v>
       </c>
       <c r="H67" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1098/rspb.2021.0937</v>
+        <f t="shared" si="69"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="J67" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="K67" s="3" t="str">
-        <f t="shared" si="45"/>
-        <v>Wimberly_etal_2021_mammalgait.txt</v>
-      </c>
-      <c r="L67" s="3" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+        <v>147</v>
+      </c>
+      <c r="K67" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Sherwood_etal_2004_I_Table5</v>
+      </c>
+      <c r="L67" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="M67" t="str">
         <f t="array" ref="M67">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L67, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
+      <c r="N67" s="13" t="s">
+        <v>204</v>
+      </c>
       <c r="P67" s="13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
+        <v>190</v>
+      </c>
+      <c r="Q67" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R67" s="14"/>
+      <c r="T67" s="13" t="str">
+        <f>IF(S67="N", R67, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U67" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V67" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y67" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="Z67" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="AE67" s="13" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="68" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="13" t="s">
-        <v>205</v>
+        <v>228</v>
       </c>
       <c r="C68" t="str">
-        <f t="shared" si="39"/>
-        <v>5</v>
+        <f t="shared" si="64"/>
+        <v>1</v>
       </c>
       <c r="D68" t="str">
-        <f t="shared" si="40"/>
-        <v>Winkler_Bryant_2021</v>
-      </c>
-      <c r="E68" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Winkler</v>
+        <f t="shared" si="65"/>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="E68" s="7" t="str">
+        <f t="shared" si="66"/>
+        <v>Smaers</v>
       </c>
       <c r="F68" s="2" t="str">
-        <f t="shared" si="42"/>
-        <v>Bryant</v>
-      </c>
-      <c r="G68" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2021</v>
+        <f t="shared" si="67"/>
+        <v>etal</v>
+      </c>
+      <c r="G68" s="7" t="str">
+        <f t="shared" si="68"/>
+        <v>2011</v>
       </c>
       <c r="H68" t="str">
-        <f t="shared" si="44"/>
-        <v>10.1080/09524622.2021.1905065</v>
+        <f t="shared" si="69"/>
+        <v>10.1159/000323671</v>
       </c>
       <c r="J68" s="13" t="s">
-        <v>206</v>
-      </c>
-      <c r="K68" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Winkler_Bryant_2021_Figure1</v>
-      </c>
-      <c r="L68" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <v>229</v>
+      </c>
+      <c r="K68" s="3" t="str">
+        <f t="shared" si="70"/>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
+      </c>
+      <c r="L68" s="3" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="M68" t="str">
         <f t="array" ref="M68">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L68, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P68" s="13" t="s">
-        <v>125</v>
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
       </c>
       <c r="Q68" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="R68" s="14"/>
-      <c r="T68" s="13" t="str">
-        <f>IF(S68="N", R68, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U68" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="V68" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="Y68" s="13" t="s">
-        <v>208</v>
-      </c>
-      <c r="AE68" s="13" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+      <c r="AI68" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="69" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="13" t="s">
-        <v>209</v>
+        <v>228</v>
       </c>
       <c r="C69" t="str">
-        <f t="shared" si="39"/>
-        <v>0</v>
+        <f t="shared" si="64"/>
+        <v>1</v>
       </c>
       <c r="D69" t="str">
-        <f t="shared" si="40"/>
-        <v>Young_etal_2013</v>
-      </c>
-      <c r="E69" s="2" t="str">
-        <f t="shared" si="41"/>
-        <v>Young</v>
+        <f t="shared" si="65"/>
+        <v>Smaers_etal_2011</v>
+      </c>
+      <c r="E69" s="7" t="str">
+        <f t="shared" si="66"/>
+        <v>Smaers</v>
       </c>
       <c r="F69" s="2" t="str">
-        <f t="shared" si="42"/>
+        <f t="shared" si="67"/>
         <v>etal</v>
       </c>
-      <c r="G69" s="2" t="str">
-        <f t="shared" si="43"/>
-        <v>2013</v>
+      <c r="G69" s="7" t="str">
+        <f t="shared" si="68"/>
+        <v>2011</v>
       </c>
       <c r="H69" t="str">
-        <f t="shared" si="44"/>
-        <v>10.3389/fncir.2013.00030</v>
+        <f t="shared" si="69"/>
+        <v>10.1159/000323671</v>
       </c>
       <c r="J69" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="K69" s="1" t="str">
-        <f t="shared" si="45"/>
-        <v>Young_etal_2013_Table1</v>
-      </c>
-      <c r="L69" s="1" t="str">
-        <f t="shared" si="46"/>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <v>231</v>
+      </c>
+      <c r="K69" s="3" t="str">
+        <f t="shared" si="70"/>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
+      </c>
+      <c r="L69" s="3" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
       <c r="M69" t="str">
         <f t="array" ref="M69">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L69, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+      </c>
+      <c r="Q69" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="AI69" s="13" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="70" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="13" t="s">
+        <v>364</v>
+      </c>
+      <c r="C70" t="str">
+        <f t="shared" si="64"/>
+        <v>2</v>
+      </c>
+      <c r="D70" t="str">
+        <f t="shared" si="65"/>
+        <v>Turner_etal_2016</v>
+      </c>
+      <c r="E70" s="7" t="str">
+        <f t="shared" si="66"/>
+        <v>Turner</v>
+      </c>
+      <c r="F70" s="2" t="str">
+        <f t="shared" si="67"/>
+        <v>etal</v>
+      </c>
+      <c r="G70" s="7" t="str">
+        <f t="shared" si="68"/>
+        <v>2016</v>
+      </c>
+      <c r="H70" t="str">
+        <f t="shared" si="69"/>
+        <v>10.1159/000446762</v>
+      </c>
+      <c r="J70" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K70" s="3" t="str">
+        <f t="shared" si="70"/>
+        <v>Turner_etal_2016_Table1</v>
+      </c>
+      <c r="L70" s="3" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1159%2F000446762_Table1</v>
+      </c>
+      <c r="M70" t="str">
+        <f t="array" ref="M70">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L70, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P69" s="13" t="s">
+      <c r="N70" s="13" t="s">
+        <v>362</v>
+      </c>
+      <c r="Y70" s="13" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="71" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="13" t="s">
+        <v>350</v>
+      </c>
+      <c r="C71" t="str">
+        <f t="shared" si="64"/>
+        <v>1</v>
+      </c>
+      <c r="D71" t="str">
+        <f t="shared" si="65"/>
+        <v>Wilman_etal_2014</v>
+      </c>
+      <c r="E71" s="7" t="str">
+        <f t="shared" si="66"/>
+        <v>Wilman</v>
+      </c>
+      <c r="F71" s="2" t="str">
+        <f t="shared" si="67"/>
+        <v>etal</v>
+      </c>
+      <c r="G71" s="7" t="str">
+        <f t="shared" si="68"/>
+        <v>2014</v>
+      </c>
+      <c r="H71" t="str">
+        <f t="shared" si="69"/>
+        <v>10.1890/13-1917.1</v>
+      </c>
+      <c r="J71" s="13" t="s">
+        <v>338</v>
+      </c>
+      <c r="K71" s="3" t="str">
+        <f t="shared" si="70"/>
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+      </c>
+      <c r="L71" s="3" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+      </c>
+      <c r="M71" t="str">
+        <f t="array" ref="M71">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L71, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+    </row>
+    <row r="72" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="13" t="s">
+        <v>348</v>
+      </c>
+      <c r="C72" t="str">
+        <f t="shared" si="64"/>
+        <v>7</v>
+      </c>
+      <c r="D72" t="str">
+        <f t="shared" si="65"/>
+        <v>Wimberly_etal_2021</v>
+      </c>
+      <c r="E72" s="7" t="str">
+        <f t="shared" si="66"/>
+        <v>Wimberly</v>
+      </c>
+      <c r="F72" s="2" t="str">
+        <f t="shared" si="67"/>
+        <v>etal</v>
+      </c>
+      <c r="G72" s="7" t="str">
+        <f t="shared" si="68"/>
+        <v>2021</v>
+      </c>
+      <c r="H72" t="str">
+        <f t="shared" si="69"/>
+        <v>10.1098/rspb.2021.0937</v>
+      </c>
+      <c r="J72" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="K72" s="3" t="str">
+        <f t="shared" si="70"/>
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
+      </c>
+      <c r="L72" s="3" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+      </c>
+      <c r="M72" t="str">
+        <f t="array" ref="M72">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L72, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P72" s="13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="73" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A73" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="C73" t="str">
+        <f t="shared" si="64"/>
+        <v>5</v>
+      </c>
+      <c r="D73" t="str">
+        <f t="shared" si="65"/>
+        <v>Winkler_Bryant_2021</v>
+      </c>
+      <c r="E73" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Winkler</v>
+      </c>
+      <c r="F73" s="2" t="str">
+        <f t="shared" si="67"/>
+        <v>Bryant</v>
+      </c>
+      <c r="G73" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2021</v>
+      </c>
+      <c r="H73" t="str">
+        <f t="shared" si="69"/>
+        <v>10.1080/09524622.2021.1905065</v>
+      </c>
+      <c r="J73" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="K73" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Winkler_Bryant_2021_Figure1</v>
+      </c>
+      <c r="L73" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+      </c>
+      <c r="M73" t="str">
+        <f t="array" ref="M73">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L73, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P73" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q73" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="R73" s="14"/>
+      <c r="T73" s="13" t="str">
+        <f>IF(S73="N", R73, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U73" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="V73" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="Y73" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="AE73" s="13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="74" spans="1:35" x14ac:dyDescent="0.2">
+      <c r="A74" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C74" t="str">
+        <f t="shared" si="64"/>
+        <v>0</v>
+      </c>
+      <c r="D74" t="str">
+        <f t="shared" si="65"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="E74" s="2" t="str">
+        <f t="shared" si="66"/>
+        <v>Young</v>
+      </c>
+      <c r="F74" s="2" t="str">
+        <f t="shared" si="67"/>
+        <v>etal</v>
+      </c>
+      <c r="G74" s="2" t="str">
+        <f t="shared" si="68"/>
+        <v>2013</v>
+      </c>
+      <c r="H74" t="str">
+        <f t="shared" si="69"/>
+        <v>10.3389/fncir.2013.00030</v>
+      </c>
+      <c r="J74" s="13" t="s">
+        <v>52</v>
+      </c>
+      <c r="K74" s="1" t="str">
+        <f t="shared" si="70"/>
+        <v>Young_etal_2013_Table1</v>
+      </c>
+      <c r="L74" s="1" t="str">
+        <f t="shared" si="71"/>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+      </c>
+      <c r="M74" t="str">
+        <f t="array" ref="M74">IFERROR(INDEX(FileList!$A$1:$A$43, MATCH(L74, _xlfn.TEXTBEFORE(FileList!$A$1:$A$43, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P74" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="Q69" s="13" t="s">
+      <c r="Q74" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="R69" s="14"/>
-      <c r="T69" s="13" t="str">
-        <f>IF(S69="N", R69, "write file name")</f>
+      <c r="R74" s="14"/>
+      <c r="T74" s="13" t="str">
+        <f>IF(S74="N", R74, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="U69" s="13" t="s">
+      <c r="U74" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="V69" s="13" t="s">
+      <c r="V74" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="Y69" s="13" t="s">
+      <c r="Y74" s="13" t="s">
         <v>210</v>
       </c>
-      <c r="AE69" s="13" t="s">
+      <c r="AE74" s="13" t="s">
         <v>64</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:AK69">
-    <sortCondition ref="K4:K69"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:AK74">
+    <sortCondition ref="K5:K74"/>
   </sortState>
   <hyperlinks>
-    <hyperlink ref="X9" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="X8" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="X11" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="X13" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="X18" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="X57" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="X60" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="X30" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="X23:X26" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="X52" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="X51" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="X49" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="X20" r:id="rId13" xr:uid="{C1F957F4-0EDC-0E49-A387-57F382261715}"/>
-    <hyperlink ref="X21" r:id="rId14" xr:uid="{9C2C9343-3842-7E45-A05C-5DD83A0C30F9}"/>
+    <hyperlink ref="X10" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="X9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="X12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="X18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="X23" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="X62" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="X65" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="X35" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="X28:X31" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="X57" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="X56" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="X54" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="X25" r:id="rId13" xr:uid="{C1F957F4-0EDC-0E49-A387-57F382261715}"/>
+    <hyperlink ref="X26" r:id="rId14" xr:uid="{9C2C9343-3842-7E45-A05C-5DD83A0C30F9}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6862,17 +7231,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="ca9bcfe5a103c514723d0bd46d8b738f">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="6b0efe988aa2f142173325409561b0e5" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
     <xsd:import namespace="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <xsd:element name="properties">
@@ -7125,6 +7485,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7137,15 +7506,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E6C6718-1083-4BA4-895F-4D544A70F5E5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{196EEE13-1E58-4887-9EDC-D5AC20223AD0}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0C9D8A3E-8F8C-4C4A-8754-0B2D6BE83FF1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -7163,19 +7524,27 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5E6C6718-1083-4BA4-895F-4D544A70F5E5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ED7313F8-A05E-4214-AA83-B148B6D9FF29}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/crossmodal/Library/CloudStorage/OneDrive-AllenInstitute/Species/Evo-M1-Trait-Data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1DDFD38-8A94-4545-B3F0-CD27884E4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{D1DDFD38-8A94-4545-B3F0-CD27884E4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693E0F28-B917-413C-835D-D3D9247F7C35}"/>
   <bookViews>
-    <workbookView xWindow="36240" yWindow="-5840" windowWidth="42680" windowHeight="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36220" yWindow="-5860" windowWidth="42680" windowHeight="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Conflicts" sheetId="4" r:id="rId3"/>
     <sheet name="FileList" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="791" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="414">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -143,15 +143,18 @@
     <t>Flags active (skips)</t>
   </si>
   <si>
+    <t>Andelin, A. K., Olavarria, J. F., Fine, I., Taber, E. N., Schwartz, D., Kroenke, C. D., &amp; Stevens, A. A. (2019). The Effect of Onset Age of Visual Deprivation on Visual Cortex Surface Area Across-Species. Cereb Cortex, 29(10), 4321-4333. https://doi.org/10.1093/cercor/bhy315</t>
+  </si>
+  <si>
+    <t>table</t>
+  </si>
+  <si>
     <t>Avelino-de-Souza, K., Patzke, N., Karlsson, K. A. E., Manger, P. R., &amp; Herculano-Houzel, S. (2025). Cellular Composition of the Brain of a Northern Minke Whale. J Comp Neurol, 533(9), e70089. https://doi.org/10.1002/cne.70089</t>
   </si>
   <si>
     <t>TABLE 1</t>
   </si>
   <si>
-    <t>table</t>
-  </si>
-  <si>
     <t>neuron number</t>
   </si>
   <si>
@@ -483,6 +486,9 @@
   </si>
   <si>
     <t>TABLE 1 | Three behavioral correlates of plasticity and the proportion of REM (versus non-REM) sleep in 25 primate species.</t>
+  </si>
+  <si>
+    <t>proportion REM and developmental milestones</t>
   </si>
   <si>
     <t>Falcone, C., Wolf-Ochoa, M., Amina, S., Hong, T., Vakilzadeh, G., Hopkins, W. D., Hof, P. R., Sherwood, C. C., Manger, P. R., Noctor, S. C., &amp; Martinez-Cerdeno, V. (2019). Cortical interlaminar astrocytes across the therian mammal radiation. J Comp Neurol, 527(10), 1654-1674. https://doi.org/10.1002/cne.24605</t>
@@ -558,6 +564,9 @@
 study.</t>
   </si>
   <si>
+    <t>Haarlem, C. S., Hynes, C., Jackson, A. L., Mitchell, K. J., O'Connell, R. G., &amp; Healy, K. (2026). Pace of ecology drives the tempo of visual perception across the animal kingdom. Nat Ecol Evol. https://doi.org/10.1038/s41559-026-02994-7</t>
+  </si>
+  <si>
     <t>Heffner, R., &amp; Masterton, B. (1975). Variation in form of the pyramidal tract and its relationship to digital dexterity. Brain Behav Evol, 12(3), 161-200. https://doi.org/10.1159/000124401</t>
   </si>
   <si>
@@ -585,6 +594,18 @@
     <t>compare to 1975</t>
   </si>
   <si>
+    <t>Heiss, W. D., Habedank, B., Klein, J. C., Herholz, K., Wienhard, K., Lenox, M., &amp; Nutt, R. (2004). Metabolic rates in small brain nuclei determined by high-resolution PET. J Nucl Med, 45(11), 1811-1815. https://www.ncbi.nlm.nih.gov/pubmed/15534048</t>
+  </si>
+  <si>
+    <t>WOS:000225086000011</t>
+  </si>
+  <si>
+    <t>TABLE 1 rCMRGlc Values</t>
+  </si>
+  <si>
+    <t>regional cerebral metabolic rates for glucose</t>
+  </si>
+  <si>
     <t>Heldstab, S. A., Kosonen, Z. K., Koski, S. E., Burkart, J. M., van Schaik, C. P., &amp; Isler, K. (2016). Manipulation complexity in primates coevolved with brain size and terrestriality. Sci Rep, 6, 24528. https://doi.org/10.1038/srep24528</t>
   </si>
   <si>
@@ -594,6 +615,15 @@
     <t>Herculano-Houzel, S. (2015). Decreasing sleep requirement with increasing numbers of neurons as a driver for bigger brains and bodies in mammalian evolution. Proc Biol Sci, 282(1816), 20151853. https://doi.org/10.1098/rspb.2015.1853</t>
   </si>
   <si>
+    <t>Table 2</t>
+  </si>
+  <si>
+    <t>Table 2. Dataset on the ontogeny of sleep and cellular composition of the rat brain used in this study.</t>
+  </si>
+  <si>
+    <t>Per cent of hours asleep and brain size and composition</t>
+  </si>
+  <si>
     <t>Herculano-Houzel, S., Watson, C., &amp; Paxinos, G. (2013). Distribution of neurons in functional areas of the mouse cerebral cortex reveals quantitatively different cortical zones. Front Neuroanat, 7, 35. https://doi.org/10.3389/fnana.2013.00035</t>
   </si>
   <si>
@@ -624,9 +654,6 @@
     <t>placental mammals</t>
   </si>
   <si>
-    <t>Table 2</t>
-  </si>
-  <si>
     <t>Table 2. Cerebellum</t>
   </si>
   <si>
@@ -768,6 +795,15 @@
     <t>companion animals</t>
   </si>
   <si>
+    <t>Johansen, A., Beliveau, V., Colliander, E., Raval, N. R., Dam, V. H., Gillings, N., Aznar, S., Svarer, C., Plaven-Sigray, P., &amp; Knudsen, G. M. (2024). An In Vivo High-Resolution Human Brain Atlas of Synaptic Density. J Neurosci, 44(33). https://doi.org/10.1523/JNEUROSCI.1750-23.2024</t>
+  </si>
+  <si>
+    <t>Table 2. Summary of SV2A Bmax (pmol/mL) in individual regions in the left and right hemisphere and for a weighted average (total)</t>
+  </si>
+  <si>
+    <t>the synaptic marker Synaptic Vesicle glycoprotein 2A (SV2A)</t>
+  </si>
+  <si>
     <t>Karl, M. T., Kim, Y. D., Rajendran, K., Manger, P. R., &amp; Sherwood, C. C. (2024). Invariance of Mitochondria and Synapses in the Primary Visual Cortex of Mammals Provides Insight Into Energetics and Function. J Comp Neurol, 532(9), e25669. https://doi.org/10.1002/cne.25669</t>
   </si>
   <si>
@@ -1246,34 +1282,13 @@
   </si>
   <si>
     <t>README.md</t>
-  </si>
-  <si>
-    <t>Per cent of hours asleep and brain size and composition</t>
-  </si>
-  <si>
-    <t>Table 2. Dataset on the ontogeny of sleep and cellular composition of the rat brain used in this study.</t>
-  </si>
-  <si>
-    <t>proportion REM and developmental milestones</t>
-  </si>
-  <si>
-    <t>Heiss, W. D., Habedank, B., Klein, J. C., Herholz, K., Wienhard, K., Lenox, M., &amp; Nutt, R. (2004). Metabolic rates in small brain nuclei determined by high-resolution PET. J Nucl Med, 45(11), 1811-1815. https://www.ncbi.nlm.nih.gov/pubmed/15534048</t>
-  </si>
-  <si>
-    <t>WOS:000225086000011</t>
-  </si>
-  <si>
-    <t>TABLE 1 rCMRGlc Values</t>
-  </si>
-  <si>
-    <t>regional cerebral metabolic rates for glucose</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1378,7 +1393,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1397,7 +1412,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1418,9 +1432,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1458,7 +1472,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1564,7 +1578,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1706,7 +1720,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1714,41 +1728,41 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH78"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:AH82"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="42.1640625" customWidth="1"/>
-    <col min="2" max="2" width="5.1640625" customWidth="1"/>
-    <col min="3" max="3" width="22.83203125" customWidth="1"/>
-    <col min="4" max="4" width="34.83203125" customWidth="1"/>
+    <col min="1" max="1" width="42.125" customWidth="1"/>
+    <col min="2" max="2" width="5.125" customWidth="1"/>
+    <col min="3" max="3" width="22.875" customWidth="1"/>
+    <col min="4" max="4" width="34.875" customWidth="1"/>
     <col min="5" max="5" width="2" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="23.625" customWidth="1"/>
+    <col min="7" max="7" width="16.875" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="5.1640625" customWidth="1"/>
+    <col min="9" max="9" width="5.125" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="31.1640625" customWidth="1"/>
+    <col min="11" max="11" width="31.125" customWidth="1"/>
     <col min="12" max="12" width="46.5" customWidth="1"/>
     <col min="13" max="13" width="21.5" customWidth="1"/>
-    <col min="14" max="14" width="15.33203125" customWidth="1"/>
+    <col min="14" max="14" width="15.375" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="20" width="14.1640625" customWidth="1"/>
-    <col min="21" max="21" width="13.83203125" customWidth="1"/>
-    <col min="22" max="22" width="12.6640625" customWidth="1"/>
-    <col min="23" max="23" width="22.1640625" customWidth="1"/>
-    <col min="24" max="24" width="14.33203125" customWidth="1"/>
+    <col min="17" max="20" width="14.125" customWidth="1"/>
+    <col min="21" max="21" width="13.875" customWidth="1"/>
+    <col min="22" max="22" width="12.625" customWidth="1"/>
+    <col min="23" max="23" width="22.125" customWidth="1"/>
+    <col min="24" max="24" width="14.375" customWidth="1"/>
     <col min="25" max="25" width="39.5" customWidth="1"/>
-    <col min="26" max="26" width="11.1640625" customWidth="1"/>
+    <col min="26" max="26" width="11.125" customWidth="1"/>
     <col min="27" max="27" width="5" customWidth="1"/>
     <col min="28" max="28" width="7.5" customWidth="1"/>
-    <col min="29" max="29" width="10.6640625" customWidth="1"/>
-    <col min="30" max="30" width="10.83203125" customWidth="1"/>
+    <col min="29" max="29" width="10.625" customWidth="1"/>
+    <col min="30" max="30" width="10.875" customWidth="1"/>
     <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="34" width="10.83203125" customWidth="1"/>
+    <col min="32" max="34" width="10.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:34" ht="15.95" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1852,24 +1866,22 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:34" ht="15.95" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>35</v>
-      </c>
+      <c r="D2" s="1"/>
       <c r="E2" t="str">
         <f t="shared" ref="E2" si="0">RIGHT(A2,1)</f>
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="str">
         <f t="shared" ref="F2" si="1">G2 &amp; IF(H2&lt;&gt;"", "_" &amp; H2, "_") &amp; IF(I2&lt;&gt;"", "_" &amp; I2, "_") &amp; IF(B2&lt;&gt;"", "_" &amp; B2, "")</f>
-        <v>AvelinodeSouza_etal_2025</v>
+        <v>Andelin_etal_2019</v>
       </c>
       <c r="G2" t="str">
         <f t="shared" ref="G2" si="2">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A2,","), "-", ""), " ", "")</f>
-        <v>AvelinodeSouza</v>
+        <v>Andelin</v>
       </c>
       <c r="H2" t="str">
         <f t="shared" ref="H2" si="3">IF(ISNUMBER(FIND("&amp;", A2)),
@@ -1880,55 +1892,48 @@
       </c>
       <c r="I2" t="str">
         <f t="shared" ref="I2" si="4">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2, "("), ")")</f>
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="J2" t="str">
         <f>IF(C2&lt;&gt;"", C2, IF(C2="", _xlfn.TEXTAFTER(A2,"https://doi.org/"), C2))</f>
-        <v>10.1002/cne.70089</v>
+        <v>10.1093/cercor/bhy315</v>
       </c>
       <c r="K2" t="str">
-        <f t="shared" ref="K2:K14" si="5">TRIM(_xlfn.TEXTJOIN("_",FALSE,F2,(SUBSTITUTE(SUBSTITUTE(D2," ",""), "_", ""))))</f>
-        <v>AvelinodeSouza_etal_2025_TABLE1</v>
+        <f t="shared" ref="K2" si="5">TRIM(_xlfn.TEXTJOIN("_",FALSE,F2,(SUBSTITUTE(SUBSTITUTE(D2," ",""), "_", ""))))</f>
+        <v>Andelin_etal_2019_</v>
       </c>
       <c r="L2" t="str">
-        <f t="shared" ref="L2:L14" si="6">IF(ISBLANK(C2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1002%2Fcne.70089_TABLE1</v>
+        <f t="shared" ref="L2" si="6">IF(ISBLANK(C2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1093%2Fcercor%2Fbhy315_</v>
       </c>
       <c r="M2" t="str">
         <f t="array" ref="M2">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L2, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.70089_TABLE1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="V2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="1"/>
+    </row>
+    <row r="3" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="Y2" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Z2" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E3" t="str">
-        <f t="shared" ref="E3:E4" si="7">RIGHT(A3,1)</f>
-        <v>5</v>
+        <f t="shared" ref="E3" si="7">RIGHT(A3,1)</f>
+        <v>9</v>
       </c>
       <c r="F3" t="str">
         <f t="shared" ref="F3" si="8">G3 &amp; IF(H3&lt;&gt;"", "_" &amp; H3, "_") &amp; IF(I3&lt;&gt;"", "_" &amp; I3, "_") &amp; IF(B3&lt;&gt;"", "_" &amp; B3, "")</f>
-        <v>Baron_etal_1983</v>
+        <v>AvelinodeSouza_etal_2025</v>
       </c>
       <c r="G3" t="str">
         <f t="shared" ref="G3" si="9">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A3,","), "-", ""), " ", "")</f>
-        <v>Baron</v>
+        <v>AvelinodeSouza</v>
       </c>
       <c r="H3" t="str">
         <f t="shared" ref="H3" si="10">IF(ISNUMBER(FIND("&amp;", A3)),
@@ -1939,991 +1944,979 @@
       </c>
       <c r="I3" t="str">
         <f t="shared" ref="I3" si="11">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
-        <v>1983</v>
+        <v>2025</v>
       </c>
       <c r="J3" t="str">
-        <f t="shared" ref="J3:J66" si="12">IF(C3&lt;&gt;"", C3, IF(C3="", _xlfn.TEXTAFTER(A3,"https://doi.org/"), C3))</f>
-        <v>10.0000/placeholder.1</v>
+        <f>IF(C3&lt;&gt;"", C3, IF(C3="", _xlfn.TEXTAFTER(A3,"https://doi.org/"), C3))</f>
+        <v>10.1002/cne.70089</v>
       </c>
       <c r="K3" t="str">
-        <f t="shared" si="5"/>
-        <v>Baron_etal_1983_Table1</v>
+        <f t="shared" ref="K3:K15" si="12">TRIM(_xlfn.TEXTJOIN("_",FALSE,F3,(SUBSTITUTE(SUBSTITUTE(D3," ",""), "_", ""))))</f>
+        <v>AvelinodeSouza_etal_2025_TABLE1</v>
       </c>
       <c r="L3" t="str">
-        <f t="shared" si="6"/>
-        <v>10.0000%2Fplaceholder.1_Table1</v>
+        <f t="shared" ref="L3:L15" si="13">IF(ISBLANK(C3),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J3, SUBSTITUTE(D3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C3, SUBSTITUTE(D3,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1002%2Fcne.70089_TABLE1</v>
       </c>
       <c r="M3" t="str">
         <f t="array" ref="M3">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L3, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.0000%2Fplaceholder.1_Table1.tsv</v>
+        <v>10.1002%2Fcne.70089_TABLE1.tsv</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y3" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="4" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Z3" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E4" t="str">
-        <f t="shared" si="7"/>
-        <v>6</v>
+        <f t="shared" ref="E4:E5" si="14">RIGHT(A4,1)</f>
+        <v>5</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" ref="F4" si="13">G4 &amp; IF(H4&lt;&gt;"", "_" &amp; H4, "_") &amp; IF(I4&lt;&gt;"", "_" &amp; I4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
-        <v>Baron_etal_1987</v>
+        <f t="shared" ref="F4" si="15">G4 &amp; IF(H4&lt;&gt;"", "_" &amp; H4, "_") &amp; IF(I4&lt;&gt;"", "_" &amp; I4, "_") &amp; IF(B4&lt;&gt;"", "_" &amp; B4, "")</f>
+        <v>Baron_etal_1983</v>
       </c>
       <c r="G4" t="str">
-        <f t="shared" ref="G4" si="14">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G4" si="16">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A4,","), "-", ""), " ", "")</f>
         <v>Baron</v>
       </c>
       <c r="H4" t="str">
-        <f t="shared" ref="H4" si="15">IF(ISNUMBER(FIND("&amp;", A4)),
+        <f t="shared" ref="H4" si="17">IF(ISNUMBER(FIND("&amp;", A4)),
     IF(LEN(A4)-LEN(SUBSTITUTE(A4, ",", ""))&gt;=6, "etal", MID(A4, SEARCH("&amp; ", A4)+2, SEARCH(",", A4, SEARCH("&amp; ", A4)+2) - SEARCH("&amp; ", A4)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
       <c r="I4" t="str">
-        <f t="shared" ref="I4" si="16">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
-        <v>1987</v>
+        <f t="shared" ref="I4" si="18">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A4, "("), ")")</f>
+        <v>1983</v>
       </c>
       <c r="J4" t="str">
+        <f t="shared" ref="J4:J70" si="19">IF(C4&lt;&gt;"", C4, IF(C4="", _xlfn.TEXTAFTER(A4,"https://doi.org/"), C4))</f>
+        <v>10.0000/placeholder.1</v>
+      </c>
+      <c r="K4" t="str">
         <f t="shared" si="12"/>
-        <v>10.0000/placeholder.2</v>
-      </c>
-      <c r="K4" t="str">
-        <f t="shared" si="5"/>
-        <v>Baron_etal_1987_Table1</v>
+        <v>Baron_etal_1983_Table1</v>
       </c>
       <c r="L4" t="str">
-        <f t="shared" si="6"/>
-        <v>10.0000%2Fplaceholder.2_Table1</v>
+        <f t="shared" si="13"/>
+        <v>10.0000%2Fplaceholder.1_Table1</v>
       </c>
       <c r="M4" t="str">
         <f t="array" ref="M4">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L4, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.0000%2Fplaceholder.1_Table1.tsv</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W4" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Z4" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="E5" t="str">
-        <f t="shared" ref="E5:E46" si="17">RIGHT(A5,1)</f>
-        <v>0</v>
+        <f t="shared" si="14"/>
+        <v>6</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" ref="F5:F46" si="18">G5 &amp; IF(H5&lt;&gt;"", "_" &amp; H5, "_") &amp; IF(I5&lt;&gt;"", "_" &amp; I5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
-        <v>Brodmann__1913</v>
+        <f t="shared" ref="F5" si="20">G5 &amp; IF(H5&lt;&gt;"", "_" &amp; H5, "_") &amp; IF(I5&lt;&gt;"", "_" &amp; I5, "_") &amp; IF(B5&lt;&gt;"", "_" &amp; B5, "")</f>
+        <v>Baron_etal_1987</v>
       </c>
       <c r="G5" t="str">
-        <f t="shared" ref="G5:G46" si="19">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
-        <v>Brodmann</v>
+        <f t="shared" ref="G5" si="21">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A5,","), "-", ""), " ", "")</f>
+        <v>Baron</v>
       </c>
       <c r="H5" t="str">
-        <f t="shared" ref="H5:H46" si="20">IF(ISNUMBER(FIND("&amp;", A5)),
+        <f t="shared" ref="H5" si="22">IF(ISNUMBER(FIND("&amp;", A5)),
     IF(LEN(A5)-LEN(SUBSTITUTE(A5, ",", ""))&gt;=6, "etal", MID(A5, SEARCH("&amp; ", A5)+2, SEARCH(",", A5, SEARCH("&amp; ", A5)+2) - SEARCH("&amp; ", A5)-2)),
     ""
 )</f>
-        <v/>
+        <v>etal</v>
       </c>
       <c r="I5" t="str">
-        <f t="shared" ref="I5:I46" si="21">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
-        <v>1913</v>
+        <f t="shared" ref="I5" si="23">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A5, "("), ")")</f>
+        <v>1987</v>
       </c>
       <c r="J5" t="str">
+        <f t="shared" si="19"/>
+        <v>10.0000/placeholder.2</v>
+      </c>
+      <c r="K5" t="str">
         <f t="shared" si="12"/>
-        <v>10.0000/placeholder</v>
-      </c>
-      <c r="K5" t="str">
-        <f t="shared" si="5"/>
-        <v>Brodmann__1913_Tabelle1</v>
+        <v>Baron_etal_1987_Table1</v>
       </c>
       <c r="L5" t="str">
-        <f t="shared" si="6"/>
-        <v>10.0000%2Fplaceholder_Tabelle1</v>
+        <f t="shared" si="13"/>
+        <v>10.0000%2Fplaceholder.2_Table1</v>
       </c>
       <c r="M5" t="str">
         <f t="array" ref="M5">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L5, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-    </row>
-    <row r="6" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="V5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W5" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="6" spans="1:34" ht="15.95" customHeight="1">
       <c r="A6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>49</v>
-      </c>
       <c r="E6" t="str">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" ref="E6:E49" si="24">RIGHT(A6,1)</f>
+        <v>0</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" si="18"/>
-        <v>Burger_etal_2019</v>
+        <f t="shared" ref="F6:F49" si="25">G6 &amp; IF(H6&lt;&gt;"", "_" &amp; H6, "_") &amp; IF(I6&lt;&gt;"", "_" &amp; I6, "_") &amp; IF(B6&lt;&gt;"", "_" &amp; B6, "")</f>
+        <v>Brodmann__1913</v>
       </c>
       <c r="G6" t="str">
+        <f t="shared" ref="G6:G49" si="26">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A6,","), "-", ""), " ", "")</f>
+        <v>Brodmann</v>
+      </c>
+      <c r="H6" t="str">
+        <f t="shared" ref="H6:H49" si="27">IF(ISNUMBER(FIND("&amp;", A6)),
+    IF(LEN(A6)-LEN(SUBSTITUTE(A6, ",", ""))&gt;=6, "etal", MID(A6, SEARCH("&amp; ", A6)+2, SEARCH(",", A6, SEARCH("&amp; ", A6)+2) - SEARCH("&amp; ", A6)-2)),
+    ""
+)</f>
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" ref="I6:I49" si="28">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A6, "("), ")")</f>
+        <v>1913</v>
+      </c>
+      <c r="J6" t="str">
         <f t="shared" si="19"/>
-        <v>Burger</v>
-      </c>
-      <c r="H6" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I6" t="str">
-        <f t="shared" si="21"/>
-        <v>2019</v>
-      </c>
-      <c r="J6" t="str">
+        <v>10.0000/placeholder</v>
+      </c>
+      <c r="K6" t="str">
         <f t="shared" si="12"/>
-        <v>10.1093/jmammal/gyz043</v>
-      </c>
-      <c r="K6" t="str">
-        <f t="shared" si="5"/>
-        <v>Burger_etal_2019_SupplementaryDataSD1</v>
+        <v>Brodmann__1913_Tabelle1</v>
       </c>
       <c r="L6" t="str">
-        <f t="shared" si="6"/>
-        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
+        <f t="shared" si="13"/>
+        <v>10.0000%2Fplaceholder_Tabelle1</v>
       </c>
       <c r="M6" t="str">
         <f t="array" ref="M6">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L6, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
-      </c>
-      <c r="O6" s="1" t="s">
+        <v>notfound</v>
+      </c>
+    </row>
+    <row r="7" spans="1:34" ht="17.100000000000001" customHeight="1">
+      <c r="A7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="P6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="T6" s="1" t="str">
-        <f>IF(S6="N", R6, "write file name")</f>
-        <v>gyz043_suppl_Supplement_Data.csv</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="Z6" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD6" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="AE6" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="7" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="E7" t="str">
-        <f t="shared" si="17"/>
-        <v>9</v>
+        <f t="shared" si="24"/>
+        <v>3</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="18"/>
-        <v>Burish_etal_2010</v>
+        <f t="shared" si="25"/>
+        <v>Burger_etal_2019</v>
       </c>
       <c r="G7" t="str">
+        <f t="shared" si="26"/>
+        <v>Burger</v>
+      </c>
+      <c r="H7" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="28"/>
+        <v>2019</v>
+      </c>
+      <c r="J7" t="str">
         <f t="shared" si="19"/>
-        <v>Burish</v>
-      </c>
-      <c r="H7" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I7" t="str">
-        <f t="shared" si="21"/>
-        <v>2010</v>
-      </c>
-      <c r="J7" t="str">
+        <v>10.1093/jmammal/gyz043</v>
+      </c>
+      <c r="K7" t="str">
         <f t="shared" si="12"/>
-        <v>10.1159/000319019</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="5"/>
-        <v>Burish_etal_2010_SupplementaryTable1</v>
+        <v>Burger_etal_2019_SupplementaryDataSD1</v>
       </c>
       <c r="L7" t="str">
-        <f t="shared" si="6"/>
-        <v>10.1159%2F000319019_SupplementaryTable1</v>
+        <f t="shared" si="13"/>
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1</v>
       </c>
       <c r="M7" t="str">
         <f t="array" ref="M7">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L7, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="N7" s="1" t="s">
+        <v>10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="R7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="T7" s="1" t="str">
+        <f>IF(S7="N", R7, "write file name")</f>
+        <v>gyz043_suppl_Supplement_Data.csv</v>
+      </c>
+      <c r="U7" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W7" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Y7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="AE7" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="8" spans="1:34" ht="17.100000000000001" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="P7" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Z7" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="AC7" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE7" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="8" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E8" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>9</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>Burish_etal_2010</v>
       </c>
       <c r="G8" t="str">
+        <f t="shared" si="26"/>
+        <v>Burish</v>
+      </c>
+      <c r="H8" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="28"/>
+        <v>2010</v>
+      </c>
+      <c r="J8" t="str">
         <f t="shared" si="19"/>
-        <v>Burish</v>
-      </c>
-      <c r="H8" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I8" t="str">
-        <f t="shared" si="21"/>
-        <v>2010</v>
-      </c>
-      <c r="J8" t="str">
+        <v>10.1159/000319019</v>
+      </c>
+      <c r="K8" t="str">
         <f t="shared" si="12"/>
-        <v>10.1159/000319019</v>
-      </c>
-      <c r="K8" t="str">
-        <f t="shared" si="5"/>
-        <v>Burish_etal_2010_Table1</v>
+        <v>Burish_etal_2010_SupplementaryTable1</v>
       </c>
       <c r="L8" t="str">
-        <f t="shared" si="6"/>
-        <v>10.1159%2F000319019_Table1</v>
+        <f t="shared" si="13"/>
+        <v>10.1159%2F000319019_SupplementaryTable1</v>
       </c>
       <c r="M8" t="str">
         <f t="array" ref="M8">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L8, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000319019_Table1.tsv</v>
+        <v>10.1159%2F000319019_SupplementaryTable1.tsv</v>
       </c>
       <c r="N8" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="R8" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="AC8" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE8" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="P8" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z8" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="AC8" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="AE8" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="9" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="9" spans="1:34" ht="15.95" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>74</v>
+        <v>42</v>
       </c>
       <c r="E9" t="str">
-        <f t="shared" si="17"/>
-        <v>5</v>
+        <f t="shared" si="24"/>
+        <v>9</v>
       </c>
       <c r="F9" t="str">
-        <f t="shared" si="18"/>
-        <v>Caspar_etal_2022</v>
+        <f t="shared" si="25"/>
+        <v>Burish_etal_2010</v>
       </c>
       <c r="G9" t="str">
+        <f t="shared" si="26"/>
+        <v>Burish</v>
+      </c>
+      <c r="H9" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="28"/>
+        <v>2010</v>
+      </c>
+      <c r="J9" t="str">
         <f t="shared" si="19"/>
-        <v>Caspar</v>
-      </c>
-      <c r="H9" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I9" t="str">
-        <f t="shared" si="21"/>
-        <v>2022</v>
-      </c>
-      <c r="J9" t="str">
+        <v>10.1159/000319019</v>
+      </c>
+      <c r="K9" t="str">
         <f t="shared" si="12"/>
-        <v>10.7554/eLife.77875</v>
-      </c>
-      <c r="K9" t="str">
-        <f t="shared" si="5"/>
-        <v>Caspar_etal_2022_Supplementaryfile3</v>
+        <v>Burish_etal_2010_Table1</v>
       </c>
       <c r="L9" t="str">
-        <f t="shared" si="6"/>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
+        <f t="shared" si="13"/>
+        <v>10.1159%2F000319019_Table1</v>
       </c>
       <c r="M9" t="str">
         <f t="array" ref="M9">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L9, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
+        <v>10.1159%2F000319019_Table1.tsv</v>
       </c>
       <c r="N9" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="P9" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="AE9" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="P9" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="T9" s="1" t="str">
-        <f>IF(S9="N", R9, "write file name")</f>
-        <v>elife-77875-supp3-v1.xlsx</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="Z9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE9" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E10" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>5</v>
       </c>
       <c r="F10" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>Caspar_etal_2022</v>
       </c>
       <c r="G10" t="str">
+        <f t="shared" si="26"/>
+        <v>Caspar</v>
+      </c>
+      <c r="H10" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="28"/>
+        <v>2022</v>
+      </c>
+      <c r="J10" t="str">
         <f t="shared" si="19"/>
-        <v>Caspar</v>
-      </c>
-      <c r="H10" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I10" t="str">
-        <f t="shared" si="21"/>
-        <v>2022</v>
-      </c>
-      <c r="J10" t="str">
+        <v>10.7554/eLife.77875</v>
+      </c>
+      <c r="K10" t="str">
         <f t="shared" si="12"/>
-        <v>10.7554/eLife.77875</v>
-      </c>
-      <c r="K10" t="str">
-        <f t="shared" si="5"/>
-        <v>Caspar_etal_2022_Table1</v>
+        <v>Caspar_etal_2022_Supplementaryfile3</v>
       </c>
       <c r="L10" t="str">
-        <f t="shared" si="6"/>
-        <v>10.7554%2FeLife.77875_Table1</v>
+        <f t="shared" si="13"/>
+        <v>10.7554%2FeLife.77875_Supplementaryfile3</v>
       </c>
       <c r="M10" t="str">
         <f t="array" ref="M10">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L10, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.7554%2FeLife.77875_Table1.tsv</v>
+        <v>10.7554%2FeLife.77875_Supplementaryfile3.tsv</v>
       </c>
       <c r="N10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="P10" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="T10" s="1" t="str">
+        <f>IF(S10="N", R10, "write file name")</f>
+        <v>elife-77875-supp3-v1.xlsx</v>
+      </c>
+      <c r="U10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y10" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE10" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="P10" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="U10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V10" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="Y10" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="Z10" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AD10" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AE10" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="11" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="11" spans="1:34" ht="15.95" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>93</v>
+        <v>42</v>
       </c>
       <c r="E11" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>5</v>
       </c>
       <c r="F11" t="str">
-        <f t="shared" si="18"/>
-        <v>Changizi__2001</v>
+        <f t="shared" si="25"/>
+        <v>Caspar_etal_2022</v>
       </c>
       <c r="G11" t="str">
+        <f t="shared" si="26"/>
+        <v>Caspar</v>
+      </c>
+      <c r="H11" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="28"/>
+        <v>2022</v>
+      </c>
+      <c r="J11" t="str">
         <f t="shared" si="19"/>
-        <v>Changizi</v>
-      </c>
-      <c r="H11" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <f t="shared" si="21"/>
-        <v>2001</v>
-      </c>
-      <c r="J11" t="str">
+        <v>10.7554/eLife.77875</v>
+      </c>
+      <c r="K11" t="str">
         <f t="shared" si="12"/>
-        <v>10.1007/s004220000205</v>
-      </c>
-      <c r="K11" t="str">
-        <f t="shared" si="5"/>
-        <v>Changizi__2001_Figure3</v>
+        <v>Caspar_etal_2022_Table1</v>
       </c>
       <c r="L11" t="str">
-        <f t="shared" si="6"/>
-        <v>10.1007%2Fs004220000205_Figure3</v>
+        <f t="shared" si="13"/>
+        <v>10.7554%2FeLife.77875_Table1</v>
       </c>
       <c r="M11" t="str">
         <f t="array" ref="M11">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L11, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
+        <v>10.7554%2FeLife.77875_Table1.tsv</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="P11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="U11" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="Y11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="AE11" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="12" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A12" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D12" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Q11" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="U11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V11" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="W11" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y11" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="Z11" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD11" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="E12" t="str">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" si="24"/>
+        <v>5</v>
       </c>
       <c r="F12" t="str">
-        <f t="shared" si="18"/>
-        <v>Chen_Wiens_2020</v>
+        <f t="shared" si="25"/>
+        <v>Changizi__2001</v>
       </c>
       <c r="G12" t="str">
+        <f t="shared" si="26"/>
+        <v>Changizi</v>
+      </c>
+      <c r="H12" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="28"/>
+        <v>2001</v>
+      </c>
+      <c r="J12" t="str">
         <f t="shared" si="19"/>
-        <v>Chen</v>
-      </c>
-      <c r="H12" t="str">
-        <f t="shared" si="20"/>
-        <v>Wiens</v>
-      </c>
-      <c r="I12" t="str">
-        <f t="shared" si="21"/>
-        <v>2020</v>
-      </c>
-      <c r="J12" t="str">
+        <v>10.1007/s004220000205</v>
+      </c>
+      <c r="K12" t="str">
         <f t="shared" si="12"/>
-        <v>10.1038/s41467-020-14356-3</v>
-      </c>
-      <c r="K12" t="str">
-        <f t="shared" si="5"/>
-        <v>Chen_Wiens_2020_SupplementaryData3</v>
+        <v>Changizi__2001_Figure3</v>
       </c>
       <c r="L12" t="str">
-        <f t="shared" si="6"/>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
+        <f t="shared" si="13"/>
+        <v>10.1007%2Fs004220000205_Figure3</v>
       </c>
       <c r="M12" t="str">
         <f t="array" ref="M12">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L12, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
+        <v>10.1007%2Fs004220000205_Figure3.tsv</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>70</v>
+        <v>96</v>
       </c>
       <c r="R12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="U12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="W12" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y12" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A13" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="S12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="T12" s="1" t="str">
-        <f>IF(S12="N", R12, "write file name")</f>
-        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
-      </c>
-      <c r="U12" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="V12" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X12" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="Y12" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="Z12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC12" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD12" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="AE12" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="13" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>112</v>
-      </c>
       <c r="E13" t="str">
-        <f t="shared" si="17"/>
-        <v>7</v>
+        <f t="shared" si="24"/>
+        <v>3</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" si="18"/>
-        <v>Collins_etal_2010</v>
+        <f t="shared" si="25"/>
+        <v>Chen_Wiens_2020</v>
       </c>
       <c r="G13" t="str">
+        <f t="shared" si="26"/>
+        <v>Chen</v>
+      </c>
+      <c r="H13" t="str">
+        <f t="shared" si="27"/>
+        <v>Wiens</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="28"/>
+        <v>2020</v>
+      </c>
+      <c r="J13" t="str">
         <f t="shared" si="19"/>
-        <v>Collins</v>
-      </c>
-      <c r="H13" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I13" t="str">
-        <f t="shared" si="21"/>
-        <v>2010</v>
-      </c>
-      <c r="J13" t="str">
+        <v>10.1038/s41467-020-14356-3</v>
+      </c>
+      <c r="K13" t="str">
         <f t="shared" si="12"/>
-        <v>10.1073/pnas.1010356107</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="5"/>
-        <v>Collins_etal_2010_DatasetS1</v>
+        <v>Chen_Wiens_2020_SupplementaryData3</v>
       </c>
       <c r="L13" t="str">
-        <f t="shared" si="6"/>
-        <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
+        <f t="shared" si="13"/>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3</v>
       </c>
       <c r="M13" t="str">
         <f t="array" ref="M13">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L13, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</v>
+      </c>
+      <c r="P13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R13" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="T13" s="1" t="str">
+        <f>IF(S13="N", R13, "write file name")</f>
+        <v>41467_2020_14356_MOESM6_ESM.xlsx</v>
+      </c>
+      <c r="U13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="V13" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W13" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>107</v>
       </c>
       <c r="Y13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="AE13" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D14" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="Z13" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="14" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="E14" t="str">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="24"/>
+        <v>7</v>
       </c>
       <c r="F14" t="str">
-        <f t="shared" si="18"/>
-        <v>DeCasien_Higham_2019</v>
+        <f t="shared" si="25"/>
+        <v>Collins_etal_2010</v>
       </c>
       <c r="G14" t="str">
+        <f t="shared" si="26"/>
+        <v>Collins</v>
+      </c>
+      <c r="H14" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="28"/>
+        <v>2010</v>
+      </c>
+      <c r="J14" t="str">
         <f t="shared" si="19"/>
-        <v>DeCasien</v>
-      </c>
-      <c r="H14" t="str">
-        <f t="shared" si="20"/>
-        <v>Higham</v>
-      </c>
-      <c r="I14" t="str">
-        <f t="shared" si="21"/>
-        <v>2019</v>
-      </c>
-      <c r="J14" t="str">
+        <v>10.1073/pnas.1010356107</v>
+      </c>
+      <c r="K14" t="str">
         <f t="shared" si="12"/>
-        <v>10.1038/s41559-019-0969-0</v>
-      </c>
-      <c r="K14" t="str">
-        <f t="shared" si="5"/>
-        <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
+        <v>Collins_etal_2010_DatasetS1</v>
       </c>
       <c r="L14" t="str">
-        <f t="shared" si="6"/>
-        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-BrainRegion</v>
+        <f t="shared" si="13"/>
+        <v>10.1073%2Fpnas.1010356107_DatasetS1</v>
       </c>
       <c r="M14" t="str">
         <f t="array" ref="M14">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L14, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N14" s="1" t="s">
+      <c r="Y14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="U14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="Z14" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AD14" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="AE14" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>121</v>
-      </c>
       <c r="E15" t="str">
-        <f t="shared" ref="E15" si="22">RIGHT(A15,1)</f>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="F15" t="str">
-        <f t="shared" ref="F15" si="23">G15 &amp; IF(H15&lt;&gt;"", "_" &amp; H15, "_") &amp; IF(I15&lt;&gt;"", "_" &amp; I15, "_") &amp; IF(B15&lt;&gt;"", "_" &amp; B15, "")</f>
+        <f t="shared" si="25"/>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G15" t="str">
-        <f t="shared" ref="G15" si="24">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A15,","), "-", ""), " ", "")</f>
+        <f t="shared" si="26"/>
         <v>DeCasien</v>
       </c>
       <c r="H15" t="str">
-        <f t="shared" ref="H15" si="25">IF(ISNUMBER(FIND("&amp;", A15)),
-    IF(LEN(A15)-LEN(SUBSTITUTE(A15, ",", ""))&gt;=6, "etal", MID(A15, SEARCH("&amp; ", A15)+2, SEARCH(",", A15, SEARCH("&amp; ", A15)+2) - SEARCH("&amp; ", A15)-2)),
-    ""
-)</f>
+        <f t="shared" si="27"/>
         <v>Higham</v>
       </c>
       <c r="I15" t="str">
-        <f t="shared" ref="I15" si="26">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A15, "("), ")")</f>
+        <f t="shared" si="28"/>
         <v>2019</v>
       </c>
       <c r="J15" t="str">
+        <f t="shared" si="19"/>
+        <v>10.1038/s41559-019-0969-0</v>
+      </c>
+      <c r="K15" t="str">
         <f t="shared" si="12"/>
-        <v>10.1038/s41559-019-0969-0</v>
-      </c>
-      <c r="K15" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F15,(SUBSTITUTE(SUBSTITUTE(D16," ",""), "_", ""))))</f>
-        <v>DeCasien_Higham_2019_SupplementaryData1-Diet</v>
+        <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="L15" t="str">
-        <f>IF(ISBLANK(C15),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J15, SUBSTITUTE(D16,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C15, SUBSTITUTE(D16,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-Diet</v>
+        <f t="shared" si="13"/>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="M15" t="str">
         <f t="array" ref="M15">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L15, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y15" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="AE15" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" ht="15.95" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="Z15" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE15" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="16" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>123</v>
-      </c>
       <c r="E16" t="str">
-        <f t="shared" ref="E16" si="27">RIGHT(A16,1)</f>
+        <f t="shared" ref="E16" si="29">RIGHT(A16,1)</f>
         <v>0</v>
       </c>
       <c r="F16" t="str">
-        <f t="shared" ref="F16" si="28">G16 &amp; IF(H16&lt;&gt;"", "_" &amp; H16, "_") &amp; IF(I16&lt;&gt;"", "_" &amp; I16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
+        <f t="shared" ref="F16" si="30">G16 &amp; IF(H16&lt;&gt;"", "_" &amp; H16, "_") &amp; IF(I16&lt;&gt;"", "_" &amp; I16, "_") &amp; IF(B16&lt;&gt;"", "_" &amp; B16, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G16" t="str">
-        <f t="shared" ref="G16" si="29">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G16" si="31">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A16,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H16" t="str">
-        <f t="shared" ref="H16" si="30">IF(ISNUMBER(FIND("&amp;", A16)),
+        <f t="shared" ref="H16" si="32">IF(ISNUMBER(FIND("&amp;", A16)),
     IF(LEN(A16)-LEN(SUBSTITUTE(A16, ",", ""))&gt;=6, "etal", MID(A16, SEARCH("&amp; ", A16)+2, SEARCH(",", A16, SEARCH("&amp; ", A16)+2) - SEARCH("&amp; ", A16)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I16" t="str">
-        <f t="shared" ref="I16" si="31">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
+        <f t="shared" ref="I16" si="33">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A16, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J16" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K16" t="str">
         <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F16,(SUBSTITUTE(SUBSTITUTE(D17," ",""), "_", ""))))</f>
-        <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
+        <v>DeCasien_Higham_2019_SupplementaryData1-Diet</v>
       </c>
       <c r="L16" t="str">
         <f>IF(ISBLANK(C16),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J16, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C16, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-Diet</v>
       </c>
       <c r="M16" t="str">
         <f t="array" ref="M16">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L16, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y16" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE16" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D17" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="Z16" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE16" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>125</v>
-      </c>
       <c r="E17" t="str">
-        <f t="shared" ref="E17" si="32">RIGHT(A17,1)</f>
+        <f t="shared" ref="E17" si="34">RIGHT(A17,1)</f>
         <v>0</v>
       </c>
       <c r="F17" t="str">
-        <f t="shared" ref="F17" si="33">G17 &amp; IF(H17&lt;&gt;"", "_" &amp; H17, "_") &amp; IF(I17&lt;&gt;"", "_" &amp; I17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
+        <f t="shared" ref="F17" si="35">G17 &amp; IF(H17&lt;&gt;"", "_" &amp; H17, "_") &amp; IF(I17&lt;&gt;"", "_" &amp; I17, "_") &amp; IF(B17&lt;&gt;"", "_" &amp; B17, "")</f>
         <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G17" t="str">
-        <f t="shared" ref="G17" si="34">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G17" si="36">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A17,","), "-", ""), " ", "")</f>
         <v>DeCasien</v>
       </c>
       <c r="H17" t="str">
-        <f t="shared" ref="H17" si="35">IF(ISNUMBER(FIND("&amp;", A17)),
+        <f t="shared" ref="H17" si="37">IF(ISNUMBER(FIND("&amp;", A17)),
     IF(LEN(A17)-LEN(SUBSTITUTE(A17, ",", ""))&gt;=6, "etal", MID(A17, SEARCH("&amp; ", A17)+2, SEARCH(",", A17, SEARCH("&amp; ", A17)+2) - SEARCH("&amp; ", A17)-2)),
     ""
 )</f>
         <v>Higham</v>
       </c>
       <c r="I17" t="str">
-        <f t="shared" ref="I17" si="36">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
+        <f t="shared" ref="I17" si="38">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A17, "("), ")")</f>
         <v>2019</v>
       </c>
       <c r="J17" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K17" t="str">
-        <f t="shared" ref="K17:K49" si="37">TRIM(_xlfn.TEXTJOIN("_",FALSE,F17,(SUBSTITUTE(SUBSTITUTE(D17," ",""), "_", ""))))</f>
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE,F17,(SUBSTITUTE(SUBSTITUTE(D18," ",""), "_", ""))))</f>
         <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L17" t="str">
-        <f t="shared" ref="L17:L49" si="38">IF(ISBLANK(C17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C17, SUBSTITUTE(D17,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <f>IF(ISBLANK(C17),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J17, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C17, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
         <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="M17" t="str">
@@ -2931,746 +2924,761 @@
         <v>notfound</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="Y17" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE17" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="Z17" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AE17" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>128</v>
-      </c>
       <c r="E18" t="str">
-        <f t="shared" si="17"/>
-        <v>6</v>
+        <f t="shared" ref="E18" si="39">RIGHT(A18,1)</f>
+        <v>0</v>
       </c>
       <c r="F18" t="str">
-        <f t="shared" si="18"/>
-        <v>DosSantos_etal_2017</v>
+        <f t="shared" ref="F18" si="40">G18 &amp; IF(H18&lt;&gt;"", "_" &amp; H18, "_") &amp; IF(I18&lt;&gt;"", "_" &amp; I18, "_") &amp; IF(B18&lt;&gt;"", "_" &amp; B18, "")</f>
+        <v>DeCasien_Higham_2019</v>
       </c>
       <c r="G18" t="str">
+        <f t="shared" ref="G18" si="41">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A18,","), "-", ""), " ", "")</f>
+        <v>DeCasien</v>
+      </c>
+      <c r="H18" t="str">
+        <f t="shared" ref="H18" si="42">IF(ISNUMBER(FIND("&amp;", A18)),
+    IF(LEN(A18)-LEN(SUBSTITUTE(A18, ",", ""))&gt;=6, "etal", MID(A18, SEARCH("&amp; ", A18)+2, SEARCH(",", A18, SEARCH("&amp; ", A18)+2) - SEARCH("&amp; ", A18)-2)),
+    ""
+)</f>
+        <v>Higham</v>
+      </c>
+      <c r="I18" t="str">
+        <f t="shared" ref="I18" si="43">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A18, "("), ")")</f>
+        <v>2019</v>
+      </c>
+      <c r="J18" t="str">
         <f t="shared" si="19"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="H18" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I18" t="str">
-        <f t="shared" si="21"/>
-        <v>2017</v>
-      </c>
-      <c r="J18" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1159/000452856</v>
+        <v>10.1038/s41559-019-0969-0</v>
       </c>
       <c r="K18" t="str">
-        <f t="shared" si="37"/>
-        <v>DosSantos_etal_2017_TableS1</v>
+        <f t="shared" ref="K18:K52" si="44">TRIM(_xlfn.TEXTJOIN("_",FALSE,F18,(SUBSTITUTE(SUBSTITUTE(D18," ",""), "_", ""))))</f>
+        <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L18" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1159%2F000452856_TableS1</v>
+        <f t="shared" ref="L18:L52" si="45">IF(ISBLANK(C18),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J18, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C18, SUBSTITUTE(D18,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1038%2Fs41559-019-0969-0_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="M18" t="str">
         <f t="array" ref="M18">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L18, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000452856_TableS1.tsv</v>
-      </c>
-      <c r="O18" s="1" t="s">
+        <v>notfound</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="U18" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="V18" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="W18" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="Y18" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AE18" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A19" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D19" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="P18" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z18" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA18" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB18" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE18" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="AF18" s="1" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E19" t="str">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="24"/>
+        <v>6</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" si="18"/>
-        <v>DosSantos_etal_2020</v>
+        <f t="shared" si="25"/>
+        <v>DosSantos_etal_2017</v>
       </c>
       <c r="G19" t="str">
+        <f t="shared" si="26"/>
+        <v>DosSantos</v>
+      </c>
+      <c r="H19" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I19" t="str">
+        <f t="shared" si="28"/>
+        <v>2017</v>
+      </c>
+      <c r="J19" t="str">
         <f t="shared" si="19"/>
-        <v>DosSantos</v>
-      </c>
-      <c r="H19" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I19" t="str">
-        <f t="shared" si="21"/>
-        <v>2020</v>
-      </c>
-      <c r="J19" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1523/JNEUROSCI.2339-19.2020</v>
+        <v>10.1159/000452856</v>
       </c>
       <c r="K19" t="str">
-        <f t="shared" si="37"/>
-        <v>DosSantos_etal_2020_Table1</v>
+        <f t="shared" si="44"/>
+        <v>DosSantos_etal_2017_TableS1</v>
       </c>
       <c r="L19" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
+        <f t="shared" si="45"/>
+        <v>10.1159%2F000452856_TableS1</v>
       </c>
       <c r="M19" t="str">
         <f t="array" ref="M19">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L19, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1159%2F000452856_TableS1.tsv</v>
+      </c>
+      <c r="O19" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="P19" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R19" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T19" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="U19" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="V19" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="W19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y19" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AA19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB19" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE19" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AF19" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A20" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E20" t="str">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="F20" t="str">
+        <f t="shared" si="25"/>
+        <v>DosSantos_etal_2020</v>
+      </c>
+      <c r="G20" t="str">
+        <f t="shared" si="26"/>
+        <v>DosSantos</v>
+      </c>
+      <c r="H20" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I20" t="str">
+        <f t="shared" si="28"/>
+        <v>2020</v>
+      </c>
+      <c r="J20" t="str">
+        <f t="shared" si="19"/>
+        <v>10.1523/JNEUROSCI.2339-19.2020</v>
+      </c>
+      <c r="K20" t="str">
+        <f t="shared" si="44"/>
+        <v>DosSantos_etal_2020_Table1</v>
+      </c>
+      <c r="L20" t="str">
+        <f t="shared" si="45"/>
+        <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1</v>
+      </c>
+      <c r="M20" t="str">
+        <f t="array" ref="M20">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L20, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</v>
       </c>
-      <c r="P19" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R19" s="4" t="s">
+      <c r="P20" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R20" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T20" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="U20" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="V20" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y20" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AA20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB20" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE20" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A21" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="S19" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z19" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="AA19" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB19" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE19" s="1" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="E20" t="str">
-        <f t="shared" ref="E20" si="39">RIGHT(A20,1)</f>
+      <c r="D21" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="E21" t="str">
+        <f t="shared" ref="E21" si="46">RIGHT(A21,1)</f>
         <v>0</v>
       </c>
-      <c r="F20" t="str">
-        <f t="shared" ref="F20" si="40">G20 &amp; IF(H20&lt;&gt;"", "_" &amp; H20, "_") &amp; IF(I20&lt;&gt;"", "_" &amp; I20, "_") &amp; IF(B20&lt;&gt;"", "_" &amp; B20, "")</f>
+      <c r="F21" t="str">
+        <f t="shared" ref="F21" si="47">G21 &amp; IF(H21&lt;&gt;"", "_" &amp; H21, "_") &amp; IF(I21&lt;&gt;"", "_" &amp; I21, "_") &amp; IF(B21&lt;&gt;"", "_" &amp; B21, "")</f>
         <v>DosSantos_etal_2020</v>
       </c>
-      <c r="G20" t="str">
-        <f t="shared" ref="G20" si="41">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A20,","), "-", ""), " ", "")</f>
+      <c r="G21" t="str">
+        <f t="shared" ref="G21" si="48">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A21,","), "-", ""), " ", "")</f>
         <v>DosSantos</v>
       </c>
-      <c r="H20" t="str">
-        <f t="shared" ref="H20" si="42">IF(ISNUMBER(FIND("&amp;", A20)),
-    IF(LEN(A20)-LEN(SUBSTITUTE(A20, ",", ""))&gt;=6, "etal", MID(A20, SEARCH("&amp; ", A20)+2, SEARCH(",", A20, SEARCH("&amp; ", A20)+2) - SEARCH("&amp; ", A20)-2)),
+      <c r="H21" t="str">
+        <f t="shared" ref="H21" si="49">IF(ISNUMBER(FIND("&amp;", A21)),
+    IF(LEN(A21)-LEN(SUBSTITUTE(A21, ",", ""))&gt;=6, "etal", MID(A21, SEARCH("&amp; ", A21)+2, SEARCH(",", A21, SEARCH("&amp; ", A21)+2) - SEARCH("&amp; ", A21)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I20" t="str">
-        <f t="shared" ref="I20" si="43">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A20, "("), ")")</f>
+      <c r="I21" t="str">
+        <f t="shared" ref="I21" si="50">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, "("), ")")</f>
         <v>2020</v>
       </c>
-      <c r="J20" t="str">
-        <f t="shared" si="12"/>
+      <c r="J21" t="str">
+        <f t="shared" si="19"/>
         <v>10.1523/JNEUROSCI.2339-19.2020</v>
       </c>
-      <c r="K20" t="str">
-        <f t="shared" si="37"/>
+      <c r="K21" t="str">
+        <f t="shared" si="44"/>
         <v>DosSantos_etal_2020_unpublished</v>
       </c>
-      <c r="L20" t="str">
-        <f t="shared" si="38"/>
+      <c r="L21" t="str">
+        <f t="shared" si="45"/>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished</v>
       </c>
-      <c r="M20" t="str">
-        <f t="array" ref="M20">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L20, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+      <c r="M21" t="str">
+        <f t="array" ref="M21">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1523%2FJNEUROSCI.2339-19.2020_unpublished.tsv</v>
       </c>
-      <c r="P20" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R20" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T20" s="1" t="s">
+      <c r="P21" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q21" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R21" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="U20" s="1" t="s">
+      <c r="S21" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T21" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="V20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z20" s="1" t="s">
+      <c r="U21" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="AA20" s="1" t="s">
+      <c r="V21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y21" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="AB20" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE20" s="1" t="s">
+      <c r="Z21" s="1" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="21" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E21" t="str">
-        <f t="shared" ref="E21" si="44">RIGHT(A21,1)</f>
+      <c r="AA21" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB21" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE21" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E22" t="str">
+        <f t="shared" ref="E22" si="51">RIGHT(A22,1)</f>
         <v>3</v>
       </c>
-      <c r="F21" t="str">
-        <f t="shared" ref="F21" si="45">G21 &amp; IF(H21&lt;&gt;"", "_" &amp; H21, "_") &amp; IF(I21&lt;&gt;"", "_" &amp; I21, "_") &amp; IF(B21&lt;&gt;"", "_" &amp; B21, "")</f>
+      <c r="F22" t="str">
+        <f t="shared" ref="F22" si="52">G22 &amp; IF(H22&lt;&gt;"", "_" &amp; H22, "_") &amp; IF(I22&lt;&gt;"", "_" &amp; I22, "_") &amp; IF(B22&lt;&gt;"", "_" &amp; B22, "")</f>
         <v>Eagleman_Vaughn_2021</v>
       </c>
-      <c r="G21" t="str">
-        <f t="shared" ref="G21" si="46">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A21,","), "-", ""), " ", "")</f>
+      <c r="G22" t="str">
+        <f t="shared" ref="G22" si="53">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A22,","), "-", ""), " ", "")</f>
         <v>Eagleman</v>
       </c>
-      <c r="H21" t="str">
-        <f t="shared" ref="H21" si="47">IF(ISNUMBER(FIND("&amp;", A21)),
-    IF(LEN(A21)-LEN(SUBSTITUTE(A21, ",", ""))&gt;=6, "etal", MID(A21, SEARCH("&amp; ", A21)+2, SEARCH(",", A21, SEARCH("&amp; ", A21)+2) - SEARCH("&amp; ", A21)-2)),
+      <c r="H22" t="str">
+        <f t="shared" ref="H22" si="54">IF(ISNUMBER(FIND("&amp;", A22)),
+    IF(LEN(A22)-LEN(SUBSTITUTE(A22, ",", ""))&gt;=6, "etal", MID(A22, SEARCH("&amp; ", A22)+2, SEARCH(",", A22, SEARCH("&amp; ", A22)+2) - SEARCH("&amp; ", A22)-2)),
     ""
 )</f>
         <v>Vaughn</v>
       </c>
-      <c r="I21" t="str">
-        <f t="shared" ref="I21" si="48">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A21, "("), ")")</f>
+      <c r="I22" t="str">
+        <f t="shared" ref="I22" si="55">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A22, "("), ")")</f>
         <v>2021</v>
       </c>
-      <c r="J21" t="str">
-        <f t="shared" si="12"/>
+      <c r="J22" t="str">
+        <f t="shared" si="19"/>
         <v>10.3389/fnins.2021.632853</v>
       </c>
-      <c r="K21" t="str">
-        <f t="shared" si="37"/>
+      <c r="K22" t="str">
+        <f t="shared" si="44"/>
         <v>Eagleman_Vaughn_2021_TABLE1</v>
       </c>
-      <c r="L21" t="str">
-        <f t="shared" si="38"/>
+      <c r="L22" t="str">
+        <f t="shared" si="45"/>
         <v>10.3389%2Ffnins.2021.632853_TABLE1</v>
-      </c>
-      <c r="M21" t="str">
-        <f t="array" ref="M21">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L21, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="R21" s="4"/>
-      <c r="U21" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y21" s="11" t="s">
-        <v>404</v>
-      </c>
-      <c r="Z21" s="1" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E22" t="str">
-        <f t="shared" si="17"/>
-        <v>5</v>
-      </c>
-      <c r="F22" t="str">
-        <f t="shared" si="18"/>
-        <v>Falcone_etal_2019</v>
-      </c>
-      <c r="G22" t="str">
-        <f t="shared" si="19"/>
-        <v>Falcone</v>
-      </c>
-      <c r="H22" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I22" t="str">
-        <f t="shared" si="21"/>
-        <v>2019</v>
-      </c>
-      <c r="J22" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1002/cne.24605</v>
-      </c>
-      <c r="K22" t="str">
-        <f t="shared" si="37"/>
-        <v>Falcone_etal_2019_TABLE1</v>
-      </c>
-      <c r="L22" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1002%2Fcne.24605_TABLE1</v>
       </c>
       <c r="M22" t="str">
         <f t="array" ref="M22">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L22, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24605_TABLE1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="R22" s="4"/>
       <c r="U22" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="Y22" s="11" t="s">
+        <v>149</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" ht="15.95" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="D23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E23" t="str">
+        <f t="shared" si="24"/>
+        <v>5</v>
+      </c>
+      <c r="F23" t="str">
+        <f t="shared" si="25"/>
+        <v>Falcone_etal_2019</v>
+      </c>
+      <c r="G23" t="str">
+        <f t="shared" si="26"/>
+        <v>Falcone</v>
+      </c>
+      <c r="H23" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I23" t="str">
+        <f t="shared" si="28"/>
+        <v>2019</v>
+      </c>
+      <c r="J23" t="str">
+        <f t="shared" si="19"/>
+        <v>10.1002/cne.24605</v>
+      </c>
+      <c r="K23" t="str">
+        <f t="shared" si="44"/>
+        <v>Falcone_etal_2019_TABLE1</v>
+      </c>
+      <c r="L23" t="str">
+        <f t="shared" si="45"/>
+        <v>10.1002%2Fcne.24605_TABLE1</v>
+      </c>
+      <c r="M23" t="str">
+        <f t="array" ref="M23">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L23, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1002%2Fcne.24605_TABLE1.tsv</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="R23" s="4"/>
+      <c r="U23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A24" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="E23" t="str">
-        <f t="shared" ref="E23" si="49">RIGHT(A23,1)</f>
+      <c r="D24" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E24" t="str">
+        <f t="shared" ref="E24" si="56">RIGHT(A24,1)</f>
         <v>5</v>
       </c>
-      <c r="F23" t="str">
-        <f t="shared" ref="F23" si="50">G23 &amp; IF(H23&lt;&gt;"", "_" &amp; H23, "_") &amp; IF(I23&lt;&gt;"", "_" &amp; I23, "_") &amp; IF(B23&lt;&gt;"", "_" &amp; B23, "")</f>
+      <c r="F24" t="str">
+        <f t="shared" ref="F24" si="57">G24 &amp; IF(H24&lt;&gt;"", "_" &amp; H24, "_") &amp; IF(I24&lt;&gt;"", "_" &amp; I24, "_") &amp; IF(B24&lt;&gt;"", "_" &amp; B24, "")</f>
         <v>Falcone_etal_2019</v>
       </c>
-      <c r="G23" t="str">
-        <f t="shared" ref="G23" si="51">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A23,","), "-", ""), " ", "")</f>
+      <c r="G24" t="str">
+        <f t="shared" ref="G24" si="58">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A24,","), "-", ""), " ", "")</f>
         <v>Falcone</v>
       </c>
-      <c r="H23" t="str">
-        <f t="shared" ref="H23" si="52">IF(ISNUMBER(FIND("&amp;", A23)),
-    IF(LEN(A23)-LEN(SUBSTITUTE(A23, ",", ""))&gt;=6, "etal", MID(A23, SEARCH("&amp; ", A23)+2, SEARCH(",", A23, SEARCH("&amp; ", A23)+2) - SEARCH("&amp; ", A23)-2)),
+      <c r="H24" t="str">
+        <f t="shared" ref="H24" si="59">IF(ISNUMBER(FIND("&amp;", A24)),
+    IF(LEN(A24)-LEN(SUBSTITUTE(A24, ",", ""))&gt;=6, "etal", MID(A24, SEARCH("&amp; ", A24)+2, SEARCH(",", A24, SEARCH("&amp; ", A24)+2) - SEARCH("&amp; ", A24)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I23" t="str">
-        <f t="shared" ref="I23" si="53">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A23, "("), ")")</f>
+      <c r="I24" t="str">
+        <f t="shared" ref="I24" si="60">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A24, "("), ")")</f>
         <v>2019</v>
       </c>
-      <c r="J23" t="str">
-        <f t="shared" si="12"/>
+      <c r="J24" t="str">
+        <f t="shared" si="19"/>
         <v>10.1002/cne.24605</v>
       </c>
-      <c r="K23" t="str">
-        <f t="shared" si="37"/>
+      <c r="K24" t="str">
+        <f t="shared" si="44"/>
         <v>Falcone_etal_2019_TABLE2</v>
       </c>
-      <c r="L23" t="str">
-        <f t="shared" si="38"/>
+      <c r="L24" t="str">
+        <f t="shared" si="45"/>
         <v>10.1002%2Fcne.24605_TABLE2</v>
-      </c>
-      <c r="M23" t="str">
-        <f t="array" ref="M23">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L23, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24605_TABLE2.tsv</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="R23" s="4"/>
-      <c r="U23" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z23" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="E24" t="str">
-        <f t="shared" si="17"/>
-        <v>6</v>
-      </c>
-      <c r="F24" t="str">
-        <f t="shared" si="18"/>
-        <v>Finlay_etal_2006</v>
-      </c>
-      <c r="G24" t="str">
-        <f t="shared" si="19"/>
-        <v>Finlay</v>
-      </c>
-      <c r="H24" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I24" t="str">
-        <f t="shared" si="21"/>
-        <v>2006</v>
-      </c>
-      <c r="J24" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1093/oso/9780198568742.003.0006</v>
-      </c>
-      <c r="K24" t="str">
-        <f t="shared" si="37"/>
-        <v>Finlay_etal_2006_Table6.1</v>
-      </c>
-      <c r="L24" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
       <c r="M24" t="str">
         <f t="array" ref="M24">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L24, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
-      </c>
-      <c r="N24" s="5"/>
-      <c r="P24" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R24" s="1" t="s">
+        <v>10.1002%2Fcne.24605_TABLE2.tsv</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="R24" s="4"/>
+      <c r="U24" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A25" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="S24" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T24" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="U24" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AD24" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="AE24" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="25" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E25" t="str">
-        <f t="shared" si="17"/>
-        <v>x</v>
+        <f t="shared" si="24"/>
+        <v>6</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" si="18"/>
-        <v>Fu_etal_2013</v>
+        <f t="shared" si="25"/>
+        <v>Finlay_etal_2006</v>
       </c>
       <c r="G25" t="str">
+        <f t="shared" si="26"/>
+        <v>Finlay</v>
+      </c>
+      <c r="H25" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I25" t="str">
+        <f t="shared" si="28"/>
+        <v>2006</v>
+      </c>
+      <c r="J25" t="str">
         <f t="shared" si="19"/>
-        <v>Fu</v>
-      </c>
-      <c r="H25" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I25" t="str">
-        <f t="shared" si="21"/>
-        <v>2013</v>
-      </c>
-      <c r="J25" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1007/s00429-012-0462-x</v>
+        <v>10.1093/oso/9780198568742.003.0006</v>
       </c>
       <c r="K25" t="str">
-        <f t="shared" si="37"/>
-        <v>Fu_etal_2013_Table1</v>
+        <f t="shared" si="44"/>
+        <v>Finlay_etal_2006_Table6.1</v>
       </c>
       <c r="L25" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
+        <f t="shared" si="45"/>
+        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1</v>
       </c>
       <c r="M25" t="str">
         <f t="array" ref="M25">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L25, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N25" s="1" t="s">
+        <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
+      </c>
+      <c r="N25" s="5"/>
+      <c r="P25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R25" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T25" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="U25" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V25" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W25" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="Y25" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="Z25" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE25" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A26" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="Z25" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="AC25" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:33" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="D26" s="1" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="E26" t="str">
-        <f t="shared" si="17"/>
-        <v>6</v>
+        <f t="shared" si="24"/>
+        <v>x</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" si="18"/>
-        <v>Garwicz_etal_2009</v>
+        <f t="shared" si="25"/>
+        <v>Fu_etal_2013</v>
       </c>
       <c r="G26" t="str">
+        <f t="shared" si="26"/>
+        <v>Fu</v>
+      </c>
+      <c r="H26" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I26" t="str">
+        <f t="shared" si="28"/>
+        <v>2013</v>
+      </c>
+      <c r="J26" t="str">
         <f t="shared" si="19"/>
-        <v>Garwicz</v>
-      </c>
-      <c r="H26" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I26" t="str">
-        <f t="shared" si="21"/>
-        <v>2009</v>
-      </c>
-      <c r="J26" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1073/pnas.0905777106</v>
+        <v>10.1007/s00429-012-0462-x</v>
       </c>
       <c r="K26" t="str">
-        <f t="shared" si="37"/>
-        <v>Garwicz_etal_2009_TableS1</v>
+        <f t="shared" si="44"/>
+        <v>Fu_etal_2013_Table1</v>
       </c>
       <c r="L26" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1073%2Fpnas.0905777106_TableS1</v>
+        <f t="shared" si="45"/>
+        <v>10.1007%2Fs00429-012-0462-x_Table1</v>
       </c>
       <c r="M26" t="str">
         <f t="array" ref="M26">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L26, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1073%2Fpnas.0905777106_TableS1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N26" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="P26" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Z26" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="U26" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X26" s="1" t="s">
+      <c r="AC26" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" ht="15" customHeight="1">
+      <c r="A27" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="27" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="1" t="s">
-        <v>162</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>165</v>
+        <v>129</v>
       </c>
       <c r="E27" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>6</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>Garwicz_etal_2009</v>
       </c>
       <c r="G27" t="str">
+        <f t="shared" si="26"/>
+        <v>Garwicz</v>
+      </c>
+      <c r="H27" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I27" t="str">
+        <f t="shared" si="28"/>
+        <v>2009</v>
+      </c>
+      <c r="J27" t="str">
         <f t="shared" si="19"/>
-        <v>Garwicz</v>
-      </c>
-      <c r="H27" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I27" t="str">
-        <f t="shared" si="21"/>
-        <v>2009</v>
-      </c>
-      <c r="J27" t="str">
-        <f t="shared" si="12"/>
         <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="K27" t="str">
-        <f t="shared" si="37"/>
-        <v>Garwicz_etal_2009_TableS2</v>
+        <f t="shared" si="44"/>
+        <v>Garwicz_etal_2009_TableS1</v>
       </c>
       <c r="L27" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1073%2Fpnas.0905777106_TableS2</v>
+        <f t="shared" si="45"/>
+        <v>10.1073%2Fpnas.0905777106_TableS1</v>
       </c>
       <c r="M27" t="str">
         <f t="array" ref="M27">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L27, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1073%2Fpnas.0905777106_TableS1.tsv</v>
       </c>
       <c r="N27" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="U27" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W27" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="X27" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="U27" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X27" s="1" t="s">
+    </row>
+    <row r="28" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A28" s="1" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="28" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
+      <c r="D28" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="D28" s="1" t="s">
-        <v>165</v>
-      </c>
       <c r="E28" t="str">
-        <f t="shared" si="17"/>
-        <v>0</v>
+        <f t="shared" si="24"/>
+        <v>6</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="18"/>
-        <v>Genoud_etal_2018</v>
+        <f t="shared" si="25"/>
+        <v>Garwicz_etal_2009</v>
       </c>
       <c r="G28" t="str">
+        <f t="shared" si="26"/>
+        <v>Garwicz</v>
+      </c>
+      <c r="H28" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I28" t="str">
+        <f t="shared" si="28"/>
+        <v>2009</v>
+      </c>
+      <c r="J28" t="str">
         <f t="shared" si="19"/>
-        <v>Genoud</v>
-      </c>
-      <c r="H28" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I28" t="str">
-        <f t="shared" si="21"/>
-        <v>2018</v>
-      </c>
-      <c r="J28" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1111/brv.12350</v>
+        <v>10.1073/pnas.0905777106</v>
       </c>
       <c r="K28" t="str">
-        <f t="shared" si="37"/>
-        <v>Genoud_etal_2018_TableS2</v>
+        <f t="shared" si="44"/>
+        <v>Garwicz_etal_2009_TableS2</v>
       </c>
       <c r="L28" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1111%2Fbrv.12350_TableS2</v>
+        <f t="shared" si="45"/>
+        <v>10.1073%2Fpnas.0905777106_TableS2</v>
       </c>
       <c r="M28" t="str">
         <f t="array" ref="M28">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L28, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
@@ -3679,329 +3687,294 @@
       <c r="N28" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="P28" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AC28" s="1" t="s">
+      <c r="U28" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A29" s="1" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="29" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>170</v>
-      </c>
       <c r="D29" s="1" t="s">
-        <v>128</v>
+        <v>167</v>
       </c>
       <c r="E29" t="str">
-        <f t="shared" si="17"/>
-        <v>8</v>
+        <f t="shared" si="24"/>
+        <v>0</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="18"/>
-        <v>Granatosky__2018</v>
+        <f t="shared" si="25"/>
+        <v>Genoud_etal_2018</v>
       </c>
       <c r="G29" t="str">
+        <f t="shared" si="26"/>
+        <v>Genoud</v>
+      </c>
+      <c r="H29" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I29" t="str">
+        <f t="shared" si="28"/>
+        <v>2018</v>
+      </c>
+      <c r="J29" t="str">
         <f t="shared" si="19"/>
-        <v>Granatosky</v>
-      </c>
-      <c r="H29" t="str">
-        <f t="shared" si="20"/>
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <f t="shared" si="21"/>
-        <v>2018</v>
-      </c>
-      <c r="J29" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1111/jzo.12608</v>
+        <v>10.1111/brv.12350</v>
       </c>
       <c r="K29" t="str">
-        <f t="shared" si="37"/>
-        <v>Granatosky__2018_TableS1</v>
+        <f t="shared" si="44"/>
+        <v>Genoud_etal_2018_TableS2</v>
       </c>
       <c r="L29" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1111%2Fjzo.12608_TableS1</v>
+        <f t="shared" si="45"/>
+        <v>10.1111%2Fbrv.12350_TableS2</v>
       </c>
       <c r="M29" t="str">
         <f t="array" ref="M29">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L29, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N29" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="P29" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC29" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="P29" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="30" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="30" spans="1:32" ht="15.95" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>172</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>173</v>
+        <v>129</v>
       </c>
       <c r="E30" t="str">
-        <f t="shared" si="17"/>
-        <v>1</v>
+        <f t="shared" si="24"/>
+        <v>8</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="18"/>
-        <v>Heffner_Masterton_1975</v>
+        <f t="shared" si="25"/>
+        <v>Granatosky__2018</v>
       </c>
       <c r="G30" t="str">
+        <f t="shared" si="26"/>
+        <v>Granatosky</v>
+      </c>
+      <c r="H30" t="str">
+        <f t="shared" si="27"/>
+        <v/>
+      </c>
+      <c r="I30" t="str">
+        <f t="shared" si="28"/>
+        <v>2018</v>
+      </c>
+      <c r="J30" t="str">
         <f t="shared" si="19"/>
-        <v>Heffner</v>
-      </c>
-      <c r="H30" t="str">
-        <f t="shared" si="20"/>
-        <v>Masterton</v>
-      </c>
-      <c r="I30" t="str">
-        <f t="shared" si="21"/>
-        <v>1975</v>
-      </c>
-      <c r="J30" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1159/000124401</v>
+        <v>10.1111/jzo.12608</v>
       </c>
       <c r="K30" t="str">
-        <f t="shared" si="37"/>
-        <v>Heffner_Masterton_1975_TableI</v>
+        <f t="shared" si="44"/>
+        <v>Granatosky__2018_TableS1</v>
       </c>
       <c r="L30" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1159%2F000124401_TableI</v>
+        <f t="shared" si="45"/>
+        <v>10.1111%2Fjzo.12608_TableS1</v>
       </c>
       <c r="M30" t="str">
         <f t="array" ref="M30">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L30, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000124401_TableI.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R30" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="S30" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>175</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y30" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="Z30" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="AC30" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="AE30" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>173</v>
-      </c>
+      <c r="D31" s="1"/>
       <c r="E31" t="str">
-        <f t="shared" si="17"/>
-        <v>4</v>
+        <f t="shared" ref="E31" si="61">RIGHT(A31,1)</f>
+        <v>7</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="18"/>
-        <v>Heffner_Masterton_1983</v>
+        <f t="shared" ref="F31" si="62">G31 &amp; IF(H31&lt;&gt;"", "_" &amp; H31, "_") &amp; IF(I31&lt;&gt;"", "_" &amp; I31, "_") &amp; IF(B31&lt;&gt;"", "_" &amp; B31, "")</f>
+        <v>Haarlem_etal_2026</v>
       </c>
       <c r="G31" t="str">
-        <f t="shared" si="19"/>
-        <v>Heffner</v>
+        <f t="shared" ref="G31" si="63">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A31,","), "-", ""), " ", "")</f>
+        <v>Haarlem</v>
       </c>
       <c r="H31" t="str">
-        <f t="shared" si="20"/>
-        <v>Masterton</v>
+        <f t="shared" ref="H31" si="64">IF(ISNUMBER(FIND("&amp;", A31)),
+    IF(LEN(A31)-LEN(SUBSTITUTE(A31, ",", ""))&gt;=6, "etal", MID(A31, SEARCH("&amp; ", A31)+2, SEARCH(",", A31, SEARCH("&amp; ", A31)+2) - SEARCH("&amp; ", A31)-2)),
+    ""
+)</f>
+        <v>etal</v>
       </c>
       <c r="I31" t="str">
-        <f t="shared" si="21"/>
-        <v>1983</v>
+        <f t="shared" ref="I31" si="65">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A31, "("), ")")</f>
+        <v>2026</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1159/000121494</v>
+        <f t="shared" ref="J31" si="66">IF(C31&lt;&gt;"", C31, IF(C31="", _xlfn.TEXTAFTER(A31,"https://doi.org/"), C31))</f>
+        <v>10.1038/s41559-026-02994-7</v>
       </c>
       <c r="K31" t="str">
-        <f t="shared" si="37"/>
-        <v>Heffner_Masterton_1983_TableI</v>
+        <f t="shared" ref="K31" si="67">TRIM(_xlfn.TEXTJOIN("_",FALSE,F31,(SUBSTITUTE(SUBSTITUTE(D31," ",""), "_", ""))))</f>
+        <v>Haarlem_etal_2026_</v>
       </c>
       <c r="L31" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1159%2F000121494_TableI</v>
+        <f t="shared" ref="L31" si="68">IF(ISBLANK(C31),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J31, SUBSTITUTE(D31,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C31, SUBSTITUTE(D31,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1038%2Fs41559-026-02994-7_</v>
       </c>
       <c r="M31" t="str">
         <f t="array" ref="M31">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L31, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P31" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R31" s="4"/>
-      <c r="T31" s="1" t="str">
-        <f>IF(S31="N", R31, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y31" s="1" t="s">
+      <c r="N31" s="10"/>
+      <c r="P31" s="1"/>
+    </row>
+    <row r="32" spans="1:32" ht="15.95" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="AE31" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AG31" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="32" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>405</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>406</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E32" t="str">
-        <f t="shared" ref="E32" si="54">RIGHT(A32,1)</f>
-        <v>8</v>
+        <f t="shared" si="24"/>
+        <v>1</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" ref="F32" si="55">G32 &amp; IF(H32&lt;&gt;"", "_" &amp; H32, "_") &amp; IF(I32&lt;&gt;"", "_" &amp; I32, "_") &amp; IF(B32&lt;&gt;"", "_" &amp; B32, "")</f>
-        <v>Heiss_etal_2004</v>
+        <f t="shared" si="25"/>
+        <v>Heffner_Masterton_1975</v>
       </c>
       <c r="G32" t="str">
-        <f t="shared" ref="G32" si="56">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A32,","), "-", ""), " ", "")</f>
-        <v>Heiss</v>
+        <f t="shared" si="26"/>
+        <v>Heffner</v>
       </c>
       <c r="H32" t="str">
-        <f t="shared" ref="H32" si="57">IF(ISNUMBER(FIND("&amp;", A32)),
-    IF(LEN(A32)-LEN(SUBSTITUTE(A32, ",", ""))&gt;=6, "etal", MID(A32, SEARCH("&amp; ", A32)+2, SEARCH(",", A32, SEARCH("&amp; ", A32)+2) - SEARCH("&amp; ", A32)-2)),
-    ""
-)</f>
-        <v>etal</v>
+        <f t="shared" si="27"/>
+        <v>Masterton</v>
       </c>
       <c r="I32" t="str">
-        <f t="shared" ref="I32" si="58">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A32, "("), ")")</f>
-        <v>2004</v>
+        <f t="shared" si="28"/>
+        <v>1975</v>
       </c>
       <c r="J32" t="str">
-        <f t="shared" si="12"/>
-        <v>WOS:000225086000011</v>
+        <f t="shared" si="19"/>
+        <v>10.1159/000124401</v>
       </c>
       <c r="K32" t="str">
-        <f t="shared" ref="K32" si="59">TRIM(_xlfn.TEXTJOIN("_",FALSE,F32,(SUBSTITUTE(SUBSTITUTE(D32," ",""), "_", ""))))</f>
-        <v>Heiss_etal_2004_TABLE1</v>
+        <f t="shared" si="44"/>
+        <v>Heffner_Masterton_1975_TableI</v>
       </c>
       <c r="L32" t="str">
-        <f t="shared" ref="L32" si="60">IF(ISBLANK(C32),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J32, SUBSTITUTE(D32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C32, SUBSTITUTE(D32,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>WOS%3A000225086000011_TABLE1</v>
+        <f t="shared" si="45"/>
+        <v>10.1159%2F000124401_TableI</v>
       </c>
       <c r="M32" t="str">
         <f t="array" ref="M32">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N32" s="12" t="s">
-        <v>407</v>
-      </c>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="4"/>
-      <c r="T32" s="1"/>
-      <c r="U32" s="1"/>
-      <c r="V32" s="1"/>
-      <c r="W32" s="12"/>
+        <v>10.1159%2F000124401_TableI.tsv</v>
+      </c>
+      <c r="P32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R32" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T32" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="U32" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W32" s="1" t="s">
+        <v>100</v>
+      </c>
       <c r="Y32" s="1" t="s">
-        <v>408</v>
-      </c>
-      <c r="AE32" s="1"/>
-      <c r="AG32" s="12"/>
-    </row>
-    <row r="33" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>179</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="AC32" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="AE32" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" ht="15.95" customHeight="1">
       <c r="A33" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="E33" t="str">
-        <f t="shared" si="17"/>
-        <v>8</v>
+        <f t="shared" si="24"/>
+        <v>4</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="18"/>
-        <v>Heldstab_etal_2016</v>
+        <f t="shared" si="25"/>
+        <v>Heffner_Masterton_1983</v>
       </c>
       <c r="G33" t="str">
+        <f t="shared" si="26"/>
+        <v>Heffner</v>
+      </c>
+      <c r="H33" t="str">
+        <f t="shared" si="27"/>
+        <v>Masterton</v>
+      </c>
+      <c r="I33" t="str">
+        <f t="shared" si="28"/>
+        <v>1983</v>
+      </c>
+      <c r="J33" t="str">
         <f t="shared" si="19"/>
-        <v>Heldstab</v>
-      </c>
-      <c r="H33" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I33" t="str">
-        <f t="shared" si="21"/>
-        <v>2016</v>
-      </c>
-      <c r="J33" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1038/srep24528</v>
+        <v>10.1159/000121494</v>
       </c>
       <c r="K33" t="str">
-        <f t="shared" si="37"/>
-        <v>Heldstab_etal_2016_TableS1</v>
+        <f t="shared" si="44"/>
+        <v>Heffner_Masterton_1983_TableI</v>
       </c>
       <c r="L33" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1038%2Fsrep24528_TableS1</v>
+        <f t="shared" si="45"/>
+        <v>10.1159%2F000121494_TableI</v>
       </c>
       <c r="M33" t="str">
         <f t="array" ref="M33">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L33, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R33" s="4"/>
       <c r="T33" s="1" t="str">
@@ -4009,1476 +3982,1458 @@
         <v>write file name</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
+      </c>
+      <c r="W33" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="AE33" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="34" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+      <c r="AG33" s="1" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" ht="15.95" customHeight="1">
       <c r="A34" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
+      </c>
+      <c r="C34" s="12" t="s">
+        <v>185</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>194</v>
+        <v>37</v>
       </c>
       <c r="E34" t="str">
-        <f t="shared" ref="E34" si="61">RIGHT(A34,1)</f>
-        <v>3</v>
+        <f t="shared" ref="E34" si="69">RIGHT(A34,1)</f>
+        <v>8</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" ref="F34" si="62">G34 &amp; IF(H34&lt;&gt;"", "_" &amp; H34, "_") &amp; IF(I34&lt;&gt;"", "_" &amp; I34, "_") &amp; IF(B34&lt;&gt;"", "_" &amp; B34, "")</f>
-        <v>HerculanoHouzel__2015</v>
+        <f t="shared" ref="F34" si="70">G34 &amp; IF(H34&lt;&gt;"", "_" &amp; H34, "_") &amp; IF(I34&lt;&gt;"", "_" &amp; I34, "_") &amp; IF(B34&lt;&gt;"", "_" &amp; B34, "")</f>
+        <v>Heiss_etal_2004</v>
       </c>
       <c r="G34" t="str">
-        <f t="shared" ref="G34" si="63">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A34,","), "-", ""), " ", "")</f>
-        <v>HerculanoHouzel</v>
+        <f t="shared" ref="G34" si="71">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A34,","), "-", ""), " ", "")</f>
+        <v>Heiss</v>
       </c>
       <c r="H34" t="str">
-        <f t="shared" ref="H34" si="64">IF(ISNUMBER(FIND("&amp;", A34)),
+        <f t="shared" ref="H34" si="72">IF(ISNUMBER(FIND("&amp;", A34)),
     IF(LEN(A34)-LEN(SUBSTITUTE(A34, ",", ""))&gt;=6, "etal", MID(A34, SEARCH("&amp; ", A34)+2, SEARCH(",", A34, SEARCH("&amp; ", A34)+2) - SEARCH("&amp; ", A34)-2)),
     ""
 )</f>
-        <v/>
+        <v>etal</v>
       </c>
       <c r="I34" t="str">
-        <f t="shared" ref="I34" si="65">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A34, "("), ")")</f>
-        <v>2015</v>
+        <f t="shared" ref="I34" si="73">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A34, "("), ")")</f>
+        <v>2004</v>
       </c>
       <c r="J34" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1098/rspb.2015.1853</v>
+        <f t="shared" si="19"/>
+        <v>WOS:000225086000011</v>
       </c>
       <c r="K34" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel__2015_Table2</v>
+        <f t="shared" ref="K34" si="74">TRIM(_xlfn.TEXTJOIN("_",FALSE,F34,(SUBSTITUTE(SUBSTITUTE(D34," ",""), "_", ""))))</f>
+        <v>Heiss_etal_2004_TABLE1</v>
       </c>
       <c r="L34" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1098%2Frspb.2015.1853_Table2</v>
+        <f t="shared" ref="L34" si="75">IF(ISBLANK(C34),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J34, SUBSTITUTE(D34,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C34, SUBSTITUTE(D34,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>WOS%3A000225086000011_TABLE1</v>
       </c>
       <c r="M34" t="str">
         <f t="array" ref="M34">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L34, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N34" s="1" t="s">
-        <v>403</v>
-      </c>
+      <c r="N34" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="P34" s="1"/>
+      <c r="Q34" s="1"/>
       <c r="R34" s="4"/>
-      <c r="U34" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="V34" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y34" s="10" t="s">
-        <v>402</v>
-      </c>
-      <c r="Z34" s="10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="35" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="T34" s="1"/>
+      <c r="U34" s="1"/>
+      <c r="V34" s="1"/>
+      <c r="W34" s="10"/>
+      <c r="Y34" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="AE34" s="1"/>
+      <c r="AG34" s="10"/>
+    </row>
+    <row r="35" spans="1:33" ht="15.95" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="E35" t="str">
-        <f t="shared" si="17"/>
-        <v>5</v>
+        <f t="shared" si="24"/>
+        <v>8</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="18"/>
-        <v>HerculanoHouzel_etal_2013</v>
+        <f t="shared" si="25"/>
+        <v>Heldstab_etal_2016</v>
       </c>
       <c r="G35" t="str">
+        <f t="shared" si="26"/>
+        <v>Heldstab</v>
+      </c>
+      <c r="H35" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I35" t="str">
+        <f t="shared" si="28"/>
+        <v>2016</v>
+      </c>
+      <c r="J35" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H35" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I35" t="str">
-        <f t="shared" si="21"/>
-        <v>2013</v>
-      </c>
-      <c r="J35" t="str">
-        <f t="shared" si="12"/>
-        <v>10.3389/fnana.2013.00035</v>
+        <v>10.1038/srep24528</v>
       </c>
       <c r="K35" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
+        <f t="shared" si="44"/>
+        <v>Heldstab_etal_2016_TableS1</v>
       </c>
       <c r="L35" t="str">
-        <f t="shared" si="38"/>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
+        <f t="shared" si="45"/>
+        <v>10.1038%2Fsrep24528_TableS1</v>
       </c>
       <c r="M35" t="str">
         <f t="array" ref="M35">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
+        <v>notfound</v>
+      </c>
+      <c r="P35" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:31" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="R35" s="4"/>
+      <c r="T35" s="1" t="str">
+        <f>IF(S35="N", R35, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U35" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V35" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y35" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="AE35" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" ht="15.95" customHeight="1">
       <c r="A36" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>186</v>
+        <v>42</v>
       </c>
       <c r="E36" t="str">
-        <f t="shared" si="17"/>
-        <v>5</v>
+        <f t="shared" si="24"/>
+        <v>3</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="18"/>
-        <v>HerculanoHouzel_etal_2013</v>
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel__2015</v>
       </c>
       <c r="G36" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="26"/>
         <v>HerculanoHouzel</v>
       </c>
       <c r="H36" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
+        <f t="shared" si="27"/>
+        <v/>
       </c>
       <c r="I36" t="str">
-        <f t="shared" si="21"/>
-        <v>2013</v>
+        <f t="shared" si="28"/>
+        <v>2015</v>
       </c>
       <c r="J36" t="str">
-        <f t="shared" si="12"/>
-        <v>10.3389/fnana.2013.00035</v>
+        <f t="shared" ref="J36" si="76">IF(C36&lt;&gt;"", C36, IF(C36="", _xlfn.TEXTAFTER(A36,"https://doi.org/"), C36))</f>
+        <v>10.1098/rspb.2015.1853</v>
       </c>
       <c r="K36" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2013_Table1-a</v>
+        <f t="shared" ref="K36" si="77">TRIM(_xlfn.TEXTJOIN("_",FALSE,F36,(SUBSTITUTE(SUBSTITUTE(D36," ",""), "_", ""))))</f>
+        <v>HerculanoHouzel__2015_Table1</v>
       </c>
       <c r="L36" t="str">
-        <f t="shared" si="38"/>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
+        <f t="shared" ref="L36" si="78">IF(ISBLANK(C36),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J36, SUBSTITUTE(D36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C36, SUBSTITUTE(D36,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1098%2Frspb.2015.1853_Table1</v>
       </c>
       <c r="M36" t="str">
         <f t="array" ref="M36">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L36, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="37" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10.1098%2Frspb.2015.1853_Table1.tsv</v>
+      </c>
+      <c r="N36" s="1"/>
+      <c r="R36" s="4"/>
+      <c r="U36" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="V36" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y36" s="10"/>
+      <c r="Z36" s="10"/>
+    </row>
+    <row r="37" spans="1:33" ht="15.95" customHeight="1">
       <c r="A37" s="1" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E37" t="str">
-        <f t="shared" si="17"/>
-        <v>5</v>
+        <f t="shared" ref="E37" si="79">RIGHT(A37,1)</f>
+        <v>3</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="18"/>
-        <v>HerculanoHouzel_etal_2013</v>
+        <f t="shared" ref="F37" si="80">G37 &amp; IF(H37&lt;&gt;"", "_" &amp; H37, "_") &amp; IF(I37&lt;&gt;"", "_" &amp; I37, "_") &amp; IF(B37&lt;&gt;"", "_" &amp; B37, "")</f>
+        <v>HerculanoHouzel__2015</v>
       </c>
       <c r="G37" t="str">
+        <f t="shared" ref="G37" si="81">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A37,","), "-", ""), " ", "")</f>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H37" t="str">
+        <f t="shared" ref="H37" si="82">IF(ISNUMBER(FIND("&amp;", A37)),
+    IF(LEN(A37)-LEN(SUBSTITUTE(A37, ",", ""))&gt;=6, "etal", MID(A37, SEARCH("&amp; ", A37)+2, SEARCH(",", A37, SEARCH("&amp; ", A37)+2) - SEARCH("&amp; ", A37)-2)),
+    ""
+)</f>
+        <v/>
+      </c>
+      <c r="I37" t="str">
+        <f t="shared" ref="I37" si="83">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A37, "("), ")")</f>
+        <v>2015</v>
+      </c>
+      <c r="J37" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H37" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I37" t="str">
-        <f t="shared" si="21"/>
-        <v>2013</v>
-      </c>
-      <c r="J37" t="str">
-        <f t="shared" si="12"/>
-        <v>10.3389/fnana.2013.00035</v>
+        <v>10.1098/rspb.2015.1853</v>
       </c>
       <c r="K37" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2013_Table1-b</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel__2015_Table2</v>
       </c>
       <c r="L37" t="str">
-        <f t="shared" si="38"/>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
+        <f t="shared" si="45"/>
+        <v>10.1098%2Frspb.2015.1853_Table2</v>
       </c>
       <c r="M37" t="str">
         <f t="array" ref="M37">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L37, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="38" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+      <c r="N37" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="R37" s="4"/>
+      <c r="U37" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="V37" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y37" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z37" s="10" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" ht="15.95" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>41</v>
+        <v>195</v>
       </c>
       <c r="E38" t="str">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" si="24"/>
+        <v>5</v>
       </c>
       <c r="F38" t="str">
-        <f t="shared" si="18"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G38" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H38" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I38" t="str">
+        <f t="shared" si="28"/>
+        <v>2013</v>
+      </c>
+      <c r="J38" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H38" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I38" t="str">
-        <f t="shared" si="21"/>
-        <v>2015</v>
-      </c>
-      <c r="J38" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1159/000437413</v>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K38" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2015_Table1</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2013_Figure2TopLeft</v>
       </c>
       <c r="L38" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1159%2F000437413_Table1</v>
+        <f t="shared" si="45"/>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft</v>
       </c>
       <c r="M38" t="str">
         <f t="array" ref="M38">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L38, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table1.tsv</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>51</v>
+        <v>10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R38" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V38" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W38" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X38" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y38" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA38" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB38" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE38" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="39" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" ht="18.95" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E39" t="str">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" si="24"/>
+        <v>5</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="18"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G39" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H39" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I39" t="str">
+        <f t="shared" si="28"/>
+        <v>2013</v>
+      </c>
+      <c r="J39" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H39" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I39" t="str">
-        <f t="shared" si="21"/>
-        <v>2015</v>
-      </c>
-      <c r="J39" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1159/000437413</v>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K39" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2015_Table2</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2013_Table1-a</v>
       </c>
       <c r="L39" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1159%2F000437413_Table2</v>
+        <f t="shared" si="45"/>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a</v>
       </c>
       <c r="M39" t="str">
         <f t="array" ref="M39">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L39, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table2.tsv</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>51</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-a.tsv</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R39" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T39" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" ht="17.100000000000001" customHeight="1">
+      <c r="A40" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="D40" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="U39" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V39" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W39" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X39" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y39" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA39" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB39" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE39" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="40" spans="1:31" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>198</v>
-      </c>
       <c r="E40" t="str">
-        <f t="shared" si="17"/>
-        <v>3</v>
+        <f t="shared" si="24"/>
+        <v>5</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="18"/>
-        <v>HerculanoHouzel_etal_2015</v>
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel_etal_2013</v>
       </c>
       <c r="G40" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H40" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I40" t="str">
+        <f t="shared" si="28"/>
+        <v>2013</v>
+      </c>
+      <c r="J40" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H40" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I40" t="str">
-        <f t="shared" si="21"/>
-        <v>2015</v>
-      </c>
-      <c r="J40" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1159/000437413</v>
+        <v>10.3389/fnana.2013.00035</v>
       </c>
       <c r="K40" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2015_Table3</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2013_Table1-b</v>
       </c>
       <c r="L40" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1159%2F000437413_Table3</v>
+        <f t="shared" si="45"/>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b</v>
       </c>
       <c r="M40" t="str">
         <f t="array" ref="M40">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L40, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table3.tsv</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>51</v>
+        <v>10.3389%2Ffnana.2013.00035_Table1-b.tsv</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R40" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>201</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V40" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W40" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X40" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y40" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA40" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB40" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE40" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="41" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" ht="17.100000000000001" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="E41" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="F41" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G41" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H41" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I41" t="str">
+        <f t="shared" si="28"/>
+        <v>2015</v>
+      </c>
+      <c r="J41" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H41" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I41" t="str">
-        <f t="shared" si="21"/>
-        <v>2015</v>
-      </c>
-      <c r="J41" t="str">
-        <f t="shared" si="12"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K41" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2015_Table4</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2015_Table1</v>
       </c>
       <c r="L41" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1159%2F000437413_Table4</v>
+        <f t="shared" si="45"/>
+        <v>10.1159%2F000437413_Table1</v>
       </c>
       <c r="M41" t="str">
         <f t="array" ref="M41">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L41, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table4.tsv</v>
+        <v>10.1159%2F000437413_Table1.tsv</v>
       </c>
       <c r="N41" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="P41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q41" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R41" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="S41" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T41" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="U41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V41" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W41" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X41" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y41" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA41" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB41" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE41" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="P41" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R41" s="4" t="s">
-        <v>204</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W41" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X41" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y41" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA41" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB41" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE41" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="42" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="42" spans="1:33" ht="17.100000000000001" customHeight="1">
       <c r="A42" s="1" t="s">
-        <v>188</v>
+        <v>198</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="E42" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="24"/>
         <v>3</v>
       </c>
       <c r="F42" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="25"/>
         <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G42" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H42" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I42" t="str">
+        <f t="shared" si="28"/>
+        <v>2015</v>
+      </c>
+      <c r="J42" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H42" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I42" t="str">
-        <f t="shared" si="21"/>
-        <v>2015</v>
-      </c>
-      <c r="J42" t="str">
-        <f t="shared" si="12"/>
         <v>10.1159/000437413</v>
       </c>
       <c r="K42" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2015_Table5</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2015_Table2</v>
       </c>
       <c r="L42" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1159%2F000437413_Table5</v>
+        <f t="shared" si="45"/>
+        <v>10.1159%2F000437413_Table2</v>
       </c>
       <c r="M42" t="str">
         <f t="array" ref="M42">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L42, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000437413_Table5.tsv</v>
+        <v>10.1159%2F000437413_Table2.tsv</v>
       </c>
       <c r="N42" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="P42" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q42" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R42" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="S42" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T42" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="U42" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V42" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X42" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y42" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA42" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB42" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE42" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" ht="17.100000000000001" customHeight="1">
+      <c r="A43" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D43" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="P42" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R42" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W42" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X42" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="Y42" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA42" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB42" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE42" s="1" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="43" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E43" t="str">
-        <f t="shared" si="17"/>
-        <v>5</v>
+        <f t="shared" si="24"/>
+        <v>3</v>
       </c>
       <c r="F43" t="str">
-        <f t="shared" si="18"/>
-        <v>HerculanoHouzel_etal_2020</v>
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G43" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H43" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I43" t="str">
+        <f t="shared" si="28"/>
+        <v>2015</v>
+      </c>
+      <c r="J43" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H43" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I43" t="str">
-        <f t="shared" si="21"/>
-        <v>2020</v>
-      </c>
-      <c r="J43" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1002/cne.24985</v>
+        <v>10.1159/000437413</v>
       </c>
       <c r="K43" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2020_TABLE1</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2015_Table3</v>
       </c>
       <c r="L43" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1002%2Fcne.24985_TABLE1</v>
+        <f t="shared" si="45"/>
+        <v>10.1159%2F000437413_Table3</v>
       </c>
       <c r="M43" t="str">
         <f t="array" ref="M43">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L43, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
+        <v>10.1159%2F000437413_Table3.tsv</v>
       </c>
       <c r="N43" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="P43" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q43" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R43" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="S43" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T43" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="U43" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V43" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W43" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X43" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y43" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA43" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB43" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE43" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A44" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="P43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R43" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>213</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W43" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y43" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="AA43" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB43" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE43" s="1" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="44" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>150</v>
-      </c>
       <c r="E44" t="str">
-        <f t="shared" si="17"/>
-        <v>5</v>
+        <f t="shared" si="24"/>
+        <v>3</v>
       </c>
       <c r="F44" t="str">
-        <f t="shared" si="18"/>
-        <v>HerculanoHouzel_etal_2020</v>
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G44" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H44" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I44" t="str">
+        <f t="shared" si="28"/>
+        <v>2015</v>
+      </c>
+      <c r="J44" t="str">
         <f t="shared" si="19"/>
-        <v>HerculanoHouzel</v>
-      </c>
-      <c r="H44" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I44" t="str">
-        <f t="shared" si="21"/>
-        <v>2020</v>
-      </c>
-      <c r="J44" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1002/cne.24985</v>
+        <v>10.1159/000437413</v>
       </c>
       <c r="K44" t="str">
-        <f t="shared" si="37"/>
-        <v>HerculanoHouzel_etal_2020_TABLE2</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2015_Table4</v>
       </c>
       <c r="L44" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1002%2Fcne.24985_TABLE2</v>
+        <f t="shared" si="45"/>
+        <v>10.1159%2F000437413_Table4</v>
       </c>
       <c r="M44" t="str">
         <f t="array" ref="M44">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L44, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
+        <v>10.1159%2F000437413_Table4.tsv</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R44" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>99</v>
+        <v>88</v>
+      </c>
+      <c r="X44" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>219</v>
+        <v>136</v>
       </c>
       <c r="AA44" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE44" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A45" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" s="1" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="45" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>194</v>
-      </c>
       <c r="E45" t="str">
-        <f t="shared" si="17"/>
-        <v>4</v>
+        <f t="shared" si="24"/>
+        <v>3</v>
       </c>
       <c r="F45" t="str">
-        <f t="shared" si="18"/>
-        <v>Isler_etal_2008</v>
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel_etal_2015</v>
       </c>
       <c r="G45" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H45" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I45" t="str">
+        <f t="shared" si="28"/>
+        <v>2015</v>
+      </c>
+      <c r="J45" t="str">
         <f t="shared" si="19"/>
-        <v>Isler</v>
-      </c>
-      <c r="H45" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I45" t="str">
-        <f t="shared" si="21"/>
-        <v>2008</v>
-      </c>
-      <c r="J45" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <v>10.1159/000437413</v>
       </c>
       <c r="K45" t="str">
-        <f t="shared" si="37"/>
-        <v>Isler_etal_2008_Table2</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2015_Table5</v>
       </c>
       <c r="L45" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
+        <f t="shared" si="45"/>
+        <v>10.1159%2F000437413_Table5</v>
       </c>
       <c r="M45" t="str">
         <f t="array" ref="M45">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L45, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+        <v>10.1159%2F000437413_Table5.tsv</v>
+      </c>
+      <c r="N45" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="P45" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+      <c r="R45" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="S45" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T45" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="U45" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V45" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W45" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X45" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="Y45" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="AA45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB45" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE45" s="1" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" ht="15.95" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>221</v>
+        <v>37</v>
       </c>
       <c r="E46" t="str">
-        <f t="shared" si="17"/>
-        <v>4</v>
+        <f t="shared" si="24"/>
+        <v>5</v>
       </c>
       <c r="F46" t="str">
-        <f t="shared" si="18"/>
-        <v>Isler_etal_2008</v>
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel_etal_2020</v>
       </c>
       <c r="G46" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H46" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I46" t="str">
+        <f t="shared" si="28"/>
+        <v>2020</v>
+      </c>
+      <c r="J46" t="str">
         <f t="shared" si="19"/>
-        <v>Isler</v>
-      </c>
-      <c r="H46" t="str">
-        <f t="shared" si="20"/>
-        <v>etal</v>
-      </c>
-      <c r="I46" t="str">
-        <f t="shared" si="21"/>
-        <v>2008</v>
-      </c>
-      <c r="J46" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
+        <v>10.1002/cne.24985</v>
       </c>
       <c r="K46" t="str">
-        <f t="shared" si="37"/>
-        <v>Isler_etal_2008_Table7</v>
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2020_TABLE1</v>
       </c>
       <c r="L46" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+        <f t="shared" si="45"/>
+        <v>10.1002%2Fcne.24985_TABLE1</v>
       </c>
       <c r="M46" t="str">
         <f t="array" ref="M46">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L46, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1002%2Fcne.24985_TABLE1.tsv</v>
+      </c>
+      <c r="N46" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="P46" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q46" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R46" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="S46" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T46" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="U46" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V46" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W46" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y46" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="AA46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB46" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE46" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A47" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E47" t="str">
+        <f t="shared" si="24"/>
+        <v>5</v>
+      </c>
+      <c r="F47" t="str">
+        <f t="shared" si="25"/>
+        <v>HerculanoHouzel_etal_2020</v>
+      </c>
+      <c r="G47" t="str">
+        <f t="shared" si="26"/>
+        <v>HerculanoHouzel</v>
+      </c>
+      <c r="H47" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I47" t="str">
+        <f t="shared" si="28"/>
+        <v>2020</v>
+      </c>
+      <c r="J47" t="str">
+        <f t="shared" si="19"/>
+        <v>10.1002/cne.24985</v>
+      </c>
+      <c r="K47" t="str">
+        <f t="shared" si="44"/>
+        <v>HerculanoHouzel_etal_2020_TABLE2</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="45"/>
+        <v>10.1002%2Fcne.24985_TABLE2</v>
+      </c>
+      <c r="M47" t="str">
+        <f t="array" ref="M47">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1002%2Fcne.24985_TABLE2.tsv</v>
+      </c>
+      <c r="N47" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="P47" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q47" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R47" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="S47" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T47" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="U47" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V47" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W47" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y47" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="AA47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AB47" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE47" s="1" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" ht="15.95" customHeight="1">
+      <c r="A48" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="E48" t="str">
+        <f t="shared" si="24"/>
+        <v>4</v>
+      </c>
+      <c r="F48" t="str">
+        <f t="shared" si="25"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="G48" t="str">
+        <f t="shared" si="26"/>
+        <v>Isler</v>
+      </c>
+      <c r="H48" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I48" t="str">
+        <f t="shared" si="28"/>
+        <v>2008</v>
+      </c>
+      <c r="J48" t="str">
+        <f t="shared" si="19"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="K48" t="str">
+        <f t="shared" si="44"/>
+        <v>Isler_etal_2008_Table2</v>
+      </c>
+      <c r="L48" t="str">
+        <f t="shared" si="45"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2</v>
+      </c>
+      <c r="M48" t="str">
+        <f t="array" ref="M48">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</v>
+      </c>
+      <c r="Q48" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="49" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A49" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="E49" t="str">
+        <f t="shared" si="24"/>
+        <v>4</v>
+      </c>
+      <c r="F49" t="str">
+        <f t="shared" si="25"/>
+        <v>Isler_etal_2008</v>
+      </c>
+      <c r="G49" t="str">
+        <f t="shared" si="26"/>
+        <v>Isler</v>
+      </c>
+      <c r="H49" t="str">
+        <f t="shared" si="27"/>
+        <v>etal</v>
+      </c>
+      <c r="I49" t="str">
+        <f t="shared" si="28"/>
+        <v>2008</v>
+      </c>
+      <c r="J49" t="str">
+        <f t="shared" si="19"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
+      </c>
+      <c r="K49" t="str">
+        <f t="shared" si="44"/>
+        <v>Isler_etal_2008_Table7</v>
+      </c>
+      <c r="L49" t="str">
+        <f t="shared" si="45"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Table7</v>
+      </c>
+      <c r="M49" t="str">
+        <f t="array" ref="M49">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</v>
       </c>
-      <c r="Q46" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="47" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="E47" t="str">
-        <f t="shared" ref="E47:E78" si="66">RIGHT(A47,1)</f>
+      <c r="Q49" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="50" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A50" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="E50" t="str">
+        <f t="shared" ref="E50:E82" si="84">RIGHT(A50,1)</f>
         <v>4</v>
       </c>
-      <c r="F47" t="str">
-        <f t="shared" ref="F47:F78" si="67">G47 &amp; IF(H47&lt;&gt;"", "_" &amp; H47, "_") &amp; IF(I47&lt;&gt;"", "_" &amp; I47, "_") &amp; IF(B47&lt;&gt;"", "_" &amp; B47, "")</f>
+      <c r="F50" t="str">
+        <f t="shared" ref="F50:F82" si="85">G50 &amp; IF(H50&lt;&gt;"", "_" &amp; H50, "_") &amp; IF(I50&lt;&gt;"", "_" &amp; I50, "_") &amp; IF(B50&lt;&gt;"", "_" &amp; B50, "")</f>
         <v>Isler_etal_2008</v>
       </c>
-      <c r="G47" t="str">
-        <f t="shared" ref="G47:G78" si="68">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A47,","), "-", ""), " ", "")</f>
+      <c r="G50" t="str">
+        <f t="shared" ref="G50:G82" si="86">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A50,","), "-", ""), " ", "")</f>
         <v>Isler</v>
       </c>
-      <c r="H47" t="str">
-        <f t="shared" ref="H47:H78" si="69">IF(ISNUMBER(FIND("&amp;", A47)),
-    IF(LEN(A47)-LEN(SUBSTITUTE(A47, ",", ""))&gt;=6, "etal", MID(A47, SEARCH("&amp; ", A47)+2, SEARCH(",", A47, SEARCH("&amp; ", A47)+2) - SEARCH("&amp; ", A47)-2)),
+      <c r="H50" t="str">
+        <f t="shared" ref="H50:H82" si="87">IF(ISNUMBER(FIND("&amp;", A50)),
+    IF(LEN(A50)-LEN(SUBSTITUTE(A50, ",", ""))&gt;=6, "etal", MID(A50, SEARCH("&amp; ", A50)+2, SEARCH(",", A50, SEARCH("&amp; ", A50)+2) - SEARCH("&amp; ", A50)-2)),
     ""
 )</f>
         <v>etal</v>
       </c>
-      <c r="I47" t="str">
-        <f t="shared" ref="I47:I78" si="70">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A47, "("), ")")</f>
+      <c r="I50" t="str">
+        <f t="shared" ref="I50:I82" si="88">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A50, "("), ")")</f>
         <v>2008</v>
       </c>
-      <c r="J47" t="str">
-        <f t="shared" si="12"/>
+      <c r="J50" t="str">
+        <f t="shared" si="19"/>
         <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
-      <c r="K47" t="str">
-        <f t="shared" si="37"/>
+      <c r="K50" t="str">
+        <f t="shared" si="44"/>
         <v>Isler_etal_2008_TableS1</v>
       </c>
-      <c r="L47" t="str">
-        <f t="shared" si="38"/>
+      <c r="L50" t="str">
+        <f t="shared" si="45"/>
         <v>10.1016%2Fj.jhevol.2008.08.004_TableS1</v>
-      </c>
-      <c r="M47" t="str">
-        <f t="array" ref="M47">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L47, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="48" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="E48" t="str">
-        <f t="shared" si="66"/>
-        <v>4</v>
-      </c>
-      <c r="F48" t="str">
-        <f t="shared" si="67"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G48" t="str">
-        <f t="shared" si="68"/>
-        <v>Isler</v>
-      </c>
-      <c r="H48" t="str">
-        <f t="shared" si="69"/>
-        <v>etal</v>
-      </c>
-      <c r="I48" t="str">
-        <f t="shared" si="70"/>
-        <v>2008</v>
-      </c>
-      <c r="J48" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="K48" t="str">
-        <f t="shared" si="37"/>
-        <v>Isler_etal_2008_TableS2</v>
-      </c>
-      <c r="L48" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
-      </c>
-      <c r="M48" t="str">
-        <f t="array" ref="M48">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L48, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
-      </c>
-      <c r="Q48" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="49" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E49" t="str">
-        <f t="shared" si="66"/>
-        <v>4</v>
-      </c>
-      <c r="F49" t="str">
-        <f t="shared" si="67"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G49" t="str">
-        <f t="shared" si="68"/>
-        <v>Isler</v>
-      </c>
-      <c r="H49" t="str">
-        <f t="shared" si="69"/>
-        <v>etal</v>
-      </c>
-      <c r="I49" t="str">
-        <f t="shared" si="70"/>
-        <v>2008</v>
-      </c>
-      <c r="J49" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="K49" t="str">
-        <f t="shared" si="37"/>
-        <v>Isler_etal_2008_TableS3</v>
-      </c>
-      <c r="L49" t="str">
-        <f t="shared" si="38"/>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
-      </c>
-      <c r="M49" t="str">
-        <f t="array" ref="M49">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L49, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
-      </c>
-      <c r="Q49" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="50" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>220</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E50" t="str">
-        <f t="shared" si="66"/>
-        <v>4</v>
-      </c>
-      <c r="F50" t="str">
-        <f t="shared" si="67"/>
-        <v>Isler_etal_2008</v>
-      </c>
-      <c r="G50" t="str">
-        <f t="shared" si="68"/>
-        <v>Isler</v>
-      </c>
-      <c r="H50" t="str">
-        <f t="shared" si="69"/>
-        <v>etal</v>
-      </c>
-      <c r="I50" t="str">
-        <f t="shared" si="70"/>
-        <v>2008</v>
-      </c>
-      <c r="J50" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1016/j.jhevol.2008.08.004</v>
-      </c>
-      <c r="K50" t="str">
-        <f t="shared" ref="K50:K78" si="71">TRIM(_xlfn.TEXTJOIN("_",FALSE,F50,(SUBSTITUTE(SUBSTITUTE(D50," ",""), "_", ""))))</f>
-        <v>Isler_etal_2008_Tree.nex</v>
-      </c>
-      <c r="L50" t="str">
-        <f t="shared" ref="L50:L78" si="72">IF(ISBLANK(C50),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J50, SUBSTITUTE(D50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C50, SUBSTITUTE(D50,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="M50" t="str">
         <f t="array" ref="M50">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L50, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="51" spans="1:31" ht="15.95" customHeight="1">
       <c r="A51" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>225</v>
+        <v>167</v>
       </c>
       <c r="E51" t="str">
-        <f t="shared" si="66"/>
-        <v>x</v>
+        <f t="shared" si="84"/>
+        <v>4</v>
       </c>
       <c r="F51" t="str">
-        <f t="shared" si="67"/>
-        <v>Iwaniuk_etal_1999</v>
+        <f t="shared" si="85"/>
+        <v>Isler_etal_2008</v>
       </c>
       <c r="G51" t="str">
-        <f t="shared" si="68"/>
-        <v>Iwaniuk</v>
+        <f t="shared" si="86"/>
+        <v>Isler</v>
       </c>
       <c r="H51" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I51" t="str">
-        <f t="shared" si="70"/>
-        <v>1999</v>
+        <f t="shared" si="88"/>
+        <v>2008</v>
       </c>
       <c r="J51" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1016/s0166-4328(98)00151-x</v>
+        <f t="shared" si="19"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K51" t="str">
-        <f t="shared" si="71"/>
-        <v>Iwaniuk_etal_1999_References</v>
+        <f t="shared" si="44"/>
+        <v>Isler_etal_2008_TableS2</v>
       </c>
       <c r="L51" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
+        <f t="shared" si="45"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2</v>
       </c>
       <c r="M51" t="str">
         <f t="array" ref="M51">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L51, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V51" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="W51" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="52" spans="1:31" ht="15.95" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>41</v>
+        <v>231</v>
       </c>
       <c r="E52" t="str">
-        <f t="shared" si="66"/>
-        <v>x</v>
+        <f t="shared" si="84"/>
+        <v>4</v>
       </c>
       <c r="F52" t="str">
-        <f t="shared" si="67"/>
-        <v>Iwaniuk_etal_1999</v>
+        <f t="shared" si="85"/>
+        <v>Isler_etal_2008</v>
       </c>
       <c r="G52" t="str">
-        <f t="shared" si="68"/>
-        <v>Iwaniuk</v>
+        <f t="shared" si="86"/>
+        <v>Isler</v>
       </c>
       <c r="H52" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I52" t="str">
-        <f t="shared" si="70"/>
-        <v>1999</v>
+        <f t="shared" si="88"/>
+        <v>2008</v>
       </c>
       <c r="J52" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1016/s0166-4328(98)00151-x</v>
+        <f t="shared" si="19"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K52" t="str">
-        <f t="shared" si="71"/>
-        <v>Iwaniuk_etal_1999_Table1</v>
+        <f t="shared" si="44"/>
+        <v>Isler_etal_2008_TableS3</v>
       </c>
       <c r="L52" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
+        <f t="shared" si="45"/>
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3</v>
       </c>
       <c r="M52" t="str">
         <f t="array" ref="M52">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L52, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</v>
-      </c>
-      <c r="N52" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="P52" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="V52" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W52" s="1" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="53" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="53" spans="1:31" ht="15.95" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>41</v>
+        <v>232</v>
       </c>
       <c r="E53" t="str">
-        <f t="shared" si="66"/>
-        <v>9</v>
+        <f t="shared" si="84"/>
+        <v>4</v>
       </c>
       <c r="F53" t="str">
-        <f t="shared" si="67"/>
-        <v>Iwaniuk_etal_2001</v>
+        <f t="shared" si="85"/>
+        <v>Isler_etal_2008</v>
       </c>
       <c r="G53" t="str">
-        <f t="shared" si="68"/>
-        <v>Iwaniuk</v>
+        <f t="shared" si="86"/>
+        <v>Isler</v>
       </c>
       <c r="H53" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I53" t="str">
-        <f t="shared" si="70"/>
-        <v>2001</v>
+        <f t="shared" si="88"/>
+        <v>2008</v>
       </c>
       <c r="J53" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="19"/>
+        <v>10.1016/j.jhevol.2008.08.004</v>
       </c>
       <c r="K53" t="str">
-        <f t="shared" si="71"/>
-        <v>Iwaniuk_etal_2001_Table1</v>
+        <f t="shared" ref="K53:K82" si="89">TRIM(_xlfn.TEXTJOIN("_",FALSE,F53,(SUBSTITUTE(SUBSTITUTE(D53," ",""), "_", ""))))</f>
+        <v>Isler_etal_2008_Tree.nex</v>
       </c>
       <c r="L53" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
+        <f t="shared" ref="L53:L82" si="90">IF(ISBLANK(C53),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J53, SUBSTITUTE(D53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C53, SUBSTITUTE(D53,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1016%2Fj.jhevol.2008.08.004_Tree.nex</v>
       </c>
       <c r="M53" t="str">
         <f t="array" ref="M53">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L53, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table1.tsv</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>229</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>230</v>
+        <v>notfound</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R53" s="4"/>
-      <c r="T53" s="1" t="str">
-        <f>IF(S53="N", R53, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U53" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V53" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y53" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="AE53" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="54" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:31" ht="15.95" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>194</v>
+        <v>234</v>
       </c>
       <c r="E54" t="str">
-        <f t="shared" si="66"/>
-        <v>9</v>
+        <f t="shared" si="84"/>
+        <v>x</v>
       </c>
       <c r="F54" t="str">
-        <f t="shared" si="67"/>
-        <v>Iwaniuk_etal_2001</v>
+        <f t="shared" si="85"/>
+        <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="G54" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="86"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H54" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I54" t="str">
-        <f t="shared" si="70"/>
-        <v>2001</v>
+        <f t="shared" si="88"/>
+        <v>1999</v>
       </c>
       <c r="J54" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="19"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="K54" t="str">
-        <f t="shared" si="71"/>
-        <v>Iwaniuk_etal_2001_Table2</v>
+        <f t="shared" si="89"/>
+        <v>Iwaniuk_etal_1999_References</v>
       </c>
       <c r="L54" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
+        <f t="shared" si="90"/>
+        <v>10.1016%2Fs0166-4328(98)00151-x_References</v>
       </c>
       <c r="M54" t="str">
         <f t="array" ref="M54">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L54, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table2.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N54" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="V54" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="W54" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A55" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="P54" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q54" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R54" s="4"/>
-      <c r="T54" s="1" t="str">
-        <f>IF(S54="N", R54, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U54" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V54" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y54" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="AE54" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="55" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="1" t="s">
-        <v>228</v>
-      </c>
       <c r="D55" s="1" t="s">
-        <v>198</v>
+        <v>42</v>
       </c>
       <c r="E55" t="str">
-        <f t="shared" si="66"/>
-        <v>9</v>
+        <f t="shared" si="84"/>
+        <v>x</v>
       </c>
       <c r="F55" t="str">
-        <f t="shared" si="67"/>
-        <v>Iwaniuk_etal_2001</v>
+        <f t="shared" si="85"/>
+        <v>Iwaniuk_etal_1999</v>
       </c>
       <c r="G55" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="86"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H55" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I55" t="str">
-        <f t="shared" si="70"/>
-        <v>2001</v>
+        <f t="shared" si="88"/>
+        <v>1999</v>
       </c>
       <c r="J55" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1037/0735-7036.115.1.29</v>
+        <f t="shared" si="19"/>
+        <v>10.1016/s0166-4328(98)00151-x</v>
       </c>
       <c r="K55" t="str">
-        <f t="shared" si="71"/>
-        <v>Iwaniuk_etal_2001_Table3</v>
+        <f t="shared" si="89"/>
+        <v>Iwaniuk_etal_1999_Table1</v>
       </c>
       <c r="L55" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
+        <f t="shared" si="90"/>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1</v>
       </c>
       <c r="M55" t="str">
         <f t="array" ref="M55">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L55, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table3.tsv</v>
+        <v>10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</v>
       </c>
       <c r="N55" s="1" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q55" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R55" s="4"/>
-      <c r="T55" s="1" t="str">
-        <f>IF(S55="N", R55, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U55" s="1" t="s">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="V55" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y55" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="AE55" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="56" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>35</v>
+      </c>
+      <c r="W55" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:31" ht="15.95" customHeight="1">
       <c r="A56" s="1" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>202</v>
+        <v>42</v>
       </c>
       <c r="E56" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>9</v>
       </c>
       <c r="F56" t="str">
-        <f t="shared" si="67"/>
+        <f t="shared" si="85"/>
         <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G56" t="str">
-        <f t="shared" si="68"/>
+        <f t="shared" si="86"/>
         <v>Iwaniuk</v>
       </c>
       <c r="H56" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I56" t="str">
-        <f t="shared" si="70"/>
+        <f t="shared" si="88"/>
         <v>2001</v>
       </c>
       <c r="J56" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="19"/>
         <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K56" t="str">
-        <f t="shared" si="71"/>
-        <v>Iwaniuk_etal_2001_Table4</v>
+        <f t="shared" si="89"/>
+        <v>Iwaniuk_etal_2001_Table1</v>
       </c>
       <c r="L56" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
+        <f t="shared" si="90"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table1</v>
       </c>
       <c r="M56" t="str">
         <f t="array" ref="M56">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L56, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1037%2F0735-7036.115.1.29_Table4.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table1.tsv</v>
       </c>
       <c r="N56" s="1" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="Q56" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R56" s="4"/>
       <c r="T56" s="1" t="str">
@@ -5486,943 +5441,952 @@
         <v>write file name</v>
       </c>
       <c r="U56" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V56" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y56" s="1" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="AE56" s="1" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="57" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="57" spans="1:31" ht="15.95" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>41</v>
+        <v>191</v>
       </c>
       <c r="E57" t="str">
-        <f t="shared" si="66"/>
-        <v>8</v>
+        <f t="shared" si="84"/>
+        <v>9</v>
       </c>
       <c r="F57" t="str">
-        <f t="shared" si="67"/>
-        <v>JardimMesseder_etal_2017</v>
+        <f t="shared" si="85"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G57" t="str">
-        <f t="shared" si="68"/>
-        <v>JardimMesseder</v>
+        <f t="shared" si="86"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="H57" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I57" t="str">
-        <f t="shared" si="70"/>
-        <v>2017</v>
+        <f t="shared" si="88"/>
+        <v>2001</v>
       </c>
       <c r="J57" t="str">
-        <f t="shared" si="12"/>
-        <v>10.3389/fnana.2017.00118</v>
+        <f t="shared" si="19"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K57" t="str">
-        <f t="shared" si="71"/>
-        <v>JardimMesseder_etal_2017_Table1</v>
+        <f t="shared" si="89"/>
+        <v>Iwaniuk_etal_2001_Table2</v>
       </c>
       <c r="L57" t="str">
-        <f t="shared" si="72"/>
-        <v>10.3389%2Ffnana.2017.00118_Table1</v>
+        <f t="shared" si="90"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table2</v>
       </c>
       <c r="M57" t="str">
         <f t="array" ref="M57">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L57, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table2.tsv</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="Q57" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R57" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="S57" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T57" s="1" t="s">
-        <v>239</v>
+        <v>96</v>
+      </c>
+      <c r="R57" s="4"/>
+      <c r="T57" s="1" t="str">
+        <f>IF(S57="N", R57, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U57" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V57" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W57" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X57" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y57" s="1" t="s">
         <v>240</v>
-      </c>
-      <c r="Y57" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z57" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA57" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB57" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="AE57" s="1" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:31" ht="15.95" customHeight="1">
       <c r="A58" s="1" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>35</v>
+        <v>207</v>
       </c>
       <c r="E58" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>9</v>
       </c>
       <c r="F58" t="str">
-        <f t="shared" si="67"/>
-        <v>Karl_etal_2024</v>
+        <f t="shared" si="85"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G58" t="str">
-        <f t="shared" si="68"/>
-        <v>Karl</v>
+        <f t="shared" si="86"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="H58" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I58" t="str">
-        <f t="shared" si="70"/>
-        <v>2024</v>
+        <f t="shared" si="88"/>
+        <v>2001</v>
       </c>
       <c r="J58" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1002/cne.25669</v>
+        <f t="shared" si="19"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K58" t="str">
-        <f t="shared" si="71"/>
-        <v>Karl_etal_2024_TABLE1</v>
+        <f t="shared" si="89"/>
+        <v>Iwaniuk_etal_2001_Table3</v>
       </c>
       <c r="L58" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1002%2Fcne.25669_TABLE1</v>
+        <f t="shared" si="90"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table3</v>
       </c>
       <c r="M58" t="str">
         <f t="array" ref="M58">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L58, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1002%2Fcne.25669_TABLE1.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table3.tsv</v>
       </c>
       <c r="N58" s="1" t="s">
         <v>243</v>
       </c>
+      <c r="P58" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q58" s="1" t="s">
+        <v>96</v>
+      </c>
       <c r="R58" s="4"/>
+      <c r="T58" s="1" t="str">
+        <f>IF(S58="N", R58, "write file name")</f>
+        <v>write file name</v>
+      </c>
       <c r="U58" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="V58" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W58" s="1" t="s">
-        <v>99</v>
+        <v>35</v>
       </c>
       <c r="Y58" s="1" t="s">
-        <v>244</v>
-      </c>
-      <c r="Z58" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="59" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>240</v>
+      </c>
+      <c r="AE58" s="1" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="59" spans="1:31" ht="15.95" customHeight="1">
       <c r="A59" s="1" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="E59" t="str">
-        <f t="shared" si="66"/>
-        <v>8</v>
+        <f t="shared" si="84"/>
+        <v>9</v>
       </c>
       <c r="F59" t="str">
-        <f t="shared" si="67"/>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="85"/>
+        <v>Iwaniuk_etal_2001</v>
       </c>
       <c r="G59" t="str">
-        <f t="shared" si="68"/>
-        <v>Kverkova</v>
+        <f t="shared" si="86"/>
+        <v>Iwaniuk</v>
       </c>
       <c r="H59" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I59" t="str">
-        <f t="shared" si="70"/>
-        <v>2018</v>
+        <f t="shared" si="88"/>
+        <v>2001</v>
       </c>
       <c r="J59" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="19"/>
+        <v>10.1037/0735-7036.115.1.29</v>
       </c>
       <c r="K59" t="str">
-        <f t="shared" si="71"/>
-        <v>Kverkova_etal_2018_Table1</v>
+        <f t="shared" si="89"/>
+        <v>Iwaniuk_etal_2001_Table4</v>
       </c>
       <c r="L59" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
+        <f t="shared" si="90"/>
+        <v>10.1037%2F0735-7036.115.1.29_Table4</v>
       </c>
       <c r="M59" t="str">
         <f t="array" ref="M59">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L59, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
+        <v>10.1037%2F0735-7036.115.1.29_Table4.tsv</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>51</v>
+        <v>239</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R59" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="S59" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T59" s="1" t="s">
-        <v>248</v>
+        <v>96</v>
+      </c>
+      <c r="R59" s="4"/>
+      <c r="T59" s="1" t="str">
+        <f>IF(S59="N", R59, "write file name")</f>
+        <v>write file name</v>
       </c>
       <c r="U59" s="1" t="s">
-        <v>249</v>
+        <v>87</v>
       </c>
       <c r="V59" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="Y59" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="Z59" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB59" s="1" t="s">
-        <v>136</v>
+        <v>240</v>
       </c>
       <c r="AE59" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="60" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="60" spans="1:31" ht="15.95" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>245</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="E60" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>8</v>
       </c>
       <c r="F60" t="str">
-        <f t="shared" si="67"/>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" si="85"/>
+        <v>JardimMesseder_etal_2017</v>
       </c>
       <c r="G60" t="str">
-        <f t="shared" si="68"/>
-        <v>Kverkova</v>
+        <f t="shared" si="86"/>
+        <v>JardimMesseder</v>
       </c>
       <c r="H60" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I60" t="str">
-        <f t="shared" si="70"/>
-        <v>2018</v>
+        <f t="shared" si="88"/>
+        <v>2017</v>
       </c>
       <c r="J60" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" si="19"/>
+        <v>10.3389/fnana.2017.00118</v>
       </c>
       <c r="K60" t="str">
-        <f t="shared" si="71"/>
-        <v>Kverkova_etal_2018_TableS1</v>
+        <f t="shared" si="89"/>
+        <v>JardimMesseder_etal_2017_Table1</v>
       </c>
       <c r="L60" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
+        <f t="shared" si="90"/>
+        <v>10.3389%2Ffnana.2017.00118_Table1</v>
       </c>
       <c r="M60" t="str">
         <f t="array" ref="M60">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L60, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
+        <v>10.3389%2Ffnana.2017.00118_Table1.tsv</v>
       </c>
       <c r="N60" s="1" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="R60" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="S60" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="T60" s="1" t="s">
         <v>248</v>
       </c>
       <c r="U60" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V60" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W60" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X60" s="1" t="s">
         <v>249</v>
       </c>
-      <c r="V60" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W60" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X60" s="1" t="s">
-        <v>254</v>
-      </c>
       <c r="Y60" s="1" t="s">
-        <v>214</v>
+        <v>136</v>
       </c>
       <c r="Z60" s="1" t="s">
-        <v>255</v>
+        <v>39</v>
+      </c>
+      <c r="AA60" s="1" t="s">
+        <v>137</v>
       </c>
       <c r="AB60" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AE60" s="1" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="61" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A61" s="1" t="s">
         <v>251</v>
       </c>
-    </row>
-    <row r="61" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="1" t="s">
-        <v>245</v>
-      </c>
       <c r="D61" s="1" t="s">
-        <v>256</v>
+        <v>191</v>
       </c>
       <c r="E61" t="str">
-        <f t="shared" si="66"/>
-        <v>8</v>
+        <f t="shared" ref="E61" si="91">RIGHT(A61,1)</f>
+        <v>4</v>
       </c>
       <c r="F61" t="str">
-        <f t="shared" si="67"/>
-        <v>Kverkova_etal_2018</v>
+        <f t="shared" ref="F61" si="92">G61 &amp; IF(H61&lt;&gt;"", "_" &amp; H61, "_") &amp; IF(I61&lt;&gt;"", "_" &amp; I61, "_") &amp; IF(B61&lt;&gt;"", "_" &amp; B61, "")</f>
+        <v>Johansen_etal_2024</v>
       </c>
       <c r="G61" t="str">
-        <f t="shared" si="68"/>
-        <v>Kverkova</v>
+        <f t="shared" ref="G61" si="93">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A61,","), "-", ""), " ", "")</f>
+        <v>Johansen</v>
       </c>
       <c r="H61" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" ref="H61" si="94">IF(ISNUMBER(FIND("&amp;", A61)),
+    IF(LEN(A61)-LEN(SUBSTITUTE(A61, ",", ""))&gt;=6, "etal", MID(A61, SEARCH("&amp; ", A61)+2, SEARCH(",", A61, SEARCH("&amp; ", A61)+2) - SEARCH("&amp; ", A61)-2)),
+    ""
+)</f>
         <v>etal</v>
       </c>
       <c r="I61" t="str">
-        <f t="shared" si="70"/>
-        <v>2018</v>
+        <f t="shared" ref="I61" si="95">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A61, "("), ")")</f>
+        <v>2024</v>
       </c>
       <c r="J61" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1038/s41598-018-26062-8</v>
+        <f t="shared" ref="J61" si="96">IF(C61&lt;&gt;"", C61, IF(C61="", _xlfn.TEXTAFTER(A61,"https://doi.org/"), C61))</f>
+        <v>10.1523/JNEUROSCI.1750-23.2024</v>
       </c>
       <c r="K61" t="str">
-        <f t="shared" si="71"/>
-        <v>Kverkova_etal_2018_TableS5</v>
+        <f t="shared" ref="K61" si="97">TRIM(_xlfn.TEXTJOIN("_",FALSE,F61,(SUBSTITUTE(SUBSTITUTE(D61," ",""), "_", ""))))</f>
+        <v>Johansen_etal_2024_Table2</v>
       </c>
       <c r="L61" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
+        <f t="shared" ref="L61" si="98">IF(ISBLANK(C61),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J61, SUBSTITUTE(D61,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C61, SUBSTITUTE(D61,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
+        <v>10.1523%2FJNEUROSCI.1750-23.2024_Table2</v>
       </c>
       <c r="M61" t="str">
         <f t="array" ref="M61">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L61, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N61" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="Q61" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="R61" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="S61" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="T61" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="U61" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="V61" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W61" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="X61" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="P61" s="10"/>
+      <c r="Q61" s="10"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="10"/>
+      <c r="T61" s="10"/>
+      <c r="U61" s="1"/>
+      <c r="V61" s="1"/>
+      <c r="W61" s="1"/>
+      <c r="X61" s="10"/>
+      <c r="Y61" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="10"/>
+      <c r="AB61" s="10"/>
+      <c r="AE61" s="10"/>
+    </row>
+    <row r="62" spans="1:31" ht="15.95" customHeight="1">
+      <c r="A62" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="Y61" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="Z61" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AB61" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="AE61" s="1" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="62" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="1" t="s">
-        <v>261</v>
-      </c>
       <c r="D62" s="1" t="s">
-        <v>262</v>
+        <v>37</v>
       </c>
       <c r="E62" t="str">
-        <f t="shared" si="66"/>
-        <v>4</v>
+        <f t="shared" si="84"/>
+        <v>9</v>
       </c>
       <c r="F62" t="str">
-        <f t="shared" si="67"/>
-        <v>Lewitus_etal_2013</v>
+        <f t="shared" si="85"/>
+        <v>Karl_etal_2024</v>
       </c>
       <c r="G62" t="str">
-        <f t="shared" si="68"/>
-        <v>Lewitus</v>
+        <f t="shared" si="86"/>
+        <v>Karl</v>
       </c>
       <c r="H62" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I62" t="str">
-        <f t="shared" si="70"/>
-        <v>2013</v>
+        <f t="shared" si="88"/>
+        <v>2024</v>
       </c>
       <c r="J62" t="str">
-        <f t="shared" si="12"/>
-        <v>10.3389/fnhum.2013.00424</v>
+        <f t="shared" si="19"/>
+        <v>10.1002/cne.25669</v>
       </c>
       <c r="K62" t="str">
-        <f t="shared" si="71"/>
-        <v>Lewitus_etal_2013_TableS2partial</v>
+        <f t="shared" si="89"/>
+        <v>Karl_etal_2024_TABLE1</v>
       </c>
       <c r="L62" t="str">
-        <f t="shared" si="72"/>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
+        <f t="shared" si="90"/>
+        <v>10.1002%2Fcne.25669_TABLE1</v>
       </c>
       <c r="M62" t="str">
         <f t="array" ref="M62">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L62, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
-      </c>
-      <c r="Q62" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA62" s="1" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="63" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>10.1002%2Fcne.25669_TABLE1.tsv</v>
+      </c>
+      <c r="N62" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="R62" s="4"/>
+      <c r="U62" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V62" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W62" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="Y62" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="Z62" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:31" ht="15.95" customHeight="1">
       <c r="A63" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D63" s="1" t="s">
-        <v>128</v>
+        <v>42</v>
       </c>
       <c r="E63" t="str">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="84"/>
+        <v>8</v>
       </c>
       <c r="F63" t="str">
-        <f t="shared" si="67"/>
-        <v>Lewitus_etal_2014</v>
+        <f t="shared" si="85"/>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="G63" t="str">
-        <f t="shared" si="68"/>
-        <v>Lewitus</v>
+        <f t="shared" si="86"/>
+        <v>Kverkova</v>
       </c>
       <c r="H63" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I63" t="str">
-        <f t="shared" si="70"/>
-        <v>2014</v>
+        <f t="shared" si="88"/>
+        <v>2018</v>
       </c>
       <c r="J63" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1371/journal.pbio.1002000</v>
+        <f t="shared" si="19"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K63" t="str">
-        <f t="shared" si="71"/>
-        <v>Lewitus_etal_2014_TableS1</v>
+        <f t="shared" si="89"/>
+        <v>Kverkova_etal_2018_Table1</v>
       </c>
       <c r="L63" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
+        <f t="shared" si="90"/>
+        <v>10.1038%2Fs41598-018-26062-8_Table1</v>
       </c>
       <c r="M63" t="str">
         <f t="array" ref="M63">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L63, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_Table1.tsv</v>
       </c>
       <c r="N63" s="1" t="s">
-        <v>265</v>
+        <v>258</v>
+      </c>
+      <c r="P63" s="1" t="s">
+        <v>52</v>
       </c>
       <c r="Q63" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA63" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R63" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="S63" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T63" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="U63" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="V63" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y63" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="Z63" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE63" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:31" ht="15.95" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D64" s="1" t="s">
-        <v>266</v>
+        <v>129</v>
       </c>
       <c r="E64" t="str">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="84"/>
+        <v>8</v>
       </c>
       <c r="F64" t="str">
-        <f t="shared" si="67"/>
-        <v>Lewitus_etal_2014</v>
+        <f t="shared" si="85"/>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="G64" t="str">
-        <f t="shared" si="68"/>
-        <v>Lewitus</v>
+        <f t="shared" si="86"/>
+        <v>Kverkova</v>
       </c>
       <c r="H64" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I64" t="str">
-        <f t="shared" si="70"/>
-        <v>2014</v>
+        <f t="shared" si="88"/>
+        <v>2018</v>
       </c>
       <c r="J64" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1371/journal.pbio.1002000</v>
+        <f t="shared" si="19"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K64" t="str">
-        <f t="shared" si="71"/>
-        <v>Lewitus_etal_2014_TableS8</v>
+        <f t="shared" si="89"/>
+        <v>Kverkova_etal_2018_TableS1</v>
       </c>
       <c r="L64" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
+        <f t="shared" si="90"/>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1</v>
       </c>
       <c r="M64" t="str">
         <f t="array" ref="M64">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L64, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS1.tsv</v>
       </c>
       <c r="N64" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="P64" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q64" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R64" s="4" t="s">
+        <v>265</v>
+      </c>
+      <c r="S64" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T64" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="U64" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="V64" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W64" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X64" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="Y64" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="Z64" s="1" t="s">
         <v>267</v>
       </c>
-      <c r="Q64" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="AA64" s="1" t="s">
+      <c r="AB64" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE64" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:31" ht="15.95" customHeight="1">
       <c r="A65" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="D65" s="1" t="s">
-        <v>41</v>
-      </c>
       <c r="E65" t="str">
-        <f t="shared" si="66"/>
-        <v>5</v>
+        <f t="shared" si="84"/>
+        <v>8</v>
       </c>
       <c r="F65" t="str">
-        <f t="shared" si="67"/>
-        <v>MacLarnon__1996</v>
+        <f t="shared" si="85"/>
+        <v>Kverkova_etal_2018</v>
       </c>
       <c r="G65" t="str">
-        <f t="shared" si="68"/>
-        <v>MacLarnon</v>
+        <f t="shared" si="86"/>
+        <v>Kverkova</v>
       </c>
       <c r="H65" t="str">
-        <f t="shared" si="69"/>
-        <v/>
+        <f t="shared" si="87"/>
+        <v>etal</v>
       </c>
       <c r="I65" t="str">
-        <f t="shared" si="70"/>
-        <v>1996</v>
+        <f t="shared" si="88"/>
+        <v>2018</v>
       </c>
       <c r="J65" t="str">
-        <f t="shared" si="12"/>
-        <v>10.1006/jhev.1996.0005</v>
+        <f t="shared" si="19"/>
+        <v>10.1038/s41598-018-26062-8</v>
       </c>
       <c r="K65" t="str">
-        <f t="shared" si="71"/>
-        <v>MacLarnon__1996_Table1</v>
+        <f t="shared" si="89"/>
+        <v>Kverkova_etal_2018_TableS5</v>
       </c>
       <c r="L65" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1006%2Fjhev.1996.0005_Table1</v>
+        <f t="shared" si="90"/>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5</v>
       </c>
       <c r="M65" t="str">
         <f t="array" ref="M65">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L65, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
+        <v>10.1038%2Fs41598-018-26062-8_TableS5.tsv</v>
       </c>
       <c r="N65" s="1" t="s">
         <v>269</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="66" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+      <c r="Q65" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="R65" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="S65" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="T65" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="U65" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="V65" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W65" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="X65" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="Y65" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="Z65" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AB65" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="AE65" s="1" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="66" spans="1:31" ht="15.95" customHeight="1">
       <c r="A66" s="1" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="E66" t="str">
-        <f t="shared" si="66"/>
-        <v>2</v>
+        <f t="shared" si="84"/>
+        <v>4</v>
       </c>
       <c r="F66" t="str">
-        <f t="shared" si="67"/>
-        <v>ManyPrimates__2022</v>
+        <f t="shared" si="85"/>
+        <v>Lewitus_etal_2013</v>
       </c>
       <c r="G66" t="str">
-        <f t="shared" si="68"/>
-        <v>ManyPrimates</v>
+        <f t="shared" si="86"/>
+        <v>Lewitus</v>
       </c>
       <c r="H66" t="str">
-        <f t="shared" si="69"/>
-        <v/>
+        <f t="shared" si="87"/>
+        <v>etal</v>
       </c>
       <c r="I66" t="str">
-        <f t="shared" si="70"/>
-        <v>2022</v>
+        <f t="shared" si="88"/>
+        <v>2013</v>
       </c>
       <c r="J66" t="str">
-        <f t="shared" si="12"/>
-        <v>10.26451/abc.09.04.06.2022</v>
+        <f t="shared" si="19"/>
+        <v>10.3389/fnhum.2013.00424</v>
       </c>
       <c r="K66" t="str">
-        <f t="shared" si="71"/>
-        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
+        <f t="shared" si="89"/>
+        <v>Lewitus_etal_2013_TableS2partial</v>
       </c>
       <c r="L66" t="str">
-        <f t="shared" si="72"/>
-        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
+        <f t="shared" si="90"/>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial</v>
       </c>
       <c r="M66" t="str">
         <f t="array" ref="M66">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L66, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P66" s="1" t="s">
-        <v>272</v>
+        <v>10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R66" s="4"/>
-      <c r="T66" s="1" t="str">
-        <f>IF(S66="N", R66, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U66" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="V66" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W66" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X66" s="1" t="s">
-        <v>273</v>
-      </c>
-      <c r="Y66" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="Z66" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC66" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA66" s="1" t="s">
         <v>275</v>
       </c>
-      <c r="AE66" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="67" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="67" spans="1:31" ht="15.95" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>276</v>
       </c>
       <c r="D67" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E67" t="str">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="84"/>
+        <v>0</v>
       </c>
       <c r="F67" t="str">
-        <f t="shared" si="67"/>
-        <v>Mota_etal_2015</v>
+        <f t="shared" si="85"/>
+        <v>Lewitus_etal_2014</v>
       </c>
       <c r="G67" t="str">
-        <f t="shared" si="68"/>
-        <v>Mota</v>
+        <f t="shared" si="86"/>
+        <v>Lewitus</v>
       </c>
       <c r="H67" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I67" t="str">
-        <f t="shared" si="70"/>
-        <v>2015</v>
+        <f t="shared" si="88"/>
+        <v>2014</v>
       </c>
       <c r="J67" t="str">
-        <f t="shared" ref="J67:J78" si="73">IF(C67&lt;&gt;"", C67, IF(C67="", _xlfn.TEXTAFTER(A67,"https://doi.org/"), C67))</f>
-        <v>10.1126/science.aaa9101</v>
+        <f t="shared" si="19"/>
+        <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="K67" t="str">
-        <f t="shared" si="71"/>
-        <v>Mota_etal_2015_TableS1</v>
+        <f t="shared" si="89"/>
+        <v>Lewitus_etal_2014_TableS1</v>
       </c>
       <c r="L67" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
+        <f t="shared" si="90"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1</v>
       </c>
       <c r="M67" t="str">
         <f t="array" ref="M67">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L67, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS1.tsv</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="68" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+      <c r="AA67" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="68" spans="1:31" ht="15.95" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D68" s="1" t="s">
         <v>278</v>
       </c>
       <c r="E68" t="str">
-        <f t="shared" si="66"/>
-        <v>6</v>
+        <f t="shared" si="84"/>
+        <v>0</v>
       </c>
       <c r="F68" t="str">
-        <f t="shared" si="67"/>
-        <v>Mota_etal_2019</v>
+        <f t="shared" si="85"/>
+        <v>Lewitus_etal_2014</v>
       </c>
       <c r="G68" t="str">
-        <f t="shared" si="68"/>
-        <v>Mota</v>
+        <f t="shared" si="86"/>
+        <v>Lewitus</v>
       </c>
       <c r="H68" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I68" t="str">
-        <f t="shared" si="70"/>
-        <v>2019</v>
+        <f t="shared" si="88"/>
+        <v>2014</v>
       </c>
       <c r="J68" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1073/pnas.1716956116</v>
+        <f t="shared" si="19"/>
+        <v>10.1371/journal.pbio.1002000</v>
       </c>
       <c r="K68" t="str">
-        <f t="shared" si="71"/>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
+        <f t="shared" si="89"/>
+        <v>Lewitus_etal_2014_TableS8</v>
       </c>
       <c r="L68" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+        <f t="shared" si="90"/>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8</v>
       </c>
       <c r="M68" t="str">
         <f t="array" ref="M68">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L68, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
+        <v>10.1371%2Fjournal.pbio.1002000_TableS8.tsv</v>
       </c>
       <c r="N68" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="P68" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="AC68" s="1" t="s">
+      <c r="Q68" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA68" s="1" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="69" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A69" s="1" t="s">
         <v>280</v>
       </c>
-    </row>
-    <row r="69" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>281</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>282</v>
-      </c>
       <c r="D69" s="1" t="s">
-        <v>283</v>
+        <v>42</v>
       </c>
       <c r="E69" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>5</v>
       </c>
       <c r="F69" t="str">
-        <f t="shared" si="67"/>
-        <v>Powell_etal_2017</v>
+        <f t="shared" si="85"/>
+        <v>MacLarnon__1996</v>
       </c>
       <c r="G69" t="str">
-        <f t="shared" si="68"/>
-        <v>Powell</v>
+        <f t="shared" si="86"/>
+        <v>MacLarnon</v>
       </c>
       <c r="H69" t="str">
-        <f t="shared" si="69"/>
-        <v>etal</v>
+        <f t="shared" si="87"/>
+        <v/>
       </c>
       <c r="I69" t="str">
-        <f t="shared" si="70"/>
-        <v>2017</v>
+        <f t="shared" si="88"/>
+        <v>1996</v>
       </c>
       <c r="J69" t="str">
-        <f t="shared" si="73"/>
-        <v>10.6084/m9.figshare.c.3899422.v1</v>
+        <f t="shared" si="19"/>
+        <v>10.1006/jhev.1996.0005</v>
       </c>
       <c r="K69" t="str">
-        <f t="shared" si="71"/>
-        <v>Powell_etal_2017_Dataset1</v>
+        <f t="shared" si="89"/>
+        <v>MacLarnon__1996_Table1</v>
       </c>
       <c r="L69" t="str">
-        <f t="shared" si="72"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <f t="shared" si="90"/>
+        <v>10.1006%2Fjhev.1996.0005_Table1</v>
       </c>
       <c r="M69" t="str">
         <f t="array" ref="M69">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L69, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
+        <v>10.1006%2Fjhev.1996.0005_Table1.tsv</v>
+      </c>
+      <c r="N69" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="Q69" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R69" s="4"/>
-      <c r="T69" s="1" t="str">
-        <f>IF(S69="N", R69, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U69" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="V69" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="W69" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="X69" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="Y69" s="1" t="s">
-        <v>285</v>
-      </c>
-      <c r="Z69" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC69" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AE69" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="70" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="70" spans="1:31" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>202</v>
+        <v>283</v>
       </c>
       <c r="E70" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>2</v>
       </c>
       <c r="F70" t="str">
-        <f t="shared" si="67"/>
-        <v>Sherwood_etal_2004_I</v>
+        <f t="shared" si="85"/>
+        <v>ManyPrimates__2022</v>
       </c>
       <c r="G70" t="str">
-        <f t="shared" si="68"/>
-        <v>Sherwood</v>
+        <f t="shared" si="86"/>
+        <v>ManyPrimates</v>
       </c>
       <c r="H70" t="str">
-        <f t="shared" si="69"/>
-        <v>etal</v>
+        <f t="shared" si="87"/>
+        <v/>
       </c>
       <c r="I70" t="str">
-        <f t="shared" si="70"/>
-        <v>2004</v>
+        <f t="shared" si="88"/>
+        <v>2022</v>
       </c>
       <c r="J70" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1159/000075672</v>
+        <f t="shared" si="19"/>
+        <v>10.26451/abc.09.04.06.2022</v>
       </c>
       <c r="K70" t="str">
-        <f t="shared" si="71"/>
-        <v>Sherwood_etal_2004_I_Table4</v>
+        <f t="shared" si="89"/>
+        <v>ManyPrimates__2022_data/speciespredictors.xlsx</v>
       </c>
       <c r="L70" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1159%2F000075672_Table4</v>
+        <f t="shared" si="90"/>
+        <v>10.26451%2Fabc.09.04.06.2022_data%2Fspeciespredictors.xlsx</v>
       </c>
       <c r="M70" t="str">
         <f t="array" ref="M70">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L70, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N70" s="1" t="s">
-        <v>288</v>
-      </c>
       <c r="P70" s="1" t="s">
-        <v>272</v>
+        <v>284</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="R70" s="4"/>
       <c r="T70" s="1" t="str">
@@ -6430,485 +6394,752 @@
         <v>write file name</v>
       </c>
       <c r="U70" s="1" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="V70" s="1" t="s">
-        <v>289</v>
+        <v>35</v>
+      </c>
+      <c r="W70" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="X70" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="Y70" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="Z70" s="1" t="s">
-        <v>38</v>
+        <v>59</v>
+      </c>
+      <c r="AC70" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="AE70" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="71" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="71" spans="1:31" ht="15.75" customHeight="1">
       <c r="A71" s="1" t="s">
-        <v>286</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>206</v>
+        <v>129</v>
       </c>
       <c r="E71" t="str">
-        <f t="shared" si="66"/>
-        <v>2</v>
+        <f t="shared" si="84"/>
+        <v>1</v>
       </c>
       <c r="F71" t="str">
-        <f t="shared" si="67"/>
-        <v>Sherwood_etal_2004_I</v>
+        <f t="shared" si="85"/>
+        <v>Mota_etal_2015</v>
       </c>
       <c r="G71" t="str">
-        <f t="shared" si="68"/>
-        <v>Sherwood</v>
+        <f t="shared" si="86"/>
+        <v>Mota</v>
       </c>
       <c r="H71" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I71" t="str">
-        <f t="shared" si="70"/>
-        <v>2004</v>
+        <f t="shared" si="88"/>
+        <v>2015</v>
       </c>
       <c r="J71" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1159/000075672</v>
+        <f t="shared" ref="J71:J82" si="99">IF(C71&lt;&gt;"", C71, IF(C71="", _xlfn.TEXTAFTER(A71,"https://doi.org/"), C71))</f>
+        <v>10.1126/science.aaa9101</v>
       </c>
       <c r="K71" t="str">
-        <f t="shared" si="71"/>
-        <v>Sherwood_etal_2004_I_Table5</v>
+        <f t="shared" si="89"/>
+        <v>Mota_etal_2015_TableS1</v>
       </c>
       <c r="L71" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1159%2F000075672_Table5</v>
+        <f t="shared" si="90"/>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="M71" t="str">
         <f t="array" ref="M71">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L71, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N71" s="1" t="s">
-        <v>291</v>
-      </c>
-      <c r="P71" s="1" t="s">
-        <v>272</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R71" s="4"/>
-      <c r="T71" s="1" t="str">
-        <f>IF(S71="N", R71, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U71" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V71" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="72" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A72" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="Y71" s="1" t="s">
+      <c r="D72" s="1" t="s">
         <v>290</v>
       </c>
-      <c r="Z71" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE71" s="1" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="72" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="1" t="s">
-        <v>292</v>
-      </c>
-      <c r="D72" s="1" t="s">
-        <v>293</v>
-      </c>
       <c r="E72" t="str">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="84"/>
+        <v>6</v>
       </c>
       <c r="F72" t="str">
-        <f t="shared" si="67"/>
-        <v>Smaers_etal_2011</v>
+        <f t="shared" si="85"/>
+        <v>Mota_etal_2019</v>
       </c>
       <c r="G72" t="str">
-        <f t="shared" si="68"/>
-        <v>Smaers</v>
+        <f t="shared" si="86"/>
+        <v>Mota</v>
       </c>
       <c r="H72" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I72" t="str">
-        <f t="shared" si="70"/>
-        <v>2011</v>
+        <f t="shared" si="88"/>
+        <v>2019</v>
       </c>
       <c r="J72" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1159/000323671</v>
+        <f t="shared" si="99"/>
+        <v>10.1073/pnas.1716956116</v>
       </c>
       <c r="K72" t="str">
-        <f t="shared" si="71"/>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
+        <f t="shared" si="89"/>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="L72" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
+        <f t="shared" si="90"/>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="M72" t="str">
         <f t="array" ref="M72">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L72, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
-      </c>
-      <c r="Q72" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="73" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>notfound</v>
+      </c>
+      <c r="N72" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="P72" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="AC72" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="73" spans="1:31" ht="15.75" customHeight="1">
       <c r="A73" s="1" t="s">
-        <v>292</v>
+        <v>293</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="D73" s="1" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E73" t="str">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="84"/>
+        <v>5</v>
       </c>
       <c r="F73" t="str">
-        <f t="shared" si="67"/>
-        <v>Smaers_etal_2011</v>
+        <f t="shared" si="85"/>
+        <v>Powell_etal_2017</v>
       </c>
       <c r="G73" t="str">
-        <f t="shared" si="68"/>
-        <v>Smaers</v>
+        <f t="shared" si="86"/>
+        <v>Powell</v>
       </c>
       <c r="H73" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I73" t="str">
-        <f t="shared" si="70"/>
-        <v>2011</v>
+        <f t="shared" si="88"/>
+        <v>2017</v>
       </c>
       <c r="J73" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1159/000323671</v>
+        <f t="shared" si="99"/>
+        <v>10.6084/m9.figshare.c.3899422.v1</v>
       </c>
       <c r="K73" t="str">
-        <f t="shared" si="71"/>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
+        <f t="shared" si="89"/>
+        <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="L73" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
+        <f t="shared" si="90"/>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="M73" t="str">
         <f t="array" ref="M73">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L73, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</v>
+      </c>
+      <c r="P73" s="1" t="s">
+        <v>162</v>
       </c>
       <c r="Q73" s="1" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="74" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>96</v>
+      </c>
+      <c r="R73" s="4"/>
+      <c r="T73" s="1" t="str">
+        <f>IF(S73="N", R73, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U73" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="V73" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="W73" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="X73" s="1" t="s">
+        <v>296</v>
+      </c>
+      <c r="Y73" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="Z73" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="AC73" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="AE73" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="74" spans="1:31" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>295</v>
+        <v>298</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="D74" s="1" t="s">
-        <v>41</v>
+        <v>211</v>
       </c>
       <c r="E74" t="str">
-        <f t="shared" si="66"/>
+        <f t="shared" si="84"/>
         <v>2</v>
       </c>
       <c r="F74" t="str">
-        <f t="shared" si="67"/>
-        <v>Turner_etal_2016</v>
+        <f t="shared" si="85"/>
+        <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G74" t="str">
-        <f t="shared" si="68"/>
-        <v>Turner</v>
+        <f t="shared" si="86"/>
+        <v>Sherwood</v>
       </c>
       <c r="H74" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I74" t="str">
-        <f t="shared" si="70"/>
-        <v>2016</v>
+        <f t="shared" si="88"/>
+        <v>2004</v>
       </c>
       <c r="J74" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1159/000446762</v>
+        <f t="shared" si="99"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="K74" t="str">
-        <f t="shared" si="71"/>
-        <v>Turner_etal_2016_Table1</v>
+        <f t="shared" si="89"/>
+        <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="L74" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1159%2F000446762_Table1</v>
+        <f t="shared" si="90"/>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="M74" t="str">
         <f t="array" ref="M74">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L74, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N74" s="1" t="s">
-        <v>296</v>
+        <v>300</v>
+      </c>
+      <c r="P74" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q74" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R74" s="4"/>
+      <c r="T74" s="1" t="str">
+        <f>IF(S74="N", R74, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U74" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V74" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="Y74" s="1" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="75" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+        <v>302</v>
+      </c>
+      <c r="Z74" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE74" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:31" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>298</v>
       </c>
+      <c r="B75" s="1" t="s">
+        <v>299</v>
+      </c>
       <c r="D75" s="1" t="s">
-        <v>299</v>
+        <v>215</v>
       </c>
       <c r="E75" t="str">
-        <f t="shared" si="66"/>
-        <v>1</v>
+        <f t="shared" si="84"/>
+        <v>2</v>
       </c>
       <c r="F75" t="str">
-        <f t="shared" si="67"/>
-        <v>Wilman_etal_2014</v>
+        <f t="shared" si="85"/>
+        <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G75" t="str">
-        <f t="shared" si="68"/>
-        <v>Wilman</v>
+        <f t="shared" si="86"/>
+        <v>Sherwood</v>
       </c>
       <c r="H75" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I75" t="str">
-        <f t="shared" si="70"/>
-        <v>2014</v>
+        <f t="shared" si="88"/>
+        <v>2004</v>
       </c>
       <c r="J75" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1890/13-1917.1</v>
+        <f t="shared" si="99"/>
+        <v>10.1159/000075672</v>
       </c>
       <c r="K75" t="str">
-        <f t="shared" si="71"/>
-        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+        <f t="shared" si="89"/>
+        <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="L75" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+        <f t="shared" si="90"/>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="M75" t="str">
         <f t="array" ref="M75">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L75, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-    </row>
-    <row r="76" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="N75" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="P75" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q75" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R75" s="4"/>
+      <c r="T75" s="1" t="str">
+        <f>IF(S75="N", R75, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U75" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V75" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="Y75" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="Z75" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE75" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="76" spans="1:31" ht="15.75" customHeight="1">
       <c r="A76" s="1" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E76" t="str">
-        <f t="shared" si="66"/>
-        <v>7</v>
+        <f t="shared" si="84"/>
+        <v>1</v>
       </c>
       <c r="F76" t="str">
-        <f t="shared" si="67"/>
-        <v>Wimberly_etal_2021</v>
+        <f t="shared" si="85"/>
+        <v>Smaers_etal_2011</v>
       </c>
       <c r="G76" t="str">
-        <f t="shared" si="68"/>
-        <v>Wimberly</v>
+        <f t="shared" si="86"/>
+        <v>Smaers</v>
       </c>
       <c r="H76" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I76" t="str">
-        <f t="shared" si="70"/>
-        <v>2021</v>
+        <f t="shared" si="88"/>
+        <v>2011</v>
       </c>
       <c r="J76" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1098/rspb.2021.0937</v>
+        <f t="shared" si="99"/>
+        <v>10.1159/000323671</v>
       </c>
       <c r="K76" t="str">
-        <f t="shared" si="71"/>
-        <v>Wimberly_etal_2021_mammalgait.txt</v>
+        <f t="shared" si="89"/>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="L76" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+        <f t="shared" si="90"/>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="M76" t="str">
         <f t="array" ref="M76">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L76, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P76" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
+        <v>10.1159%2F000323671_SupplementaryTable1.tsv</v>
+      </c>
+      <c r="Q76" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="77" spans="1:31" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="E77" t="str">
-        <f t="shared" si="66"/>
-        <v>5</v>
+        <f t="shared" si="84"/>
+        <v>1</v>
       </c>
       <c r="F77" t="str">
-        <f t="shared" si="67"/>
-        <v>Winkler_Bryant_2021</v>
+        <f t="shared" si="85"/>
+        <v>Smaers_etal_2011</v>
       </c>
       <c r="G77" t="str">
-        <f t="shared" si="68"/>
-        <v>Winkler</v>
+        <f t="shared" si="86"/>
+        <v>Smaers</v>
       </c>
       <c r="H77" t="str">
-        <f t="shared" si="69"/>
-        <v>Bryant</v>
+        <f t="shared" si="87"/>
+        <v>etal</v>
       </c>
       <c r="I77" t="str">
-        <f t="shared" si="70"/>
-        <v>2021</v>
+        <f t="shared" si="88"/>
+        <v>2011</v>
       </c>
       <c r="J77" t="str">
-        <f t="shared" si="73"/>
-        <v>10.1080/09524622.2021.1905065</v>
+        <f t="shared" si="99"/>
+        <v>10.1159/000323671</v>
       </c>
       <c r="K77" t="str">
-        <f t="shared" si="71"/>
-        <v>Winkler_Bryant_2021_Figure1</v>
+        <f t="shared" si="89"/>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="L77" t="str">
-        <f t="shared" si="72"/>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <f t="shared" si="90"/>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
       <c r="M77" t="str">
         <f t="array" ref="M77">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L77, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P77" s="1" t="s">
-        <v>160</v>
+        <v>10.1159%2F000323671_SupplementaryTable2.tsv</v>
       </c>
       <c r="Q77" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R77" s="4"/>
-      <c r="T77" s="1" t="str">
-        <f>IF(S77="N", R77, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U77" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V77" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="Y77" s="1" t="s">
-        <v>305</v>
-      </c>
-      <c r="AE77" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="78" spans="1:31" ht="15.75" customHeight="1">
       <c r="A78" s="1" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D78" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E78" t="str">
-        <f t="shared" si="66"/>
-        <v>0</v>
+        <f t="shared" si="84"/>
+        <v>2</v>
       </c>
       <c r="F78" t="str">
-        <f t="shared" si="67"/>
-        <v>Young_etal_2013</v>
+        <f t="shared" si="85"/>
+        <v>Turner_etal_2016</v>
       </c>
       <c r="G78" t="str">
-        <f t="shared" si="68"/>
-        <v>Young</v>
+        <f t="shared" si="86"/>
+        <v>Turner</v>
       </c>
       <c r="H78" t="str">
-        <f t="shared" si="69"/>
+        <f t="shared" si="87"/>
         <v>etal</v>
       </c>
       <c r="I78" t="str">
-        <f t="shared" si="70"/>
-        <v>2013</v>
+        <f t="shared" si="88"/>
+        <v>2016</v>
       </c>
       <c r="J78" t="str">
-        <f t="shared" si="73"/>
-        <v>10.3389/fncir.2013.00030</v>
+        <f t="shared" si="99"/>
+        <v>10.1159/000446762</v>
       </c>
       <c r="K78" t="str">
-        <f t="shared" si="71"/>
-        <v>Young_etal_2013_Table1</v>
+        <f t="shared" si="89"/>
+        <v>Turner_etal_2016_Table1</v>
       </c>
       <c r="L78" t="str">
-        <f t="shared" si="72"/>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <f t="shared" si="90"/>
+        <v>10.1159%2F000446762_Table1</v>
       </c>
       <c r="M78" t="str">
         <f t="array" ref="M78">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L78, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="P78" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="Q78" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="R78" s="4"/>
-      <c r="T78" s="1" t="str">
-        <f>IF(S78="N", R78, "write file name")</f>
+      <c r="N78" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="Y78" s="1" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="79" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A79" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E79" t="str">
+        <f t="shared" si="84"/>
+        <v>1</v>
+      </c>
+      <c r="F79" t="str">
+        <f t="shared" si="85"/>
+        <v>Wilman_etal_2014</v>
+      </c>
+      <c r="G79" t="str">
+        <f t="shared" si="86"/>
+        <v>Wilman</v>
+      </c>
+      <c r="H79" t="str">
+        <f t="shared" si="87"/>
+        <v>etal</v>
+      </c>
+      <c r="I79" t="str">
+        <f t="shared" si="88"/>
+        <v>2014</v>
+      </c>
+      <c r="J79" t="str">
+        <f t="shared" si="99"/>
+        <v>10.1890/13-1917.1</v>
+      </c>
+      <c r="K79" t="str">
+        <f t="shared" si="89"/>
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+      </c>
+      <c r="L79" t="str">
+        <f t="shared" si="90"/>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+      </c>
+      <c r="M79" t="str">
+        <f t="array" ref="M79">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L79, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+    </row>
+    <row r="80" spans="1:31" ht="15.75" customHeight="1">
+      <c r="A80" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="E80" t="str">
+        <f t="shared" si="84"/>
+        <v>7</v>
+      </c>
+      <c r="F80" t="str">
+        <f t="shared" si="85"/>
+        <v>Wimberly_etal_2021</v>
+      </c>
+      <c r="G80" t="str">
+        <f t="shared" si="86"/>
+        <v>Wimberly</v>
+      </c>
+      <c r="H80" t="str">
+        <f t="shared" si="87"/>
+        <v>etal</v>
+      </c>
+      <c r="I80" t="str">
+        <f t="shared" si="88"/>
+        <v>2021</v>
+      </c>
+      <c r="J80" t="str">
+        <f t="shared" si="99"/>
+        <v>10.1098/rspb.2021.0937</v>
+      </c>
+      <c r="K80" t="str">
+        <f t="shared" si="89"/>
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
+      </c>
+      <c r="L80" t="str">
+        <f t="shared" si="90"/>
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+      </c>
+      <c r="M80" t="str">
+        <f t="array" ref="M80">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L80, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P80" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="1:31">
+      <c r="A81" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D81" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="E81" t="str">
+        <f t="shared" si="84"/>
+        <v>5</v>
+      </c>
+      <c r="F81" t="str">
+        <f t="shared" si="85"/>
+        <v>Winkler_Bryant_2021</v>
+      </c>
+      <c r="G81" t="str">
+        <f t="shared" si="86"/>
+        <v>Winkler</v>
+      </c>
+      <c r="H81" t="str">
+        <f t="shared" si="87"/>
+        <v>Bryant</v>
+      </c>
+      <c r="I81" t="str">
+        <f t="shared" si="88"/>
+        <v>2021</v>
+      </c>
+      <c r="J81" t="str">
+        <f t="shared" si="99"/>
+        <v>10.1080/09524622.2021.1905065</v>
+      </c>
+      <c r="K81" t="str">
+        <f t="shared" si="89"/>
+        <v>Winkler_Bryant_2021_Figure1</v>
+      </c>
+      <c r="L81" t="str">
+        <f t="shared" si="90"/>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+      </c>
+      <c r="M81" t="str">
+        <f t="array" ref="M81">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L81, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P81" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="Q81" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R81" s="4"/>
+      <c r="T81" s="1" t="str">
+        <f>IF(S81="N", R81, "write file name")</f>
         <v>write file name</v>
       </c>
-      <c r="U78" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="V78" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="Y78" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="Z78" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AE78" s="1" t="s">
-        <v>81</v>
+      <c r="U81" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V81" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="Y81" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="AE81" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="82" spans="1:31">
+      <c r="A82" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E82" t="str">
+        <f t="shared" si="84"/>
+        <v>0</v>
+      </c>
+      <c r="F82" t="str">
+        <f t="shared" si="85"/>
+        <v>Young_etal_2013</v>
+      </c>
+      <c r="G82" t="str">
+        <f t="shared" si="86"/>
+        <v>Young</v>
+      </c>
+      <c r="H82" t="str">
+        <f t="shared" si="87"/>
+        <v>etal</v>
+      </c>
+      <c r="I82" t="str">
+        <f t="shared" si="88"/>
+        <v>2013</v>
+      </c>
+      <c r="J82" t="str">
+        <f t="shared" si="99"/>
+        <v>10.3389/fncir.2013.00030</v>
+      </c>
+      <c r="K82" t="str">
+        <f t="shared" si="89"/>
+        <v>Young_etal_2013_Table1</v>
+      </c>
+      <c r="L82" t="str">
+        <f t="shared" si="90"/>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+      </c>
+      <c r="M82" t="str">
+        <f t="array" ref="M82">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L82, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="P82" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="Q82" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="R82" s="4"/>
+      <c r="T82" s="1" t="str">
+        <f>IF(S82="N", R82, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U82" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="V82" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="Y82" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Z82" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE82" s="1" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="X10" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="X9" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="X12" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="X18" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="X24" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="X66" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="X69" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="X38" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="X29:X33" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="X61" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="X60" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="X57" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="X26" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="X27" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="X11" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="X10" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
+    <hyperlink ref="X13" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
+    <hyperlink ref="X19" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
+    <hyperlink ref="X25" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
+    <hyperlink ref="X70" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
+    <hyperlink ref="X73" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
+    <hyperlink ref="X41" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
+    <hyperlink ref="X30:X35" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
+    <hyperlink ref="X65" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
+    <hyperlink ref="X64" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
+    <hyperlink ref="X60" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
+    <hyperlink ref="X27" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
+    <hyperlink ref="X28" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6918,104 +7149,104 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" customWidth="1"/>
+    <col min="1" max="1" width="26.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="7" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B3" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="7" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="B4" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="7" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="B5" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" s="7" t="s">
-        <v>316</v>
+        <v>328</v>
       </c>
       <c r="B6" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" s="7" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="B7" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" s="7" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="B8" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" s="7" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="B9" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" s="7" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="B10" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" s="7" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="B11" t="s">
-        <v>327</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="17.100000000000001" customHeight="1">
       <c r="A12" s="9" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="B12" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" s="8" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
     </row>
   </sheetData>
@@ -7027,64 +7258,64 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <cols>
-    <col min="1" max="1" width="1.83203125" customWidth="1"/>
+    <col min="1" max="1" width="1.875" customWidth="1"/>
     <col min="2" max="2" width="126" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="C2" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="C3" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="C4" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="C5" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="C6" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -7096,311 +7327,311 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A61"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
       <c r="A9" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
       <c r="A10" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
       <c r="A11" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
       <c r="A12" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
       <c r="A13" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
       <c r="A14" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
       <c r="A15" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
       <c r="A16" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
   </sheetData>
@@ -7410,6 +7641,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
@@ -7418,15 +7658,6 @@
     <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7685,39 +7916,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
-    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10517"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="13_ncr:1_{D1DDFD38-8A94-4545-B3F0-CD27884E4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{693E0F28-B917-413C-835D-D3D9247F7C35}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{D1DDFD38-8A94-4545-B3F0-CD27884E4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F42699D6-E23D-4040-BEF7-F45B8BE07AC0}"/>
   <bookViews>
-    <workbookView xWindow="36220" yWindow="-5860" windowWidth="42680" windowHeight="26640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="660" windowWidth="34560" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="414">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -1288,7 +1288,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1432,9 +1432,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1472,7 +1472,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1578,7 +1578,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1720,7 +1720,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1729,40 +1729,40 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AH82"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="42.125" customWidth="1"/>
-    <col min="2" max="2" width="5.125" customWidth="1"/>
-    <col min="3" max="3" width="22.875" customWidth="1"/>
-    <col min="4" max="4" width="34.875" customWidth="1"/>
+    <col min="1" max="1" width="42.1640625" customWidth="1"/>
+    <col min="2" max="2" width="5.1640625" customWidth="1"/>
+    <col min="3" max="3" width="22.83203125" customWidth="1"/>
+    <col min="4" max="4" width="34.83203125" customWidth="1"/>
     <col min="5" max="5" width="2" customWidth="1"/>
-    <col min="6" max="6" width="23.625" customWidth="1"/>
-    <col min="7" max="7" width="16.875" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="5.125" customWidth="1"/>
+    <col min="9" max="9" width="5.1640625" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="31.125" customWidth="1"/>
+    <col min="11" max="11" width="31.1640625" customWidth="1"/>
     <col min="12" max="12" width="46.5" customWidth="1"/>
     <col min="13" max="13" width="21.5" customWidth="1"/>
-    <col min="14" max="14" width="15.375" customWidth="1"/>
+    <col min="14" max="14" width="15.33203125" customWidth="1"/>
     <col min="15" max="15" width="24" customWidth="1"/>
     <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="20" width="14.125" customWidth="1"/>
-    <col min="21" max="21" width="13.875" customWidth="1"/>
-    <col min="22" max="22" width="12.625" customWidth="1"/>
-    <col min="23" max="23" width="22.125" customWidth="1"/>
-    <col min="24" max="24" width="14.375" customWidth="1"/>
+    <col min="17" max="20" width="14.1640625" customWidth="1"/>
+    <col min="21" max="21" width="13.83203125" customWidth="1"/>
+    <col min="22" max="22" width="12.6640625" customWidth="1"/>
+    <col min="23" max="23" width="22.1640625" customWidth="1"/>
+    <col min="24" max="24" width="14.33203125" customWidth="1"/>
     <col min="25" max="25" width="39.5" customWidth="1"/>
-    <col min="26" max="26" width="11.125" customWidth="1"/>
+    <col min="26" max="26" width="11.1640625" customWidth="1"/>
     <col min="27" max="27" width="5" customWidth="1"/>
     <col min="28" max="28" width="7.5" customWidth="1"/>
-    <col min="29" max="29" width="10.625" customWidth="1"/>
-    <col min="30" max="30" width="10.875" customWidth="1"/>
+    <col min="29" max="29" width="10.6640625" customWidth="1"/>
+    <col min="30" max="30" width="10.83203125" customWidth="1"/>
     <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="34" width="10.875" customWidth="1"/>
+    <col min="32" max="34" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.95" customHeight="1">
+    <row r="1" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1866,11 +1866,13 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15.95" customHeight="1">
+    <row r="2" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D2" s="1"/>
+      <c r="D2" s="1" t="s">
+        <v>211</v>
+      </c>
       <c r="E2" t="str">
         <f t="shared" ref="E2" si="0">RIGHT(A2,1)</f>
         <v>5</v>
@@ -1900,11 +1902,11 @@
       </c>
       <c r="K2" t="str">
         <f t="shared" ref="K2" si="5">TRIM(_xlfn.TEXTJOIN("_",FALSE,F2,(SUBSTITUTE(SUBSTITUTE(D2," ",""), "_", ""))))</f>
-        <v>Andelin_etal_2019_</v>
+        <v>Andelin_etal_2019_Table4</v>
       </c>
       <c r="L2" t="str">
         <f t="shared" ref="L2" si="6">IF(ISBLANK(C2),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, J2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")),TRIM(SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTJOIN("_", FALSE, C2, SUBSTITUTE(D2,"_", "")), "/", "%2F"), ":", "%3A"), " ", "")))</f>
-        <v>10.1093%2Fcercor%2Fbhy315_</v>
+        <v>10.1093%2Fcercor%2Fbhy315_Table4</v>
       </c>
       <c r="M2" t="str">
         <f t="array" ref="M2">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L2, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
@@ -1916,7 +1918,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:34" ht="15.95" customHeight="1">
+    <row r="3" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>36</v>
       </c>
@@ -1972,7 +1974,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:34" ht="15.95" customHeight="1">
+    <row r="4" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>40</v>
       </c>
@@ -2031,7 +2033,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:34" ht="15.95" customHeight="1">
+    <row r="5" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>44</v>
       </c>
@@ -2090,7 +2092,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="15.95" customHeight="1">
+    <row r="6" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>46</v>
       </c>
@@ -2140,7 +2142,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="17.100000000000001" customHeight="1">
+    <row r="7" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>49</v>
       </c>
@@ -2224,7 +2226,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="17.100000000000001" customHeight="1">
+    <row r="8" spans="1:34" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>62</v>
       </c>
@@ -2286,7 +2288,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="15.95" customHeight="1">
+    <row r="9" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>62</v>
       </c>
@@ -2351,7 +2353,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="15.95" customHeight="1">
+    <row r="10" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
         <v>74</v>
       </c>
@@ -2435,7 +2437,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="15.95" customHeight="1">
+    <row r="11" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>74</v>
       </c>
@@ -2521,7 +2523,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="15.95" customHeight="1">
+    <row r="12" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>93</v>
       </c>
@@ -2598,7 +2600,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15.95" customHeight="1">
+    <row r="13" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>104</v>
       </c>
@@ -2685,7 +2687,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="15.95" customHeight="1">
+    <row r="14" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>112</v>
       </c>
@@ -2735,7 +2737,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="15.95" customHeight="1">
+    <row r="15" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>115</v>
       </c>
@@ -2806,7 +2808,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="15.95" customHeight="1">
+    <row r="16" spans="1:34" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>115</v>
       </c>
@@ -2877,7 +2879,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="15.95" customHeight="1">
+    <row r="17" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>115</v>
       </c>
@@ -2948,7 +2950,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="15.95" customHeight="1">
+    <row r="18" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>115</v>
       </c>
@@ -3019,7 +3021,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="15.95" customHeight="1">
+    <row r="19" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>128</v>
       </c>
@@ -3111,7 +3113,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="15.95" customHeight="1">
+    <row r="20" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>140</v>
       </c>
@@ -3191,7 +3193,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="15.95" customHeight="1">
+    <row r="21" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>140</v>
       </c>
@@ -3274,7 +3276,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="15.95" customHeight="1">
+    <row r="22" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
         <v>147</v>
       </c>
@@ -3334,7 +3336,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="15.95" customHeight="1">
+    <row r="23" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
         <v>150</v>
       </c>
@@ -3388,7 +3390,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="15.95" customHeight="1">
+    <row r="24" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>150</v>
       </c>
@@ -3445,7 +3447,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="25" spans="1:32" ht="15.95" customHeight="1">
+    <row r="25" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>154</v>
       </c>
@@ -3529,7 +3531,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="15.95" customHeight="1">
+    <row r="26" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>160</v>
       </c>
@@ -3585,7 +3587,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="27" spans="1:32" ht="15" customHeight="1">
+    <row r="27" spans="1:32" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>164</v>
       </c>
@@ -3641,7 +3643,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="15.95" customHeight="1">
+    <row r="28" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>164</v>
       </c>
@@ -3697,7 +3699,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="29" spans="1:32" ht="15.95" customHeight="1">
+    <row r="29" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
         <v>169</v>
       </c>
@@ -3750,7 +3752,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="30" spans="1:32" ht="15.95" customHeight="1">
+    <row r="30" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>172</v>
       </c>
@@ -3800,7 +3802,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:32" ht="15.95" customHeight="1">
+    <row r="31" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>174</v>
       </c>
@@ -3847,7 +3849,7 @@
       <c r="N31" s="10"/>
       <c r="P31" s="1"/>
     </row>
-    <row r="32" spans="1:32" ht="15.95" customHeight="1">
+    <row r="32" spans="1:32" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>175</v>
       </c>
@@ -3927,7 +3929,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="15.95" customHeight="1">
+    <row r="33" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>182</v>
       </c>
@@ -4000,7 +4002,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="15.95" customHeight="1">
+    <row r="34" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
         <v>184</v>
       </c>
@@ -4065,7 +4067,7 @@
       <c r="AE34" s="1"/>
       <c r="AG34" s="10"/>
     </row>
-    <row r="35" spans="1:33" ht="15.95" customHeight="1">
+    <row r="35" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="1" t="s">
         <v>188</v>
       </c>
@@ -4132,7 +4134,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="15.95" customHeight="1">
+    <row r="36" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>190</v>
       </c>
@@ -4186,7 +4188,7 @@
       <c r="Y36" s="10"/>
       <c r="Z36" s="10"/>
     </row>
-    <row r="37" spans="1:33" ht="15.95" customHeight="1">
+    <row r="37" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>190</v>
       </c>
@@ -4249,7 +4251,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:33" ht="15.95" customHeight="1">
+    <row r="38" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>194</v>
       </c>
@@ -4296,7 +4298,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="18.95" customHeight="1">
+    <row r="39" spans="1:33" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>194</v>
       </c>
@@ -4343,7 +4345,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="40" spans="1:33" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>194</v>
       </c>
@@ -4390,7 +4392,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="41" spans="1:33" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>198</v>
       </c>
@@ -4476,7 +4478,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="42" spans="1:33" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>198</v>
       </c>
@@ -4562,7 +4564,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="43" spans="1:33" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>198</v>
       </c>
@@ -4648,7 +4650,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="15.95" customHeight="1">
+    <row r="44" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>198</v>
       </c>
@@ -4734,7 +4736,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="15.95" customHeight="1">
+    <row r="45" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>198</v>
       </c>
@@ -4820,7 +4822,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="15.95" customHeight="1">
+    <row r="46" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>219</v>
       </c>
@@ -4903,7 +4905,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="15.95" customHeight="1">
+    <row r="47" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>219</v>
       </c>
@@ -4986,7 +4988,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="15.95" customHeight="1">
+    <row r="48" spans="1:33" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>229</v>
       </c>
@@ -5033,7 +5035,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="15.95" customHeight="1">
+    <row r="49" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>229</v>
       </c>
@@ -5080,7 +5082,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="15.95" customHeight="1">
+    <row r="50" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>229</v>
       </c>
@@ -5130,7 +5132,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="15.95" customHeight="1">
+    <row r="51" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>229</v>
       </c>
@@ -5177,7 +5179,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="15.95" customHeight="1">
+    <row r="52" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>229</v>
       </c>
@@ -5224,7 +5226,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="15.95" customHeight="1">
+    <row r="53" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>229</v>
       </c>
@@ -5271,7 +5273,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="15.95" customHeight="1">
+    <row r="54" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>233</v>
       </c>
@@ -5327,7 +5329,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="15.95" customHeight="1">
+    <row r="55" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>233</v>
       </c>
@@ -5383,7 +5385,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="15.95" customHeight="1">
+    <row r="56" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>237</v>
       </c>
@@ -5453,7 +5455,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="15.95" customHeight="1">
+    <row r="57" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>237</v>
       </c>
@@ -5523,7 +5525,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="15.95" customHeight="1">
+    <row r="58" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>237</v>
       </c>
@@ -5593,7 +5595,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="15.95" customHeight="1">
+    <row r="59" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>237</v>
       </c>
@@ -5663,7 +5665,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="15.95" customHeight="1">
+    <row r="60" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>245</v>
       </c>
@@ -5752,7 +5754,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="15.95" customHeight="1">
+    <row r="61" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>251</v>
       </c>
@@ -5818,7 +5820,7 @@
       <c r="AB61" s="10"/>
       <c r="AE61" s="10"/>
     </row>
-    <row r="62" spans="1:31" ht="15.95" customHeight="1">
+    <row r="62" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>254</v>
       </c>
@@ -5881,7 +5883,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="63" spans="1:31" ht="15.95" customHeight="1">
+    <row r="63" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>257</v>
       </c>
@@ -5961,7 +5963,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="15.95" customHeight="1">
+    <row r="64" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>257</v>
       </c>
@@ -6047,7 +6049,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="15.95" customHeight="1">
+    <row r="65" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>257</v>
       </c>
@@ -6133,7 +6135,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="15.95" customHeight="1">
+    <row r="66" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>273</v>
       </c>
@@ -6183,7 +6185,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="15.95" customHeight="1">
+    <row r="67" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>276</v>
       </c>
@@ -6236,7 +6238,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="15.95" customHeight="1">
+    <row r="68" spans="1:31" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>276</v>
       </c>
@@ -6289,7 +6291,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="15.75" customHeight="1">
+    <row r="69" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>280</v>
       </c>
@@ -6339,7 +6341,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="15.75" customHeight="1">
+    <row r="70" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>282</v>
       </c>
@@ -6418,7 +6420,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="15.75" customHeight="1">
+    <row r="71" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>288</v>
       </c>
@@ -6465,7 +6467,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="15.75" customHeight="1">
+    <row r="72" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>289</v>
       </c>
@@ -6518,7 +6520,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="15.75" customHeight="1">
+    <row r="73" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>293</v>
       </c>
@@ -6600,7 +6602,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="15.75" customHeight="1">
+    <row r="74" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>298</v>
       </c>
@@ -6676,7 +6678,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="15.75" customHeight="1">
+    <row r="75" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>298</v>
       </c>
@@ -6752,7 +6754,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="15.75" customHeight="1">
+    <row r="76" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>304</v>
       </c>
@@ -6799,7 +6801,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="15.75" customHeight="1">
+    <row r="77" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>304</v>
       </c>
@@ -6846,7 +6848,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="15.75" customHeight="1">
+    <row r="78" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>307</v>
       </c>
@@ -6896,7 +6898,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="15.75" customHeight="1">
+    <row r="79" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>310</v>
       </c>
@@ -6940,7 +6942,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="15.75" customHeight="1">
+    <row r="80" spans="1:31" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>312</v>
       </c>
@@ -6987,7 +6989,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="81" spans="1:31">
+    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>314</v>
       </c>
@@ -7054,7 +7056,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="82" spans="1:31">
+    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>318</v>
       </c>
@@ -7149,22 +7151,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="26.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>321</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="7" t="s">
         <v>322</v>
       </c>
@@ -7172,7 +7174,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="7" t="s">
         <v>324</v>
       </c>
@@ -7180,7 +7182,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
         <v>326</v>
       </c>
@@ -7188,7 +7190,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="7" t="s">
         <v>328</v>
       </c>
@@ -7196,7 +7198,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="7" t="s">
         <v>330</v>
       </c>
@@ -7204,7 +7206,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="7" t="s">
         <v>332</v>
       </c>
@@ -7212,7 +7214,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>334</v>
       </c>
@@ -7220,7 +7222,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="7" t="s">
         <v>336</v>
       </c>
@@ -7228,7 +7230,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="7" t="s">
         <v>338</v>
       </c>
@@ -7236,7 +7238,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17.100000000000001" customHeight="1">
+    <row r="12" spans="1:2" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>340</v>
       </c>
@@ -7244,7 +7246,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
         <v>342</v>
       </c>
@@ -7258,23 +7260,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.875" customWidth="1"/>
+    <col min="1" max="1" width="1.83203125" customWidth="1"/>
     <col min="2" max="2" width="126" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="C2" t="s">
         <v>344</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>1</v>
       </c>
@@ -7285,7 +7287,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>2</v>
       </c>
@@ -7296,7 +7298,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>3</v>
       </c>
@@ -7307,7 +7309,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>4</v>
       </c>
@@ -7327,309 +7329,309 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>354</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>355</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>356</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>357</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>358</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>360</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>363</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>364</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>368</v>
       </c>
     </row>
-    <row r="17" spans="1:1">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>369</v>
       </c>
     </row>
-    <row r="18" spans="1:1">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="19" spans="1:1">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>371</v>
       </c>
     </row>
-    <row r="20" spans="1:1">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>372</v>
       </c>
     </row>
-    <row r="21" spans="1:1">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>373</v>
       </c>
     </row>
-    <row r="22" spans="1:1">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="23" spans="1:1">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>375</v>
       </c>
     </row>
-    <row r="24" spans="1:1">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>376</v>
       </c>
     </row>
-    <row r="25" spans="1:1">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>377</v>
       </c>
     </row>
-    <row r="26" spans="1:1">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="27" spans="1:1">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>379</v>
       </c>
     </row>
-    <row r="28" spans="1:1">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>380</v>
       </c>
     </row>
-    <row r="29" spans="1:1">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="30" spans="1:1">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>382</v>
       </c>
     </row>
-    <row r="31" spans="1:1">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>383</v>
       </c>
     </row>
-    <row r="32" spans="1:1">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="33" spans="1:1">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>385</v>
       </c>
     </row>
-    <row r="34" spans="1:1">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="35" spans="1:1">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="36" spans="1:1">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>388</v>
       </c>
     </row>
-    <row r="37" spans="1:1">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="38" spans="1:1">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>390</v>
       </c>
     </row>
-    <row r="39" spans="1:1">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="40" spans="1:1">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>392</v>
       </c>
     </row>
-    <row r="41" spans="1:1">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>393</v>
       </c>
     </row>
-    <row r="42" spans="1:1">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="43" spans="1:1">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>395</v>
       </c>
     </row>
-    <row r="44" spans="1:1">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="45" spans="1:1">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="46" spans="1:1">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>398</v>
       </c>
     </row>
-    <row r="47" spans="1:1">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>399</v>
       </c>
     </row>
-    <row r="48" spans="1:1">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>400</v>
       </c>
     </row>
-    <row r="49" spans="1:1">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>401</v>
       </c>
     </row>
-    <row r="50" spans="1:1">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="51" spans="1:1">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>403</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="53" spans="1:1">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="54" spans="1:1">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="55" spans="1:1">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>407</v>
       </c>
     </row>
-    <row r="56" spans="1:1">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>408</v>
       </c>
     </row>
-    <row r="57" spans="1:1">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>409</v>
       </c>
     </row>
-    <row r="58" spans="1:1">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>410</v>
       </c>
     </row>
-    <row r="59" spans="1:1">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="60" spans="1:1">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="61" spans="1:1">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>413</v>
       </c>
@@ -7641,26 +7643,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009B0162F312A93D41AE706303C1572F17" ma:contentTypeVersion="18" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="3dd70bd28c77d4108edb5ca6812bb84f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="8e1efd23-f4ba-42d2-85fd-6a510437bae6" xmlns:ns3="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="4cd59d6f2988212fc297a6d404d3fed4" ns2:_="" ns3:_="">
     <xsd:import namespace="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
@@ -7915,14 +7897,66 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="8e1efd23-f4ba-42d2-85fd-6a510437bae6">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="3bad6c6a-329d-45e9-b8b0-1ebecc8a8764"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="8e1efd23-f4ba-42d2-85fd-6a510437bae6"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,45 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30125"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{D1DDFD38-8A94-4545-B3F0-CD27884E4A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA981651-3638-4A6B-8CAB-97603806A668}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="660" windowWidth="34560" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="660" windowWidth="34560" windowHeight="20460" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Pipeline" sheetId="3" r:id="rId2"/>
-    <sheet name="Conflicts" sheetId="4" r:id="rId3"/>
-    <sheet name="FileList" sheetId="5" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pipeline" sheetId="3" state="visible" r:id="rId2"/>
+    <sheet name="Conflicts" sheetId="4" state="visible" r:id="rId3"/>
+    <sheet name="FileList" sheetId="5" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="805" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="481">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -1288,12 +1265,208 @@
   </si>
   <si>
     <t>README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Files</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0000%2Fplaceholder.1_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24605_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24605_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24985_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24985_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.25669_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.70089_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1006%2Fjhev.1996.0005_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007%2Fs004220000205_Figure3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_Tree.nex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037%2F0735-7036.115.1.29_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037%2F0735-7036.115.1.29_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037%2F0735-7036.115.1.29_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037%2F0735-7036.115.1.29_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_TableS5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1073%2Fpnas.0905777106_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fjmammal%2Fgyz043.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frspb.2015.1853_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1126%2Fscience.aaa9101_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000124401_TableI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000319019_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000319019_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000323671_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000323671_SupplementaryTable2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000323671.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000452856_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pbio.1002000_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pbio.1002000_TableS8.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pbio.1002000_TableS8.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523%2FJNEUROSCI.2339-19.2020_unpublished.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%25Ffnana.2013.00035.svg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Figure2TopLeft.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Table1-a.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Table1-b.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2017.00118_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnhum.2013.00424.ReadMe.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnins.2021.632853_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554%2FeLife.77875_Supplementaryfile3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554%2FeLife.77875_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">README.md</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WOS%3A000225086000011_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andelin_etal_2019_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fcercor%2Fbhy315_Table4.tsv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="7">
     <font>
       <sz val="12"/>
@@ -1306,45 +1479,34 @@
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <b/>
     </font>
     <font>
-      <i/>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <b/>
+    </font>
+    <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <i/>
     </font>
   </fonts>
   <fills count="3">
@@ -1381,7 +1543,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -1390,39 +1551,33 @@
       <right style="thin">
         <color rgb="FF7F7F7F"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Input" xfId="1" builtinId="20"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1734,146 +1889,151 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AH83"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="42.125" customWidth="1"/>
-    <col min="2" max="2" width="5.125" customWidth="1"/>
-    <col min="3" max="3" width="22.875" customWidth="1"/>
-    <col min="4" max="4" width="34.875" customWidth="1"/>
-    <col min="5" max="5" width="2" customWidth="1"/>
-    <col min="6" max="6" width="23.625" customWidth="1"/>
-    <col min="7" max="7" width="16.875" customWidth="1"/>
-    <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="9" max="9" width="5.125" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
-    <col min="11" max="11" width="31.125" customWidth="1"/>
-    <col min="12" max="12" width="46.5" customWidth="1"/>
-    <col min="13" max="13" width="21.5" customWidth="1"/>
-    <col min="14" max="14" width="15.375" customWidth="1"/>
-    <col min="15" max="15" width="24" customWidth="1"/>
-    <col min="16" max="16" width="10" customWidth="1"/>
-    <col min="17" max="20" width="14.125" customWidth="1"/>
-    <col min="21" max="21" width="13.875" customWidth="1"/>
-    <col min="22" max="22" width="12.625" customWidth="1"/>
-    <col min="23" max="23" width="22.125" customWidth="1"/>
-    <col min="24" max="24" width="14.375" customWidth="1"/>
-    <col min="25" max="25" width="39.5" customWidth="1"/>
-    <col min="26" max="26" width="11.125" customWidth="1"/>
-    <col min="27" max="27" width="5" customWidth="1"/>
-    <col min="28" max="28" width="7.5" customWidth="1"/>
-    <col min="29" max="29" width="10.625" customWidth="1"/>
-    <col min="30" max="30" width="10.875" customWidth="1"/>
-    <col min="31" max="31" width="11" customWidth="1"/>
-    <col min="32" max="34" width="10.875" customWidth="1"/>
+    <col min="1" max="1" width="42.125" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="5.125" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="22.875" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="34.875" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="2" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="23.625" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="16.875" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="15" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="5.125" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="12" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="31.125" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="46.5" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="21.5" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="15.375" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="24" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="10" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="14.125" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="14.125" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="14.125" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="14.125" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="13.875" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="12.625" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="22.125" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="14.375" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="39.5" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="11.125" hidden="0" customWidth="1"/>
+    <col min="27" max="27" width="5" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="7.5" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="10.625" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="10.875" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="11" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="10.875" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="10.875" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="10.875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:34" ht="15.95" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" ht="15.95" customHeight="1">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="O1" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="P1" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="6" t="s">
+      <c r="Q1" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="6" t="s">
+      <c r="R1" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="6" t="s">
+      <c r="S1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="6" t="s">
+      <c r="T1" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="6" t="s">
+      <c r="U1" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="6" t="s">
+      <c r="V1" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="W1" s="6" t="s">
+      <c r="W1" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="6" t="s">
+      <c r="X1" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="6" t="s">
+      <c r="Y1" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="AA1" s="6" t="s">
+      <c r="AA1" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" s="6" t="s">
+      <c r="AB1" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="AC1" s="6" t="s">
+      <c r="AC1" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="6" t="s">
+      <c r="AD1" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="AE1" s="6" t="s">
+      <c r="AE1" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" s="6" t="s">
+      <c r="AF1" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="AG1" s="6" t="s">
+      <c r="AG1" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="AH1" s="6" t="s">
+      <c r="AH1" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:34" ht="15.95" customHeight="1">
+    <row r="2" ht="15.95" customHeight="1">
       <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
@@ -1925,7 +2085,7 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
     </row>
-    <row r="3" spans="1:34" ht="15.95" customHeight="1">
+    <row r="3" ht="15.95" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>37</v>
       </c>
@@ -1971,17 +2131,77 @@
         <f t="array" ref="M3">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L3, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1002%2Fcne.70089_TABLE1.tsv</v>
       </c>
+      <c r="N3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;Table 1. Cellular composition of the brain of a Northern minke whale (Balaenoptera acutorostrata)</t>
+        </is>
+      </c>
+      <c r="P3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;FINISHED</t>
+        </is>
+      </c>
+      <c r="Q3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;added</t>
+        </is>
+      </c>
+      <c r="R3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;AvelinodeSouza_etal_2025_TABLE1_snapshot.csv</t>
+        </is>
+      </c>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;Y</t>
+        </is>
+      </c>
+      <c r="T3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;AvelinodeSouza_etal_2025_TABLE1.csv</t>
+        </is>
+      </c>
+      <c r="U3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;pdf</t>
+        </is>
+      </c>
       <c r="V3" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="W3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;https://onlinelibrary.wiley.com/doi/10.1002/cne.70089</t>
+        </is>
+      </c>
+      <c r="X3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;https://doi.org/10.1002/cne.70089</t>
+        </is>
+      </c>
       <c r="Y3" s="1" t="s">
         <v>39</v>
       </c>
       <c r="Z3" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:34" ht="15.95" customHeight="1">
+      <c r="AA3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;HH</t>
+        </is>
+      </c>
+      <c r="AB3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;HH</t>
+        </is>
+      </c>
+      <c r="AE3" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;placental mammals</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="15.95" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>41</v>
       </c>
@@ -2028,10 +2248,10 @@
         <v>notfound</v>
       </c>
       <c r="V4" s="1"/>
-      <c r="Y4" s="13"/>
+      <c r="Y4" s="2"/>
       <c r="Z4" s="1"/>
     </row>
-    <row r="5" spans="1:34" ht="15.95" customHeight="1">
+    <row r="5" ht="15.95" customHeight="1">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
@@ -2090,7 +2310,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:34" ht="15.95" customHeight="1">
+    <row r="6" ht="15.95" customHeight="1">
       <c r="A6" s="1" t="s">
         <v>47</v>
       </c>
@@ -2149,7 +2369,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="7" spans="1:34" ht="15.95" customHeight="1">
+    <row r="7" ht="15.95" customHeight="1">
       <c r="A7" s="1" t="s">
         <v>49</v>
       </c>
@@ -2176,7 +2396,6 @@
     IF(LEN(A7)-LEN(SUBSTITUTE(A7, ",", ""))&gt;=6, "etal", MID(A7, SEARCH("&amp; ", A7)+2, SEARCH(",", A7, SEARCH("&amp; ", A7)+2) - SEARCH("&amp; ", A7)-2)),
     ""
 )</f>
-        <v/>
       </c>
       <c r="I7" t="str">
         <f t="shared" ref="I7:I50" si="35">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A7, "("), ")")</f>
@@ -2199,7 +2418,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="8" spans="1:34" ht="17.100000000000001" customHeight="1">
+    <row r="8" ht="17.100000000000001" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>52</v>
       </c>
@@ -2283,7 +2502,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:34" ht="17.100000000000001" customHeight="1">
+    <row r="9" ht="17.100000000000001" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>65</v>
       </c>
@@ -2345,7 +2564,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:34" ht="15.95" customHeight="1">
+    <row r="10" ht="15.95" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>65</v>
       </c>
@@ -2400,6 +2619,26 @@
       <c r="R10" s="1" t="s">
         <v>75</v>
       </c>
+      <c r="T10" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;Burish_etal_2010_Table1.csv</t>
+        </is>
+      </c>
+      <c r="U10" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;pdf</t>
+        </is>
+      </c>
+      <c r="V10" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;table</t>
+        </is>
+      </c>
+      <c r="X10" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;https://doi.org/10.1159/000319019</t>
+        </is>
+      </c>
       <c r="Z10" s="1" t="s">
         <v>76</v>
       </c>
@@ -2410,7 +2649,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="11" spans="1:34" ht="15.95" customHeight="1">
+    <row r="11" ht="15.95" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>77</v>
       </c>
@@ -2494,7 +2733,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="12" spans="1:34" ht="15.95" customHeight="1">
+    <row r="12" ht="15.95" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>77</v>
       </c>
@@ -2580,7 +2819,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="13" spans="1:34" ht="15.95" customHeight="1">
+    <row r="13" ht="15.95" customHeight="1">
       <c r="A13" s="1" t="s">
         <v>96</v>
       </c>
@@ -2601,7 +2840,6 @@
       </c>
       <c r="H13" t="str">
         <f t="shared" si="34"/>
-        <v/>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="35"/>
@@ -2657,7 +2895,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="14" spans="1:34" ht="15.95" customHeight="1">
+    <row r="14" ht="15.95" customHeight="1">
       <c r="A14" s="1" t="s">
         <v>107</v>
       </c>
@@ -2744,7 +2982,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="1:34" ht="15.95" customHeight="1">
+    <row r="15" ht="15.95" customHeight="1">
       <c r="A15" s="1" t="s">
         <v>115</v>
       </c>
@@ -2794,7 +3032,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:34" ht="15.95" customHeight="1">
+    <row r="16" ht="15.95" customHeight="1">
       <c r="A16" s="1" t="s">
         <v>118</v>
       </c>
@@ -2865,7 +3103,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="17" spans="1:32" ht="15.95" customHeight="1">
+    <row r="17" ht="15.95" customHeight="1">
       <c r="A17" s="1" t="s">
         <v>118</v>
       </c>
@@ -2936,7 +3174,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="18" spans="1:32" ht="15.95" customHeight="1">
+    <row r="18" ht="15.95" customHeight="1">
       <c r="A18" s="1" t="s">
         <v>118</v>
       </c>
@@ -3007,7 +3245,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="19" spans="1:32" ht="15.95" customHeight="1">
+    <row r="19" ht="15.95" customHeight="1">
       <c r="A19" s="1" t="s">
         <v>118</v>
       </c>
@@ -3078,7 +3316,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="20" spans="1:32" ht="15.95" customHeight="1">
+    <row r="20" ht="15.95" customHeight="1">
       <c r="A20" s="1" t="s">
         <v>131</v>
       </c>
@@ -3170,7 +3408,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="21" spans="1:32" ht="15.95" customHeight="1">
+    <row r="21" ht="15.95" customHeight="1">
       <c r="A21" s="1" t="s">
         <v>143</v>
       </c>
@@ -3219,7 +3457,7 @@
       <c r="Q21" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R21" s="4" t="s">
+      <c r="R21" s="7" t="s">
         <v>144</v>
       </c>
       <c r="S21" s="1" t="s">
@@ -3250,7 +3488,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="22" spans="1:32" ht="15.95" customHeight="1">
+    <row r="22" ht="15.95" customHeight="1">
       <c r="A22" s="1" t="s">
         <v>143</v>
       </c>
@@ -3302,7 +3540,7 @@
       <c r="Q22" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R22" s="4" t="s">
+      <c r="R22" s="7" t="s">
         <v>144</v>
       </c>
       <c r="S22" s="1" t="s">
@@ -3317,6 +3555,11 @@
       <c r="V22" s="1" t="s">
         <v>36</v>
       </c>
+      <c r="X22" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;https://doi.org/10.1523/JNEUROSCI.2339-19.2020</t>
+        </is>
+      </c>
       <c r="Y22" s="1" t="s">
         <v>139</v>
       </c>
@@ -3333,8 +3576,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="23" spans="1:32" ht="15.95" customHeight="1">
-      <c r="A23" s="3" t="s">
+    <row r="23" ht="15.95" customHeight="1">
+      <c r="A23" s="6" t="s">
         <v>150</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -3382,18 +3625,18 @@
       <c r="N23" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="R23" s="4"/>
+      <c r="R23" s="7"/>
       <c r="U23" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="Y23" s="11" t="s">
+      <c r="Y23" s="3" t="s">
         <v>152</v>
       </c>
       <c r="Z23" s="1" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:32" ht="15.95" customHeight="1">
+    <row r="24" ht="15.95" customHeight="1">
       <c r="A24" s="1" t="s">
         <v>153</v>
       </c>
@@ -3439,7 +3682,7 @@
       <c r="N24" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="R24" s="4"/>
+      <c r="R24" s="7"/>
       <c r="U24" s="1" t="s">
         <v>90</v>
       </c>
@@ -3447,7 +3690,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="25" spans="1:32" ht="15.95" customHeight="1">
+    <row r="25" ht="15.95" customHeight="1">
       <c r="A25" s="1" t="s">
         <v>153</v>
       </c>
@@ -3496,7 +3739,7 @@
       <c r="N25" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="R25" s="4"/>
+      <c r="R25" s="7"/>
       <c r="U25" s="1" t="s">
         <v>90</v>
       </c>
@@ -3504,7 +3747,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="26" spans="1:32" ht="15.95" customHeight="1">
+    <row r="26" ht="15.95" customHeight="1">
       <c r="A26" s="1" t="s">
         <v>157</v>
       </c>
@@ -3547,7 +3790,7 @@
         <f t="array" ref="M26">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L26, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</v>
       </c>
-      <c r="N26" s="5"/>
+      <c r="N26" s="8"/>
       <c r="P26" s="1" t="s">
         <v>98</v>
       </c>
@@ -3588,7 +3831,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:32" ht="15.95" customHeight="1">
+    <row r="27" ht="15.95" customHeight="1">
       <c r="A27" s="1" t="s">
         <v>163</v>
       </c>
@@ -3644,7 +3887,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:32" ht="15" customHeight="1">
+    <row r="28" ht="15" customHeight="1">
       <c r="A28" s="1" t="s">
         <v>167</v>
       </c>
@@ -3700,7 +3943,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="29" spans="1:32" ht="15.95" customHeight="1">
+    <row r="29" ht="15.95" customHeight="1">
       <c r="A29" s="1" t="s">
         <v>167</v>
       </c>
@@ -3756,7 +3999,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="30" spans="1:32" ht="15.95" customHeight="1">
+    <row r="30" ht="15.95" customHeight="1">
       <c r="A30" s="1" t="s">
         <v>172</v>
       </c>
@@ -3809,7 +4052,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="31" spans="1:32" ht="15.95" customHeight="1">
+    <row r="31" ht="15.95" customHeight="1">
       <c r="A31" s="1" t="s">
         <v>175</v>
       </c>
@@ -3830,7 +4073,6 @@
       </c>
       <c r="H31" t="str">
         <f t="shared" si="34"/>
-        <v/>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="35"/>
@@ -3859,7 +4101,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="32" spans="1:32" ht="15.95" customHeight="1">
+    <row r="32" ht="15.95" customHeight="1">
       <c r="A32" s="1" t="s">
         <v>177</v>
       </c>
@@ -3903,10 +4145,10 @@
         <f t="array" ref="M32">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L32, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N32" s="10"/>
+      <c r="N32" s="2"/>
       <c r="P32" s="1"/>
     </row>
-    <row r="33" spans="1:33" ht="15.95" customHeight="1">
+    <row r="33" ht="15.95" customHeight="1">
       <c r="A33" s="1" t="s">
         <v>178</v>
       </c>
@@ -3986,7 +4228,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="15.95" customHeight="1">
+    <row r="34" ht="15.95" customHeight="1">
       <c r="A34" s="1" t="s">
         <v>185</v>
       </c>
@@ -4035,7 +4277,7 @@
       <c r="Q34" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R34" s="4"/>
+      <c r="R34" s="7"/>
       <c r="T34" s="1" t="str">
         <f>IF(S34="N", R34, "write file name")</f>
         <v>write file name</v>
@@ -4059,11 +4301,11 @@
         <v>186</v>
       </c>
     </row>
-    <row r="35" spans="1:33" ht="15.95" customHeight="1">
+    <row r="35" ht="15.95" customHeight="1">
       <c r="A35" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="C35" s="12" t="s">
+      <c r="C35" s="4" t="s">
         <v>188</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -4108,23 +4350,23 @@
         <f t="array" ref="M35">IFERROR(INDEX(FileList!$A$1:$A$100, MATCH(L35, _xlfn.TEXTBEFORE(FileList!$A$1:$A$100, ".tsv"), 0)), "notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N35" s="10" t="s">
+      <c r="N35" s="2" t="s">
         <v>189</v>
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1"/>
-      <c r="R35" s="4"/>
+      <c r="R35" s="7"/>
       <c r="T35" s="1"/>
       <c r="U35" s="1"/>
       <c r="V35" s="1"/>
-      <c r="W35" s="10"/>
+      <c r="W35" s="2"/>
       <c r="Y35" s="1" t="s">
         <v>190</v>
       </c>
       <c r="AE35" s="1"/>
-      <c r="AG35" s="10"/>
-    </row>
-    <row r="36" spans="1:33" ht="15.95" customHeight="1">
+      <c r="AG35" s="2"/>
+    </row>
+    <row r="36" ht="15.95" customHeight="1">
       <c r="A36" s="1" t="s">
         <v>191</v>
       </c>
@@ -4173,7 +4415,7 @@
       <c r="Q36" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R36" s="4"/>
+      <c r="R36" s="7"/>
       <c r="T36" s="1" t="str">
         <f>IF(S36="N", R36, "write file name")</f>
         <v>write file name</v>
@@ -4191,7 +4433,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:33" ht="15.95" customHeight="1">
+    <row r="37" ht="15.95" customHeight="1">
       <c r="A37" s="1" t="s">
         <v>193</v>
       </c>
@@ -4212,7 +4454,6 @@
       </c>
       <c r="H37" t="str">
         <f t="shared" si="34"/>
-        <v/>
       </c>
       <c r="I37" t="str">
         <f t="shared" si="35"/>
@@ -4235,17 +4476,17 @@
         <v>10.1098%2Frspb.2015.1853_Table1.tsv</v>
       </c>
       <c r="N37" s="1"/>
-      <c r="R37" s="4"/>
-      <c r="U37" s="10" t="s">
+      <c r="R37" s="7"/>
+      <c r="U37" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="V37" s="10" t="s">
+      <c r="V37" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y37" s="10"/>
-      <c r="Z37" s="10"/>
-    </row>
-    <row r="38" spans="1:33" ht="15.95" customHeight="1">
+      <c r="Y37" s="2"/>
+      <c r="Z37" s="2"/>
+    </row>
+    <row r="38" ht="15.95" customHeight="1">
       <c r="A38" s="1" t="s">
         <v>193</v>
       </c>
@@ -4269,7 +4510,6 @@
     IF(LEN(A38)-LEN(SUBSTITUTE(A38, ",", ""))&gt;=6, "etal", MID(A38, SEARCH("&amp; ", A38)+2, SEARCH(",", A38, SEARCH("&amp; ", A38)+2) - SEARCH("&amp; ", A38)-2)),
     ""
 )</f>
-        <v/>
       </c>
       <c r="I38" t="str">
         <f t="shared" ref="I38" si="90">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A38, "("), ")")</f>
@@ -4294,21 +4534,21 @@
       <c r="N38" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="R38" s="4"/>
-      <c r="U38" s="10" t="s">
+      <c r="R38" s="7"/>
+      <c r="U38" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="V38" s="10" t="s">
+      <c r="V38" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="Y38" s="10" t="s">
+      <c r="Y38" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="Z38" s="10" t="s">
+      <c r="Z38" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="39" spans="1:33" ht="15.95" customHeight="1">
+    <row r="39" ht="15.95" customHeight="1">
       <c r="A39" s="1" t="s">
         <v>197</v>
       </c>
@@ -4355,7 +4595,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="40" spans="1:33" ht="18.95" customHeight="1">
+    <row r="40" ht="18.95" customHeight="1">
       <c r="A40" s="1" t="s">
         <v>197</v>
       </c>
@@ -4402,7 +4642,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="41" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="41" ht="17.100000000000001" customHeight="1">
       <c r="A41" s="1" t="s">
         <v>197</v>
       </c>
@@ -4449,7 +4689,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="42" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="42" ht="17.100000000000001" customHeight="1">
       <c r="A42" s="1" t="s">
         <v>201</v>
       </c>
@@ -4501,7 +4741,7 @@
       <c r="Q42" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R42" s="4" t="s">
+      <c r="R42" s="7" t="s">
         <v>203</v>
       </c>
       <c r="S42" s="1" t="s">
@@ -4535,7 +4775,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="43" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="43" ht="17.100000000000001" customHeight="1">
       <c r="A43" s="1" t="s">
         <v>201</v>
       </c>
@@ -4587,7 +4827,7 @@
       <c r="Q43" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R43" s="4" t="s">
+      <c r="R43" s="7" t="s">
         <v>208</v>
       </c>
       <c r="S43" s="1" t="s">
@@ -4621,7 +4861,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="44" spans="1:33" ht="17.100000000000001" customHeight="1">
+    <row r="44" ht="17.100000000000001" customHeight="1">
       <c r="A44" s="1" t="s">
         <v>201</v>
       </c>
@@ -4673,7 +4913,7 @@
       <c r="Q44" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R44" s="4" t="s">
+      <c r="R44" s="7" t="s">
         <v>212</v>
       </c>
       <c r="S44" s="1" t="s">
@@ -4707,7 +4947,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="45" spans="1:33" ht="15.95" customHeight="1">
+    <row r="45" ht="15.95" customHeight="1">
       <c r="A45" s="1" t="s">
         <v>201</v>
       </c>
@@ -4759,7 +4999,7 @@
       <c r="Q45" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R45" s="4" t="s">
+      <c r="R45" s="7" t="s">
         <v>215</v>
       </c>
       <c r="S45" s="1" t="s">
@@ -4793,7 +5033,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="15.95" customHeight="1">
+    <row r="46" ht="15.95" customHeight="1">
       <c r="A46" s="1" t="s">
         <v>201</v>
       </c>
@@ -4845,7 +5085,7 @@
       <c r="Q46" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R46" s="4" t="s">
+      <c r="R46" s="7" t="s">
         <v>219</v>
       </c>
       <c r="S46" s="1" t="s">
@@ -4879,7 +5119,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="15.95" customHeight="1">
+    <row r="47" ht="15.95" customHeight="1">
       <c r="A47" s="1" t="s">
         <v>221</v>
       </c>
@@ -4931,7 +5171,7 @@
       <c r="Q47" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R47" s="4" t="s">
+      <c r="R47" s="7" t="s">
         <v>223</v>
       </c>
       <c r="S47" s="1" t="s">
@@ -4949,6 +5189,11 @@
       <c r="W47" s="1" t="s">
         <v>103</v>
       </c>
+      <c r="X47" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;https://doi.org/10.1002/cne.24985</t>
+        </is>
+      </c>
       <c r="Y47" s="1" t="s">
         <v>225</v>
       </c>
@@ -4962,7 +5207,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="48" spans="1:33" ht="15.95" customHeight="1">
+    <row r="48" ht="15.95" customHeight="1">
       <c r="A48" s="1" t="s">
         <v>221</v>
       </c>
@@ -5014,7 +5259,7 @@
       <c r="Q48" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R48" s="4" t="s">
+      <c r="R48" s="7" t="s">
         <v>228</v>
       </c>
       <c r="S48" s="1" t="s">
@@ -5032,6 +5277,11 @@
       <c r="W48" s="1" t="s">
         <v>103</v>
       </c>
+      <c r="X48" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;https://doi.org/10.1002/cne.24985</t>
+        </is>
+      </c>
       <c r="Y48" s="1" t="s">
         <v>230</v>
       </c>
@@ -5045,7 +5295,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="49" spans="1:31" ht="15.95" customHeight="1">
+    <row r="49" ht="15.95" customHeight="1">
       <c r="A49" s="1" t="s">
         <v>231</v>
       </c>
@@ -5092,7 +5342,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="50" spans="1:31" ht="15.95" customHeight="1">
+    <row r="50" ht="15.95" customHeight="1">
       <c r="A50" s="1" t="s">
         <v>231</v>
       </c>
@@ -5139,7 +5389,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="51" spans="1:31" ht="15.95" customHeight="1">
+    <row r="51" ht="15.95" customHeight="1">
       <c r="A51" s="1" t="s">
         <v>231</v>
       </c>
@@ -5189,7 +5439,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="52" spans="1:31" ht="15.95" customHeight="1">
+    <row r="52" ht="15.95" customHeight="1">
       <c r="A52" s="1" t="s">
         <v>231</v>
       </c>
@@ -5236,7 +5486,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="1:31" ht="15.95" customHeight="1">
+    <row r="53" ht="15.95" customHeight="1">
       <c r="A53" s="1" t="s">
         <v>231</v>
       </c>
@@ -5283,7 +5533,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:31" ht="15.95" customHeight="1">
+    <row r="54" ht="15.95" customHeight="1">
       <c r="A54" s="1" t="s">
         <v>231</v>
       </c>
@@ -5330,7 +5580,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="55" spans="1:31" ht="15.95" customHeight="1">
+    <row r="55" ht="15.95" customHeight="1">
       <c r="A55" s="1" t="s">
         <v>235</v>
       </c>
@@ -5386,7 +5636,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="56" spans="1:31" ht="15.95" customHeight="1">
+    <row r="56" ht="15.95" customHeight="1">
       <c r="A56" s="1" t="s">
         <v>235</v>
       </c>
@@ -5442,7 +5692,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="57" spans="1:31" ht="15.95" customHeight="1">
+    <row r="57" ht="15.95" customHeight="1">
       <c r="A57" s="1" t="s">
         <v>239</v>
       </c>
@@ -5494,7 +5744,7 @@
       <c r="Q57" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R57" s="4"/>
+      <c r="R57" s="7"/>
       <c r="T57" s="1" t="str">
         <f>IF(S57="N", R57, "write file name")</f>
         <v>write file name</v>
@@ -5512,7 +5762,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="58" spans="1:31" ht="15.95" customHeight="1">
+    <row r="58" ht="15.95" customHeight="1">
       <c r="A58" s="1" t="s">
         <v>239</v>
       </c>
@@ -5564,7 +5814,7 @@
       <c r="Q58" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R58" s="4"/>
+      <c r="R58" s="7"/>
       <c r="T58" s="1" t="str">
         <f>IF(S58="N", R58, "write file name")</f>
         <v>write file name</v>
@@ -5582,7 +5832,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="59" spans="1:31" ht="15.95" customHeight="1">
+    <row r="59" ht="15.95" customHeight="1">
       <c r="A59" s="1" t="s">
         <v>239</v>
       </c>
@@ -5634,7 +5884,7 @@
       <c r="Q59" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R59" s="4"/>
+      <c r="R59" s="7"/>
       <c r="T59" s="1" t="str">
         <f>IF(S59="N", R59, "write file name")</f>
         <v>write file name</v>
@@ -5652,7 +5902,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="60" spans="1:31" ht="15.95" customHeight="1">
+    <row r="60" ht="15.95" customHeight="1">
       <c r="A60" s="1" t="s">
         <v>239</v>
       </c>
@@ -5704,7 +5954,7 @@
       <c r="Q60" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R60" s="4"/>
+      <c r="R60" s="7"/>
       <c r="T60" s="1" t="str">
         <f>IF(S60="N", R60, "write file name")</f>
         <v>write file name</v>
@@ -5722,7 +5972,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="61" spans="1:31" ht="15.95" customHeight="1">
+    <row r="61" ht="15.95" customHeight="1">
       <c r="A61" s="1" t="s">
         <v>247</v>
       </c>
@@ -5774,7 +6024,7 @@
       <c r="Q61" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R61" s="4" t="s">
+      <c r="R61" s="7" t="s">
         <v>249</v>
       </c>
       <c r="S61" s="1" t="s">
@@ -5811,7 +6061,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="62" spans="1:31" ht="15.95" customHeight="1">
+    <row r="62" ht="15.95" customHeight="1">
       <c r="A62" s="1" t="s">
         <v>253</v>
       </c>
@@ -5860,24 +6110,24 @@
       <c r="N62" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="P62" s="10"/>
-      <c r="Q62" s="10"/>
-      <c r="R62" s="4"/>
-      <c r="S62" s="10"/>
-      <c r="T62" s="10"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="7"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="2"/>
       <c r="U62" s="1"/>
       <c r="V62" s="1"/>
       <c r="W62" s="1"/>
-      <c r="X62" s="10"/>
+      <c r="X62" s="2"/>
       <c r="Y62" s="1" t="s">
         <v>255</v>
       </c>
       <c r="Z62" s="1"/>
-      <c r="AA62" s="10"/>
-      <c r="AB62" s="10"/>
-      <c r="AE62" s="10"/>
-    </row>
-    <row r="63" spans="1:31" ht="15.95" customHeight="1">
+      <c r="AA62" s="2"/>
+      <c r="AB62" s="2"/>
+      <c r="AE62" s="2"/>
+    </row>
+    <row r="63" ht="15.95" customHeight="1">
       <c r="A63" s="1" t="s">
         <v>256</v>
       </c>
@@ -5923,7 +6173,7 @@
       <c r="N63" s="1" t="s">
         <v>257</v>
       </c>
-      <c r="R63" s="4"/>
+      <c r="R63" s="7"/>
       <c r="U63" s="1" t="s">
         <v>90</v>
       </c>
@@ -5940,7 +6190,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="64" spans="1:31" ht="15.95" customHeight="1">
+    <row r="64" ht="15.95" customHeight="1">
       <c r="A64" s="1" t="s">
         <v>259</v>
       </c>
@@ -5992,7 +6242,7 @@
       <c r="Q64" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R64" s="4" t="s">
+      <c r="R64" s="7" t="s">
         <v>261</v>
       </c>
       <c r="S64" s="1" t="s">
@@ -6020,7 +6270,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="65" spans="1:31" ht="15.95" customHeight="1">
+    <row r="65" ht="15.95" customHeight="1">
       <c r="A65" s="1" t="s">
         <v>259</v>
       </c>
@@ -6072,7 +6322,7 @@
       <c r="Q65" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R65" s="4" t="s">
+      <c r="R65" s="7" t="s">
         <v>267</v>
       </c>
       <c r="S65" s="1" t="s">
@@ -6099,6 +6349,11 @@
       <c r="Z65" s="1" t="s">
         <v>269</v>
       </c>
+      <c r="AA65" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;Kverkova</t>
+        </is>
+      </c>
       <c r="AB65" s="1" t="s">
         <v>140</v>
       </c>
@@ -6106,7 +6361,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="66" spans="1:31" ht="15.95" customHeight="1">
+    <row r="66" ht="15.95" customHeight="1">
       <c r="A66" s="1" t="s">
         <v>259</v>
       </c>
@@ -6158,7 +6413,7 @@
       <c r="Q66" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="R66" s="4" t="s">
+      <c r="R66" s="7" t="s">
         <v>272</v>
       </c>
       <c r="S66" s="1" t="s">
@@ -6185,6 +6440,11 @@
       <c r="Z66" s="1" t="s">
         <v>40</v>
       </c>
+      <c r="AA66" s="1" t="inlineStr">
+        <is>
+          <t>xml:space="preserve"&gt;Kverkova</t>
+        </is>
+      </c>
       <c r="AB66" s="1" t="s">
         <v>140</v>
       </c>
@@ -6192,7 +6452,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="67" spans="1:31" ht="15.95" customHeight="1">
+    <row r="67" ht="15.95" customHeight="1">
       <c r="A67" s="1" t="s">
         <v>275</v>
       </c>
@@ -6242,7 +6502,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="68" spans="1:31" ht="15.95" customHeight="1">
+    <row r="68" ht="15.95" customHeight="1">
       <c r="A68" s="1" t="s">
         <v>278</v>
       </c>
@@ -6295,7 +6555,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="69" spans="1:31" ht="15.95" customHeight="1">
+    <row r="69" ht="15.95" customHeight="1">
       <c r="A69" s="1" t="s">
         <v>278</v>
       </c>
@@ -6348,7 +6608,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="70" spans="1:31" ht="15.75" customHeight="1">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1" t="s">
         <v>282</v>
       </c>
@@ -6369,7 +6629,6 @@
       </c>
       <c r="H70" t="str">
         <f t="shared" si="94"/>
-        <v/>
       </c>
       <c r="I70" t="str">
         <f t="shared" si="95"/>
@@ -6398,7 +6657,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="71" spans="1:31" ht="15.75" customHeight="1">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1" t="s">
         <v>284</v>
       </c>
@@ -6419,7 +6678,6 @@
       </c>
       <c r="H71" t="str">
         <f t="shared" si="94"/>
-        <v/>
       </c>
       <c r="I71" t="str">
         <f t="shared" si="95"/>
@@ -6447,7 +6705,7 @@
       <c r="Q71" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R71" s="4"/>
+      <c r="R71" s="7"/>
       <c r="T71" s="1" t="str">
         <f>IF(S71="N", R71, "write file name")</f>
         <v>write file name</v>
@@ -6477,7 +6735,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="72" spans="1:31" ht="15.75" customHeight="1">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="s">
         <v>290</v>
       </c>
@@ -6524,7 +6782,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="73" spans="1:31" ht="15.75" customHeight="1">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1" t="s">
         <v>291</v>
       </c>
@@ -6577,7 +6835,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="74" spans="1:31" ht="15.75" customHeight="1">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
         <v>295</v>
       </c>
@@ -6629,7 +6887,7 @@
       <c r="Q74" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R74" s="4"/>
+      <c r="R74" s="7"/>
       <c r="T74" s="1" t="str">
         <f>IF(S74="N", R74, "write file name")</f>
         <v>write file name</v>
@@ -6659,7 +6917,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="75" spans="1:31" ht="15.75" customHeight="1">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
         <v>300</v>
       </c>
@@ -6714,7 +6972,7 @@
       <c r="Q75" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R75" s="4"/>
+      <c r="R75" s="7"/>
       <c r="T75" s="1" t="str">
         <f>IF(S75="N", R75, "write file name")</f>
         <v>write file name</v>
@@ -6735,7 +6993,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="76" spans="1:31" ht="15.75" customHeight="1">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1" t="s">
         <v>300</v>
       </c>
@@ -6790,7 +7048,7 @@
       <c r="Q76" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R76" s="4"/>
+      <c r="R76" s="7"/>
       <c r="T76" s="1" t="str">
         <f>IF(S76="N", R76, "write file name")</f>
         <v>write file name</v>
@@ -6811,7 +7069,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="77" spans="1:31" ht="15.75" customHeight="1">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
         <v>306</v>
       </c>
@@ -6858,7 +7116,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="78" spans="1:31" ht="15.75" customHeight="1">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1" t="s">
         <v>306</v>
       </c>
@@ -6905,7 +7163,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="79" spans="1:31" ht="15.75" customHeight="1">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="s">
         <v>309</v>
       </c>
@@ -6955,7 +7213,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="80" spans="1:31" ht="15.75" customHeight="1">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="s">
         <v>312</v>
       </c>
@@ -6999,7 +7257,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="81" spans="1:31" ht="15.75" customHeight="1">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
         <v>314</v>
       </c>
@@ -7046,7 +7304,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="82" spans="1:31">
+    <row r="82">
       <c r="A82" s="1" t="s">
         <v>316</v>
       </c>
@@ -7095,7 +7353,7 @@
       <c r="Q82" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R82" s="4"/>
+      <c r="R82" s="7"/>
       <c r="T82" s="1" t="str">
         <f>IF(S82="N", R82, "write file name")</f>
         <v>write file name</v>
@@ -7113,7 +7371,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" spans="1:31">
+    <row r="83">
       <c r="A83" s="1" t="s">
         <v>320</v>
       </c>
@@ -7162,7 +7420,7 @@
       <c r="Q83" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="R83" s="4"/>
+      <c r="R83" s="7"/>
       <c r="T83" s="1" t="str">
         <f>IF(S83="N", R83, "write file name")</f>
         <v>write file name</v>
@@ -7185,20 +7443,20 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="X12" r:id="rId1" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="X11" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="X14" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000002000000}"/>
-    <hyperlink ref="X20" r:id="rId4" xr:uid="{00000000-0004-0000-0000-000003000000}"/>
-    <hyperlink ref="X26" r:id="rId5" xr:uid="{00000000-0004-0000-0000-000004000000}"/>
-    <hyperlink ref="X71" r:id="rId6" xr:uid="{00000000-0004-0000-0000-000005000000}"/>
-    <hyperlink ref="X74" r:id="rId7" xr:uid="{00000000-0004-0000-0000-000006000000}"/>
-    <hyperlink ref="X42" r:id="rId8" xr:uid="{00000000-0004-0000-0000-000007000000}"/>
-    <hyperlink ref="X31:X36" r:id="rId9" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf" xr:uid="{00000000-0004-0000-0000-000008000000}"/>
-    <hyperlink ref="X66" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000009000000}"/>
-    <hyperlink ref="X65" r:id="rId11" xr:uid="{00000000-0004-0000-0000-00000A000000}"/>
-    <hyperlink ref="X61" r:id="rId12" xr:uid="{00000000-0004-0000-0000-00000B000000}"/>
-    <hyperlink ref="X28" r:id="rId13" xr:uid="{00000000-0004-0000-0000-00000C000000}"/>
-    <hyperlink ref="X29" r:id="rId14" xr:uid="{00000000-0004-0000-0000-00000D000000}"/>
+    <hyperlink ref="X12" r:id="rId1h" display="https://elifesciences.org/download/aHR0cHM6Ly9jZG4uZWxpZmVzY2llbmNlcy5vcmcvYXJ0aWNsZXMvNzc4NzUvZWxpZmUtNzc4NzUtdjEucGRmP2Nhbm9uaWNhbFVyaT1odHRwczovL2VsaWZlc2NpZW5jZXMub3JnL2FydGljbGVzLzc3ODc1/elife-77875-v1.pdf?_hash=NStjcL9fTlmy3AQDwSiM0YgMVB3UYjO8nDg0UbwN5gM%3D"/>
+    <hyperlink ref="X11" r:id="rId2h"/>
+    <hyperlink ref="X14" r:id="rId3h"/>
+    <hyperlink ref="X20" r:id="rId4h"/>
+    <hyperlink ref="X26" r:id="rId5h"/>
+    <hyperlink ref="X71" r:id="rId6h"/>
+    <hyperlink ref="X74" r:id="rId7h"/>
+    <hyperlink ref="X42" r:id="rId8h"/>
+    <hyperlink ref="X31:X36" r:id="rId9h" display="https://karger.com/bbe/article-pdf/86/3-4/145/2264694/000437413.pdf"/>
+    <hyperlink ref="X66" r:id="rId10h"/>
+    <hyperlink ref="X65" r:id="rId11h"/>
+    <hyperlink ref="X61" r:id="rId12h"/>
+    <hyperlink ref="X28" r:id="rId13h"/>
+    <hyperlink ref="X29" r:id="rId14h"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -7206,105 +7464,105 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="26.125" customWidth="1"/>
+    <col min="1" max="1" width="26.125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1">
       <c r="A1" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2">
       <c r="A2" t="s">
         <v>323</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="7" t="s">
+    <row r="3">
+      <c r="A3" s="10" t="s">
         <v>324</v>
       </c>
       <c r="B3" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="7" t="s">
+    <row r="4">
+      <c r="A4" s="10" t="s">
         <v>326</v>
       </c>
       <c r="B4" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="7" t="s">
+    <row r="5">
+      <c r="A5" s="10" t="s">
         <v>328</v>
       </c>
       <c r="B5" t="s">
         <v>329</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="7" t="s">
+    <row r="6">
+      <c r="A6" s="10" t="s">
         <v>330</v>
       </c>
       <c r="B6" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="7" t="s">
+    <row r="7">
+      <c r="A7" s="10" t="s">
         <v>332</v>
       </c>
       <c r="B7" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="7" t="s">
+    <row r="8">
+      <c r="A8" s="10" t="s">
         <v>334</v>
       </c>
       <c r="B8" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="7" t="s">
+    <row r="9">
+      <c r="A9" s="10" t="s">
         <v>336</v>
       </c>
       <c r="B9" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="7" t="s">
+    <row r="10">
+      <c r="A10" s="10" t="s">
         <v>338</v>
       </c>
       <c r="B10" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="7" t="s">
+    <row r="11">
+      <c r="A11" s="10" t="s">
         <v>340</v>
       </c>
       <c r="B11" t="s">
         <v>341</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="17.100000000000001" customHeight="1">
-      <c r="A12" s="9" t="s">
+    <row r="12" ht="17.100000000000001" customHeight="1">
+      <c r="A12" s="12" t="s">
         <v>342</v>
       </c>
       <c r="B12" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="8" t="s">
+    <row r="13">
+      <c r="A13" s="11" t="s">
         <v>344</v>
       </c>
     </row>
@@ -7315,26 +7573,26 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="1.875" customWidth="1"/>
-    <col min="2" max="2" width="126" customWidth="1"/>
+    <col min="1" max="1" width="1.875" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="126" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1">
       <c r="A1" t="s">
         <v>345</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2">
       <c r="C2" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
+    <row r="3">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="s">
@@ -7344,8 +7602,8 @@
         <v>348</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="s">
@@ -7355,8 +7613,8 @@
         <v>350</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
+    <row r="5">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="s">
@@ -7366,8 +7624,8 @@
         <v>352</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
+    <row r="6">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="s">
@@ -7384,318 +7642,333 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:A61"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.95"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1">
       <c r="A1" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="2">
       <c r="A2" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="3">
       <c r="A3" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="4">
       <c r="A4" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="5">
       <c r="A5" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="6">
       <c r="A6" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="7">
       <c r="A7" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="8">
       <c r="A8" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="10">
       <c r="A10" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="11">
       <c r="A11" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="13">
       <c r="A13" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="s">
-        <v>368</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="15">
       <c r="A15" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="16">
       <c r="A16" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="17">
       <c r="A17" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="18">
       <c r="A18" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="19">
       <c r="A19" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="20">
       <c r="A20" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="21">
       <c r="A21" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="22">
       <c r="A22" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="23">
       <c r="A23" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="24">
       <c r="A24" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="25">
       <c r="A25" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="26">
       <c r="A26" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="27">
       <c r="A27" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="28">
       <c r="A28" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="29">
       <c r="A29" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30">
       <c r="A30" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="31">
       <c r="A31" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="34">
       <c r="A34" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="35" spans="1:1">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="35">
       <c r="A35" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="36" spans="1:1">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="36">
       <c r="A36" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="37" spans="1:1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="37">
       <c r="A37" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="38" spans="1:1">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="38">
       <c r="A38" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="39" spans="1:1">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="39">
       <c r="A39" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="40" spans="1:1">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="40">
       <c r="A40" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="41" spans="1:1">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="41">
       <c r="A41" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="42" spans="1:1">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="42">
       <c r="A42" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="43" spans="1:1">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="43">
       <c r="A43" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="44" spans="1:1">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="44">
       <c r="A44" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="45" spans="1:1">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="45">
       <c r="A45" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="46" spans="1:1">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="46">
       <c r="A46" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="47" spans="1:1">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="47">
       <c r="A47" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="48" spans="1:1">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="48">
       <c r="A48" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="49" spans="1:1">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="49">
       <c r="A49" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="50" spans="1:1">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="50">
       <c r="A50" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="51" spans="1:1">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="51">
       <c r="A51" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="52" spans="1:1">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="52">
       <c r="A52" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="53" spans="1:1">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="53">
       <c r="A53" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="54" spans="1:1">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="54">
       <c r="A54" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="55" spans="1:1">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="55">
       <c r="A55" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="56" spans="1:1">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="56">
       <c r="A56" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="57" spans="1:1">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="57">
       <c r="A57" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="58" spans="1:1">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="58">
       <c r="A58" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="59" spans="1:1">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="59">
       <c r="A59" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="60" spans="1:1">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="60">
       <c r="A60" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="61" spans="1:1">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="61">
       <c r="A61" t="s">
-        <v>415</v>
+        <v>475</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>478</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -7975,13 +8248,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{393CEB05-6A9C-454A-BDDF-E9F23897B6BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3175246-AD22-47A4-A702-60D9C2849160}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{05209338-5D48-4750-BEDF-5F912B2D3EB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AF41B972-5A98-4727-887F-6AF19ECD88DB}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C092463B-DEE0-4311-BA63-23860C1DD18C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C345D4DD-977A-400F-B0B3-D8636C363C95}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1930,7 +1930,7 @@
     <t>ManyPrimates, Aguenounon, G., Allritz, M., Altschul, D., Ballesta, S., Beaud, A., Bohn, M., Bornbusch, S., Brandão, A., Brooks, J., Bugnyar, T., Burkart, J., Bustamante, L., Call, J., Canteloup, C., Cao, C., Caspar, K., da Silva, D., de Sousa, A., . . . Zablocki-Thomas, P. (2022). The Evolution of Primate Short-Term Memory. Animal Behavior and Cognition, 9(4), 428-516. https://doi.org/10.26451/abc.09.04.06.2022</t>
   </si>
   <si>
-    <t>data/species_predictors.xlsx</t>
+    <t>speciespredictors</t>
   </si>
   <si>
     <t>need to record steps</t>
@@ -2428,7 +2428,7 @@
     <t>Wilman, H., Belmaker, J., Simpson, J., de la Rosa, C., Rivadeneira, M. M., &amp; Jetz, W. (2014). EltonTraits 1.0: Species‐level foraging attributes of the world's birds and mammals. Ecology, 95(7), 2027-2027. https://doi.org/10.1890/13-1917.1</t>
   </si>
   <si>
-    <t>MamFuncDat.txt</t>
+    <t>MamFuncDat</t>
   </si>
   <si>
     <t>diet &amp; body mass (functional traits)</t>
@@ -2440,7 +2440,7 @@
     <t>Wimberly, A. N., Slater, G. J., &amp; Granatosky, M. C. (2021). Evolutionary history of quadrupedal walking gaits shows mammalian release from locomotor constraint. Proc Biol Sci, 288(1957), 20210937. https://doi.org/10.1098/rspb.2021.0937</t>
   </si>
   <si>
-    <t>mammal_gait.txt</t>
+    <t>MammalGait</t>
   </si>
   <si>
     <t>Winkler, S. L., &amp; Bryant, G. A. (2021). Play vocalisations and human laughter: a comparative review. Bioacoustics, 1-28. https://doi.org/10.1080/09524622.2021.1905065</t>
@@ -3525,7 +3525,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM224"/>
+  <dimension ref="A1:AM222"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="67.1640625" customWidth="1"/>
@@ -6690,7 +6690,7 @@
         <v>10.1038%2Fs41559-019-0969-0</v>
       </c>
       <c r="K44" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE(),F44,(SUBSTITUTE(SUBSTITUTE(D45," ",""), "_", ""))))</f>
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE(),F44,(SUBSTITUTE(SUBSTITUTE(D44," ",""), "_", ""))))</f>
         <v>DeCasien_Higham_2019_SupplementaryData1-BrainRegion</v>
       </c>
       <c r="L44" t="str">
@@ -6853,7 +6853,7 @@
         <v>10.1038%2Fs41559-019-0969-0</v>
       </c>
       <c r="K46" t="str">
-        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE(),F46,(SUBSTITUTE(SUBSTITUTE(D47," ",""), "_", ""))))</f>
+        <f>TRIM(_xlfn.TEXTJOIN("_",FALSE(),F46,(SUBSTITUTE(SUBSTITUTE(D46," ",""), "_", ""))))</f>
         <v>DeCasien_Higham_2019_SupplementaryData1-SocialSystem</v>
       </c>
       <c r="L46" t="str">
@@ -13215,19 +13215,19 @@
         <v>547</v>
       </c>
       <c r="E131" t="str">
-        <f t="shared" ref="E131:E195" si="28">RIGHT(A131,1)</f>
+        <f t="shared" ref="E131:E194" si="28">RIGHT(A131,1)</f>
         <v>.</v>
       </c>
       <c r="F131" t="str">
-        <f t="shared" ref="F131:F195" si="29">G131 &amp; IF(H131&lt;&gt;"", "_" &amp; H131, "_") &amp; IF(I131&lt;&gt;"", "_" &amp; I131, "_") &amp; IF(B131&lt;&gt;"", "_" &amp; B131, "")</f>
+        <f t="shared" ref="F131:F194" si="29">G131 &amp; IF(H131&lt;&gt;"", "_" &amp; H131, "_") &amp; IF(I131&lt;&gt;"", "_" &amp; I131, "_") &amp; IF(B131&lt;&gt;"", "_" &amp; B131, "")</f>
         <v>Kaufman__2004</v>
       </c>
       <c r="G131" t="str">
-        <f t="shared" ref="G131:G195" si="30">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A131,","), "-", ""), " ", "")</f>
+        <f t="shared" ref="G131:G194" si="30">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A131,","), "-", ""), " ", "")</f>
         <v>Kaufman</v>
       </c>
       <c r="H131" t="str">
-        <f t="shared" ref="H131:H195" si="31">_xlfn.LET(
+        <f t="shared" ref="H131:H194" si="31">_xlfn.LET(
 _xlpm.authors,_xlfn.TEXTBEFORE(A131," ("&amp;I131&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
@@ -13236,7 +13236,7 @@
         <v/>
       </c>
       <c r="I131" t="str">
-        <f t="shared" ref="I131:I195" si="32">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A131, "("), ")")</f>
+        <f t="shared" ref="I131:I194" si="32">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A131, "("), ")")</f>
         <v>2004</v>
       </c>
       <c r="J131" t="str">
@@ -13259,7 +13259,7 @@
         <v>Kaufman__2004_TableA10</v>
       </c>
       <c r="L131" t="str">
-        <f t="shared" ref="L131:L195" si="34">J131 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D131,CHAR(160),"")," ",""),"_","")</f>
+        <f t="shared" ref="L131:L194" si="34">J131 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D131,CHAR(160),"")," ",""),"_","")</f>
         <v>UMI%3A3147447_TableA10</v>
       </c>
       <c r="M131" t="str">
@@ -14051,7 +14051,7 @@
         <v>10.1038%2Fs41598-018-24331-0</v>
       </c>
       <c r="K143" t="str">
-        <f t="shared" ref="K143:K175" si="35">TRIM(_xlfn.TEXTJOIN("_",FALSE(),F143,(SUBSTITUTE(SUBSTITUTE(D143," ",""), "_", ""))))</f>
+        <f t="shared" ref="K143:K174" si="35">TRIM(_xlfn.TEXTJOIN("_",FALSE(),F143,(SUBSTITUTE(SUBSTITUTE(D143," ",""), "_", ""))))</f>
         <v>Kochiyama_etal_2018_FossilSpecimensText</v>
       </c>
       <c r="L143" t="str">
@@ -14959,20 +14959,23 @@
     </row>
     <row r="156" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A156" s="1" t="s">
-        <v>630</v>
-      </c>
-      <c r="D156" s="1"/>
+        <v>637</v>
+      </c>
+      <c r="B156" s="6"/>
+      <c r="D156" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="E156" t="str">
         <f t="shared" si="28"/>
-        <v>2</v>
+        <v>F</v>
       </c>
       <c r="F156" t="str">
         <f t="shared" si="29"/>
-        <v>ManyPrimates__2022</v>
+        <v>Matano__2001</v>
       </c>
       <c r="G156" t="str">
         <f t="shared" si="30"/>
-        <v>ManyPrimates</v>
+        <v>Matano</v>
       </c>
       <c r="H156" t="str">
         <f t="shared" si="31"/>
@@ -14980,79 +14983,11 @@
       </c>
       <c r="I156" t="str">
         <f t="shared" si="32"/>
-        <v>2022</v>
+        <v>2001</v>
       </c>
       <c r="J156" t="str">
-        <f>_xlfn.LET(
-_xlpm.doi,IF(C153&lt;&gt;"",C153,_xlfn.TEXTAFTER(A156,"https://doi.org/")),
-SUBSTITUTE(
-SUBSTITUTE(
-SUBSTITUTE(
-SUBSTITUTE(
-_xlpm.doi,
-"/","%2F"),
-":","%3A"),
-"&lt;","%3C"),
-"&gt;","%3E")
-)</f>
-        <v>10.26451%2Fabc.09.04.06.2022</v>
-      </c>
-      <c r="K156" t="str">
-        <f t="shared" si="35"/>
-        <v>ManyPrimates__2022_</v>
-      </c>
-      <c r="L156" t="str">
-        <f t="shared" si="34"/>
-        <v>10.26451%2Fabc.09.04.06.2022_</v>
-      </c>
-      <c r="M156" t="str">
-        <f t="array" ref="M156">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L156,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P156" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="AJ156" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL156" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM156" s="1" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="157" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A157" s="1" t="s">
-        <v>637</v>
-      </c>
-      <c r="B157" s="6"/>
-      <c r="D157" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="E157" t="str">
-        <f t="shared" si="28"/>
-        <v>F</v>
-      </c>
-      <c r="F157" t="str">
-        <f t="shared" si="29"/>
-        <v>Matano__2001</v>
-      </c>
-      <c r="G157" t="str">
-        <f t="shared" si="30"/>
-        <v>Matano</v>
-      </c>
-      <c r="H157" t="str">
-        <f t="shared" si="31"/>
-        <v/>
-      </c>
-      <c r="I157" t="str">
-        <f t="shared" si="32"/>
-        <v>2001</v>
-      </c>
-      <c r="J157" t="str">
-        <f t="shared" ref="J157:J188" si="44">_xlfn.LET(
-_xlpm.doi,IF(C157&lt;&gt;"",C157,_xlfn.TEXTAFTER(A157,"https://doi.org/")),
+        <f t="shared" ref="J156:J187" si="44">_xlfn.LET(
+_xlpm.doi,IF(C156&lt;&gt;"",C156,_xlfn.TEXTAFTER(A156,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -15065,39 +15000,122 @@
 )</f>
         <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F</v>
       </c>
+      <c r="K156" t="str">
+        <f t="shared" si="35"/>
+        <v>Matano__2001_TABLE2</v>
+      </c>
+      <c r="L156" t="str">
+        <f t="shared" si="34"/>
+        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2</v>
+      </c>
+      <c r="M156" t="str">
+        <f t="array" ref="M156">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L156,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
+        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2.tsv</v>
+      </c>
+      <c r="N156" s="1" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="157" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A157" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E157" t="str">
+        <f t="shared" si="28"/>
+        <v>2</v>
+      </c>
+      <c r="F157" t="str">
+        <f t="shared" si="29"/>
+        <v>Matano_etal_1985_a</v>
+      </c>
+      <c r="G157" t="str">
+        <f t="shared" si="30"/>
+        <v>Matano</v>
+      </c>
+      <c r="H157" t="str">
+        <f t="shared" si="31"/>
+        <v>etal</v>
+      </c>
+      <c r="I157" t="str">
+        <f t="shared" si="32"/>
+        <v>1985</v>
+      </c>
+      <c r="J157" t="str">
+        <f t="shared" si="44"/>
+        <v>10.1159%2F000156212</v>
+      </c>
       <c r="K157" t="str">
         <f t="shared" si="35"/>
-        <v>Matano__2001_TABLE2</v>
+        <v>Matano_etal_1985_a_Table1</v>
       </c>
       <c r="L157" t="str">
         <f t="shared" si="34"/>
-        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2</v>
+        <v>10.1159%2F000156212_Table1</v>
       </c>
       <c r="M157" t="str">
         <f t="array" ref="M157">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L157,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N157" s="1" t="s">
-        <v>638</v>
+        <v>640</v>
+      </c>
+      <c r="P157" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V157" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y157" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z157" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF157" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG157" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI157" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="AJ157" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK157" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL157" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM157" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="158" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A158" s="1" t="s">
-        <v>639</v>
-      </c>
-      <c r="B158" s="1" t="s">
-        <v>164</v>
+        <v>642</v>
+      </c>
+      <c r="B158" s="4" t="s">
+        <v>172</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>75</v>
       </c>
       <c r="E158" t="str">
         <f t="shared" si="28"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F158" t="str">
         <f t="shared" si="29"/>
-        <v>Matano_etal_1985_a</v>
+        <v>Matano_etal_1985_b</v>
       </c>
       <c r="G158" t="str">
         <f t="shared" si="30"/>
@@ -15113,29 +15131,23 @@
       </c>
       <c r="J158" t="str">
         <f t="shared" si="44"/>
-        <v>10.1159%2F000156212</v>
+        <v>10.1159%2F000156211</v>
       </c>
       <c r="K158" t="str">
         <f t="shared" si="35"/>
-        <v>Matano_etal_1985_a_Table1</v>
+        <v>Matano_etal_1985_b_Table1</v>
       </c>
       <c r="L158" t="str">
         <f t="shared" si="34"/>
-        <v>10.1159%2F000156212_Table1</v>
+        <v>10.1159%2F000156211_Table1</v>
       </c>
       <c r="M158" t="str">
         <f t="array" ref="M158">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L158,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N158" s="1" t="s">
-        <v>640</v>
-      </c>
       <c r="P158" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="V158" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="Y158" s="1" t="s">
         <v>99</v>
       </c>
@@ -15145,34 +15157,13 @@
       <c r="AF158" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AG158" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI158" s="1" t="s">
-        <v>641</v>
-      </c>
-      <c r="AJ158" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK158" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL158" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM158" s="1" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="159" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A159" s="1" t="s">
-        <v>642</v>
-      </c>
-      <c r="B159" s="4" t="s">
-        <v>172</v>
+        <v>643</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>75</v>
+        <v>198</v>
       </c>
       <c r="E159" t="str">
         <f t="shared" si="28"/>
@@ -15180,63 +15171,66 @@
       </c>
       <c r="F159" t="str">
         <f t="shared" si="29"/>
-        <v>Matano_etal_1985_b</v>
+        <v>Mota_Herculano-Houzel_2015</v>
       </c>
       <c r="G159" t="str">
         <f t="shared" si="30"/>
-        <v>Matano</v>
+        <v>Mota</v>
       </c>
       <c r="H159" t="str">
         <f t="shared" si="31"/>
-        <v>etal</v>
+        <v>Herculano-Houzel</v>
       </c>
       <c r="I159" t="str">
         <f t="shared" si="32"/>
-        <v>1985</v>
+        <v>2015</v>
       </c>
       <c r="J159" t="str">
         <f t="shared" si="44"/>
-        <v>10.1159%2F000156211</v>
+        <v>10.1126%2Fscience.aaa9101</v>
       </c>
       <c r="K159" t="str">
         <f t="shared" si="35"/>
-        <v>Matano_etal_1985_b_Table1</v>
+        <v>Mota_Herculano-Houzel_2015_TableS1</v>
       </c>
       <c r="L159" t="str">
         <f t="shared" si="34"/>
-        <v>10.1159%2F000156211_Table1</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1</v>
       </c>
       <c r="M159" t="str">
         <f t="array" ref="M159">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L159,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P159" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y159" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z159" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF159" s="1" t="s">
-        <v>78</v>
+        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
+      </c>
+      <c r="Q159" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AI159" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="AJ159" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AL159" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="AM159" s="1" t="s">
+        <v>644</v>
       </c>
     </row>
     <row r="160" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A160" s="1" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>198</v>
+        <v>646</v>
       </c>
       <c r="E160" t="str">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F160" t="str">
         <f t="shared" si="29"/>
-        <v>Mota_Herculano-Houzel_2015</v>
+        <v>Mota_etal_2019</v>
       </c>
       <c r="G160" t="str">
         <f t="shared" si="30"/>
@@ -15244,33 +15238,39 @@
       </c>
       <c r="H160" t="str">
         <f t="shared" si="31"/>
-        <v>Herculano-Houzel</v>
+        <v>etal</v>
       </c>
       <c r="I160" t="str">
         <f t="shared" si="32"/>
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="J160" t="str">
         <f t="shared" si="44"/>
-        <v>10.1126%2Fscience.aaa9101</v>
+        <v>10.1073%2Fpnas.1716956116</v>
       </c>
       <c r="K160" t="str">
         <f t="shared" si="35"/>
-        <v>Mota_Herculano-Houzel_2015_TableS1</v>
+        <v>Mota_etal_2019_SupplementaryTableS1</v>
       </c>
       <c r="L160" t="str">
         <f t="shared" si="34"/>
-        <v>10.1126%2Fscience.aaa9101_TableS1</v>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
       </c>
       <c r="M160" t="str">
         <f t="array" ref="M160">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L160,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1126%2Fscience.aaa9101_TableS1.tsv</v>
-      </c>
-      <c r="Q160" s="1" t="s">
-        <v>132</v>
+        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1.tsv</v>
+      </c>
+      <c r="N160" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="P160" s="1" t="s">
+        <v>335</v>
+      </c>
+      <c r="AA160" s="1" t="s">
+        <v>648</v>
       </c>
       <c r="AI160" s="1" t="s">
-        <v>644</v>
+        <v>649</v>
       </c>
       <c r="AJ160" s="1" t="s">
         <v>140</v>
@@ -15279,27 +15279,30 @@
         <v>362</v>
       </c>
       <c r="AM160" s="1" t="s">
-        <v>644</v>
+        <v>650</v>
       </c>
     </row>
     <row r="161" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A161" s="1" t="s">
-        <v>645</v>
+        <v>651</v>
+      </c>
+      <c r="C161" s="1" t="s">
+        <v>652</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="E161" t="str">
         <f t="shared" si="28"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F161" t="str">
         <f t="shared" si="29"/>
-        <v>Mota_etal_2019</v>
+        <v>Powell_etal_2017</v>
       </c>
       <c r="G161" t="str">
         <f t="shared" si="30"/>
-        <v>Mota</v>
+        <v>Powell</v>
       </c>
       <c r="H161" t="str">
         <f t="shared" si="31"/>
@@ -15307,55 +15310,74 @@
       </c>
       <c r="I161" t="str">
         <f t="shared" si="32"/>
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="J161" t="str">
         <f t="shared" si="44"/>
-        <v>10.1073%2Fpnas.1716956116</v>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1</v>
       </c>
       <c r="K161" t="str">
         <f t="shared" si="35"/>
-        <v>Mota_etal_2019_SupplementaryTableS1</v>
+        <v>Powell_etal_2017_Dataset1</v>
       </c>
       <c r="L161" t="str">
         <f t="shared" si="34"/>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1</v>
+        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
       </c>
       <c r="M161" t="str">
         <f t="array" ref="M161">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L161,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1073%2Fpnas.1716956116_SupplementaryTableS1.tsv</v>
-      </c>
-      <c r="N161" s="1" t="s">
-        <v>647</v>
+        <v>notfound</v>
       </c>
       <c r="P161" s="1" t="s">
         <v>335</v>
       </c>
+      <c r="Q161" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="T161" s="1" t="str">
+        <f>IF(S161="N", R161, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U161" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="V161" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W161" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="X161" s="1" t="s">
+        <v>654</v>
+      </c>
       <c r="AA161" s="1" t="s">
-        <v>648</v>
+        <v>139</v>
+      </c>
+      <c r="AH161" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="AI161" s="1" t="s">
-        <v>649</v>
+        <v>655</v>
       </c>
       <c r="AJ161" s="1" t="s">
-        <v>140</v>
+        <v>118</v>
+      </c>
+      <c r="AK161" s="1" t="s">
+        <v>141</v>
       </c>
       <c r="AL161" s="1" t="s">
-        <v>362</v>
+        <v>141</v>
       </c>
       <c r="AM161" s="1" t="s">
-        <v>650</v>
+        <v>655</v>
       </c>
     </row>
     <row r="162" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A162" s="1" t="s">
-        <v>651</v>
-      </c>
-      <c r="C162" s="1" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>653</v>
+        <v>75</v>
       </c>
       <c r="E162" t="str">
         <f t="shared" si="28"/>
@@ -15363,94 +15385,66 @@
       </c>
       <c r="F162" t="str">
         <f t="shared" si="29"/>
-        <v>Powell_etal_2017</v>
+        <v>Rilling_Insel_1998</v>
       </c>
       <c r="G162" t="str">
         <f t="shared" si="30"/>
-        <v>Powell</v>
+        <v>Rilling</v>
       </c>
       <c r="H162" t="str">
         <f t="shared" si="31"/>
-        <v>etal</v>
+        <v>Insel</v>
       </c>
       <c r="I162" t="str">
         <f t="shared" si="32"/>
-        <v>2017</v>
+        <v>1998</v>
       </c>
       <c r="J162" t="str">
         <f t="shared" si="44"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1</v>
+        <v>10.1159%2F000006575</v>
       </c>
       <c r="K162" t="str">
         <f t="shared" si="35"/>
-        <v>Powell_etal_2017_Dataset1</v>
+        <v>Rilling_Insel_1998_Table1</v>
       </c>
       <c r="L162" t="str">
         <f t="shared" si="34"/>
-        <v>10.6084%2Fm9.figshare.c.3899422.v1_Dataset1</v>
+        <v>10.1159%2F000006575_Table1</v>
       </c>
       <c r="M162" t="str">
         <f t="array" ref="M162">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L162,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P162" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="Q162" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="T162" s="1" t="str">
-        <f>IF(S162="N", R162, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U162" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="V162" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W162" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="X162" s="1" t="s">
-        <v>654</v>
-      </c>
-      <c r="AA162" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH162" s="1" t="s">
-        <v>177</v>
-      </c>
-      <c r="AI162" s="1" t="s">
-        <v>655</v>
-      </c>
-      <c r="AJ162" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK162" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AL162" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM162" s="1" t="s">
-        <v>655</v>
+        <v>10.1159%2F000006575_Table1.tsv</v>
+      </c>
+      <c r="N162" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="Y162" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="Z162" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="AF162" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="AG162" s="1" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="163" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A163" s="1" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>75</v>
       </c>
       <c r="E163" t="str">
         <f t="shared" si="28"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F163" t="str">
         <f t="shared" si="29"/>
-        <v>Rilling_Insel_1998</v>
+        <v>Rilling_Insel_1999</v>
       </c>
       <c r="G163" t="str">
         <f t="shared" si="30"/>
@@ -15462,26 +15456,26 @@
       </c>
       <c r="I163" t="str">
         <f t="shared" si="32"/>
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="J163" t="str">
         <f t="shared" si="44"/>
-        <v>10.1159%2F000006575</v>
+        <v>10.1006%2Fjhev.1999.0313</v>
       </c>
       <c r="K163" t="str">
         <f t="shared" si="35"/>
-        <v>Rilling_Insel_1998_Table1</v>
+        <v>Rilling_Insel_1999_Table1</v>
       </c>
       <c r="L163" t="str">
         <f t="shared" si="34"/>
-        <v>10.1159%2F000006575_Table1</v>
+        <v>10.1006%2Fjhev.1999.0313_Table1</v>
       </c>
       <c r="M163" t="str">
         <f t="array" ref="M163">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L163,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000006575_Table1.tsv</v>
+        <v>10.1006%2Fjhev.1999.0313_Table1.tsv</v>
       </c>
       <c r="N163" s="1" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="Y163" s="1" t="s">
         <v>626</v>
@@ -15489,137 +15483,122 @@
       <c r="Z163" s="1" t="s">
         <v>626</v>
       </c>
-      <c r="AF163" s="1" t="s">
-        <v>627</v>
-      </c>
-      <c r="AG163" s="1" t="s">
-        <v>112</v>
-      </c>
     </row>
     <row r="164" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A164" s="1" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>75</v>
+        <v>661</v>
       </c>
       <c r="E164" t="str">
         <f t="shared" si="28"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F164" t="str">
         <f t="shared" si="29"/>
-        <v>Rilling_Insel_1999</v>
+        <v>Schniter_Penaherrera-Aguirre_2026</v>
       </c>
       <c r="G164" t="str">
         <f t="shared" si="30"/>
-        <v>Rilling</v>
+        <v>Schniter</v>
       </c>
       <c r="H164" t="str">
         <f t="shared" si="31"/>
-        <v>Insel</v>
+        <v>Penaherrera-Aguirre</v>
       </c>
       <c r="I164" t="str">
         <f t="shared" si="32"/>
-        <v>1999</v>
+        <v>2026</v>
       </c>
       <c r="J164" t="str">
         <f t="shared" si="44"/>
-        <v>10.1006%2Fjhev.1999.0313</v>
+        <v>10.1007%2Fs10329-026-01271-2</v>
       </c>
       <c r="K164" t="str">
         <f t="shared" si="35"/>
-        <v>Rilling_Insel_1999_Table1</v>
+        <v>Schniter_Penaherrera-Aguirre_2026_data</v>
       </c>
       <c r="L164" t="str">
         <f t="shared" si="34"/>
-        <v>10.1006%2Fjhev.1999.0313_Table1</v>
+        <v>10.1007%2Fs10329-026-01271-2_data</v>
       </c>
       <c r="M164" t="str">
         <f t="array" ref="M164">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L164,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1006%2Fjhev.1999.0313_Table1.tsv</v>
+        <v>10.1007%2Fs10329-026-01271-2_data.tsv</v>
       </c>
       <c r="N164" s="1" t="s">
-        <v>659</v>
-      </c>
-      <c r="Y164" s="1" t="s">
-        <v>626</v>
-      </c>
-      <c r="Z164" s="1" t="s">
-        <v>626</v>
+        <v>661</v>
+      </c>
+      <c r="P164" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AI164" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="AL164" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM164" s="1" t="s">
+        <v>1025</v>
       </c>
     </row>
     <row r="165" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A165" s="1" t="s">
-        <v>660</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>661</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="D165" s="1"/>
       <c r="E165" t="str">
         <f t="shared" si="28"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F165" t="str">
         <f t="shared" si="29"/>
-        <v>Schniter_Penaherrera-Aguirre_2026</v>
+        <v>Semendeferi_Damasio_2000</v>
       </c>
       <c r="G165" t="str">
         <f t="shared" si="30"/>
-        <v>Schniter</v>
+        <v>Semendeferi</v>
       </c>
       <c r="H165" t="str">
         <f t="shared" si="31"/>
-        <v>Penaherrera-Aguirre</v>
+        <v>Damasio</v>
       </c>
       <c r="I165" t="str">
         <f t="shared" si="32"/>
-        <v>2026</v>
+        <v>2000</v>
       </c>
       <c r="J165" t="str">
         <f t="shared" si="44"/>
-        <v>10.1007%2Fs10329-026-01271-2</v>
+        <v>10.1006%2Fjhev.1999.0381</v>
       </c>
       <c r="K165" t="str">
         <f t="shared" si="35"/>
-        <v>Schniter_Penaherrera-Aguirre_2026_data</v>
+        <v>Semendeferi_Damasio_2000_</v>
       </c>
       <c r="L165" t="str">
         <f t="shared" si="34"/>
-        <v>10.1007%2Fs10329-026-01271-2_data</v>
+        <v>10.1006%2Fjhev.1999.0381_</v>
       </c>
       <c r="M165" t="str">
         <f t="array" ref="M165">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L165,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1007%2Fs10329-026-01271-2_data.tsv</v>
-      </c>
-      <c r="N165" s="1" t="s">
-        <v>661</v>
-      </c>
-      <c r="P165" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AI165" s="1" t="s">
-        <v>1024</v>
-      </c>
-      <c r="AL165" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM165" s="1" t="s">
-        <v>1025</v>
+        <v>notfound</v>
       </c>
     </row>
     <row r="166" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A166" s="1" t="s">
-        <v>662</v>
-      </c>
-      <c r="D166" s="1"/>
+        <v>663</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="E166" t="str">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>L</v>
       </c>
       <c r="F166" t="str">
         <f t="shared" si="29"/>
-        <v>Semendeferi_Damasio_2000</v>
+        <v>Semendeferi_etal_1998</v>
       </c>
       <c r="G166" t="str">
         <f t="shared" si="30"/>
@@ -15627,43 +15606,73 @@
       </c>
       <c r="H166" t="str">
         <f t="shared" si="31"/>
-        <v>Damasio</v>
+        <v>etal</v>
       </c>
       <c r="I166" t="str">
         <f t="shared" si="32"/>
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="J166" t="str">
         <f t="shared" si="44"/>
-        <v>10.1006%2Fjhev.1999.0381</v>
+        <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L</v>
       </c>
       <c r="K166" t="str">
         <f t="shared" si="35"/>
-        <v>Semendeferi_Damasio_2000_</v>
+        <v>Semendeferi_etal_1998_TABLE2</v>
       </c>
       <c r="L166" t="str">
         <f t="shared" si="34"/>
-        <v>10.1006%2Fjhev.1999.0381_</v>
+        <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L_TABLE2</v>
       </c>
       <c r="M166" t="str">
         <f t="array" ref="M166">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L166,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L_TABLE2.tsv</v>
+      </c>
+      <c r="N166" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="P166" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y166" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF166" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG166" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI166" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="AJ166" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AK166" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL166" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM166" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="167" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A167" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E167" t="str">
         <f t="shared" si="28"/>
-        <v>L</v>
+        <v>I</v>
       </c>
       <c r="F167" t="str">
         <f t="shared" si="29"/>
-        <v>Semendeferi_etal_1998</v>
+        <v>Semendeferi_etal_2001</v>
       </c>
       <c r="G167" t="str">
         <f t="shared" si="30"/>
@@ -15675,26 +15684,26 @@
       </c>
       <c r="I167" t="str">
         <f t="shared" si="32"/>
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="J167" t="str">
         <f t="shared" si="44"/>
-        <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L</v>
+        <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I</v>
       </c>
       <c r="K167" t="str">
         <f t="shared" si="35"/>
-        <v>Semendeferi_etal_1998_TABLE2</v>
+        <v>Semendeferi_etal_2001_TABLE2</v>
       </c>
       <c r="L167" t="str">
         <f t="shared" si="34"/>
-        <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L_TABLE2</v>
+        <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I_TABLE2</v>
       </c>
       <c r="M167" t="str">
         <f t="array" ref="M167">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L167,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L_TABLE2.tsv</v>
+        <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I_TABLE2.tsv</v>
       </c>
       <c r="N167" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="P167" s="1" t="s">
         <v>41</v>
@@ -15709,7 +15718,7 @@
         <v>112</v>
       </c>
       <c r="AI167" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="AJ167" s="1" t="s">
         <v>83</v>
@@ -15726,18 +15735,18 @@
     </row>
     <row r="168" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A168" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="E168" t="str">
         <f t="shared" si="28"/>
-        <v>I</v>
+        <v>4</v>
       </c>
       <c r="F168" t="str">
         <f t="shared" si="29"/>
-        <v>Semendeferi_etal_2001</v>
+        <v>Semendeferi_etal_2002</v>
       </c>
       <c r="G168" t="str">
         <f t="shared" si="30"/>
@@ -15749,29 +15758,26 @@
       </c>
       <c r="I168" t="str">
         <f t="shared" si="32"/>
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="J168" t="str">
         <f t="shared" si="44"/>
-        <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I</v>
+        <v>10.1038%2Fnn814</v>
       </c>
       <c r="K168" t="str">
         <f t="shared" si="35"/>
-        <v>Semendeferi_etal_2001_TABLE2</v>
+        <v>Semendeferi_etal_2002_Table1</v>
       </c>
       <c r="L168" t="str">
         <f t="shared" si="34"/>
-        <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I_TABLE2</v>
+        <v>10.1038%2Fnn814_Table1</v>
       </c>
       <c r="M168" t="str">
         <f t="array" ref="M168">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L168,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I_TABLE2.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N168" s="1" t="s">
-        <v>667</v>
-      </c>
-      <c r="P168" s="1" t="s">
-        <v>41</v>
+        <v>670</v>
       </c>
       <c r="Y168" s="1" t="s">
         <v>77</v>
@@ -15783,7 +15789,7 @@
         <v>112</v>
       </c>
       <c r="AI168" s="1" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="AJ168" s="1" t="s">
         <v>83</v>
@@ -15800,22 +15806,22 @@
     </row>
     <row r="169" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A169" s="1" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>75</v>
+        <v>673</v>
       </c>
       <c r="E169" t="str">
         <f t="shared" si="28"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F169" t="str">
         <f t="shared" si="29"/>
-        <v>Semendeferi_etal_2002</v>
+        <v>Seymour_etal_2015</v>
       </c>
       <c r="G169" t="str">
         <f t="shared" si="30"/>
-        <v>Semendeferi</v>
+        <v>Seymour</v>
       </c>
       <c r="H169" t="str">
         <f t="shared" si="31"/>
@@ -15823,58 +15829,31 @@
       </c>
       <c r="I169" t="str">
         <f t="shared" si="32"/>
-        <v>2002</v>
+        <v>2015</v>
       </c>
       <c r="J169" t="str">
         <f t="shared" si="44"/>
-        <v>10.1038%2Fnn814</v>
+        <v>10.1242%2Fjeb.124826</v>
       </c>
       <c r="K169" t="str">
         <f t="shared" si="35"/>
-        <v>Semendeferi_etal_2002_Table1</v>
+        <v>Seymour_etal_2015_TableS1</v>
       </c>
       <c r="L169" t="str">
         <f t="shared" si="34"/>
-        <v>10.1038%2Fnn814_Table1</v>
+        <v>10.1242%2Fjeb.124826_TableS1</v>
       </c>
       <c r="M169" t="str">
         <f t="array" ref="M169">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L169,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N169" s="1" t="s">
-        <v>670</v>
-      </c>
-      <c r="Y169" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AF169" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG169" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI169" s="1" t="s">
-        <v>671</v>
-      </c>
-      <c r="AJ169" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="AK169" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL169" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM169" s="1" t="s">
-        <v>84</v>
-      </c>
     </row>
     <row r="170" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A170" s="1" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>673</v>
+        <v>198</v>
       </c>
       <c r="E170" t="str">
         <f t="shared" si="28"/>
@@ -15882,7 +15861,7 @@
       </c>
       <c r="F170" t="str">
         <f t="shared" si="29"/>
-        <v>Seymour_etal_2015</v>
+        <v>Seymour_etal_2017</v>
       </c>
       <c r="G170" t="str">
         <f t="shared" si="30"/>
@@ -15894,39 +15873,39 @@
       </c>
       <c r="I170" t="str">
         <f t="shared" si="32"/>
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="J170" t="str">
         <f t="shared" si="44"/>
-        <v>10.1242%2Fjeb.124826</v>
+        <v>10.1098%2Frsos.170846</v>
       </c>
       <c r="K170" t="str">
         <f t="shared" si="35"/>
-        <v>Seymour_etal_2015_TableS1</v>
+        <v>Seymour_etal_2017_TableS1</v>
       </c>
       <c r="L170" t="str">
         <f t="shared" si="34"/>
-        <v>10.1242%2Fjeb.124826_TableS1</v>
+        <v>10.1098%2Frsos.170846_TableS1</v>
       </c>
       <c r="M170" t="str">
         <f t="array" ref="M170">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L170,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>10.1098%2Frsos.170846_TableS1.tsv</v>
       </c>
     </row>
     <row r="171" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A171" s="1" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>198</v>
+        <v>676</v>
       </c>
       <c r="E171" t="str">
         <f t="shared" si="28"/>
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F171" t="str">
         <f t="shared" si="29"/>
-        <v>Seymour_etal_2017</v>
+        <v>Seymour_etal_2019</v>
       </c>
       <c r="G171" t="str">
         <f t="shared" si="30"/>
@@ -15938,31 +15917,31 @@
       </c>
       <c r="I171" t="str">
         <f t="shared" si="32"/>
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="J171" t="str">
         <f t="shared" si="44"/>
-        <v>10.1098%2Frsos.170846</v>
+        <v>10.1098%2Frspb.2019.2208</v>
       </c>
       <c r="K171" t="str">
         <f t="shared" si="35"/>
-        <v>Seymour_etal_2017_TableS1</v>
+        <v>Seymour_etal_2019_rspb20192208si002</v>
       </c>
       <c r="L171" t="str">
         <f t="shared" si="34"/>
-        <v>10.1098%2Frsos.170846_TableS1</v>
+        <v>10.1098%2Frspb.2019.2208_rspb20192208si002</v>
       </c>
       <c r="M171" t="str">
         <f t="array" ref="M171">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L171,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1098%2Frsos.170846_TableS1.tsv</v>
+        <v>10.1098%2Frspb.2019.2208_rspb20192208si002.tsv</v>
       </c>
     </row>
     <row r="172" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A172" s="1" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="E172" t="str">
         <f t="shared" si="28"/>
@@ -15970,11 +15949,11 @@
       </c>
       <c r="F172" t="str">
         <f t="shared" si="29"/>
-        <v>Seymour_etal_2019</v>
+        <v>Sherwood_etal_2004</v>
       </c>
       <c r="G172" t="str">
         <f t="shared" si="30"/>
-        <v>Seymour</v>
+        <v>Sherwood</v>
       </c>
       <c r="H172" t="str">
         <f t="shared" si="31"/>
@@ -15982,31 +15961,50 @@
       </c>
       <c r="I172" t="str">
         <f t="shared" si="32"/>
-        <v>2019</v>
+        <v>2004</v>
       </c>
       <c r="J172" t="str">
         <f t="shared" si="44"/>
-        <v>10.1098%2Frspb.2019.2208</v>
+        <v>10.1002%2Fajp.20048</v>
       </c>
       <c r="K172" t="str">
         <f t="shared" si="35"/>
-        <v>Seymour_etal_2019_rspb20192208si002</v>
+        <v>Sherwood_etal_2004_TABLEI</v>
       </c>
       <c r="L172" t="str">
         <f t="shared" si="34"/>
-        <v>10.1098%2Frspb.2019.2208_rspb20192208si002</v>
+        <v>10.1002%2Fajp.20048_TABLEI</v>
       </c>
       <c r="M172" t="str">
         <f t="array" ref="M172">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L172,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1098%2Frspb.2019.2208_rspb20192208si002.tsv</v>
+        <v>10.1002%2Fajp.20048_TABLEI.tsv</v>
+      </c>
+      <c r="N172" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="Y172" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="Z172" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="AF172" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="AG172" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK172" s="1" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="173" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A173" s="1" t="s">
         <v>677</v>
       </c>
+      <c r="B173" s="6"/>
       <c r="D173" s="1" t="s">
-        <v>678</v>
+        <v>94</v>
       </c>
       <c r="E173" t="str">
         <f t="shared" si="28"/>
@@ -16034,18 +16032,18 @@
       </c>
       <c r="K173" t="str">
         <f t="shared" si="35"/>
-        <v>Sherwood_etal_2004_TABLEI</v>
+        <v>Sherwood_etal_2004_unpublishedviaDeCasien</v>
       </c>
       <c r="L173" t="str">
         <f t="shared" si="34"/>
-        <v>10.1002%2Fajp.20048_TABLEI</v>
+        <v>10.1002%2Fajp.20048_unpublishedviaDeCasien</v>
       </c>
       <c r="M173" t="str">
         <f t="array" ref="M173">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L173,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1002%2Fajp.20048_TABLEI.tsv</v>
-      </c>
-      <c r="N173" s="1" t="s">
-        <v>679</v>
+        <v>10.1002%2Fajp.20048_unpublishedviaDeCasien.tsv</v>
+      </c>
+      <c r="O173" s="1" t="s">
+        <v>95</v>
       </c>
       <c r="Y173" s="1" t="s">
         <v>680</v>
@@ -16065,19 +16063,19 @@
     </row>
     <row r="174" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A174" s="1" t="s">
-        <v>677</v>
+        <v>682</v>
       </c>
       <c r="B174" s="6"/>
       <c r="D174" s="1" t="s">
-        <v>94</v>
+        <v>75</v>
       </c>
       <c r="E174" t="str">
         <f t="shared" si="28"/>
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F174" t="str">
         <f t="shared" si="29"/>
-        <v>Sherwood_etal_2004</v>
+        <v>Sherwood_etal_2005</v>
       </c>
       <c r="G174" t="str">
         <f t="shared" si="30"/>
@@ -16089,58 +16087,75 @@
       </c>
       <c r="I174" t="str">
         <f t="shared" si="32"/>
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="J174" t="str">
         <f t="shared" si="44"/>
-        <v>10.1002%2Fajp.20048</v>
+        <v>10.1016%2Fj.jhevol.2004.10.003</v>
       </c>
       <c r="K174" t="str">
         <f t="shared" si="35"/>
-        <v>Sherwood_etal_2004_unpublishedviaDeCasien</v>
+        <v>Sherwood_etal_2005_Table1</v>
       </c>
       <c r="L174" t="str">
         <f t="shared" si="34"/>
-        <v>10.1002%2Fajp.20048_unpublishedviaDeCasien</v>
+        <v>10.1016%2Fj.jhevol.2004.10.003_Table1</v>
       </c>
       <c r="M174" t="str">
         <f t="array" ref="M174">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L174,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1002%2Fajp.20048_unpublishedviaDeCasien.tsv</v>
-      </c>
-      <c r="O174" s="1" t="s">
-        <v>95</v>
+        <v>10.1016%2Fj.jhevol.2004.10.003_Table1.tsv</v>
+      </c>
+      <c r="N174" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="V174" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y174" s="1" t="s">
-        <v>680</v>
+        <v>99</v>
       </c>
       <c r="Z174" s="1" t="s">
-        <v>681</v>
+        <v>233</v>
       </c>
       <c r="AF174" s="1" t="s">
-        <v>627</v>
+        <v>78</v>
       </c>
       <c r="AG174" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="AI174" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="AJ174" s="1" t="s">
+        <v>150</v>
+      </c>
       <c r="AK174" s="1" t="s">
         <v>63</v>
       </c>
+      <c r="AL174" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM174" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="175" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A175" s="1" t="s">
-        <v>682</v>
-      </c>
-      <c r="B175" s="6"/>
+        <v>685</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>686</v>
+      </c>
       <c r="D175" s="1" t="s">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="E175" t="str">
         <f t="shared" si="28"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F175" t="str">
         <f t="shared" si="29"/>
-        <v>Sherwood_etal_2005</v>
+        <v>Sherwood_etal_2004_I</v>
       </c>
       <c r="G175" t="str">
         <f t="shared" si="30"/>
@@ -16152,47 +16167,57 @@
       </c>
       <c r="I175" t="str">
         <f t="shared" si="32"/>
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="J175" t="str">
         <f t="shared" si="44"/>
-        <v>10.1016%2Fj.jhevol.2004.10.003</v>
+        <v>10.1159%2F000075672</v>
       </c>
       <c r="K175" t="str">
-        <f t="shared" si="35"/>
-        <v>Sherwood_etal_2005_Table1</v>
+        <f t="shared" ref="K175:K206" si="45">TRIM(_xlfn.TEXTJOIN("_",FALSE(),F175,(SUBSTITUTE(SUBSTITUTE(D175," ",""), "_", ""))))</f>
+        <v>Sherwood_etal_2004_I_Table4</v>
       </c>
       <c r="L175" t="str">
         <f t="shared" si="34"/>
-        <v>10.1016%2Fj.jhevol.2004.10.003_Table1</v>
+        <v>10.1159%2F000075672_Table4</v>
       </c>
       <c r="M175" t="str">
         <f t="array" ref="M175">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L175,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1016%2Fj.jhevol.2004.10.003_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N175" s="1" t="s">
-        <v>683</v>
+        <v>687</v>
+      </c>
+      <c r="P175" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="Q175" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="T175" s="1" t="str">
+        <f>IF(S175="N", R175, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U175" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="V175" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y175" s="1" t="s">
-        <v>99</v>
+        <v>688</v>
       </c>
       <c r="Z175" s="1" t="s">
-        <v>233</v>
+        <v>77</v>
       </c>
       <c r="AF175" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="AG175" s="1" t="s">
-        <v>112</v>
+      <c r="AH175" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="AI175" s="1" t="s">
-        <v>684</v>
+        <v>689</v>
       </c>
       <c r="AJ175" s="1" t="s">
-        <v>150</v>
+        <v>118</v>
       </c>
       <c r="AK175" s="1" t="s">
         <v>63</v>
@@ -16201,7 +16226,7 @@
         <v>63</v>
       </c>
       <c r="AM175" s="1" t="s">
-        <v>84</v>
+        <v>690</v>
       </c>
     </row>
     <row r="176" spans="1:39" x14ac:dyDescent="0.2">
@@ -16212,7 +16237,7 @@
         <v>686</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E176" t="str">
         <f t="shared" si="28"/>
@@ -16239,19 +16264,19 @@
         <v>10.1159%2F000075672</v>
       </c>
       <c r="K176" t="str">
-        <f t="shared" ref="K176:K207" si="45">TRIM(_xlfn.TEXTJOIN("_",FALSE(),F176,(SUBSTITUTE(SUBSTITUTE(D176," ",""), "_", ""))))</f>
-        <v>Sherwood_etal_2004_I_Table4</v>
+        <f t="shared" si="45"/>
+        <v>Sherwood_etal_2004_I_Table5</v>
       </c>
       <c r="L176" t="str">
         <f t="shared" si="34"/>
-        <v>10.1159%2F000075672_Table4</v>
+        <v>10.1159%2F000075672_Table5</v>
       </c>
       <c r="M176" t="str">
         <f t="array" ref="M176">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L176,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N176" s="1" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="P176" s="1" t="s">
         <v>632</v>
@@ -16270,11 +16295,14 @@
         <v>688</v>
       </c>
       <c r="Z176" s="1" t="s">
-        <v>77</v>
+        <v>233</v>
       </c>
       <c r="AF176" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="AG176" s="1" t="s">
+        <v>112</v>
+      </c>
       <c r="AH176" s="1" t="s">
         <v>177</v>
       </c>
@@ -16296,71 +16324,52 @@
     </row>
     <row r="177" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A177" s="1" t="s">
-        <v>685</v>
-      </c>
-      <c r="B177" s="4" t="s">
-        <v>686</v>
+        <v>692</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>693</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>68</v>
+        <v>694</v>
       </c>
       <c r="E177" t="str">
         <f t="shared" si="28"/>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="F177" t="str">
         <f t="shared" si="29"/>
-        <v>Sherwood_etal_2004_I</v>
+        <v>Smaers_Soligo_2013</v>
       </c>
       <c r="G177" t="str">
         <f t="shared" si="30"/>
-        <v>Sherwood</v>
+        <v>Smaers</v>
       </c>
       <c r="H177" t="str">
         <f t="shared" si="31"/>
-        <v>etal</v>
+        <v>Soligo</v>
       </c>
       <c r="I177" t="str">
         <f t="shared" si="32"/>
-        <v>2004</v>
+        <v>2013</v>
       </c>
       <c r="J177" t="str">
         <f t="shared" si="44"/>
-        <v>10.1159%2F000075672</v>
+        <v>10.1098%2Frspb.2013.0269</v>
       </c>
       <c r="K177" t="str">
         <f t="shared" si="45"/>
-        <v>Sherwood_etal_2004_I_Table5</v>
+        <v>Smaers_Soligo_2013_Supplement</v>
       </c>
       <c r="L177" t="str">
         <f t="shared" si="34"/>
-        <v>10.1159%2F000075672_Table5</v>
+        <v>10.1098%2Frspb.2013.0269_Supplement</v>
       </c>
       <c r="M177" t="str">
         <f t="array" ref="M177">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L177,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N177" s="1" t="s">
-        <v>691</v>
-      </c>
-      <c r="P177" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="Q177" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="T177" s="1" t="str">
-        <f>IF(S177="N", R177, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U177" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="V177" s="1" t="s">
-        <v>688</v>
-      </c>
-      <c r="Z177" s="1" t="s">
-        <v>233</v>
+        <v>695</v>
       </c>
       <c r="AF177" s="1" t="s">
         <v>78</v>
@@ -16368,42 +16377,33 @@
       <c r="AG177" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="AH177" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="AI177" s="1" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="AJ177" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AK177" s="1" t="s">
-        <v>63</v>
+        <v>697</v>
       </c>
       <c r="AL177" s="1" t="s">
-        <v>63</v>
+        <v>362</v>
       </c>
       <c r="AM177" s="1" t="s">
-        <v>690</v>
+        <v>84</v>
       </c>
     </row>
     <row r="178" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A178" s="1" t="s">
-        <v>692</v>
-      </c>
-      <c r="C178" s="1" t="s">
-        <v>693</v>
+        <v>698</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>694</v>
+        <v>699</v>
       </c>
       <c r="E178" t="str">
         <f t="shared" si="28"/>
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F178" t="str">
         <f t="shared" si="29"/>
-        <v>Smaers_Soligo_2013</v>
+        <v>Smaers_etal_2017</v>
       </c>
       <c r="G178" t="str">
         <f t="shared" si="30"/>
@@ -16411,30 +16411,48 @@
       </c>
       <c r="H178" t="str">
         <f t="shared" si="31"/>
-        <v>Soligo</v>
+        <v>etal</v>
       </c>
       <c r="I178" t="str">
         <f t="shared" si="32"/>
-        <v>2013</v>
+        <v>2017</v>
       </c>
       <c r="J178" t="str">
         <f t="shared" si="44"/>
-        <v>10.1098%2Frspb.2013.0269</v>
+        <v>10.1016%2Fj.cub.2017.01.020</v>
       </c>
       <c r="K178" t="str">
         <f t="shared" si="45"/>
-        <v>Smaers_Soligo_2013_Supplement</v>
+        <v>Smaers_etal_2017_TableS1part1</v>
       </c>
       <c r="L178" t="str">
         <f t="shared" si="34"/>
-        <v>10.1098%2Frspb.2013.0269_Supplement</v>
+        <v>10.1016%2Fj.cub.2017.01.020_TableS1part1</v>
       </c>
       <c r="M178" t="str">
         <f t="array" ref="M178">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L178,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>10.1016%2Fj.cub.2017.01.020_TableS1part1.tsv</v>
       </c>
       <c r="N178" s="1" t="s">
-        <v>695</v>
+        <v>700</v>
+      </c>
+      <c r="O178" s="1" t="s">
+        <v>701</v>
+      </c>
+      <c r="P178" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V178" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y178" s="1" t="s">
+        <v>702</v>
+      </c>
+      <c r="Z178" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AC178" s="1" t="s">
+        <v>703</v>
       </c>
       <c r="AF178" s="1" t="s">
         <v>78</v>
@@ -16443,10 +16461,13 @@
         <v>112</v>
       </c>
       <c r="AI178" s="1" t="s">
-        <v>696</v>
+        <v>704</v>
       </c>
       <c r="AJ178" s="1" t="s">
-        <v>697</v>
+        <v>118</v>
+      </c>
+      <c r="AK178" s="1" t="s">
+        <v>705</v>
       </c>
       <c r="AL178" s="1" t="s">
         <v>362</v>
@@ -16460,7 +16481,7 @@
         <v>698</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="E179" t="str">
         <f t="shared" si="28"/>
@@ -16488,21 +16509,21 @@
       </c>
       <c r="K179" t="str">
         <f t="shared" si="45"/>
-        <v>Smaers_etal_2017_TableS1part1</v>
+        <v>Smaers_etal_2017_TableS1part2</v>
       </c>
       <c r="L179" t="str">
         <f t="shared" si="34"/>
-        <v>10.1016%2Fj.cub.2017.01.020_TableS1part1</v>
+        <v>10.1016%2Fj.cub.2017.01.020_TableS1part2</v>
       </c>
       <c r="M179" t="str">
         <f t="array" ref="M179">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L179,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1016%2Fj.cub.2017.01.020_TableS1part1.tsv</v>
+        <v>10.1016%2Fj.cub.2017.01.020_TableS1part2.tsv</v>
       </c>
       <c r="N179" s="1" t="s">
         <v>700</v>
       </c>
       <c r="O179" s="1" t="s">
-        <v>701</v>
+        <v>707</v>
       </c>
       <c r="P179" s="1" t="s">
         <v>41</v>
@@ -16543,18 +16564,18 @@
     </row>
     <row r="180" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A180" s="1" t="s">
-        <v>698</v>
+        <v>708</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E180" t="str">
         <f t="shared" si="28"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F180" t="str">
         <f t="shared" si="29"/>
-        <v>Smaers_etal_2017</v>
+        <v>Smaers_etal_2011</v>
       </c>
       <c r="G180" t="str">
         <f t="shared" si="30"/>
@@ -16566,45 +16587,33 @@
       </c>
       <c r="I180" t="str">
         <f t="shared" si="32"/>
-        <v>2017</v>
+        <v>2011</v>
       </c>
       <c r="J180" t="str">
         <f t="shared" si="44"/>
-        <v>10.1016%2Fj.cub.2017.01.020</v>
+        <v>10.1159%2F000323671</v>
       </c>
       <c r="K180" t="str">
         <f t="shared" si="45"/>
-        <v>Smaers_etal_2017_TableS1part2</v>
+        <v>Smaers_etal_2011_SupplementaryTable1</v>
       </c>
       <c r="L180" t="str">
         <f t="shared" si="34"/>
-        <v>10.1016%2Fj.cub.2017.01.020_TableS1part2</v>
+        <v>10.1159%2F000323671_SupplementaryTable1</v>
       </c>
       <c r="M180" t="str">
         <f t="array" ref="M180">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L180,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1016%2Fj.cub.2017.01.020_TableS1part2.tsv</v>
-      </c>
-      <c r="N180" s="1" t="s">
-        <v>700</v>
-      </c>
-      <c r="O180" s="1" t="s">
-        <v>707</v>
-      </c>
-      <c r="P180" s="1" t="s">
-        <v>41</v>
+        <v>notfound</v>
+      </c>
+      <c r="Q180" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="V180" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="Y180" s="1" t="s">
-        <v>702</v>
-      </c>
       <c r="Z180" s="1" t="s">
         <v>233</v>
       </c>
-      <c r="AC180" s="1" t="s">
-        <v>703</v>
-      </c>
       <c r="AF180" s="1" t="s">
         <v>78</v>
       </c>
@@ -16612,13 +16621,10 @@
         <v>112</v>
       </c>
       <c r="AI180" s="1" t="s">
-        <v>704</v>
+        <v>710</v>
       </c>
       <c r="AJ180" s="1" t="s">
         <v>118</v>
-      </c>
-      <c r="AK180" s="1" t="s">
-        <v>705</v>
       </c>
       <c r="AL180" s="1" t="s">
         <v>362</v>
@@ -16632,7 +16638,7 @@
         <v>708</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="E181" t="str">
         <f t="shared" si="28"/>
@@ -16660,11 +16666,11 @@
       </c>
       <c r="K181" t="str">
         <f t="shared" si="45"/>
-        <v>Smaers_etal_2011_SupplementaryTable1</v>
+        <v>Smaers_etal_2011_SupplementaryTable2</v>
       </c>
       <c r="L181" t="str">
         <f t="shared" si="34"/>
-        <v>10.1159%2F000323671_SupplementaryTable1</v>
+        <v>10.1159%2F000323671_SupplementaryTable2</v>
       </c>
       <c r="M181" t="str">
         <f t="array" ref="M181">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L181,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -16700,18 +16706,21 @@
     </row>
     <row r="182" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A182" s="1" t="s">
-        <v>708</v>
+        <v>712</v>
+      </c>
+      <c r="C182" s="1" t="s">
+        <v>713</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="E182" t="str">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="F182" t="str">
         <f t="shared" si="29"/>
-        <v>Smaers_etal_2011</v>
+        <v>Smaers_etal_2018</v>
       </c>
       <c r="G182" t="str">
         <f t="shared" si="30"/>
@@ -16723,29 +16732,26 @@
       </c>
       <c r="I182" t="str">
         <f t="shared" si="32"/>
-        <v>2011</v>
+        <v>2018</v>
       </c>
       <c r="J182" t="str">
         <f t="shared" si="44"/>
-        <v>10.1159%2F000323671</v>
+        <v>10.7554%2FeLife.35696</v>
       </c>
       <c r="K182" t="str">
         <f t="shared" si="45"/>
-        <v>Smaers_etal_2011_SupplementaryTable2</v>
+        <v>Smaers_etal_2018_Figure2-data1</v>
       </c>
       <c r="L182" t="str">
         <f t="shared" si="34"/>
-        <v>10.1159%2F000323671_SupplementaryTable2</v>
+        <v>10.7554%2FeLife.35696_Figure2-data1</v>
       </c>
       <c r="M182" t="str">
         <f t="array" ref="M182">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L182,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="Q182" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="V182" s="1" t="s">
-        <v>42</v>
+      <c r="N182" s="1" t="s">
+        <v>715</v>
       </c>
       <c r="Z182" s="1" t="s">
         <v>233</v>
@@ -16757,10 +16763,10 @@
         <v>112</v>
       </c>
       <c r="AI182" s="1" t="s">
-        <v>710</v>
+        <v>716</v>
       </c>
       <c r="AJ182" s="1" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="AL182" s="1" t="s">
         <v>362</v>
@@ -16771,25 +16777,25 @@
     </row>
     <row r="183" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A183" s="1" t="s">
-        <v>712</v>
+        <v>717</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>713</v>
+        <v>718</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>714</v>
+        <v>75</v>
       </c>
       <c r="E183" t="str">
         <f t="shared" si="28"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F183" t="str">
         <f t="shared" si="29"/>
-        <v>Smaers_etal_2018</v>
+        <v>Stephan_etal_1982</v>
       </c>
       <c r="G183" t="str">
         <f t="shared" si="30"/>
-        <v>Smaers</v>
+        <v>Stephan</v>
       </c>
       <c r="H183" t="str">
         <f t="shared" si="31"/>
@@ -16797,29 +16803,41 @@
       </c>
       <c r="I183" t="str">
         <f t="shared" si="32"/>
-        <v>2018</v>
+        <v>1982</v>
       </c>
       <c r="J183" t="str">
         <f t="shared" si="44"/>
-        <v>10.7554%2FeLife.35696</v>
+        <v>PMID%3A7161483</v>
       </c>
       <c r="K183" t="str">
         <f t="shared" si="45"/>
-        <v>Smaers_etal_2018_Figure2-data1</v>
+        <v>Stephan_etal_1982_Table1</v>
       </c>
       <c r="L183" t="str">
         <f t="shared" si="34"/>
-        <v>10.7554%2FeLife.35696_Figure2-data1</v>
+        <v>PMID%3A7161483_Table1</v>
       </c>
       <c r="M183" t="str">
         <f t="array" ref="M183">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L183,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N183" s="1" t="s">
-        <v>715</v>
+        <v>719</v>
+      </c>
+      <c r="P183" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="V183" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="W183" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="Y183" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="Z183" s="1" t="s">
-        <v>233</v>
+        <v>99</v>
       </c>
       <c r="AF183" s="1" t="s">
         <v>78</v>
@@ -16828,13 +16846,16 @@
         <v>112</v>
       </c>
       <c r="AI183" s="1" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="AJ183" s="1" t="s">
-        <v>140</v>
+        <v>101</v>
+      </c>
+      <c r="AK183" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="AL183" s="1" t="s">
-        <v>362</v>
+        <v>63</v>
       </c>
       <c r="AM183" s="1" t="s">
         <v>84</v>
@@ -16842,21 +16863,21 @@
     </row>
     <row r="184" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A184" s="1" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="C184" s="1" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="E184" t="str">
         <f t="shared" si="28"/>
-        <v>3</v>
+        <v>.</v>
       </c>
       <c r="F184" t="str">
         <f t="shared" si="29"/>
-        <v>Stephan_etal_1982</v>
+        <v>Stephan_etal_1988</v>
       </c>
       <c r="G184" t="str">
         <f t="shared" si="30"/>
@@ -16868,81 +16889,45 @@
       </c>
       <c r="I184" t="str">
         <f t="shared" si="32"/>
-        <v>1982</v>
+        <v>1988</v>
       </c>
       <c r="J184" t="str">
         <f t="shared" si="44"/>
-        <v>PMID%3A7161483</v>
+        <v>ISBN%3A0845140000</v>
       </c>
       <c r="K184" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1982_Table1</v>
+        <v>Stephan_etal_1988_TABLE1</v>
       </c>
       <c r="L184" t="str">
         <f t="shared" si="34"/>
-        <v>PMID%3A7161483_Table1</v>
+        <v>ISBN%3A0845140000_TABLE1</v>
       </c>
       <c r="M184" t="str">
         <f t="array" ref="M184">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L184,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N184" s="1" t="s">
-        <v>719</v>
-      </c>
-      <c r="P184" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V184" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="W184" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="Y184" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z184" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF184" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG184" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI184" s="1" t="s">
-        <v>720</v>
-      </c>
-      <c r="AJ184" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK184" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL184" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM184" s="1" t="s">
-        <v>84</v>
+        <v>723</v>
       </c>
     </row>
     <row r="185" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A185" s="1" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="D185" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E185" t="str">
         <f t="shared" si="28"/>
-        <v>.</v>
+        <v>s</v>
       </c>
       <c r="F185" t="str">
         <f t="shared" si="29"/>
-        <v>Stephan_etal_1988</v>
+        <v>Stephan_etal_1970</v>
       </c>
       <c r="G185" t="str">
         <f t="shared" si="30"/>
@@ -16954,26 +16939,47 @@
       </c>
       <c r="I185" t="str">
         <f t="shared" si="32"/>
-        <v>1988</v>
+        <v>1970</v>
       </c>
       <c r="J185" t="str">
         <f t="shared" si="44"/>
-        <v>ISBN%3A0845140000</v>
+        <v>ISBN%3A0390672505</v>
       </c>
       <c r="K185" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1988_TABLE1</v>
+        <v>Stephan_etal_1970_TABLE1</v>
       </c>
       <c r="L185" t="str">
         <f t="shared" si="34"/>
-        <v>ISBN%3A0845140000_TABLE1</v>
+        <v>ISBN%3A0390672505_TABLE1</v>
       </c>
       <c r="M185" t="str">
         <f t="array" ref="M185">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L185,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N185" s="1" t="s">
-        <v>723</v>
+        <v>726</v>
+      </c>
+      <c r="V185" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z185" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF185" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG185" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ185" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="AL185" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM185" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="186" spans="1:39" x14ac:dyDescent="0.2">
@@ -16984,7 +16990,7 @@
         <v>725</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>49</v>
+        <v>92</v>
       </c>
       <c r="E186" t="str">
         <f t="shared" si="28"/>
@@ -17012,18 +17018,18 @@
       </c>
       <c r="K186" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1970_TABLE1</v>
+        <v>Stephan_etal_1970_TABLE2</v>
       </c>
       <c r="L186" t="str">
         <f t="shared" si="34"/>
-        <v>ISBN%3A0390672505_TABLE1</v>
+        <v>ISBN%3A0390672505_TABLE2</v>
       </c>
       <c r="M186" t="str">
         <f t="array" ref="M186">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L186,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N186" s="1" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="V186" s="1" t="s">
         <v>42</v>
@@ -17038,7 +17044,7 @@
         <v>112</v>
       </c>
       <c r="AJ186" s="1" t="s">
-        <v>727</v>
+        <v>118</v>
       </c>
       <c r="AL186" s="1" t="s">
         <v>63</v>
@@ -17055,7 +17061,7 @@
         <v>725</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>92</v>
+        <v>729</v>
       </c>
       <c r="E187" t="str">
         <f t="shared" si="28"/>
@@ -17083,18 +17089,18 @@
       </c>
       <c r="K187" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1970_TABLE2</v>
+        <v>Stephan_etal_1970_TABLE3</v>
       </c>
       <c r="L187" t="str">
         <f t="shared" si="34"/>
-        <v>ISBN%3A0390672505_TABLE2</v>
+        <v>ISBN%3A0390672505_TABLE3</v>
       </c>
       <c r="M187" t="str">
         <f t="array" ref="M187">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L187,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N187" s="1" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="V187" s="1" t="s">
         <v>42</v>
@@ -17126,7 +17132,7 @@
         <v>725</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="E188" t="str">
         <f t="shared" si="28"/>
@@ -17149,79 +17155,8 @@
         <v>1970</v>
       </c>
       <c r="J188" t="str">
-        <f t="shared" si="44"/>
-        <v>ISBN%3A0390672505</v>
-      </c>
-      <c r="K188" t="str">
-        <f t="shared" si="45"/>
-        <v>Stephan_etal_1970_TABLE3</v>
-      </c>
-      <c r="L188" t="str">
-        <f t="shared" si="34"/>
-        <v>ISBN%3A0390672505_TABLE3</v>
-      </c>
-      <c r="M188" t="str">
-        <f t="array" ref="M188">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L188,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N188" s="1" t="s">
-        <v>730</v>
-      </c>
-      <c r="V188" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Z188" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF188" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG188" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AJ188" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="AL188" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM188" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="189" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A189" s="1" t="s">
-        <v>724</v>
-      </c>
-      <c r="C189" s="1" t="s">
-        <v>725</v>
-      </c>
-      <c r="D189" s="1" t="s">
-        <v>731</v>
-      </c>
-      <c r="E189" t="str">
-        <f t="shared" si="28"/>
-        <v>s</v>
-      </c>
-      <c r="F189" t="str">
-        <f t="shared" si="29"/>
-        <v>Stephan_etal_1970</v>
-      </c>
-      <c r="G189" t="str">
-        <f t="shared" si="30"/>
-        <v>Stephan</v>
-      </c>
-      <c r="H189" t="str">
-        <f t="shared" si="31"/>
-        <v>etal</v>
-      </c>
-      <c r="I189" t="str">
-        <f t="shared" si="32"/>
-        <v>1970</v>
-      </c>
-      <c r="J189" t="str">
-        <f t="shared" ref="J189:J224" si="46">_xlfn.LET(
-_xlpm.doi,IF(C189&lt;&gt;"",C189,_xlfn.TEXTAFTER(A189,"https://doi.org/")),
+        <f t="shared" ref="J188:J222" si="46">_xlfn.LET(
+_xlpm.doi,IF(C188&lt;&gt;"",C188,_xlfn.TEXTAFTER(A188,"https://doi.org/")),
 SUBSTITUTE(
 SUBSTITUTE(
 SUBSTITUTE(
@@ -17234,20 +17169,91 @@
 )</f>
         <v>ISBN%3A0390672505</v>
       </c>
+      <c r="K188" t="str">
+        <f t="shared" si="45"/>
+        <v>Stephan_etal_1970_TABLE4</v>
+      </c>
+      <c r="L188" t="str">
+        <f t="shared" si="34"/>
+        <v>ISBN%3A0390672505_TABLE4</v>
+      </c>
+      <c r="M188" t="str">
+        <f t="array" ref="M188">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L188,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
+        <v>notfound</v>
+      </c>
+      <c r="N188" s="1" t="s">
+        <v>732</v>
+      </c>
+      <c r="V188" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z188" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF188" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG188" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AJ188" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="AL188" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM188" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="189" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A189" s="1" t="s">
+        <v>724</v>
+      </c>
+      <c r="C189" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>733</v>
+      </c>
+      <c r="E189" t="str">
+        <f t="shared" si="28"/>
+        <v>s</v>
+      </c>
+      <c r="F189" t="str">
+        <f t="shared" si="29"/>
+        <v>Stephan_etal_1970</v>
+      </c>
+      <c r="G189" t="str">
+        <f t="shared" si="30"/>
+        <v>Stephan</v>
+      </c>
+      <c r="H189" t="str">
+        <f t="shared" si="31"/>
+        <v>etal</v>
+      </c>
+      <c r="I189" t="str">
+        <f t="shared" si="32"/>
+        <v>1970</v>
+      </c>
+      <c r="J189" t="str">
+        <f t="shared" si="46"/>
+        <v>ISBN%3A0390672505</v>
+      </c>
       <c r="K189" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1970_TABLE4</v>
+        <v>Stephan_etal_1970_TABLE5</v>
       </c>
       <c r="L189" t="str">
         <f t="shared" si="34"/>
-        <v>ISBN%3A0390672505_TABLE4</v>
+        <v>ISBN%3A0390672505_TABLE5</v>
       </c>
       <c r="M189" t="str">
         <f t="array" ref="M189">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L189,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N189" s="1" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="V189" s="1" t="s">
         <v>42</v>
@@ -17262,7 +17268,7 @@
         <v>112</v>
       </c>
       <c r="AJ189" s="1" t="s">
-        <v>727</v>
+        <v>118</v>
       </c>
       <c r="AL189" s="1" t="s">
         <v>63</v>
@@ -17279,7 +17285,7 @@
         <v>725</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="E190" t="str">
         <f t="shared" si="28"/>
@@ -17307,18 +17313,18 @@
       </c>
       <c r="K190" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1970_TABLE5</v>
+        <v>Stephan_etal_1970_TABLE6</v>
       </c>
       <c r="L190" t="str">
         <f t="shared" si="34"/>
-        <v>ISBN%3A0390672505_TABLE5</v>
+        <v>ISBN%3A0390672505_TABLE6</v>
       </c>
       <c r="M190" t="str">
         <f t="array" ref="M190">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L190,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N190" s="1" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="V190" s="1" t="s">
         <v>42</v>
@@ -17350,7 +17356,7 @@
         <v>725</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="E191" t="str">
         <f t="shared" si="28"/>
@@ -17378,21 +17384,27 @@
       </c>
       <c r="K191" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1970_TABLE6</v>
+        <v>Stephan_etal_1970_Tables1-6</v>
       </c>
       <c r="L191" t="str">
         <f t="shared" si="34"/>
-        <v>ISBN%3A0390672505_TABLE6</v>
+        <v>ISBN%3A0390672505_Tables1-6</v>
       </c>
       <c r="M191" t="str">
         <f t="array" ref="M191">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L191,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N191" s="1" t="s">
-        <v>736</v>
+      <c r="O191" s="1" t="s">
+        <v>738</v>
+      </c>
+      <c r="P191" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V191" s="1" t="s">
-        <v>42</v>
+        <v>688</v>
+      </c>
+      <c r="Y191" s="1" t="s">
+        <v>99</v>
       </c>
       <c r="Z191" s="1" t="s">
         <v>99</v>
@@ -17404,7 +17416,7 @@
         <v>112</v>
       </c>
       <c r="AJ191" s="1" t="s">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="AL191" s="1" t="s">
         <v>63</v>
@@ -17415,21 +17427,21 @@
     </row>
     <row r="192" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A192" s="1" t="s">
-        <v>724</v>
+        <v>739</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>725</v>
+        <v>740</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>737</v>
+        <v>75</v>
       </c>
       <c r="E192" t="str">
         <f t="shared" si="28"/>
-        <v>s</v>
+        <v>4</v>
       </c>
       <c r="F192" t="str">
         <f t="shared" si="29"/>
-        <v>Stephan_etal_1970</v>
+        <v>Stephan_etal_1984</v>
       </c>
       <c r="G192" t="str">
         <f t="shared" si="30"/>
@@ -17441,32 +17453,35 @@
       </c>
       <c r="I192" t="str">
         <f t="shared" si="32"/>
-        <v>1970</v>
+        <v>1984</v>
       </c>
       <c r="J192" t="str">
         <f t="shared" si="46"/>
-        <v>ISBN%3A0390672505</v>
+        <v>PMID%3A6481154</v>
       </c>
       <c r="K192" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1970_Tables1-6</v>
+        <v>Stephan_etal_1984_Table1</v>
       </c>
       <c r="L192" t="str">
         <f t="shared" si="34"/>
-        <v>ISBN%3A0390672505_Tables1-6</v>
+        <v>PMID%3A6481154_Table1</v>
       </c>
       <c r="M192" t="str">
         <f t="array" ref="M192">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L192,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="O192" s="1" t="s">
-        <v>738</v>
+      <c r="N192" s="1" t="s">
+        <v>741</v>
       </c>
       <c r="P192" s="1" t="s">
         <v>41</v>
       </c>
       <c r="V192" s="1" t="s">
-        <v>688</v>
+        <v>42</v>
+      </c>
+      <c r="W192" s="1" t="s">
+        <v>104</v>
       </c>
       <c r="Y192" s="1" t="s">
         <v>99</v>
@@ -17480,9 +17495,15 @@
       <c r="AG192" s="1" t="s">
         <v>112</v>
       </c>
+      <c r="AI192" s="1" t="s">
+        <v>742</v>
+      </c>
       <c r="AJ192" s="1" t="s">
         <v>101</v>
       </c>
+      <c r="AK192" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="AL192" s="1" t="s">
         <v>63</v>
       </c>
@@ -17492,21 +17513,21 @@
     </row>
     <row r="193" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A193" s="1" t="s">
-        <v>739</v>
-      </c>
-      <c r="C193" s="1" t="s">
-        <v>740</v>
+        <v>743</v>
+      </c>
+      <c r="C193" s="4" t="s">
+        <v>744</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>75</v>
       </c>
       <c r="E193" t="str">
         <f t="shared" si="28"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F193" t="str">
         <f t="shared" si="29"/>
-        <v>Stephan_etal_1984</v>
+        <v>Stephan_etal_1987</v>
       </c>
       <c r="G193" t="str">
         <f t="shared" si="30"/>
@@ -17518,26 +17539,26 @@
       </c>
       <c r="I193" t="str">
         <f t="shared" si="32"/>
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="J193" t="str">
         <f t="shared" si="46"/>
-        <v>PMID%3A6481154</v>
+        <v>PMID%3A3693895</v>
       </c>
       <c r="K193" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1984_Table1</v>
+        <v>Stephan_etal_1987_Table1</v>
       </c>
       <c r="L193" t="str">
         <f t="shared" si="34"/>
-        <v>PMID%3A6481154_Table1</v>
+        <v>PMID%3A3693895_Table1</v>
       </c>
       <c r="M193" t="str">
         <f t="array" ref="M193">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L193,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N193" s="1" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="P193" s="1" t="s">
         <v>41</v>
@@ -17561,7 +17582,7 @@
         <v>112</v>
       </c>
       <c r="AI193" s="1" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="AJ193" s="1" t="s">
         <v>101</v>
@@ -17578,21 +17599,18 @@
     </row>
     <row r="194" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A194" s="1" t="s">
-        <v>743</v>
-      </c>
-      <c r="C194" s="4" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>75</v>
+        <v>353</v>
       </c>
       <c r="E194" t="str">
         <f t="shared" si="28"/>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F194" t="str">
         <f t="shared" si="29"/>
-        <v>Stephan_etal_1987</v>
+        <v>Stephan_etal_1981</v>
       </c>
       <c r="G194" t="str">
         <f t="shared" si="30"/>
@@ -17604,36 +17622,30 @@
       </c>
       <c r="I194" t="str">
         <f t="shared" si="32"/>
-        <v>1987</v>
+        <v>1981</v>
       </c>
       <c r="J194" t="str">
         <f t="shared" si="46"/>
-        <v>PMID%3A3693895</v>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K194" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1987_Table1</v>
+        <v>Stephan_etal_1981_TableI</v>
       </c>
       <c r="L194" t="str">
         <f t="shared" si="34"/>
-        <v>PMID%3A3693895_Table1</v>
+        <v>10.1159%2F000155963_TableI</v>
       </c>
       <c r="M194" t="str">
         <f t="array" ref="M194">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L194,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>10.1159%2F000155963_TableI.tsv</v>
       </c>
       <c r="N194" s="1" t="s">
-        <v>745</v>
-      </c>
-      <c r="P194" s="1" t="s">
-        <v>41</v>
+        <v>748</v>
       </c>
       <c r="V194" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="W194" s="1" t="s">
-        <v>104</v>
-      </c>
       <c r="Y194" s="1" t="s">
         <v>99</v>
       </c>
@@ -17647,7 +17659,7 @@
         <v>112</v>
       </c>
       <c r="AI194" s="1" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="AJ194" s="1" t="s">
         <v>101</v>
@@ -17667,108 +17679,108 @@
         <v>747</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>353</v>
+        <v>750</v>
       </c>
       <c r="E195" t="str">
-        <f t="shared" si="28"/>
+        <f t="shared" ref="E195:E222" si="47">RIGHT(A195,1)</f>
         <v>3</v>
       </c>
       <c r="F195" t="str">
-        <f t="shared" si="29"/>
+        <f t="shared" ref="F195:F222" si="48">G195 &amp; IF(H195&lt;&gt;"", "_" &amp; H195, "_") &amp; IF(I195&lt;&gt;"", "_" &amp; I195, "_") &amp; IF(B195&lt;&gt;"", "_" &amp; B195, "")</f>
         <v>Stephan_etal_1981</v>
       </c>
       <c r="G195" t="str">
-        <f t="shared" si="30"/>
+        <f t="shared" ref="G195:G222" si="49">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A195,","), "-", ""), " ", "")</f>
         <v>Stephan</v>
       </c>
       <c r="H195" t="str">
-        <f t="shared" si="31"/>
-        <v>etal</v>
-      </c>
-      <c r="I195" t="str">
-        <f t="shared" si="32"/>
-        <v>1981</v>
-      </c>
-      <c r="J195" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1159%2F000155963</v>
-      </c>
-      <c r="K195" t="str">
-        <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableI</v>
-      </c>
-      <c r="L195" t="str">
-        <f t="shared" si="34"/>
-        <v>10.1159%2F000155963_TableI</v>
-      </c>
-      <c r="M195" t="str">
-        <f t="array" ref="M195">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L195,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableI.tsv</v>
-      </c>
-      <c r="N195" s="1" t="s">
-        <v>748</v>
-      </c>
-      <c r="V195" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y195" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z195" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF195" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG195" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI195" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="AJ195" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK195" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL195" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM195" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="196" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A196" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="D196" s="1" t="s">
-        <v>750</v>
-      </c>
-      <c r="E196" t="str">
-        <f t="shared" ref="E196:E224" si="47">RIGHT(A196,1)</f>
-        <v>3</v>
-      </c>
-      <c r="F196" t="str">
-        <f t="shared" ref="F196:F224" si="48">G196 &amp; IF(H196&lt;&gt;"", "_" &amp; H196, "_") &amp; IF(I196&lt;&gt;"", "_" &amp; I196, "_") &amp; IF(B196&lt;&gt;"", "_" &amp; B196, "")</f>
-        <v>Stephan_etal_1981</v>
-      </c>
-      <c r="G196" t="str">
-        <f t="shared" ref="G196:G224" si="49">SUBSTITUTE(SUBSTITUTE(_xlfn.TEXTBEFORE(A196,","), "-", ""), " ", "")</f>
-        <v>Stephan</v>
-      </c>
-      <c r="H196" t="str">
-        <f t="shared" ref="H196:H224" si="50">_xlfn.LET(
-_xlpm.authors,_xlfn.TEXTBEFORE(A196," ("&amp;I196&amp;")"),
+        <f t="shared" ref="H195:H222" si="50">_xlfn.LET(
+_xlpm.authors,_xlfn.TEXTBEFORE(A195," ("&amp;I195&amp;")"),
 _xlpm.hasAmp,ISNUMBER(SEARCH("&amp;",_xlpm.authors)),
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
         <v>etal</v>
       </c>
+      <c r="I195" t="str">
+        <f t="shared" ref="I195:I222" si="51">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A195, "("), ")")</f>
+        <v>1981</v>
+      </c>
+      <c r="J195" t="str">
+        <f t="shared" si="46"/>
+        <v>10.1159%2F000155963</v>
+      </c>
+      <c r="K195" t="str">
+        <f t="shared" si="45"/>
+        <v>Stephan_etal_1981_TableII</v>
+      </c>
+      <c r="L195" t="str">
+        <f t="shared" ref="L195:L222" si="52">J195 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D195,CHAR(160),"")," ",""),"_","")</f>
+        <v>10.1159%2F000155963_TableII</v>
+      </c>
+      <c r="M195" t="str">
+        <f t="array" ref="M195">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L195,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
+        <v>10.1159%2F000155963_TableII.tsv</v>
+      </c>
+      <c r="N195" s="1" t="s">
+        <v>751</v>
+      </c>
+      <c r="V195" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y195" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z195" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF195" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG195" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI195" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="AJ195" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK195" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL195" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM195" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="196" spans="1:39" x14ac:dyDescent="0.2">
+      <c r="A196" s="1" t="s">
+        <v>747</v>
+      </c>
+      <c r="D196" s="1" t="s">
+        <v>752</v>
+      </c>
+      <c r="E196" t="str">
+        <f t="shared" si="47"/>
+        <v>3</v>
+      </c>
+      <c r="F196" t="str">
+        <f t="shared" si="48"/>
+        <v>Stephan_etal_1981</v>
+      </c>
+      <c r="G196" t="str">
+        <f t="shared" si="49"/>
+        <v>Stephan</v>
+      </c>
+      <c r="H196" t="str">
+        <f t="shared" si="50"/>
+        <v>etal</v>
+      </c>
       <c r="I196" t="str">
-        <f t="shared" ref="I196:I224" si="51">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A196, "("), ")")</f>
+        <f t="shared" si="51"/>
         <v>1981</v>
       </c>
       <c r="J196" t="str">
@@ -17777,18 +17789,18 @@
       </c>
       <c r="K196" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableII</v>
+        <v>Stephan_etal_1981_TableIII</v>
       </c>
       <c r="L196" t="str">
-        <f t="shared" ref="L196:L224" si="52">J196 &amp; "_" &amp; SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(D196,CHAR(160),"")," ",""),"_","")</f>
-        <v>10.1159%2F000155963_TableII</v>
+        <f t="shared" si="52"/>
+        <v>10.1159%2F000155963_TableIII</v>
       </c>
       <c r="M196" t="str">
         <f t="array" ref="M196">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L196,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableII.tsv</v>
+        <v>10.1159%2F000155963_TableIII.tsv</v>
       </c>
       <c r="N196" s="1" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="V196" s="1" t="s">
         <v>42</v>
@@ -17826,7 +17838,7 @@
         <v>747</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="E197" t="str">
         <f t="shared" si="47"/>
@@ -17854,18 +17866,18 @@
       </c>
       <c r="K197" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableIII</v>
+        <v>Stephan_etal_1981_TableIV</v>
       </c>
       <c r="L197" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableIII</v>
+        <v>10.1159%2F000155963_TableIV</v>
       </c>
       <c r="M197" t="str">
         <f t="array" ref="M197">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L197,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableIII.tsv</v>
+        <v>10.1159%2F000155963_TableIV.tsv</v>
       </c>
       <c r="N197" s="1" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="V197" s="1" t="s">
         <v>42</v>
@@ -17903,7 +17915,7 @@
         <v>747</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="E198" t="str">
         <f t="shared" si="47"/>
@@ -17931,18 +17943,18 @@
       </c>
       <c r="K198" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableIV</v>
+        <v>Stephan_etal_1981_TableV</v>
       </c>
       <c r="L198" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableIV</v>
+        <v>10.1159%2F000155963_TableV</v>
       </c>
       <c r="M198" t="str">
         <f t="array" ref="M198">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L198,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableIV.tsv</v>
+        <v>10.1159%2F000155963_TableV.tsv</v>
       </c>
       <c r="N198" s="1" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="V198" s="1" t="s">
         <v>42</v>
@@ -17980,7 +17992,7 @@
         <v>747</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="E199" t="str">
         <f t="shared" si="47"/>
@@ -18008,18 +18020,18 @@
       </c>
       <c r="K199" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableV</v>
+        <v>Stephan_etal_1981_TableVI</v>
       </c>
       <c r="L199" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableV</v>
+        <v>10.1159%2F000155963_TableVI</v>
       </c>
       <c r="M199" t="str">
         <f t="array" ref="M199">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L199,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableV.tsv</v>
+        <v>10.1159%2F000155963_TableVI.tsv</v>
       </c>
       <c r="N199" s="1" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="V199" s="1" t="s">
         <v>42</v>
@@ -18056,8 +18068,9 @@
       <c r="A200" s="1" t="s">
         <v>747</v>
       </c>
+      <c r="C200" s="7"/>
       <c r="D200" s="1" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="E200" t="str">
         <f t="shared" si="47"/>
@@ -18085,18 +18098,18 @@
       </c>
       <c r="K200" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableVI</v>
+        <v>Stephan_etal_1981_TableVII</v>
       </c>
       <c r="L200" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableVI</v>
+        <v>10.1159%2F000155963_TableVII</v>
       </c>
       <c r="M200" t="str">
         <f t="array" ref="M200">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L200,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableVI.tsv</v>
+        <v>10.1159%2F000155963_TableVII.tsv</v>
       </c>
       <c r="N200" s="1" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="V200" s="1" t="s">
         <v>42</v>
@@ -18131,15 +18144,15 @@
     </row>
     <row r="201" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A201" s="1" t="s">
-        <v>747</v>
+        <v>762</v>
       </c>
       <c r="C201" s="7"/>
       <c r="D201" s="1" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="E201" t="str">
         <f t="shared" si="47"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F201" t="str">
         <f t="shared" si="48"/>
@@ -18159,65 +18172,35 @@
       </c>
       <c r="J201" t="str">
         <f t="shared" si="46"/>
-        <v>10.1159%2F000155963</v>
+        <v>10.1159%2F000155964</v>
       </c>
       <c r="K201" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableVII</v>
+        <v>Stephan_etal_1981_TableVIII</v>
       </c>
       <c r="L201" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableVII</v>
+        <v>10.1159%2F000155964_TableVIII</v>
       </c>
       <c r="M201" t="str">
         <f t="array" ref="M201">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L201,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableVII.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N201" s="1" t="s">
-        <v>761</v>
-      </c>
-      <c r="V201" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y201" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z201" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="AF201" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG201" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="AI201" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="AJ201" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK201" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL201" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM201" s="1" t="s">
-        <v>84</v>
+        <v>764</v>
       </c>
     </row>
     <row r="202" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A202" s="1" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="C202" s="7"/>
       <c r="D202" s="1" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E202" t="str">
         <f t="shared" si="47"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F202" t="str">
         <f t="shared" si="48"/>
@@ -18237,35 +18220,35 @@
       </c>
       <c r="J202" t="str">
         <f t="shared" si="46"/>
-        <v>10.1159%2F000155964</v>
+        <v>10.1159%2F000155965</v>
       </c>
       <c r="K202" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableVIII</v>
+        <v>Stephan_etal_1981_TableIX</v>
       </c>
       <c r="L202" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155964_TableVIII</v>
+        <v>10.1159%2F000155965_TableIX</v>
       </c>
       <c r="M202" t="str">
         <f t="array" ref="M202">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L202,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N202" s="1" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
     </row>
     <row r="203" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A203" s="1" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
       <c r="C203" s="7"/>
       <c r="D203" s="1" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="E203" t="str">
         <f t="shared" si="47"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F203" t="str">
         <f t="shared" si="48"/>
@@ -18285,35 +18268,34 @@
       </c>
       <c r="J203" t="str">
         <f t="shared" si="46"/>
-        <v>10.1159%2F000155965</v>
+        <v>10.1159%2F000155966</v>
       </c>
       <c r="K203" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableIX</v>
+        <v>Stephan_etal_1981_TableX</v>
       </c>
       <c r="L203" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155965_TableIX</v>
+        <v>10.1159%2F000155966_TableX</v>
       </c>
       <c r="M203" t="str">
         <f t="array" ref="M203">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L203,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N203" s="1" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
     </row>
     <row r="204" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A204" s="1" t="s">
-        <v>768</v>
-      </c>
-      <c r="C204" s="7"/>
+        <v>747</v>
+      </c>
       <c r="D204" s="1" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="E204" t="str">
         <f t="shared" si="47"/>
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F204" t="str">
         <f t="shared" si="48"/>
@@ -18333,22 +18315,52 @@
       </c>
       <c r="J204" t="str">
         <f t="shared" si="46"/>
-        <v>10.1159%2F000155966</v>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K204" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableX</v>
+        <v>Stephan_etal_1981_TableXI</v>
       </c>
       <c r="L204" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155966_TableX</v>
+        <v>10.1159%2F000155963_TableXI</v>
       </c>
       <c r="M204" t="str">
         <f t="array" ref="M204">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L204,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>10.1159%2F000155963_TableXI.tsv</v>
       </c>
       <c r="N204" s="1" t="s">
-        <v>770</v>
+        <v>772</v>
+      </c>
+      <c r="V204" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y204" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="Z204" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="AF204" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG204" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="AI204" s="1" t="s">
+        <v>749</v>
+      </c>
+      <c r="AJ204" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK204" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AL204" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="AM204" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="205" spans="1:39" x14ac:dyDescent="0.2">
@@ -18356,7 +18368,7 @@
         <v>747</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="E205" t="str">
         <f t="shared" si="47"/>
@@ -18384,18 +18396,18 @@
       </c>
       <c r="K205" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableXI</v>
+        <v>Stephan_etal_1981_TableXII</v>
       </c>
       <c r="L205" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableXI</v>
+        <v>10.1159%2F000155963_TableXII</v>
       </c>
       <c r="M205" t="str">
         <f t="array" ref="M205">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L205,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableXI.tsv</v>
+        <v>10.1159%2F000155963_TableXII.tsv</v>
       </c>
       <c r="N205" s="1" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="V205" s="1" t="s">
         <v>42</v>
@@ -18433,7 +18445,7 @@
         <v>747</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E206" t="str">
         <f t="shared" si="47"/>
@@ -18461,18 +18473,18 @@
       </c>
       <c r="K206" t="str">
         <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableXII</v>
+        <v>Stephan_etal_1981_TableXIII</v>
       </c>
       <c r="L206" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableXII</v>
+        <v>10.1159%2F000155963_TableXIII</v>
       </c>
       <c r="M206" t="str">
         <f t="array" ref="M206">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L206,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableXII.tsv</v>
+        <v>10.1159%2F000155963_TableXIII.tsv</v>
       </c>
       <c r="N206" s="1" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="V206" s="1" t="s">
         <v>42</v>
@@ -18510,7 +18522,7 @@
         <v>747</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="E207" t="str">
         <f t="shared" si="47"/>
@@ -18537,19 +18549,19 @@
         <v>10.1159%2F000155963</v>
       </c>
       <c r="K207" t="str">
-        <f t="shared" si="45"/>
-        <v>Stephan_etal_1981_TableXIII</v>
+        <f t="shared" ref="K207:K222" si="53">TRIM(_xlfn.TEXTJOIN("_",FALSE(),F207,(SUBSTITUTE(SUBSTITUTE(D207," ",""), "_", ""))))</f>
+        <v>Stephan_etal_1981_TableXIV</v>
       </c>
       <c r="L207" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableXIII</v>
+        <v>10.1159%2F000155963_TableXIV</v>
       </c>
       <c r="M207" t="str">
         <f t="array" ref="M207">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L207,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableXIII.tsv</v>
+        <v>10.1159%2F000155963_TableXIV.tsv</v>
       </c>
       <c r="N207" s="1" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="V207" s="1" t="s">
         <v>42</v>
@@ -18587,7 +18599,7 @@
         <v>747</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="E208" t="str">
         <f t="shared" si="47"/>
@@ -18614,19 +18626,19 @@
         <v>10.1159%2F000155963</v>
       </c>
       <c r="K208" t="str">
-        <f t="shared" ref="K208:K224" si="53">TRIM(_xlfn.TEXTJOIN("_",FALSE(),F208,(SUBSTITUTE(SUBSTITUTE(D208," ",""), "_", ""))))</f>
-        <v>Stephan_etal_1981_TableXIV</v>
+        <f t="shared" si="53"/>
+        <v>Stephan_etal_1981_TableXV</v>
       </c>
       <c r="L208" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableXIV</v>
+        <v>10.1159%2F000155963_TableXV</v>
       </c>
       <c r="M208" t="str">
         <f t="array" ref="M208">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L208,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableXIV.tsv</v>
+        <v>10.1159%2F000155963_TableXV.tsv</v>
       </c>
       <c r="N208" s="1" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="V208" s="1" t="s">
         <v>42</v>
@@ -18664,7 +18676,7 @@
         <v>747</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="E209" t="str">
         <f t="shared" si="47"/>
@@ -18692,18 +18704,18 @@
       </c>
       <c r="K209" t="str">
         <f t="shared" si="53"/>
-        <v>Stephan_etal_1981_TableXV</v>
+        <v>Stephan_etal_1981_TableXVI</v>
       </c>
       <c r="L209" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableXV</v>
+        <v>10.1159%2F000155963_TableXVI</v>
       </c>
       <c r="M209" t="str">
         <f t="array" ref="M209">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L209,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableXV.tsv</v>
+        <v>10.1159%2F000155963_TableXVI.tsv</v>
       </c>
       <c r="N209" s="1" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="V209" s="1" t="s">
         <v>42</v>
@@ -18740,8 +18752,9 @@
       <c r="A210" s="1" t="s">
         <v>747</v>
       </c>
+      <c r="C210" s="7"/>
       <c r="D210" s="1" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="E210" t="str">
         <f t="shared" si="47"/>
@@ -18769,18 +18782,21 @@
       </c>
       <c r="K210" t="str">
         <f t="shared" si="53"/>
-        <v>Stephan_etal_1981_TableXVI</v>
+        <v>Stephan_etal_1981_TablesI-VI</v>
       </c>
       <c r="L210" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TableXVI</v>
+        <v>10.1159%2F000155963_TablesI-VI</v>
       </c>
       <c r="M210" t="str">
         <f t="array" ref="M210">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L210,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TableXVI.tsv</v>
-      </c>
-      <c r="N210" s="1" t="s">
-        <v>782</v>
+        <v>10.1159%2F000155963_TablesI-VI.tsv</v>
+      </c>
+      <c r="O210" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="P210" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="V210" s="1" t="s">
         <v>42</v>
@@ -18815,23 +18831,22 @@
     </row>
     <row r="211" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A211" s="1" t="s">
-        <v>747</v>
-      </c>
-      <c r="C211" s="7"/>
+        <v>785</v>
+      </c>
       <c r="D211" s="1" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="E211" t="str">
         <f t="shared" si="47"/>
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="F211" t="str">
         <f t="shared" si="48"/>
-        <v>Stephan_etal_1981</v>
+        <v>Stimpson_etal_2015</v>
       </c>
       <c r="G211" t="str">
         <f t="shared" si="49"/>
-        <v>Stephan</v>
+        <v>Stimpson</v>
       </c>
       <c r="H211" t="str">
         <f t="shared" si="50"/>
@@ -18839,26 +18854,26 @@
       </c>
       <c r="I211" t="str">
         <f t="shared" si="51"/>
-        <v>1981</v>
+        <v>2015</v>
       </c>
       <c r="J211" t="str">
         <f t="shared" si="46"/>
-        <v>10.1159%2F000155963</v>
+        <v>10.1093%2Fscan%2Fnsv128</v>
       </c>
       <c r="K211" t="str">
         <f t="shared" si="53"/>
-        <v>Stephan_etal_1981_TablesI-VI</v>
+        <v>Stimpson_etal_2015_TableS1</v>
       </c>
       <c r="L211" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000155963_TablesI-VI</v>
+        <v>10.1093%2Fscan%2Fnsv128_TableS1</v>
       </c>
       <c r="M211" t="str">
         <f t="array" ref="M211">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L211,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1159%2F000155963_TablesI-VI.tsv</v>
-      </c>
-      <c r="O211" s="1" t="s">
-        <v>784</v>
+        <v>10.1093%2Fscan%2Fnsv128_TableS1.tsv</v>
+      </c>
+      <c r="N211" s="1" t="s">
+        <v>786</v>
       </c>
       <c r="P211" s="1" t="s">
         <v>41</v>
@@ -18867,25 +18882,16 @@
         <v>42</v>
       </c>
       <c r="Y211" s="1" t="s">
-        <v>99</v>
+        <v>680</v>
       </c>
       <c r="Z211" s="1" t="s">
-        <v>99</v>
+        <v>680</v>
       </c>
       <c r="AF211" s="1" t="s">
         <v>78</v>
       </c>
       <c r="AG211" s="1" t="s">
         <v>112</v>
-      </c>
-      <c r="AI211" s="1" t="s">
-        <v>749</v>
-      </c>
-      <c r="AJ211" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="AK211" s="1" t="s">
-        <v>63</v>
       </c>
       <c r="AL211" s="1" t="s">
         <v>63</v>
@@ -18899,7 +18905,7 @@
         <v>785</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E212" t="str">
         <f t="shared" si="47"/>
@@ -18927,18 +18933,18 @@
       </c>
       <c r="K212" t="str">
         <f t="shared" si="53"/>
-        <v>Stimpson_etal_2015_TableS1</v>
+        <v>Stimpson_etal_2015_TableS2</v>
       </c>
       <c r="L212" t="str">
         <f t="shared" si="52"/>
-        <v>10.1093%2Fscan%2Fnsv128_TableS1</v>
+        <v>10.1093%2Fscan%2Fnsv128_TableS2</v>
       </c>
       <c r="M212" t="str">
         <f t="array" ref="M212">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L212,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1093%2Fscan%2Fnsv128_TableS1.tsv</v>
+        <v>10.1093%2Fscan%2Fnsv128_TableS2.tsv</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="P212" s="1" t="s">
         <v>41</v>
@@ -18967,22 +18973,22 @@
     </row>
     <row r="213" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A213" s="1" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>787</v>
+        <v>75</v>
       </c>
       <c r="E213" t="str">
         <f t="shared" si="47"/>
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F213" t="str">
         <f t="shared" si="48"/>
-        <v>Stimpson_etal_2015</v>
+        <v>Turner_etal_2016</v>
       </c>
       <c r="G213" t="str">
         <f t="shared" si="49"/>
-        <v>Stimpson</v>
+        <v>Turner</v>
       </c>
       <c r="H213" t="str">
         <f t="shared" si="50"/>
@@ -18990,109 +18996,88 @@
       </c>
       <c r="I213" t="str">
         <f t="shared" si="51"/>
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="J213" t="str">
         <f t="shared" si="46"/>
-        <v>10.1093%2Fscan%2Fnsv128</v>
+        <v>10.1159%2F000446762</v>
       </c>
       <c r="K213" t="str">
         <f t="shared" si="53"/>
-        <v>Stimpson_etal_2015_TableS2</v>
+        <v>Turner_etal_2016_Table1</v>
       </c>
       <c r="L213" t="str">
         <f t="shared" si="52"/>
-        <v>10.1093%2Fscan%2Fnsv128_TableS2</v>
+        <v>10.1159%2F000446762_Table1</v>
       </c>
       <c r="M213" t="str">
         <f t="array" ref="M213">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L213,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1093%2Fscan%2Fnsv128_TableS2.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>787</v>
-      </c>
-      <c r="P213" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="V213" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y213" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="Z213" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="AF213" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AG213" s="1" t="s">
-        <v>112</v>
+        <v>789</v>
+      </c>
+      <c r="AI213" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="AJ213" s="1" t="s">
+        <v>140</v>
       </c>
       <c r="AL213" s="1" t="s">
         <v>63</v>
       </c>
       <c r="AM213" s="1" t="s">
-        <v>84</v>
+        <v>127</v>
       </c>
     </row>
     <row r="214" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A214" s="1" t="s">
-        <v>788</v>
+        <v>791</v>
+      </c>
+      <c r="C214" t="s">
+        <v>792</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>75</v>
+        <v>793</v>
       </c>
       <c r="E214" t="str">
         <f t="shared" si="47"/>
-        <v>2</v>
+        <v>.</v>
       </c>
       <c r="F214" t="str">
         <f t="shared" si="48"/>
-        <v>Turner_etal_2016</v>
+        <v>Weaver__2001</v>
       </c>
       <c r="G214" t="str">
         <f t="shared" si="49"/>
-        <v>Turner</v>
+        <v>Weaver</v>
       </c>
       <c r="H214" t="str">
         <f t="shared" si="50"/>
-        <v>etal</v>
+        <v/>
       </c>
       <c r="I214" t="str">
         <f t="shared" si="51"/>
-        <v>2016</v>
+        <v>2001</v>
       </c>
       <c r="J214" t="str">
         <f t="shared" si="46"/>
-        <v>10.1159%2F000446762</v>
+        <v>UMI%3A3017523</v>
       </c>
       <c r="K214" t="str">
         <f t="shared" si="53"/>
-        <v>Turner_etal_2016_Table1</v>
+        <v>Weaver__2001_NotesforTableA-15</v>
       </c>
       <c r="L214" t="str">
         <f t="shared" si="52"/>
-        <v>10.1159%2F000446762_Table1</v>
+        <v>UMI%3A3017523_NotesforTableA-15</v>
       </c>
       <c r="M214" t="str">
         <f t="array" ref="M214">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L214,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N214" s="1" t="s">
-        <v>789</v>
-      </c>
-      <c r="AI214" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="AJ214" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="AL214" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AM214" s="1" t="s">
-        <v>127</v>
+        <v>793</v>
       </c>
     </row>
     <row r="215" spans="1:39" x14ac:dyDescent="0.2">
@@ -19103,7 +19088,7 @@
         <v>792</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="E215" t="str">
         <f t="shared" si="47"/>
@@ -19131,88 +19116,94 @@
       </c>
       <c r="K215" t="str">
         <f t="shared" si="53"/>
-        <v>Weaver__2001_NotesforTableA-15</v>
+        <v>Weaver__2001_TableA-15</v>
       </c>
       <c r="L215" t="str">
         <f t="shared" si="52"/>
-        <v>UMI%3A3017523_NotesforTableA-15</v>
+        <v>UMI%3A3017523_TableA-15</v>
       </c>
       <c r="M215" t="str">
         <f t="array" ref="M215">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L215,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
       <c r="N215" s="1" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
     </row>
     <row r="216" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A216" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="C216" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="E216" t="str">
         <f t="shared" si="47"/>
-        <v>.</v>
+        <v>1</v>
       </c>
       <c r="F216" t="str">
         <f t="shared" si="48"/>
-        <v>Weaver__2001</v>
+        <v>Wilman_etal_2014</v>
       </c>
       <c r="G216" t="str">
         <f t="shared" si="49"/>
-        <v>Weaver</v>
+        <v>Wilman</v>
       </c>
       <c r="H216" t="str">
         <f t="shared" si="50"/>
-        <v/>
+        <v>etal</v>
       </c>
       <c r="I216" t="str">
         <f t="shared" si="51"/>
-        <v>2001</v>
+        <v>2014</v>
       </c>
       <c r="J216" t="str">
         <f t="shared" si="46"/>
-        <v>UMI%3A3017523</v>
+        <v>10.1890%2F13-1917.1</v>
       </c>
       <c r="K216" t="str">
         <f t="shared" si="53"/>
-        <v>Weaver__2001_TableA-15</v>
+        <v>Wilman_etal_2014_MamFuncDat.txt</v>
       </c>
       <c r="L216" t="str">
         <f t="shared" si="52"/>
-        <v>UMI%3A3017523_TableA-15</v>
+        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
       </c>
       <c r="M216" t="str">
         <f t="array" ref="M216">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L216,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="N216" s="1" t="s">
-        <v>795</v>
+      <c r="AI216" s="1" t="s">
+        <v>798</v>
+      </c>
+      <c r="AJ216" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="AL216" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AM216" s="1" t="s">
+        <v>799</v>
       </c>
     </row>
     <row r="217" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A217" s="1" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="E217" t="str">
         <f t="shared" si="47"/>
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F217" t="str">
         <f t="shared" si="48"/>
-        <v>Wilman_etal_2014</v>
+        <v>Wimberly_etal_2021</v>
       </c>
       <c r="G217" t="str">
         <f t="shared" si="49"/>
-        <v>Wilman</v>
+        <v>Wimberly</v>
       </c>
       <c r="H217" t="str">
         <f t="shared" si="50"/>
@@ -19220,59 +19211,59 @@
       </c>
       <c r="I217" t="str">
         <f t="shared" si="51"/>
-        <v>2014</v>
+        <v>2021</v>
       </c>
       <c r="J217" t="str">
         <f t="shared" si="46"/>
-        <v>10.1890%2F13-1917.1</v>
+        <v>10.1098%2Frspb.2021.0937</v>
       </c>
       <c r="K217" t="str">
         <f t="shared" si="53"/>
-        <v>Wilman_etal_2014_MamFuncDat.txt</v>
+        <v>Wimberly_etal_2021_mammalgait.txt</v>
       </c>
       <c r="L217" t="str">
         <f t="shared" si="52"/>
-        <v>10.1890%2F13-1917.1_MamFuncDat.txt</v>
+        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
       </c>
       <c r="M217" t="str">
         <f t="array" ref="M217">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L217,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
         <v>notfound</v>
       </c>
-      <c r="AI217" s="1" t="s">
-        <v>798</v>
+      <c r="P217" s="1" t="s">
+        <v>335</v>
       </c>
       <c r="AJ217" s="1" t="s">
-        <v>140</v>
+        <v>43</v>
       </c>
       <c r="AL217" s="1" t="s">
-        <v>141</v>
+        <v>43</v>
       </c>
       <c r="AM217" s="1" t="s">
-        <v>799</v>
+        <v>43</v>
       </c>
     </row>
     <row r="218" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A218" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="E218" t="str">
         <f t="shared" si="47"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F218" t="str">
         <f t="shared" si="48"/>
-        <v>Wimberly_etal_2021</v>
+        <v>Winkler_Bryant_2021</v>
       </c>
       <c r="G218" t="str">
         <f t="shared" si="49"/>
-        <v>Wimberly</v>
+        <v>Winkler</v>
       </c>
       <c r="H218" t="str">
         <f t="shared" si="50"/>
-        <v>etal</v>
+        <v>Bryant</v>
       </c>
       <c r="I218" t="str">
         <f t="shared" si="51"/>
@@ -19280,78 +19271,97 @@
       </c>
       <c r="J218" t="str">
         <f t="shared" si="46"/>
-        <v>10.1098%2Frspb.2021.0937</v>
+        <v>10.1080%2F09524622.2021.1905065</v>
       </c>
       <c r="K218" t="str">
         <f t="shared" si="53"/>
-        <v>Wimberly_etal_2021_mammalgait.txt</v>
+        <v>Winkler_Bryant_2021_Figure1</v>
       </c>
       <c r="L218" t="str">
         <f t="shared" si="52"/>
-        <v>10.1098%2Frspb.2021.0937_mammalgait.txt</v>
+        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
       </c>
       <c r="M218" t="str">
         <f t="array" ref="M218">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L218,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>10.1080%2F09524622.2021.1905065_Figure1.tsv</v>
       </c>
       <c r="P218" s="1" t="s">
         <v>335</v>
       </c>
+      <c r="Q218" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="T218" s="1" t="str">
+        <f>IF(S218="N", R218, "write file name")</f>
+        <v>write file name</v>
+      </c>
+      <c r="U218" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="V218" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="AH218" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AI218" s="1" t="s">
+        <v>805</v>
+      </c>
       <c r="AJ218" s="1" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="AL218" s="1" t="s">
-        <v>43</v>
+        <v>141</v>
       </c>
       <c r="AM218" s="1" t="s">
-        <v>43</v>
+        <v>806</v>
       </c>
     </row>
     <row r="219" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A219" s="1" t="s">
-        <v>802</v>
+        <v>807</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>803</v>
+        <v>75</v>
       </c>
       <c r="E219" t="str">
         <f t="shared" si="47"/>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F219" t="str">
         <f t="shared" si="48"/>
-        <v>Winkler_Bryant_2021</v>
+        <v>Young_etal_2013</v>
       </c>
       <c r="G219" t="str">
         <f t="shared" si="49"/>
-        <v>Winkler</v>
+        <v>Young</v>
       </c>
       <c r="H219" t="str">
         <f t="shared" si="50"/>
-        <v>Bryant</v>
+        <v>etal</v>
       </c>
       <c r="I219" t="str">
         <f t="shared" si="51"/>
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="J219" t="str">
         <f t="shared" si="46"/>
-        <v>10.1080%2F09524622.2021.1905065</v>
+        <v>10.3389%2Ffncir.2013.00030</v>
       </c>
       <c r="K219" t="str">
         <f t="shared" si="53"/>
-        <v>Winkler_Bryant_2021_Figure1</v>
+        <v>Young_etal_2013_Table1</v>
       </c>
       <c r="L219" t="str">
         <f t="shared" si="52"/>
-        <v>10.1080%2F09524622.2021.1905065_Figure1</v>
+        <v>10.3389%2Ffncir.2013.00030_Table1</v>
       </c>
       <c r="M219" t="str">
         <f t="array" ref="M219">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L219,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1080%2F09524622.2021.1905065_Figure1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="P219" s="1" t="s">
-        <v>335</v>
+        <v>632</v>
       </c>
       <c r="Q219" s="1" t="s">
         <v>202</v>
@@ -19364,27 +19374,30 @@
         <v>55</v>
       </c>
       <c r="V219" s="1" t="s">
-        <v>804</v>
+        <v>42</v>
       </c>
       <c r="AH219" s="1" t="s">
-        <v>138</v>
+        <v>177</v>
       </c>
       <c r="AI219" s="1" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
       <c r="AJ219" s="1" t="s">
-        <v>140</v>
+        <v>118</v>
+      </c>
+      <c r="AK219" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="AL219" s="1" t="s">
-        <v>141</v>
+        <v>63</v>
       </c>
       <c r="AM219" s="1" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
     </row>
     <row r="220" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A220" s="1" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>75</v>
@@ -19411,7 +19424,7 @@
       </c>
       <c r="J220" t="str">
         <f t="shared" si="46"/>
-        <v>10.3389%2Ffncir.2013.00030</v>
+        <v>10.1073%2Fpnas.1318894110</v>
       </c>
       <c r="K220" t="str">
         <f t="shared" si="53"/>
@@ -19419,36 +19432,29 @@
       </c>
       <c r="L220" t="str">
         <f t="shared" si="52"/>
-        <v>10.3389%2Ffncir.2013.00030_Table1</v>
+        <v>10.1073%2Fpnas.1318894110_Table1</v>
       </c>
       <c r="M220" t="str">
         <f t="array" ref="M220">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L220,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="P220" s="1" t="s">
-        <v>632</v>
-      </c>
-      <c r="Q220" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="T220" s="1" t="str">
-        <f>IF(S220="N", R220, "write file name")</f>
-        <v>write file name</v>
-      </c>
-      <c r="U220" s="1" t="s">
-        <v>55</v>
+        <v>10.1073%2Fpnas.1318894110_Table1.tsv</v>
+      </c>
+      <c r="N220" s="1" t="s">
+        <v>811</v>
       </c>
       <c r="V220" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="AH220" s="1" t="s">
-        <v>177</v>
+      <c r="Y220" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="AG220" s="1" t="s">
+        <v>59</v>
       </c>
       <c r="AI220" s="1" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="AJ220" s="1" t="s">
-        <v>118</v>
+        <v>813</v>
       </c>
       <c r="AK220" s="1" t="s">
         <v>63</v>
@@ -19457,97 +19463,97 @@
         <v>63</v>
       </c>
       <c r="AM220" s="1" t="s">
-        <v>809</v>
+        <v>814</v>
       </c>
     </row>
     <row r="221" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A221" s="1" t="s">
-        <v>810</v>
+        <v>815</v>
+      </c>
+      <c r="C221" s="1" t="s">
+        <v>816</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>75</v>
+        <v>817</v>
       </c>
       <c r="E221" t="str">
         <f t="shared" si="47"/>
-        <v>0</v>
+        <v>s</v>
       </c>
       <c r="F221" t="str">
         <f t="shared" si="48"/>
-        <v>Young_etal_2013</v>
+        <v>Zilles_Rehkämper_1988</v>
       </c>
       <c r="G221" t="str">
         <f t="shared" si="49"/>
-        <v>Young</v>
+        <v>Zilles</v>
       </c>
       <c r="H221" t="str">
         <f t="shared" si="50"/>
-        <v>etal</v>
+        <v>Rehkämper</v>
       </c>
       <c r="I221" t="str">
         <f t="shared" si="51"/>
-        <v>2013</v>
+        <v>1988</v>
       </c>
       <c r="J221" t="str">
         <f t="shared" si="46"/>
-        <v>10.1073%2Fpnas.1318894110</v>
+        <v>ISBN%3A9780195043716</v>
       </c>
       <c r="K221" t="str">
         <f t="shared" si="53"/>
-        <v>Young_etal_2013_Table1</v>
+        <v>Zilles_Rehkämper_1988_Table12-2</v>
       </c>
       <c r="L221" t="str">
         <f t="shared" si="52"/>
-        <v>10.1073%2Fpnas.1318894110_Table1</v>
+        <v>ISBN%3A9780195043716_Table12-2</v>
       </c>
       <c r="M221" t="str">
         <f t="array" ref="M221">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L221,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1073%2Fpnas.1318894110_Table1.tsv</v>
+        <v>notfound</v>
       </c>
       <c r="N221" s="1" t="s">
-        <v>811</v>
-      </c>
-      <c r="V221" s="1" t="s">
-        <v>42</v>
+        <v>818</v>
       </c>
       <c r="Y221" s="1" t="s">
-        <v>223</v>
+        <v>99</v>
+      </c>
+      <c r="Z221" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="AF221" s="1" t="s">
+        <v>78</v>
       </c>
       <c r="AG221" s="1" t="s">
-        <v>59</v>
+        <v>112</v>
       </c>
       <c r="AI221" s="1" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="AJ221" s="1" t="s">
-        <v>813</v>
-      </c>
-      <c r="AK221" s="1" t="s">
-        <v>63</v>
+        <v>820</v>
       </c>
       <c r="AL221" s="1" t="s">
         <v>63</v>
       </c>
       <c r="AM221" s="1" t="s">
-        <v>814</v>
+        <v>84</v>
       </c>
     </row>
     <row r="222" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A222" s="1" t="s">
-        <v>815</v>
-      </c>
-      <c r="C222" s="1" t="s">
-        <v>816</v>
+        <v>821</v>
       </c>
       <c r="D222" s="1" t="s">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="E222" t="str">
         <f t="shared" si="47"/>
-        <v>s</v>
+        <v>6</v>
       </c>
       <c r="F222" t="str">
         <f t="shared" si="48"/>
-        <v>Zilles_Rehkämper_1988</v>
+        <v>Zilles_etal_2013</v>
       </c>
       <c r="G222" t="str">
         <f t="shared" si="49"/>
@@ -19555,196 +19561,54 @@
       </c>
       <c r="H222" t="str">
         <f t="shared" si="50"/>
-        <v>Rehkämper</v>
+        <v>etal</v>
       </c>
       <c r="I222" t="str">
         <f t="shared" si="51"/>
-        <v>1988</v>
+        <v>2013</v>
       </c>
       <c r="J222" t="str">
         <f t="shared" si="46"/>
-        <v>ISBN%3A9780195043716</v>
+        <v>10.1016%2Fj.tins.2013.01.006</v>
       </c>
       <c r="K222" t="str">
         <f t="shared" si="53"/>
-        <v>Zilles_Rehkämper_1988_Table12-2</v>
+        <v>Zilles_etal_2013_Table1</v>
       </c>
       <c r="L222" t="str">
         <f t="shared" si="52"/>
-        <v>ISBN%3A9780195043716_Table12-2</v>
+        <v>10.1016%2Fj.tins.2013.01.006_Table1</v>
       </c>
       <c r="M222" t="str">
         <f t="array" ref="M222">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L222,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
+        <v>10.1016%2Fj.tins.2013.01.006_Table1.tsv</v>
       </c>
       <c r="N222" s="1" t="s">
-        <v>818</v>
+        <v>823</v>
+      </c>
+      <c r="V222" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="Y222" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="Z222" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="AF222" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="AG222" s="1" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="AI222" s="1" t="s">
-        <v>819</v>
+        <v>824</v>
       </c>
       <c r="AJ222" s="1" t="s">
-        <v>820</v>
+        <v>825</v>
+      </c>
+      <c r="AK222" s="1" t="s">
+        <v>63</v>
       </c>
       <c r="AL222" s="1" t="s">
-        <v>63</v>
+        <v>141</v>
       </c>
       <c r="AM222" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="223" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A223" s="1" t="s">
-        <v>821</v>
-      </c>
-      <c r="D223" s="1" t="s">
-        <v>822</v>
-      </c>
-      <c r="E223" t="str">
-        <f t="shared" si="47"/>
-        <v>6</v>
-      </c>
-      <c r="F223" t="str">
-        <f t="shared" si="48"/>
-        <v>Zilles_etal_2013</v>
-      </c>
-      <c r="G223" t="str">
-        <f t="shared" si="49"/>
-        <v>Zilles</v>
-      </c>
-      <c r="H223" t="str">
-        <f t="shared" si="50"/>
-        <v>etal</v>
-      </c>
-      <c r="I223" t="str">
-        <f t="shared" si="51"/>
-        <v>2013</v>
-      </c>
-      <c r="J223" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1016%2Fj.tins.2013.01.006</v>
-      </c>
-      <c r="K223" t="str">
-        <f t="shared" si="53"/>
-        <v>Zilles_etal_2013_Table1</v>
-      </c>
-      <c r="L223" t="str">
-        <f t="shared" si="52"/>
-        <v>10.1016%2Fj.tins.2013.01.006_Table1</v>
-      </c>
-      <c r="M223" t="str">
-        <f t="array" ref="M223">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L223,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>10.1016%2Fj.tins.2013.01.006_Table1.tsv</v>
-      </c>
-      <c r="N223" s="1" t="s">
-        <v>823</v>
-      </c>
-      <c r="V223" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y223" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG223" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AI223" s="1" t="s">
-        <v>824</v>
-      </c>
-      <c r="AJ223" s="1" t="s">
-        <v>825</v>
-      </c>
-      <c r="AK223" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL223" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="AM223" s="1" t="s">
         <v>826</v>
-      </c>
-    </row>
-    <row r="224" spans="1:39" x14ac:dyDescent="0.2">
-      <c r="A224" s="1" t="s">
-        <v>1026</v>
-      </c>
-      <c r="D224" s="1" t="s">
-        <v>1027</v>
-      </c>
-      <c r="E224" t="str">
-        <f t="shared" si="47"/>
-        <v>7</v>
-      </c>
-      <c r="F224" t="str">
-        <f t="shared" si="48"/>
-        <v>xml:space="preserve"&gt;Wimberly_etal_2021</v>
-      </c>
-      <c r="G224" t="str">
-        <f t="shared" si="49"/>
-        <v>xml:space="preserve"&gt;Wimberly</v>
-      </c>
-      <c r="H224" t="str">
-        <f t="shared" si="50"/>
-        <v>etal</v>
-      </c>
-      <c r="I224" t="str">
-        <f t="shared" si="51"/>
-        <v>2021</v>
-      </c>
-      <c r="J224" t="str">
-        <f t="shared" si="46"/>
-        <v>10.1098%2Frspb.2021.0937</v>
-      </c>
-      <c r="K224" t="str">
-        <f t="shared" si="53"/>
-        <v>xml:space="preserve"&gt;Wimberly_etal_2021_xml:space="preserve"&gt;MammalGait</v>
-      </c>
-      <c r="L224" t="str">
-        <f t="shared" si="52"/>
-        <v>10.1098%2Frspb.2021.0937_xml:space="preserve"&gt;MammalGait</v>
-      </c>
-      <c r="M224" t="str">
-        <f t="array" ref="M224">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L224,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
-        <v>notfound</v>
-      </c>
-      <c r="N224" s="1" t="s">
-        <v>1028</v>
-      </c>
-      <c r="V224" s="1" t="s">
-        <v>1029</v>
-      </c>
-      <c r="Y224" s="1" t="s">
-        <v>1030</v>
-      </c>
-      <c r="AG224" s="1" t="s">
-        <v>1031</v>
-      </c>
-      <c r="AI224" s="1" t="s">
-        <v>1032</v>
-      </c>
-      <c r="AJ224" s="1" t="s">
-        <v>1033</v>
-      </c>
-      <c r="AK224" s="1" t="s">
-        <v>1034</v>
-      </c>
-      <c r="AL224" s="1" t="s">
-        <v>1035</v>
-      </c>
-      <c r="AM224" s="1" t="s">
-        <v>1036</v>
       </c>
     </row>
   </sheetData>
@@ -19772,7 +19636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:A195"/>
+  <dimension ref="A1:A196"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
@@ -20748,6 +20612,13 @@
     <row r="195" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
         <v>1009</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>10.1038%2Fs42003-025-08686-5_SupplementaryData1.tsv</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="FileList" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FileList" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2695" uniqueCount="1038">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1042" uniqueCount="1042">
   <si>
     <t xml:space="preserve">Citation (APA 7th-Annotated)</t>
   </si>
@@ -3136,16 +3130,28 @@
   </si>
   <si>
     <t xml:space="preserve">UMI%3A3147447_TableA9.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.23118_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1006%2Fjhev.1999.0381_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523%2FJNEUROSCI.1750-23.2024_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554%2FeLife.35696_Figure2-data1.tsv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3154,49 +3160,35 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
+      <b/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3213,15 +3205,15 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="3">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -3234,100 +3226,54 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
         <color rgb="FF7F7F7F"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="8">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="9">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -3564,33 +3510,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AM225"/>
-  <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="67.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="1.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="37.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="46.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="1" width="7.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="16.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="19" style="1" width="7.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="28" style="1" width="7.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="10.84"/>
+    <col min="1" max="1" width="67.16" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="2" max="2" width="1.66" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="3" max="3" width="42.66" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="8.5" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="1.5" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="26" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="7" max="7" width="10.33" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="8" max="8" width="10.33" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="9" max="9" width="6.16" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="10" max="10" width="37.16" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="11" max="11" width="46.16" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="12" max="12" width="41.33" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="13" max="13" width="48" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="14" max="14" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="15" max="15" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="16" max="16" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="17" max="17" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="18" max="18" width="16.66" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="19" max="19" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="20" max="20" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="21" max="21" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="22" max="22" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="23" max="23" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="24" max="24" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="25" max="25" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="26" max="26" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="28" max="28" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="29" max="29" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="30" max="30" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="31" max="31" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="32" max="32" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="33" max="33" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="34" max="34" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="35" max="35" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="36" max="36" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="37" max="37" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="38" max="38" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="39" max="39" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="40" max="40" width="10.84" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3709,7 +3677,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>39</v>
       </c>
@@ -3784,7 +3752,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>44</v>
       </c>
@@ -3853,7 +3821,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>48</v>
       </c>
@@ -3967,7 +3935,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>65</v>
       </c>
@@ -4027,25 +3995,25 @@
         <v>notfound</v>
       </c>
       <c r="N5" s="4"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="AG5" s="5"/>
-      <c r="AH5" s="5"/>
-      <c r="AI5" s="5"/>
-      <c r="AJ5" s="5"/>
-      <c r="AK5" s="5"/>
-      <c r="AL5" s="5"/>
-      <c r="AM5" s="5"/>
-    </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="P5" s="4"/>
+      <c r="Q5" s="4"/>
+      <c r="R5" s="4"/>
+      <c r="S5" s="4"/>
+      <c r="T5" s="4"/>
+      <c r="U5" s="4"/>
+      <c r="V5" s="4"/>
+      <c r="W5" s="4"/>
+      <c r="X5" s="4"/>
+      <c r="Y5" s="4"/>
+      <c r="AG5" s="4"/>
+      <c r="AH5" s="4"/>
+      <c r="AI5" s="4"/>
+      <c r="AJ5" s="4"/>
+      <c r="AK5" s="4"/>
+      <c r="AL5" s="4"/>
+      <c r="AM5" s="4"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>67</v>
       </c>
@@ -4108,7 +4076,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>67</v>
       </c>
@@ -4171,7 +4139,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>72</v>
       </c>
@@ -4243,7 +4211,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>72</v>
       </c>
@@ -4315,7 +4283,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>72</v>
       </c>
@@ -4387,7 +4355,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>76</v>
       </c>
@@ -4459,7 +4427,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>81</v>
       </c>
@@ -4546,7 +4514,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>87</v>
       </c>
@@ -4615,7 +4583,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>87</v>
       </c>
@@ -4681,7 +4649,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>87</v>
       </c>
@@ -4750,7 +4718,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>87</v>
       </c>
@@ -4816,7 +4784,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>87</v>
       </c>
@@ -4879,7 +4847,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>98</v>
       </c>
@@ -4972,7 +4940,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="16.5" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>104</v>
       </c>
@@ -5071,7 +5039,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>108</v>
       </c>
@@ -5170,7 +5138,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>111</v>
       </c>
@@ -5272,7 +5240,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>116</v>
       </c>
@@ -5365,7 +5333,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>116</v>
       </c>
@@ -5455,7 +5423,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>116</v>
       </c>
@@ -5542,7 +5510,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>122</v>
       </c>
@@ -5605,7 +5573,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>124</v>
       </c>
@@ -5665,7 +5633,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>126</v>
       </c>
@@ -5740,7 +5708,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>131</v>
       </c>
@@ -5849,7 +5817,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>145</v>
       </c>
@@ -5945,7 +5913,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>145</v>
       </c>
@@ -6059,7 +6027,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>160</v>
       </c>
@@ -6131,7 +6099,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>165</v>
       </c>
@@ -6236,7 +6204,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>173</v>
       </c>
@@ -6341,7 +6309,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>181</v>
       </c>
@@ -6450,7 +6418,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>181</v>
       </c>
@@ -6561,7 +6529,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>199</v>
       </c>
@@ -6621,7 +6589,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>201</v>
       </c>
@@ -6723,7 +6691,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>213</v>
       </c>
@@ -6835,7 +6803,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>223</v>
       </c>
@@ -6913,7 +6881,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>227</v>
       </c>
@@ -7003,7 +6971,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>231</v>
       </c>
@@ -7114,7 +7082,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>240</v>
       </c>
@@ -7237,7 +7205,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>240</v>
       </c>
@@ -7330,7 +7298,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>257</v>
       </c>
@@ -7426,7 +7394,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>257</v>
       </c>
@@ -7525,7 +7493,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>257</v>
       </c>
@@ -7621,7 +7589,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>257</v>
       </c>
@@ -7717,7 +7685,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>273</v>
       </c>
@@ -7834,7 +7802,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>273</v>
       </c>
@@ -7951,7 +7919,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>288</v>
       </c>
@@ -8071,7 +8039,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>298</v>
       </c>
@@ -8152,7 +8120,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>302</v>
       </c>
@@ -8233,7 +8201,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>302</v>
       </c>
@@ -8314,7 +8282,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>308</v>
       </c>
@@ -8422,7 +8390,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>315</v>
       </c>
@@ -8521,7 +8489,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>315</v>
       </c>
@@ -8584,7 +8552,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>319</v>
       </c>
@@ -8683,7 +8651,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>323</v>
       </c>
@@ -8782,7 +8750,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" ht="16.5" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>327</v>
       </c>
@@ -8881,7 +8849,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" ht="16.5" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>331</v>
       </c>
@@ -8980,7 +8948,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" ht="16.5" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>335</v>
       </c>
@@ -9061,7 +9029,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" ht="16.5" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>339</v>
       </c>
@@ -9142,7 +9110,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" ht="16.5" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>339</v>
       </c>
@@ -9223,7 +9191,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>345</v>
       </c>
@@ -9301,7 +9269,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>348</v>
       </c>
@@ -9379,7 +9347,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>352</v>
       </c>
@@ -9454,7 +9422,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>354</v>
       </c>
@@ -9554,7 +9522,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>359</v>
       </c>
@@ -9662,7 +9630,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>366</v>
       </c>
@@ -9743,7 +9711,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>372</v>
       </c>
@@ -9837,7 +9805,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>375</v>
       </c>
@@ -9915,7 +9883,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="4" t="s">
         <v>375</v>
       </c>
@@ -9999,7 +9967,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="4" t="s">
         <v>381</v>
       </c>
@@ -10116,7 +10084,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>381</v>
       </c>
@@ -10230,7 +10198,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>381</v>
       </c>
@@ -10344,7 +10312,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="4" t="s">
         <v>381</v>
       </c>
@@ -10458,7 +10426,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>381</v>
       </c>
@@ -10572,7 +10540,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="4" t="s">
         <v>399</v>
       </c>
@@ -10689,7 +10657,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="4" t="s">
         <v>399</v>
       </c>
@@ -10806,7 +10774,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>412</v>
       </c>
@@ -10890,7 +10858,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="4" t="s">
         <v>412</v>
       </c>
@@ -10977,7 +10945,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="4" t="s">
         <v>412</v>
       </c>
@@ -11064,7 +11032,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>417</v>
       </c>
@@ -11142,7 +11110,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="4" t="s">
         <v>417</v>
       </c>
@@ -11220,7 +11188,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="4" t="s">
         <v>417</v>
       </c>
@@ -11298,7 +11266,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>417</v>
       </c>
@@ -11376,7 +11344,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="4" t="s">
         <v>417</v>
       </c>
@@ -11454,7 +11422,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="4" t="s">
         <v>417</v>
       </c>
@@ -11532,7 +11500,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>426</v>
       </c>
@@ -11626,7 +11594,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>426</v>
       </c>
@@ -11720,7 +11688,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="4" t="s">
         <v>426</v>
       </c>
@@ -11814,7 +11782,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>426</v>
       </c>
@@ -11908,7 +11876,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="4" t="s">
         <v>435</v>
       </c>
@@ -11992,7 +11960,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="4" t="s">
         <v>435</v>
       </c>
@@ -12076,7 +12044,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="4" t="s">
         <v>441</v>
       </c>
@@ -12193,7 +12161,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="4" t="s">
         <v>448</v>
       </c>
@@ -12271,7 +12239,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="4" t="s">
         <v>453</v>
       </c>
@@ -12355,7 +12323,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="4" t="s">
         <v>453</v>
       </c>
@@ -12439,7 +12407,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="4" t="s">
         <v>453</v>
       </c>
@@ -12523,7 +12491,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>453</v>
       </c>
@@ -12607,7 +12575,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="4" t="s">
         <v>453</v>
       </c>
@@ -12691,7 +12659,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="4" t="s">
         <v>453</v>
       </c>
@@ -12775,7 +12743,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="4" t="s">
         <v>453</v>
       </c>
@@ -12859,7 +12827,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="4" t="s">
         <v>453</v>
       </c>
@@ -12943,7 +12911,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="4" t="s">
         <v>453</v>
       </c>
@@ -13027,7 +12995,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="4" t="s">
         <v>453</v>
       </c>
@@ -13111,7 +13079,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="4" t="s">
         <v>453</v>
       </c>
@@ -13195,7 +13163,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="4" t="s">
         <v>453</v>
       </c>
@@ -13279,7 +13247,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="4" t="s">
         <v>453</v>
       </c>
@@ -13363,7 +13331,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="4" t="s">
         <v>453</v>
       </c>
@@ -13447,7 +13415,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="4" t="s">
         <v>453</v>
       </c>
@@ -13531,7 +13499,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="4" t="s">
         <v>453</v>
       </c>
@@ -13615,7 +13583,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="4" t="s">
         <v>453</v>
       </c>
@@ -13699,7 +13667,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="4" t="s">
         <v>453</v>
       </c>
@@ -13783,7 +13751,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="4" t="s">
         <v>453</v>
       </c>
@@ -13867,7 +13835,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="4" t="s">
         <v>453</v>
       </c>
@@ -13951,7 +13919,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="4" t="s">
         <v>453</v>
       </c>
@@ -14035,7 +14003,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="4" t="s">
         <v>453</v>
       </c>
@@ -14119,7 +14087,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="4" t="s">
         <v>453</v>
       </c>
@@ -14203,7 +14171,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="4" t="s">
         <v>453</v>
       </c>
@@ -14287,7 +14255,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="4" t="s">
         <v>505</v>
       </c>
@@ -14377,7 +14345,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" ht="15" customHeight="1">
       <c r="A122" s="4" t="s">
         <v>508</v>
       </c>
@@ -14473,7 +14441,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" ht="15" customHeight="1">
       <c r="A123" s="4" t="s">
         <v>508</v>
       </c>
@@ -14569,7 +14537,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" ht="15" customHeight="1">
       <c r="A124" s="4" t="s">
         <v>508</v>
       </c>
@@ -14665,7 +14633,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" ht="15" customHeight="1">
       <c r="A125" s="4" t="s">
         <v>508</v>
       </c>
@@ -14761,7 +14729,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" ht="15" customHeight="1">
       <c r="A126" s="4" t="s">
         <v>508</v>
       </c>
@@ -14857,7 +14825,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" ht="15" customHeight="1">
       <c r="A127" s="4" t="s">
         <v>508</v>
       </c>
@@ -14953,7 +14921,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="128" ht="15" customHeight="1">
       <c r="A128" s="4" t="s">
         <v>508</v>
       </c>
@@ -15049,7 +15017,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" ht="15" customHeight="1">
       <c r="A129" s="4" t="s">
         <v>508</v>
       </c>
@@ -15145,7 +15113,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" ht="15" customHeight="1">
       <c r="A130" s="4" t="s">
         <v>508</v>
       </c>
@@ -15241,7 +15209,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" ht="15" customHeight="1">
       <c r="A131" s="4" t="s">
         <v>508</v>
       </c>
@@ -15337,7 +15305,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" ht="15" customHeight="1">
       <c r="A132" s="4" t="s">
         <v>508</v>
       </c>
@@ -15433,7 +15401,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="133" ht="15" customHeight="1">
       <c r="A133" s="4" t="s">
         <v>508</v>
       </c>
@@ -15529,7 +15497,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="134" ht="15" customHeight="1">
       <c r="A134" s="4" t="s">
         <v>508</v>
       </c>
@@ -15625,7 +15593,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="135" ht="15" customHeight="1">
       <c r="A135" s="4" t="s">
         <v>508</v>
       </c>
@@ -15721,7 +15689,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="136" ht="15" customHeight="1">
       <c r="A136" s="4" t="s">
         <v>508</v>
       </c>
@@ -15817,11 +15785,11 @@
         <v>516</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="137" ht="15" customHeight="1">
       <c r="A137" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C137" s="5"/>
+      <c r="C137" s="4"/>
       <c r="D137" s="4" t="s">
         <v>574</v>
       </c>
@@ -15887,11 +15855,11 @@
         <v>577</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="138" ht="15" customHeight="1">
       <c r="A138" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C138" s="5"/>
+      <c r="C138" s="4"/>
       <c r="D138" s="4" t="s">
         <v>578</v>
       </c>
@@ -15954,11 +15922,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="139" ht="15" customHeight="1">
       <c r="A139" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C139" s="5"/>
+      <c r="C139" s="4"/>
       <c r="D139" s="4" t="s">
         <v>580</v>
       </c>
@@ -16021,11 +15989,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="140" ht="15" customHeight="1">
       <c r="A140" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C140" s="5"/>
+      <c r="C140" s="4"/>
       <c r="D140" s="4" t="s">
         <v>582</v>
       </c>
@@ -16091,11 +16059,11 @@
         <v>585</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="141" ht="15" customHeight="1">
       <c r="A141" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C141" s="5"/>
+      <c r="C141" s="4"/>
       <c r="D141" s="4" t="s">
         <v>586</v>
       </c>
@@ -16161,11 +16129,11 @@
         <v>577</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="142" ht="15" customHeight="1">
       <c r="A142" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C142" s="5"/>
+      <c r="C142" s="4"/>
       <c r="D142" s="4" t="s">
         <v>587</v>
       </c>
@@ -16231,11 +16199,11 @@
         <v>577</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" ht="15" customHeight="1">
       <c r="A143" s="4" t="s">
         <v>573</v>
       </c>
-      <c r="C143" s="5"/>
+      <c r="C143" s="4"/>
       <c r="D143" s="4" t="s">
         <v>588</v>
       </c>
@@ -16301,11 +16269,11 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="144" ht="15" customHeight="1">
       <c r="A144" s="4" t="s">
         <v>591</v>
       </c>
-      <c r="C144" s="5"/>
+      <c r="C144" s="4"/>
       <c r="D144" s="4" t="s">
         <v>77</v>
       </c>
@@ -16365,7 +16333,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="145" ht="15" customHeight="1">
       <c r="A145" s="4" t="s">
         <v>593</v>
       </c>
@@ -16473,7 +16441,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" ht="15" customHeight="1">
       <c r="A146" s="4" t="s">
         <v>593</v>
       </c>
@@ -16587,7 +16555,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="147" ht="15" customHeight="1">
       <c r="A147" s="4" t="s">
         <v>593</v>
       </c>
@@ -16704,7 +16672,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="148" ht="15" customHeight="1">
       <c r="A148" s="4" t="s">
         <v>611</v>
       </c>
@@ -16779,7 +16747,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="149" ht="15" customHeight="1">
       <c r="A149" s="4" t="s">
         <v>615</v>
       </c>
@@ -16857,7 +16825,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="150" ht="15" customHeight="1">
       <c r="A150" s="4" t="s">
         <v>615</v>
       </c>
@@ -16935,7 +16903,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" ht="15" customHeight="1">
       <c r="A151" s="4" t="s">
         <v>620</v>
       </c>
@@ -17013,7 +16981,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="152" ht="15" customHeight="1">
       <c r="A152" s="4" t="s">
         <v>624</v>
       </c>
@@ -17079,7 +17047,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="153" ht="15" customHeight="1">
       <c r="A153" s="4" t="s">
         <v>628</v>
       </c>
@@ -17169,7 +17137,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="154" ht="15" customHeight="1">
       <c r="A154" s="4" t="s">
         <v>628</v>
       </c>
@@ -17259,11 +17227,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="155" ht="15" customHeight="1">
       <c r="A155" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D155" s="5" t="s">
         <v>635</v>
       </c>
       <c r="E155" s="1" t="str">
@@ -17362,11 +17330,11 @@
         <v>639</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="156" ht="15" customHeight="1">
       <c r="A156" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="B156" s="7"/>
+      <c r="B156" s="6"/>
       <c r="D156" s="4" t="s">
         <v>94</v>
       </c>
@@ -17426,7 +17394,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="157" ht="15" customHeight="1">
       <c r="A157" s="4" t="s">
         <v>642</v>
       </c>
@@ -17525,11 +17493,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="158" ht="15" customHeight="1">
       <c r="A158" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="B158" s="5" t="s">
+      <c r="B158" s="4" t="s">
         <v>174</v>
       </c>
       <c r="D158" s="4" t="s">
@@ -17600,7 +17568,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="159" ht="15" customHeight="1">
       <c r="A159" s="4" t="s">
         <v>646</v>
       </c>
@@ -17675,7 +17643,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="160" ht="15" customHeight="1">
       <c r="A160" s="4" t="s">
         <v>648</v>
       </c>
@@ -17756,7 +17724,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" ht="15" customHeight="1">
       <c r="A161" s="4" t="s">
         <v>654</v>
       </c>
@@ -17862,7 +17830,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="162" ht="15" customHeight="1">
       <c r="A162" s="4" t="s">
         <v>659</v>
       </c>
@@ -17937,7 +17905,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="163" ht="15" customHeight="1">
       <c r="A163" s="4" t="s">
         <v>661</v>
       </c>
@@ -18006,7 +17974,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" ht="15" customHeight="1">
       <c r="A164" s="4" t="s">
         <v>663</v>
       </c>
@@ -18081,7 +18049,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" ht="15" customHeight="1">
       <c r="A165" s="4" t="s">
         <v>667</v>
       </c>
@@ -18141,7 +18109,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="166" ht="15" customHeight="1">
       <c r="A166" s="4" t="s">
         <v>668</v>
       </c>
@@ -18231,7 +18199,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="167" ht="15" customHeight="1">
       <c r="A167" s="4" t="s">
         <v>671</v>
       </c>
@@ -18321,7 +18289,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" ht="15" customHeight="1">
       <c r="A168" s="4" t="s">
         <v>674</v>
       </c>
@@ -18408,7 +18376,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="169" ht="15" customHeight="1">
       <c r="A169" s="4" t="s">
         <v>677</v>
       </c>
@@ -18468,7 +18436,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="170" ht="15" customHeight="1">
       <c r="A170" s="4" t="s">
         <v>679</v>
       </c>
@@ -18528,7 +18496,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="171" ht="15" customHeight="1">
       <c r="A171" s="4" t="s">
         <v>680</v>
       </c>
@@ -18588,7 +18556,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="172" ht="15" customHeight="1">
       <c r="A172" s="4" t="s">
         <v>682</v>
       </c>
@@ -18666,11 +18634,11 @@
         <v>63</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="173" ht="15" customHeight="1">
       <c r="A173" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="B173" s="7"/>
+      <c r="B173" s="6"/>
       <c r="D173" s="4" t="s">
         <v>96</v>
       </c>
@@ -18745,11 +18713,11 @@
         <v>63</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="174" ht="15" customHeight="1">
       <c r="A174" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="B174" s="7"/>
+      <c r="B174" s="6"/>
       <c r="D174" s="4" t="s">
         <v>77</v>
       </c>
@@ -18839,11 +18807,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="175" ht="15" customHeight="1">
       <c r="A175" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="B175" s="5" t="s">
+      <c r="B175" s="4" t="s">
         <v>691</v>
       </c>
       <c r="D175" s="4" t="s">
@@ -18945,11 +18913,11 @@
         <v>696</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="176" ht="15" customHeight="1">
       <c r="A176" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B176" s="4" t="s">
         <v>691</v>
       </c>
       <c r="D176" s="4" t="s">
@@ -19054,7 +19022,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="177" ht="15" customHeight="1">
       <c r="A177" s="4" t="s">
         <v>698</v>
       </c>
@@ -19138,7 +19106,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="178" ht="15" customHeight="1">
       <c r="A178" s="4" t="s">
         <v>704</v>
       </c>
@@ -19240,7 +19208,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="179" ht="15" customHeight="1">
       <c r="A179" s="4" t="s">
         <v>704</v>
       </c>
@@ -19342,7 +19310,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="180" ht="15" customHeight="1">
       <c r="A180" s="4" t="s">
         <v>714</v>
       </c>
@@ -19429,7 +19397,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="181" ht="15" customHeight="1">
       <c r="A181" s="4" t="s">
         <v>714</v>
       </c>
@@ -19516,7 +19484,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="182" ht="15" customHeight="1">
       <c r="A182" s="4" t="s">
         <v>718</v>
       </c>
@@ -19603,7 +19571,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" ht="15" customHeight="1">
       <c r="A183" s="4" t="s">
         <v>723</v>
       </c>
@@ -19705,7 +19673,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="184" ht="15" customHeight="1">
       <c r="A184" s="4" t="s">
         <v>727</v>
       </c>
@@ -19771,7 +19739,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="185" ht="15" customHeight="1">
       <c r="A185" s="4" t="s">
         <v>730</v>
       </c>
@@ -19858,7 +19826,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="186" ht="15" customHeight="1">
       <c r="A186" s="4" t="s">
         <v>730</v>
       </c>
@@ -19945,7 +19913,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="187" ht="15" customHeight="1">
       <c r="A187" s="4" t="s">
         <v>730</v>
       </c>
@@ -20032,7 +20000,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="188" ht="15" customHeight="1">
       <c r="A188" s="4" t="s">
         <v>730</v>
       </c>
@@ -20119,7 +20087,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="189" ht="15" customHeight="1">
       <c r="A189" s="4" t="s">
         <v>730</v>
       </c>
@@ -20206,7 +20174,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="190" ht="15" customHeight="1">
       <c r="A190" s="4" t="s">
         <v>730</v>
       </c>
@@ -20293,7 +20261,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="191" ht="15" customHeight="1">
       <c r="A191" s="4" t="s">
         <v>730</v>
       </c>
@@ -20386,7 +20354,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="192" ht="15" customHeight="1">
       <c r="A192" s="4" t="s">
         <v>745</v>
       </c>
@@ -20488,11 +20456,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="193" ht="15" customHeight="1">
       <c r="A193" s="4" t="s">
         <v>749</v>
       </c>
-      <c r="C193" s="5" t="s">
+      <c r="C193" s="4" t="s">
         <v>750</v>
       </c>
       <c r="D193" s="4" t="s">
@@ -20590,7 +20558,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="194" ht="15" customHeight="1">
       <c r="A194" s="4" t="s">
         <v>753</v>
       </c>
@@ -20683,7 +20651,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="195" ht="15" customHeight="1">
       <c r="A195" s="4" t="s">
         <v>753</v>
       </c>
@@ -20776,7 +20744,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="196" ht="15" customHeight="1">
       <c r="A196" s="4" t="s">
         <v>753</v>
       </c>
@@ -20869,7 +20837,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="197" ht="15" customHeight="1">
       <c r="A197" s="4" t="s">
         <v>753</v>
       </c>
@@ -20962,7 +20930,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="198" ht="15" customHeight="1">
       <c r="A198" s="4" t="s">
         <v>753</v>
       </c>
@@ -21055,7 +21023,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="199" ht="15" customHeight="1">
       <c r="A199" s="4" t="s">
         <v>753</v>
       </c>
@@ -21148,11 +21116,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="200" ht="15" customHeight="1">
       <c r="A200" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="C200" s="8"/>
+      <c r="C200" s="7"/>
       <c r="D200" s="4" t="s">
         <v>766</v>
       </c>
@@ -21242,11 +21210,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="201" ht="15" customHeight="1">
       <c r="A201" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="C201" s="8"/>
+      <c r="C201" s="7"/>
       <c r="D201" s="4" t="s">
         <v>769</v>
       </c>
@@ -21306,11 +21274,11 @@
         <v>770</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="202" ht="15" customHeight="1">
       <c r="A202" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="C202" s="8"/>
+      <c r="C202" s="7"/>
       <c r="D202" s="4" t="s">
         <v>772</v>
       </c>
@@ -21370,11 +21338,11 @@
         <v>773</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="203" ht="15" customHeight="1">
       <c r="A203" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="C203" s="8"/>
+      <c r="C203" s="7"/>
       <c r="D203" s="4" t="s">
         <v>775</v>
       </c>
@@ -21434,7 +21402,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="204" ht="15" customHeight="1">
       <c r="A204" s="4" t="s">
         <v>753</v>
       </c>
@@ -21527,7 +21495,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="205" ht="15" customHeight="1">
       <c r="A205" s="4" t="s">
         <v>753</v>
       </c>
@@ -21620,7 +21588,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="206" ht="15" customHeight="1">
       <c r="A206" s="4" t="s">
         <v>753</v>
       </c>
@@ -21713,7 +21681,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="207" ht="15" customHeight="1">
       <c r="A207" s="4" t="s">
         <v>753</v>
       </c>
@@ -21806,7 +21774,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="208" ht="15" customHeight="1">
       <c r="A208" s="4" t="s">
         <v>753</v>
       </c>
@@ -21899,7 +21867,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="209" ht="15" customHeight="1">
       <c r="A209" s="4" t="s">
         <v>753</v>
       </c>
@@ -21992,11 +21960,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="210" ht="15" customHeight="1">
       <c r="A210" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="C210" s="8"/>
+      <c r="C210" s="7"/>
       <c r="D210" s="4" t="s">
         <v>789</v>
       </c>
@@ -22089,7 +22057,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="211" ht="15" customHeight="1">
       <c r="A211" s="4" t="s">
         <v>791</v>
       </c>
@@ -22176,7 +22144,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="212" ht="15" customHeight="1">
       <c r="A212" s="4" t="s">
         <v>791</v>
       </c>
@@ -22263,7 +22231,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="213" ht="15" customHeight="1">
       <c r="A213" s="4" t="s">
         <v>794</v>
       </c>
@@ -22338,7 +22306,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="214" ht="15" customHeight="1">
       <c r="A214" s="4" t="s">
         <v>797</v>
       </c>
@@ -22404,7 +22372,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="215" ht="15" customHeight="1">
       <c r="A215" s="4" t="s">
         <v>797</v>
       </c>
@@ -22470,7 +22438,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="216" ht="15" customHeight="1">
       <c r="A216" s="4" t="s">
         <v>802</v>
       </c>
@@ -22542,7 +22510,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="217" ht="15" customHeight="1">
       <c r="A217" s="4" t="s">
         <v>806</v>
       </c>
@@ -22614,7 +22582,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="218" ht="15" customHeight="1">
       <c r="A218" s="4" t="s">
         <v>808</v>
       </c>
@@ -22705,7 +22673,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="219" ht="15" customHeight="1">
       <c r="A219" s="4" t="s">
         <v>813</v>
       </c>
@@ -22799,7 +22767,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="220" ht="15" customHeight="1">
       <c r="A220" s="4" t="s">
         <v>816</v>
       </c>
@@ -22886,7 +22854,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="221" ht="15" customHeight="1">
       <c r="A221" s="4" t="s">
         <v>821</v>
       </c>
@@ -22976,7 +22944,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="222" ht="15" customHeight="1">
       <c r="A222" s="4" t="s">
         <v>827</v>
       </c>
@@ -23063,7 +23031,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="223" ht="15" customHeight="1">
       <c r="A223" s="1" t="s">
         <v>67</v>
       </c>
@@ -23126,7 +23094,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="224" ht="15" customHeight="1">
       <c r="A224" s="1" t="s">
         <v>797</v>
       </c>
@@ -23192,7 +23160,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="225" ht="15" customHeight="1">
       <c r="A225" s="1" t="s">
         <v>836</v>
       </c>
@@ -23274,1022 +23242,1033 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:A198"/>
-  <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2">
+      <c r="A2" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+    <row r="3">
+      <c r="A3" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="4">
+      <c r="A4" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+    <row r="5">
+      <c r="A5" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6">
+      <c r="A6" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="7">
+      <c r="A7" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="8">
+      <c r="A8" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="9">
+      <c r="A9" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10">
+      <c r="A10" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+    <row r="11">
+      <c r="A11" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="12">
+      <c r="A12" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+    <row r="13">
+      <c r="A13" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="15">
+      <c r="A15" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="16">
+      <c r="A16" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="17">
+      <c r="A17" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="18">
+      <c r="A18" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="19">
+      <c r="A19" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="20">
+      <c r="A20" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="21">
+      <c r="A21" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="22">
+      <c r="A22" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="24">
+      <c r="A24" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="25">
+      <c r="A25" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="26">
+      <c r="A26" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="27">
+      <c r="A27" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="28">
+      <c r="A28" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+    <row r="29">
+      <c r="A29" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+    <row r="30">
+      <c r="A30" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+    <row r="31">
+      <c r="A31" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+    <row r="32">
+      <c r="A32" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+    <row r="33">
+      <c r="A33" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+    <row r="34">
+      <c r="A34" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+    <row r="35">
+      <c r="A35" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+    <row r="36">
+      <c r="A36" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+    <row r="37">
+      <c r="A37" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+    <row r="38">
+      <c r="A38" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+    <row r="39">
+      <c r="A39" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+    <row r="40">
+      <c r="A40" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+    <row r="41">
+      <c r="A41" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+    <row r="42">
+      <c r="A42" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+    <row r="43">
+      <c r="A43" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+    <row r="44">
+      <c r="A44" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+    <row r="45">
+      <c r="A45" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+    <row r="46">
+      <c r="A46" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+    <row r="47">
+      <c r="A47" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+    <row r="48">
+      <c r="A48" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+    <row r="49">
+      <c r="A49" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+    <row r="50">
+      <c r="A50" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+    <row r="51">
+      <c r="A51" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+    <row r="52">
+      <c r="A52" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+    <row r="53">
+      <c r="A53" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+    <row r="54">
+      <c r="A54" t="s">
         <v>891</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+    <row r="55">
+      <c r="A55" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+    <row r="56">
+      <c r="A56" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+    <row r="57">
+      <c r="A57" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+    <row r="58">
+      <c r="A58" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+    <row r="59">
+      <c r="A59" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+    <row r="60">
+      <c r="A60" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+    <row r="61">
+      <c r="A61" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+    <row r="62">
+      <c r="A62" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+    <row r="63">
+      <c r="A63" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+    <row r="64">
+      <c r="A64" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+    <row r="65">
+      <c r="A65" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+    <row r="66">
+      <c r="A66" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+    <row r="67">
+      <c r="A67" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
+    <row r="68">
+      <c r="A68" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+    <row r="69">
+      <c r="A69" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+    <row r="70">
+      <c r="A70" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+    <row r="71">
+      <c r="A71" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+    <row r="72">
+      <c r="A72" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+    <row r="73">
+      <c r="A73" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+    <row r="74">
+      <c r="A74" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+    <row r="75">
+      <c r="A75" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+    <row r="76">
+      <c r="A76" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+    <row r="77">
+      <c r="A77" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+    <row r="78">
+      <c r="A78" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+    <row r="79">
+      <c r="A79" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+    <row r="80">
+      <c r="A80" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+    <row r="81">
+      <c r="A81" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+    <row r="82">
+      <c r="A82" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+    <row r="83">
+      <c r="A83" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+    <row r="84">
+      <c r="A84" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+    <row r="85">
+      <c r="A85" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+    <row r="86">
+      <c r="A86" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+    <row r="87">
+      <c r="A87" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+    <row r="88">
+      <c r="A88" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+    <row r="89">
+      <c r="A89" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
+    <row r="90">
+      <c r="A90" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+    <row r="91">
+      <c r="A91" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
+    <row r="92">
+      <c r="A92" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+    <row r="93">
+      <c r="A93" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+    <row r="94">
+      <c r="A94" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+    <row r="95">
+      <c r="A95" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+    <row r="96">
+      <c r="A96" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+    <row r="97">
+      <c r="A97" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+    <row r="98">
+      <c r="A98" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+    <row r="99">
+      <c r="A99" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
+    <row r="100">
+      <c r="A100" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+    <row r="101">
+      <c r="A101" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+    <row r="102">
+      <c r="A102" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+    <row r="103">
+      <c r="A103" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+    <row r="104">
+      <c r="A104" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+    <row r="105">
+      <c r="A105" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+    <row r="106">
+      <c r="A106" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+    <row r="107">
+      <c r="A107" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
+    <row r="108">
+      <c r="A108" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+    <row r="109">
+      <c r="A109" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+    <row r="110">
+      <c r="A110" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+    <row r="111">
+      <c r="A111" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+    <row r="112">
+      <c r="A112" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+    <row r="113">
+      <c r="A113" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
+    <row r="114">
+      <c r="A114" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
+    <row r="115">
+      <c r="A115" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+    <row r="116">
+      <c r="A116" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+    <row r="117">
+      <c r="A117" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+    <row r="118">
+      <c r="A118" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+    <row r="119">
+      <c r="A119" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
+    <row r="120">
+      <c r="A120" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+    <row r="121">
+      <c r="A121" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+    <row r="122">
+      <c r="A122" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
+    <row r="123">
+      <c r="A123" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
+    <row r="124">
+      <c r="A124" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="s">
+    <row r="125">
+      <c r="A125" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
+    <row r="126">
+      <c r="A126" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="s">
+    <row r="127">
+      <c r="A127" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="s">
+    <row r="128">
+      <c r="A128" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="s">
+    <row r="129">
+      <c r="A129" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
+    <row r="130">
+      <c r="A130" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="s">
+    <row r="131">
+      <c r="A131" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="s">
+    <row r="132">
+      <c r="A132" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="s">
+    <row r="133">
+      <c r="A133" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="1" t="s">
+    <row r="134">
+      <c r="A134" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1" t="s">
+    <row r="135">
+      <c r="A135" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
+    <row r="136">
+      <c r="A136" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="1" t="s">
+    <row r="137">
+      <c r="A137" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="1" t="s">
+    <row r="138">
+      <c r="A138" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1" t="s">
+    <row r="139">
+      <c r="A139" t="s">
         <v>976</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="s">
+    <row r="140">
+      <c r="A140" t="s">
         <v>977</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="1" t="s">
+    <row r="141">
+      <c r="A141" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="s">
+    <row r="142">
+      <c r="A142" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="s">
+    <row r="143">
+      <c r="A143" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="1" t="s">
+    <row r="144">
+      <c r="A144" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
         <v>981</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="s">
+    <row r="146">
+      <c r="A146" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="s">
+    <row r="147">
+      <c r="A147" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1" t="s">
+    <row r="148">
+      <c r="A148" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
+    <row r="149">
+      <c r="A149" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1" t="s">
+    <row r="150">
+      <c r="A150" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="s">
+    <row r="151">
+      <c r="A151" t="s">
         <v>987</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="1" t="s">
+    <row r="152">
+      <c r="A152" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="s">
+    <row r="153">
+      <c r="A153" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1" t="s">
+    <row r="154">
+      <c r="A154" t="s">
         <v>990</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1" t="s">
+    <row r="155">
+      <c r="A155" t="s">
         <v>991</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
+    <row r="156">
+      <c r="A156" t="s">
         <v>992</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="s">
+    <row r="157">
+      <c r="A157" t="s">
         <v>993</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1" t="s">
+    <row r="158">
+      <c r="A158" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="s">
+    <row r="160">
+      <c r="A160" t="s">
         <v>995</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="s">
+    <row r="161">
+      <c r="A161" t="s">
         <v>996</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
+    <row r="162">
+      <c r="A162" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="1" t="s">
+    <row r="163">
+      <c r="A163" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
+    <row r="164">
+      <c r="A164" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
+    <row r="165">
+      <c r="A165" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1" t="s">
+    <row r="166">
+      <c r="A166" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="s">
+    <row r="167">
+      <c r="A167" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="s">
+    <row r="168">
+      <c r="A168" t="s">
         <v>1003</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="s">
+    <row r="169">
+      <c r="A169" t="s">
         <v>1004</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="1" t="s">
+    <row r="170">
+      <c r="A170" t="s">
         <v>1005</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="s">
+    <row r="171">
+      <c r="A171" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1" t="s">
+    <row r="172">
+      <c r="A172" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="1" t="s">
+    <row r="173">
+      <c r="A173" t="s">
         <v>1008</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="1" t="s">
+    <row r="174">
+      <c r="A174" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1" t="s">
+    <row r="175">
+      <c r="A175" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1" t="s">
+    <row r="176">
+      <c r="A176" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="1" t="s">
+    <row r="177">
+      <c r="A177" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1" t="s">
+    <row r="178">
+      <c r="A178" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="1" t="s">
+    <row r="179">
+      <c r="A179" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="1" t="s">
+    <row r="180">
+      <c r="A180" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1" t="s">
+    <row r="181">
+      <c r="A181" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="1" t="s">
+    <row r="182">
+      <c r="A182" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="1" t="s">
+    <row r="183">
+      <c r="A183" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="1" t="s">
+    <row r="184">
+      <c r="A184" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1" t="s">
+    <row r="185">
+      <c r="A185" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1" t="s">
+    <row r="186">
+      <c r="A186" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="1" t="s">
+    <row r="187">
+      <c r="A187" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1" t="s">
+    <row r="188">
+      <c r="A188" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="1" t="s">
+    <row r="189">
+      <c r="A189" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="1" t="s">
+    <row r="190">
+      <c r="A190" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="1" t="s">
+    <row r="191">
+      <c r="A191" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="1" t="s">
+    <row r="192">
+      <c r="A192" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="1" t="s">
+    <row r="193">
+      <c r="A193" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="1" t="s">
+    <row r="194">
+      <c r="A194" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="s">
+    <row r="195">
+      <c r="A195" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1" t="s">
+    <row r="196">
+      <c r="A196" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1" t="s">
+    <row r="197">
+      <c r="A197" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1" t="s">
+    <row r="198">
+      <c r="A198" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="s">
+    <row r="199">
+      <c r="A199" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="s">
+    <row r="200">
+      <c r="A200" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1" t="s">
+    <row r="201">
+      <c r="A201" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="s">
+    <row r="202">
+      <c r="A202" t="s">
         <v>1037</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -24569,13 +24548,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DFB1BA48-6859-40B6-8941-0BE426E75326}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{149B4E93-A0C2-46DC-AB12-A4C970BDF621}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6825743B-A19E-477F-BC63-517BD72B0436}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{29AAC093-6BD8-4770-9864-5A90F495B16B}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{18FAEDCC-6552-46D6-96EA-E694CD1A4572}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6724B929-6CB6-4285-8113-85BA668AEC7B}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="600" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="FileList" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FileList" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2709" uniqueCount="1048">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1049" uniqueCount="1049">
   <si>
     <t xml:space="preserve">Citation (APA 7th-Annotated)</t>
   </si>
@@ -3166,16 +3160,19 @@
   </si>
   <si>
     <t xml:space="preserve">UMI%3A3147447_TableA9.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCLC%3A8777719_Table1.tsv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -3184,49 +3181,35 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="12"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="0"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
+      <b/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="0"/>
-      <charset val="1"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="3">
@@ -3243,15 +3226,15 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
-    <border diagonalUp="false" diagonalDown="false">
+  <borders count="2">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -3264,87 +3247,42 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  </cellStyleXfs>
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-  </cellStyleXfs>
-  <cellXfs count="8">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyNumberFormat="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="false" hidden="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment textRotation="0" horizontal="general" vertical="bottom" indent="0"/>
+      <protection hidden="0" locked="0"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -3581,33 +3519,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AM226"/>
-  <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="67.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="1.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="42.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="8.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="1.5"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="7" style="1" width="10.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="6.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="37.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="46.16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="41.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="1" width="7.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="16.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="19" style="1" width="7.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="39" min="28" style="1" width="7.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="40" min="40" style="1" width="10.84"/>
+    <col min="1" max="1" width="67.16" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="2" max="2" width="1.66" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="3" max="3" width="42.66" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="4" max="4" width="8.5" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="5" max="5" width="1.5" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="6" max="6" width="26" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="7" max="7" width="10.33" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="8" max="8" width="10.33" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="9" max="9" width="6.16" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="10" max="10" width="37.16" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="11" max="11" width="46.16" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="12" max="12" width="41.33" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="13" max="13" width="48" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="14" max="14" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="15" max="15" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="16" max="16" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="17" max="17" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="18" max="18" width="16.66" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="19" max="19" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="20" max="20" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="21" max="21" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="22" max="22" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="23" max="23" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="24" max="24" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="25" max="25" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="26" max="26" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="28" max="28" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="29" max="29" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="30" max="30" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="31" max="31" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="32" max="32" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="33" max="33" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="34" max="34" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="35" max="35" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="36" max="36" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="37" max="37" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="38" max="38" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="39" max="39" width="7.34" hidden="false" outlineLevel="0" customWidth="1"/>
+    <col min="40" max="40" width="10.84" hidden="false" outlineLevel="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -3726,7 +3686,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="4" t="s">
         <v>39</v>
       </c>
@@ -3801,7 +3761,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="4" t="s">
         <v>44</v>
       </c>
@@ -3870,7 +3830,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="4" t="s">
         <v>48</v>
       </c>
@@ -3984,7 +3944,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="4" t="s">
         <v>65</v>
       </c>
@@ -4062,7 +4022,7 @@
       <c r="AL5" s="4"/>
       <c r="AM5" s="4"/>
     </row>
-    <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="4" t="s">
         <v>67</v>
       </c>
@@ -4125,7 +4085,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="4" t="s">
         <v>67</v>
       </c>
@@ -4188,7 +4148,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="4" t="s">
         <v>72</v>
       </c>
@@ -4260,7 +4220,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="4" t="s">
         <v>72</v>
       </c>
@@ -4332,7 +4292,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="4" t="s">
         <v>72</v>
       </c>
@@ -4404,7 +4364,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="4" t="s">
         <v>76</v>
       </c>
@@ -4476,7 +4436,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="4" t="s">
         <v>81</v>
       </c>
@@ -4563,7 +4523,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="4" t="s">
         <v>87</v>
       </c>
@@ -4632,7 +4592,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="4" t="s">
         <v>87</v>
       </c>
@@ -4698,7 +4658,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="4" t="s">
         <v>87</v>
       </c>
@@ -4767,7 +4727,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="4" t="s">
         <v>87</v>
       </c>
@@ -4833,7 +4793,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="4" t="s">
         <v>87</v>
       </c>
@@ -4896,7 +4856,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="4" t="s">
         <v>98</v>
       </c>
@@ -4989,7 +4949,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" ht="16.5" customHeight="1">
       <c r="A19" s="4" t="s">
         <v>104</v>
       </c>
@@ -5088,7 +5048,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="4" t="s">
         <v>108</v>
       </c>
@@ -5187,7 +5147,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="4" t="s">
         <v>111</v>
       </c>
@@ -5289,7 +5249,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="4" t="s">
         <v>116</v>
       </c>
@@ -5382,7 +5342,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="4" t="s">
         <v>116</v>
       </c>
@@ -5472,7 +5432,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="4" t="s">
         <v>116</v>
       </c>
@@ -5559,7 +5519,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="4" t="s">
         <v>122</v>
       </c>
@@ -5622,7 +5582,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="4" t="s">
         <v>124</v>
       </c>
@@ -5682,7 +5642,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="4" t="s">
         <v>126</v>
       </c>
@@ -5757,7 +5717,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="4" t="s">
         <v>131</v>
       </c>
@@ -5866,7 +5826,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="4" t="s">
         <v>145</v>
       </c>
@@ -5962,7 +5922,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="4" t="s">
         <v>145</v>
       </c>
@@ -6076,7 +6036,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="4" t="s">
         <v>160</v>
       </c>
@@ -6148,7 +6108,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="4" t="s">
         <v>165</v>
       </c>
@@ -6253,7 +6213,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="4" t="s">
         <v>173</v>
       </c>
@@ -6358,7 +6318,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="4" t="s">
         <v>181</v>
       </c>
@@ -6467,7 +6427,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="4" t="s">
         <v>181</v>
       </c>
@@ -6578,7 +6538,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="4" t="s">
         <v>199</v>
       </c>
@@ -6638,7 +6598,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="4" t="s">
         <v>201</v>
       </c>
@@ -6740,7 +6700,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>213</v>
       </c>
@@ -6852,7 +6812,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>223</v>
       </c>
@@ -6930,7 +6890,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>227</v>
       </c>
@@ -7020,7 +6980,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="4" t="s">
         <v>231</v>
       </c>
@@ -7131,7 +7091,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="4" t="s">
         <v>240</v>
       </c>
@@ -7254,7 +7214,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="4" t="s">
         <v>240</v>
       </c>
@@ -7347,7 +7307,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="4" t="s">
         <v>257</v>
       </c>
@@ -7443,7 +7403,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="4" t="s">
         <v>257</v>
       </c>
@@ -7542,7 +7502,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" ht="15" customHeight="1">
       <c r="A46" s="4" t="s">
         <v>257</v>
       </c>
@@ -7638,7 +7598,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="4" t="s">
         <v>257</v>
       </c>
@@ -7734,7 +7694,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="4" t="s">
         <v>273</v>
       </c>
@@ -7851,7 +7811,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="4" t="s">
         <v>273</v>
       </c>
@@ -7968,7 +7928,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="4" t="s">
         <v>288</v>
       </c>
@@ -8088,7 +8048,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="4" t="s">
         <v>298</v>
       </c>
@@ -8169,7 +8129,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="4" t="s">
         <v>302</v>
       </c>
@@ -8250,7 +8210,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>302</v>
       </c>
@@ -8331,7 +8291,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="4" t="s">
         <v>308</v>
       </c>
@@ -8439,7 +8399,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="4" t="s">
         <v>315</v>
       </c>
@@ -8538,7 +8498,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="4" t="s">
         <v>315</v>
       </c>
@@ -8601,7 +8561,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="4" t="s">
         <v>319</v>
       </c>
@@ -8700,7 +8660,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="58" ht="18.75" customHeight="1">
       <c r="A58" s="4" t="s">
         <v>323</v>
       </c>
@@ -8799,7 +8759,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="59" ht="16.5" customHeight="1">
       <c r="A59" s="4" t="s">
         <v>327</v>
       </c>
@@ -8898,7 +8858,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="60" ht="16.5" customHeight="1">
       <c r="A60" s="4" t="s">
         <v>331</v>
       </c>
@@ -8997,7 +8957,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="61" ht="16.5" customHeight="1">
       <c r="A61" s="4" t="s">
         <v>335</v>
       </c>
@@ -9078,7 +9038,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="62" ht="16.5" customHeight="1">
       <c r="A62" s="4" t="s">
         <v>339</v>
       </c>
@@ -9159,7 +9119,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="63" ht="16.5" customHeight="1">
       <c r="A63" s="4" t="s">
         <v>339</v>
       </c>
@@ -9240,7 +9200,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="4" t="s">
         <v>345</v>
       </c>
@@ -9318,7 +9278,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="4" t="s">
         <v>348</v>
       </c>
@@ -9396,7 +9356,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="4" t="s">
         <v>352</v>
       </c>
@@ -9471,7 +9431,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="4" t="s">
         <v>354</v>
       </c>
@@ -9571,7 +9531,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="4" t="s">
         <v>359</v>
       </c>
@@ -9679,7 +9639,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="4" t="s">
         <v>366</v>
       </c>
@@ -9760,7 +9720,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="4" t="s">
         <v>372</v>
       </c>
@@ -9854,7 +9814,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="4" t="s">
         <v>375</v>
       </c>
@@ -9932,7 +9892,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="4" t="s">
         <v>375</v>
       </c>
@@ -10016,7 +9976,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="4" t="s">
         <v>381</v>
       </c>
@@ -10133,7 +10093,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="4" t="s">
         <v>381</v>
       </c>
@@ -10247,7 +10207,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>381</v>
       </c>
@@ -10361,7 +10321,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="4" t="s">
         <v>381</v>
       </c>
@@ -10475,7 +10435,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="4" t="s">
         <v>381</v>
       </c>
@@ -10589,7 +10549,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="4" t="s">
         <v>399</v>
       </c>
@@ -10706,7 +10666,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="4" t="s">
         <v>399</v>
       </c>
@@ -10823,7 +10783,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="4" t="s">
         <v>412</v>
       </c>
@@ -10907,7 +10867,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="4" t="s">
         <v>412</v>
       </c>
@@ -10994,7 +10954,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="4" t="s">
         <v>412</v>
       </c>
@@ -11081,7 +11041,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="4" t="s">
         <v>417</v>
       </c>
@@ -11159,7 +11119,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="4" t="s">
         <v>417</v>
       </c>
@@ -11237,7 +11197,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="4" t="s">
         <v>417</v>
       </c>
@@ -11315,7 +11275,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="4" t="s">
         <v>417</v>
       </c>
@@ -11393,7 +11353,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="4" t="s">
         <v>417</v>
       </c>
@@ -11471,7 +11431,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="4" t="s">
         <v>417</v>
       </c>
@@ -11549,7 +11509,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="4" t="s">
         <v>426</v>
       </c>
@@ -11643,7 +11603,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="4" t="s">
         <v>426</v>
       </c>
@@ -11737,7 +11697,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="4" t="s">
         <v>426</v>
       </c>
@@ -11831,7 +11791,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="4" t="s">
         <v>426</v>
       </c>
@@ -11925,7 +11885,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="4" t="s">
         <v>435</v>
       </c>
@@ -12009,7 +11969,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="4" t="s">
         <v>435</v>
       </c>
@@ -12093,7 +12053,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="4" t="s">
         <v>441</v>
       </c>
@@ -12210,7 +12170,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="4" t="s">
         <v>448</v>
       </c>
@@ -12288,7 +12248,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="4" t="s">
         <v>453</v>
       </c>
@@ -12372,7 +12332,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="4" t="s">
         <v>453</v>
       </c>
@@ -12456,7 +12416,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="4" t="s">
         <v>453</v>
       </c>
@@ -12540,7 +12500,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>453</v>
       </c>
@@ -12624,7 +12584,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="4" t="s">
         <v>453</v>
       </c>
@@ -12708,7 +12668,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="4" t="s">
         <v>453</v>
       </c>
@@ -12792,7 +12752,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="4" t="s">
         <v>453</v>
       </c>
@@ -12876,7 +12836,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="4" t="s">
         <v>453</v>
       </c>
@@ -12960,7 +12920,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="4" t="s">
         <v>453</v>
       </c>
@@ -13044,7 +13004,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="4" t="s">
         <v>453</v>
       </c>
@@ -13128,7 +13088,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="4" t="s">
         <v>453</v>
       </c>
@@ -13212,7 +13172,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="4" t="s">
         <v>453</v>
       </c>
@@ -13296,7 +13256,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="4" t="s">
         <v>453</v>
       </c>
@@ -13380,7 +13340,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="4" t="s">
         <v>453</v>
       </c>
@@ -13464,7 +13424,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="4" t="s">
         <v>453</v>
       </c>
@@ -13548,7 +13508,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="4" t="s">
         <v>453</v>
       </c>
@@ -13632,7 +13592,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="4" t="s">
         <v>453</v>
       </c>
@@ -13716,7 +13676,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="4" t="s">
         <v>453</v>
       </c>
@@ -13800,7 +13760,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="4" t="s">
         <v>453</v>
       </c>
@@ -13884,7 +13844,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="4" t="s">
         <v>453</v>
       </c>
@@ -13968,7 +13928,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="4" t="s">
         <v>453</v>
       </c>
@@ -14052,7 +14012,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="4" t="s">
         <v>453</v>
       </c>
@@ -14136,7 +14096,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="4" t="s">
         <v>453</v>
       </c>
@@ -14220,7 +14180,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="4" t="s">
         <v>453</v>
       </c>
@@ -14304,7 +14264,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="4" t="s">
         <v>505</v>
       </c>
@@ -14394,7 +14354,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="122" ht="15" customHeight="1">
       <c r="A122" s="4" t="s">
         <v>508</v>
       </c>
@@ -14490,7 +14450,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="123" ht="15" customHeight="1">
       <c r="A123" s="4" t="s">
         <v>508</v>
       </c>
@@ -14586,7 +14546,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="124" ht="15" customHeight="1">
       <c r="A124" s="4" t="s">
         <v>508</v>
       </c>
@@ -14682,7 +14642,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="125" ht="15" customHeight="1">
       <c r="A125" s="4" t="s">
         <v>508</v>
       </c>
@@ -14778,7 +14738,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="126" ht="15" customHeight="1">
       <c r="A126" s="4" t="s">
         <v>508</v>
       </c>
@@ -14874,7 +14834,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="127" ht="15" customHeight="1">
       <c r="A127" s="4" t="s">
         <v>508</v>
       </c>
@@ -14970,7 +14930,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="128" ht="15" customHeight="1">
       <c r="A128" s="4" t="s">
         <v>508</v>
       </c>
@@ -15066,7 +15026,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="129" ht="15" customHeight="1">
       <c r="A129" s="4" t="s">
         <v>508</v>
       </c>
@@ -15162,7 +15122,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="130" ht="15" customHeight="1">
       <c r="A130" s="4" t="s">
         <v>508</v>
       </c>
@@ -15258,7 +15218,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="131" ht="15" customHeight="1">
       <c r="A131" s="4" t="s">
         <v>508</v>
       </c>
@@ -15354,7 +15314,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="132" ht="15" customHeight="1">
       <c r="A132" s="4" t="s">
         <v>508</v>
       </c>
@@ -15450,7 +15410,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="133" ht="15" customHeight="1">
       <c r="A133" s="4" t="s">
         <v>508</v>
       </c>
@@ -15546,7 +15506,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="134" ht="15" customHeight="1">
       <c r="A134" s="4" t="s">
         <v>508</v>
       </c>
@@ -15642,7 +15602,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="135" ht="15" customHeight="1">
       <c r="A135" s="4" t="s">
         <v>508</v>
       </c>
@@ -15738,7 +15698,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="136" ht="15" customHeight="1">
       <c r="A136" s="4" t="s">
         <v>508</v>
       </c>
@@ -15834,7 +15794,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="137" ht="15" customHeight="1">
       <c r="A137" s="4" t="s">
         <v>573</v>
       </c>
@@ -15904,7 +15864,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="138" ht="15" customHeight="1">
       <c r="A138" s="4" t="s">
         <v>573</v>
       </c>
@@ -15971,7 +15931,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="139" ht="15" customHeight="1">
       <c r="A139" s="4" t="s">
         <v>573</v>
       </c>
@@ -16038,7 +15998,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="140" ht="15" customHeight="1">
       <c r="A140" s="4" t="s">
         <v>573</v>
       </c>
@@ -16108,7 +16068,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="141" ht="15" customHeight="1">
       <c r="A141" s="4" t="s">
         <v>573</v>
       </c>
@@ -16178,7 +16138,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="142" ht="15" customHeight="1">
       <c r="A142" s="4" t="s">
         <v>573</v>
       </c>
@@ -16248,7 +16208,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="143" ht="15" customHeight="1">
       <c r="A143" s="4" t="s">
         <v>573</v>
       </c>
@@ -16318,7 +16278,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="144" ht="15" customHeight="1">
       <c r="A144" s="4" t="s">
         <v>591</v>
       </c>
@@ -16382,7 +16342,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="145" ht="15" customHeight="1">
       <c r="A145" s="4" t="s">
         <v>593</v>
       </c>
@@ -16490,7 +16450,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="146" ht="15" customHeight="1">
       <c r="A146" s="4" t="s">
         <v>593</v>
       </c>
@@ -16604,7 +16564,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="147" ht="15" customHeight="1">
       <c r="A147" s="4" t="s">
         <v>593</v>
       </c>
@@ -16721,7 +16681,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="148" ht="15" customHeight="1">
       <c r="A148" s="4" t="s">
         <v>611</v>
       </c>
@@ -16796,7 +16756,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="149" ht="15" customHeight="1">
       <c r="A149" s="4" t="s">
         <v>615</v>
       </c>
@@ -16874,7 +16834,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="150" ht="15" customHeight="1">
       <c r="A150" s="4" t="s">
         <v>615</v>
       </c>
@@ -16952,7 +16912,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="151" ht="15" customHeight="1">
       <c r="A151" s="4" t="s">
         <v>620</v>
       </c>
@@ -17030,7 +16990,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="152" ht="15" customHeight="1">
       <c r="A152" s="4" t="s">
         <v>624</v>
       </c>
@@ -17096,7 +17056,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="153" ht="15" customHeight="1">
       <c r="A153" s="4" t="s">
         <v>628</v>
       </c>
@@ -17186,7 +17146,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="154" ht="15" customHeight="1">
       <c r="A154" s="4" t="s">
         <v>628</v>
       </c>
@@ -17276,11 +17236,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="155" ht="15" customHeight="1">
       <c r="A155" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="D155" s="6" t="s">
+      <c r="D155" s="4" t="s">
         <v>635</v>
       </c>
       <c r="E155" s="5" t="str">
@@ -17379,7 +17339,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="156" ht="15" customHeight="1">
       <c r="A156" s="4" t="s">
         <v>640</v>
       </c>
@@ -17443,7 +17403,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="157" ht="15" customHeight="1">
       <c r="A157" s="4" t="s">
         <v>642</v>
       </c>
@@ -17542,7 +17502,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="158" ht="15" customHeight="1">
       <c r="A158" s="4" t="s">
         <v>645</v>
       </c>
@@ -17617,7 +17577,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="159" ht="15" customHeight="1">
       <c r="A159" s="4" t="s">
         <v>646</v>
       </c>
@@ -17692,7 +17652,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="160" ht="15" customHeight="1">
       <c r="A160" s="4" t="s">
         <v>648</v>
       </c>
@@ -17773,7 +17733,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="161" ht="15" customHeight="1">
       <c r="A161" s="4" t="s">
         <v>654</v>
       </c>
@@ -17879,7 +17839,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="162" ht="15" customHeight="1">
       <c r="A162" s="4" t="s">
         <v>659</v>
       </c>
@@ -17954,7 +17914,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="163" ht="15" customHeight="1">
       <c r="A163" s="4" t="s">
         <v>661</v>
       </c>
@@ -18023,7 +17983,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="164" ht="15" customHeight="1">
       <c r="A164" s="4" t="s">
         <v>663</v>
       </c>
@@ -18098,7 +18058,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="165" ht="15" customHeight="1">
       <c r="A165" s="4" t="s">
         <v>667</v>
       </c>
@@ -18158,7 +18118,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="166" ht="15" customHeight="1">
       <c r="A166" s="4" t="s">
         <v>668</v>
       </c>
@@ -18248,7 +18208,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="167" ht="15" customHeight="1">
       <c r="A167" s="4" t="s">
         <v>671</v>
       </c>
@@ -18338,7 +18298,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="168" ht="15" customHeight="1">
       <c r="A168" s="4" t="s">
         <v>674</v>
       </c>
@@ -18425,7 +18385,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="169" ht="15" customHeight="1">
       <c r="A169" s="4" t="s">
         <v>677</v>
       </c>
@@ -18485,7 +18445,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="170" ht="15" customHeight="1">
       <c r="A170" s="4" t="s">
         <v>679</v>
       </c>
@@ -18545,7 +18505,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="171" ht="15" customHeight="1">
       <c r="A171" s="4" t="s">
         <v>680</v>
       </c>
@@ -18605,7 +18565,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="172" ht="15" customHeight="1">
       <c r="A172" s="4" t="s">
         <v>682</v>
       </c>
@@ -18683,7 +18643,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="173" ht="15" customHeight="1">
       <c r="A173" s="4" t="s">
         <v>682</v>
       </c>
@@ -18762,7 +18722,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="174" ht="15" customHeight="1">
       <c r="A174" s="4" t="s">
         <v>687</v>
       </c>
@@ -18856,7 +18816,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="175" ht="15" customHeight="1">
       <c r="A175" s="4" t="s">
         <v>690</v>
       </c>
@@ -18962,7 +18922,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="176" ht="15" customHeight="1">
       <c r="A176" s="4" t="s">
         <v>690</v>
       </c>
@@ -19071,7 +19031,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="177" ht="15" customHeight="1">
       <c r="A177" s="4" t="s">
         <v>698</v>
       </c>
@@ -19155,7 +19115,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="178" ht="15" customHeight="1">
       <c r="A178" s="4" t="s">
         <v>704</v>
       </c>
@@ -19257,7 +19217,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="179" ht="15" customHeight="1">
       <c r="A179" s="4" t="s">
         <v>704</v>
       </c>
@@ -19359,7 +19319,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="180" ht="15" customHeight="1">
       <c r="A180" s="4" t="s">
         <v>714</v>
       </c>
@@ -19446,7 +19406,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="181" ht="15" customHeight="1">
       <c r="A181" s="4" t="s">
         <v>714</v>
       </c>
@@ -19533,7 +19493,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="182" ht="15" customHeight="1">
       <c r="A182" s="4" t="s">
         <v>718</v>
       </c>
@@ -19620,7 +19580,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="183" ht="15" customHeight="1">
       <c r="A183" s="4" t="s">
         <v>723</v>
       </c>
@@ -19722,7 +19682,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="184" ht="15" customHeight="1">
       <c r="A184" s="4" t="s">
         <v>727</v>
       </c>
@@ -19788,7 +19748,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="185" ht="15" customHeight="1">
       <c r="A185" s="4" t="s">
         <v>730</v>
       </c>
@@ -19875,7 +19835,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="186" ht="15" customHeight="1">
       <c r="A186" s="4" t="s">
         <v>730</v>
       </c>
@@ -19962,7 +19922,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="187" ht="15" customHeight="1">
       <c r="A187" s="4" t="s">
         <v>730</v>
       </c>
@@ -20049,7 +20009,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="188" ht="15" customHeight="1">
       <c r="A188" s="4" t="s">
         <v>730</v>
       </c>
@@ -20136,7 +20096,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="189" ht="15" customHeight="1">
       <c r="A189" s="4" t="s">
         <v>730</v>
       </c>
@@ -20223,7 +20183,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="190" ht="15" customHeight="1">
       <c r="A190" s="4" t="s">
         <v>730</v>
       </c>
@@ -20310,7 +20270,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="191" ht="15" customHeight="1">
       <c r="A191" s="4" t="s">
         <v>730</v>
       </c>
@@ -20403,7 +20363,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="192" ht="15" customHeight="1">
       <c r="A192" s="4" t="s">
         <v>745</v>
       </c>
@@ -20505,7 +20465,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="193" ht="15" customHeight="1">
       <c r="A193" s="4" t="s">
         <v>749</v>
       </c>
@@ -20607,7 +20567,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="194" ht="15" customHeight="1">
       <c r="A194" s="4" t="s">
         <v>753</v>
       </c>
@@ -20700,7 +20660,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="195" ht="15" customHeight="1">
       <c r="A195" s="4" t="s">
         <v>753</v>
       </c>
@@ -20793,7 +20753,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="196" ht="15" customHeight="1">
       <c r="A196" s="4" t="s">
         <v>753</v>
       </c>
@@ -20886,7 +20846,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="197" ht="15" customHeight="1">
       <c r="A197" s="4" t="s">
         <v>753</v>
       </c>
@@ -20979,7 +20939,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="198" ht="15" customHeight="1">
       <c r="A198" s="4" t="s">
         <v>753</v>
       </c>
@@ -21072,7 +21032,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="199" ht="15" customHeight="1">
       <c r="A199" s="4" t="s">
         <v>753</v>
       </c>
@@ -21165,11 +21125,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="200" ht="15" customHeight="1">
       <c r="A200" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="C200" s="7"/>
+      <c r="C200" s="6"/>
       <c r="D200" s="4" t="s">
         <v>766</v>
       </c>
@@ -21259,11 +21219,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="201" ht="15" customHeight="1">
       <c r="A201" s="4" t="s">
         <v>768</v>
       </c>
-      <c r="C201" s="7"/>
+      <c r="C201" s="6"/>
       <c r="D201" s="4" t="s">
         <v>769</v>
       </c>
@@ -21323,11 +21283,11 @@
         <v>770</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="202" ht="15" customHeight="1">
       <c r="A202" s="4" t="s">
         <v>771</v>
       </c>
-      <c r="C202" s="7"/>
+      <c r="C202" s="6"/>
       <c r="D202" s="4" t="s">
         <v>772</v>
       </c>
@@ -21387,11 +21347,11 @@
         <v>773</v>
       </c>
     </row>
-    <row r="203" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="203" ht="15" customHeight="1">
       <c r="A203" s="4" t="s">
         <v>774</v>
       </c>
-      <c r="C203" s="7"/>
+      <c r="C203" s="6"/>
       <c r="D203" s="4" t="s">
         <v>775</v>
       </c>
@@ -21451,7 +21411,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="204" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="204" ht="15" customHeight="1">
       <c r="A204" s="4" t="s">
         <v>753</v>
       </c>
@@ -21544,7 +21504,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="205" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="205" ht="15" customHeight="1">
       <c r="A205" s="4" t="s">
         <v>753</v>
       </c>
@@ -21637,7 +21597,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="206" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="206" ht="15" customHeight="1">
       <c r="A206" s="4" t="s">
         <v>753</v>
       </c>
@@ -21730,7 +21690,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="207" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="207" ht="15" customHeight="1">
       <c r="A207" s="4" t="s">
         <v>753</v>
       </c>
@@ -21823,7 +21783,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="208" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="208" ht="15" customHeight="1">
       <c r="A208" s="4" t="s">
         <v>753</v>
       </c>
@@ -21916,7 +21876,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="209" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="209" ht="15" customHeight="1">
       <c r="A209" s="4" t="s">
         <v>753</v>
       </c>
@@ -22009,11 +21969,11 @@
         <v>86</v>
       </c>
     </row>
-    <row r="210" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="210" ht="15" customHeight="1">
       <c r="A210" s="4" t="s">
         <v>753</v>
       </c>
-      <c r="C210" s="7"/>
+      <c r="C210" s="6"/>
       <c r="D210" s="4" t="s">
         <v>789</v>
       </c>
@@ -22106,7 +22066,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="211" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="211" ht="15" customHeight="1">
       <c r="A211" s="4" t="s">
         <v>791</v>
       </c>
@@ -22193,7 +22153,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="212" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="212" ht="15" customHeight="1">
       <c r="A212" s="4" t="s">
         <v>791</v>
       </c>
@@ -22280,7 +22240,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="213" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="213" ht="15" customHeight="1">
       <c r="A213" s="4" t="s">
         <v>794</v>
       </c>
@@ -22355,7 +22315,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="214" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="214" ht="15" customHeight="1">
       <c r="A214" s="4" t="s">
         <v>797</v>
       </c>
@@ -22421,7 +22381,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="215" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="215" ht="15" customHeight="1">
       <c r="A215" s="4" t="s">
         <v>797</v>
       </c>
@@ -22487,7 +22447,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="216" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="216" ht="15" customHeight="1">
       <c r="A216" s="4" t="s">
         <v>802</v>
       </c>
@@ -22559,7 +22519,7 @@
         <v>805</v>
       </c>
     </row>
-    <row r="217" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="217" ht="15" customHeight="1">
       <c r="A217" s="4" t="s">
         <v>806</v>
       </c>
@@ -22631,7 +22591,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="218" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="218" ht="15" customHeight="1">
       <c r="A218" s="4" t="s">
         <v>808</v>
       </c>
@@ -22722,7 +22682,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="219" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="219" ht="15" customHeight="1">
       <c r="A219" s="4" t="s">
         <v>813</v>
       </c>
@@ -22816,7 +22776,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="220" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="220" ht="15" customHeight="1">
       <c r="A220" s="4" t="s">
         <v>816</v>
       </c>
@@ -22903,7 +22863,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="221" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="221" ht="15" customHeight="1">
       <c r="A221" s="4" t="s">
         <v>821</v>
       </c>
@@ -22993,7 +22953,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="222" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="222" ht="15" customHeight="1">
       <c r="A222" s="4" t="s">
         <v>827</v>
       </c>
@@ -23080,7 +23040,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="223" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="223" ht="15" customHeight="1">
       <c r="A223" s="5" t="s">
         <v>67</v>
       </c>
@@ -23143,7 +23103,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="224" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="224" ht="15" customHeight="1">
       <c r="A224" s="5" t="s">
         <v>797</v>
       </c>
@@ -23209,7 +23169,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="225" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="225" ht="15" customHeight="1">
       <c r="A225" s="5" t="s">
         <v>836</v>
       </c>
@@ -23290,7 +23250,7 @@
         <v>839</v>
       </c>
     </row>
-    <row r="226" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="226" ht="15" customHeight="1">
       <c r="A226" s="1" t="s">
         <v>840</v>
       </c>
@@ -23375,1042 +23335,1038 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.583333333333333" bottom="0.583333333333333" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
+  <headerFooter differentOddEven="0" differentFirst="0" scaleWithDoc="0" alignWithMargins="0">
+    <oddHeader>&amp;L&amp;C&amp;R</oddHeader>
+    <oddFooter>&amp;L&amp;C&amp;R</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:A202"/>
-  <sheetFormatPr defaultColWidth="10.6171875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="s">
+    <row r="2">
+      <c r="A2" t="s">
         <v>847</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="s">
+    <row r="3">
+      <c r="A3" t="s">
         <v>848</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="s">
+    <row r="4">
+      <c r="A4" t="s">
         <v>849</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
+    <row r="5">
+      <c r="A5" t="s">
         <v>850</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="s">
+    <row r="6">
+      <c r="A6" t="s">
         <v>851</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="s">
+    <row r="7">
+      <c r="A7" t="s">
         <v>852</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="s">
+    <row r="8">
+      <c r="A8" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="s">
+    <row r="9">
+      <c r="A9" t="s">
         <v>854</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="s">
+    <row r="10">
+      <c r="A10" t="s">
         <v>855</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="s">
+    <row r="11">
+      <c r="A11" t="s">
         <v>856</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="s">
+    <row r="12">
+      <c r="A12" t="s">
         <v>857</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="s">
+    <row r="13">
+      <c r="A13" t="s">
         <v>858</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="s">
+    <row r="14">
+      <c r="A14" t="s">
         <v>859</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="s">
+    <row r="15">
+      <c r="A15" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
+    <row r="16">
+      <c r="A16" t="s">
         <v>861</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="s">
+    <row r="17">
+      <c r="A17" t="s">
         <v>862</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="s">
+    <row r="18">
+      <c r="A18" t="s">
         <v>863</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="s">
+    <row r="19">
+      <c r="A19" t="s">
         <v>864</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="20">
+      <c r="A20" t="s">
         <v>865</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21">
+      <c r="A21" t="s">
         <v>866</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="22">
+      <c r="A22" t="s">
         <v>867</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="23">
+      <c r="A23" t="s">
         <v>868</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+    <row r="24">
+      <c r="A24" t="s">
         <v>869</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="s">
+    <row r="25">
+      <c r="A25" t="s">
         <v>870</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="s">
+    <row r="26">
+      <c r="A26" t="s">
         <v>871</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
+    <row r="27">
+      <c r="A27" t="s">
         <v>872</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
+    <row r="28">
+      <c r="A28" t="s">
         <v>873</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
+    <row r="29">
+      <c r="A29" t="s">
         <v>874</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
+    <row r="30">
+      <c r="A30" t="s">
         <v>875</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
+    <row r="31">
+      <c r="A31" t="s">
         <v>876</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
+    <row r="32">
+      <c r="A32" t="s">
         <v>877</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
+    <row r="33">
+      <c r="A33" t="s">
         <v>878</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
+    <row r="34">
+      <c r="A34" t="s">
         <v>879</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
+    <row r="35">
+      <c r="A35" t="s">
         <v>880</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
+    <row r="36">
+      <c r="A36" t="s">
         <v>881</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
+    <row r="37">
+      <c r="A37" t="s">
         <v>882</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
+    <row r="38">
+      <c r="A38" t="s">
         <v>883</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
+    <row r="39">
+      <c r="A39" t="s">
         <v>884</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
+    <row r="40">
+      <c r="A40" t="s">
         <v>885</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
+    <row r="41">
+      <c r="A41" t="s">
         <v>886</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
+    <row r="42">
+      <c r="A42" t="s">
         <v>887</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
+    <row r="43">
+      <c r="A43" t="s">
         <v>888</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
+    <row r="44">
+      <c r="A44" t="s">
         <v>889</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
+    <row r="45">
+      <c r="A45" t="s">
         <v>890</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
+    <row r="46">
+      <c r="A46" t="s">
         <v>891</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
+    <row r="47">
+      <c r="A47" t="s">
         <v>892</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="s">
+    <row r="48">
+      <c r="A48" t="s">
         <v>893</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
+    <row r="49">
+      <c r="A49" t="s">
         <v>894</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+    <row r="50">
+      <c r="A50" t="s">
         <v>895</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+    <row r="51">
+      <c r="A51" t="s">
         <v>896</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
+    <row r="52">
+      <c r="A52" t="s">
         <v>897</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+    <row r="53">
+      <c r="A53" t="s">
         <v>898</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+    <row r="54">
+      <c r="A54" t="s">
         <v>899</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+    <row r="55">
+      <c r="A55" t="s">
         <v>900</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+    <row r="56">
+      <c r="A56" t="s">
         <v>901</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
+    <row r="57">
+      <c r="A57" t="s">
         <v>902</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+    <row r="58">
+      <c r="A58" t="s">
         <v>903</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+    <row r="59">
+      <c r="A59" t="s">
         <v>904</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="1" t="s">
+    <row r="60">
+      <c r="A60" t="s">
         <v>905</v>
       </c>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="1" t="s">
+    <row r="61">
+      <c r="A61" t="s">
         <v>906</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="1" t="s">
+    <row r="62">
+      <c r="A62" t="s">
         <v>907</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="1" t="s">
+    <row r="63">
+      <c r="A63" t="s">
         <v>908</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A64" s="1" t="s">
+    <row r="64">
+      <c r="A64" t="s">
         <v>909</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="1" t="s">
+    <row r="65">
+      <c r="A65" t="s">
         <v>910</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="1" t="s">
+    <row r="66">
+      <c r="A66" t="s">
         <v>911</v>
       </c>
     </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="1" t="s">
+    <row r="67">
+      <c r="A67" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="1" t="s">
+    <row r="68">
+      <c r="A68" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A69" s="1" t="s">
+    <row r="69">
+      <c r="A69" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A70" s="1" t="s">
+    <row r="70">
+      <c r="A70" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+    <row r="71">
+      <c r="A71" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="1" t="s">
+    <row r="72">
+      <c r="A72" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A73" s="1" t="s">
+    <row r="73">
+      <c r="A73" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A74" s="1" t="s">
+    <row r="74">
+      <c r="A74" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="1" t="s">
+    <row r="75">
+      <c r="A75" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="1" t="s">
+    <row r="76">
+      <c r="A76" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="1" t="s">
+    <row r="77">
+      <c r="A77" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="1" t="s">
+    <row r="78">
+      <c r="A78" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="1" t="s">
+    <row r="79">
+      <c r="A79" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="1" t="s">
+    <row r="80">
+      <c r="A80" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="1" t="s">
+    <row r="81">
+      <c r="A81" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A82" s="1" t="s">
+    <row r="82">
+      <c r="A82" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="1" t="s">
+    <row r="83">
+      <c r="A83" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="1" t="s">
+    <row r="84">
+      <c r="A84" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="1" t="s">
+    <row r="85">
+      <c r="A85" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="1" t="s">
+    <row r="86">
+      <c r="A86" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="1" t="s">
+    <row r="87">
+      <c r="A87" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="1" t="s">
+    <row r="88">
+      <c r="A88" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="1" t="s">
+    <row r="89">
+      <c r="A89" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="1" t="s">
+    <row r="90">
+      <c r="A90" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A91" s="1" t="s">
+    <row r="91">
+      <c r="A91" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="1" t="s">
+    <row r="92">
+      <c r="A92" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
+    <row r="93">
+      <c r="A93" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="1" t="s">
+    <row r="94">
+      <c r="A94" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
+    <row r="95">
+      <c r="A95" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A96" s="1" t="s">
+    <row r="96">
+      <c r="A96" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+    <row r="97">
+      <c r="A97" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A98" s="1" t="s">
+    <row r="98">
+      <c r="A98" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+    <row r="99">
+      <c r="A99" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A100" s="1" t="s">
+    <row r="100">
+      <c r="A100" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A101" s="1" t="s">
+    <row r="101">
+      <c r="A101" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A102" s="1" t="s">
+    <row r="102">
+      <c r="A102" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A103" s="1" t="s">
+    <row r="103">
+      <c r="A103" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A104" s="1" t="s">
+    <row r="104">
+      <c r="A104" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+    <row r="105">
+      <c r="A105" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A106" s="1" t="s">
+    <row r="106">
+      <c r="A106" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+    <row r="107">
+      <c r="A107" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+    <row r="108">
+      <c r="A108" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+    <row r="109">
+      <c r="A109" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A110" s="1" t="s">
+    <row r="110">
+      <c r="A110" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+    <row r="111">
+      <c r="A111" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
+    <row r="112">
+      <c r="A112" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
+    <row r="113">
+      <c r="A113" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+    <row r="114">
+      <c r="A114" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+    <row r="115">
+      <c r="A115" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A116" s="1" t="s">
+    <row r="116">
+      <c r="A116" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+    <row r="117">
+      <c r="A117" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A118" s="1" t="s">
+    <row r="118">
+      <c r="A118" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A119" s="1" t="s">
+    <row r="119">
+      <c r="A119" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A120" s="1" t="s">
+    <row r="120">
+      <c r="A120" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A121" s="1" t="s">
+    <row r="121">
+      <c r="A121" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A122" s="1" t="s">
+    <row r="122">
+      <c r="A122" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A123" s="1" t="s">
+    <row r="123">
+      <c r="A123" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A124" s="1" t="s">
+    <row r="124">
+      <c r="A124" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A125" s="1" t="s">
+    <row r="125">
+      <c r="A125" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A126" s="1" t="s">
+    <row r="126">
+      <c r="A126" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A127" s="1" t="s">
+    <row r="127">
+      <c r="A127" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A128" s="1" t="s">
+    <row r="128">
+      <c r="A128" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A129" s="1" t="s">
+    <row r="129">
+      <c r="A129" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A130" s="1" t="s">
+    <row r="130">
+      <c r="A130" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A131" s="1" t="s">
+    <row r="131">
+      <c r="A131" t="s">
         <v>976</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A132" s="1" t="s">
+    <row r="132">
+      <c r="A132" t="s">
         <v>977</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A133" s="1" t="s">
+    <row r="133">
+      <c r="A133" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
+    <row r="134">
+      <c r="A134" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A135" s="1" t="s">
+    <row r="135">
+      <c r="A135" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A136" s="1" t="s">
+    <row r="136">
+      <c r="A136" t="s">
         <v>981</v>
       </c>
     </row>
-    <row r="137" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A137" s="1" t="s">
+    <row r="137">
+      <c r="A137" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="138" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A138" s="1" t="s">
+    <row r="138">
+      <c r="A138" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="139" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A139" s="1" t="s">
+    <row r="139">
+      <c r="A139" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="140" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A140" s="1" t="s">
+    <row r="140">
+      <c r="A140" t="s">
         <v>985</v>
       </c>
     </row>
-    <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A141" s="1" t="s">
+    <row r="141">
+      <c r="A141" t="s">
         <v>986</v>
       </c>
     </row>
-    <row r="142" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A142" s="1" t="s">
+    <row r="142">
+      <c r="A142" t="s">
         <v>987</v>
       </c>
     </row>
-    <row r="143" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A143" s="1" t="s">
+    <row r="143">
+      <c r="A143" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="144" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A144" s="1" t="s">
+    <row r="144">
+      <c r="A144" t="s">
         <v>989</v>
       </c>
     </row>
-    <row r="145" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A145" s="1" t="s">
+    <row r="145">
+      <c r="A145" t="s">
         <v>990</v>
       </c>
     </row>
-    <row r="146" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A146" s="1" t="s">
+    <row r="146">
+      <c r="A146" t="s">
         <v>991</v>
       </c>
     </row>
-    <row r="147" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A147" s="1" t="s">
+    <row r="147">
+      <c r="A147" t="s">
         <v>992</v>
       </c>
     </row>
-    <row r="148" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A148" s="1" t="s">
+    <row r="148">
+      <c r="A148" t="s">
         <v>993</v>
       </c>
     </row>
-    <row r="149" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A149" s="1" t="s">
+    <row r="149">
+      <c r="A149" t="s">
         <v>994</v>
       </c>
     </row>
-    <row r="150" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A150" s="1" t="s">
+    <row r="150">
+      <c r="A150" t="s">
         <v>995</v>
       </c>
     </row>
-    <row r="151" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A151" s="1" t="s">
+    <row r="151">
+      <c r="A151" t="s">
         <v>996</v>
       </c>
     </row>
-    <row r="152" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A152" s="1" t="s">
+    <row r="152">
+      <c r="A152" t="s">
         <v>997</v>
       </c>
     </row>
-    <row r="153" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A153" s="1" t="s">
+    <row r="153">
+      <c r="A153" t="s">
         <v>998</v>
       </c>
     </row>
-    <row r="154" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A154" s="1" t="s">
+    <row r="154">
+      <c r="A154" t="s">
         <v>999</v>
       </c>
     </row>
-    <row r="155" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A155" s="1" t="s">
+    <row r="155">
+      <c r="A155" t="s">
         <v>1000</v>
       </c>
     </row>
-    <row r="156" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A156" s="1" t="s">
+    <row r="156">
+      <c r="A156" t="s">
         <v>1001</v>
       </c>
     </row>
-    <row r="157" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="1" t="s">
+    <row r="157">
+      <c r="A157" t="s">
         <v>1002</v>
       </c>
     </row>
-    <row r="158" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A158" s="1" t="s">
+    <row r="158">
+      <c r="A158" t="s">
         <v>1003</v>
       </c>
     </row>
-    <row r="159" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A159" s="1" t="s">
+    <row r="159">
+      <c r="A159" t="s">
         <v>1004</v>
       </c>
     </row>
-    <row r="160" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A160" s="1" t="s">
+    <row r="160">
+      <c r="A160" t="s">
         <v>1005</v>
       </c>
     </row>
-    <row r="161" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A161" s="1" t="s">
+    <row r="161">
+      <c r="A161" t="s">
         <v>1006</v>
       </c>
     </row>
-    <row r="162" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A162" s="1" t="s">
+    <row r="162">
+      <c r="A162" t="s">
         <v>1007</v>
       </c>
     </row>
-    <row r="163" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A163" s="1" t="s">
+    <row r="163">
+      <c r="A163" t="s">
         <v>1008</v>
       </c>
     </row>
-    <row r="164" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A164" s="1" t="s">
+    <row r="164">
+      <c r="A164" t="s">
         <v>1009</v>
       </c>
     </row>
-    <row r="165" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A165" s="1" t="s">
+    <row r="165">
+      <c r="A165" t="s">
         <v>1010</v>
       </c>
     </row>
-    <row r="166" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A166" s="1" t="s">
+    <row r="166">
+      <c r="A166" t="s">
         <v>1011</v>
       </c>
     </row>
-    <row r="167" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A167" s="1" t="s">
+    <row r="167">
+      <c r="A167" t="s">
         <v>1012</v>
       </c>
     </row>
-    <row r="168" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A168" s="1" t="s">
+    <row r="168">
+      <c r="A168" t="s">
         <v>1013</v>
       </c>
     </row>
-    <row r="169" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A169" s="1" t="s">
+    <row r="169">
+      <c r="A169" t="s">
         <v>1014</v>
       </c>
     </row>
-    <row r="170" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A170" s="1" t="s">
+    <row r="170">
+      <c r="A170" t="s">
         <v>1015</v>
       </c>
     </row>
-    <row r="171" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A171" s="1" t="s">
+    <row r="171">
+      <c r="A171" t="s">
         <v>1016</v>
       </c>
     </row>
-    <row r="172" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A172" s="1" t="s">
+    <row r="172">
+      <c r="A172" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
         <v>1017</v>
       </c>
     </row>
-    <row r="173" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A173" s="1" t="s">
+    <row r="174">
+      <c r="A174" t="s">
         <v>1018</v>
       </c>
     </row>
-    <row r="174" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A174" s="1" t="s">
+    <row r="175">
+      <c r="A175" t="s">
         <v>1019</v>
       </c>
     </row>
-    <row r="175" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A175" s="1" t="s">
+    <row r="176">
+      <c r="A176" t="s">
         <v>1020</v>
       </c>
     </row>
-    <row r="176" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A176" s="1" t="s">
+    <row r="177">
+      <c r="A177" t="s">
         <v>1021</v>
       </c>
     </row>
-    <row r="177" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A177" s="1" t="s">
+    <row r="178">
+      <c r="A178" t="s">
         <v>1022</v>
       </c>
     </row>
-    <row r="178" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A178" s="1" t="s">
+    <row r="179">
+      <c r="A179" t="s">
         <v>1023</v>
       </c>
     </row>
-    <row r="179" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A179" s="1" t="s">
+    <row r="180">
+      <c r="A180" t="s">
         <v>1024</v>
       </c>
     </row>
-    <row r="180" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A180" s="1" t="s">
+    <row r="181">
+      <c r="A181" t="s">
         <v>1025</v>
       </c>
     </row>
-    <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A181" s="1" t="s">
+    <row r="182">
+      <c r="A182" t="s">
         <v>1026</v>
       </c>
     </row>
-    <row r="182" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A182" s="1" t="s">
+    <row r="183">
+      <c r="A183" t="s">
         <v>1027</v>
       </c>
     </row>
-    <row r="183" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A183" s="1" t="s">
+    <row r="184">
+      <c r="A184" t="s">
         <v>1028</v>
       </c>
     </row>
-    <row r="184" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A184" s="1" t="s">
+    <row r="185">
+      <c r="A185" t="s">
         <v>1029</v>
       </c>
     </row>
-    <row r="185" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A185" s="1" t="s">
+    <row r="186">
+      <c r="A186" t="s">
         <v>1030</v>
       </c>
     </row>
-    <row r="186" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A186" s="1" t="s">
+    <row r="187">
+      <c r="A187" t="s">
         <v>1031</v>
       </c>
     </row>
-    <row r="187" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A187" s="1" t="s">
+    <row r="188">
+      <c r="A188" t="s">
         <v>1032</v>
       </c>
     </row>
-    <row r="188" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A188" s="1" t="s">
+    <row r="189">
+      <c r="A189" t="s">
         <v>1033</v>
       </c>
     </row>
-    <row r="189" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A189" s="1" t="s">
+    <row r="190">
+      <c r="A190" t="s">
         <v>1034</v>
       </c>
     </row>
-    <row r="190" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A190" s="1" t="s">
+    <row r="191">
+      <c r="A191" t="s">
         <v>1035</v>
       </c>
     </row>
-    <row r="191" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A191" s="1" t="s">
+    <row r="192">
+      <c r="A192" t="s">
         <v>1036</v>
       </c>
     </row>
-    <row r="192" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A192" s="1" t="s">
+    <row r="193">
+      <c r="A193" t="s">
         <v>1037</v>
       </c>
     </row>
-    <row r="193" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A193" s="1" t="s">
+    <row r="194">
+      <c r="A194" t="s">
         <v>1038</v>
       </c>
     </row>
-    <row r="194" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A194" s="1" t="s">
+    <row r="195">
+      <c r="A195" t="s">
         <v>1039</v>
       </c>
     </row>
-    <row r="195" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A195" s="1" t="s">
+    <row r="196">
+      <c r="A196" t="s">
         <v>1040</v>
       </c>
     </row>
-    <row r="196" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A196" s="1" t="s">
+    <row r="197">
+      <c r="A197" t="s">
         <v>1041</v>
       </c>
     </row>
-    <row r="197" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A197" s="1" t="s">
+    <row r="198">
+      <c r="A198" t="s">
         <v>1042</v>
       </c>
     </row>
-    <row r="198" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A198" s="1" t="s">
+    <row r="199">
+      <c r="A199" t="s">
         <v>1043</v>
       </c>
     </row>
-    <row r="199" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A199" s="1" t="s">
+    <row r="200">
+      <c r="A200" t="s">
         <v>1044</v>
       </c>
     </row>
-    <row r="200" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A200" s="1" t="s">
+    <row r="201">
+      <c r="A201" t="s">
         <v>1045</v>
       </c>
     </row>
-    <row r="201" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A201" s="1" t="s">
+    <row r="202">
+      <c r="A202" t="s">
         <v>1046</v>
       </c>
     </row>
-    <row r="202" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A202" s="1" t="s">
+    <row r="203">
+      <c r="A203" t="s">
         <v>1047</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -24690,13 +24646,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BC5E9245-EA92-4BD1-9032-ED6EEB7A1FF7}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DC5408FE-841A-4D10-BCCC-62BE7074371F}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{422AE216-1DB8-465B-963B-83D5395D476B}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{89359ED4-5A81-4746-B195-73112D5DB6A1}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{24CE6DAF-C39D-455C-933B-244719431B7F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D38FEB4D-F656-4D9D-B606-970B4003E0CC}"/>
 </file>
--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -4331,7 +4331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
+  <dimension ref="A1:AM266"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="67.1640625" hidden="0" customWidth="1"/>
@@ -17355,7 +17355,11 @@
         <v>839</v>
       </c>
       <c r="B181" s="3"/>
-      <c r="D181" s="3"/>
+      <c r="D181" s="3" t="inlineStr">
+        <is>
+          <t>Tables1to4</t>
+        </is>
+      </c>
       <c r="E181" s="1" t="str">
         <f t="shared" si="40"/>
         <v>9</v>
@@ -17381,11 +17385,11 @@
       </c>
       <c r="K181" s="1" t="str">
         <f t="shared" si="46"/>
-        <v>Matano__1992_</v>
+        <v>Matano__1992_Tables1to4</v>
       </c>
       <c r="L181" s="1" t="str">
         <f t="shared" si="47"/>
-        <v>10.1537%2Fase1911.100.69_</v>
+        <v>10.1537%2Fase1911.100.69_Tables1to4</v>
       </c>
       <c r="M181" s="1" t="str">
         <f t="array" ref="M181">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L181,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -21868,8 +21872,8 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="3" t="s">
-        <v>762</v>
+      <c r="A247" s="4" t="s">
+        <v>747</v>
       </c>
       <c r="C247" s="3"/>
       <c r="D247" s="3" t="s">
@@ -21897,7 +21901,7 @@
       </c>
       <c r="J247" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>10.1159%2F000155964</v>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K247" s="1" t="str">
         <f t="shared" si="101"/>
@@ -21905,7 +21909,7 @@
       </c>
       <c r="L247" s="1" t="str">
         <f t="shared" si="102"/>
-        <v>10.1159%2F000155964_TableVIII</v>
+        <v>10.1159%2F000155963_TableVIII</v>
       </c>
       <c r="M247" s="1" t="str">
         <f t="array" ref="M247">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L247,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -21916,8 +21920,8 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="3" t="s">
-        <v>765</v>
+      <c r="A248" s="4" t="s">
+        <v>747</v>
       </c>
       <c r="C248" s="3"/>
       <c r="D248" s="3" t="s">
@@ -21945,7 +21949,7 @@
       </c>
       <c r="J248" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>10.1159%2F000155965</v>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K248" s="1" t="str">
         <f t="shared" si="101"/>
@@ -21953,7 +21957,7 @@
       </c>
       <c r="L248" s="1" t="str">
         <f t="shared" si="102"/>
-        <v>10.1159%2F000155965_TableIX</v>
+        <v>10.1159%2F000155963_TableIX</v>
       </c>
       <c r="M248" s="1" t="str">
         <f t="array" ref="M248">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L248,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -21964,8 +21968,8 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="3" t="s">
-        <v>768</v>
+      <c r="A249" s="4" t="s">
+        <v>747</v>
       </c>
       <c r="C249" s="3"/>
       <c r="D249" s="3" t="s">
@@ -21993,7 +21997,7 @@
       </c>
       <c r="J249" s="1" t="str">
         <f t="shared" si="100"/>
-        <v>10.1159%2F000155966</v>
+        <v>10.1159%2F000155963</v>
       </c>
       <c r="K249" s="1" t="str">
         <f t="shared" si="101"/>
@@ -22001,7 +22005,7 @@
       </c>
       <c r="L249" s="1" t="str">
         <f t="shared" si="102"/>
-        <v>10.1159%2F000155966_TableX</v>
+        <v>10.1159%2F000155963_TableX</v>
       </c>
       <c r="M249" s="1" t="str">
         <f t="array" ref="M249">IFERROR(INDEX(FileList!$A$1:$A$1000,MATCH(TRUE(),EXACT(L249,IFERROR(_xlfn.TEXTBEFORE(FileList!$A$1:$A$1000,".tsv"),"")),0)),"notfound")</f>
@@ -22919,217 +22923,217 @@
       <c r="AL264" s="3"/>
       <c r="AM264" s="3"/>
     </row>
-    <row r="265">
+    <row r="265" spans="1:39">
       <c r="A265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Heuer, K., Gulban, O. F., Bazin, P. L., Osoianu, A., Valabregue, R., Santin, M., Herbin, M., &amp; Toro, R. (2019). Evolution of neocortical folding: A phylogenetic comparative analysis of MRI from 34 primate species. Cortex, 118, 275-291. https://doi.org/10.1016/j.cortex.2019.04.011</t>
+          <t>Heuer, K., Gulban, O. F., Bazin, P. L., Osoianu, A., Valabregue, R., Santin, M., Herbin, M., &amp; Toro, R. (2019). Evolution of neocortical folding: A phylogenetic comparative analysis of MRI from 34 primate species. Cortex, 118, 275-291. https://doi.org/10.1016/j.cortex.2019.04.011</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;S1</t>
+          <t>S1</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Heuer_etal_2019</t>
+          <t>Heuer_etal_2019</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Heuer</t>
+          <t>Heuer</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;etal</t>
+          <t>etal</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;2019</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="J265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;10.1016%2Fj.cortex.2019.04.011</t>
+          <t>10.1016%2Fj.cortex.2019.04.011</t>
         </is>
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Heuer_etal_2019_S1</t>
+          <t>Heuer_etal_2019_S1</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;10.1016%2Fj.cortex.2019.04.011_S1</t>
+          <t>10.1016%2Fj.cortex.2019.04.011_S1</t>
         </is>
       </c>
       <c r="P265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;FINISHED</t>
+          <t>FINISHED</t>
         </is>
       </c>
       <c r="R265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;none - digital-native (S1_QCtable_mmc1.tsv, unpacked from mmc1.zip)</t>
+          <t>none - digital-native (S1_QCtable_mmc1.tsv, unpacked from mmc1.zip)</t>
         </is>
       </c>
       <c r="T265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Heuer_etal_2019_S1.csv</t>
+          <t>Heuer_etal_2019_S1.csv</t>
         </is>
       </c>
       <c r="U265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;zipped tsv</t>
+          <t>zipped tsv</t>
         </is>
       </c>
       <c r="V265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;table</t>
+          <t>table</t>
         </is>
       </c>
       <c r="Y265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Heuer/Toro</t>
+          <t>Heuer/Toro</t>
         </is>
       </c>
       <c r="AB265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Supplementary QC table. Carries 66 scanned specimens against the 65 analysed - the extra one is a red howler monkey absent from Table 1. The two 'Gorilla' rows are two species (BC = G. beringei, NCBR = G. gorilla) and stay unresolved. Folding metrics are on Zenodo doi:10.5281/zenodo.2538751, not in this repo.</t>
+          <t>Supplementary QC table. Carries 66 scanned specimens against the 65 analysed - the extra one is a red howler monkey absent from Table 1. The two 'Gorilla' rows are two species (BC = G. beringei, NCBR = G. gorilla) and stay unresolved. Folding metrics are on Zenodo doi:10.5281/zenodo.2538751, not in this repo.</t>
         </is>
       </c>
       <c r="AI265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;MRI scan quality and provenance (66 specimens) - no folding value</t>
+          <t>MRI scan quality and provenance (66 specimens) - no folding value</t>
         </is>
       </c>
       <c r="AJ265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Primates</t>
+          <t>Primates</t>
         </is>
       </c>
       <c r="AK265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;secondary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="AL265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;secondary</t>
+          <t>secondary</t>
         </is>
       </c>
       <c r="AM265" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;metadata (MRI scan QC)</t>
+          <t>metadata (MRI scan QC)</t>
         </is>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:39">
       <c r="A266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Jacobs, B., Garcia, M. E., Shea-Shumsky, N. B., Tennison, M. E., Schall, M., Saviano, M. S., Tummino, T. A., Bull, A. J., Driscoll, L. L., Raghanti, M. A., Lewandowski, A. H., Wicinski, B., Ki Chui, H., Bertelsen, M. F., Walsh, T., Bhagwandin, A., Spocter, M. A., Hof, P. R., Sherwood, C. C., &amp; Manger, P. R. (2018). Comparative morphology of gigantopyramidal neurons in primary motor cortex across mammals. J Comp Neurol, 526(3), 496-536. https://doi.org/10.1002/cne.24349</t>
+          <t>Jacobs, B., Garcia, M. E., Shea-Shumsky, N. B., Tennison, M. E., Schall, M., Saviano, M. S., Tummino, T. A., Bull, A. J., Driscoll, L. L., Raghanti, M. A., Lewandowski, A. H., Wicinski, B., Ki Chui, H., Bertelsen, M. F., Walsh, T., Bhagwandin, A., Spocter, M. A., Hof, P. R., Sherwood, C. C., &amp; Manger, P. R. (2018). Comparative morphology of gigantopyramidal neurons in primary motor cortex across mammals. J Comp Neurol, 526(3), 496-536. https://doi.org/10.1002/cne.24349</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Table 5</t>
+          <t>Table 5</t>
         </is>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Jacobs_etal_2018</t>
+          <t>Jacobs_etal_2018</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Jacobs</t>
+          <t>Jacobs</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;etal</t>
+          <t>etal</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;2018</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="J266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;10.1002%2Fcne.24349</t>
+          <t>10.1002%2Fcne.24349</t>
         </is>
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Jacobs_etal_2018_Table5</t>
+          <t>Jacobs_etal_2018_Table5</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;10.1002%2Fcne.24349_Table5</t>
+          <t>10.1002%2Fcne.24349_Table5</t>
         </is>
       </c>
       <c r="P266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;FINISHED</t>
+          <t>FINISHED</t>
         </is>
       </c>
       <c r="R266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Jacobs_etal_2018_Table5_snapshot.xlsx</t>
+          <t>Jacobs_etal_2018_Table5_snapshot.xlsx</t>
         </is>
       </c>
       <c r="T266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Jacobs_etal_2018_Table5.csv</t>
+          <t>Jacobs_etal_2018_Table5.csv</t>
         </is>
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;pdf</t>
+          <t>pdf</t>
         </is>
       </c>
       <c r="V266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;table</t>
+          <t>table</t>
         </is>
       </c>
       <c r="Y266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Jacobs/Manger</t>
+          <t>Jacobs/Manger</t>
         </is>
       </c>
       <c r="AB266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;617 traced neurons, 19 species. Regional M1 sub-trait - never pool with whole-cortex counts. neuron_type must stay explicit. Golgi tracing is NOT interchangeable with the stereology in Table 3. gigantopyramidal_absent is a real biological zero in mongoose, rabbit, rat and wallaby.</t>
+          <t>617 traced neurons, 19 species. Regional M1 sub-trait - never pool with whole-cortex counts. neuron_type must stay explicit. Golgi tracing is NOT interchangeable with the stereology in Table 3. gigantopyramidal_absent is a real biological zero in mongoose, rabbit, rat and wallaby.</t>
         </is>
       </c>
       <c r="AI266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;somatodendritic morphology of three M1 neuron types (superficial, deep, gigantopyramidal)</t>
+          <t>somatodendritic morphology of three M1 neuron types (superficial, deep, gigantopyramidal)</t>
         </is>
       </c>
       <c r="AJ266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;Mammals (7 orders)</t>
+          <t>Mammals (7 orders)</t>
         </is>
       </c>
       <c r="AK266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;primary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="AL266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;primary</t>
+          <t>primary</t>
         </is>
       </c>
       <c r="AM266" t="inlineStr">
         <is>
-          <t>xml:space="preserve"&gt;cell morphology (Golgi 2-D tracing, M1 regional)</t>
+          <t>cell morphology (Golgi 2-D tracing, M1 regional)</t>
         </is>
       </c>
     </row>

--- a/__ReadMe.xlsx
+++ b/__ReadMe.xlsx
@@ -1,40 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://alleninstitute.sharepoint.com/sites/MammalianM1/Shared Documents/General/Species/Evo-M1-Trait-Data/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="132" documentId="11_C9899FD343DE0E1AAF8ABA0755916B8CA43B56A8" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1DC69BEE-ECF6-7341-9E7D-55FD4B558599}"/>
   <bookViews>
-    <workbookView xWindow="40140" yWindow="-5860" windowWidth="36160" windowHeight="28200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="40140" yWindow="-5860" windowWidth="36160" windowHeight="28200" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="FileList" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FileList" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3192" uniqueCount="1324">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1569" uniqueCount="1569">
   <si>
     <t>Citation (APA 7th-Annotated)</t>
   </si>
@@ -4007,13 +3987,749 @@
   </si>
   <si>
     <t>Schleifenbaum, C. (1973). Untersuchungen zur postnatalen Ontogenese des Gehirns von Großpudeln und Wölfen. Z Anat Entwicklungsgesch, 141(2), 179-205. https://doi.org/10.1007/BF00519885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2F(SICI)1096-8644(199806)106%3A2%3C129%3A%3AAID-AJPA3%3E3.0.CO;2-L_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2F1096-8644(200102)114%3A2%3C163%3A%3AAID-AJPA1016%3E3.0.CO;2-F_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2F1096-8644(200103)114%3A3%3C224%3A%3AAID-AJPA1022%3E3.0.CO;2-I_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fajp.20048_TABLEI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fajp.20048_unpublishedviaDeCasien.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fajpa.20684_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fajpa.22646_Fig4A.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fajpa.22646_Fig5A.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fajpa.22646_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fajpa.22646_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fajpa.22646_unpublishedviaDeCasien.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Far.a.20114_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.23118_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24349_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24349_Table5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24605_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24605_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24985_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.24985_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.25669_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.70089_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.903580203_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.903580203_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.903580203_TABLE3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.903580203_TABLE4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1002%2Fcne.903580203_TABLE5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1006%2Fjhev.1996.0005_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1006%2Fjhev.1999.0313_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1006%2Fjhev.1999.0381_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007%2Fs004220000205_Figure3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1007%2Fs10329-026-01271-2_data.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.cortex.2019.04.011_S1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.cortex.2019.04.011_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.cub.2004.12.064_Fig2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.cub.2017.01.020_TableS1part1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.cub.2017.01.020_TableS1part2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2004.10.003_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_Table7.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2008.08.004_TableS3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2009.11.011_SupTable2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2009.11.011_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2012.03.007_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2012.03.007_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2012.03.007_Table5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2012.12.003_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2012.12.003_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2012.12.003_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2017.09.003_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.jhevol.2018.10.002_SOMTableS6.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.neubiorev.2008.05.023_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.neubiorev.2008.05.023_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.tins.2013.01.006_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.tree.2018.03.001_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fj.zool.2020.125753_SupplementaryTable.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fs0047-2484(03)00028-9_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fs0047-2484(03)00028-9_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fs0166-4328(98)00151-x_References.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1016%2Fs0166-4328(98)00151-x_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1017%2Fs0952523800000213_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037%2F0735-7036.115.1.29_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037%2F0735-7036.115.1.29_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037%2F0735-7036.115.1.29_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1037%2F0735-7036.115.1.29_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fnn814_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41467-020-14356-3_SupplementaryData3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-24331-0_ExtendedDataFigure4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-24331-0_ExtendedDataTable1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-24331-0_ExtendedDataTable3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-24331-0_Figure3A.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-24331-0_Figure3B.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-24331-0_Figure3legend.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-24331-0_FossilSpecimensText.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs41598-018-26062-8_TableS5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fs42003-025-08686-5_SupplementaryData1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1038%2Fsrep24528_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1073%2Fpnas.0305760101_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1073%2Fpnas.0905777106_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1073%2Fpnas.1010356107_DatasetS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1073%2Fpnas.1318894110_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1073%2Fpnas.1524208113_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1073%2Fpnas.1610178113_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1073%2Fpnas.1716956116_SupplementaryTableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1080%2F09524622.2021.1905065_Figure1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fcercor%2Fbhy315_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fjmammal%2Fgyz043_SupplementaryDataSD1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Foso%2F9780198568742.003.0006_Table6.1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fscan%2Fnsv128_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1093%2Fscan%2Fnsv128_TableS2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frsos.170846_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frspb.2015.1853_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frspb.2015.1853_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frspb.2016.1923_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frspb.2019.2208_rspb20192208si002.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frspb.2021.0937_MammalGait.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1098%2Frstb.2010.0342_Data.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111%2Fbrv.12137_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111%2Fbrv.12350_TableS2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111%2Fj.1558-5646.2008.00392.x_sleep-dataFemale.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111%2Fj.1558-5646.2008.00392.x_sleep-dataMale.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111%2Fj.1558-5646.2008.00392.x_sleep-dataMixed.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111%2Fjoa.13681_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1111%2Fjzo.12608_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1126%2Fscience.aaa9101_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000006575_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000068880_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000075672_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000075672_Table5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000085942_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000085942_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000085942_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000085942_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000085942_Table5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000121494_TableI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000124401_TableI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableII.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableIII.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableIV.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableIX.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TablesI-VI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableV.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableVI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableVII.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableVIII.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableX.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableXI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableXII.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableXIII.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableXIV.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableXV.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000155963_TableXVI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000156211_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000156212_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000156277_TableI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000319019_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000319019_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000323671_SupplementaryTable1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000323671_SupplementaryTable2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000346495_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000437413_Table5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000446762_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1159%2F000452856_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS10.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS11.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS12.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS13.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS14.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS15.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS16.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS17.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS18.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS19.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS20.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS21.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS22.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS23.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS6.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS7.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS8.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1186%2F1741-7007-5-18_TableS9.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1242%2Fjeb.124826_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1242%2Fjeb.204651_celldensity.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1242%2Fjeb.204651_cellnumber.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1242%2Fjeb.204651_volumes.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pbio.1002000_TableS1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pbio.1002000_TableS8.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1371%2Fjournal.pone.0009123_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523%2FJNEUROSCI.1750-23.2024_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523%2FJNEUROSCI.2339-19.2020_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1523%2FJNEUROSCI.2339-19.2020_unpublished.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1537%2Fase1911.100.69_Tables1to4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1890%2F13-1917.1_MamFuncDat.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.26451%2Fabc.09.04.06.2022_speciespredictors.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00028_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Figure2TopLeft.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Table1-a.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2013.00035_Table1-b.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2014.00128_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2015.00039_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnana.2017.00118_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffncir.2013.00030_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnhum.2013.00424_TableS2partial.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnhum.2014.00277_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3389%2Ffnins.2021.632853_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6084%2Fm9.figshare.c.3899422.v1_Dataset1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554%2FeLife.35696_Figure2-data1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554%2FeLife.77875_Supplementaryfile3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7554%2FeLife.77875_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A0390672505_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A0390672505_TABLE2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A0390672505_TABLE3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A0390672505_TABLE4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A0390672505_TABLE5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A0390672505_TABLE6.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A0390672505_Tables1-6.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A0845140000_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ISBN%3A9780195043716_Table12-2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NQ%3A61662_APPENDIXI.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OCLC%3A8777719_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A15534048_TABLE1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A2358663_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A3116076_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A3216099_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A3693895_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A6481154_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A6501869_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A6663055_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A7161477_Table2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A7161483_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A7983368_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A9176733_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PMID%3A9672110_Table1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3017523_NotesforTableA-15.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3017523_TableA-11.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3017523_TableA-15.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA1.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA10.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA11.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA12.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA13.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA14.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA15.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA2.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA3.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA4.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA5.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA6.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA7.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA8.tsv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UMI%3A3147447_TableA9.tsv</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <numFmts count="0"/>
+  <fonts count="4">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -4028,11 +4744,11 @@
       <family val="2"/>
     </font>
     <font>
-      <b/>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b/>
     </font>
     <font>
       <sz val="12"/>
@@ -4075,7 +4791,6 @@
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -4084,9 +4799,6 @@
       <right style="thin">
         <color rgb="FF7F7F7F"/>
       </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -4370,25 +5082,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM334"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
-    <col min="1" max="1" width="67.1640625" customWidth="1"/>
-    <col min="2" max="2" width="1.6640625" customWidth="1"/>
-    <col min="3" max="3" width="29.1640625" customWidth="1"/>
-    <col min="4" max="4" width="8.5" customWidth="1"/>
-    <col min="5" max="5" width="1.5" customWidth="1"/>
-    <col min="6" max="10" width="7" customWidth="1"/>
-    <col min="11" max="13" width="19" customWidth="1"/>
-    <col min="14" max="17" width="7.33203125" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" customWidth="1"/>
-    <col min="19" max="26" width="7.33203125" customWidth="1"/>
-    <col min="28" max="39" width="7.33203125" customWidth="1"/>
-    <col min="40" max="40" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="67.1640625" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="1.6640625" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="29.1640625" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="8.5" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="1.5" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="7" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="7" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="7" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="7" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="7" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="19" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="19" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="19" hidden="0" customWidth="1"/>
+    <col min="14" max="14" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="16" max="16" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="17" max="17" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" hidden="0" customWidth="1"/>
+    <col min="19" max="19" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="20" max="20" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="21" max="21" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="22" max="22" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="23" max="23" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="24" max="24" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="25" max="25" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="26" max="26" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="28" max="28" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="29" max="29" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="30" max="30" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="31" max="31" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="32" max="32" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="33" max="33" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="34" max="34" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="35" max="35" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="36" max="36" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="37" max="37" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="38" max="38" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="39" max="39" width="7.33203125" hidden="0" customWidth="1"/>
+    <col min="40" max="40" width="10.83203125" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -4507,7 +5246,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="3" t="s">
         <v>38</v>
       </c>
@@ -4582,7 +5321,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="3" t="s">
         <v>43</v>
       </c>
@@ -4608,7 +5347,6 @@
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
-        <v/>
       </c>
       <c r="I3" s="1" t="str">
         <f t="shared" ref="I3:I67" si="12">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A3, "("), ")")</f>
@@ -4651,7 +5389,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>47</v>
       </c>
@@ -4749,7 +5487,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" ht="15.75" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>64</v>
       </c>
@@ -4811,7 +5549,7 @@
       <c r="AL5" s="3"/>
       <c r="AM5" s="3"/>
     </row>
-    <row r="6" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" ht="15.75" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>66</v>
       </c>
@@ -4858,7 +5596,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="7" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" ht="15.75" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>66</v>
       </c>
@@ -4905,7 +5643,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>66</v>
       </c>
@@ -4952,7 +5690,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="9" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>71</v>
       </c>
@@ -5008,7 +5746,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>71</v>
       </c>
@@ -5064,7 +5802,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="11" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>71</v>
       </c>
@@ -5120,7 +5858,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>75</v>
       </c>
@@ -5176,7 +5914,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="3" t="s">
         <v>80</v>
       </c>
@@ -5247,7 +5985,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="3" t="s">
         <v>826</v>
       </c>
@@ -5312,7 +6050,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="15" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="3" t="s">
         <v>85</v>
       </c>
@@ -5365,7 +6103,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="16" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="3" t="s">
         <v>85</v>
       </c>
@@ -5415,7 +6153,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="17" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="3" t="s">
         <v>85</v>
       </c>
@@ -5468,7 +6206,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="3" t="s">
         <v>85</v>
       </c>
@@ -5518,7 +6256,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="19" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="3" t="s">
         <v>85</v>
       </c>
@@ -5565,7 +6303,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" ht="16.5" customHeight="1">
       <c r="A20" s="3" t="s">
         <v>96</v>
       </c>
@@ -5642,7 +6380,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="21" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" ht="16.5" customHeight="1">
       <c r="A21" s="3" t="s">
         <v>102</v>
       </c>
@@ -5725,7 +6463,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
         <v>106</v>
       </c>
@@ -5808,7 +6546,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="23" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
         <v>109</v>
       </c>
@@ -5894,7 +6632,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
         <v>838</v>
       </c>
@@ -5950,7 +6688,7 @@
       <c r="AL24" s="3"/>
       <c r="AM24" s="3"/>
     </row>
-    <row r="25" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
         <v>113</v>
       </c>
@@ -6027,7 +6765,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="26" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
         <v>113</v>
       </c>
@@ -6101,7 +6839,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="27" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
         <v>113</v>
       </c>
@@ -6172,7 +6910,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="28" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
         <v>119</v>
       </c>
@@ -6219,7 +6957,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="29" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>121</v>
       </c>
@@ -6263,7 +7001,7 @@
         <v>10.1016%2Fj.jhevol.2018.10.002_SOMTableS6.tsv</v>
       </c>
     </row>
-    <row r="30" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>830</v>
       </c>
@@ -6287,7 +7025,6 @@
       </c>
       <c r="H30" s="1" t="str">
         <f t="shared" si="11"/>
-        <v/>
       </c>
       <c r="I30" s="1" t="str">
         <f t="shared" si="12"/>
@@ -6331,7 +7068,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="31" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>123</v>
       </c>
@@ -6355,7 +7092,6 @@
       </c>
       <c r="H31" s="1" t="str">
         <f t="shared" si="11"/>
-        <v/>
       </c>
       <c r="I31" s="1" t="str">
         <f t="shared" si="12"/>
@@ -6390,7 +7126,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="32" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>128</v>
       </c>
@@ -6483,7 +7219,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="33" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
         <v>142</v>
       </c>
@@ -6563,7 +7299,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="34" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
         <v>142</v>
       </c>
@@ -6661,7 +7397,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
         <v>157</v>
       </c>
@@ -6717,7 +7453,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="36" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
         <v>162</v>
       </c>
@@ -6806,7 +7542,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="3" t="s">
         <v>170</v>
       </c>
@@ -6895,7 +7631,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="38" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="4" t="s">
         <v>845</v>
       </c>
@@ -6978,7 +7714,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="39" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="4" t="s">
         <v>845</v>
       </c>
@@ -7061,7 +7797,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="40" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="4" t="s">
         <v>845</v>
       </c>
@@ -7144,7 +7880,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="41" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="3" t="s">
         <v>178</v>
       </c>
@@ -7237,7 +7973,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="42" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
         <v>178</v>
       </c>
@@ -7332,7 +8068,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="43" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="3" t="s">
         <v>196</v>
       </c>
@@ -7376,7 +8112,7 @@
         <v>10.1016%2Fj.tree.2018.03.001_TableS1.tsv</v>
       </c>
     </row>
-    <row r="44" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
         <v>198</v>
       </c>
@@ -7397,7 +8133,6 @@
       </c>
       <c r="H44" s="1" t="str">
         <f t="shared" si="11"/>
-        <v/>
       </c>
       <c r="I44" s="1" t="str">
         <f t="shared" si="12"/>
@@ -7462,7 +8197,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="45" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="3" t="s">
         <v>876</v>
       </c>
@@ -7545,7 +8280,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="46" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="3" t="s">
         <v>876</v>
       </c>
@@ -7628,7 +8363,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="47" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="3" t="s">
         <v>876</v>
       </c>
@@ -7711,7 +8446,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="48" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="3" t="s">
         <v>876</v>
       </c>
@@ -7794,7 +8529,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="49" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="3" t="s">
         <v>876</v>
       </c>
@@ -7877,7 +8612,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="50" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="3" t="s">
         <v>210</v>
       </c>
@@ -7973,7 +8708,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="51" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="3" t="s">
         <v>220</v>
       </c>
@@ -8035,7 +8770,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="52" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="3" t="s">
         <v>224</v>
       </c>
@@ -8109,7 +8844,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="53" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="4" t="s">
         <v>846</v>
       </c>
@@ -8153,7 +8888,7 @@
         <v>10.1111%2Fjoa.13681_Table1.tsv</v>
       </c>
     </row>
-    <row r="54" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="3" t="s">
         <v>228</v>
       </c>
@@ -8248,7 +8983,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="55" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="55" ht="15" customHeight="1">
       <c r="A55" s="3" t="s">
         <v>237</v>
       </c>
@@ -8355,7 +9090,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="56" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="3" t="s">
         <v>237</v>
       </c>
@@ -8432,7 +9167,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="57" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="3" t="s">
         <v>254</v>
       </c>
@@ -8512,7 +9247,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="58" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="3" t="s">
         <v>254</v>
       </c>
@@ -8595,7 +9330,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="59" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="3" t="s">
         <v>254</v>
       </c>
@@ -8675,7 +9410,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="60" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="3" t="s">
         <v>254</v>
       </c>
@@ -8755,7 +9490,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="61" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="3" t="s">
         <v>270</v>
       </c>
@@ -8856,7 +9591,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="62" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="3" t="s">
         <v>270</v>
       </c>
@@ -8957,7 +9692,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="63" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="3" t="s">
         <v>285</v>
       </c>
@@ -9061,7 +9796,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="64" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="3" t="s">
         <v>295</v>
       </c>
@@ -9126,7 +9861,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="65" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="3" t="s">
         <v>1322</v>
       </c>
@@ -9150,7 +9885,6 @@
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
-        <v/>
       </c>
       <c r="I65" s="1" t="str">
         <f t="shared" ref="I65" si="20">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A65, "("), ")")</f>
@@ -9191,7 +9925,7 @@
       <c r="AL65" s="3"/>
       <c r="AM65" s="3"/>
     </row>
-    <row r="66" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="3" t="s">
         <v>299</v>
       </c>
@@ -9256,7 +9990,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="67" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="3" t="s">
         <v>299</v>
       </c>
@@ -9321,7 +10055,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="68" spans="1:39" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="3" t="s">
         <v>305</v>
       </c>
@@ -9429,7 +10163,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="69" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="69" ht="16.5" customHeight="1">
       <c r="A69" s="3" t="s">
         <v>312</v>
       </c>
@@ -9512,7 +10246,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="70" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="70" ht="16.5" customHeight="1">
       <c r="A70" s="3" t="s">
         <v>312</v>
       </c>
@@ -9559,7 +10293,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="71" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="71" ht="16.5" customHeight="1">
       <c r="A71" s="3" t="s">
         <v>316</v>
       </c>
@@ -9642,7 +10376,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="72" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="72" ht="16.5" customHeight="1">
       <c r="A72" s="3" t="s">
         <v>320</v>
       </c>
@@ -9725,7 +10459,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="73" spans="1:39" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="73" ht="16.5" customHeight="1">
       <c r="A73" s="3" t="s">
         <v>324</v>
       </c>
@@ -9808,7 +10542,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="74" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="3" t="s">
         <v>328</v>
       </c>
@@ -9891,7 +10625,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="75" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="4" t="s">
         <v>847</v>
       </c>
@@ -9935,7 +10669,7 @@
         <v>10.1016%2Fj.cub.2004.12.064_Fig2.tsv</v>
       </c>
     </row>
-    <row r="76" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="3" t="s">
         <v>332</v>
       </c>
@@ -10000,7 +10734,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="77" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="3" t="s">
         <v>839</v>
       </c>
@@ -10080,7 +10814,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="78" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="3" t="s">
         <v>336</v>
       </c>
@@ -10145,7 +10879,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="79" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="3" t="s">
         <v>336</v>
       </c>
@@ -10210,7 +10944,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="80" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="3" t="s">
         <v>342</v>
       </c>
@@ -10272,7 +11006,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="81" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="3" t="s">
         <v>345</v>
       </c>
@@ -10293,7 +11027,6 @@
       </c>
       <c r="H81" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I81" s="1" t="str">
         <f t="shared" si="28"/>
@@ -10334,7 +11067,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="82" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="3" t="s">
         <v>349</v>
       </c>
@@ -10393,7 +11126,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="3" t="s">
         <v>351</v>
       </c>
@@ -10477,7 +11210,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="84" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="3" t="s">
         <v>356</v>
       </c>
@@ -10569,7 +11302,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="85" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="3" t="s">
         <v>363</v>
       </c>
@@ -10634,7 +11367,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="86" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="3" t="s">
         <v>369</v>
       </c>
@@ -10712,7 +11445,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="87" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="3" t="s">
         <v>372</v>
       </c>
@@ -10733,7 +11466,6 @@
       </c>
       <c r="H87" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I87" s="1" t="str">
         <f t="shared" si="28"/>
@@ -10774,7 +11506,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="88" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="3" t="s">
         <v>372</v>
       </c>
@@ -10795,7 +11527,6 @@
       </c>
       <c r="H88" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I88" s="1" t="str">
         <f t="shared" si="28"/>
@@ -10842,7 +11573,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="89" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="3" t="s">
         <v>378</v>
       </c>
@@ -10943,7 +11674,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="90" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="3" t="s">
         <v>378</v>
       </c>
@@ -11041,7 +11772,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="91" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="3" t="s">
         <v>378</v>
       </c>
@@ -11139,7 +11870,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="92" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="3" t="s">
         <v>378</v>
       </c>
@@ -11237,7 +11968,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="93" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="3" t="s">
         <v>378</v>
       </c>
@@ -11335,7 +12066,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="94" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="3" t="s">
         <v>396</v>
       </c>
@@ -11436,7 +12167,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="95" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="3" t="s">
         <v>396</v>
       </c>
@@ -11537,7 +12268,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="96" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="3" t="s">
         <v>409</v>
       </c>
@@ -11605,7 +12336,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="97" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="3" t="s">
         <v>409</v>
       </c>
@@ -11676,7 +12407,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="98" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="3" t="s">
         <v>409</v>
       </c>
@@ -11747,7 +12478,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="99" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="3" t="s">
         <v>863</v>
       </c>
@@ -11830,7 +12561,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="100" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="4" t="s">
         <v>863</v>
       </c>
@@ -11910,7 +12641,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="101" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="3" t="s">
         <v>414</v>
       </c>
@@ -11972,7 +12703,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="102" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="3" t="s">
         <v>414</v>
       </c>
@@ -12034,7 +12765,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="103" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="3" t="s">
         <v>414</v>
       </c>
@@ -12096,7 +12827,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="104" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="3" t="s">
         <v>414</v>
       </c>
@@ -12158,7 +12889,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="105" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="3" t="s">
         <v>414</v>
       </c>
@@ -12220,7 +12951,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="106" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="3" t="s">
         <v>414</v>
       </c>
@@ -12282,7 +13013,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="107" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="3" t="s">
         <v>423</v>
       </c>
@@ -12360,7 +13091,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="108" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="3" t="s">
         <v>423</v>
       </c>
@@ -12438,7 +13169,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="109" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="3" t="s">
         <v>423</v>
       </c>
@@ -12516,7 +13247,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="110" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="3" t="s">
         <v>423</v>
       </c>
@@ -12594,7 +13325,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="111" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="3" t="s">
         <v>432</v>
       </c>
@@ -12662,7 +13393,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="112" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="3" t="s">
         <v>432</v>
       </c>
@@ -12730,7 +13461,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="113" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="4" t="s">
         <v>855</v>
       </c>
@@ -12810,7 +13541,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="114" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="4" t="s">
         <v>855</v>
       </c>
@@ -12890,7 +13621,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="115" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="4" t="s">
         <v>850</v>
       </c>
@@ -12937,7 +13668,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="116" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="116" ht="15.75" customHeight="1">
       <c r="A116" s="4" t="s">
         <v>850</v>
       </c>
@@ -12984,7 +13715,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="117" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="117" ht="15.75" customHeight="1">
       <c r="A117" s="4" t="s">
         <v>850</v>
       </c>
@@ -13031,7 +13762,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="118" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="118" ht="15.75" customHeight="1">
       <c r="A118" s="3" t="s">
         <v>438</v>
       </c>
@@ -13132,7 +13863,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="119" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="119" ht="15.75" customHeight="1">
       <c r="A119" s="3" t="s">
         <v>445</v>
       </c>
@@ -13194,7 +13925,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="120" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="120" ht="15.75" customHeight="1">
       <c r="A120" s="3" t="s">
         <v>450</v>
       </c>
@@ -13215,7 +13946,6 @@
       </c>
       <c r="H120" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I120" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13262,7 +13992,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="121" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="121" ht="15.75" customHeight="1">
       <c r="A121" s="3" t="s">
         <v>450</v>
       </c>
@@ -13283,7 +14013,6 @@
       </c>
       <c r="H121" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I121" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13330,7 +14059,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="122" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="122" ht="15.75" customHeight="1">
       <c r="A122" s="3" t="s">
         <v>450</v>
       </c>
@@ -13351,7 +14080,6 @@
       </c>
       <c r="H122" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I122" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13398,7 +14126,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="123" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="123" ht="15.75" customHeight="1">
       <c r="A123" s="3" t="s">
         <v>450</v>
       </c>
@@ -13419,7 +14147,6 @@
       </c>
       <c r="H123" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I123" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13466,7 +14193,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="124" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="124" ht="15.75" customHeight="1">
       <c r="A124" s="3" t="s">
         <v>450</v>
       </c>
@@ -13487,7 +14214,6 @@
       </c>
       <c r="H124" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I124" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13534,7 +14260,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="125" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="125" ht="15.75" customHeight="1">
       <c r="A125" s="3" t="s">
         <v>450</v>
       </c>
@@ -13555,7 +14281,6 @@
       </c>
       <c r="H125" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I125" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13602,7 +14327,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="126" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="126" ht="15.75" customHeight="1">
       <c r="A126" s="3" t="s">
         <v>450</v>
       </c>
@@ -13623,7 +14348,6 @@
       </c>
       <c r="H126" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I126" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13670,7 +14394,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="127" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="127" ht="15.75" customHeight="1">
       <c r="A127" s="3" t="s">
         <v>450</v>
       </c>
@@ -13691,7 +14415,6 @@
       </c>
       <c r="H127" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I127" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13738,7 +14461,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="128" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="128" ht="15.75" customHeight="1">
       <c r="A128" s="3" t="s">
         <v>450</v>
       </c>
@@ -13759,7 +14482,6 @@
       </c>
       <c r="H128" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I128" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13806,7 +14528,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="129" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="129" ht="15.75" customHeight="1">
       <c r="A129" s="3" t="s">
         <v>450</v>
       </c>
@@ -13827,7 +14549,6 @@
       </c>
       <c r="H129" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I129" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13874,7 +14595,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="130" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="130" ht="15.75" customHeight="1">
       <c r="A130" s="3" t="s">
         <v>450</v>
       </c>
@@ -13895,7 +14616,6 @@
       </c>
       <c r="H130" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I130" s="1" t="str">
         <f t="shared" si="28"/>
@@ -13942,7 +14662,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="131" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="131" ht="15.75" customHeight="1">
       <c r="A131" s="3" t="s">
         <v>450</v>
       </c>
@@ -13963,7 +14683,6 @@
       </c>
       <c r="H131" s="1" t="str">
         <f t="shared" si="27"/>
-        <v/>
       </c>
       <c r="I131" s="1" t="str">
         <f t="shared" si="28"/>
@@ -14010,7 +14729,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="132" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="132" ht="15.75" customHeight="1">
       <c r="A132" s="3" t="s">
         <v>450</v>
       </c>
@@ -14036,7 +14755,6 @@
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
-        <v/>
       </c>
       <c r="I132" s="1" t="str">
         <f t="shared" ref="I132:I195" si="36">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A132, "("), ")")</f>
@@ -14094,7 +14812,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="133" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="133" ht="15.75" customHeight="1">
       <c r="A133" s="3" t="s">
         <v>450</v>
       </c>
@@ -14115,7 +14833,6 @@
       </c>
       <c r="H133" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I133" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14162,7 +14879,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="134" spans="1:39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="134" ht="15.75" customHeight="1">
       <c r="A134" s="3" t="s">
         <v>450</v>
       </c>
@@ -14183,7 +14900,6 @@
       </c>
       <c r="H134" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I134" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14230,7 +14946,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="135" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="135" ht="15" customHeight="1">
       <c r="A135" s="3" t="s">
         <v>450</v>
       </c>
@@ -14251,7 +14967,6 @@
       </c>
       <c r="H135" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I135" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14298,7 +15013,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="136" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="136" ht="15" customHeight="1">
       <c r="A136" s="3" t="s">
         <v>450</v>
       </c>
@@ -14319,7 +15034,6 @@
       </c>
       <c r="H136" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I136" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14366,7 +15080,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="137" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="137" ht="15" customHeight="1">
       <c r="A137" s="3" t="s">
         <v>450</v>
       </c>
@@ -14387,7 +15101,6 @@
       </c>
       <c r="H137" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I137" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14434,7 +15147,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="138" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="138" ht="15" customHeight="1">
       <c r="A138" s="3" t="s">
         <v>450</v>
       </c>
@@ -14455,7 +15168,6 @@
       </c>
       <c r="H138" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I138" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14502,7 +15214,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="139" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="139" ht="15" customHeight="1">
       <c r="A139" s="3" t="s">
         <v>450</v>
       </c>
@@ -14523,7 +15235,6 @@
       </c>
       <c r="H139" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I139" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14570,7 +15281,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="140" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="140" ht="15" customHeight="1">
       <c r="A140" s="3" t="s">
         <v>450</v>
       </c>
@@ -14591,7 +15302,6 @@
       </c>
       <c r="H140" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I140" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14638,7 +15348,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="141" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="141" ht="15" customHeight="1">
       <c r="A141" s="3" t="s">
         <v>450</v>
       </c>
@@ -14659,7 +15369,6 @@
       </c>
       <c r="H141" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I141" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14706,7 +15415,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="142" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="142" ht="15" customHeight="1">
       <c r="A142" s="3" t="s">
         <v>450</v>
       </c>
@@ -14727,7 +15436,6 @@
       </c>
       <c r="H142" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I142" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14774,7 +15482,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="143" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="143" ht="15" customHeight="1">
       <c r="A143" s="3" t="s">
         <v>450</v>
       </c>
@@ -14795,7 +15503,6 @@
       </c>
       <c r="H143" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I143" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14842,7 +15549,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="144" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="144" ht="15" customHeight="1">
       <c r="A144" s="3" t="s">
         <v>502</v>
       </c>
@@ -14916,7 +15623,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="145" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" ht="15" customHeight="1">
       <c r="A145" s="3" t="s">
         <v>505</v>
       </c>
@@ -14940,7 +15647,6 @@
       </c>
       <c r="H145" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I145" s="1" t="str">
         <f t="shared" si="36"/>
@@ -14996,7 +15702,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="146" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="146" ht="15" customHeight="1">
       <c r="A146" s="3" t="s">
         <v>505</v>
       </c>
@@ -15020,7 +15726,6 @@
       </c>
       <c r="H146" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I146" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15076,7 +15781,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="147" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="147" ht="15" customHeight="1">
       <c r="A147" s="3" t="s">
         <v>505</v>
       </c>
@@ -15100,7 +15805,6 @@
       </c>
       <c r="H147" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I147" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15156,7 +15860,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="148" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="148" ht="15" customHeight="1">
       <c r="A148" s="3" t="s">
         <v>505</v>
       </c>
@@ -15180,7 +15884,6 @@
       </c>
       <c r="H148" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I148" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15236,7 +15939,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="149" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="149" ht="15" customHeight="1">
       <c r="A149" s="3" t="s">
         <v>505</v>
       </c>
@@ -15260,7 +15963,6 @@
       </c>
       <c r="H149" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I149" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15316,7 +16018,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="150" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="150" ht="15" customHeight="1">
       <c r="A150" s="3" t="s">
         <v>505</v>
       </c>
@@ -15340,7 +16042,6 @@
       </c>
       <c r="H150" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I150" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15396,7 +16097,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="151" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="151" ht="15" customHeight="1">
       <c r="A151" s="3" t="s">
         <v>505</v>
       </c>
@@ -15420,7 +16121,6 @@
       </c>
       <c r="H151" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I151" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15476,7 +16176,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="152" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="152" ht="15" customHeight="1">
       <c r="A152" s="3" t="s">
         <v>505</v>
       </c>
@@ -15500,7 +16200,6 @@
       </c>
       <c r="H152" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I152" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15556,7 +16255,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="153" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="153" ht="15" customHeight="1">
       <c r="A153" s="3" t="s">
         <v>505</v>
       </c>
@@ -15580,7 +16279,6 @@
       </c>
       <c r="H153" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I153" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15636,7 +16334,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="154" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="154" ht="15" customHeight="1">
       <c r="A154" s="3" t="s">
         <v>505</v>
       </c>
@@ -15660,7 +16358,6 @@
       </c>
       <c r="H154" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I154" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15716,7 +16413,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="155" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="155" ht="15" customHeight="1">
       <c r="A155" s="3" t="s">
         <v>505</v>
       </c>
@@ -15740,7 +16437,6 @@
       </c>
       <c r="H155" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I155" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15796,7 +16492,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="156" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="156" ht="15" customHeight="1">
       <c r="A156" s="3" t="s">
         <v>505</v>
       </c>
@@ -15820,7 +16516,6 @@
       </c>
       <c r="H156" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I156" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15876,7 +16571,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="157" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="157" ht="15" customHeight="1">
       <c r="A157" s="3" t="s">
         <v>505</v>
       </c>
@@ -15900,7 +16595,6 @@
       </c>
       <c r="H157" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I157" s="1" t="str">
         <f t="shared" si="36"/>
@@ -15956,7 +16650,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="158" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="158" ht="15" customHeight="1">
       <c r="A158" s="3" t="s">
         <v>505</v>
       </c>
@@ -15980,7 +16674,6 @@
       </c>
       <c r="H158" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I158" s="1" t="str">
         <f t="shared" si="36"/>
@@ -16036,7 +16729,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="159" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="159" ht="15" customHeight="1">
       <c r="A159" s="3" t="s">
         <v>505</v>
       </c>
@@ -16060,7 +16753,6 @@
       </c>
       <c r="H159" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I159" s="1" t="str">
         <f t="shared" si="36"/>
@@ -16116,7 +16808,7 @@
         <v>513</v>
       </c>
     </row>
-    <row r="160" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="160" ht="15" customHeight="1">
       <c r="A160" s="3" t="s">
         <v>840</v>
       </c>
@@ -16199,7 +16891,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="161" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" ht="15" customHeight="1">
       <c r="A161" s="3" t="s">
         <v>875</v>
       </c>
@@ -16282,7 +16974,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="162" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="162" ht="15" customHeight="1">
       <c r="A162" s="3" t="s">
         <v>570</v>
       </c>
@@ -16336,7 +17028,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="163" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="163" ht="15" customHeight="1">
       <c r="A163" s="3" t="s">
         <v>570</v>
       </c>
@@ -16387,7 +17079,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="164" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="164" ht="15" customHeight="1">
       <c r="A164" s="3" t="s">
         <v>570</v>
       </c>
@@ -16438,7 +17130,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="165" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="165" ht="15" customHeight="1">
       <c r="A165" s="3" t="s">
         <v>570</v>
       </c>
@@ -16492,7 +17184,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="166" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="166" ht="15" customHeight="1">
       <c r="A166" s="3" t="s">
         <v>570</v>
       </c>
@@ -16546,7 +17238,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="167" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="167" ht="15" customHeight="1">
       <c r="A167" s="3" t="s">
         <v>570</v>
       </c>
@@ -16600,7 +17292,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="168" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" ht="15" customHeight="1">
       <c r="A168" s="3" t="s">
         <v>570</v>
       </c>
@@ -16654,7 +17346,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="169" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="169" ht="15" customHeight="1">
       <c r="A169" s="3" t="s">
         <v>585</v>
       </c>
@@ -16702,7 +17394,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="170" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="170" ht="15" customHeight="1">
       <c r="A170" s="3" t="s">
         <v>587</v>
       </c>
@@ -16794,7 +17486,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="171" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="171" ht="15" customHeight="1">
       <c r="A171" s="3" t="s">
         <v>587</v>
       </c>
@@ -16892,7 +17584,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="172" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="172" ht="15" customHeight="1">
       <c r="A172" s="3" t="s">
         <v>587</v>
       </c>
@@ -16993,7 +17685,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="173" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="173" ht="15" customHeight="1">
       <c r="A173" s="3" t="s">
         <v>605</v>
       </c>
@@ -17052,7 +17744,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="174" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="174" ht="15" customHeight="1">
       <c r="A174" s="3" t="s">
         <v>609</v>
       </c>
@@ -17114,7 +17806,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="175" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="175" ht="15" customHeight="1">
       <c r="A175" s="3" t="s">
         <v>609</v>
       </c>
@@ -17176,7 +17868,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="176" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="176" ht="15" customHeight="1">
       <c r="A176" s="4" t="s">
         <v>852</v>
       </c>
@@ -17256,7 +17948,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="177" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="177" ht="15" customHeight="1">
       <c r="A177" s="4" t="s">
         <v>843</v>
       </c>
@@ -17300,7 +17992,7 @@
         <v>10.1016%2Fj.neubiorev.2008.05.023_Table1.tsv</v>
       </c>
     </row>
-    <row r="178" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="178" ht="15" customHeight="1">
       <c r="A178" s="4" t="s">
         <v>843</v>
       </c>
@@ -17344,7 +18036,7 @@
         <v>10.1016%2Fj.neubiorev.2008.05.023_Table2.tsv</v>
       </c>
     </row>
-    <row r="179" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="179" ht="15" customHeight="1">
       <c r="A179" s="3" t="s">
         <v>614</v>
       </c>
@@ -17365,7 +18057,6 @@
       </c>
       <c r="H179" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I179" s="1" t="str">
         <f t="shared" si="36"/>
@@ -17406,7 +18097,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="180" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="180" ht="15" customHeight="1">
       <c r="A180" s="3" t="s">
         <v>618</v>
       </c>
@@ -17430,7 +18121,6 @@
       </c>
       <c r="H180" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I180" s="1" t="str">
         <f t="shared" si="36"/>
@@ -17456,7 +18146,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="181" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="181" ht="15" customHeight="1">
       <c r="A181" s="3" t="s">
         <v>622</v>
       </c>
@@ -17530,7 +18220,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="182" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="182" ht="15" customHeight="1">
       <c r="A182" s="3" t="s">
         <v>622</v>
       </c>
@@ -17604,7 +18294,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="183" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="183" ht="15" customHeight="1">
       <c r="A183" s="4" t="s">
         <v>849</v>
       </c>
@@ -17625,7 +18315,6 @@
       </c>
       <c r="H183" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I183" s="1" t="str">
         <f t="shared" si="36"/>
@@ -17648,7 +18337,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="184" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="184" ht="15" customHeight="1">
       <c r="A184" s="3" t="s">
         <v>628</v>
       </c>
@@ -17669,7 +18358,6 @@
       </c>
       <c r="H184" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I184" s="1" t="str">
         <f t="shared" si="36"/>
@@ -17735,7 +18423,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="185" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="185" ht="15" customHeight="1">
       <c r="A185" s="3" t="s">
         <v>837</v>
       </c>
@@ -17757,7 +18445,6 @@
       </c>
       <c r="H185" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I185" s="1" t="str">
         <f t="shared" si="36"/>
@@ -17784,7 +18471,7 @@
       <c r="Z185" s="3"/>
       <c r="AF185" s="3"/>
     </row>
-    <row r="186" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="186" ht="15" customHeight="1">
       <c r="A186" s="3" t="s">
         <v>836</v>
       </c>
@@ -17806,7 +18493,6 @@
       </c>
       <c r="H186" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I186" s="1" t="str">
         <f t="shared" si="36"/>
@@ -17833,7 +18519,7 @@
       <c r="Z186" s="3"/>
       <c r="AF186" s="3"/>
     </row>
-    <row r="187" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="187" ht="15" customHeight="1">
       <c r="A187" s="3" t="s">
         <v>634</v>
       </c>
@@ -17855,7 +18541,6 @@
       </c>
       <c r="H187" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I187" s="1" t="str">
         <f t="shared" si="36"/>
@@ -17881,7 +18566,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="188" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="188" ht="15" customHeight="1">
       <c r="A188" s="3" t="s">
         <v>636</v>
       </c>
@@ -17964,7 +18649,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="189" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="189" ht="15" customHeight="1">
       <c r="A189" s="3" t="s">
         <v>639</v>
       </c>
@@ -18023,7 +18708,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="190" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="190" ht="15" customHeight="1">
       <c r="A190" s="4" t="s">
         <v>851</v>
       </c>
@@ -18041,7 +18726,6 @@
       </c>
       <c r="H190" s="1" t="str">
         <f t="shared" si="35"/>
-        <v/>
       </c>
       <c r="I190" s="1" t="str">
         <f t="shared" si="36"/>
@@ -18064,7 +18748,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="191" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="191" ht="15" customHeight="1">
       <c r="A191" s="3" t="s">
         <v>640</v>
       </c>
@@ -18123,7 +18807,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="192" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="192" ht="15" customHeight="1">
       <c r="A192" s="3" t="s">
         <v>642</v>
       </c>
@@ -18188,7 +18872,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="193" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="193" ht="15" customHeight="1">
       <c r="A193" s="3" t="s">
         <v>873</v>
       </c>
@@ -18237,7 +18921,7 @@
       <c r="AL193" s="3"/>
       <c r="AM193" s="3"/>
     </row>
-    <row r="194" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="194" ht="15" customHeight="1">
       <c r="A194" s="4" t="s">
         <v>856</v>
       </c>
@@ -18278,7 +18962,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="195" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="195" ht="15" customHeight="1">
       <c r="A195" s="3" t="s">
         <v>874</v>
       </c>
@@ -18360,7 +19044,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="196" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="196" ht="15" customHeight="1">
       <c r="A196" s="3" t="s">
         <v>874</v>
       </c>
@@ -18458,7 +19142,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="197" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="197" ht="15" customHeight="1">
       <c r="A197" s="3" t="s">
         <v>874</v>
       </c>
@@ -18540,7 +19224,7 @@
         <v>970</v>
       </c>
     </row>
-    <row r="198" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="198" ht="15" customHeight="1">
       <c r="A198" s="3" t="s">
         <v>874</v>
       </c>
@@ -18622,7 +19306,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="199" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="199" ht="15" customHeight="1">
       <c r="A199" s="3" t="s">
         <v>874</v>
       </c>
@@ -18704,7 +19388,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="200" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="200" ht="15" customHeight="1">
       <c r="A200" s="3" t="s">
         <v>841</v>
       </c>
@@ -18745,7 +19429,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="201" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="201" ht="15" customHeight="1">
       <c r="A201" s="3" t="s">
         <v>648</v>
       </c>
@@ -18835,7 +19519,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="202" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="202" ht="15" customHeight="1">
       <c r="A202" s="3" t="s">
         <v>872</v>
       </c>
@@ -18921,7 +19605,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="203" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="203" ht="15" customHeight="1">
       <c r="A203" s="3" t="s">
         <v>842</v>
       </c>
@@ -19001,7 +19685,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="204" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="204" ht="15" customHeight="1">
       <c r="A204" s="3" t="s">
         <v>653</v>
       </c>
@@ -19060,7 +19744,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="205" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="205" ht="15" customHeight="1">
       <c r="A205" s="3" t="s">
         <v>655</v>
       </c>
@@ -19113,7 +19797,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="206" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="206" ht="15" customHeight="1">
       <c r="A206" s="4" t="s">
         <v>844</v>
       </c>
@@ -19157,7 +19841,7 @@
         <v>10.1111%2Fbrv.12137_Table1.tsv</v>
       </c>
     </row>
-    <row r="207" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="207" ht="15" customHeight="1">
       <c r="A207" s="4" t="s">
         <v>1323</v>
       </c>
@@ -19181,7 +19865,6 @@
 _xlpm.commasBeforeAmp,IF(_xlpm.hasAmp,LEN(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"))-LEN(SUBSTITUTE(_xlfn.TEXTBEFORE(_xlpm.authors,"&amp;"),",","")),0),
 IF(NOT(_xlpm.hasAmp),"",IF(_xlpm.commasBeforeAmp&gt;2,"etal",TRIM(_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(_xlpm.authors,"&amp; "),","))))
 )</f>
-        <v/>
       </c>
       <c r="I207" s="1" t="str">
         <f t="shared" ref="I207" si="52">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A207, "("), ")")</f>
@@ -19215,7 +19898,7 @@
         <v>notfound</v>
       </c>
     </row>
-    <row r="208" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="208" ht="15" customHeight="1">
       <c r="A208" s="3" t="s">
         <v>657</v>
       </c>
@@ -19274,7 +19957,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="209" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="209" ht="15" customHeight="1">
       <c r="A209" s="3" t="s">
         <v>661</v>
       </c>
@@ -19318,7 +20001,7 @@
         <v>10.1006%2Fjhev.1999.0381_Table2.tsv</v>
       </c>
     </row>
-    <row r="210" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="210" ht="15" customHeight="1">
       <c r="A210" s="3" t="s">
         <v>662</v>
       </c>
@@ -19392,7 +20075,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="211" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="211" ht="15" customHeight="1">
       <c r="A211" s="3" t="s">
         <v>665</v>
       </c>
@@ -19466,7 +20149,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="212" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="212" ht="15" customHeight="1">
       <c r="A212" s="3" t="s">
         <v>668</v>
       </c>
@@ -19537,7 +20220,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="213" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="213" ht="15" customHeight="1">
       <c r="A213" s="3" t="s">
         <v>671</v>
       </c>
@@ -19581,7 +20264,7 @@
         <v>10.1242%2Fjeb.124826_TableS1.tsv</v>
       </c>
     </row>
-    <row r="214" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="214" ht="15" customHeight="1">
       <c r="A214" s="3" t="s">
         <v>673</v>
       </c>
@@ -19625,7 +20308,7 @@
         <v>10.1098%2Frsos.170846_TableS1.tsv</v>
       </c>
     </row>
-    <row r="215" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="215" ht="15" customHeight="1">
       <c r="A215" s="3" t="s">
         <v>674</v>
       </c>
@@ -19669,7 +20352,7 @@
         <v>10.1098%2Frspb.2019.2208_rspb20192208si002.tsv</v>
       </c>
     </row>
-    <row r="216" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="216" ht="15" customHeight="1">
       <c r="A216" s="3" t="s">
         <v>676</v>
       </c>
@@ -19731,7 +20414,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="217" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="217" ht="15" customHeight="1">
       <c r="A217" s="3" t="s">
         <v>676</v>
       </c>
@@ -19794,7 +20477,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="218" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="218" ht="15" customHeight="1">
       <c r="A218" s="3" t="s">
         <v>681</v>
       </c>
@@ -19872,7 +20555,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="219" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="219" ht="15" customHeight="1">
       <c r="A219" s="3" t="s">
         <v>684</v>
       </c>
@@ -19962,7 +20645,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="220" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="220" ht="15" customHeight="1">
       <c r="A220" s="3" t="s">
         <v>684</v>
       </c>
@@ -20055,7 +20738,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="221" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="221" ht="15" customHeight="1">
       <c r="A221" s="4" t="s">
         <v>853</v>
       </c>
@@ -20102,7 +20785,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="222" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="222" ht="15" customHeight="1">
       <c r="A222" s="4" t="s">
         <v>1320</v>
       </c>
@@ -20165,7 +20848,7 @@
         <v>1321</v>
       </c>
     </row>
-    <row r="223" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="223" ht="15" customHeight="1">
       <c r="A223" s="3" t="s">
         <v>692</v>
       </c>
@@ -20233,7 +20916,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="224" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="224" ht="15" customHeight="1">
       <c r="A224" s="3" t="s">
         <v>698</v>
       </c>
@@ -20319,7 +21002,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="225" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="225" ht="15" customHeight="1">
       <c r="A225" s="3" t="s">
         <v>698</v>
       </c>
@@ -20405,7 +21088,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="226" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="226" ht="15" customHeight="1">
       <c r="A226" s="3" t="s">
         <v>708</v>
       </c>
@@ -20476,7 +21159,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="227" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="227" ht="15" customHeight="1">
       <c r="A227" s="3" t="s">
         <v>708</v>
       </c>
@@ -20547,7 +21230,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="228" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="228" ht="15" customHeight="1">
       <c r="A228" s="3" t="s">
         <v>712</v>
       </c>
@@ -20618,7 +21301,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="229" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="229" ht="15" customHeight="1">
       <c r="A229" s="3" t="s">
         <v>1271</v>
       </c>
@@ -20673,7 +21356,7 @@
       <c r="AL229" s="3"/>
       <c r="AM229" s="3"/>
     </row>
-    <row r="230" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="230" ht="15" customHeight="1">
       <c r="A230" s="3" t="s">
         <v>1271</v>
       </c>
@@ -20744,7 +21427,7 @@
       <c r="AL230" s="3"/>
       <c r="AM230" s="3"/>
     </row>
-    <row r="231" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="231" ht="15" customHeight="1">
       <c r="A231" s="3" t="s">
         <v>1271</v>
       </c>
@@ -20815,7 +21498,7 @@
       <c r="AL231" s="3"/>
       <c r="AM231" s="3"/>
     </row>
-    <row r="232" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="232" ht="15" customHeight="1">
       <c r="A232" s="3" t="s">
         <v>1271</v>
       </c>
@@ -20886,7 +21569,7 @@
       <c r="AL232" s="3"/>
       <c r="AM232" s="3"/>
     </row>
-    <row r="233" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="233" ht="15" customHeight="1">
       <c r="A233" s="3" t="s">
         <v>1271</v>
       </c>
@@ -20957,7 +21640,7 @@
       <c r="AL233" s="3"/>
       <c r="AM233" s="3"/>
     </row>
-    <row r="234" spans="1:39" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="234" ht="15" customHeight